--- a/content/W01/SAT/answer-key/C2_W01_SAT_item_analysis_TRAINER.xlsx
+++ b/content/W01/SAT/answer-key/C2_W01_SAT_item_analysis_TRAINER.xlsx
@@ -505,7 +505,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BC39"/>
+  <dimension ref="A1:BF39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -636,13 +636,13 @@
         <v>4</v>
       </c>
       <c r="AN2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AO2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AP2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AQ2" t="n">
         <v>5</v>
@@ -657,13 +657,13 @@
         <v>5</v>
       </c>
       <c r="AU2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AX2" t="n">
         <v>6</v>
@@ -674,6 +674,15 @@
       <c r="AZ2" t="n">
         <v>6</v>
       </c>
+      <c r="BA2" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -848,90 +857,105 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
+          <t>[D]</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
           <t>[S]</t>
         </is>
       </c>
-      <c r="AJ3" t="inlineStr">
+      <c r="AK3" t="inlineStr">
         <is>
           <t>[S]</t>
         </is>
       </c>
-      <c r="AK3" t="inlineStr">
+      <c r="AL3" t="inlineStr">
         <is>
           <t>[D]</t>
         </is>
       </c>
-      <c r="AL3" t="inlineStr">
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>[S]</t>
+        </is>
+      </c>
+      <c r="AN3" t="inlineStr">
         <is>
           <t>[F]</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>[F]</t>
+        </is>
+      </c>
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>[F]</t>
+        </is>
+      </c>
+      <c r="AQ3" t="inlineStr">
+        <is>
+          <t>[S]</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>[F]</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>[F]</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr">
+        <is>
+          <t>[S]</t>
+        </is>
+      </c>
+      <c r="AU3" t="inlineStr">
         <is>
           <t>[D]</t>
         </is>
       </c>
-      <c r="AN3" t="inlineStr">
+      <c r="AV3" t="inlineStr">
+        <is>
+          <t>[F]</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>[D]</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
         <is>
           <t>[S]</t>
         </is>
       </c>
-      <c r="AO3" t="inlineStr">
+      <c r="AY3" t="inlineStr">
         <is>
           <t>[F]</t>
         </is>
       </c>
-      <c r="AP3" t="inlineStr">
-        <is>
-          <t>[F]</t>
-        </is>
-      </c>
-      <c r="AQ3" t="inlineStr">
+      <c r="AZ3" t="inlineStr">
         <is>
           <t>[S]</t>
         </is>
       </c>
-      <c r="AR3" t="inlineStr">
-        <is>
-          <t>[D]</t>
-        </is>
-      </c>
-      <c r="AS3" t="inlineStr">
-        <is>
-          <t>[F]</t>
-        </is>
-      </c>
-      <c r="AT3" t="inlineStr">
-        <is>
-          <t>[D]</t>
-        </is>
-      </c>
-      <c r="AU3" t="inlineStr">
+      <c r="BA3" t="inlineStr">
         <is>
           <t>[S]</t>
         </is>
       </c>
-      <c r="AV3" t="inlineStr">
-        <is>
-          <t>[F]</t>
-        </is>
-      </c>
-      <c r="AW3" t="inlineStr">
+      <c r="BB3" t="inlineStr">
         <is>
           <t>[S]</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>[S]</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>[S]</t>
-        </is>
-      </c>
-      <c r="AZ3" t="inlineStr">
+      <c r="BC3" t="inlineStr">
         <is>
           <t>[S]</t>
         </is>
@@ -1200,15 +1224,30 @@
       </c>
       <c r="BA4" s="4" t="inlineStr">
         <is>
+          <t>Q52</t>
+        </is>
+      </c>
+      <c r="BB4" s="4" t="inlineStr">
+        <is>
+          <t>Q53</t>
+        </is>
+      </c>
+      <c r="BC4" s="4" t="inlineStr">
+        <is>
+          <t>Q54</t>
+        </is>
+      </c>
+      <c r="BD4" s="4" t="inlineStr">
+        <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="BB4" s="4" t="inlineStr">
+      <c r="BE4" s="4" t="inlineStr">
         <is>
           <t>Answered</t>
         </is>
       </c>
-      <c r="BC4" s="4" t="inlineStr">
+      <c r="BF4" s="4" t="inlineStr">
         <is>
           <t>Band</t>
         </is>
@@ -1269,16 +1308,19 @@
       <c r="AX5" s="5" t="n"/>
       <c r="AY5" s="5" t="n"/>
       <c r="AZ5" s="5" t="n"/>
-      <c r="BA5">
-        <f>IF(COUNT(B5:AZ5)=0,"",SUM(B5:AZ5))</f>
-        <v/>
-      </c>
-      <c r="BB5">
-        <f>COUNT(B5:AZ5)</f>
-        <v/>
-      </c>
-      <c r="BC5">
-        <f>IF(OR(BA5="",COUNT($BA$5:$BA$39)&lt;3),"",IF(RANK(BA5,$BA$5:$BA$39,0)&lt;=ROUND(COUNT($BA$5:$BA$39)/3,0),"top",IF(RANK(BA5,$BA$5:$BA$39,1)&lt;=ROUND(COUNT($BA$5:$BA$39)/3,0),"bottom","middle")))</f>
+      <c r="BA5" s="5" t="n"/>
+      <c r="BB5" s="5" t="n"/>
+      <c r="BC5" s="5" t="n"/>
+      <c r="BD5">
+        <f>IF(COUNT(B5:BC5)=0,"",SUM(B5:BC5))</f>
+        <v/>
+      </c>
+      <c r="BE5">
+        <f>COUNT(B5:BC5)</f>
+        <v/>
+      </c>
+      <c r="BF5">
+        <f>IF(OR(BD5="",COUNT($BD$5:$BD$39)&lt;3),"",IF(RANK(BD5,$BD$5:$BD$39,0)&lt;=ROUND(COUNT($BD$5:$BD$39)/3,0),"top",IF(RANK(BD5,$BD$5:$BD$39,1)&lt;=ROUND(COUNT($BD$5:$BD$39)/3,0),"bottom","middle")))</f>
         <v/>
       </c>
     </row>
@@ -1337,16 +1379,19 @@
       <c r="AX6" s="5" t="n"/>
       <c r="AY6" s="5" t="n"/>
       <c r="AZ6" s="5" t="n"/>
-      <c r="BA6">
-        <f>IF(COUNT(B6:AZ6)=0,"",SUM(B6:AZ6))</f>
-        <v/>
-      </c>
-      <c r="BB6">
-        <f>COUNT(B6:AZ6)</f>
-        <v/>
-      </c>
-      <c r="BC6">
-        <f>IF(OR(BA6="",COUNT($BA$5:$BA$39)&lt;3),"",IF(RANK(BA6,$BA$5:$BA$39,0)&lt;=ROUND(COUNT($BA$5:$BA$39)/3,0),"top",IF(RANK(BA6,$BA$5:$BA$39,1)&lt;=ROUND(COUNT($BA$5:$BA$39)/3,0),"bottom","middle")))</f>
+      <c r="BA6" s="5" t="n"/>
+      <c r="BB6" s="5" t="n"/>
+      <c r="BC6" s="5" t="n"/>
+      <c r="BD6">
+        <f>IF(COUNT(B6:BC6)=0,"",SUM(B6:BC6))</f>
+        <v/>
+      </c>
+      <c r="BE6">
+        <f>COUNT(B6:BC6)</f>
+        <v/>
+      </c>
+      <c r="BF6">
+        <f>IF(OR(BD6="",COUNT($BD$5:$BD$39)&lt;3),"",IF(RANK(BD6,$BD$5:$BD$39,0)&lt;=ROUND(COUNT($BD$5:$BD$39)/3,0),"top",IF(RANK(BD6,$BD$5:$BD$39,1)&lt;=ROUND(COUNT($BD$5:$BD$39)/3,0),"bottom","middle")))</f>
         <v/>
       </c>
     </row>
@@ -1405,16 +1450,19 @@
       <c r="AX7" s="5" t="n"/>
       <c r="AY7" s="5" t="n"/>
       <c r="AZ7" s="5" t="n"/>
-      <c r="BA7">
-        <f>IF(COUNT(B7:AZ7)=0,"",SUM(B7:AZ7))</f>
-        <v/>
-      </c>
-      <c r="BB7">
-        <f>COUNT(B7:AZ7)</f>
-        <v/>
-      </c>
-      <c r="BC7">
-        <f>IF(OR(BA7="",COUNT($BA$5:$BA$39)&lt;3),"",IF(RANK(BA7,$BA$5:$BA$39,0)&lt;=ROUND(COUNT($BA$5:$BA$39)/3,0),"top",IF(RANK(BA7,$BA$5:$BA$39,1)&lt;=ROUND(COUNT($BA$5:$BA$39)/3,0),"bottom","middle")))</f>
+      <c r="BA7" s="5" t="n"/>
+      <c r="BB7" s="5" t="n"/>
+      <c r="BC7" s="5" t="n"/>
+      <c r="BD7">
+        <f>IF(COUNT(B7:BC7)=0,"",SUM(B7:BC7))</f>
+        <v/>
+      </c>
+      <c r="BE7">
+        <f>COUNT(B7:BC7)</f>
+        <v/>
+      </c>
+      <c r="BF7">
+        <f>IF(OR(BD7="",COUNT($BD$5:$BD$39)&lt;3),"",IF(RANK(BD7,$BD$5:$BD$39,0)&lt;=ROUND(COUNT($BD$5:$BD$39)/3,0),"top",IF(RANK(BD7,$BD$5:$BD$39,1)&lt;=ROUND(COUNT($BD$5:$BD$39)/3,0),"bottom","middle")))</f>
         <v/>
       </c>
     </row>
@@ -1473,16 +1521,19 @@
       <c r="AX8" s="5" t="n"/>
       <c r="AY8" s="5" t="n"/>
       <c r="AZ8" s="5" t="n"/>
-      <c r="BA8">
-        <f>IF(COUNT(B8:AZ8)=0,"",SUM(B8:AZ8))</f>
-        <v/>
-      </c>
-      <c r="BB8">
-        <f>COUNT(B8:AZ8)</f>
-        <v/>
-      </c>
-      <c r="BC8">
-        <f>IF(OR(BA8="",COUNT($BA$5:$BA$39)&lt;3),"",IF(RANK(BA8,$BA$5:$BA$39,0)&lt;=ROUND(COUNT($BA$5:$BA$39)/3,0),"top",IF(RANK(BA8,$BA$5:$BA$39,1)&lt;=ROUND(COUNT($BA$5:$BA$39)/3,0),"bottom","middle")))</f>
+      <c r="BA8" s="5" t="n"/>
+      <c r="BB8" s="5" t="n"/>
+      <c r="BC8" s="5" t="n"/>
+      <c r="BD8">
+        <f>IF(COUNT(B8:BC8)=0,"",SUM(B8:BC8))</f>
+        <v/>
+      </c>
+      <c r="BE8">
+        <f>COUNT(B8:BC8)</f>
+        <v/>
+      </c>
+      <c r="BF8">
+        <f>IF(OR(BD8="",COUNT($BD$5:$BD$39)&lt;3),"",IF(RANK(BD8,$BD$5:$BD$39,0)&lt;=ROUND(COUNT($BD$5:$BD$39)/3,0),"top",IF(RANK(BD8,$BD$5:$BD$39,1)&lt;=ROUND(COUNT($BD$5:$BD$39)/3,0),"bottom","middle")))</f>
         <v/>
       </c>
     </row>
@@ -1541,16 +1592,19 @@
       <c r="AX9" s="5" t="n"/>
       <c r="AY9" s="5" t="n"/>
       <c r="AZ9" s="5" t="n"/>
-      <c r="BA9">
-        <f>IF(COUNT(B9:AZ9)=0,"",SUM(B9:AZ9))</f>
-        <v/>
-      </c>
-      <c r="BB9">
-        <f>COUNT(B9:AZ9)</f>
-        <v/>
-      </c>
-      <c r="BC9">
-        <f>IF(OR(BA9="",COUNT($BA$5:$BA$39)&lt;3),"",IF(RANK(BA9,$BA$5:$BA$39,0)&lt;=ROUND(COUNT($BA$5:$BA$39)/3,0),"top",IF(RANK(BA9,$BA$5:$BA$39,1)&lt;=ROUND(COUNT($BA$5:$BA$39)/3,0),"bottom","middle")))</f>
+      <c r="BA9" s="5" t="n"/>
+      <c r="BB9" s="5" t="n"/>
+      <c r="BC9" s="5" t="n"/>
+      <c r="BD9">
+        <f>IF(COUNT(B9:BC9)=0,"",SUM(B9:BC9))</f>
+        <v/>
+      </c>
+      <c r="BE9">
+        <f>COUNT(B9:BC9)</f>
+        <v/>
+      </c>
+      <c r="BF9">
+        <f>IF(OR(BD9="",COUNT($BD$5:$BD$39)&lt;3),"",IF(RANK(BD9,$BD$5:$BD$39,0)&lt;=ROUND(COUNT($BD$5:$BD$39)/3,0),"top",IF(RANK(BD9,$BD$5:$BD$39,1)&lt;=ROUND(COUNT($BD$5:$BD$39)/3,0),"bottom","middle")))</f>
         <v/>
       </c>
     </row>
@@ -1609,16 +1663,19 @@
       <c r="AX10" s="5" t="n"/>
       <c r="AY10" s="5" t="n"/>
       <c r="AZ10" s="5" t="n"/>
-      <c r="BA10">
-        <f>IF(COUNT(B10:AZ10)=0,"",SUM(B10:AZ10))</f>
-        <v/>
-      </c>
-      <c r="BB10">
-        <f>COUNT(B10:AZ10)</f>
-        <v/>
-      </c>
-      <c r="BC10">
-        <f>IF(OR(BA10="",COUNT($BA$5:$BA$39)&lt;3),"",IF(RANK(BA10,$BA$5:$BA$39,0)&lt;=ROUND(COUNT($BA$5:$BA$39)/3,0),"top",IF(RANK(BA10,$BA$5:$BA$39,1)&lt;=ROUND(COUNT($BA$5:$BA$39)/3,0),"bottom","middle")))</f>
+      <c r="BA10" s="5" t="n"/>
+      <c r="BB10" s="5" t="n"/>
+      <c r="BC10" s="5" t="n"/>
+      <c r="BD10">
+        <f>IF(COUNT(B10:BC10)=0,"",SUM(B10:BC10))</f>
+        <v/>
+      </c>
+      <c r="BE10">
+        <f>COUNT(B10:BC10)</f>
+        <v/>
+      </c>
+      <c r="BF10">
+        <f>IF(OR(BD10="",COUNT($BD$5:$BD$39)&lt;3),"",IF(RANK(BD10,$BD$5:$BD$39,0)&lt;=ROUND(COUNT($BD$5:$BD$39)/3,0),"top",IF(RANK(BD10,$BD$5:$BD$39,1)&lt;=ROUND(COUNT($BD$5:$BD$39)/3,0),"bottom","middle")))</f>
         <v/>
       </c>
     </row>
@@ -1677,16 +1734,19 @@
       <c r="AX11" s="5" t="n"/>
       <c r="AY11" s="5" t="n"/>
       <c r="AZ11" s="5" t="n"/>
-      <c r="BA11">
-        <f>IF(COUNT(B11:AZ11)=0,"",SUM(B11:AZ11))</f>
-        <v/>
-      </c>
-      <c r="BB11">
-        <f>COUNT(B11:AZ11)</f>
-        <v/>
-      </c>
-      <c r="BC11">
-        <f>IF(OR(BA11="",COUNT($BA$5:$BA$39)&lt;3),"",IF(RANK(BA11,$BA$5:$BA$39,0)&lt;=ROUND(COUNT($BA$5:$BA$39)/3,0),"top",IF(RANK(BA11,$BA$5:$BA$39,1)&lt;=ROUND(COUNT($BA$5:$BA$39)/3,0),"bottom","middle")))</f>
+      <c r="BA11" s="5" t="n"/>
+      <c r="BB11" s="5" t="n"/>
+      <c r="BC11" s="5" t="n"/>
+      <c r="BD11">
+        <f>IF(COUNT(B11:BC11)=0,"",SUM(B11:BC11))</f>
+        <v/>
+      </c>
+      <c r="BE11">
+        <f>COUNT(B11:BC11)</f>
+        <v/>
+      </c>
+      <c r="BF11">
+        <f>IF(OR(BD11="",COUNT($BD$5:$BD$39)&lt;3),"",IF(RANK(BD11,$BD$5:$BD$39,0)&lt;=ROUND(COUNT($BD$5:$BD$39)/3,0),"top",IF(RANK(BD11,$BD$5:$BD$39,1)&lt;=ROUND(COUNT($BD$5:$BD$39)/3,0),"bottom","middle")))</f>
         <v/>
       </c>
     </row>
@@ -1745,16 +1805,19 @@
       <c r="AX12" s="5" t="n"/>
       <c r="AY12" s="5" t="n"/>
       <c r="AZ12" s="5" t="n"/>
-      <c r="BA12">
-        <f>IF(COUNT(B12:AZ12)=0,"",SUM(B12:AZ12))</f>
-        <v/>
-      </c>
-      <c r="BB12">
-        <f>COUNT(B12:AZ12)</f>
-        <v/>
-      </c>
-      <c r="BC12">
-        <f>IF(OR(BA12="",COUNT($BA$5:$BA$39)&lt;3),"",IF(RANK(BA12,$BA$5:$BA$39,0)&lt;=ROUND(COUNT($BA$5:$BA$39)/3,0),"top",IF(RANK(BA12,$BA$5:$BA$39,1)&lt;=ROUND(COUNT($BA$5:$BA$39)/3,0),"bottom","middle")))</f>
+      <c r="BA12" s="5" t="n"/>
+      <c r="BB12" s="5" t="n"/>
+      <c r="BC12" s="5" t="n"/>
+      <c r="BD12">
+        <f>IF(COUNT(B12:BC12)=0,"",SUM(B12:BC12))</f>
+        <v/>
+      </c>
+      <c r="BE12">
+        <f>COUNT(B12:BC12)</f>
+        <v/>
+      </c>
+      <c r="BF12">
+        <f>IF(OR(BD12="",COUNT($BD$5:$BD$39)&lt;3),"",IF(RANK(BD12,$BD$5:$BD$39,0)&lt;=ROUND(COUNT($BD$5:$BD$39)/3,0),"top",IF(RANK(BD12,$BD$5:$BD$39,1)&lt;=ROUND(COUNT($BD$5:$BD$39)/3,0),"bottom","middle")))</f>
         <v/>
       </c>
     </row>
@@ -1813,16 +1876,19 @@
       <c r="AX13" s="5" t="n"/>
       <c r="AY13" s="5" t="n"/>
       <c r="AZ13" s="5" t="n"/>
-      <c r="BA13">
-        <f>IF(COUNT(B13:AZ13)=0,"",SUM(B13:AZ13))</f>
-        <v/>
-      </c>
-      <c r="BB13">
-        <f>COUNT(B13:AZ13)</f>
-        <v/>
-      </c>
-      <c r="BC13">
-        <f>IF(OR(BA13="",COUNT($BA$5:$BA$39)&lt;3),"",IF(RANK(BA13,$BA$5:$BA$39,0)&lt;=ROUND(COUNT($BA$5:$BA$39)/3,0),"top",IF(RANK(BA13,$BA$5:$BA$39,1)&lt;=ROUND(COUNT($BA$5:$BA$39)/3,0),"bottom","middle")))</f>
+      <c r="BA13" s="5" t="n"/>
+      <c r="BB13" s="5" t="n"/>
+      <c r="BC13" s="5" t="n"/>
+      <c r="BD13">
+        <f>IF(COUNT(B13:BC13)=0,"",SUM(B13:BC13))</f>
+        <v/>
+      </c>
+      <c r="BE13">
+        <f>COUNT(B13:BC13)</f>
+        <v/>
+      </c>
+      <c r="BF13">
+        <f>IF(OR(BD13="",COUNT($BD$5:$BD$39)&lt;3),"",IF(RANK(BD13,$BD$5:$BD$39,0)&lt;=ROUND(COUNT($BD$5:$BD$39)/3,0),"top",IF(RANK(BD13,$BD$5:$BD$39,1)&lt;=ROUND(COUNT($BD$5:$BD$39)/3,0),"bottom","middle")))</f>
         <v/>
       </c>
     </row>
@@ -1881,16 +1947,19 @@
       <c r="AX14" s="5" t="n"/>
       <c r="AY14" s="5" t="n"/>
       <c r="AZ14" s="5" t="n"/>
-      <c r="BA14">
-        <f>IF(COUNT(B14:AZ14)=0,"",SUM(B14:AZ14))</f>
-        <v/>
-      </c>
-      <c r="BB14">
-        <f>COUNT(B14:AZ14)</f>
-        <v/>
-      </c>
-      <c r="BC14">
-        <f>IF(OR(BA14="",COUNT($BA$5:$BA$39)&lt;3),"",IF(RANK(BA14,$BA$5:$BA$39,0)&lt;=ROUND(COUNT($BA$5:$BA$39)/3,0),"top",IF(RANK(BA14,$BA$5:$BA$39,1)&lt;=ROUND(COUNT($BA$5:$BA$39)/3,0),"bottom","middle")))</f>
+      <c r="BA14" s="5" t="n"/>
+      <c r="BB14" s="5" t="n"/>
+      <c r="BC14" s="5" t="n"/>
+      <c r="BD14">
+        <f>IF(COUNT(B14:BC14)=0,"",SUM(B14:BC14))</f>
+        <v/>
+      </c>
+      <c r="BE14">
+        <f>COUNT(B14:BC14)</f>
+        <v/>
+      </c>
+      <c r="BF14">
+        <f>IF(OR(BD14="",COUNT($BD$5:$BD$39)&lt;3),"",IF(RANK(BD14,$BD$5:$BD$39,0)&lt;=ROUND(COUNT($BD$5:$BD$39)/3,0),"top",IF(RANK(BD14,$BD$5:$BD$39,1)&lt;=ROUND(COUNT($BD$5:$BD$39)/3,0),"bottom","middle")))</f>
         <v/>
       </c>
     </row>
@@ -1949,16 +2018,19 @@
       <c r="AX15" s="5" t="n"/>
       <c r="AY15" s="5" t="n"/>
       <c r="AZ15" s="5" t="n"/>
-      <c r="BA15">
-        <f>IF(COUNT(B15:AZ15)=0,"",SUM(B15:AZ15))</f>
-        <v/>
-      </c>
-      <c r="BB15">
-        <f>COUNT(B15:AZ15)</f>
-        <v/>
-      </c>
-      <c r="BC15">
-        <f>IF(OR(BA15="",COUNT($BA$5:$BA$39)&lt;3),"",IF(RANK(BA15,$BA$5:$BA$39,0)&lt;=ROUND(COUNT($BA$5:$BA$39)/3,0),"top",IF(RANK(BA15,$BA$5:$BA$39,1)&lt;=ROUND(COUNT($BA$5:$BA$39)/3,0),"bottom","middle")))</f>
+      <c r="BA15" s="5" t="n"/>
+      <c r="BB15" s="5" t="n"/>
+      <c r="BC15" s="5" t="n"/>
+      <c r="BD15">
+        <f>IF(COUNT(B15:BC15)=0,"",SUM(B15:BC15))</f>
+        <v/>
+      </c>
+      <c r="BE15">
+        <f>COUNT(B15:BC15)</f>
+        <v/>
+      </c>
+      <c r="BF15">
+        <f>IF(OR(BD15="",COUNT($BD$5:$BD$39)&lt;3),"",IF(RANK(BD15,$BD$5:$BD$39,0)&lt;=ROUND(COUNT($BD$5:$BD$39)/3,0),"top",IF(RANK(BD15,$BD$5:$BD$39,1)&lt;=ROUND(COUNT($BD$5:$BD$39)/3,0),"bottom","middle")))</f>
         <v/>
       </c>
     </row>
@@ -2017,16 +2089,19 @@
       <c r="AX16" s="5" t="n"/>
       <c r="AY16" s="5" t="n"/>
       <c r="AZ16" s="5" t="n"/>
-      <c r="BA16">
-        <f>IF(COUNT(B16:AZ16)=0,"",SUM(B16:AZ16))</f>
-        <v/>
-      </c>
-      <c r="BB16">
-        <f>COUNT(B16:AZ16)</f>
-        <v/>
-      </c>
-      <c r="BC16">
-        <f>IF(OR(BA16="",COUNT($BA$5:$BA$39)&lt;3),"",IF(RANK(BA16,$BA$5:$BA$39,0)&lt;=ROUND(COUNT($BA$5:$BA$39)/3,0),"top",IF(RANK(BA16,$BA$5:$BA$39,1)&lt;=ROUND(COUNT($BA$5:$BA$39)/3,0),"bottom","middle")))</f>
+      <c r="BA16" s="5" t="n"/>
+      <c r="BB16" s="5" t="n"/>
+      <c r="BC16" s="5" t="n"/>
+      <c r="BD16">
+        <f>IF(COUNT(B16:BC16)=0,"",SUM(B16:BC16))</f>
+        <v/>
+      </c>
+      <c r="BE16">
+        <f>COUNT(B16:BC16)</f>
+        <v/>
+      </c>
+      <c r="BF16">
+        <f>IF(OR(BD16="",COUNT($BD$5:$BD$39)&lt;3),"",IF(RANK(BD16,$BD$5:$BD$39,0)&lt;=ROUND(COUNT($BD$5:$BD$39)/3,0),"top",IF(RANK(BD16,$BD$5:$BD$39,1)&lt;=ROUND(COUNT($BD$5:$BD$39)/3,0),"bottom","middle")))</f>
         <v/>
       </c>
     </row>
@@ -2085,16 +2160,19 @@
       <c r="AX17" s="5" t="n"/>
       <c r="AY17" s="5" t="n"/>
       <c r="AZ17" s="5" t="n"/>
-      <c r="BA17">
-        <f>IF(COUNT(B17:AZ17)=0,"",SUM(B17:AZ17))</f>
-        <v/>
-      </c>
-      <c r="BB17">
-        <f>COUNT(B17:AZ17)</f>
-        <v/>
-      </c>
-      <c r="BC17">
-        <f>IF(OR(BA17="",COUNT($BA$5:$BA$39)&lt;3),"",IF(RANK(BA17,$BA$5:$BA$39,0)&lt;=ROUND(COUNT($BA$5:$BA$39)/3,0),"top",IF(RANK(BA17,$BA$5:$BA$39,1)&lt;=ROUND(COUNT($BA$5:$BA$39)/3,0),"bottom","middle")))</f>
+      <c r="BA17" s="5" t="n"/>
+      <c r="BB17" s="5" t="n"/>
+      <c r="BC17" s="5" t="n"/>
+      <c r="BD17">
+        <f>IF(COUNT(B17:BC17)=0,"",SUM(B17:BC17))</f>
+        <v/>
+      </c>
+      <c r="BE17">
+        <f>COUNT(B17:BC17)</f>
+        <v/>
+      </c>
+      <c r="BF17">
+        <f>IF(OR(BD17="",COUNT($BD$5:$BD$39)&lt;3),"",IF(RANK(BD17,$BD$5:$BD$39,0)&lt;=ROUND(COUNT($BD$5:$BD$39)/3,0),"top",IF(RANK(BD17,$BD$5:$BD$39,1)&lt;=ROUND(COUNT($BD$5:$BD$39)/3,0),"bottom","middle")))</f>
         <v/>
       </c>
     </row>
@@ -2153,16 +2231,19 @@
       <c r="AX18" s="5" t="n"/>
       <c r="AY18" s="5" t="n"/>
       <c r="AZ18" s="5" t="n"/>
-      <c r="BA18">
-        <f>IF(COUNT(B18:AZ18)=0,"",SUM(B18:AZ18))</f>
-        <v/>
-      </c>
-      <c r="BB18">
-        <f>COUNT(B18:AZ18)</f>
-        <v/>
-      </c>
-      <c r="BC18">
-        <f>IF(OR(BA18="",COUNT($BA$5:$BA$39)&lt;3),"",IF(RANK(BA18,$BA$5:$BA$39,0)&lt;=ROUND(COUNT($BA$5:$BA$39)/3,0),"top",IF(RANK(BA18,$BA$5:$BA$39,1)&lt;=ROUND(COUNT($BA$5:$BA$39)/3,0),"bottom","middle")))</f>
+      <c r="BA18" s="5" t="n"/>
+      <c r="BB18" s="5" t="n"/>
+      <c r="BC18" s="5" t="n"/>
+      <c r="BD18">
+        <f>IF(COUNT(B18:BC18)=0,"",SUM(B18:BC18))</f>
+        <v/>
+      </c>
+      <c r="BE18">
+        <f>COUNT(B18:BC18)</f>
+        <v/>
+      </c>
+      <c r="BF18">
+        <f>IF(OR(BD18="",COUNT($BD$5:$BD$39)&lt;3),"",IF(RANK(BD18,$BD$5:$BD$39,0)&lt;=ROUND(COUNT($BD$5:$BD$39)/3,0),"top",IF(RANK(BD18,$BD$5:$BD$39,1)&lt;=ROUND(COUNT($BD$5:$BD$39)/3,0),"bottom","middle")))</f>
         <v/>
       </c>
     </row>
@@ -2221,16 +2302,19 @@
       <c r="AX19" s="5" t="n"/>
       <c r="AY19" s="5" t="n"/>
       <c r="AZ19" s="5" t="n"/>
-      <c r="BA19">
-        <f>IF(COUNT(B19:AZ19)=0,"",SUM(B19:AZ19))</f>
-        <v/>
-      </c>
-      <c r="BB19">
-        <f>COUNT(B19:AZ19)</f>
-        <v/>
-      </c>
-      <c r="BC19">
-        <f>IF(OR(BA19="",COUNT($BA$5:$BA$39)&lt;3),"",IF(RANK(BA19,$BA$5:$BA$39,0)&lt;=ROUND(COUNT($BA$5:$BA$39)/3,0),"top",IF(RANK(BA19,$BA$5:$BA$39,1)&lt;=ROUND(COUNT($BA$5:$BA$39)/3,0),"bottom","middle")))</f>
+      <c r="BA19" s="5" t="n"/>
+      <c r="BB19" s="5" t="n"/>
+      <c r="BC19" s="5" t="n"/>
+      <c r="BD19">
+        <f>IF(COUNT(B19:BC19)=0,"",SUM(B19:BC19))</f>
+        <v/>
+      </c>
+      <c r="BE19">
+        <f>COUNT(B19:BC19)</f>
+        <v/>
+      </c>
+      <c r="BF19">
+        <f>IF(OR(BD19="",COUNT($BD$5:$BD$39)&lt;3),"",IF(RANK(BD19,$BD$5:$BD$39,0)&lt;=ROUND(COUNT($BD$5:$BD$39)/3,0),"top",IF(RANK(BD19,$BD$5:$BD$39,1)&lt;=ROUND(COUNT($BD$5:$BD$39)/3,0),"bottom","middle")))</f>
         <v/>
       </c>
     </row>
@@ -2289,16 +2373,19 @@
       <c r="AX20" s="5" t="n"/>
       <c r="AY20" s="5" t="n"/>
       <c r="AZ20" s="5" t="n"/>
-      <c r="BA20">
-        <f>IF(COUNT(B20:AZ20)=0,"",SUM(B20:AZ20))</f>
-        <v/>
-      </c>
-      <c r="BB20">
-        <f>COUNT(B20:AZ20)</f>
-        <v/>
-      </c>
-      <c r="BC20">
-        <f>IF(OR(BA20="",COUNT($BA$5:$BA$39)&lt;3),"",IF(RANK(BA20,$BA$5:$BA$39,0)&lt;=ROUND(COUNT($BA$5:$BA$39)/3,0),"top",IF(RANK(BA20,$BA$5:$BA$39,1)&lt;=ROUND(COUNT($BA$5:$BA$39)/3,0),"bottom","middle")))</f>
+      <c r="BA20" s="5" t="n"/>
+      <c r="BB20" s="5" t="n"/>
+      <c r="BC20" s="5" t="n"/>
+      <c r="BD20">
+        <f>IF(COUNT(B20:BC20)=0,"",SUM(B20:BC20))</f>
+        <v/>
+      </c>
+      <c r="BE20">
+        <f>COUNT(B20:BC20)</f>
+        <v/>
+      </c>
+      <c r="BF20">
+        <f>IF(OR(BD20="",COUNT($BD$5:$BD$39)&lt;3),"",IF(RANK(BD20,$BD$5:$BD$39,0)&lt;=ROUND(COUNT($BD$5:$BD$39)/3,0),"top",IF(RANK(BD20,$BD$5:$BD$39,1)&lt;=ROUND(COUNT($BD$5:$BD$39)/3,0),"bottom","middle")))</f>
         <v/>
       </c>
     </row>
@@ -2357,16 +2444,19 @@
       <c r="AX21" s="5" t="n"/>
       <c r="AY21" s="5" t="n"/>
       <c r="AZ21" s="5" t="n"/>
-      <c r="BA21">
-        <f>IF(COUNT(B21:AZ21)=0,"",SUM(B21:AZ21))</f>
-        <v/>
-      </c>
-      <c r="BB21">
-        <f>COUNT(B21:AZ21)</f>
-        <v/>
-      </c>
-      <c r="BC21">
-        <f>IF(OR(BA21="",COUNT($BA$5:$BA$39)&lt;3),"",IF(RANK(BA21,$BA$5:$BA$39,0)&lt;=ROUND(COUNT($BA$5:$BA$39)/3,0),"top",IF(RANK(BA21,$BA$5:$BA$39,1)&lt;=ROUND(COUNT($BA$5:$BA$39)/3,0),"bottom","middle")))</f>
+      <c r="BA21" s="5" t="n"/>
+      <c r="BB21" s="5" t="n"/>
+      <c r="BC21" s="5" t="n"/>
+      <c r="BD21">
+        <f>IF(COUNT(B21:BC21)=0,"",SUM(B21:BC21))</f>
+        <v/>
+      </c>
+      <c r="BE21">
+        <f>COUNT(B21:BC21)</f>
+        <v/>
+      </c>
+      <c r="BF21">
+        <f>IF(OR(BD21="",COUNT($BD$5:$BD$39)&lt;3),"",IF(RANK(BD21,$BD$5:$BD$39,0)&lt;=ROUND(COUNT($BD$5:$BD$39)/3,0),"top",IF(RANK(BD21,$BD$5:$BD$39,1)&lt;=ROUND(COUNT($BD$5:$BD$39)/3,0),"bottom","middle")))</f>
         <v/>
       </c>
     </row>
@@ -2425,16 +2515,19 @@
       <c r="AX22" s="5" t="n"/>
       <c r="AY22" s="5" t="n"/>
       <c r="AZ22" s="5" t="n"/>
-      <c r="BA22">
-        <f>IF(COUNT(B22:AZ22)=0,"",SUM(B22:AZ22))</f>
-        <v/>
-      </c>
-      <c r="BB22">
-        <f>COUNT(B22:AZ22)</f>
-        <v/>
-      </c>
-      <c r="BC22">
-        <f>IF(OR(BA22="",COUNT($BA$5:$BA$39)&lt;3),"",IF(RANK(BA22,$BA$5:$BA$39,0)&lt;=ROUND(COUNT($BA$5:$BA$39)/3,0),"top",IF(RANK(BA22,$BA$5:$BA$39,1)&lt;=ROUND(COUNT($BA$5:$BA$39)/3,0),"bottom","middle")))</f>
+      <c r="BA22" s="5" t="n"/>
+      <c r="BB22" s="5" t="n"/>
+      <c r="BC22" s="5" t="n"/>
+      <c r="BD22">
+        <f>IF(COUNT(B22:BC22)=0,"",SUM(B22:BC22))</f>
+        <v/>
+      </c>
+      <c r="BE22">
+        <f>COUNT(B22:BC22)</f>
+        <v/>
+      </c>
+      <c r="BF22">
+        <f>IF(OR(BD22="",COUNT($BD$5:$BD$39)&lt;3),"",IF(RANK(BD22,$BD$5:$BD$39,0)&lt;=ROUND(COUNT($BD$5:$BD$39)/3,0),"top",IF(RANK(BD22,$BD$5:$BD$39,1)&lt;=ROUND(COUNT($BD$5:$BD$39)/3,0),"bottom","middle")))</f>
         <v/>
       </c>
     </row>
@@ -2493,16 +2586,19 @@
       <c r="AX23" s="5" t="n"/>
       <c r="AY23" s="5" t="n"/>
       <c r="AZ23" s="5" t="n"/>
-      <c r="BA23">
-        <f>IF(COUNT(B23:AZ23)=0,"",SUM(B23:AZ23))</f>
-        <v/>
-      </c>
-      <c r="BB23">
-        <f>COUNT(B23:AZ23)</f>
-        <v/>
-      </c>
-      <c r="BC23">
-        <f>IF(OR(BA23="",COUNT($BA$5:$BA$39)&lt;3),"",IF(RANK(BA23,$BA$5:$BA$39,0)&lt;=ROUND(COUNT($BA$5:$BA$39)/3,0),"top",IF(RANK(BA23,$BA$5:$BA$39,1)&lt;=ROUND(COUNT($BA$5:$BA$39)/3,0),"bottom","middle")))</f>
+      <c r="BA23" s="5" t="n"/>
+      <c r="BB23" s="5" t="n"/>
+      <c r="BC23" s="5" t="n"/>
+      <c r="BD23">
+        <f>IF(COUNT(B23:BC23)=0,"",SUM(B23:BC23))</f>
+        <v/>
+      </c>
+      <c r="BE23">
+        <f>COUNT(B23:BC23)</f>
+        <v/>
+      </c>
+      <c r="BF23">
+        <f>IF(OR(BD23="",COUNT($BD$5:$BD$39)&lt;3),"",IF(RANK(BD23,$BD$5:$BD$39,0)&lt;=ROUND(COUNT($BD$5:$BD$39)/3,0),"top",IF(RANK(BD23,$BD$5:$BD$39,1)&lt;=ROUND(COUNT($BD$5:$BD$39)/3,0),"bottom","middle")))</f>
         <v/>
       </c>
     </row>
@@ -2561,16 +2657,19 @@
       <c r="AX24" s="5" t="n"/>
       <c r="AY24" s="5" t="n"/>
       <c r="AZ24" s="5" t="n"/>
-      <c r="BA24">
-        <f>IF(COUNT(B24:AZ24)=0,"",SUM(B24:AZ24))</f>
-        <v/>
-      </c>
-      <c r="BB24">
-        <f>COUNT(B24:AZ24)</f>
-        <v/>
-      </c>
-      <c r="BC24">
-        <f>IF(OR(BA24="",COUNT($BA$5:$BA$39)&lt;3),"",IF(RANK(BA24,$BA$5:$BA$39,0)&lt;=ROUND(COUNT($BA$5:$BA$39)/3,0),"top",IF(RANK(BA24,$BA$5:$BA$39,1)&lt;=ROUND(COUNT($BA$5:$BA$39)/3,0),"bottom","middle")))</f>
+      <c r="BA24" s="5" t="n"/>
+      <c r="BB24" s="5" t="n"/>
+      <c r="BC24" s="5" t="n"/>
+      <c r="BD24">
+        <f>IF(COUNT(B24:BC24)=0,"",SUM(B24:BC24))</f>
+        <v/>
+      </c>
+      <c r="BE24">
+        <f>COUNT(B24:BC24)</f>
+        <v/>
+      </c>
+      <c r="BF24">
+        <f>IF(OR(BD24="",COUNT($BD$5:$BD$39)&lt;3),"",IF(RANK(BD24,$BD$5:$BD$39,0)&lt;=ROUND(COUNT($BD$5:$BD$39)/3,0),"top",IF(RANK(BD24,$BD$5:$BD$39,1)&lt;=ROUND(COUNT($BD$5:$BD$39)/3,0),"bottom","middle")))</f>
         <v/>
       </c>
     </row>
@@ -2629,16 +2728,19 @@
       <c r="AX25" s="5" t="n"/>
       <c r="AY25" s="5" t="n"/>
       <c r="AZ25" s="5" t="n"/>
-      <c r="BA25">
-        <f>IF(COUNT(B25:AZ25)=0,"",SUM(B25:AZ25))</f>
-        <v/>
-      </c>
-      <c r="BB25">
-        <f>COUNT(B25:AZ25)</f>
-        <v/>
-      </c>
-      <c r="BC25">
-        <f>IF(OR(BA25="",COUNT($BA$5:$BA$39)&lt;3),"",IF(RANK(BA25,$BA$5:$BA$39,0)&lt;=ROUND(COUNT($BA$5:$BA$39)/3,0),"top",IF(RANK(BA25,$BA$5:$BA$39,1)&lt;=ROUND(COUNT($BA$5:$BA$39)/3,0),"bottom","middle")))</f>
+      <c r="BA25" s="5" t="n"/>
+      <c r="BB25" s="5" t="n"/>
+      <c r="BC25" s="5" t="n"/>
+      <c r="BD25">
+        <f>IF(COUNT(B25:BC25)=0,"",SUM(B25:BC25))</f>
+        <v/>
+      </c>
+      <c r="BE25">
+        <f>COUNT(B25:BC25)</f>
+        <v/>
+      </c>
+      <c r="BF25">
+        <f>IF(OR(BD25="",COUNT($BD$5:$BD$39)&lt;3),"",IF(RANK(BD25,$BD$5:$BD$39,0)&lt;=ROUND(COUNT($BD$5:$BD$39)/3,0),"top",IF(RANK(BD25,$BD$5:$BD$39,1)&lt;=ROUND(COUNT($BD$5:$BD$39)/3,0),"bottom","middle")))</f>
         <v/>
       </c>
     </row>
@@ -2697,16 +2799,19 @@
       <c r="AX26" s="5" t="n"/>
       <c r="AY26" s="5" t="n"/>
       <c r="AZ26" s="5" t="n"/>
-      <c r="BA26">
-        <f>IF(COUNT(B26:AZ26)=0,"",SUM(B26:AZ26))</f>
-        <v/>
-      </c>
-      <c r="BB26">
-        <f>COUNT(B26:AZ26)</f>
-        <v/>
-      </c>
-      <c r="BC26">
-        <f>IF(OR(BA26="",COUNT($BA$5:$BA$39)&lt;3),"",IF(RANK(BA26,$BA$5:$BA$39,0)&lt;=ROUND(COUNT($BA$5:$BA$39)/3,0),"top",IF(RANK(BA26,$BA$5:$BA$39,1)&lt;=ROUND(COUNT($BA$5:$BA$39)/3,0),"bottom","middle")))</f>
+      <c r="BA26" s="5" t="n"/>
+      <c r="BB26" s="5" t="n"/>
+      <c r="BC26" s="5" t="n"/>
+      <c r="BD26">
+        <f>IF(COUNT(B26:BC26)=0,"",SUM(B26:BC26))</f>
+        <v/>
+      </c>
+      <c r="BE26">
+        <f>COUNT(B26:BC26)</f>
+        <v/>
+      </c>
+      <c r="BF26">
+        <f>IF(OR(BD26="",COUNT($BD$5:$BD$39)&lt;3),"",IF(RANK(BD26,$BD$5:$BD$39,0)&lt;=ROUND(COUNT($BD$5:$BD$39)/3,0),"top",IF(RANK(BD26,$BD$5:$BD$39,1)&lt;=ROUND(COUNT($BD$5:$BD$39)/3,0),"bottom","middle")))</f>
         <v/>
       </c>
     </row>
@@ -2765,16 +2870,19 @@
       <c r="AX27" s="5" t="n"/>
       <c r="AY27" s="5" t="n"/>
       <c r="AZ27" s="5" t="n"/>
-      <c r="BA27">
-        <f>IF(COUNT(B27:AZ27)=0,"",SUM(B27:AZ27))</f>
-        <v/>
-      </c>
-      <c r="BB27">
-        <f>COUNT(B27:AZ27)</f>
-        <v/>
-      </c>
-      <c r="BC27">
-        <f>IF(OR(BA27="",COUNT($BA$5:$BA$39)&lt;3),"",IF(RANK(BA27,$BA$5:$BA$39,0)&lt;=ROUND(COUNT($BA$5:$BA$39)/3,0),"top",IF(RANK(BA27,$BA$5:$BA$39,1)&lt;=ROUND(COUNT($BA$5:$BA$39)/3,0),"bottom","middle")))</f>
+      <c r="BA27" s="5" t="n"/>
+      <c r="BB27" s="5" t="n"/>
+      <c r="BC27" s="5" t="n"/>
+      <c r="BD27">
+        <f>IF(COUNT(B27:BC27)=0,"",SUM(B27:BC27))</f>
+        <v/>
+      </c>
+      <c r="BE27">
+        <f>COUNT(B27:BC27)</f>
+        <v/>
+      </c>
+      <c r="BF27">
+        <f>IF(OR(BD27="",COUNT($BD$5:$BD$39)&lt;3),"",IF(RANK(BD27,$BD$5:$BD$39,0)&lt;=ROUND(COUNT($BD$5:$BD$39)/3,0),"top",IF(RANK(BD27,$BD$5:$BD$39,1)&lt;=ROUND(COUNT($BD$5:$BD$39)/3,0),"bottom","middle")))</f>
         <v/>
       </c>
     </row>
@@ -2833,16 +2941,19 @@
       <c r="AX28" s="5" t="n"/>
       <c r="AY28" s="5" t="n"/>
       <c r="AZ28" s="5" t="n"/>
-      <c r="BA28">
-        <f>IF(COUNT(B28:AZ28)=0,"",SUM(B28:AZ28))</f>
-        <v/>
-      </c>
-      <c r="BB28">
-        <f>COUNT(B28:AZ28)</f>
-        <v/>
-      </c>
-      <c r="BC28">
-        <f>IF(OR(BA28="",COUNT($BA$5:$BA$39)&lt;3),"",IF(RANK(BA28,$BA$5:$BA$39,0)&lt;=ROUND(COUNT($BA$5:$BA$39)/3,0),"top",IF(RANK(BA28,$BA$5:$BA$39,1)&lt;=ROUND(COUNT($BA$5:$BA$39)/3,0),"bottom","middle")))</f>
+      <c r="BA28" s="5" t="n"/>
+      <c r="BB28" s="5" t="n"/>
+      <c r="BC28" s="5" t="n"/>
+      <c r="BD28">
+        <f>IF(COUNT(B28:BC28)=0,"",SUM(B28:BC28))</f>
+        <v/>
+      </c>
+      <c r="BE28">
+        <f>COUNT(B28:BC28)</f>
+        <v/>
+      </c>
+      <c r="BF28">
+        <f>IF(OR(BD28="",COUNT($BD$5:$BD$39)&lt;3),"",IF(RANK(BD28,$BD$5:$BD$39,0)&lt;=ROUND(COUNT($BD$5:$BD$39)/3,0),"top",IF(RANK(BD28,$BD$5:$BD$39,1)&lt;=ROUND(COUNT($BD$5:$BD$39)/3,0),"bottom","middle")))</f>
         <v/>
       </c>
     </row>
@@ -2901,16 +3012,19 @@
       <c r="AX29" s="5" t="n"/>
       <c r="AY29" s="5" t="n"/>
       <c r="AZ29" s="5" t="n"/>
-      <c r="BA29">
-        <f>IF(COUNT(B29:AZ29)=0,"",SUM(B29:AZ29))</f>
-        <v/>
-      </c>
-      <c r="BB29">
-        <f>COUNT(B29:AZ29)</f>
-        <v/>
-      </c>
-      <c r="BC29">
-        <f>IF(OR(BA29="",COUNT($BA$5:$BA$39)&lt;3),"",IF(RANK(BA29,$BA$5:$BA$39,0)&lt;=ROUND(COUNT($BA$5:$BA$39)/3,0),"top",IF(RANK(BA29,$BA$5:$BA$39,1)&lt;=ROUND(COUNT($BA$5:$BA$39)/3,0),"bottom","middle")))</f>
+      <c r="BA29" s="5" t="n"/>
+      <c r="BB29" s="5" t="n"/>
+      <c r="BC29" s="5" t="n"/>
+      <c r="BD29">
+        <f>IF(COUNT(B29:BC29)=0,"",SUM(B29:BC29))</f>
+        <v/>
+      </c>
+      <c r="BE29">
+        <f>COUNT(B29:BC29)</f>
+        <v/>
+      </c>
+      <c r="BF29">
+        <f>IF(OR(BD29="",COUNT($BD$5:$BD$39)&lt;3),"",IF(RANK(BD29,$BD$5:$BD$39,0)&lt;=ROUND(COUNT($BD$5:$BD$39)/3,0),"top",IF(RANK(BD29,$BD$5:$BD$39,1)&lt;=ROUND(COUNT($BD$5:$BD$39)/3,0),"bottom","middle")))</f>
         <v/>
       </c>
     </row>
@@ -2969,16 +3083,19 @@
       <c r="AX30" s="5" t="n"/>
       <c r="AY30" s="5" t="n"/>
       <c r="AZ30" s="5" t="n"/>
-      <c r="BA30">
-        <f>IF(COUNT(B30:AZ30)=0,"",SUM(B30:AZ30))</f>
-        <v/>
-      </c>
-      <c r="BB30">
-        <f>COUNT(B30:AZ30)</f>
-        <v/>
-      </c>
-      <c r="BC30">
-        <f>IF(OR(BA30="",COUNT($BA$5:$BA$39)&lt;3),"",IF(RANK(BA30,$BA$5:$BA$39,0)&lt;=ROUND(COUNT($BA$5:$BA$39)/3,0),"top",IF(RANK(BA30,$BA$5:$BA$39,1)&lt;=ROUND(COUNT($BA$5:$BA$39)/3,0),"bottom","middle")))</f>
+      <c r="BA30" s="5" t="n"/>
+      <c r="BB30" s="5" t="n"/>
+      <c r="BC30" s="5" t="n"/>
+      <c r="BD30">
+        <f>IF(COUNT(B30:BC30)=0,"",SUM(B30:BC30))</f>
+        <v/>
+      </c>
+      <c r="BE30">
+        <f>COUNT(B30:BC30)</f>
+        <v/>
+      </c>
+      <c r="BF30">
+        <f>IF(OR(BD30="",COUNT($BD$5:$BD$39)&lt;3),"",IF(RANK(BD30,$BD$5:$BD$39,0)&lt;=ROUND(COUNT($BD$5:$BD$39)/3,0),"top",IF(RANK(BD30,$BD$5:$BD$39,1)&lt;=ROUND(COUNT($BD$5:$BD$39)/3,0),"bottom","middle")))</f>
         <v/>
       </c>
     </row>
@@ -3037,16 +3154,19 @@
       <c r="AX31" s="5" t="n"/>
       <c r="AY31" s="5" t="n"/>
       <c r="AZ31" s="5" t="n"/>
-      <c r="BA31">
-        <f>IF(COUNT(B31:AZ31)=0,"",SUM(B31:AZ31))</f>
-        <v/>
-      </c>
-      <c r="BB31">
-        <f>COUNT(B31:AZ31)</f>
-        <v/>
-      </c>
-      <c r="BC31">
-        <f>IF(OR(BA31="",COUNT($BA$5:$BA$39)&lt;3),"",IF(RANK(BA31,$BA$5:$BA$39,0)&lt;=ROUND(COUNT($BA$5:$BA$39)/3,0),"top",IF(RANK(BA31,$BA$5:$BA$39,1)&lt;=ROUND(COUNT($BA$5:$BA$39)/3,0),"bottom","middle")))</f>
+      <c r="BA31" s="5" t="n"/>
+      <c r="BB31" s="5" t="n"/>
+      <c r="BC31" s="5" t="n"/>
+      <c r="BD31">
+        <f>IF(COUNT(B31:BC31)=0,"",SUM(B31:BC31))</f>
+        <v/>
+      </c>
+      <c r="BE31">
+        <f>COUNT(B31:BC31)</f>
+        <v/>
+      </c>
+      <c r="BF31">
+        <f>IF(OR(BD31="",COUNT($BD$5:$BD$39)&lt;3),"",IF(RANK(BD31,$BD$5:$BD$39,0)&lt;=ROUND(COUNT($BD$5:$BD$39)/3,0),"top",IF(RANK(BD31,$BD$5:$BD$39,1)&lt;=ROUND(COUNT($BD$5:$BD$39)/3,0),"bottom","middle")))</f>
         <v/>
       </c>
     </row>
@@ -3105,16 +3225,19 @@
       <c r="AX32" s="5" t="n"/>
       <c r="AY32" s="5" t="n"/>
       <c r="AZ32" s="5" t="n"/>
-      <c r="BA32">
-        <f>IF(COUNT(B32:AZ32)=0,"",SUM(B32:AZ32))</f>
-        <v/>
-      </c>
-      <c r="BB32">
-        <f>COUNT(B32:AZ32)</f>
-        <v/>
-      </c>
-      <c r="BC32">
-        <f>IF(OR(BA32="",COUNT($BA$5:$BA$39)&lt;3),"",IF(RANK(BA32,$BA$5:$BA$39,0)&lt;=ROUND(COUNT($BA$5:$BA$39)/3,0),"top",IF(RANK(BA32,$BA$5:$BA$39,1)&lt;=ROUND(COUNT($BA$5:$BA$39)/3,0),"bottom","middle")))</f>
+      <c r="BA32" s="5" t="n"/>
+      <c r="BB32" s="5" t="n"/>
+      <c r="BC32" s="5" t="n"/>
+      <c r="BD32">
+        <f>IF(COUNT(B32:BC32)=0,"",SUM(B32:BC32))</f>
+        <v/>
+      </c>
+      <c r="BE32">
+        <f>COUNT(B32:BC32)</f>
+        <v/>
+      </c>
+      <c r="BF32">
+        <f>IF(OR(BD32="",COUNT($BD$5:$BD$39)&lt;3),"",IF(RANK(BD32,$BD$5:$BD$39,0)&lt;=ROUND(COUNT($BD$5:$BD$39)/3,0),"top",IF(RANK(BD32,$BD$5:$BD$39,1)&lt;=ROUND(COUNT($BD$5:$BD$39)/3,0),"bottom","middle")))</f>
         <v/>
       </c>
     </row>
@@ -3173,16 +3296,19 @@
       <c r="AX33" s="5" t="n"/>
       <c r="AY33" s="5" t="n"/>
       <c r="AZ33" s="5" t="n"/>
-      <c r="BA33">
-        <f>IF(COUNT(B33:AZ33)=0,"",SUM(B33:AZ33))</f>
-        <v/>
-      </c>
-      <c r="BB33">
-        <f>COUNT(B33:AZ33)</f>
-        <v/>
-      </c>
-      <c r="BC33">
-        <f>IF(OR(BA33="",COUNT($BA$5:$BA$39)&lt;3),"",IF(RANK(BA33,$BA$5:$BA$39,0)&lt;=ROUND(COUNT($BA$5:$BA$39)/3,0),"top",IF(RANK(BA33,$BA$5:$BA$39,1)&lt;=ROUND(COUNT($BA$5:$BA$39)/3,0),"bottom","middle")))</f>
+      <c r="BA33" s="5" t="n"/>
+      <c r="BB33" s="5" t="n"/>
+      <c r="BC33" s="5" t="n"/>
+      <c r="BD33">
+        <f>IF(COUNT(B33:BC33)=0,"",SUM(B33:BC33))</f>
+        <v/>
+      </c>
+      <c r="BE33">
+        <f>COUNT(B33:BC33)</f>
+        <v/>
+      </c>
+      <c r="BF33">
+        <f>IF(OR(BD33="",COUNT($BD$5:$BD$39)&lt;3),"",IF(RANK(BD33,$BD$5:$BD$39,0)&lt;=ROUND(COUNT($BD$5:$BD$39)/3,0),"top",IF(RANK(BD33,$BD$5:$BD$39,1)&lt;=ROUND(COUNT($BD$5:$BD$39)/3,0),"bottom","middle")))</f>
         <v/>
       </c>
     </row>
@@ -3241,16 +3367,19 @@
       <c r="AX34" s="5" t="n"/>
       <c r="AY34" s="5" t="n"/>
       <c r="AZ34" s="5" t="n"/>
-      <c r="BA34">
-        <f>IF(COUNT(B34:AZ34)=0,"",SUM(B34:AZ34))</f>
-        <v/>
-      </c>
-      <c r="BB34">
-        <f>COUNT(B34:AZ34)</f>
-        <v/>
-      </c>
-      <c r="BC34">
-        <f>IF(OR(BA34="",COUNT($BA$5:$BA$39)&lt;3),"",IF(RANK(BA34,$BA$5:$BA$39,0)&lt;=ROUND(COUNT($BA$5:$BA$39)/3,0),"top",IF(RANK(BA34,$BA$5:$BA$39,1)&lt;=ROUND(COUNT($BA$5:$BA$39)/3,0),"bottom","middle")))</f>
+      <c r="BA34" s="5" t="n"/>
+      <c r="BB34" s="5" t="n"/>
+      <c r="BC34" s="5" t="n"/>
+      <c r="BD34">
+        <f>IF(COUNT(B34:BC34)=0,"",SUM(B34:BC34))</f>
+        <v/>
+      </c>
+      <c r="BE34">
+        <f>COUNT(B34:BC34)</f>
+        <v/>
+      </c>
+      <c r="BF34">
+        <f>IF(OR(BD34="",COUNT($BD$5:$BD$39)&lt;3),"",IF(RANK(BD34,$BD$5:$BD$39,0)&lt;=ROUND(COUNT($BD$5:$BD$39)/3,0),"top",IF(RANK(BD34,$BD$5:$BD$39,1)&lt;=ROUND(COUNT($BD$5:$BD$39)/3,0),"bottom","middle")))</f>
         <v/>
       </c>
     </row>
@@ -3309,16 +3438,19 @@
       <c r="AX35" s="5" t="n"/>
       <c r="AY35" s="5" t="n"/>
       <c r="AZ35" s="5" t="n"/>
-      <c r="BA35">
-        <f>IF(COUNT(B35:AZ35)=0,"",SUM(B35:AZ35))</f>
-        <v/>
-      </c>
-      <c r="BB35">
-        <f>COUNT(B35:AZ35)</f>
-        <v/>
-      </c>
-      <c r="BC35">
-        <f>IF(OR(BA35="",COUNT($BA$5:$BA$39)&lt;3),"",IF(RANK(BA35,$BA$5:$BA$39,0)&lt;=ROUND(COUNT($BA$5:$BA$39)/3,0),"top",IF(RANK(BA35,$BA$5:$BA$39,1)&lt;=ROUND(COUNT($BA$5:$BA$39)/3,0),"bottom","middle")))</f>
+      <c r="BA35" s="5" t="n"/>
+      <c r="BB35" s="5" t="n"/>
+      <c r="BC35" s="5" t="n"/>
+      <c r="BD35">
+        <f>IF(COUNT(B35:BC35)=0,"",SUM(B35:BC35))</f>
+        <v/>
+      </c>
+      <c r="BE35">
+        <f>COUNT(B35:BC35)</f>
+        <v/>
+      </c>
+      <c r="BF35">
+        <f>IF(OR(BD35="",COUNT($BD$5:$BD$39)&lt;3),"",IF(RANK(BD35,$BD$5:$BD$39,0)&lt;=ROUND(COUNT($BD$5:$BD$39)/3,0),"top",IF(RANK(BD35,$BD$5:$BD$39,1)&lt;=ROUND(COUNT($BD$5:$BD$39)/3,0),"bottom","middle")))</f>
         <v/>
       </c>
     </row>
@@ -3377,16 +3509,19 @@
       <c r="AX36" s="5" t="n"/>
       <c r="AY36" s="5" t="n"/>
       <c r="AZ36" s="5" t="n"/>
-      <c r="BA36">
-        <f>IF(COUNT(B36:AZ36)=0,"",SUM(B36:AZ36))</f>
-        <v/>
-      </c>
-      <c r="BB36">
-        <f>COUNT(B36:AZ36)</f>
-        <v/>
-      </c>
-      <c r="BC36">
-        <f>IF(OR(BA36="",COUNT($BA$5:$BA$39)&lt;3),"",IF(RANK(BA36,$BA$5:$BA$39,0)&lt;=ROUND(COUNT($BA$5:$BA$39)/3,0),"top",IF(RANK(BA36,$BA$5:$BA$39,1)&lt;=ROUND(COUNT($BA$5:$BA$39)/3,0),"bottom","middle")))</f>
+      <c r="BA36" s="5" t="n"/>
+      <c r="BB36" s="5" t="n"/>
+      <c r="BC36" s="5" t="n"/>
+      <c r="BD36">
+        <f>IF(COUNT(B36:BC36)=0,"",SUM(B36:BC36))</f>
+        <v/>
+      </c>
+      <c r="BE36">
+        <f>COUNT(B36:BC36)</f>
+        <v/>
+      </c>
+      <c r="BF36">
+        <f>IF(OR(BD36="",COUNT($BD$5:$BD$39)&lt;3),"",IF(RANK(BD36,$BD$5:$BD$39,0)&lt;=ROUND(COUNT($BD$5:$BD$39)/3,0),"top",IF(RANK(BD36,$BD$5:$BD$39,1)&lt;=ROUND(COUNT($BD$5:$BD$39)/3,0),"bottom","middle")))</f>
         <v/>
       </c>
     </row>
@@ -3445,16 +3580,19 @@
       <c r="AX37" s="5" t="n"/>
       <c r="AY37" s="5" t="n"/>
       <c r="AZ37" s="5" t="n"/>
-      <c r="BA37">
-        <f>IF(COUNT(B37:AZ37)=0,"",SUM(B37:AZ37))</f>
-        <v/>
-      </c>
-      <c r="BB37">
-        <f>COUNT(B37:AZ37)</f>
-        <v/>
-      </c>
-      <c r="BC37">
-        <f>IF(OR(BA37="",COUNT($BA$5:$BA$39)&lt;3),"",IF(RANK(BA37,$BA$5:$BA$39,0)&lt;=ROUND(COUNT($BA$5:$BA$39)/3,0),"top",IF(RANK(BA37,$BA$5:$BA$39,1)&lt;=ROUND(COUNT($BA$5:$BA$39)/3,0),"bottom","middle")))</f>
+      <c r="BA37" s="5" t="n"/>
+      <c r="BB37" s="5" t="n"/>
+      <c r="BC37" s="5" t="n"/>
+      <c r="BD37">
+        <f>IF(COUNT(B37:BC37)=0,"",SUM(B37:BC37))</f>
+        <v/>
+      </c>
+      <c r="BE37">
+        <f>COUNT(B37:BC37)</f>
+        <v/>
+      </c>
+      <c r="BF37">
+        <f>IF(OR(BD37="",COUNT($BD$5:$BD$39)&lt;3),"",IF(RANK(BD37,$BD$5:$BD$39,0)&lt;=ROUND(COUNT($BD$5:$BD$39)/3,0),"top",IF(RANK(BD37,$BD$5:$BD$39,1)&lt;=ROUND(COUNT($BD$5:$BD$39)/3,0),"bottom","middle")))</f>
         <v/>
       </c>
     </row>
@@ -3513,16 +3651,19 @@
       <c r="AX38" s="5" t="n"/>
       <c r="AY38" s="5" t="n"/>
       <c r="AZ38" s="5" t="n"/>
-      <c r="BA38">
-        <f>IF(COUNT(B38:AZ38)=0,"",SUM(B38:AZ38))</f>
-        <v/>
-      </c>
-      <c r="BB38">
-        <f>COUNT(B38:AZ38)</f>
-        <v/>
-      </c>
-      <c r="BC38">
-        <f>IF(OR(BA38="",COUNT($BA$5:$BA$39)&lt;3),"",IF(RANK(BA38,$BA$5:$BA$39,0)&lt;=ROUND(COUNT($BA$5:$BA$39)/3,0),"top",IF(RANK(BA38,$BA$5:$BA$39,1)&lt;=ROUND(COUNT($BA$5:$BA$39)/3,0),"bottom","middle")))</f>
+      <c r="BA38" s="5" t="n"/>
+      <c r="BB38" s="5" t="n"/>
+      <c r="BC38" s="5" t="n"/>
+      <c r="BD38">
+        <f>IF(COUNT(B38:BC38)=0,"",SUM(B38:BC38))</f>
+        <v/>
+      </c>
+      <c r="BE38">
+        <f>COUNT(B38:BC38)</f>
+        <v/>
+      </c>
+      <c r="BF38">
+        <f>IF(OR(BD38="",COUNT($BD$5:$BD$39)&lt;3),"",IF(RANK(BD38,$BD$5:$BD$39,0)&lt;=ROUND(COUNT($BD$5:$BD$39)/3,0),"top",IF(RANK(BD38,$BD$5:$BD$39,1)&lt;=ROUND(COUNT($BD$5:$BD$39)/3,0),"bottom","middle")))</f>
         <v/>
       </c>
     </row>
@@ -3581,16 +3722,19 @@
       <c r="AX39" s="5" t="n"/>
       <c r="AY39" s="5" t="n"/>
       <c r="AZ39" s="5" t="n"/>
-      <c r="BA39">
-        <f>IF(COUNT(B39:AZ39)=0,"",SUM(B39:AZ39))</f>
-        <v/>
-      </c>
-      <c r="BB39">
-        <f>COUNT(B39:AZ39)</f>
-        <v/>
-      </c>
-      <c r="BC39">
-        <f>IF(OR(BA39="",COUNT($BA$5:$BA$39)&lt;3),"",IF(RANK(BA39,$BA$5:$BA$39,0)&lt;=ROUND(COUNT($BA$5:$BA$39)/3,0),"top",IF(RANK(BA39,$BA$5:$BA$39,1)&lt;=ROUND(COUNT($BA$5:$BA$39)/3,0),"bottom","middle")))</f>
+      <c r="BA39" s="5" t="n"/>
+      <c r="BB39" s="5" t="n"/>
+      <c r="BC39" s="5" t="n"/>
+      <c r="BD39">
+        <f>IF(COUNT(B39:BC39)=0,"",SUM(B39:BC39))</f>
+        <v/>
+      </c>
+      <c r="BE39">
+        <f>COUNT(B39:BC39)</f>
+        <v/>
+      </c>
+      <c r="BF39">
+        <f>IF(OR(BD39="",COUNT($BD$5:$BD$39)&lt;3),"",IF(RANK(BD39,$BD$5:$BD$39,0)&lt;=ROUND(COUNT($BD$5:$BD$39)/3,0),"top",IF(RANK(BD39,$BD$5:$BD$39,1)&lt;=ROUND(COUNT($BD$5:$BD$39)/3,0),"bottom","middle")))</f>
         <v/>
       </c>
     </row>
@@ -3605,7 +3749,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N55"/>
+  <dimension ref="A1:N58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="13" max="13"/>
@@ -3730,11 +3874,11 @@
         <v/>
       </c>
       <c r="J5" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BC$5:$BC$39="top")*ISNUMBER(Marks!B$5:B$39))=0,"",SUMPRODUCT((Marks!$BC$5:$BC$39="top")*(Marks!B$5:B$39=1))/SUMPRODUCT((Marks!$BC$5:$BC$39="top")*ISNUMBER(Marks!B$5:B$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$BF$5:$BF$39="top")*ISNUMBER(Marks!B$5:B$39))=0,"",SUMPRODUCT((Marks!$BF$5:$BF$39="top")*(Marks!B$5:B$39=1))/SUMPRODUCT((Marks!$BF$5:$BF$39="top")*ISNUMBER(Marks!B$5:B$39)))</f>
         <v/>
       </c>
       <c r="K5" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BC$5:$BC$39="bottom")*ISNUMBER(Marks!B$5:B$39))=0,"",SUMPRODUCT((Marks!$BC$5:$BC$39="bottom")*(Marks!B$5:B$39=1))/SUMPRODUCT((Marks!$BC$5:$BC$39="bottom")*ISNUMBER(Marks!B$5:B$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*ISNUMBER(Marks!B$5:B$39))=0,"",SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*(Marks!B$5:B$39=1))/SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*ISNUMBER(Marks!B$5:B$39)))</f>
         <v/>
       </c>
       <c r="L5" s="6">
@@ -3790,11 +3934,11 @@
         <v/>
       </c>
       <c r="J6" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BC$5:$BC$39="top")*ISNUMBER(Marks!C$5:C$39))=0,"",SUMPRODUCT((Marks!$BC$5:$BC$39="top")*(Marks!C$5:C$39=1))/SUMPRODUCT((Marks!$BC$5:$BC$39="top")*ISNUMBER(Marks!C$5:C$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$BF$5:$BF$39="top")*ISNUMBER(Marks!C$5:C$39))=0,"",SUMPRODUCT((Marks!$BF$5:$BF$39="top")*(Marks!C$5:C$39=1))/SUMPRODUCT((Marks!$BF$5:$BF$39="top")*ISNUMBER(Marks!C$5:C$39)))</f>
         <v/>
       </c>
       <c r="K6" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BC$5:$BC$39="bottom")*ISNUMBER(Marks!C$5:C$39))=0,"",SUMPRODUCT((Marks!$BC$5:$BC$39="bottom")*(Marks!C$5:C$39=1))/SUMPRODUCT((Marks!$BC$5:$BC$39="bottom")*ISNUMBER(Marks!C$5:C$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*ISNUMBER(Marks!C$5:C$39))=0,"",SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*(Marks!C$5:C$39=1))/SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*ISNUMBER(Marks!C$5:C$39)))</f>
         <v/>
       </c>
       <c r="L6" s="6">
@@ -3850,11 +3994,11 @@
         <v/>
       </c>
       <c r="J7" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BC$5:$BC$39="top")*ISNUMBER(Marks!D$5:D$39))=0,"",SUMPRODUCT((Marks!$BC$5:$BC$39="top")*(Marks!D$5:D$39=1))/SUMPRODUCT((Marks!$BC$5:$BC$39="top")*ISNUMBER(Marks!D$5:D$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$BF$5:$BF$39="top")*ISNUMBER(Marks!D$5:D$39))=0,"",SUMPRODUCT((Marks!$BF$5:$BF$39="top")*(Marks!D$5:D$39=1))/SUMPRODUCT((Marks!$BF$5:$BF$39="top")*ISNUMBER(Marks!D$5:D$39)))</f>
         <v/>
       </c>
       <c r="K7" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BC$5:$BC$39="bottom")*ISNUMBER(Marks!D$5:D$39))=0,"",SUMPRODUCT((Marks!$BC$5:$BC$39="bottom")*(Marks!D$5:D$39=1))/SUMPRODUCT((Marks!$BC$5:$BC$39="bottom")*ISNUMBER(Marks!D$5:D$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*ISNUMBER(Marks!D$5:D$39))=0,"",SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*(Marks!D$5:D$39=1))/SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*ISNUMBER(Marks!D$5:D$39)))</f>
         <v/>
       </c>
       <c r="L7" s="6">
@@ -3910,11 +4054,11 @@
         <v/>
       </c>
       <c r="J8" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BC$5:$BC$39="top")*ISNUMBER(Marks!E$5:E$39))=0,"",SUMPRODUCT((Marks!$BC$5:$BC$39="top")*(Marks!E$5:E$39=1))/SUMPRODUCT((Marks!$BC$5:$BC$39="top")*ISNUMBER(Marks!E$5:E$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$BF$5:$BF$39="top")*ISNUMBER(Marks!E$5:E$39))=0,"",SUMPRODUCT((Marks!$BF$5:$BF$39="top")*(Marks!E$5:E$39=1))/SUMPRODUCT((Marks!$BF$5:$BF$39="top")*ISNUMBER(Marks!E$5:E$39)))</f>
         <v/>
       </c>
       <c r="K8" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BC$5:$BC$39="bottom")*ISNUMBER(Marks!E$5:E$39))=0,"",SUMPRODUCT((Marks!$BC$5:$BC$39="bottom")*(Marks!E$5:E$39=1))/SUMPRODUCT((Marks!$BC$5:$BC$39="bottom")*ISNUMBER(Marks!E$5:E$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*ISNUMBER(Marks!E$5:E$39))=0,"",SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*(Marks!E$5:E$39=1))/SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*ISNUMBER(Marks!E$5:E$39)))</f>
         <v/>
       </c>
       <c r="L8" s="6">
@@ -3970,11 +4114,11 @@
         <v/>
       </c>
       <c r="J9" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BC$5:$BC$39="top")*ISNUMBER(Marks!F$5:F$39))=0,"",SUMPRODUCT((Marks!$BC$5:$BC$39="top")*(Marks!F$5:F$39=1))/SUMPRODUCT((Marks!$BC$5:$BC$39="top")*ISNUMBER(Marks!F$5:F$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$BF$5:$BF$39="top")*ISNUMBER(Marks!F$5:F$39))=0,"",SUMPRODUCT((Marks!$BF$5:$BF$39="top")*(Marks!F$5:F$39=1))/SUMPRODUCT((Marks!$BF$5:$BF$39="top")*ISNUMBER(Marks!F$5:F$39)))</f>
         <v/>
       </c>
       <c r="K9" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BC$5:$BC$39="bottom")*ISNUMBER(Marks!F$5:F$39))=0,"",SUMPRODUCT((Marks!$BC$5:$BC$39="bottom")*(Marks!F$5:F$39=1))/SUMPRODUCT((Marks!$BC$5:$BC$39="bottom")*ISNUMBER(Marks!F$5:F$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*ISNUMBER(Marks!F$5:F$39))=0,"",SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*(Marks!F$5:F$39=1))/SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*ISNUMBER(Marks!F$5:F$39)))</f>
         <v/>
       </c>
       <c r="L9" s="6">
@@ -4030,11 +4174,11 @@
         <v/>
       </c>
       <c r="J10" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BC$5:$BC$39="top")*ISNUMBER(Marks!G$5:G$39))=0,"",SUMPRODUCT((Marks!$BC$5:$BC$39="top")*(Marks!G$5:G$39=1))/SUMPRODUCT((Marks!$BC$5:$BC$39="top")*ISNUMBER(Marks!G$5:G$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$BF$5:$BF$39="top")*ISNUMBER(Marks!G$5:G$39))=0,"",SUMPRODUCT((Marks!$BF$5:$BF$39="top")*(Marks!G$5:G$39=1))/SUMPRODUCT((Marks!$BF$5:$BF$39="top")*ISNUMBER(Marks!G$5:G$39)))</f>
         <v/>
       </c>
       <c r="K10" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BC$5:$BC$39="bottom")*ISNUMBER(Marks!G$5:G$39))=0,"",SUMPRODUCT((Marks!$BC$5:$BC$39="bottom")*(Marks!G$5:G$39=1))/SUMPRODUCT((Marks!$BC$5:$BC$39="bottom")*ISNUMBER(Marks!G$5:G$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*ISNUMBER(Marks!G$5:G$39))=0,"",SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*(Marks!G$5:G$39=1))/SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*ISNUMBER(Marks!G$5:G$39)))</f>
         <v/>
       </c>
       <c r="L10" s="6">
@@ -4090,11 +4234,11 @@
         <v/>
       </c>
       <c r="J11" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BC$5:$BC$39="top")*ISNUMBER(Marks!H$5:H$39))=0,"",SUMPRODUCT((Marks!$BC$5:$BC$39="top")*(Marks!H$5:H$39=1))/SUMPRODUCT((Marks!$BC$5:$BC$39="top")*ISNUMBER(Marks!H$5:H$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$BF$5:$BF$39="top")*ISNUMBER(Marks!H$5:H$39))=0,"",SUMPRODUCT((Marks!$BF$5:$BF$39="top")*(Marks!H$5:H$39=1))/SUMPRODUCT((Marks!$BF$5:$BF$39="top")*ISNUMBER(Marks!H$5:H$39)))</f>
         <v/>
       </c>
       <c r="K11" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BC$5:$BC$39="bottom")*ISNUMBER(Marks!H$5:H$39))=0,"",SUMPRODUCT((Marks!$BC$5:$BC$39="bottom")*(Marks!H$5:H$39=1))/SUMPRODUCT((Marks!$BC$5:$BC$39="bottom")*ISNUMBER(Marks!H$5:H$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*ISNUMBER(Marks!H$5:H$39))=0,"",SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*(Marks!H$5:H$39=1))/SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*ISNUMBER(Marks!H$5:H$39)))</f>
         <v/>
       </c>
       <c r="L11" s="6">
@@ -4150,11 +4294,11 @@
         <v/>
       </c>
       <c r="J12" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BC$5:$BC$39="top")*ISNUMBER(Marks!I$5:I$39))=0,"",SUMPRODUCT((Marks!$BC$5:$BC$39="top")*(Marks!I$5:I$39=1))/SUMPRODUCT((Marks!$BC$5:$BC$39="top")*ISNUMBER(Marks!I$5:I$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$BF$5:$BF$39="top")*ISNUMBER(Marks!I$5:I$39))=0,"",SUMPRODUCT((Marks!$BF$5:$BF$39="top")*(Marks!I$5:I$39=1))/SUMPRODUCT((Marks!$BF$5:$BF$39="top")*ISNUMBER(Marks!I$5:I$39)))</f>
         <v/>
       </c>
       <c r="K12" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BC$5:$BC$39="bottom")*ISNUMBER(Marks!I$5:I$39))=0,"",SUMPRODUCT((Marks!$BC$5:$BC$39="bottom")*(Marks!I$5:I$39=1))/SUMPRODUCT((Marks!$BC$5:$BC$39="bottom")*ISNUMBER(Marks!I$5:I$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*ISNUMBER(Marks!I$5:I$39))=0,"",SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*(Marks!I$5:I$39=1))/SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*ISNUMBER(Marks!I$5:I$39)))</f>
         <v/>
       </c>
       <c r="L12" s="6">
@@ -4210,11 +4354,11 @@
         <v/>
       </c>
       <c r="J13" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BC$5:$BC$39="top")*ISNUMBER(Marks!J$5:J$39))=0,"",SUMPRODUCT((Marks!$BC$5:$BC$39="top")*(Marks!J$5:J$39=1))/SUMPRODUCT((Marks!$BC$5:$BC$39="top")*ISNUMBER(Marks!J$5:J$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$BF$5:$BF$39="top")*ISNUMBER(Marks!J$5:J$39))=0,"",SUMPRODUCT((Marks!$BF$5:$BF$39="top")*(Marks!J$5:J$39=1))/SUMPRODUCT((Marks!$BF$5:$BF$39="top")*ISNUMBER(Marks!J$5:J$39)))</f>
         <v/>
       </c>
       <c r="K13" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BC$5:$BC$39="bottom")*ISNUMBER(Marks!J$5:J$39))=0,"",SUMPRODUCT((Marks!$BC$5:$BC$39="bottom")*(Marks!J$5:J$39=1))/SUMPRODUCT((Marks!$BC$5:$BC$39="bottom")*ISNUMBER(Marks!J$5:J$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*ISNUMBER(Marks!J$5:J$39))=0,"",SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*(Marks!J$5:J$39=1))/SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*ISNUMBER(Marks!J$5:J$39)))</f>
         <v/>
       </c>
       <c r="L13" s="6">
@@ -4270,11 +4414,11 @@
         <v/>
       </c>
       <c r="J14" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BC$5:$BC$39="top")*ISNUMBER(Marks!K$5:K$39))=0,"",SUMPRODUCT((Marks!$BC$5:$BC$39="top")*(Marks!K$5:K$39=1))/SUMPRODUCT((Marks!$BC$5:$BC$39="top")*ISNUMBER(Marks!K$5:K$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$BF$5:$BF$39="top")*ISNUMBER(Marks!K$5:K$39))=0,"",SUMPRODUCT((Marks!$BF$5:$BF$39="top")*(Marks!K$5:K$39=1))/SUMPRODUCT((Marks!$BF$5:$BF$39="top")*ISNUMBER(Marks!K$5:K$39)))</f>
         <v/>
       </c>
       <c r="K14" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BC$5:$BC$39="bottom")*ISNUMBER(Marks!K$5:K$39))=0,"",SUMPRODUCT((Marks!$BC$5:$BC$39="bottom")*(Marks!K$5:K$39=1))/SUMPRODUCT((Marks!$BC$5:$BC$39="bottom")*ISNUMBER(Marks!K$5:K$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*ISNUMBER(Marks!K$5:K$39))=0,"",SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*(Marks!K$5:K$39=1))/SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*ISNUMBER(Marks!K$5:K$39)))</f>
         <v/>
       </c>
       <c r="L14" s="6">
@@ -4330,11 +4474,11 @@
         <v/>
       </c>
       <c r="J15" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BC$5:$BC$39="top")*ISNUMBER(Marks!L$5:L$39))=0,"",SUMPRODUCT((Marks!$BC$5:$BC$39="top")*(Marks!L$5:L$39=1))/SUMPRODUCT((Marks!$BC$5:$BC$39="top")*ISNUMBER(Marks!L$5:L$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$BF$5:$BF$39="top")*ISNUMBER(Marks!L$5:L$39))=0,"",SUMPRODUCT((Marks!$BF$5:$BF$39="top")*(Marks!L$5:L$39=1))/SUMPRODUCT((Marks!$BF$5:$BF$39="top")*ISNUMBER(Marks!L$5:L$39)))</f>
         <v/>
       </c>
       <c r="K15" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BC$5:$BC$39="bottom")*ISNUMBER(Marks!L$5:L$39))=0,"",SUMPRODUCT((Marks!$BC$5:$BC$39="bottom")*(Marks!L$5:L$39=1))/SUMPRODUCT((Marks!$BC$5:$BC$39="bottom")*ISNUMBER(Marks!L$5:L$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*ISNUMBER(Marks!L$5:L$39))=0,"",SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*(Marks!L$5:L$39=1))/SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*ISNUMBER(Marks!L$5:L$39)))</f>
         <v/>
       </c>
       <c r="L15" s="6">
@@ -4390,11 +4534,11 @@
         <v/>
       </c>
       <c r="J16" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BC$5:$BC$39="top")*ISNUMBER(Marks!M$5:M$39))=0,"",SUMPRODUCT((Marks!$BC$5:$BC$39="top")*(Marks!M$5:M$39=1))/SUMPRODUCT((Marks!$BC$5:$BC$39="top")*ISNUMBER(Marks!M$5:M$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$BF$5:$BF$39="top")*ISNUMBER(Marks!M$5:M$39))=0,"",SUMPRODUCT((Marks!$BF$5:$BF$39="top")*(Marks!M$5:M$39=1))/SUMPRODUCT((Marks!$BF$5:$BF$39="top")*ISNUMBER(Marks!M$5:M$39)))</f>
         <v/>
       </c>
       <c r="K16" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BC$5:$BC$39="bottom")*ISNUMBER(Marks!M$5:M$39))=0,"",SUMPRODUCT((Marks!$BC$5:$BC$39="bottom")*(Marks!M$5:M$39=1))/SUMPRODUCT((Marks!$BC$5:$BC$39="bottom")*ISNUMBER(Marks!M$5:M$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*ISNUMBER(Marks!M$5:M$39))=0,"",SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*(Marks!M$5:M$39=1))/SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*ISNUMBER(Marks!M$5:M$39)))</f>
         <v/>
       </c>
       <c r="L16" s="6">
@@ -4450,11 +4594,11 @@
         <v/>
       </c>
       <c r="J17" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BC$5:$BC$39="top")*ISNUMBER(Marks!N$5:N$39))=0,"",SUMPRODUCT((Marks!$BC$5:$BC$39="top")*(Marks!N$5:N$39=1))/SUMPRODUCT((Marks!$BC$5:$BC$39="top")*ISNUMBER(Marks!N$5:N$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$BF$5:$BF$39="top")*ISNUMBER(Marks!N$5:N$39))=0,"",SUMPRODUCT((Marks!$BF$5:$BF$39="top")*(Marks!N$5:N$39=1))/SUMPRODUCT((Marks!$BF$5:$BF$39="top")*ISNUMBER(Marks!N$5:N$39)))</f>
         <v/>
       </c>
       <c r="K17" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BC$5:$BC$39="bottom")*ISNUMBER(Marks!N$5:N$39))=0,"",SUMPRODUCT((Marks!$BC$5:$BC$39="bottom")*(Marks!N$5:N$39=1))/SUMPRODUCT((Marks!$BC$5:$BC$39="bottom")*ISNUMBER(Marks!N$5:N$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*ISNUMBER(Marks!N$5:N$39))=0,"",SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*(Marks!N$5:N$39=1))/SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*ISNUMBER(Marks!N$5:N$39)))</f>
         <v/>
       </c>
       <c r="L17" s="6">
@@ -4510,11 +4654,11 @@
         <v/>
       </c>
       <c r="J18" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BC$5:$BC$39="top")*ISNUMBER(Marks!O$5:O$39))=0,"",SUMPRODUCT((Marks!$BC$5:$BC$39="top")*(Marks!O$5:O$39=1))/SUMPRODUCT((Marks!$BC$5:$BC$39="top")*ISNUMBER(Marks!O$5:O$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$BF$5:$BF$39="top")*ISNUMBER(Marks!O$5:O$39))=0,"",SUMPRODUCT((Marks!$BF$5:$BF$39="top")*(Marks!O$5:O$39=1))/SUMPRODUCT((Marks!$BF$5:$BF$39="top")*ISNUMBER(Marks!O$5:O$39)))</f>
         <v/>
       </c>
       <c r="K18" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BC$5:$BC$39="bottom")*ISNUMBER(Marks!O$5:O$39))=0,"",SUMPRODUCT((Marks!$BC$5:$BC$39="bottom")*(Marks!O$5:O$39=1))/SUMPRODUCT((Marks!$BC$5:$BC$39="bottom")*ISNUMBER(Marks!O$5:O$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*ISNUMBER(Marks!O$5:O$39))=0,"",SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*(Marks!O$5:O$39=1))/SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*ISNUMBER(Marks!O$5:O$39)))</f>
         <v/>
       </c>
       <c r="L18" s="6">
@@ -4570,11 +4714,11 @@
         <v/>
       </c>
       <c r="J19" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BC$5:$BC$39="top")*ISNUMBER(Marks!P$5:P$39))=0,"",SUMPRODUCT((Marks!$BC$5:$BC$39="top")*(Marks!P$5:P$39=1))/SUMPRODUCT((Marks!$BC$5:$BC$39="top")*ISNUMBER(Marks!P$5:P$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$BF$5:$BF$39="top")*ISNUMBER(Marks!P$5:P$39))=0,"",SUMPRODUCT((Marks!$BF$5:$BF$39="top")*(Marks!P$5:P$39=1))/SUMPRODUCT((Marks!$BF$5:$BF$39="top")*ISNUMBER(Marks!P$5:P$39)))</f>
         <v/>
       </c>
       <c r="K19" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BC$5:$BC$39="bottom")*ISNUMBER(Marks!P$5:P$39))=0,"",SUMPRODUCT((Marks!$BC$5:$BC$39="bottom")*(Marks!P$5:P$39=1))/SUMPRODUCT((Marks!$BC$5:$BC$39="bottom")*ISNUMBER(Marks!P$5:P$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*ISNUMBER(Marks!P$5:P$39))=0,"",SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*(Marks!P$5:P$39=1))/SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*ISNUMBER(Marks!P$5:P$39)))</f>
         <v/>
       </c>
       <c r="L19" s="6">
@@ -4630,11 +4774,11 @@
         <v/>
       </c>
       <c r="J20" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BC$5:$BC$39="top")*ISNUMBER(Marks!Q$5:Q$39))=0,"",SUMPRODUCT((Marks!$BC$5:$BC$39="top")*(Marks!Q$5:Q$39=1))/SUMPRODUCT((Marks!$BC$5:$BC$39="top")*ISNUMBER(Marks!Q$5:Q$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$BF$5:$BF$39="top")*ISNUMBER(Marks!Q$5:Q$39))=0,"",SUMPRODUCT((Marks!$BF$5:$BF$39="top")*(Marks!Q$5:Q$39=1))/SUMPRODUCT((Marks!$BF$5:$BF$39="top")*ISNUMBER(Marks!Q$5:Q$39)))</f>
         <v/>
       </c>
       <c r="K20" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BC$5:$BC$39="bottom")*ISNUMBER(Marks!Q$5:Q$39))=0,"",SUMPRODUCT((Marks!$BC$5:$BC$39="bottom")*(Marks!Q$5:Q$39=1))/SUMPRODUCT((Marks!$BC$5:$BC$39="bottom")*ISNUMBER(Marks!Q$5:Q$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*ISNUMBER(Marks!Q$5:Q$39))=0,"",SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*(Marks!Q$5:Q$39=1))/SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*ISNUMBER(Marks!Q$5:Q$39)))</f>
         <v/>
       </c>
       <c r="L20" s="6">
@@ -4690,11 +4834,11 @@
         <v/>
       </c>
       <c r="J21" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BC$5:$BC$39="top")*ISNUMBER(Marks!R$5:R$39))=0,"",SUMPRODUCT((Marks!$BC$5:$BC$39="top")*(Marks!R$5:R$39=1))/SUMPRODUCT((Marks!$BC$5:$BC$39="top")*ISNUMBER(Marks!R$5:R$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$BF$5:$BF$39="top")*ISNUMBER(Marks!R$5:R$39))=0,"",SUMPRODUCT((Marks!$BF$5:$BF$39="top")*(Marks!R$5:R$39=1))/SUMPRODUCT((Marks!$BF$5:$BF$39="top")*ISNUMBER(Marks!R$5:R$39)))</f>
         <v/>
       </c>
       <c r="K21" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BC$5:$BC$39="bottom")*ISNUMBER(Marks!R$5:R$39))=0,"",SUMPRODUCT((Marks!$BC$5:$BC$39="bottom")*(Marks!R$5:R$39=1))/SUMPRODUCT((Marks!$BC$5:$BC$39="bottom")*ISNUMBER(Marks!R$5:R$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*ISNUMBER(Marks!R$5:R$39))=0,"",SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*(Marks!R$5:R$39=1))/SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*ISNUMBER(Marks!R$5:R$39)))</f>
         <v/>
       </c>
       <c r="L21" s="6">
@@ -4750,11 +4894,11 @@
         <v/>
       </c>
       <c r="J22" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BC$5:$BC$39="top")*ISNUMBER(Marks!S$5:S$39))=0,"",SUMPRODUCT((Marks!$BC$5:$BC$39="top")*(Marks!S$5:S$39=1))/SUMPRODUCT((Marks!$BC$5:$BC$39="top")*ISNUMBER(Marks!S$5:S$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$BF$5:$BF$39="top")*ISNUMBER(Marks!S$5:S$39))=0,"",SUMPRODUCT((Marks!$BF$5:$BF$39="top")*(Marks!S$5:S$39=1))/SUMPRODUCT((Marks!$BF$5:$BF$39="top")*ISNUMBER(Marks!S$5:S$39)))</f>
         <v/>
       </c>
       <c r="K22" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BC$5:$BC$39="bottom")*ISNUMBER(Marks!S$5:S$39))=0,"",SUMPRODUCT((Marks!$BC$5:$BC$39="bottom")*(Marks!S$5:S$39=1))/SUMPRODUCT((Marks!$BC$5:$BC$39="bottom")*ISNUMBER(Marks!S$5:S$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*ISNUMBER(Marks!S$5:S$39))=0,"",SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*(Marks!S$5:S$39=1))/SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*ISNUMBER(Marks!S$5:S$39)))</f>
         <v/>
       </c>
       <c r="L22" s="6">
@@ -4810,11 +4954,11 @@
         <v/>
       </c>
       <c r="J23" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BC$5:$BC$39="top")*ISNUMBER(Marks!T$5:T$39))=0,"",SUMPRODUCT((Marks!$BC$5:$BC$39="top")*(Marks!T$5:T$39=1))/SUMPRODUCT((Marks!$BC$5:$BC$39="top")*ISNUMBER(Marks!T$5:T$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$BF$5:$BF$39="top")*ISNUMBER(Marks!T$5:T$39))=0,"",SUMPRODUCT((Marks!$BF$5:$BF$39="top")*(Marks!T$5:T$39=1))/SUMPRODUCT((Marks!$BF$5:$BF$39="top")*ISNUMBER(Marks!T$5:T$39)))</f>
         <v/>
       </c>
       <c r="K23" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BC$5:$BC$39="bottom")*ISNUMBER(Marks!T$5:T$39))=0,"",SUMPRODUCT((Marks!$BC$5:$BC$39="bottom")*(Marks!T$5:T$39=1))/SUMPRODUCT((Marks!$BC$5:$BC$39="bottom")*ISNUMBER(Marks!T$5:T$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*ISNUMBER(Marks!T$5:T$39))=0,"",SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*(Marks!T$5:T$39=1))/SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*ISNUMBER(Marks!T$5:T$39)))</f>
         <v/>
       </c>
       <c r="L23" s="6">
@@ -4870,11 +5014,11 @@
         <v/>
       </c>
       <c r="J24" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BC$5:$BC$39="top")*ISNUMBER(Marks!U$5:U$39))=0,"",SUMPRODUCT((Marks!$BC$5:$BC$39="top")*(Marks!U$5:U$39=1))/SUMPRODUCT((Marks!$BC$5:$BC$39="top")*ISNUMBER(Marks!U$5:U$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$BF$5:$BF$39="top")*ISNUMBER(Marks!U$5:U$39))=0,"",SUMPRODUCT((Marks!$BF$5:$BF$39="top")*(Marks!U$5:U$39=1))/SUMPRODUCT((Marks!$BF$5:$BF$39="top")*ISNUMBER(Marks!U$5:U$39)))</f>
         <v/>
       </c>
       <c r="K24" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BC$5:$BC$39="bottom")*ISNUMBER(Marks!U$5:U$39))=0,"",SUMPRODUCT((Marks!$BC$5:$BC$39="bottom")*(Marks!U$5:U$39=1))/SUMPRODUCT((Marks!$BC$5:$BC$39="bottom")*ISNUMBER(Marks!U$5:U$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*ISNUMBER(Marks!U$5:U$39))=0,"",SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*(Marks!U$5:U$39=1))/SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*ISNUMBER(Marks!U$5:U$39)))</f>
         <v/>
       </c>
       <c r="L24" s="6">
@@ -4930,11 +5074,11 @@
         <v/>
       </c>
       <c r="J25" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BC$5:$BC$39="top")*ISNUMBER(Marks!V$5:V$39))=0,"",SUMPRODUCT((Marks!$BC$5:$BC$39="top")*(Marks!V$5:V$39=1))/SUMPRODUCT((Marks!$BC$5:$BC$39="top")*ISNUMBER(Marks!V$5:V$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$BF$5:$BF$39="top")*ISNUMBER(Marks!V$5:V$39))=0,"",SUMPRODUCT((Marks!$BF$5:$BF$39="top")*(Marks!V$5:V$39=1))/SUMPRODUCT((Marks!$BF$5:$BF$39="top")*ISNUMBER(Marks!V$5:V$39)))</f>
         <v/>
       </c>
       <c r="K25" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BC$5:$BC$39="bottom")*ISNUMBER(Marks!V$5:V$39))=0,"",SUMPRODUCT((Marks!$BC$5:$BC$39="bottom")*(Marks!V$5:V$39=1))/SUMPRODUCT((Marks!$BC$5:$BC$39="bottom")*ISNUMBER(Marks!V$5:V$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*ISNUMBER(Marks!V$5:V$39))=0,"",SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*(Marks!V$5:V$39=1))/SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*ISNUMBER(Marks!V$5:V$39)))</f>
         <v/>
       </c>
       <c r="L25" s="6">
@@ -4990,11 +5134,11 @@
         <v/>
       </c>
       <c r="J26" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BC$5:$BC$39="top")*ISNUMBER(Marks!W$5:W$39))=0,"",SUMPRODUCT((Marks!$BC$5:$BC$39="top")*(Marks!W$5:W$39=1))/SUMPRODUCT((Marks!$BC$5:$BC$39="top")*ISNUMBER(Marks!W$5:W$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$BF$5:$BF$39="top")*ISNUMBER(Marks!W$5:W$39))=0,"",SUMPRODUCT((Marks!$BF$5:$BF$39="top")*(Marks!W$5:W$39=1))/SUMPRODUCT((Marks!$BF$5:$BF$39="top")*ISNUMBER(Marks!W$5:W$39)))</f>
         <v/>
       </c>
       <c r="K26" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BC$5:$BC$39="bottom")*ISNUMBER(Marks!W$5:W$39))=0,"",SUMPRODUCT((Marks!$BC$5:$BC$39="bottom")*(Marks!W$5:W$39=1))/SUMPRODUCT((Marks!$BC$5:$BC$39="bottom")*ISNUMBER(Marks!W$5:W$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*ISNUMBER(Marks!W$5:W$39))=0,"",SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*(Marks!W$5:W$39=1))/SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*ISNUMBER(Marks!W$5:W$39)))</f>
         <v/>
       </c>
       <c r="L26" s="6">
@@ -5050,11 +5194,11 @@
         <v/>
       </c>
       <c r="J27" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BC$5:$BC$39="top")*ISNUMBER(Marks!X$5:X$39))=0,"",SUMPRODUCT((Marks!$BC$5:$BC$39="top")*(Marks!X$5:X$39=1))/SUMPRODUCT((Marks!$BC$5:$BC$39="top")*ISNUMBER(Marks!X$5:X$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$BF$5:$BF$39="top")*ISNUMBER(Marks!X$5:X$39))=0,"",SUMPRODUCT((Marks!$BF$5:$BF$39="top")*(Marks!X$5:X$39=1))/SUMPRODUCT((Marks!$BF$5:$BF$39="top")*ISNUMBER(Marks!X$5:X$39)))</f>
         <v/>
       </c>
       <c r="K27" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BC$5:$BC$39="bottom")*ISNUMBER(Marks!X$5:X$39))=0,"",SUMPRODUCT((Marks!$BC$5:$BC$39="bottom")*(Marks!X$5:X$39=1))/SUMPRODUCT((Marks!$BC$5:$BC$39="bottom")*ISNUMBER(Marks!X$5:X$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*ISNUMBER(Marks!X$5:X$39))=0,"",SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*(Marks!X$5:X$39=1))/SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*ISNUMBER(Marks!X$5:X$39)))</f>
         <v/>
       </c>
       <c r="L27" s="6">
@@ -5110,11 +5254,11 @@
         <v/>
       </c>
       <c r="J28" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BC$5:$BC$39="top")*ISNUMBER(Marks!Y$5:Y$39))=0,"",SUMPRODUCT((Marks!$BC$5:$BC$39="top")*(Marks!Y$5:Y$39=1))/SUMPRODUCT((Marks!$BC$5:$BC$39="top")*ISNUMBER(Marks!Y$5:Y$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$BF$5:$BF$39="top")*ISNUMBER(Marks!Y$5:Y$39))=0,"",SUMPRODUCT((Marks!$BF$5:$BF$39="top")*(Marks!Y$5:Y$39=1))/SUMPRODUCT((Marks!$BF$5:$BF$39="top")*ISNUMBER(Marks!Y$5:Y$39)))</f>
         <v/>
       </c>
       <c r="K28" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BC$5:$BC$39="bottom")*ISNUMBER(Marks!Y$5:Y$39))=0,"",SUMPRODUCT((Marks!$BC$5:$BC$39="bottom")*(Marks!Y$5:Y$39=1))/SUMPRODUCT((Marks!$BC$5:$BC$39="bottom")*ISNUMBER(Marks!Y$5:Y$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*ISNUMBER(Marks!Y$5:Y$39))=0,"",SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*(Marks!Y$5:Y$39=1))/SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*ISNUMBER(Marks!Y$5:Y$39)))</f>
         <v/>
       </c>
       <c r="L28" s="6">
@@ -5170,11 +5314,11 @@
         <v/>
       </c>
       <c r="J29" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BC$5:$BC$39="top")*ISNUMBER(Marks!Z$5:Z$39))=0,"",SUMPRODUCT((Marks!$BC$5:$BC$39="top")*(Marks!Z$5:Z$39=1))/SUMPRODUCT((Marks!$BC$5:$BC$39="top")*ISNUMBER(Marks!Z$5:Z$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$BF$5:$BF$39="top")*ISNUMBER(Marks!Z$5:Z$39))=0,"",SUMPRODUCT((Marks!$BF$5:$BF$39="top")*(Marks!Z$5:Z$39=1))/SUMPRODUCT((Marks!$BF$5:$BF$39="top")*ISNUMBER(Marks!Z$5:Z$39)))</f>
         <v/>
       </c>
       <c r="K29" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BC$5:$BC$39="bottom")*ISNUMBER(Marks!Z$5:Z$39))=0,"",SUMPRODUCT((Marks!$BC$5:$BC$39="bottom")*(Marks!Z$5:Z$39=1))/SUMPRODUCT((Marks!$BC$5:$BC$39="bottom")*ISNUMBER(Marks!Z$5:Z$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*ISNUMBER(Marks!Z$5:Z$39))=0,"",SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*(Marks!Z$5:Z$39=1))/SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*ISNUMBER(Marks!Z$5:Z$39)))</f>
         <v/>
       </c>
       <c r="L29" s="6">
@@ -5230,11 +5374,11 @@
         <v/>
       </c>
       <c r="J30" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BC$5:$BC$39="top")*ISNUMBER(Marks!AA$5:AA$39))=0,"",SUMPRODUCT((Marks!$BC$5:$BC$39="top")*(Marks!AA$5:AA$39=1))/SUMPRODUCT((Marks!$BC$5:$BC$39="top")*ISNUMBER(Marks!AA$5:AA$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$BF$5:$BF$39="top")*ISNUMBER(Marks!AA$5:AA$39))=0,"",SUMPRODUCT((Marks!$BF$5:$BF$39="top")*(Marks!AA$5:AA$39=1))/SUMPRODUCT((Marks!$BF$5:$BF$39="top")*ISNUMBER(Marks!AA$5:AA$39)))</f>
         <v/>
       </c>
       <c r="K30" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BC$5:$BC$39="bottom")*ISNUMBER(Marks!AA$5:AA$39))=0,"",SUMPRODUCT((Marks!$BC$5:$BC$39="bottom")*(Marks!AA$5:AA$39=1))/SUMPRODUCT((Marks!$BC$5:$BC$39="bottom")*ISNUMBER(Marks!AA$5:AA$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*ISNUMBER(Marks!AA$5:AA$39))=0,"",SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*(Marks!AA$5:AA$39=1))/SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*ISNUMBER(Marks!AA$5:AA$39)))</f>
         <v/>
       </c>
       <c r="L30" s="6">
@@ -5290,11 +5434,11 @@
         <v/>
       </c>
       <c r="J31" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BC$5:$BC$39="top")*ISNUMBER(Marks!AB$5:AB$39))=0,"",SUMPRODUCT((Marks!$BC$5:$BC$39="top")*(Marks!AB$5:AB$39=1))/SUMPRODUCT((Marks!$BC$5:$BC$39="top")*ISNUMBER(Marks!AB$5:AB$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$BF$5:$BF$39="top")*ISNUMBER(Marks!AB$5:AB$39))=0,"",SUMPRODUCT((Marks!$BF$5:$BF$39="top")*(Marks!AB$5:AB$39=1))/SUMPRODUCT((Marks!$BF$5:$BF$39="top")*ISNUMBER(Marks!AB$5:AB$39)))</f>
         <v/>
       </c>
       <c r="K31" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BC$5:$BC$39="bottom")*ISNUMBER(Marks!AB$5:AB$39))=0,"",SUMPRODUCT((Marks!$BC$5:$BC$39="bottom")*(Marks!AB$5:AB$39=1))/SUMPRODUCT((Marks!$BC$5:$BC$39="bottom")*ISNUMBER(Marks!AB$5:AB$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*ISNUMBER(Marks!AB$5:AB$39))=0,"",SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*(Marks!AB$5:AB$39=1))/SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*ISNUMBER(Marks!AB$5:AB$39)))</f>
         <v/>
       </c>
       <c r="L31" s="6">
@@ -5350,11 +5494,11 @@
         <v/>
       </c>
       <c r="J32" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BC$5:$BC$39="top")*ISNUMBER(Marks!AC$5:AC$39))=0,"",SUMPRODUCT((Marks!$BC$5:$BC$39="top")*(Marks!AC$5:AC$39=1))/SUMPRODUCT((Marks!$BC$5:$BC$39="top")*ISNUMBER(Marks!AC$5:AC$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$BF$5:$BF$39="top")*ISNUMBER(Marks!AC$5:AC$39))=0,"",SUMPRODUCT((Marks!$BF$5:$BF$39="top")*(Marks!AC$5:AC$39=1))/SUMPRODUCT((Marks!$BF$5:$BF$39="top")*ISNUMBER(Marks!AC$5:AC$39)))</f>
         <v/>
       </c>
       <c r="K32" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BC$5:$BC$39="bottom")*ISNUMBER(Marks!AC$5:AC$39))=0,"",SUMPRODUCT((Marks!$BC$5:$BC$39="bottom")*(Marks!AC$5:AC$39=1))/SUMPRODUCT((Marks!$BC$5:$BC$39="bottom")*ISNUMBER(Marks!AC$5:AC$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*ISNUMBER(Marks!AC$5:AC$39))=0,"",SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*(Marks!AC$5:AC$39=1))/SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*ISNUMBER(Marks!AC$5:AC$39)))</f>
         <v/>
       </c>
       <c r="L32" s="6">
@@ -5410,11 +5554,11 @@
         <v/>
       </c>
       <c r="J33" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BC$5:$BC$39="top")*ISNUMBER(Marks!AD$5:AD$39))=0,"",SUMPRODUCT((Marks!$BC$5:$BC$39="top")*(Marks!AD$5:AD$39=1))/SUMPRODUCT((Marks!$BC$5:$BC$39="top")*ISNUMBER(Marks!AD$5:AD$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$BF$5:$BF$39="top")*ISNUMBER(Marks!AD$5:AD$39))=0,"",SUMPRODUCT((Marks!$BF$5:$BF$39="top")*(Marks!AD$5:AD$39=1))/SUMPRODUCT((Marks!$BF$5:$BF$39="top")*ISNUMBER(Marks!AD$5:AD$39)))</f>
         <v/>
       </c>
       <c r="K33" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BC$5:$BC$39="bottom")*ISNUMBER(Marks!AD$5:AD$39))=0,"",SUMPRODUCT((Marks!$BC$5:$BC$39="bottom")*(Marks!AD$5:AD$39=1))/SUMPRODUCT((Marks!$BC$5:$BC$39="bottom")*ISNUMBER(Marks!AD$5:AD$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*ISNUMBER(Marks!AD$5:AD$39))=0,"",SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*(Marks!AD$5:AD$39=1))/SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*ISNUMBER(Marks!AD$5:AD$39)))</f>
         <v/>
       </c>
       <c r="L33" s="6">
@@ -5470,11 +5614,11 @@
         <v/>
       </c>
       <c r="J34" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BC$5:$BC$39="top")*ISNUMBER(Marks!AE$5:AE$39))=0,"",SUMPRODUCT((Marks!$BC$5:$BC$39="top")*(Marks!AE$5:AE$39=1))/SUMPRODUCT((Marks!$BC$5:$BC$39="top")*ISNUMBER(Marks!AE$5:AE$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$BF$5:$BF$39="top")*ISNUMBER(Marks!AE$5:AE$39))=0,"",SUMPRODUCT((Marks!$BF$5:$BF$39="top")*(Marks!AE$5:AE$39=1))/SUMPRODUCT((Marks!$BF$5:$BF$39="top")*ISNUMBER(Marks!AE$5:AE$39)))</f>
         <v/>
       </c>
       <c r="K34" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BC$5:$BC$39="bottom")*ISNUMBER(Marks!AE$5:AE$39))=0,"",SUMPRODUCT((Marks!$BC$5:$BC$39="bottom")*(Marks!AE$5:AE$39=1))/SUMPRODUCT((Marks!$BC$5:$BC$39="bottom")*ISNUMBER(Marks!AE$5:AE$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*ISNUMBER(Marks!AE$5:AE$39))=0,"",SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*(Marks!AE$5:AE$39=1))/SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*ISNUMBER(Marks!AE$5:AE$39)))</f>
         <v/>
       </c>
       <c r="L34" s="6">
@@ -5530,11 +5674,11 @@
         <v/>
       </c>
       <c r="J35" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BC$5:$BC$39="top")*ISNUMBER(Marks!AF$5:AF$39))=0,"",SUMPRODUCT((Marks!$BC$5:$BC$39="top")*(Marks!AF$5:AF$39=1))/SUMPRODUCT((Marks!$BC$5:$BC$39="top")*ISNUMBER(Marks!AF$5:AF$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$BF$5:$BF$39="top")*ISNUMBER(Marks!AF$5:AF$39))=0,"",SUMPRODUCT((Marks!$BF$5:$BF$39="top")*(Marks!AF$5:AF$39=1))/SUMPRODUCT((Marks!$BF$5:$BF$39="top")*ISNUMBER(Marks!AF$5:AF$39)))</f>
         <v/>
       </c>
       <c r="K35" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BC$5:$BC$39="bottom")*ISNUMBER(Marks!AF$5:AF$39))=0,"",SUMPRODUCT((Marks!$BC$5:$BC$39="bottom")*(Marks!AF$5:AF$39=1))/SUMPRODUCT((Marks!$BC$5:$BC$39="bottom")*ISNUMBER(Marks!AF$5:AF$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*ISNUMBER(Marks!AF$5:AF$39))=0,"",SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*(Marks!AF$5:AF$39=1))/SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*ISNUMBER(Marks!AF$5:AF$39)))</f>
         <v/>
       </c>
       <c r="L35" s="6">
@@ -5590,11 +5734,11 @@
         <v/>
       </c>
       <c r="J36" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BC$5:$BC$39="top")*ISNUMBER(Marks!AG$5:AG$39))=0,"",SUMPRODUCT((Marks!$BC$5:$BC$39="top")*(Marks!AG$5:AG$39=1))/SUMPRODUCT((Marks!$BC$5:$BC$39="top")*ISNUMBER(Marks!AG$5:AG$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$BF$5:$BF$39="top")*ISNUMBER(Marks!AG$5:AG$39))=0,"",SUMPRODUCT((Marks!$BF$5:$BF$39="top")*(Marks!AG$5:AG$39=1))/SUMPRODUCT((Marks!$BF$5:$BF$39="top")*ISNUMBER(Marks!AG$5:AG$39)))</f>
         <v/>
       </c>
       <c r="K36" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BC$5:$BC$39="bottom")*ISNUMBER(Marks!AG$5:AG$39))=0,"",SUMPRODUCT((Marks!$BC$5:$BC$39="bottom")*(Marks!AG$5:AG$39=1))/SUMPRODUCT((Marks!$BC$5:$BC$39="bottom")*ISNUMBER(Marks!AG$5:AG$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*ISNUMBER(Marks!AG$5:AG$39))=0,"",SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*(Marks!AG$5:AG$39=1))/SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*ISNUMBER(Marks!AG$5:AG$39)))</f>
         <v/>
       </c>
       <c r="L36" s="6">
@@ -5619,12 +5763,12 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>One correct option</t>
+          <t>Scenario set</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -5634,7 +5778,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>c</t>
+          <t>d</t>
         </is>
       </c>
       <c r="G37">
@@ -5650,11 +5794,11 @@
         <v/>
       </c>
       <c r="J37" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BC$5:$BC$39="top")*ISNUMBER(Marks!AH$5:AH$39))=0,"",SUMPRODUCT((Marks!$BC$5:$BC$39="top")*(Marks!AH$5:AH$39=1))/SUMPRODUCT((Marks!$BC$5:$BC$39="top")*ISNUMBER(Marks!AH$5:AH$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$BF$5:$BF$39="top")*ISNUMBER(Marks!AH$5:AH$39))=0,"",SUMPRODUCT((Marks!$BF$5:$BF$39="top")*(Marks!AH$5:AH$39=1))/SUMPRODUCT((Marks!$BF$5:$BF$39="top")*ISNUMBER(Marks!AH$5:AH$39)))</f>
         <v/>
       </c>
       <c r="K37" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BC$5:$BC$39="bottom")*ISNUMBER(Marks!AH$5:AH$39))=0,"",SUMPRODUCT((Marks!$BC$5:$BC$39="bottom")*(Marks!AH$5:AH$39=1))/SUMPRODUCT((Marks!$BC$5:$BC$39="bottom")*ISNUMBER(Marks!AH$5:AH$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*ISNUMBER(Marks!AH$5:AH$39))=0,"",SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*(Marks!AH$5:AH$39=1))/SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*ISNUMBER(Marks!AH$5:AH$39)))</f>
         <v/>
       </c>
       <c r="L37" s="6">
@@ -5684,17 +5828,17 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>Hard</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>[S]</t>
+          <t>[D]</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2.00 (or 2)</t>
+          <t>b</t>
         </is>
       </c>
       <c r="G38">
@@ -5710,11 +5854,11 @@
         <v/>
       </c>
       <c r="J38" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BC$5:$BC$39="top")*ISNUMBER(Marks!AI$5:AI$39))=0,"",SUMPRODUCT((Marks!$BC$5:$BC$39="top")*(Marks!AI$5:AI$39=1))/SUMPRODUCT((Marks!$BC$5:$BC$39="top")*ISNUMBER(Marks!AI$5:AI$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$BF$5:$BF$39="top")*ISNUMBER(Marks!AI$5:AI$39))=0,"",SUMPRODUCT((Marks!$BF$5:$BF$39="top")*(Marks!AI$5:AI$39=1))/SUMPRODUCT((Marks!$BF$5:$BF$39="top")*ISNUMBER(Marks!AI$5:AI$39)))</f>
         <v/>
       </c>
       <c r="K38" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BC$5:$BC$39="bottom")*ISNUMBER(Marks!AI$5:AI$39))=0,"",SUMPRODUCT((Marks!$BC$5:$BC$39="bottom")*(Marks!AI$5:AI$39=1))/SUMPRODUCT((Marks!$BC$5:$BC$39="bottom")*ISNUMBER(Marks!AI$5:AI$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*ISNUMBER(Marks!AI$5:AI$39))=0,"",SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*(Marks!AI$5:AI$39=1))/SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*ISNUMBER(Marks!AI$5:AI$39)))</f>
         <v/>
       </c>
       <c r="L38" s="6">
@@ -5744,7 +5888,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Easy</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -5754,7 +5898,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>4,000 (Rs 4,000)</t>
+          <t>2.00 (or 2)</t>
         </is>
       </c>
       <c r="G39">
@@ -5770,11 +5914,11 @@
         <v/>
       </c>
       <c r="J39" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BC$5:$BC$39="top")*ISNUMBER(Marks!AJ$5:AJ$39))=0,"",SUMPRODUCT((Marks!$BC$5:$BC$39="top")*(Marks!AJ$5:AJ$39=1))/SUMPRODUCT((Marks!$BC$5:$BC$39="top")*ISNUMBER(Marks!AJ$5:AJ$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$BF$5:$BF$39="top")*ISNUMBER(Marks!AJ$5:AJ$39))=0,"",SUMPRODUCT((Marks!$BF$5:$BF$39="top")*(Marks!AJ$5:AJ$39=1))/SUMPRODUCT((Marks!$BF$5:$BF$39="top")*ISNUMBER(Marks!AJ$5:AJ$39)))</f>
         <v/>
       </c>
       <c r="K39" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BC$5:$BC$39="bottom")*ISNUMBER(Marks!AJ$5:AJ$39))=0,"",SUMPRODUCT((Marks!$BC$5:$BC$39="bottom")*(Marks!AJ$5:AJ$39=1))/SUMPRODUCT((Marks!$BC$5:$BC$39="bottom")*ISNUMBER(Marks!AJ$5:AJ$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*ISNUMBER(Marks!AJ$5:AJ$39))=0,"",SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*(Marks!AJ$5:AJ$39=1))/SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*ISNUMBER(Marks!AJ$5:AJ$39)))</f>
         <v/>
       </c>
       <c r="L39" s="6">
@@ -5804,17 +5948,17 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Hard</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>[D]</t>
+          <t>[S]</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>c</t>
+          <t>4,000 (Rs 4,000)</t>
         </is>
       </c>
       <c r="G40">
@@ -5830,11 +5974,11 @@
         <v/>
       </c>
       <c r="J40" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BC$5:$BC$39="top")*ISNUMBER(Marks!AK$5:AK$39))=0,"",SUMPRODUCT((Marks!$BC$5:$BC$39="top")*(Marks!AK$5:AK$39=1))/SUMPRODUCT((Marks!$BC$5:$BC$39="top")*ISNUMBER(Marks!AK$5:AK$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$BF$5:$BF$39="top")*ISNUMBER(Marks!AK$5:AK$39))=0,"",SUMPRODUCT((Marks!$BF$5:$BF$39="top")*(Marks!AK$5:AK$39=1))/SUMPRODUCT((Marks!$BF$5:$BF$39="top")*ISNUMBER(Marks!AK$5:AK$39)))</f>
         <v/>
       </c>
       <c r="K40" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BC$5:$BC$39="bottom")*ISNUMBER(Marks!AK$5:AK$39))=0,"",SUMPRODUCT((Marks!$BC$5:$BC$39="bottom")*(Marks!AK$5:AK$39=1))/SUMPRODUCT((Marks!$BC$5:$BC$39="bottom")*ISNUMBER(Marks!AK$5:AK$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*ISNUMBER(Marks!AK$5:AK$39))=0,"",SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*(Marks!AK$5:AK$39=1))/SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*ISNUMBER(Marks!AK$5:AK$39)))</f>
         <v/>
       </c>
       <c r="L40" s="6">
@@ -5864,17 +6008,17 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Hard</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>[F]</t>
+          <t>[D]</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>d</t>
+          <t>c</t>
         </is>
       </c>
       <c r="G41">
@@ -5890,11 +6034,11 @@
         <v/>
       </c>
       <c r="J41" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BC$5:$BC$39="top")*ISNUMBER(Marks!AL$5:AL$39))=0,"",SUMPRODUCT((Marks!$BC$5:$BC$39="top")*(Marks!AL$5:AL$39=1))/SUMPRODUCT((Marks!$BC$5:$BC$39="top")*ISNUMBER(Marks!AL$5:AL$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$BF$5:$BF$39="top")*ISNUMBER(Marks!AL$5:AL$39))=0,"",SUMPRODUCT((Marks!$BF$5:$BF$39="top")*(Marks!AL$5:AL$39=1))/SUMPRODUCT((Marks!$BF$5:$BF$39="top")*ISNUMBER(Marks!AL$5:AL$39)))</f>
         <v/>
       </c>
       <c r="K41" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BC$5:$BC$39="bottom")*ISNUMBER(Marks!AL$5:AL$39))=0,"",SUMPRODUCT((Marks!$BC$5:$BC$39="bottom")*(Marks!AL$5:AL$39=1))/SUMPRODUCT((Marks!$BC$5:$BC$39="bottom")*ISNUMBER(Marks!AL$5:AL$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*ISNUMBER(Marks!AL$5:AL$39))=0,"",SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*(Marks!AL$5:AL$39=1))/SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*ISNUMBER(Marks!AL$5:AL$39)))</f>
         <v/>
       </c>
       <c r="L41" s="6">
@@ -5919,22 +6063,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Scenario set</t>
+          <t>One correct option</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Hard</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>[D]</t>
+          <t>[S]</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>d</t>
         </is>
       </c>
       <c r="G42">
@@ -5950,11 +6094,11 @@
         <v/>
       </c>
       <c r="J42" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BC$5:$BC$39="top")*ISNUMBER(Marks!AM$5:AM$39))=0,"",SUMPRODUCT((Marks!$BC$5:$BC$39="top")*(Marks!AM$5:AM$39=1))/SUMPRODUCT((Marks!$BC$5:$BC$39="top")*ISNUMBER(Marks!AM$5:AM$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$BF$5:$BF$39="top")*ISNUMBER(Marks!AM$5:AM$39))=0,"",SUMPRODUCT((Marks!$BF$5:$BF$39="top")*(Marks!AM$5:AM$39=1))/SUMPRODUCT((Marks!$BF$5:$BF$39="top")*ISNUMBER(Marks!AM$5:AM$39)))</f>
         <v/>
       </c>
       <c r="K42" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BC$5:$BC$39="bottom")*ISNUMBER(Marks!AM$5:AM$39))=0,"",SUMPRODUCT((Marks!$BC$5:$BC$39="bottom")*(Marks!AM$5:AM$39=1))/SUMPRODUCT((Marks!$BC$5:$BC$39="bottom")*ISNUMBER(Marks!AM$5:AM$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*ISNUMBER(Marks!AM$5:AM$39))=0,"",SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*(Marks!AM$5:AM$39=1))/SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*ISNUMBER(Marks!AM$5:AM$39)))</f>
         <v/>
       </c>
       <c r="L42" s="6">
@@ -5975,7 +6119,7 @@
         <v>39</v>
       </c>
       <c r="B43" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5984,12 +6128,12 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Hard</t>
+          <t>Easy</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>[S]</t>
+          <t>[F]</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -6010,11 +6154,11 @@
         <v/>
       </c>
       <c r="J43" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BC$5:$BC$39="top")*ISNUMBER(Marks!AN$5:AN$39))=0,"",SUMPRODUCT((Marks!$BC$5:$BC$39="top")*(Marks!AN$5:AN$39=1))/SUMPRODUCT((Marks!$BC$5:$BC$39="top")*ISNUMBER(Marks!AN$5:AN$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$BF$5:$BF$39="top")*ISNUMBER(Marks!AN$5:AN$39))=0,"",SUMPRODUCT((Marks!$BF$5:$BF$39="top")*(Marks!AN$5:AN$39=1))/SUMPRODUCT((Marks!$BF$5:$BF$39="top")*ISNUMBER(Marks!AN$5:AN$39)))</f>
         <v/>
       </c>
       <c r="K43" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BC$5:$BC$39="bottom")*ISNUMBER(Marks!AN$5:AN$39))=0,"",SUMPRODUCT((Marks!$BC$5:$BC$39="bottom")*(Marks!AN$5:AN$39=1))/SUMPRODUCT((Marks!$BC$5:$BC$39="bottom")*ISNUMBER(Marks!AN$5:AN$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*ISNUMBER(Marks!AN$5:AN$39))=0,"",SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*(Marks!AN$5:AN$39=1))/SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*ISNUMBER(Marks!AN$5:AN$39)))</f>
         <v/>
       </c>
       <c r="L43" s="6">
@@ -6035,7 +6179,7 @@
         <v>40</v>
       </c>
       <c r="B44" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -6044,7 +6188,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>Hard</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -6070,11 +6214,11 @@
         <v/>
       </c>
       <c r="J44" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BC$5:$BC$39="top")*ISNUMBER(Marks!AO$5:AO$39))=0,"",SUMPRODUCT((Marks!$BC$5:$BC$39="top")*(Marks!AO$5:AO$39=1))/SUMPRODUCT((Marks!$BC$5:$BC$39="top")*ISNUMBER(Marks!AO$5:AO$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$BF$5:$BF$39="top")*ISNUMBER(Marks!AO$5:AO$39))=0,"",SUMPRODUCT((Marks!$BF$5:$BF$39="top")*(Marks!AO$5:AO$39=1))/SUMPRODUCT((Marks!$BF$5:$BF$39="top")*ISNUMBER(Marks!AO$5:AO$39)))</f>
         <v/>
       </c>
       <c r="K44" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BC$5:$BC$39="bottom")*ISNUMBER(Marks!AO$5:AO$39))=0,"",SUMPRODUCT((Marks!$BC$5:$BC$39="bottom")*(Marks!AO$5:AO$39=1))/SUMPRODUCT((Marks!$BC$5:$BC$39="bottom")*ISNUMBER(Marks!AO$5:AO$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*ISNUMBER(Marks!AO$5:AO$39))=0,"",SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*(Marks!AO$5:AO$39=1))/SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*ISNUMBER(Marks!AO$5:AO$39)))</f>
         <v/>
       </c>
       <c r="L44" s="6">
@@ -6095,16 +6239,16 @@
         <v>41</v>
       </c>
       <c r="B45" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>More than one correct</t>
+          <t>One correct option</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Hard</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -6114,7 +6258,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>a, b, c</t>
+          <t>a</t>
         </is>
       </c>
       <c r="G45">
@@ -6130,11 +6274,11 @@
         <v/>
       </c>
       <c r="J45" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BC$5:$BC$39="top")*ISNUMBER(Marks!AP$5:AP$39))=0,"",SUMPRODUCT((Marks!$BC$5:$BC$39="top")*(Marks!AP$5:AP$39=1))/SUMPRODUCT((Marks!$BC$5:$BC$39="top")*ISNUMBER(Marks!AP$5:AP$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$BF$5:$BF$39="top")*ISNUMBER(Marks!AP$5:AP$39))=0,"",SUMPRODUCT((Marks!$BF$5:$BF$39="top")*(Marks!AP$5:AP$39=1))/SUMPRODUCT((Marks!$BF$5:$BF$39="top")*ISNUMBER(Marks!AP$5:AP$39)))</f>
         <v/>
       </c>
       <c r="K45" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BC$5:$BC$39="bottom")*ISNUMBER(Marks!AP$5:AP$39))=0,"",SUMPRODUCT((Marks!$BC$5:$BC$39="bottom")*(Marks!AP$5:AP$39=1))/SUMPRODUCT((Marks!$BC$5:$BC$39="bottom")*ISNUMBER(Marks!AP$5:AP$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*ISNUMBER(Marks!AP$5:AP$39))=0,"",SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*(Marks!AP$5:AP$39=1))/SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*ISNUMBER(Marks!AP$5:AP$39)))</f>
         <v/>
       </c>
       <c r="L45" s="6">
@@ -6159,7 +6303,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>More than one correct</t>
+          <t>One correct option</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6174,7 +6318,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>a, b, d</t>
+          <t>c</t>
         </is>
       </c>
       <c r="G46">
@@ -6190,11 +6334,11 @@
         <v/>
       </c>
       <c r="J46" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BC$5:$BC$39="top")*ISNUMBER(Marks!AQ$5:AQ$39))=0,"",SUMPRODUCT((Marks!$BC$5:$BC$39="top")*(Marks!AQ$5:AQ$39=1))/SUMPRODUCT((Marks!$BC$5:$BC$39="top")*ISNUMBER(Marks!AQ$5:AQ$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$BF$5:$BF$39="top")*ISNUMBER(Marks!AQ$5:AQ$39))=0,"",SUMPRODUCT((Marks!$BF$5:$BF$39="top")*(Marks!AQ$5:AQ$39=1))/SUMPRODUCT((Marks!$BF$5:$BF$39="top")*ISNUMBER(Marks!AQ$5:AQ$39)))</f>
         <v/>
       </c>
       <c r="K46" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BC$5:$BC$39="bottom")*ISNUMBER(Marks!AQ$5:AQ$39))=0,"",SUMPRODUCT((Marks!$BC$5:$BC$39="bottom")*(Marks!AQ$5:AQ$39=1))/SUMPRODUCT((Marks!$BC$5:$BC$39="bottom")*ISNUMBER(Marks!AQ$5:AQ$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*ISNUMBER(Marks!AQ$5:AQ$39))=0,"",SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*(Marks!AQ$5:AQ$39=1))/SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*ISNUMBER(Marks!AQ$5:AQ$39)))</f>
         <v/>
       </c>
       <c r="L46" s="6">
@@ -6219,22 +6363,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Scenario set</t>
+          <t>One correct option</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Hard</t>
+          <t>Easy</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>[D]</t>
+          <t>[F]</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>a</t>
+          <t>b</t>
         </is>
       </c>
       <c r="G47">
@@ -6250,11 +6394,11 @@
         <v/>
       </c>
       <c r="J47" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BC$5:$BC$39="top")*ISNUMBER(Marks!AR$5:AR$39))=0,"",SUMPRODUCT((Marks!$BC$5:$BC$39="top")*(Marks!AR$5:AR$39=1))/SUMPRODUCT((Marks!$BC$5:$BC$39="top")*ISNUMBER(Marks!AR$5:AR$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$BF$5:$BF$39="top")*ISNUMBER(Marks!AR$5:AR$39))=0,"",SUMPRODUCT((Marks!$BF$5:$BF$39="top")*(Marks!AR$5:AR$39=1))/SUMPRODUCT((Marks!$BF$5:$BF$39="top")*ISNUMBER(Marks!AR$5:AR$39)))</f>
         <v/>
       </c>
       <c r="K47" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BC$5:$BC$39="bottom")*ISNUMBER(Marks!AR$5:AR$39))=0,"",SUMPRODUCT((Marks!$BC$5:$BC$39="bottom")*(Marks!AR$5:AR$39=1))/SUMPRODUCT((Marks!$BC$5:$BC$39="bottom")*ISNUMBER(Marks!AR$5:AR$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*ISNUMBER(Marks!AR$5:AR$39))=0,"",SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*(Marks!AR$5:AR$39=1))/SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*ISNUMBER(Marks!AR$5:AR$39)))</f>
         <v/>
       </c>
       <c r="L47" s="6">
@@ -6279,7 +6423,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Scenario set</t>
+          <t>More than one correct</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6294,7 +6438,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>a, b, c</t>
         </is>
       </c>
       <c r="G48">
@@ -6310,11 +6454,11 @@
         <v/>
       </c>
       <c r="J48" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BC$5:$BC$39="top")*ISNUMBER(Marks!AS$5:AS$39))=0,"",SUMPRODUCT((Marks!$BC$5:$BC$39="top")*(Marks!AS$5:AS$39=1))/SUMPRODUCT((Marks!$BC$5:$BC$39="top")*ISNUMBER(Marks!AS$5:AS$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$BF$5:$BF$39="top")*ISNUMBER(Marks!AS$5:AS$39))=0,"",SUMPRODUCT((Marks!$BF$5:$BF$39="top")*(Marks!AS$5:AS$39=1))/SUMPRODUCT((Marks!$BF$5:$BF$39="top")*ISNUMBER(Marks!AS$5:AS$39)))</f>
         <v/>
       </c>
       <c r="K48" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BC$5:$BC$39="bottom")*ISNUMBER(Marks!AS$5:AS$39))=0,"",SUMPRODUCT((Marks!$BC$5:$BC$39="bottom")*(Marks!AS$5:AS$39=1))/SUMPRODUCT((Marks!$BC$5:$BC$39="bottom")*ISNUMBER(Marks!AS$5:AS$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*ISNUMBER(Marks!AS$5:AS$39))=0,"",SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*(Marks!AS$5:AS$39=1))/SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*ISNUMBER(Marks!AS$5:AS$39)))</f>
         <v/>
       </c>
       <c r="L48" s="6">
@@ -6339,7 +6483,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Scenario set</t>
+          <t>More than one correct</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6349,12 +6493,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>[D]</t>
+          <t>[S]</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>d</t>
+          <t>a, b, d</t>
         </is>
       </c>
       <c r="G49">
@@ -6370,11 +6514,11 @@
         <v/>
       </c>
       <c r="J49" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BC$5:$BC$39="top")*ISNUMBER(Marks!AT$5:AT$39))=0,"",SUMPRODUCT((Marks!$BC$5:$BC$39="top")*(Marks!AT$5:AT$39=1))/SUMPRODUCT((Marks!$BC$5:$BC$39="top")*ISNUMBER(Marks!AT$5:AT$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$BF$5:$BF$39="top")*ISNUMBER(Marks!AT$5:AT$39))=0,"",SUMPRODUCT((Marks!$BF$5:$BF$39="top")*(Marks!AT$5:AT$39=1))/SUMPRODUCT((Marks!$BF$5:$BF$39="top")*ISNUMBER(Marks!AT$5:AT$39)))</f>
         <v/>
       </c>
       <c r="K49" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BC$5:$BC$39="bottom")*ISNUMBER(Marks!AT$5:AT$39))=0,"",SUMPRODUCT((Marks!$BC$5:$BC$39="bottom")*(Marks!AT$5:AT$39=1))/SUMPRODUCT((Marks!$BC$5:$BC$39="bottom")*ISNUMBER(Marks!AT$5:AT$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*ISNUMBER(Marks!AT$5:AT$39))=0,"",SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*(Marks!AT$5:AT$39=1))/SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*ISNUMBER(Marks!AT$5:AT$39)))</f>
         <v/>
       </c>
       <c r="L49" s="6">
@@ -6395,26 +6539,26 @@
         <v>46</v>
       </c>
       <c r="B50" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>One correct option</t>
+          <t>Scenario set</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>Hard</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>[S]</t>
+          <t>[D]</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>d</t>
+          <t>a</t>
         </is>
       </c>
       <c r="G50">
@@ -6430,11 +6574,11 @@
         <v/>
       </c>
       <c r="J50" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BC$5:$BC$39="top")*ISNUMBER(Marks!AU$5:AU$39))=0,"",SUMPRODUCT((Marks!$BC$5:$BC$39="top")*(Marks!AU$5:AU$39=1))/SUMPRODUCT((Marks!$BC$5:$BC$39="top")*ISNUMBER(Marks!AU$5:AU$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$BF$5:$BF$39="top")*ISNUMBER(Marks!AU$5:AU$39))=0,"",SUMPRODUCT((Marks!$BF$5:$BF$39="top")*(Marks!AU$5:AU$39=1))/SUMPRODUCT((Marks!$BF$5:$BF$39="top")*ISNUMBER(Marks!AU$5:AU$39)))</f>
         <v/>
       </c>
       <c r="K50" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BC$5:$BC$39="bottom")*ISNUMBER(Marks!AU$5:AU$39))=0,"",SUMPRODUCT((Marks!$BC$5:$BC$39="bottom")*(Marks!AU$5:AU$39=1))/SUMPRODUCT((Marks!$BC$5:$BC$39="bottom")*ISNUMBER(Marks!AU$5:AU$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*ISNUMBER(Marks!AU$5:AU$39))=0,"",SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*(Marks!AU$5:AU$39=1))/SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*ISNUMBER(Marks!AU$5:AU$39)))</f>
         <v/>
       </c>
       <c r="L50" s="6">
@@ -6455,16 +6599,16 @@
         <v>47</v>
       </c>
       <c r="B51" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Applied maths</t>
+          <t>Scenario set</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Hard</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -6474,7 +6618,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Revenue falls by 6.5 percent (1.10 x 0.85 = 0.935).</t>
+          <t>True</t>
         </is>
       </c>
       <c r="G51">
@@ -6490,11 +6634,11 @@
         <v/>
       </c>
       <c r="J51" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BC$5:$BC$39="top")*ISNUMBER(Marks!AV$5:AV$39))=0,"",SUMPRODUCT((Marks!$BC$5:$BC$39="top")*(Marks!AV$5:AV$39=1))/SUMPRODUCT((Marks!$BC$5:$BC$39="top")*ISNUMBER(Marks!AV$5:AV$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$BF$5:$BF$39="top")*ISNUMBER(Marks!AV$5:AV$39))=0,"",SUMPRODUCT((Marks!$BF$5:$BF$39="top")*(Marks!AV$5:AV$39=1))/SUMPRODUCT((Marks!$BF$5:$BF$39="top")*ISNUMBER(Marks!AV$5:AV$39)))</f>
         <v/>
       </c>
       <c r="K51" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BC$5:$BC$39="bottom")*ISNUMBER(Marks!AV$5:AV$39))=0,"",SUMPRODUCT((Marks!$BC$5:$BC$39="bottom")*(Marks!AV$5:AV$39=1))/SUMPRODUCT((Marks!$BC$5:$BC$39="bottom")*ISNUMBER(Marks!AV$5:AV$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*ISNUMBER(Marks!AV$5:AV$39))=0,"",SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*(Marks!AV$5:AV$39=1))/SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*ISNUMBER(Marks!AV$5:AV$39)))</f>
         <v/>
       </c>
       <c r="L51" s="6">
@@ -6515,26 +6659,26 @@
         <v>48</v>
       </c>
       <c r="B52" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Applied maths</t>
+          <t>Scenario set</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>Hard</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>[S]</t>
+          <t>[D]</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Median Rs 1,400; mean Rs 97,080.</t>
+          <t>d</t>
         </is>
       </c>
       <c r="G52">
@@ -6550,11 +6694,11 @@
         <v/>
       </c>
       <c r="J52" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BC$5:$BC$39="top")*ISNUMBER(Marks!AW$5:AW$39))=0,"",SUMPRODUCT((Marks!$BC$5:$BC$39="top")*(Marks!AW$5:AW$39=1))/SUMPRODUCT((Marks!$BC$5:$BC$39="top")*ISNUMBER(Marks!AW$5:AW$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$BF$5:$BF$39="top")*ISNUMBER(Marks!AW$5:AW$39))=0,"",SUMPRODUCT((Marks!$BF$5:$BF$39="top")*(Marks!AW$5:AW$39=1))/SUMPRODUCT((Marks!$BF$5:$BF$39="top")*ISNUMBER(Marks!AW$5:AW$39)))</f>
         <v/>
       </c>
       <c r="K52" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BC$5:$BC$39="bottom")*ISNUMBER(Marks!AW$5:AW$39))=0,"",SUMPRODUCT((Marks!$BC$5:$BC$39="bottom")*(Marks!AW$5:AW$39=1))/SUMPRODUCT((Marks!$BC$5:$BC$39="bottom")*ISNUMBER(Marks!AW$5:AW$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*ISNUMBER(Marks!AW$5:AW$39))=0,"",SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*(Marks!AW$5:AW$39=1))/SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*ISNUMBER(Marks!AW$5:AW$39)))</f>
         <v/>
       </c>
       <c r="L52" s="6">
@@ -6579,7 +6723,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Applied maths</t>
+          <t>One correct option</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6594,7 +6738,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>A fall of 9.5 percent ((1.9 - 2.1) / 2.1).</t>
+          <t>d</t>
         </is>
       </c>
       <c r="G53">
@@ -6610,11 +6754,11 @@
         <v/>
       </c>
       <c r="J53" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BC$5:$BC$39="top")*ISNUMBER(Marks!AX$5:AX$39))=0,"",SUMPRODUCT((Marks!$BC$5:$BC$39="top")*(Marks!AX$5:AX$39=1))/SUMPRODUCT((Marks!$BC$5:$BC$39="top")*ISNUMBER(Marks!AX$5:AX$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$BF$5:$BF$39="top")*ISNUMBER(Marks!AX$5:AX$39))=0,"",SUMPRODUCT((Marks!$BF$5:$BF$39="top")*(Marks!AX$5:AX$39=1))/SUMPRODUCT((Marks!$BF$5:$BF$39="top")*ISNUMBER(Marks!AX$5:AX$39)))</f>
         <v/>
       </c>
       <c r="K53" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BC$5:$BC$39="bottom")*ISNUMBER(Marks!AX$5:AX$39))=0,"",SUMPRODUCT((Marks!$BC$5:$BC$39="bottom")*(Marks!AX$5:AX$39=1))/SUMPRODUCT((Marks!$BC$5:$BC$39="bottom")*ISNUMBER(Marks!AX$5:AX$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*ISNUMBER(Marks!AX$5:AX$39))=0,"",SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*(Marks!AX$5:AX$39=1))/SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*ISNUMBER(Marks!AX$5:AX$39)))</f>
         <v/>
       </c>
       <c r="L53" s="6">
@@ -6644,17 +6788,17 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Hard</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>[S]</t>
+          <t>[F]</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>0.028 (140 / 5,000).</t>
+          <t>Revenue falls by 6.5 percent (1.10 x 0.85 = 0.935).</t>
         </is>
       </c>
       <c r="G54">
@@ -6670,11 +6814,11 @@
         <v/>
       </c>
       <c r="J54" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BC$5:$BC$39="top")*ISNUMBER(Marks!AY$5:AY$39))=0,"",SUMPRODUCT((Marks!$BC$5:$BC$39="top")*(Marks!AY$5:AY$39=1))/SUMPRODUCT((Marks!$BC$5:$BC$39="top")*ISNUMBER(Marks!AY$5:AY$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$BF$5:$BF$39="top")*ISNUMBER(Marks!AY$5:AY$39))=0,"",SUMPRODUCT((Marks!$BF$5:$BF$39="top")*(Marks!AY$5:AY$39=1))/SUMPRODUCT((Marks!$BF$5:$BF$39="top")*ISNUMBER(Marks!AY$5:AY$39)))</f>
         <v/>
       </c>
       <c r="K54" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BC$5:$BC$39="bottom")*ISNUMBER(Marks!AY$5:AY$39))=0,"",SUMPRODUCT((Marks!$BC$5:$BC$39="bottom")*(Marks!AY$5:AY$39=1))/SUMPRODUCT((Marks!$BC$5:$BC$39="bottom")*ISNUMBER(Marks!AY$5:AY$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*ISNUMBER(Marks!AY$5:AY$39))=0,"",SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*(Marks!AY$5:AY$39=1))/SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*ISNUMBER(Marks!AY$5:AY$39)))</f>
         <v/>
       </c>
       <c r="L54" s="6">
@@ -6704,7 +6848,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Easy</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -6714,7 +6858,7 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Rs 11 crore (Rs 12 crore before discounts).</t>
+          <t>Median Rs 1,400; mean Rs 97,080.</t>
         </is>
       </c>
       <c r="G55">
@@ -6730,11 +6874,11 @@
         <v/>
       </c>
       <c r="J55" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BC$5:$BC$39="top")*ISNUMBER(Marks!AZ$5:AZ$39))=0,"",SUMPRODUCT((Marks!$BC$5:$BC$39="top")*(Marks!AZ$5:AZ$39=1))/SUMPRODUCT((Marks!$BC$5:$BC$39="top")*ISNUMBER(Marks!AZ$5:AZ$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$BF$5:$BF$39="top")*ISNUMBER(Marks!AZ$5:AZ$39))=0,"",SUMPRODUCT((Marks!$BF$5:$BF$39="top")*(Marks!AZ$5:AZ$39=1))/SUMPRODUCT((Marks!$BF$5:$BF$39="top")*ISNUMBER(Marks!AZ$5:AZ$39)))</f>
         <v/>
       </c>
       <c r="K55" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BC$5:$BC$39="bottom")*ISNUMBER(Marks!AZ$5:AZ$39))=0,"",SUMPRODUCT((Marks!$BC$5:$BC$39="bottom")*(Marks!AZ$5:AZ$39=1))/SUMPRODUCT((Marks!$BC$5:$BC$39="bottom")*ISNUMBER(Marks!AZ$5:AZ$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*ISNUMBER(Marks!AZ$5:AZ$39))=0,"",SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*(Marks!AZ$5:AZ$39=1))/SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*ISNUMBER(Marks!AZ$5:AZ$39)))</f>
         <v/>
       </c>
       <c r="L55" s="6">
@@ -6747,6 +6891,186 @@
       </c>
       <c r="N55">
         <f>IF(H55=0,"",I55+ROW()/1000000)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>52</v>
+      </c>
+      <c r="B56" t="n">
+        <v>6</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Applied maths</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>[S]</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>A fall of 9.5 percent ((1.9 - 2.1) / 2.1).</t>
+        </is>
+      </c>
+      <c r="G56">
+        <f>COUNTIF(Marks!BA$5:BA$39,1)</f>
+        <v/>
+      </c>
+      <c r="H56">
+        <f>COUNT(Marks!BA$5:BA$39)</f>
+        <v/>
+      </c>
+      <c r="I56" s="6">
+        <f>IF(H56=0,"",G56/H56)</f>
+        <v/>
+      </c>
+      <c r="J56" s="6">
+        <f>IF(SUMPRODUCT((Marks!$BF$5:$BF$39="top")*ISNUMBER(Marks!BA$5:BA$39))=0,"",SUMPRODUCT((Marks!$BF$5:$BF$39="top")*(Marks!BA$5:BA$39=1))/SUMPRODUCT((Marks!$BF$5:$BF$39="top")*ISNUMBER(Marks!BA$5:BA$39)))</f>
+        <v/>
+      </c>
+      <c r="K56" s="6">
+        <f>IF(SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*ISNUMBER(Marks!BA$5:BA$39))=0,"",SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*(Marks!BA$5:BA$39=1))/SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*ISNUMBER(Marks!BA$5:BA$39)))</f>
+        <v/>
+      </c>
+      <c r="L56" s="6">
+        <f>IF(OR(J56="",K56=""),"",J56-K56)</f>
+        <v/>
+      </c>
+      <c r="M56">
+        <f>IF(H56=0,"",IF(I56&lt;0.2,"Check the item: fewer than one in five got it right",IF(AND(L56&lt;&gt;"",N(L56)&lt;0),"Check the item: the bottom third beat the top third","")))</f>
+        <v/>
+      </c>
+      <c r="N56">
+        <f>IF(H56=0,"",I56+ROW()/1000000)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>53</v>
+      </c>
+      <c r="B57" t="n">
+        <v>6</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Applied maths</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>[S]</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>0.028 (140 / 5,000).</t>
+        </is>
+      </c>
+      <c r="G57">
+        <f>COUNTIF(Marks!BB$5:BB$39,1)</f>
+        <v/>
+      </c>
+      <c r="H57">
+        <f>COUNT(Marks!BB$5:BB$39)</f>
+        <v/>
+      </c>
+      <c r="I57" s="6">
+        <f>IF(H57=0,"",G57/H57)</f>
+        <v/>
+      </c>
+      <c r="J57" s="6">
+        <f>IF(SUMPRODUCT((Marks!$BF$5:$BF$39="top")*ISNUMBER(Marks!BB$5:BB$39))=0,"",SUMPRODUCT((Marks!$BF$5:$BF$39="top")*(Marks!BB$5:BB$39=1))/SUMPRODUCT((Marks!$BF$5:$BF$39="top")*ISNUMBER(Marks!BB$5:BB$39)))</f>
+        <v/>
+      </c>
+      <c r="K57" s="6">
+        <f>IF(SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*ISNUMBER(Marks!BB$5:BB$39))=0,"",SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*(Marks!BB$5:BB$39=1))/SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*ISNUMBER(Marks!BB$5:BB$39)))</f>
+        <v/>
+      </c>
+      <c r="L57" s="6">
+        <f>IF(OR(J57="",K57=""),"",J57-K57)</f>
+        <v/>
+      </c>
+      <c r="M57">
+        <f>IF(H57=0,"",IF(I57&lt;0.2,"Check the item: fewer than one in five got it right",IF(AND(L57&lt;&gt;"",N(L57)&lt;0),"Check the item: the bottom third beat the top third","")))</f>
+        <v/>
+      </c>
+      <c r="N57">
+        <f>IF(H57=0,"",I57+ROW()/1000000)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>54</v>
+      </c>
+      <c r="B58" t="n">
+        <v>6</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Applied maths</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>[S]</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Rs 11 crore (Rs 12 crore before discounts).</t>
+        </is>
+      </c>
+      <c r="G58">
+        <f>COUNTIF(Marks!BC$5:BC$39,1)</f>
+        <v/>
+      </c>
+      <c r="H58">
+        <f>COUNT(Marks!BC$5:BC$39)</f>
+        <v/>
+      </c>
+      <c r="I58" s="6">
+        <f>IF(H58=0,"",G58/H58)</f>
+        <v/>
+      </c>
+      <c r="J58" s="6">
+        <f>IF(SUMPRODUCT((Marks!$BF$5:$BF$39="top")*ISNUMBER(Marks!BC$5:BC$39))=0,"",SUMPRODUCT((Marks!$BF$5:$BF$39="top")*(Marks!BC$5:BC$39=1))/SUMPRODUCT((Marks!$BF$5:$BF$39="top")*ISNUMBER(Marks!BC$5:BC$39)))</f>
+        <v/>
+      </c>
+      <c r="K58" s="6">
+        <f>IF(SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*ISNUMBER(Marks!BC$5:BC$39))=0,"",SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*(Marks!BC$5:BC$39=1))/SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*ISNUMBER(Marks!BC$5:BC$39)))</f>
+        <v/>
+      </c>
+      <c r="L58" s="6">
+        <f>IF(OR(J58="",K58=""),"",J58-K58)</f>
+        <v/>
+      </c>
+      <c r="M58">
+        <f>IF(H58=0,"",IF(I58&lt;0.2,"Check the item: fewer than one in five got it right",IF(AND(L58&lt;&gt;"",N(L58)&lt;0),"Check the item: the bottom third beat the top third","")))</f>
+        <v/>
+      </c>
+      <c r="N58">
+        <f>IF(H58=0,"",I58+ROW()/1000000)</f>
         <v/>
       </c>
     </row>
@@ -6761,7 +7085,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F55"/>
+  <dimension ref="A1:F58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="6" max="6"/>
@@ -6776,7 +7100,7 @@
     </row>
     <row r="2">
       <c r="B2">
-        <f>IF(SUM(Items!H5:H55)=0,"No marks entered yet.","Most-missed first: take the items from the top.")</f>
+        <f>IF(SUM(Items!H5:H58)=0,"No marks entered yet.","Most-missed first: take the items from the top.")</f>
         <v/>
       </c>
     </row>
@@ -6817,23 +7141,23 @@
         <v>1</v>
       </c>
       <c r="B5">
-        <f>IF(COUNT(Items!$N$5:$N$55)&lt;A5,"",INDEX(Items!$A$5:$A$55,MATCH(SMALL(Items!$N$5:$N$55,A5),Items!$N$5:$N$55,0)))</f>
+        <f>IF(COUNT(Items!$N$5:$N$58)&lt;A5,"",INDEX(Items!$A$5:$A$58,MATCH(SMALL(Items!$N$5:$N$58,A5),Items!$N$5:$N$58,0)))</f>
         <v/>
       </c>
       <c r="C5" s="6">
-        <f>IF(B5="","",INDEX(Items!$I$5:$I$55,MATCH(B5,Items!$A$5:$A$55,0)))</f>
+        <f>IF(B5="","",INDEX(Items!$I$5:$I$58,MATCH(B5,Items!$A$5:$A$58,0)))</f>
         <v/>
       </c>
       <c r="D5">
-        <f>IF(B5="","",INDEX(Items!$B$5:$B$55,MATCH(B5,Items!$A$5:$A$55,0)))</f>
+        <f>IF(B5="","",INDEX(Items!$B$5:$B$58,MATCH(B5,Items!$A$5:$A$58,0)))</f>
         <v/>
       </c>
       <c r="E5">
-        <f>IF(B5="","",INDEX(Items!$E$5:$E$55,MATCH(B5,Items!$A$5:$A$55,0)))</f>
+        <f>IF(B5="","",INDEX(Items!$E$5:$E$58,MATCH(B5,Items!$A$5:$A$58,0)))</f>
         <v/>
       </c>
       <c r="F5">
-        <f>IF(B5="","",INDEX(Items!$M$5:$M$55,MATCH(B5,Items!$A$5:$A$55,0)))</f>
+        <f>IF(B5="","",INDEX(Items!$M$5:$M$58,MATCH(B5,Items!$A$5:$A$58,0)))</f>
         <v/>
       </c>
     </row>
@@ -6842,23 +7166,23 @@
         <v>2</v>
       </c>
       <c r="B6">
-        <f>IF(COUNT(Items!$N$5:$N$55)&lt;A6,"",INDEX(Items!$A$5:$A$55,MATCH(SMALL(Items!$N$5:$N$55,A6),Items!$N$5:$N$55,0)))</f>
+        <f>IF(COUNT(Items!$N$5:$N$58)&lt;A6,"",INDEX(Items!$A$5:$A$58,MATCH(SMALL(Items!$N$5:$N$58,A6),Items!$N$5:$N$58,0)))</f>
         <v/>
       </c>
       <c r="C6" s="6">
-        <f>IF(B6="","",INDEX(Items!$I$5:$I$55,MATCH(B6,Items!$A$5:$A$55,0)))</f>
+        <f>IF(B6="","",INDEX(Items!$I$5:$I$58,MATCH(B6,Items!$A$5:$A$58,0)))</f>
         <v/>
       </c>
       <c r="D6">
-        <f>IF(B6="","",INDEX(Items!$B$5:$B$55,MATCH(B6,Items!$A$5:$A$55,0)))</f>
+        <f>IF(B6="","",INDEX(Items!$B$5:$B$58,MATCH(B6,Items!$A$5:$A$58,0)))</f>
         <v/>
       </c>
       <c r="E6">
-        <f>IF(B6="","",INDEX(Items!$E$5:$E$55,MATCH(B6,Items!$A$5:$A$55,0)))</f>
+        <f>IF(B6="","",INDEX(Items!$E$5:$E$58,MATCH(B6,Items!$A$5:$A$58,0)))</f>
         <v/>
       </c>
       <c r="F6">
-        <f>IF(B6="","",INDEX(Items!$M$5:$M$55,MATCH(B6,Items!$A$5:$A$55,0)))</f>
+        <f>IF(B6="","",INDEX(Items!$M$5:$M$58,MATCH(B6,Items!$A$5:$A$58,0)))</f>
         <v/>
       </c>
     </row>
@@ -6867,23 +7191,23 @@
         <v>3</v>
       </c>
       <c r="B7">
-        <f>IF(COUNT(Items!$N$5:$N$55)&lt;A7,"",INDEX(Items!$A$5:$A$55,MATCH(SMALL(Items!$N$5:$N$55,A7),Items!$N$5:$N$55,0)))</f>
+        <f>IF(COUNT(Items!$N$5:$N$58)&lt;A7,"",INDEX(Items!$A$5:$A$58,MATCH(SMALL(Items!$N$5:$N$58,A7),Items!$N$5:$N$58,0)))</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>IF(B7="","",INDEX(Items!$I$5:$I$55,MATCH(B7,Items!$A$5:$A$55,0)))</f>
+        <f>IF(B7="","",INDEX(Items!$I$5:$I$58,MATCH(B7,Items!$A$5:$A$58,0)))</f>
         <v/>
       </c>
       <c r="D7">
-        <f>IF(B7="","",INDEX(Items!$B$5:$B$55,MATCH(B7,Items!$A$5:$A$55,0)))</f>
+        <f>IF(B7="","",INDEX(Items!$B$5:$B$58,MATCH(B7,Items!$A$5:$A$58,0)))</f>
         <v/>
       </c>
       <c r="E7">
-        <f>IF(B7="","",INDEX(Items!$E$5:$E$55,MATCH(B7,Items!$A$5:$A$55,0)))</f>
+        <f>IF(B7="","",INDEX(Items!$E$5:$E$58,MATCH(B7,Items!$A$5:$A$58,0)))</f>
         <v/>
       </c>
       <c r="F7">
-        <f>IF(B7="","",INDEX(Items!$M$5:$M$55,MATCH(B7,Items!$A$5:$A$55,0)))</f>
+        <f>IF(B7="","",INDEX(Items!$M$5:$M$58,MATCH(B7,Items!$A$5:$A$58,0)))</f>
         <v/>
       </c>
     </row>
@@ -6892,23 +7216,23 @@
         <v>4</v>
       </c>
       <c r="B8">
-        <f>IF(COUNT(Items!$N$5:$N$55)&lt;A8,"",INDEX(Items!$A$5:$A$55,MATCH(SMALL(Items!$N$5:$N$55,A8),Items!$N$5:$N$55,0)))</f>
+        <f>IF(COUNT(Items!$N$5:$N$58)&lt;A8,"",INDEX(Items!$A$5:$A$58,MATCH(SMALL(Items!$N$5:$N$58,A8),Items!$N$5:$N$58,0)))</f>
         <v/>
       </c>
       <c r="C8" s="6">
-        <f>IF(B8="","",INDEX(Items!$I$5:$I$55,MATCH(B8,Items!$A$5:$A$55,0)))</f>
+        <f>IF(B8="","",INDEX(Items!$I$5:$I$58,MATCH(B8,Items!$A$5:$A$58,0)))</f>
         <v/>
       </c>
       <c r="D8">
-        <f>IF(B8="","",INDEX(Items!$B$5:$B$55,MATCH(B8,Items!$A$5:$A$55,0)))</f>
+        <f>IF(B8="","",INDEX(Items!$B$5:$B$58,MATCH(B8,Items!$A$5:$A$58,0)))</f>
         <v/>
       </c>
       <c r="E8">
-        <f>IF(B8="","",INDEX(Items!$E$5:$E$55,MATCH(B8,Items!$A$5:$A$55,0)))</f>
+        <f>IF(B8="","",INDEX(Items!$E$5:$E$58,MATCH(B8,Items!$A$5:$A$58,0)))</f>
         <v/>
       </c>
       <c r="F8">
-        <f>IF(B8="","",INDEX(Items!$M$5:$M$55,MATCH(B8,Items!$A$5:$A$55,0)))</f>
+        <f>IF(B8="","",INDEX(Items!$M$5:$M$58,MATCH(B8,Items!$A$5:$A$58,0)))</f>
         <v/>
       </c>
     </row>
@@ -6917,23 +7241,23 @@
         <v>5</v>
       </c>
       <c r="B9">
-        <f>IF(COUNT(Items!$N$5:$N$55)&lt;A9,"",INDEX(Items!$A$5:$A$55,MATCH(SMALL(Items!$N$5:$N$55,A9),Items!$N$5:$N$55,0)))</f>
+        <f>IF(COUNT(Items!$N$5:$N$58)&lt;A9,"",INDEX(Items!$A$5:$A$58,MATCH(SMALL(Items!$N$5:$N$58,A9),Items!$N$5:$N$58,0)))</f>
         <v/>
       </c>
       <c r="C9" s="6">
-        <f>IF(B9="","",INDEX(Items!$I$5:$I$55,MATCH(B9,Items!$A$5:$A$55,0)))</f>
+        <f>IF(B9="","",INDEX(Items!$I$5:$I$58,MATCH(B9,Items!$A$5:$A$58,0)))</f>
         <v/>
       </c>
       <c r="D9">
-        <f>IF(B9="","",INDEX(Items!$B$5:$B$55,MATCH(B9,Items!$A$5:$A$55,0)))</f>
+        <f>IF(B9="","",INDEX(Items!$B$5:$B$58,MATCH(B9,Items!$A$5:$A$58,0)))</f>
         <v/>
       </c>
       <c r="E9">
-        <f>IF(B9="","",INDEX(Items!$E$5:$E$55,MATCH(B9,Items!$A$5:$A$55,0)))</f>
+        <f>IF(B9="","",INDEX(Items!$E$5:$E$58,MATCH(B9,Items!$A$5:$A$58,0)))</f>
         <v/>
       </c>
       <c r="F9">
-        <f>IF(B9="","",INDEX(Items!$M$5:$M$55,MATCH(B9,Items!$A$5:$A$55,0)))</f>
+        <f>IF(B9="","",INDEX(Items!$M$5:$M$58,MATCH(B9,Items!$A$5:$A$58,0)))</f>
         <v/>
       </c>
     </row>
@@ -6942,23 +7266,23 @@
         <v>6</v>
       </c>
       <c r="B10">
-        <f>IF(COUNT(Items!$N$5:$N$55)&lt;A10,"",INDEX(Items!$A$5:$A$55,MATCH(SMALL(Items!$N$5:$N$55,A10),Items!$N$5:$N$55,0)))</f>
+        <f>IF(COUNT(Items!$N$5:$N$58)&lt;A10,"",INDEX(Items!$A$5:$A$58,MATCH(SMALL(Items!$N$5:$N$58,A10),Items!$N$5:$N$58,0)))</f>
         <v/>
       </c>
       <c r="C10" s="6">
-        <f>IF(B10="","",INDEX(Items!$I$5:$I$55,MATCH(B10,Items!$A$5:$A$55,0)))</f>
+        <f>IF(B10="","",INDEX(Items!$I$5:$I$58,MATCH(B10,Items!$A$5:$A$58,0)))</f>
         <v/>
       </c>
       <c r="D10">
-        <f>IF(B10="","",INDEX(Items!$B$5:$B$55,MATCH(B10,Items!$A$5:$A$55,0)))</f>
+        <f>IF(B10="","",INDEX(Items!$B$5:$B$58,MATCH(B10,Items!$A$5:$A$58,0)))</f>
         <v/>
       </c>
       <c r="E10">
-        <f>IF(B10="","",INDEX(Items!$E$5:$E$55,MATCH(B10,Items!$A$5:$A$55,0)))</f>
+        <f>IF(B10="","",INDEX(Items!$E$5:$E$58,MATCH(B10,Items!$A$5:$A$58,0)))</f>
         <v/>
       </c>
       <c r="F10">
-        <f>IF(B10="","",INDEX(Items!$M$5:$M$55,MATCH(B10,Items!$A$5:$A$55,0)))</f>
+        <f>IF(B10="","",INDEX(Items!$M$5:$M$58,MATCH(B10,Items!$A$5:$A$58,0)))</f>
         <v/>
       </c>
     </row>
@@ -6967,23 +7291,23 @@
         <v>7</v>
       </c>
       <c r="B11">
-        <f>IF(COUNT(Items!$N$5:$N$55)&lt;A11,"",INDEX(Items!$A$5:$A$55,MATCH(SMALL(Items!$N$5:$N$55,A11),Items!$N$5:$N$55,0)))</f>
+        <f>IF(COUNT(Items!$N$5:$N$58)&lt;A11,"",INDEX(Items!$A$5:$A$58,MATCH(SMALL(Items!$N$5:$N$58,A11),Items!$N$5:$N$58,0)))</f>
         <v/>
       </c>
       <c r="C11" s="6">
-        <f>IF(B11="","",INDEX(Items!$I$5:$I$55,MATCH(B11,Items!$A$5:$A$55,0)))</f>
+        <f>IF(B11="","",INDEX(Items!$I$5:$I$58,MATCH(B11,Items!$A$5:$A$58,0)))</f>
         <v/>
       </c>
       <c r="D11">
-        <f>IF(B11="","",INDEX(Items!$B$5:$B$55,MATCH(B11,Items!$A$5:$A$55,0)))</f>
+        <f>IF(B11="","",INDEX(Items!$B$5:$B$58,MATCH(B11,Items!$A$5:$A$58,0)))</f>
         <v/>
       </c>
       <c r="E11">
-        <f>IF(B11="","",INDEX(Items!$E$5:$E$55,MATCH(B11,Items!$A$5:$A$55,0)))</f>
+        <f>IF(B11="","",INDEX(Items!$E$5:$E$58,MATCH(B11,Items!$A$5:$A$58,0)))</f>
         <v/>
       </c>
       <c r="F11">
-        <f>IF(B11="","",INDEX(Items!$M$5:$M$55,MATCH(B11,Items!$A$5:$A$55,0)))</f>
+        <f>IF(B11="","",INDEX(Items!$M$5:$M$58,MATCH(B11,Items!$A$5:$A$58,0)))</f>
         <v/>
       </c>
     </row>
@@ -6992,23 +7316,23 @@
         <v>8</v>
       </c>
       <c r="B12">
-        <f>IF(COUNT(Items!$N$5:$N$55)&lt;A12,"",INDEX(Items!$A$5:$A$55,MATCH(SMALL(Items!$N$5:$N$55,A12),Items!$N$5:$N$55,0)))</f>
+        <f>IF(COUNT(Items!$N$5:$N$58)&lt;A12,"",INDEX(Items!$A$5:$A$58,MATCH(SMALL(Items!$N$5:$N$58,A12),Items!$N$5:$N$58,0)))</f>
         <v/>
       </c>
       <c r="C12" s="6">
-        <f>IF(B12="","",INDEX(Items!$I$5:$I$55,MATCH(B12,Items!$A$5:$A$55,0)))</f>
+        <f>IF(B12="","",INDEX(Items!$I$5:$I$58,MATCH(B12,Items!$A$5:$A$58,0)))</f>
         <v/>
       </c>
       <c r="D12">
-        <f>IF(B12="","",INDEX(Items!$B$5:$B$55,MATCH(B12,Items!$A$5:$A$55,0)))</f>
+        <f>IF(B12="","",INDEX(Items!$B$5:$B$58,MATCH(B12,Items!$A$5:$A$58,0)))</f>
         <v/>
       </c>
       <c r="E12">
-        <f>IF(B12="","",INDEX(Items!$E$5:$E$55,MATCH(B12,Items!$A$5:$A$55,0)))</f>
+        <f>IF(B12="","",INDEX(Items!$E$5:$E$58,MATCH(B12,Items!$A$5:$A$58,0)))</f>
         <v/>
       </c>
       <c r="F12">
-        <f>IF(B12="","",INDEX(Items!$M$5:$M$55,MATCH(B12,Items!$A$5:$A$55,0)))</f>
+        <f>IF(B12="","",INDEX(Items!$M$5:$M$58,MATCH(B12,Items!$A$5:$A$58,0)))</f>
         <v/>
       </c>
     </row>
@@ -7017,23 +7341,23 @@
         <v>9</v>
       </c>
       <c r="B13">
-        <f>IF(COUNT(Items!$N$5:$N$55)&lt;A13,"",INDEX(Items!$A$5:$A$55,MATCH(SMALL(Items!$N$5:$N$55,A13),Items!$N$5:$N$55,0)))</f>
+        <f>IF(COUNT(Items!$N$5:$N$58)&lt;A13,"",INDEX(Items!$A$5:$A$58,MATCH(SMALL(Items!$N$5:$N$58,A13),Items!$N$5:$N$58,0)))</f>
         <v/>
       </c>
       <c r="C13" s="6">
-        <f>IF(B13="","",INDEX(Items!$I$5:$I$55,MATCH(B13,Items!$A$5:$A$55,0)))</f>
+        <f>IF(B13="","",INDEX(Items!$I$5:$I$58,MATCH(B13,Items!$A$5:$A$58,0)))</f>
         <v/>
       </c>
       <c r="D13">
-        <f>IF(B13="","",INDEX(Items!$B$5:$B$55,MATCH(B13,Items!$A$5:$A$55,0)))</f>
+        <f>IF(B13="","",INDEX(Items!$B$5:$B$58,MATCH(B13,Items!$A$5:$A$58,0)))</f>
         <v/>
       </c>
       <c r="E13">
-        <f>IF(B13="","",INDEX(Items!$E$5:$E$55,MATCH(B13,Items!$A$5:$A$55,0)))</f>
+        <f>IF(B13="","",INDEX(Items!$E$5:$E$58,MATCH(B13,Items!$A$5:$A$58,0)))</f>
         <v/>
       </c>
       <c r="F13">
-        <f>IF(B13="","",INDEX(Items!$M$5:$M$55,MATCH(B13,Items!$A$5:$A$55,0)))</f>
+        <f>IF(B13="","",INDEX(Items!$M$5:$M$58,MATCH(B13,Items!$A$5:$A$58,0)))</f>
         <v/>
       </c>
     </row>
@@ -7042,23 +7366,23 @@
         <v>10</v>
       </c>
       <c r="B14">
-        <f>IF(COUNT(Items!$N$5:$N$55)&lt;A14,"",INDEX(Items!$A$5:$A$55,MATCH(SMALL(Items!$N$5:$N$55,A14),Items!$N$5:$N$55,0)))</f>
+        <f>IF(COUNT(Items!$N$5:$N$58)&lt;A14,"",INDEX(Items!$A$5:$A$58,MATCH(SMALL(Items!$N$5:$N$58,A14),Items!$N$5:$N$58,0)))</f>
         <v/>
       </c>
       <c r="C14" s="6">
-        <f>IF(B14="","",INDEX(Items!$I$5:$I$55,MATCH(B14,Items!$A$5:$A$55,0)))</f>
+        <f>IF(B14="","",INDEX(Items!$I$5:$I$58,MATCH(B14,Items!$A$5:$A$58,0)))</f>
         <v/>
       </c>
       <c r="D14">
-        <f>IF(B14="","",INDEX(Items!$B$5:$B$55,MATCH(B14,Items!$A$5:$A$55,0)))</f>
+        <f>IF(B14="","",INDEX(Items!$B$5:$B$58,MATCH(B14,Items!$A$5:$A$58,0)))</f>
         <v/>
       </c>
       <c r="E14">
-        <f>IF(B14="","",INDEX(Items!$E$5:$E$55,MATCH(B14,Items!$A$5:$A$55,0)))</f>
+        <f>IF(B14="","",INDEX(Items!$E$5:$E$58,MATCH(B14,Items!$A$5:$A$58,0)))</f>
         <v/>
       </c>
       <c r="F14">
-        <f>IF(B14="","",INDEX(Items!$M$5:$M$55,MATCH(B14,Items!$A$5:$A$55,0)))</f>
+        <f>IF(B14="","",INDEX(Items!$M$5:$M$58,MATCH(B14,Items!$A$5:$A$58,0)))</f>
         <v/>
       </c>
     </row>
@@ -7067,23 +7391,23 @@
         <v>11</v>
       </c>
       <c r="B15">
-        <f>IF(COUNT(Items!$N$5:$N$55)&lt;A15,"",INDEX(Items!$A$5:$A$55,MATCH(SMALL(Items!$N$5:$N$55,A15),Items!$N$5:$N$55,0)))</f>
+        <f>IF(COUNT(Items!$N$5:$N$58)&lt;A15,"",INDEX(Items!$A$5:$A$58,MATCH(SMALL(Items!$N$5:$N$58,A15),Items!$N$5:$N$58,0)))</f>
         <v/>
       </c>
       <c r="C15" s="6">
-        <f>IF(B15="","",INDEX(Items!$I$5:$I$55,MATCH(B15,Items!$A$5:$A$55,0)))</f>
+        <f>IF(B15="","",INDEX(Items!$I$5:$I$58,MATCH(B15,Items!$A$5:$A$58,0)))</f>
         <v/>
       </c>
       <c r="D15">
-        <f>IF(B15="","",INDEX(Items!$B$5:$B$55,MATCH(B15,Items!$A$5:$A$55,0)))</f>
+        <f>IF(B15="","",INDEX(Items!$B$5:$B$58,MATCH(B15,Items!$A$5:$A$58,0)))</f>
         <v/>
       </c>
       <c r="E15">
-        <f>IF(B15="","",INDEX(Items!$E$5:$E$55,MATCH(B15,Items!$A$5:$A$55,0)))</f>
+        <f>IF(B15="","",INDEX(Items!$E$5:$E$58,MATCH(B15,Items!$A$5:$A$58,0)))</f>
         <v/>
       </c>
       <c r="F15">
-        <f>IF(B15="","",INDEX(Items!$M$5:$M$55,MATCH(B15,Items!$A$5:$A$55,0)))</f>
+        <f>IF(B15="","",INDEX(Items!$M$5:$M$58,MATCH(B15,Items!$A$5:$A$58,0)))</f>
         <v/>
       </c>
     </row>
@@ -7092,23 +7416,23 @@
         <v>12</v>
       </c>
       <c r="B16">
-        <f>IF(COUNT(Items!$N$5:$N$55)&lt;A16,"",INDEX(Items!$A$5:$A$55,MATCH(SMALL(Items!$N$5:$N$55,A16),Items!$N$5:$N$55,0)))</f>
+        <f>IF(COUNT(Items!$N$5:$N$58)&lt;A16,"",INDEX(Items!$A$5:$A$58,MATCH(SMALL(Items!$N$5:$N$58,A16),Items!$N$5:$N$58,0)))</f>
         <v/>
       </c>
       <c r="C16" s="6">
-        <f>IF(B16="","",INDEX(Items!$I$5:$I$55,MATCH(B16,Items!$A$5:$A$55,0)))</f>
+        <f>IF(B16="","",INDEX(Items!$I$5:$I$58,MATCH(B16,Items!$A$5:$A$58,0)))</f>
         <v/>
       </c>
       <c r="D16">
-        <f>IF(B16="","",INDEX(Items!$B$5:$B$55,MATCH(B16,Items!$A$5:$A$55,0)))</f>
+        <f>IF(B16="","",INDEX(Items!$B$5:$B$58,MATCH(B16,Items!$A$5:$A$58,0)))</f>
         <v/>
       </c>
       <c r="E16">
-        <f>IF(B16="","",INDEX(Items!$E$5:$E$55,MATCH(B16,Items!$A$5:$A$55,0)))</f>
+        <f>IF(B16="","",INDEX(Items!$E$5:$E$58,MATCH(B16,Items!$A$5:$A$58,0)))</f>
         <v/>
       </c>
       <c r="F16">
-        <f>IF(B16="","",INDEX(Items!$M$5:$M$55,MATCH(B16,Items!$A$5:$A$55,0)))</f>
+        <f>IF(B16="","",INDEX(Items!$M$5:$M$58,MATCH(B16,Items!$A$5:$A$58,0)))</f>
         <v/>
       </c>
     </row>
@@ -7117,23 +7441,23 @@
         <v>13</v>
       </c>
       <c r="B17">
-        <f>IF(COUNT(Items!$N$5:$N$55)&lt;A17,"",INDEX(Items!$A$5:$A$55,MATCH(SMALL(Items!$N$5:$N$55,A17),Items!$N$5:$N$55,0)))</f>
+        <f>IF(COUNT(Items!$N$5:$N$58)&lt;A17,"",INDEX(Items!$A$5:$A$58,MATCH(SMALL(Items!$N$5:$N$58,A17),Items!$N$5:$N$58,0)))</f>
         <v/>
       </c>
       <c r="C17" s="6">
-        <f>IF(B17="","",INDEX(Items!$I$5:$I$55,MATCH(B17,Items!$A$5:$A$55,0)))</f>
+        <f>IF(B17="","",INDEX(Items!$I$5:$I$58,MATCH(B17,Items!$A$5:$A$58,0)))</f>
         <v/>
       </c>
       <c r="D17">
-        <f>IF(B17="","",INDEX(Items!$B$5:$B$55,MATCH(B17,Items!$A$5:$A$55,0)))</f>
+        <f>IF(B17="","",INDEX(Items!$B$5:$B$58,MATCH(B17,Items!$A$5:$A$58,0)))</f>
         <v/>
       </c>
       <c r="E17">
-        <f>IF(B17="","",INDEX(Items!$E$5:$E$55,MATCH(B17,Items!$A$5:$A$55,0)))</f>
+        <f>IF(B17="","",INDEX(Items!$E$5:$E$58,MATCH(B17,Items!$A$5:$A$58,0)))</f>
         <v/>
       </c>
       <c r="F17">
-        <f>IF(B17="","",INDEX(Items!$M$5:$M$55,MATCH(B17,Items!$A$5:$A$55,0)))</f>
+        <f>IF(B17="","",INDEX(Items!$M$5:$M$58,MATCH(B17,Items!$A$5:$A$58,0)))</f>
         <v/>
       </c>
     </row>
@@ -7142,23 +7466,23 @@
         <v>14</v>
       </c>
       <c r="B18">
-        <f>IF(COUNT(Items!$N$5:$N$55)&lt;A18,"",INDEX(Items!$A$5:$A$55,MATCH(SMALL(Items!$N$5:$N$55,A18),Items!$N$5:$N$55,0)))</f>
+        <f>IF(COUNT(Items!$N$5:$N$58)&lt;A18,"",INDEX(Items!$A$5:$A$58,MATCH(SMALL(Items!$N$5:$N$58,A18),Items!$N$5:$N$58,0)))</f>
         <v/>
       </c>
       <c r="C18" s="6">
-        <f>IF(B18="","",INDEX(Items!$I$5:$I$55,MATCH(B18,Items!$A$5:$A$55,0)))</f>
+        <f>IF(B18="","",INDEX(Items!$I$5:$I$58,MATCH(B18,Items!$A$5:$A$58,0)))</f>
         <v/>
       </c>
       <c r="D18">
-        <f>IF(B18="","",INDEX(Items!$B$5:$B$55,MATCH(B18,Items!$A$5:$A$55,0)))</f>
+        <f>IF(B18="","",INDEX(Items!$B$5:$B$58,MATCH(B18,Items!$A$5:$A$58,0)))</f>
         <v/>
       </c>
       <c r="E18">
-        <f>IF(B18="","",INDEX(Items!$E$5:$E$55,MATCH(B18,Items!$A$5:$A$55,0)))</f>
+        <f>IF(B18="","",INDEX(Items!$E$5:$E$58,MATCH(B18,Items!$A$5:$A$58,0)))</f>
         <v/>
       </c>
       <c r="F18">
-        <f>IF(B18="","",INDEX(Items!$M$5:$M$55,MATCH(B18,Items!$A$5:$A$55,0)))</f>
+        <f>IF(B18="","",INDEX(Items!$M$5:$M$58,MATCH(B18,Items!$A$5:$A$58,0)))</f>
         <v/>
       </c>
     </row>
@@ -7167,23 +7491,23 @@
         <v>15</v>
       </c>
       <c r="B19">
-        <f>IF(COUNT(Items!$N$5:$N$55)&lt;A19,"",INDEX(Items!$A$5:$A$55,MATCH(SMALL(Items!$N$5:$N$55,A19),Items!$N$5:$N$55,0)))</f>
+        <f>IF(COUNT(Items!$N$5:$N$58)&lt;A19,"",INDEX(Items!$A$5:$A$58,MATCH(SMALL(Items!$N$5:$N$58,A19),Items!$N$5:$N$58,0)))</f>
         <v/>
       </c>
       <c r="C19" s="6">
-        <f>IF(B19="","",INDEX(Items!$I$5:$I$55,MATCH(B19,Items!$A$5:$A$55,0)))</f>
+        <f>IF(B19="","",INDEX(Items!$I$5:$I$58,MATCH(B19,Items!$A$5:$A$58,0)))</f>
         <v/>
       </c>
       <c r="D19">
-        <f>IF(B19="","",INDEX(Items!$B$5:$B$55,MATCH(B19,Items!$A$5:$A$55,0)))</f>
+        <f>IF(B19="","",INDEX(Items!$B$5:$B$58,MATCH(B19,Items!$A$5:$A$58,0)))</f>
         <v/>
       </c>
       <c r="E19">
-        <f>IF(B19="","",INDEX(Items!$E$5:$E$55,MATCH(B19,Items!$A$5:$A$55,0)))</f>
+        <f>IF(B19="","",INDEX(Items!$E$5:$E$58,MATCH(B19,Items!$A$5:$A$58,0)))</f>
         <v/>
       </c>
       <c r="F19">
-        <f>IF(B19="","",INDEX(Items!$M$5:$M$55,MATCH(B19,Items!$A$5:$A$55,0)))</f>
+        <f>IF(B19="","",INDEX(Items!$M$5:$M$58,MATCH(B19,Items!$A$5:$A$58,0)))</f>
         <v/>
       </c>
     </row>
@@ -7192,23 +7516,23 @@
         <v>16</v>
       </c>
       <c r="B20">
-        <f>IF(COUNT(Items!$N$5:$N$55)&lt;A20,"",INDEX(Items!$A$5:$A$55,MATCH(SMALL(Items!$N$5:$N$55,A20),Items!$N$5:$N$55,0)))</f>
+        <f>IF(COUNT(Items!$N$5:$N$58)&lt;A20,"",INDEX(Items!$A$5:$A$58,MATCH(SMALL(Items!$N$5:$N$58,A20),Items!$N$5:$N$58,0)))</f>
         <v/>
       </c>
       <c r="C20" s="6">
-        <f>IF(B20="","",INDEX(Items!$I$5:$I$55,MATCH(B20,Items!$A$5:$A$55,0)))</f>
+        <f>IF(B20="","",INDEX(Items!$I$5:$I$58,MATCH(B20,Items!$A$5:$A$58,0)))</f>
         <v/>
       </c>
       <c r="D20">
-        <f>IF(B20="","",INDEX(Items!$B$5:$B$55,MATCH(B20,Items!$A$5:$A$55,0)))</f>
+        <f>IF(B20="","",INDEX(Items!$B$5:$B$58,MATCH(B20,Items!$A$5:$A$58,0)))</f>
         <v/>
       </c>
       <c r="E20">
-        <f>IF(B20="","",INDEX(Items!$E$5:$E$55,MATCH(B20,Items!$A$5:$A$55,0)))</f>
+        <f>IF(B20="","",INDEX(Items!$E$5:$E$58,MATCH(B20,Items!$A$5:$A$58,0)))</f>
         <v/>
       </c>
       <c r="F20">
-        <f>IF(B20="","",INDEX(Items!$M$5:$M$55,MATCH(B20,Items!$A$5:$A$55,0)))</f>
+        <f>IF(B20="","",INDEX(Items!$M$5:$M$58,MATCH(B20,Items!$A$5:$A$58,0)))</f>
         <v/>
       </c>
     </row>
@@ -7217,23 +7541,23 @@
         <v>17</v>
       </c>
       <c r="B21">
-        <f>IF(COUNT(Items!$N$5:$N$55)&lt;A21,"",INDEX(Items!$A$5:$A$55,MATCH(SMALL(Items!$N$5:$N$55,A21),Items!$N$5:$N$55,0)))</f>
+        <f>IF(COUNT(Items!$N$5:$N$58)&lt;A21,"",INDEX(Items!$A$5:$A$58,MATCH(SMALL(Items!$N$5:$N$58,A21),Items!$N$5:$N$58,0)))</f>
         <v/>
       </c>
       <c r="C21" s="6">
-        <f>IF(B21="","",INDEX(Items!$I$5:$I$55,MATCH(B21,Items!$A$5:$A$55,0)))</f>
+        <f>IF(B21="","",INDEX(Items!$I$5:$I$58,MATCH(B21,Items!$A$5:$A$58,0)))</f>
         <v/>
       </c>
       <c r="D21">
-        <f>IF(B21="","",INDEX(Items!$B$5:$B$55,MATCH(B21,Items!$A$5:$A$55,0)))</f>
+        <f>IF(B21="","",INDEX(Items!$B$5:$B$58,MATCH(B21,Items!$A$5:$A$58,0)))</f>
         <v/>
       </c>
       <c r="E21">
-        <f>IF(B21="","",INDEX(Items!$E$5:$E$55,MATCH(B21,Items!$A$5:$A$55,0)))</f>
+        <f>IF(B21="","",INDEX(Items!$E$5:$E$58,MATCH(B21,Items!$A$5:$A$58,0)))</f>
         <v/>
       </c>
       <c r="F21">
-        <f>IF(B21="","",INDEX(Items!$M$5:$M$55,MATCH(B21,Items!$A$5:$A$55,0)))</f>
+        <f>IF(B21="","",INDEX(Items!$M$5:$M$58,MATCH(B21,Items!$A$5:$A$58,0)))</f>
         <v/>
       </c>
     </row>
@@ -7242,23 +7566,23 @@
         <v>18</v>
       </c>
       <c r="B22">
-        <f>IF(COUNT(Items!$N$5:$N$55)&lt;A22,"",INDEX(Items!$A$5:$A$55,MATCH(SMALL(Items!$N$5:$N$55,A22),Items!$N$5:$N$55,0)))</f>
+        <f>IF(COUNT(Items!$N$5:$N$58)&lt;A22,"",INDEX(Items!$A$5:$A$58,MATCH(SMALL(Items!$N$5:$N$58,A22),Items!$N$5:$N$58,0)))</f>
         <v/>
       </c>
       <c r="C22" s="6">
-        <f>IF(B22="","",INDEX(Items!$I$5:$I$55,MATCH(B22,Items!$A$5:$A$55,0)))</f>
+        <f>IF(B22="","",INDEX(Items!$I$5:$I$58,MATCH(B22,Items!$A$5:$A$58,0)))</f>
         <v/>
       </c>
       <c r="D22">
-        <f>IF(B22="","",INDEX(Items!$B$5:$B$55,MATCH(B22,Items!$A$5:$A$55,0)))</f>
+        <f>IF(B22="","",INDEX(Items!$B$5:$B$58,MATCH(B22,Items!$A$5:$A$58,0)))</f>
         <v/>
       </c>
       <c r="E22">
-        <f>IF(B22="","",INDEX(Items!$E$5:$E$55,MATCH(B22,Items!$A$5:$A$55,0)))</f>
+        <f>IF(B22="","",INDEX(Items!$E$5:$E$58,MATCH(B22,Items!$A$5:$A$58,0)))</f>
         <v/>
       </c>
       <c r="F22">
-        <f>IF(B22="","",INDEX(Items!$M$5:$M$55,MATCH(B22,Items!$A$5:$A$55,0)))</f>
+        <f>IF(B22="","",INDEX(Items!$M$5:$M$58,MATCH(B22,Items!$A$5:$A$58,0)))</f>
         <v/>
       </c>
     </row>
@@ -7267,23 +7591,23 @@
         <v>19</v>
       </c>
       <c r="B23">
-        <f>IF(COUNT(Items!$N$5:$N$55)&lt;A23,"",INDEX(Items!$A$5:$A$55,MATCH(SMALL(Items!$N$5:$N$55,A23),Items!$N$5:$N$55,0)))</f>
+        <f>IF(COUNT(Items!$N$5:$N$58)&lt;A23,"",INDEX(Items!$A$5:$A$58,MATCH(SMALL(Items!$N$5:$N$58,A23),Items!$N$5:$N$58,0)))</f>
         <v/>
       </c>
       <c r="C23" s="6">
-        <f>IF(B23="","",INDEX(Items!$I$5:$I$55,MATCH(B23,Items!$A$5:$A$55,0)))</f>
+        <f>IF(B23="","",INDEX(Items!$I$5:$I$58,MATCH(B23,Items!$A$5:$A$58,0)))</f>
         <v/>
       </c>
       <c r="D23">
-        <f>IF(B23="","",INDEX(Items!$B$5:$B$55,MATCH(B23,Items!$A$5:$A$55,0)))</f>
+        <f>IF(B23="","",INDEX(Items!$B$5:$B$58,MATCH(B23,Items!$A$5:$A$58,0)))</f>
         <v/>
       </c>
       <c r="E23">
-        <f>IF(B23="","",INDEX(Items!$E$5:$E$55,MATCH(B23,Items!$A$5:$A$55,0)))</f>
+        <f>IF(B23="","",INDEX(Items!$E$5:$E$58,MATCH(B23,Items!$A$5:$A$58,0)))</f>
         <v/>
       </c>
       <c r="F23">
-        <f>IF(B23="","",INDEX(Items!$M$5:$M$55,MATCH(B23,Items!$A$5:$A$55,0)))</f>
+        <f>IF(B23="","",INDEX(Items!$M$5:$M$58,MATCH(B23,Items!$A$5:$A$58,0)))</f>
         <v/>
       </c>
     </row>
@@ -7292,23 +7616,23 @@
         <v>20</v>
       </c>
       <c r="B24">
-        <f>IF(COUNT(Items!$N$5:$N$55)&lt;A24,"",INDEX(Items!$A$5:$A$55,MATCH(SMALL(Items!$N$5:$N$55,A24),Items!$N$5:$N$55,0)))</f>
+        <f>IF(COUNT(Items!$N$5:$N$58)&lt;A24,"",INDEX(Items!$A$5:$A$58,MATCH(SMALL(Items!$N$5:$N$58,A24),Items!$N$5:$N$58,0)))</f>
         <v/>
       </c>
       <c r="C24" s="6">
-        <f>IF(B24="","",INDEX(Items!$I$5:$I$55,MATCH(B24,Items!$A$5:$A$55,0)))</f>
+        <f>IF(B24="","",INDEX(Items!$I$5:$I$58,MATCH(B24,Items!$A$5:$A$58,0)))</f>
         <v/>
       </c>
       <c r="D24">
-        <f>IF(B24="","",INDEX(Items!$B$5:$B$55,MATCH(B24,Items!$A$5:$A$55,0)))</f>
+        <f>IF(B24="","",INDEX(Items!$B$5:$B$58,MATCH(B24,Items!$A$5:$A$58,0)))</f>
         <v/>
       </c>
       <c r="E24">
-        <f>IF(B24="","",INDEX(Items!$E$5:$E$55,MATCH(B24,Items!$A$5:$A$55,0)))</f>
+        <f>IF(B24="","",INDEX(Items!$E$5:$E$58,MATCH(B24,Items!$A$5:$A$58,0)))</f>
         <v/>
       </c>
       <c r="F24">
-        <f>IF(B24="","",INDEX(Items!$M$5:$M$55,MATCH(B24,Items!$A$5:$A$55,0)))</f>
+        <f>IF(B24="","",INDEX(Items!$M$5:$M$58,MATCH(B24,Items!$A$5:$A$58,0)))</f>
         <v/>
       </c>
     </row>
@@ -7317,23 +7641,23 @@
         <v>21</v>
       </c>
       <c r="B25">
-        <f>IF(COUNT(Items!$N$5:$N$55)&lt;A25,"",INDEX(Items!$A$5:$A$55,MATCH(SMALL(Items!$N$5:$N$55,A25),Items!$N$5:$N$55,0)))</f>
+        <f>IF(COUNT(Items!$N$5:$N$58)&lt;A25,"",INDEX(Items!$A$5:$A$58,MATCH(SMALL(Items!$N$5:$N$58,A25),Items!$N$5:$N$58,0)))</f>
         <v/>
       </c>
       <c r="C25" s="6">
-        <f>IF(B25="","",INDEX(Items!$I$5:$I$55,MATCH(B25,Items!$A$5:$A$55,0)))</f>
+        <f>IF(B25="","",INDEX(Items!$I$5:$I$58,MATCH(B25,Items!$A$5:$A$58,0)))</f>
         <v/>
       </c>
       <c r="D25">
-        <f>IF(B25="","",INDEX(Items!$B$5:$B$55,MATCH(B25,Items!$A$5:$A$55,0)))</f>
+        <f>IF(B25="","",INDEX(Items!$B$5:$B$58,MATCH(B25,Items!$A$5:$A$58,0)))</f>
         <v/>
       </c>
       <c r="E25">
-        <f>IF(B25="","",INDEX(Items!$E$5:$E$55,MATCH(B25,Items!$A$5:$A$55,0)))</f>
+        <f>IF(B25="","",INDEX(Items!$E$5:$E$58,MATCH(B25,Items!$A$5:$A$58,0)))</f>
         <v/>
       </c>
       <c r="F25">
-        <f>IF(B25="","",INDEX(Items!$M$5:$M$55,MATCH(B25,Items!$A$5:$A$55,0)))</f>
+        <f>IF(B25="","",INDEX(Items!$M$5:$M$58,MATCH(B25,Items!$A$5:$A$58,0)))</f>
         <v/>
       </c>
     </row>
@@ -7342,23 +7666,23 @@
         <v>22</v>
       </c>
       <c r="B26">
-        <f>IF(COUNT(Items!$N$5:$N$55)&lt;A26,"",INDEX(Items!$A$5:$A$55,MATCH(SMALL(Items!$N$5:$N$55,A26),Items!$N$5:$N$55,0)))</f>
+        <f>IF(COUNT(Items!$N$5:$N$58)&lt;A26,"",INDEX(Items!$A$5:$A$58,MATCH(SMALL(Items!$N$5:$N$58,A26),Items!$N$5:$N$58,0)))</f>
         <v/>
       </c>
       <c r="C26" s="6">
-        <f>IF(B26="","",INDEX(Items!$I$5:$I$55,MATCH(B26,Items!$A$5:$A$55,0)))</f>
+        <f>IF(B26="","",INDEX(Items!$I$5:$I$58,MATCH(B26,Items!$A$5:$A$58,0)))</f>
         <v/>
       </c>
       <c r="D26">
-        <f>IF(B26="","",INDEX(Items!$B$5:$B$55,MATCH(B26,Items!$A$5:$A$55,0)))</f>
+        <f>IF(B26="","",INDEX(Items!$B$5:$B$58,MATCH(B26,Items!$A$5:$A$58,0)))</f>
         <v/>
       </c>
       <c r="E26">
-        <f>IF(B26="","",INDEX(Items!$E$5:$E$55,MATCH(B26,Items!$A$5:$A$55,0)))</f>
+        <f>IF(B26="","",INDEX(Items!$E$5:$E$58,MATCH(B26,Items!$A$5:$A$58,0)))</f>
         <v/>
       </c>
       <c r="F26">
-        <f>IF(B26="","",INDEX(Items!$M$5:$M$55,MATCH(B26,Items!$A$5:$A$55,0)))</f>
+        <f>IF(B26="","",INDEX(Items!$M$5:$M$58,MATCH(B26,Items!$A$5:$A$58,0)))</f>
         <v/>
       </c>
     </row>
@@ -7367,23 +7691,23 @@
         <v>23</v>
       </c>
       <c r="B27">
-        <f>IF(COUNT(Items!$N$5:$N$55)&lt;A27,"",INDEX(Items!$A$5:$A$55,MATCH(SMALL(Items!$N$5:$N$55,A27),Items!$N$5:$N$55,0)))</f>
+        <f>IF(COUNT(Items!$N$5:$N$58)&lt;A27,"",INDEX(Items!$A$5:$A$58,MATCH(SMALL(Items!$N$5:$N$58,A27),Items!$N$5:$N$58,0)))</f>
         <v/>
       </c>
       <c r="C27" s="6">
-        <f>IF(B27="","",INDEX(Items!$I$5:$I$55,MATCH(B27,Items!$A$5:$A$55,0)))</f>
+        <f>IF(B27="","",INDEX(Items!$I$5:$I$58,MATCH(B27,Items!$A$5:$A$58,0)))</f>
         <v/>
       </c>
       <c r="D27">
-        <f>IF(B27="","",INDEX(Items!$B$5:$B$55,MATCH(B27,Items!$A$5:$A$55,0)))</f>
+        <f>IF(B27="","",INDEX(Items!$B$5:$B$58,MATCH(B27,Items!$A$5:$A$58,0)))</f>
         <v/>
       </c>
       <c r="E27">
-        <f>IF(B27="","",INDEX(Items!$E$5:$E$55,MATCH(B27,Items!$A$5:$A$55,0)))</f>
+        <f>IF(B27="","",INDEX(Items!$E$5:$E$58,MATCH(B27,Items!$A$5:$A$58,0)))</f>
         <v/>
       </c>
       <c r="F27">
-        <f>IF(B27="","",INDEX(Items!$M$5:$M$55,MATCH(B27,Items!$A$5:$A$55,0)))</f>
+        <f>IF(B27="","",INDEX(Items!$M$5:$M$58,MATCH(B27,Items!$A$5:$A$58,0)))</f>
         <v/>
       </c>
     </row>
@@ -7392,23 +7716,23 @@
         <v>24</v>
       </c>
       <c r="B28">
-        <f>IF(COUNT(Items!$N$5:$N$55)&lt;A28,"",INDEX(Items!$A$5:$A$55,MATCH(SMALL(Items!$N$5:$N$55,A28),Items!$N$5:$N$55,0)))</f>
+        <f>IF(COUNT(Items!$N$5:$N$58)&lt;A28,"",INDEX(Items!$A$5:$A$58,MATCH(SMALL(Items!$N$5:$N$58,A28),Items!$N$5:$N$58,0)))</f>
         <v/>
       </c>
       <c r="C28" s="6">
-        <f>IF(B28="","",INDEX(Items!$I$5:$I$55,MATCH(B28,Items!$A$5:$A$55,0)))</f>
+        <f>IF(B28="","",INDEX(Items!$I$5:$I$58,MATCH(B28,Items!$A$5:$A$58,0)))</f>
         <v/>
       </c>
       <c r="D28">
-        <f>IF(B28="","",INDEX(Items!$B$5:$B$55,MATCH(B28,Items!$A$5:$A$55,0)))</f>
+        <f>IF(B28="","",INDEX(Items!$B$5:$B$58,MATCH(B28,Items!$A$5:$A$58,0)))</f>
         <v/>
       </c>
       <c r="E28">
-        <f>IF(B28="","",INDEX(Items!$E$5:$E$55,MATCH(B28,Items!$A$5:$A$55,0)))</f>
+        <f>IF(B28="","",INDEX(Items!$E$5:$E$58,MATCH(B28,Items!$A$5:$A$58,0)))</f>
         <v/>
       </c>
       <c r="F28">
-        <f>IF(B28="","",INDEX(Items!$M$5:$M$55,MATCH(B28,Items!$A$5:$A$55,0)))</f>
+        <f>IF(B28="","",INDEX(Items!$M$5:$M$58,MATCH(B28,Items!$A$5:$A$58,0)))</f>
         <v/>
       </c>
     </row>
@@ -7417,23 +7741,23 @@
         <v>25</v>
       </c>
       <c r="B29">
-        <f>IF(COUNT(Items!$N$5:$N$55)&lt;A29,"",INDEX(Items!$A$5:$A$55,MATCH(SMALL(Items!$N$5:$N$55,A29),Items!$N$5:$N$55,0)))</f>
+        <f>IF(COUNT(Items!$N$5:$N$58)&lt;A29,"",INDEX(Items!$A$5:$A$58,MATCH(SMALL(Items!$N$5:$N$58,A29),Items!$N$5:$N$58,0)))</f>
         <v/>
       </c>
       <c r="C29" s="6">
-        <f>IF(B29="","",INDEX(Items!$I$5:$I$55,MATCH(B29,Items!$A$5:$A$55,0)))</f>
+        <f>IF(B29="","",INDEX(Items!$I$5:$I$58,MATCH(B29,Items!$A$5:$A$58,0)))</f>
         <v/>
       </c>
       <c r="D29">
-        <f>IF(B29="","",INDEX(Items!$B$5:$B$55,MATCH(B29,Items!$A$5:$A$55,0)))</f>
+        <f>IF(B29="","",INDEX(Items!$B$5:$B$58,MATCH(B29,Items!$A$5:$A$58,0)))</f>
         <v/>
       </c>
       <c r="E29">
-        <f>IF(B29="","",INDEX(Items!$E$5:$E$55,MATCH(B29,Items!$A$5:$A$55,0)))</f>
+        <f>IF(B29="","",INDEX(Items!$E$5:$E$58,MATCH(B29,Items!$A$5:$A$58,0)))</f>
         <v/>
       </c>
       <c r="F29">
-        <f>IF(B29="","",INDEX(Items!$M$5:$M$55,MATCH(B29,Items!$A$5:$A$55,0)))</f>
+        <f>IF(B29="","",INDEX(Items!$M$5:$M$58,MATCH(B29,Items!$A$5:$A$58,0)))</f>
         <v/>
       </c>
     </row>
@@ -7442,23 +7766,23 @@
         <v>26</v>
       </c>
       <c r="B30">
-        <f>IF(COUNT(Items!$N$5:$N$55)&lt;A30,"",INDEX(Items!$A$5:$A$55,MATCH(SMALL(Items!$N$5:$N$55,A30),Items!$N$5:$N$55,0)))</f>
+        <f>IF(COUNT(Items!$N$5:$N$58)&lt;A30,"",INDEX(Items!$A$5:$A$58,MATCH(SMALL(Items!$N$5:$N$58,A30),Items!$N$5:$N$58,0)))</f>
         <v/>
       </c>
       <c r="C30" s="6">
-        <f>IF(B30="","",INDEX(Items!$I$5:$I$55,MATCH(B30,Items!$A$5:$A$55,0)))</f>
+        <f>IF(B30="","",INDEX(Items!$I$5:$I$58,MATCH(B30,Items!$A$5:$A$58,0)))</f>
         <v/>
       </c>
       <c r="D30">
-        <f>IF(B30="","",INDEX(Items!$B$5:$B$55,MATCH(B30,Items!$A$5:$A$55,0)))</f>
+        <f>IF(B30="","",INDEX(Items!$B$5:$B$58,MATCH(B30,Items!$A$5:$A$58,0)))</f>
         <v/>
       </c>
       <c r="E30">
-        <f>IF(B30="","",INDEX(Items!$E$5:$E$55,MATCH(B30,Items!$A$5:$A$55,0)))</f>
+        <f>IF(B30="","",INDEX(Items!$E$5:$E$58,MATCH(B30,Items!$A$5:$A$58,0)))</f>
         <v/>
       </c>
       <c r="F30">
-        <f>IF(B30="","",INDEX(Items!$M$5:$M$55,MATCH(B30,Items!$A$5:$A$55,0)))</f>
+        <f>IF(B30="","",INDEX(Items!$M$5:$M$58,MATCH(B30,Items!$A$5:$A$58,0)))</f>
         <v/>
       </c>
     </row>
@@ -7467,23 +7791,23 @@
         <v>27</v>
       </c>
       <c r="B31">
-        <f>IF(COUNT(Items!$N$5:$N$55)&lt;A31,"",INDEX(Items!$A$5:$A$55,MATCH(SMALL(Items!$N$5:$N$55,A31),Items!$N$5:$N$55,0)))</f>
+        <f>IF(COUNT(Items!$N$5:$N$58)&lt;A31,"",INDEX(Items!$A$5:$A$58,MATCH(SMALL(Items!$N$5:$N$58,A31),Items!$N$5:$N$58,0)))</f>
         <v/>
       </c>
       <c r="C31" s="6">
-        <f>IF(B31="","",INDEX(Items!$I$5:$I$55,MATCH(B31,Items!$A$5:$A$55,0)))</f>
+        <f>IF(B31="","",INDEX(Items!$I$5:$I$58,MATCH(B31,Items!$A$5:$A$58,0)))</f>
         <v/>
       </c>
       <c r="D31">
-        <f>IF(B31="","",INDEX(Items!$B$5:$B$55,MATCH(B31,Items!$A$5:$A$55,0)))</f>
+        <f>IF(B31="","",INDEX(Items!$B$5:$B$58,MATCH(B31,Items!$A$5:$A$58,0)))</f>
         <v/>
       </c>
       <c r="E31">
-        <f>IF(B31="","",INDEX(Items!$E$5:$E$55,MATCH(B31,Items!$A$5:$A$55,0)))</f>
+        <f>IF(B31="","",INDEX(Items!$E$5:$E$58,MATCH(B31,Items!$A$5:$A$58,0)))</f>
         <v/>
       </c>
       <c r="F31">
-        <f>IF(B31="","",INDEX(Items!$M$5:$M$55,MATCH(B31,Items!$A$5:$A$55,0)))</f>
+        <f>IF(B31="","",INDEX(Items!$M$5:$M$58,MATCH(B31,Items!$A$5:$A$58,0)))</f>
         <v/>
       </c>
     </row>
@@ -7492,23 +7816,23 @@
         <v>28</v>
       </c>
       <c r="B32">
-        <f>IF(COUNT(Items!$N$5:$N$55)&lt;A32,"",INDEX(Items!$A$5:$A$55,MATCH(SMALL(Items!$N$5:$N$55,A32),Items!$N$5:$N$55,0)))</f>
+        <f>IF(COUNT(Items!$N$5:$N$58)&lt;A32,"",INDEX(Items!$A$5:$A$58,MATCH(SMALL(Items!$N$5:$N$58,A32),Items!$N$5:$N$58,0)))</f>
         <v/>
       </c>
       <c r="C32" s="6">
-        <f>IF(B32="","",INDEX(Items!$I$5:$I$55,MATCH(B32,Items!$A$5:$A$55,0)))</f>
+        <f>IF(B32="","",INDEX(Items!$I$5:$I$58,MATCH(B32,Items!$A$5:$A$58,0)))</f>
         <v/>
       </c>
       <c r="D32">
-        <f>IF(B32="","",INDEX(Items!$B$5:$B$55,MATCH(B32,Items!$A$5:$A$55,0)))</f>
+        <f>IF(B32="","",INDEX(Items!$B$5:$B$58,MATCH(B32,Items!$A$5:$A$58,0)))</f>
         <v/>
       </c>
       <c r="E32">
-        <f>IF(B32="","",INDEX(Items!$E$5:$E$55,MATCH(B32,Items!$A$5:$A$55,0)))</f>
+        <f>IF(B32="","",INDEX(Items!$E$5:$E$58,MATCH(B32,Items!$A$5:$A$58,0)))</f>
         <v/>
       </c>
       <c r="F32">
-        <f>IF(B32="","",INDEX(Items!$M$5:$M$55,MATCH(B32,Items!$A$5:$A$55,0)))</f>
+        <f>IF(B32="","",INDEX(Items!$M$5:$M$58,MATCH(B32,Items!$A$5:$A$58,0)))</f>
         <v/>
       </c>
     </row>
@@ -7517,23 +7841,23 @@
         <v>29</v>
       </c>
       <c r="B33">
-        <f>IF(COUNT(Items!$N$5:$N$55)&lt;A33,"",INDEX(Items!$A$5:$A$55,MATCH(SMALL(Items!$N$5:$N$55,A33),Items!$N$5:$N$55,0)))</f>
+        <f>IF(COUNT(Items!$N$5:$N$58)&lt;A33,"",INDEX(Items!$A$5:$A$58,MATCH(SMALL(Items!$N$5:$N$58,A33),Items!$N$5:$N$58,0)))</f>
         <v/>
       </c>
       <c r="C33" s="6">
-        <f>IF(B33="","",INDEX(Items!$I$5:$I$55,MATCH(B33,Items!$A$5:$A$55,0)))</f>
+        <f>IF(B33="","",INDEX(Items!$I$5:$I$58,MATCH(B33,Items!$A$5:$A$58,0)))</f>
         <v/>
       </c>
       <c r="D33">
-        <f>IF(B33="","",INDEX(Items!$B$5:$B$55,MATCH(B33,Items!$A$5:$A$55,0)))</f>
+        <f>IF(B33="","",INDEX(Items!$B$5:$B$58,MATCH(B33,Items!$A$5:$A$58,0)))</f>
         <v/>
       </c>
       <c r="E33">
-        <f>IF(B33="","",INDEX(Items!$E$5:$E$55,MATCH(B33,Items!$A$5:$A$55,0)))</f>
+        <f>IF(B33="","",INDEX(Items!$E$5:$E$58,MATCH(B33,Items!$A$5:$A$58,0)))</f>
         <v/>
       </c>
       <c r="F33">
-        <f>IF(B33="","",INDEX(Items!$M$5:$M$55,MATCH(B33,Items!$A$5:$A$55,0)))</f>
+        <f>IF(B33="","",INDEX(Items!$M$5:$M$58,MATCH(B33,Items!$A$5:$A$58,0)))</f>
         <v/>
       </c>
     </row>
@@ -7542,23 +7866,23 @@
         <v>30</v>
       </c>
       <c r="B34">
-        <f>IF(COUNT(Items!$N$5:$N$55)&lt;A34,"",INDEX(Items!$A$5:$A$55,MATCH(SMALL(Items!$N$5:$N$55,A34),Items!$N$5:$N$55,0)))</f>
+        <f>IF(COUNT(Items!$N$5:$N$58)&lt;A34,"",INDEX(Items!$A$5:$A$58,MATCH(SMALL(Items!$N$5:$N$58,A34),Items!$N$5:$N$58,0)))</f>
         <v/>
       </c>
       <c r="C34" s="6">
-        <f>IF(B34="","",INDEX(Items!$I$5:$I$55,MATCH(B34,Items!$A$5:$A$55,0)))</f>
+        <f>IF(B34="","",INDEX(Items!$I$5:$I$58,MATCH(B34,Items!$A$5:$A$58,0)))</f>
         <v/>
       </c>
       <c r="D34">
-        <f>IF(B34="","",INDEX(Items!$B$5:$B$55,MATCH(B34,Items!$A$5:$A$55,0)))</f>
+        <f>IF(B34="","",INDEX(Items!$B$5:$B$58,MATCH(B34,Items!$A$5:$A$58,0)))</f>
         <v/>
       </c>
       <c r="E34">
-        <f>IF(B34="","",INDEX(Items!$E$5:$E$55,MATCH(B34,Items!$A$5:$A$55,0)))</f>
+        <f>IF(B34="","",INDEX(Items!$E$5:$E$58,MATCH(B34,Items!$A$5:$A$58,0)))</f>
         <v/>
       </c>
       <c r="F34">
-        <f>IF(B34="","",INDEX(Items!$M$5:$M$55,MATCH(B34,Items!$A$5:$A$55,0)))</f>
+        <f>IF(B34="","",INDEX(Items!$M$5:$M$58,MATCH(B34,Items!$A$5:$A$58,0)))</f>
         <v/>
       </c>
     </row>
@@ -7567,23 +7891,23 @@
         <v>31</v>
       </c>
       <c r="B35">
-        <f>IF(COUNT(Items!$N$5:$N$55)&lt;A35,"",INDEX(Items!$A$5:$A$55,MATCH(SMALL(Items!$N$5:$N$55,A35),Items!$N$5:$N$55,0)))</f>
+        <f>IF(COUNT(Items!$N$5:$N$58)&lt;A35,"",INDEX(Items!$A$5:$A$58,MATCH(SMALL(Items!$N$5:$N$58,A35),Items!$N$5:$N$58,0)))</f>
         <v/>
       </c>
       <c r="C35" s="6">
-        <f>IF(B35="","",INDEX(Items!$I$5:$I$55,MATCH(B35,Items!$A$5:$A$55,0)))</f>
+        <f>IF(B35="","",INDEX(Items!$I$5:$I$58,MATCH(B35,Items!$A$5:$A$58,0)))</f>
         <v/>
       </c>
       <c r="D35">
-        <f>IF(B35="","",INDEX(Items!$B$5:$B$55,MATCH(B35,Items!$A$5:$A$55,0)))</f>
+        <f>IF(B35="","",INDEX(Items!$B$5:$B$58,MATCH(B35,Items!$A$5:$A$58,0)))</f>
         <v/>
       </c>
       <c r="E35">
-        <f>IF(B35="","",INDEX(Items!$E$5:$E$55,MATCH(B35,Items!$A$5:$A$55,0)))</f>
+        <f>IF(B35="","",INDEX(Items!$E$5:$E$58,MATCH(B35,Items!$A$5:$A$58,0)))</f>
         <v/>
       </c>
       <c r="F35">
-        <f>IF(B35="","",INDEX(Items!$M$5:$M$55,MATCH(B35,Items!$A$5:$A$55,0)))</f>
+        <f>IF(B35="","",INDEX(Items!$M$5:$M$58,MATCH(B35,Items!$A$5:$A$58,0)))</f>
         <v/>
       </c>
     </row>
@@ -7592,23 +7916,23 @@
         <v>32</v>
       </c>
       <c r="B36">
-        <f>IF(COUNT(Items!$N$5:$N$55)&lt;A36,"",INDEX(Items!$A$5:$A$55,MATCH(SMALL(Items!$N$5:$N$55,A36),Items!$N$5:$N$55,0)))</f>
+        <f>IF(COUNT(Items!$N$5:$N$58)&lt;A36,"",INDEX(Items!$A$5:$A$58,MATCH(SMALL(Items!$N$5:$N$58,A36),Items!$N$5:$N$58,0)))</f>
         <v/>
       </c>
       <c r="C36" s="6">
-        <f>IF(B36="","",INDEX(Items!$I$5:$I$55,MATCH(B36,Items!$A$5:$A$55,0)))</f>
+        <f>IF(B36="","",INDEX(Items!$I$5:$I$58,MATCH(B36,Items!$A$5:$A$58,0)))</f>
         <v/>
       </c>
       <c r="D36">
-        <f>IF(B36="","",INDEX(Items!$B$5:$B$55,MATCH(B36,Items!$A$5:$A$55,0)))</f>
+        <f>IF(B36="","",INDEX(Items!$B$5:$B$58,MATCH(B36,Items!$A$5:$A$58,0)))</f>
         <v/>
       </c>
       <c r="E36">
-        <f>IF(B36="","",INDEX(Items!$E$5:$E$55,MATCH(B36,Items!$A$5:$A$55,0)))</f>
+        <f>IF(B36="","",INDEX(Items!$E$5:$E$58,MATCH(B36,Items!$A$5:$A$58,0)))</f>
         <v/>
       </c>
       <c r="F36">
-        <f>IF(B36="","",INDEX(Items!$M$5:$M$55,MATCH(B36,Items!$A$5:$A$55,0)))</f>
+        <f>IF(B36="","",INDEX(Items!$M$5:$M$58,MATCH(B36,Items!$A$5:$A$58,0)))</f>
         <v/>
       </c>
     </row>
@@ -7617,23 +7941,23 @@
         <v>33</v>
       </c>
       <c r="B37">
-        <f>IF(COUNT(Items!$N$5:$N$55)&lt;A37,"",INDEX(Items!$A$5:$A$55,MATCH(SMALL(Items!$N$5:$N$55,A37),Items!$N$5:$N$55,0)))</f>
+        <f>IF(COUNT(Items!$N$5:$N$58)&lt;A37,"",INDEX(Items!$A$5:$A$58,MATCH(SMALL(Items!$N$5:$N$58,A37),Items!$N$5:$N$58,0)))</f>
         <v/>
       </c>
       <c r="C37" s="6">
-        <f>IF(B37="","",INDEX(Items!$I$5:$I$55,MATCH(B37,Items!$A$5:$A$55,0)))</f>
+        <f>IF(B37="","",INDEX(Items!$I$5:$I$58,MATCH(B37,Items!$A$5:$A$58,0)))</f>
         <v/>
       </c>
       <c r="D37">
-        <f>IF(B37="","",INDEX(Items!$B$5:$B$55,MATCH(B37,Items!$A$5:$A$55,0)))</f>
+        <f>IF(B37="","",INDEX(Items!$B$5:$B$58,MATCH(B37,Items!$A$5:$A$58,0)))</f>
         <v/>
       </c>
       <c r="E37">
-        <f>IF(B37="","",INDEX(Items!$E$5:$E$55,MATCH(B37,Items!$A$5:$A$55,0)))</f>
+        <f>IF(B37="","",INDEX(Items!$E$5:$E$58,MATCH(B37,Items!$A$5:$A$58,0)))</f>
         <v/>
       </c>
       <c r="F37">
-        <f>IF(B37="","",INDEX(Items!$M$5:$M$55,MATCH(B37,Items!$A$5:$A$55,0)))</f>
+        <f>IF(B37="","",INDEX(Items!$M$5:$M$58,MATCH(B37,Items!$A$5:$A$58,0)))</f>
         <v/>
       </c>
     </row>
@@ -7642,23 +7966,23 @@
         <v>34</v>
       </c>
       <c r="B38">
-        <f>IF(COUNT(Items!$N$5:$N$55)&lt;A38,"",INDEX(Items!$A$5:$A$55,MATCH(SMALL(Items!$N$5:$N$55,A38),Items!$N$5:$N$55,0)))</f>
+        <f>IF(COUNT(Items!$N$5:$N$58)&lt;A38,"",INDEX(Items!$A$5:$A$58,MATCH(SMALL(Items!$N$5:$N$58,A38),Items!$N$5:$N$58,0)))</f>
         <v/>
       </c>
       <c r="C38" s="6">
-        <f>IF(B38="","",INDEX(Items!$I$5:$I$55,MATCH(B38,Items!$A$5:$A$55,0)))</f>
+        <f>IF(B38="","",INDEX(Items!$I$5:$I$58,MATCH(B38,Items!$A$5:$A$58,0)))</f>
         <v/>
       </c>
       <c r="D38">
-        <f>IF(B38="","",INDEX(Items!$B$5:$B$55,MATCH(B38,Items!$A$5:$A$55,0)))</f>
+        <f>IF(B38="","",INDEX(Items!$B$5:$B$58,MATCH(B38,Items!$A$5:$A$58,0)))</f>
         <v/>
       </c>
       <c r="E38">
-        <f>IF(B38="","",INDEX(Items!$E$5:$E$55,MATCH(B38,Items!$A$5:$A$55,0)))</f>
+        <f>IF(B38="","",INDEX(Items!$E$5:$E$58,MATCH(B38,Items!$A$5:$A$58,0)))</f>
         <v/>
       </c>
       <c r="F38">
-        <f>IF(B38="","",INDEX(Items!$M$5:$M$55,MATCH(B38,Items!$A$5:$A$55,0)))</f>
+        <f>IF(B38="","",INDEX(Items!$M$5:$M$58,MATCH(B38,Items!$A$5:$A$58,0)))</f>
         <v/>
       </c>
     </row>
@@ -7667,23 +7991,23 @@
         <v>35</v>
       </c>
       <c r="B39">
-        <f>IF(COUNT(Items!$N$5:$N$55)&lt;A39,"",INDEX(Items!$A$5:$A$55,MATCH(SMALL(Items!$N$5:$N$55,A39),Items!$N$5:$N$55,0)))</f>
+        <f>IF(COUNT(Items!$N$5:$N$58)&lt;A39,"",INDEX(Items!$A$5:$A$58,MATCH(SMALL(Items!$N$5:$N$58,A39),Items!$N$5:$N$58,0)))</f>
         <v/>
       </c>
       <c r="C39" s="6">
-        <f>IF(B39="","",INDEX(Items!$I$5:$I$55,MATCH(B39,Items!$A$5:$A$55,0)))</f>
+        <f>IF(B39="","",INDEX(Items!$I$5:$I$58,MATCH(B39,Items!$A$5:$A$58,0)))</f>
         <v/>
       </c>
       <c r="D39">
-        <f>IF(B39="","",INDEX(Items!$B$5:$B$55,MATCH(B39,Items!$A$5:$A$55,0)))</f>
+        <f>IF(B39="","",INDEX(Items!$B$5:$B$58,MATCH(B39,Items!$A$5:$A$58,0)))</f>
         <v/>
       </c>
       <c r="E39">
-        <f>IF(B39="","",INDEX(Items!$E$5:$E$55,MATCH(B39,Items!$A$5:$A$55,0)))</f>
+        <f>IF(B39="","",INDEX(Items!$E$5:$E$58,MATCH(B39,Items!$A$5:$A$58,0)))</f>
         <v/>
       </c>
       <c r="F39">
-        <f>IF(B39="","",INDEX(Items!$M$5:$M$55,MATCH(B39,Items!$A$5:$A$55,0)))</f>
+        <f>IF(B39="","",INDEX(Items!$M$5:$M$58,MATCH(B39,Items!$A$5:$A$58,0)))</f>
         <v/>
       </c>
     </row>
@@ -7692,23 +8016,23 @@
         <v>36</v>
       </c>
       <c r="B40">
-        <f>IF(COUNT(Items!$N$5:$N$55)&lt;A40,"",INDEX(Items!$A$5:$A$55,MATCH(SMALL(Items!$N$5:$N$55,A40),Items!$N$5:$N$55,0)))</f>
+        <f>IF(COUNT(Items!$N$5:$N$58)&lt;A40,"",INDEX(Items!$A$5:$A$58,MATCH(SMALL(Items!$N$5:$N$58,A40),Items!$N$5:$N$58,0)))</f>
         <v/>
       </c>
       <c r="C40" s="6">
-        <f>IF(B40="","",INDEX(Items!$I$5:$I$55,MATCH(B40,Items!$A$5:$A$55,0)))</f>
+        <f>IF(B40="","",INDEX(Items!$I$5:$I$58,MATCH(B40,Items!$A$5:$A$58,0)))</f>
         <v/>
       </c>
       <c r="D40">
-        <f>IF(B40="","",INDEX(Items!$B$5:$B$55,MATCH(B40,Items!$A$5:$A$55,0)))</f>
+        <f>IF(B40="","",INDEX(Items!$B$5:$B$58,MATCH(B40,Items!$A$5:$A$58,0)))</f>
         <v/>
       </c>
       <c r="E40">
-        <f>IF(B40="","",INDEX(Items!$E$5:$E$55,MATCH(B40,Items!$A$5:$A$55,0)))</f>
+        <f>IF(B40="","",INDEX(Items!$E$5:$E$58,MATCH(B40,Items!$A$5:$A$58,0)))</f>
         <v/>
       </c>
       <c r="F40">
-        <f>IF(B40="","",INDEX(Items!$M$5:$M$55,MATCH(B40,Items!$A$5:$A$55,0)))</f>
+        <f>IF(B40="","",INDEX(Items!$M$5:$M$58,MATCH(B40,Items!$A$5:$A$58,0)))</f>
         <v/>
       </c>
     </row>
@@ -7717,23 +8041,23 @@
         <v>37</v>
       </c>
       <c r="B41">
-        <f>IF(COUNT(Items!$N$5:$N$55)&lt;A41,"",INDEX(Items!$A$5:$A$55,MATCH(SMALL(Items!$N$5:$N$55,A41),Items!$N$5:$N$55,0)))</f>
+        <f>IF(COUNT(Items!$N$5:$N$58)&lt;A41,"",INDEX(Items!$A$5:$A$58,MATCH(SMALL(Items!$N$5:$N$58,A41),Items!$N$5:$N$58,0)))</f>
         <v/>
       </c>
       <c r="C41" s="6">
-        <f>IF(B41="","",INDEX(Items!$I$5:$I$55,MATCH(B41,Items!$A$5:$A$55,0)))</f>
+        <f>IF(B41="","",INDEX(Items!$I$5:$I$58,MATCH(B41,Items!$A$5:$A$58,0)))</f>
         <v/>
       </c>
       <c r="D41">
-        <f>IF(B41="","",INDEX(Items!$B$5:$B$55,MATCH(B41,Items!$A$5:$A$55,0)))</f>
+        <f>IF(B41="","",INDEX(Items!$B$5:$B$58,MATCH(B41,Items!$A$5:$A$58,0)))</f>
         <v/>
       </c>
       <c r="E41">
-        <f>IF(B41="","",INDEX(Items!$E$5:$E$55,MATCH(B41,Items!$A$5:$A$55,0)))</f>
+        <f>IF(B41="","",INDEX(Items!$E$5:$E$58,MATCH(B41,Items!$A$5:$A$58,0)))</f>
         <v/>
       </c>
       <c r="F41">
-        <f>IF(B41="","",INDEX(Items!$M$5:$M$55,MATCH(B41,Items!$A$5:$A$55,0)))</f>
+        <f>IF(B41="","",INDEX(Items!$M$5:$M$58,MATCH(B41,Items!$A$5:$A$58,0)))</f>
         <v/>
       </c>
     </row>
@@ -7742,23 +8066,23 @@
         <v>38</v>
       </c>
       <c r="B42">
-        <f>IF(COUNT(Items!$N$5:$N$55)&lt;A42,"",INDEX(Items!$A$5:$A$55,MATCH(SMALL(Items!$N$5:$N$55,A42),Items!$N$5:$N$55,0)))</f>
+        <f>IF(COUNT(Items!$N$5:$N$58)&lt;A42,"",INDEX(Items!$A$5:$A$58,MATCH(SMALL(Items!$N$5:$N$58,A42),Items!$N$5:$N$58,0)))</f>
         <v/>
       </c>
       <c r="C42" s="6">
-        <f>IF(B42="","",INDEX(Items!$I$5:$I$55,MATCH(B42,Items!$A$5:$A$55,0)))</f>
+        <f>IF(B42="","",INDEX(Items!$I$5:$I$58,MATCH(B42,Items!$A$5:$A$58,0)))</f>
         <v/>
       </c>
       <c r="D42">
-        <f>IF(B42="","",INDEX(Items!$B$5:$B$55,MATCH(B42,Items!$A$5:$A$55,0)))</f>
+        <f>IF(B42="","",INDEX(Items!$B$5:$B$58,MATCH(B42,Items!$A$5:$A$58,0)))</f>
         <v/>
       </c>
       <c r="E42">
-        <f>IF(B42="","",INDEX(Items!$E$5:$E$55,MATCH(B42,Items!$A$5:$A$55,0)))</f>
+        <f>IF(B42="","",INDEX(Items!$E$5:$E$58,MATCH(B42,Items!$A$5:$A$58,0)))</f>
         <v/>
       </c>
       <c r="F42">
-        <f>IF(B42="","",INDEX(Items!$M$5:$M$55,MATCH(B42,Items!$A$5:$A$55,0)))</f>
+        <f>IF(B42="","",INDEX(Items!$M$5:$M$58,MATCH(B42,Items!$A$5:$A$58,0)))</f>
         <v/>
       </c>
     </row>
@@ -7767,23 +8091,23 @@
         <v>39</v>
       </c>
       <c r="B43">
-        <f>IF(COUNT(Items!$N$5:$N$55)&lt;A43,"",INDEX(Items!$A$5:$A$55,MATCH(SMALL(Items!$N$5:$N$55,A43),Items!$N$5:$N$55,0)))</f>
+        <f>IF(COUNT(Items!$N$5:$N$58)&lt;A43,"",INDEX(Items!$A$5:$A$58,MATCH(SMALL(Items!$N$5:$N$58,A43),Items!$N$5:$N$58,0)))</f>
         <v/>
       </c>
       <c r="C43" s="6">
-        <f>IF(B43="","",INDEX(Items!$I$5:$I$55,MATCH(B43,Items!$A$5:$A$55,0)))</f>
+        <f>IF(B43="","",INDEX(Items!$I$5:$I$58,MATCH(B43,Items!$A$5:$A$58,0)))</f>
         <v/>
       </c>
       <c r="D43">
-        <f>IF(B43="","",INDEX(Items!$B$5:$B$55,MATCH(B43,Items!$A$5:$A$55,0)))</f>
+        <f>IF(B43="","",INDEX(Items!$B$5:$B$58,MATCH(B43,Items!$A$5:$A$58,0)))</f>
         <v/>
       </c>
       <c r="E43">
-        <f>IF(B43="","",INDEX(Items!$E$5:$E$55,MATCH(B43,Items!$A$5:$A$55,0)))</f>
+        <f>IF(B43="","",INDEX(Items!$E$5:$E$58,MATCH(B43,Items!$A$5:$A$58,0)))</f>
         <v/>
       </c>
       <c r="F43">
-        <f>IF(B43="","",INDEX(Items!$M$5:$M$55,MATCH(B43,Items!$A$5:$A$55,0)))</f>
+        <f>IF(B43="","",INDEX(Items!$M$5:$M$58,MATCH(B43,Items!$A$5:$A$58,0)))</f>
         <v/>
       </c>
     </row>
@@ -7792,23 +8116,23 @@
         <v>40</v>
       </c>
       <c r="B44">
-        <f>IF(COUNT(Items!$N$5:$N$55)&lt;A44,"",INDEX(Items!$A$5:$A$55,MATCH(SMALL(Items!$N$5:$N$55,A44),Items!$N$5:$N$55,0)))</f>
+        <f>IF(COUNT(Items!$N$5:$N$58)&lt;A44,"",INDEX(Items!$A$5:$A$58,MATCH(SMALL(Items!$N$5:$N$58,A44),Items!$N$5:$N$58,0)))</f>
         <v/>
       </c>
       <c r="C44" s="6">
-        <f>IF(B44="","",INDEX(Items!$I$5:$I$55,MATCH(B44,Items!$A$5:$A$55,0)))</f>
+        <f>IF(B44="","",INDEX(Items!$I$5:$I$58,MATCH(B44,Items!$A$5:$A$58,0)))</f>
         <v/>
       </c>
       <c r="D44">
-        <f>IF(B44="","",INDEX(Items!$B$5:$B$55,MATCH(B44,Items!$A$5:$A$55,0)))</f>
+        <f>IF(B44="","",INDEX(Items!$B$5:$B$58,MATCH(B44,Items!$A$5:$A$58,0)))</f>
         <v/>
       </c>
       <c r="E44">
-        <f>IF(B44="","",INDEX(Items!$E$5:$E$55,MATCH(B44,Items!$A$5:$A$55,0)))</f>
+        <f>IF(B44="","",INDEX(Items!$E$5:$E$58,MATCH(B44,Items!$A$5:$A$58,0)))</f>
         <v/>
       </c>
       <c r="F44">
-        <f>IF(B44="","",INDEX(Items!$M$5:$M$55,MATCH(B44,Items!$A$5:$A$55,0)))</f>
+        <f>IF(B44="","",INDEX(Items!$M$5:$M$58,MATCH(B44,Items!$A$5:$A$58,0)))</f>
         <v/>
       </c>
     </row>
@@ -7817,23 +8141,23 @@
         <v>41</v>
       </c>
       <c r="B45">
-        <f>IF(COUNT(Items!$N$5:$N$55)&lt;A45,"",INDEX(Items!$A$5:$A$55,MATCH(SMALL(Items!$N$5:$N$55,A45),Items!$N$5:$N$55,0)))</f>
+        <f>IF(COUNT(Items!$N$5:$N$58)&lt;A45,"",INDEX(Items!$A$5:$A$58,MATCH(SMALL(Items!$N$5:$N$58,A45),Items!$N$5:$N$58,0)))</f>
         <v/>
       </c>
       <c r="C45" s="6">
-        <f>IF(B45="","",INDEX(Items!$I$5:$I$55,MATCH(B45,Items!$A$5:$A$55,0)))</f>
+        <f>IF(B45="","",INDEX(Items!$I$5:$I$58,MATCH(B45,Items!$A$5:$A$58,0)))</f>
         <v/>
       </c>
       <c r="D45">
-        <f>IF(B45="","",INDEX(Items!$B$5:$B$55,MATCH(B45,Items!$A$5:$A$55,0)))</f>
+        <f>IF(B45="","",INDEX(Items!$B$5:$B$58,MATCH(B45,Items!$A$5:$A$58,0)))</f>
         <v/>
       </c>
       <c r="E45">
-        <f>IF(B45="","",INDEX(Items!$E$5:$E$55,MATCH(B45,Items!$A$5:$A$55,0)))</f>
+        <f>IF(B45="","",INDEX(Items!$E$5:$E$58,MATCH(B45,Items!$A$5:$A$58,0)))</f>
         <v/>
       </c>
       <c r="F45">
-        <f>IF(B45="","",INDEX(Items!$M$5:$M$55,MATCH(B45,Items!$A$5:$A$55,0)))</f>
+        <f>IF(B45="","",INDEX(Items!$M$5:$M$58,MATCH(B45,Items!$A$5:$A$58,0)))</f>
         <v/>
       </c>
     </row>
@@ -7842,23 +8166,23 @@
         <v>42</v>
       </c>
       <c r="B46">
-        <f>IF(COUNT(Items!$N$5:$N$55)&lt;A46,"",INDEX(Items!$A$5:$A$55,MATCH(SMALL(Items!$N$5:$N$55,A46),Items!$N$5:$N$55,0)))</f>
+        <f>IF(COUNT(Items!$N$5:$N$58)&lt;A46,"",INDEX(Items!$A$5:$A$58,MATCH(SMALL(Items!$N$5:$N$58,A46),Items!$N$5:$N$58,0)))</f>
         <v/>
       </c>
       <c r="C46" s="6">
-        <f>IF(B46="","",INDEX(Items!$I$5:$I$55,MATCH(B46,Items!$A$5:$A$55,0)))</f>
+        <f>IF(B46="","",INDEX(Items!$I$5:$I$58,MATCH(B46,Items!$A$5:$A$58,0)))</f>
         <v/>
       </c>
       <c r="D46">
-        <f>IF(B46="","",INDEX(Items!$B$5:$B$55,MATCH(B46,Items!$A$5:$A$55,0)))</f>
+        <f>IF(B46="","",INDEX(Items!$B$5:$B$58,MATCH(B46,Items!$A$5:$A$58,0)))</f>
         <v/>
       </c>
       <c r="E46">
-        <f>IF(B46="","",INDEX(Items!$E$5:$E$55,MATCH(B46,Items!$A$5:$A$55,0)))</f>
+        <f>IF(B46="","",INDEX(Items!$E$5:$E$58,MATCH(B46,Items!$A$5:$A$58,0)))</f>
         <v/>
       </c>
       <c r="F46">
-        <f>IF(B46="","",INDEX(Items!$M$5:$M$55,MATCH(B46,Items!$A$5:$A$55,0)))</f>
+        <f>IF(B46="","",INDEX(Items!$M$5:$M$58,MATCH(B46,Items!$A$5:$A$58,0)))</f>
         <v/>
       </c>
     </row>
@@ -7867,23 +8191,23 @@
         <v>43</v>
       </c>
       <c r="B47">
-        <f>IF(COUNT(Items!$N$5:$N$55)&lt;A47,"",INDEX(Items!$A$5:$A$55,MATCH(SMALL(Items!$N$5:$N$55,A47),Items!$N$5:$N$55,0)))</f>
+        <f>IF(COUNT(Items!$N$5:$N$58)&lt;A47,"",INDEX(Items!$A$5:$A$58,MATCH(SMALL(Items!$N$5:$N$58,A47),Items!$N$5:$N$58,0)))</f>
         <v/>
       </c>
       <c r="C47" s="6">
-        <f>IF(B47="","",INDEX(Items!$I$5:$I$55,MATCH(B47,Items!$A$5:$A$55,0)))</f>
+        <f>IF(B47="","",INDEX(Items!$I$5:$I$58,MATCH(B47,Items!$A$5:$A$58,0)))</f>
         <v/>
       </c>
       <c r="D47">
-        <f>IF(B47="","",INDEX(Items!$B$5:$B$55,MATCH(B47,Items!$A$5:$A$55,0)))</f>
+        <f>IF(B47="","",INDEX(Items!$B$5:$B$58,MATCH(B47,Items!$A$5:$A$58,0)))</f>
         <v/>
       </c>
       <c r="E47">
-        <f>IF(B47="","",INDEX(Items!$E$5:$E$55,MATCH(B47,Items!$A$5:$A$55,0)))</f>
+        <f>IF(B47="","",INDEX(Items!$E$5:$E$58,MATCH(B47,Items!$A$5:$A$58,0)))</f>
         <v/>
       </c>
       <c r="F47">
-        <f>IF(B47="","",INDEX(Items!$M$5:$M$55,MATCH(B47,Items!$A$5:$A$55,0)))</f>
+        <f>IF(B47="","",INDEX(Items!$M$5:$M$58,MATCH(B47,Items!$A$5:$A$58,0)))</f>
         <v/>
       </c>
     </row>
@@ -7892,23 +8216,23 @@
         <v>44</v>
       </c>
       <c r="B48">
-        <f>IF(COUNT(Items!$N$5:$N$55)&lt;A48,"",INDEX(Items!$A$5:$A$55,MATCH(SMALL(Items!$N$5:$N$55,A48),Items!$N$5:$N$55,0)))</f>
+        <f>IF(COUNT(Items!$N$5:$N$58)&lt;A48,"",INDEX(Items!$A$5:$A$58,MATCH(SMALL(Items!$N$5:$N$58,A48),Items!$N$5:$N$58,0)))</f>
         <v/>
       </c>
       <c r="C48" s="6">
-        <f>IF(B48="","",INDEX(Items!$I$5:$I$55,MATCH(B48,Items!$A$5:$A$55,0)))</f>
+        <f>IF(B48="","",INDEX(Items!$I$5:$I$58,MATCH(B48,Items!$A$5:$A$58,0)))</f>
         <v/>
       </c>
       <c r="D48">
-        <f>IF(B48="","",INDEX(Items!$B$5:$B$55,MATCH(B48,Items!$A$5:$A$55,0)))</f>
+        <f>IF(B48="","",INDEX(Items!$B$5:$B$58,MATCH(B48,Items!$A$5:$A$58,0)))</f>
         <v/>
       </c>
       <c r="E48">
-        <f>IF(B48="","",INDEX(Items!$E$5:$E$55,MATCH(B48,Items!$A$5:$A$55,0)))</f>
+        <f>IF(B48="","",INDEX(Items!$E$5:$E$58,MATCH(B48,Items!$A$5:$A$58,0)))</f>
         <v/>
       </c>
       <c r="F48">
-        <f>IF(B48="","",INDEX(Items!$M$5:$M$55,MATCH(B48,Items!$A$5:$A$55,0)))</f>
+        <f>IF(B48="","",INDEX(Items!$M$5:$M$58,MATCH(B48,Items!$A$5:$A$58,0)))</f>
         <v/>
       </c>
     </row>
@@ -7917,23 +8241,23 @@
         <v>45</v>
       </c>
       <c r="B49">
-        <f>IF(COUNT(Items!$N$5:$N$55)&lt;A49,"",INDEX(Items!$A$5:$A$55,MATCH(SMALL(Items!$N$5:$N$55,A49),Items!$N$5:$N$55,0)))</f>
+        <f>IF(COUNT(Items!$N$5:$N$58)&lt;A49,"",INDEX(Items!$A$5:$A$58,MATCH(SMALL(Items!$N$5:$N$58,A49),Items!$N$5:$N$58,0)))</f>
         <v/>
       </c>
       <c r="C49" s="6">
-        <f>IF(B49="","",INDEX(Items!$I$5:$I$55,MATCH(B49,Items!$A$5:$A$55,0)))</f>
+        <f>IF(B49="","",INDEX(Items!$I$5:$I$58,MATCH(B49,Items!$A$5:$A$58,0)))</f>
         <v/>
       </c>
       <c r="D49">
-        <f>IF(B49="","",INDEX(Items!$B$5:$B$55,MATCH(B49,Items!$A$5:$A$55,0)))</f>
+        <f>IF(B49="","",INDEX(Items!$B$5:$B$58,MATCH(B49,Items!$A$5:$A$58,0)))</f>
         <v/>
       </c>
       <c r="E49">
-        <f>IF(B49="","",INDEX(Items!$E$5:$E$55,MATCH(B49,Items!$A$5:$A$55,0)))</f>
+        <f>IF(B49="","",INDEX(Items!$E$5:$E$58,MATCH(B49,Items!$A$5:$A$58,0)))</f>
         <v/>
       </c>
       <c r="F49">
-        <f>IF(B49="","",INDEX(Items!$M$5:$M$55,MATCH(B49,Items!$A$5:$A$55,0)))</f>
+        <f>IF(B49="","",INDEX(Items!$M$5:$M$58,MATCH(B49,Items!$A$5:$A$58,0)))</f>
         <v/>
       </c>
     </row>
@@ -7942,23 +8266,23 @@
         <v>46</v>
       </c>
       <c r="B50">
-        <f>IF(COUNT(Items!$N$5:$N$55)&lt;A50,"",INDEX(Items!$A$5:$A$55,MATCH(SMALL(Items!$N$5:$N$55,A50),Items!$N$5:$N$55,0)))</f>
+        <f>IF(COUNT(Items!$N$5:$N$58)&lt;A50,"",INDEX(Items!$A$5:$A$58,MATCH(SMALL(Items!$N$5:$N$58,A50),Items!$N$5:$N$58,0)))</f>
         <v/>
       </c>
       <c r="C50" s="6">
-        <f>IF(B50="","",INDEX(Items!$I$5:$I$55,MATCH(B50,Items!$A$5:$A$55,0)))</f>
+        <f>IF(B50="","",INDEX(Items!$I$5:$I$58,MATCH(B50,Items!$A$5:$A$58,0)))</f>
         <v/>
       </c>
       <c r="D50">
-        <f>IF(B50="","",INDEX(Items!$B$5:$B$55,MATCH(B50,Items!$A$5:$A$55,0)))</f>
+        <f>IF(B50="","",INDEX(Items!$B$5:$B$58,MATCH(B50,Items!$A$5:$A$58,0)))</f>
         <v/>
       </c>
       <c r="E50">
-        <f>IF(B50="","",INDEX(Items!$E$5:$E$55,MATCH(B50,Items!$A$5:$A$55,0)))</f>
+        <f>IF(B50="","",INDEX(Items!$E$5:$E$58,MATCH(B50,Items!$A$5:$A$58,0)))</f>
         <v/>
       </c>
       <c r="F50">
-        <f>IF(B50="","",INDEX(Items!$M$5:$M$55,MATCH(B50,Items!$A$5:$A$55,0)))</f>
+        <f>IF(B50="","",INDEX(Items!$M$5:$M$58,MATCH(B50,Items!$A$5:$A$58,0)))</f>
         <v/>
       </c>
     </row>
@@ -7967,23 +8291,23 @@
         <v>47</v>
       </c>
       <c r="B51">
-        <f>IF(COUNT(Items!$N$5:$N$55)&lt;A51,"",INDEX(Items!$A$5:$A$55,MATCH(SMALL(Items!$N$5:$N$55,A51),Items!$N$5:$N$55,0)))</f>
+        <f>IF(COUNT(Items!$N$5:$N$58)&lt;A51,"",INDEX(Items!$A$5:$A$58,MATCH(SMALL(Items!$N$5:$N$58,A51),Items!$N$5:$N$58,0)))</f>
         <v/>
       </c>
       <c r="C51" s="6">
-        <f>IF(B51="","",INDEX(Items!$I$5:$I$55,MATCH(B51,Items!$A$5:$A$55,0)))</f>
+        <f>IF(B51="","",INDEX(Items!$I$5:$I$58,MATCH(B51,Items!$A$5:$A$58,0)))</f>
         <v/>
       </c>
       <c r="D51">
-        <f>IF(B51="","",INDEX(Items!$B$5:$B$55,MATCH(B51,Items!$A$5:$A$55,0)))</f>
+        <f>IF(B51="","",INDEX(Items!$B$5:$B$58,MATCH(B51,Items!$A$5:$A$58,0)))</f>
         <v/>
       </c>
       <c r="E51">
-        <f>IF(B51="","",INDEX(Items!$E$5:$E$55,MATCH(B51,Items!$A$5:$A$55,0)))</f>
+        <f>IF(B51="","",INDEX(Items!$E$5:$E$58,MATCH(B51,Items!$A$5:$A$58,0)))</f>
         <v/>
       </c>
       <c r="F51">
-        <f>IF(B51="","",INDEX(Items!$M$5:$M$55,MATCH(B51,Items!$A$5:$A$55,0)))</f>
+        <f>IF(B51="","",INDEX(Items!$M$5:$M$58,MATCH(B51,Items!$A$5:$A$58,0)))</f>
         <v/>
       </c>
     </row>
@@ -7992,23 +8316,23 @@
         <v>48</v>
       </c>
       <c r="B52">
-        <f>IF(COUNT(Items!$N$5:$N$55)&lt;A52,"",INDEX(Items!$A$5:$A$55,MATCH(SMALL(Items!$N$5:$N$55,A52),Items!$N$5:$N$55,0)))</f>
+        <f>IF(COUNT(Items!$N$5:$N$58)&lt;A52,"",INDEX(Items!$A$5:$A$58,MATCH(SMALL(Items!$N$5:$N$58,A52),Items!$N$5:$N$58,0)))</f>
         <v/>
       </c>
       <c r="C52" s="6">
-        <f>IF(B52="","",INDEX(Items!$I$5:$I$55,MATCH(B52,Items!$A$5:$A$55,0)))</f>
+        <f>IF(B52="","",INDEX(Items!$I$5:$I$58,MATCH(B52,Items!$A$5:$A$58,0)))</f>
         <v/>
       </c>
       <c r="D52">
-        <f>IF(B52="","",INDEX(Items!$B$5:$B$55,MATCH(B52,Items!$A$5:$A$55,0)))</f>
+        <f>IF(B52="","",INDEX(Items!$B$5:$B$58,MATCH(B52,Items!$A$5:$A$58,0)))</f>
         <v/>
       </c>
       <c r="E52">
-        <f>IF(B52="","",INDEX(Items!$E$5:$E$55,MATCH(B52,Items!$A$5:$A$55,0)))</f>
+        <f>IF(B52="","",INDEX(Items!$E$5:$E$58,MATCH(B52,Items!$A$5:$A$58,0)))</f>
         <v/>
       </c>
       <c r="F52">
-        <f>IF(B52="","",INDEX(Items!$M$5:$M$55,MATCH(B52,Items!$A$5:$A$55,0)))</f>
+        <f>IF(B52="","",INDEX(Items!$M$5:$M$58,MATCH(B52,Items!$A$5:$A$58,0)))</f>
         <v/>
       </c>
     </row>
@@ -8017,23 +8341,23 @@
         <v>49</v>
       </c>
       <c r="B53">
-        <f>IF(COUNT(Items!$N$5:$N$55)&lt;A53,"",INDEX(Items!$A$5:$A$55,MATCH(SMALL(Items!$N$5:$N$55,A53),Items!$N$5:$N$55,0)))</f>
+        <f>IF(COUNT(Items!$N$5:$N$58)&lt;A53,"",INDEX(Items!$A$5:$A$58,MATCH(SMALL(Items!$N$5:$N$58,A53),Items!$N$5:$N$58,0)))</f>
         <v/>
       </c>
       <c r="C53" s="6">
-        <f>IF(B53="","",INDEX(Items!$I$5:$I$55,MATCH(B53,Items!$A$5:$A$55,0)))</f>
+        <f>IF(B53="","",INDEX(Items!$I$5:$I$58,MATCH(B53,Items!$A$5:$A$58,0)))</f>
         <v/>
       </c>
       <c r="D53">
-        <f>IF(B53="","",INDEX(Items!$B$5:$B$55,MATCH(B53,Items!$A$5:$A$55,0)))</f>
+        <f>IF(B53="","",INDEX(Items!$B$5:$B$58,MATCH(B53,Items!$A$5:$A$58,0)))</f>
         <v/>
       </c>
       <c r="E53">
-        <f>IF(B53="","",INDEX(Items!$E$5:$E$55,MATCH(B53,Items!$A$5:$A$55,0)))</f>
+        <f>IF(B53="","",INDEX(Items!$E$5:$E$58,MATCH(B53,Items!$A$5:$A$58,0)))</f>
         <v/>
       </c>
       <c r="F53">
-        <f>IF(B53="","",INDEX(Items!$M$5:$M$55,MATCH(B53,Items!$A$5:$A$55,0)))</f>
+        <f>IF(B53="","",INDEX(Items!$M$5:$M$58,MATCH(B53,Items!$A$5:$A$58,0)))</f>
         <v/>
       </c>
     </row>
@@ -8042,23 +8366,23 @@
         <v>50</v>
       </c>
       <c r="B54">
-        <f>IF(COUNT(Items!$N$5:$N$55)&lt;A54,"",INDEX(Items!$A$5:$A$55,MATCH(SMALL(Items!$N$5:$N$55,A54),Items!$N$5:$N$55,0)))</f>
+        <f>IF(COUNT(Items!$N$5:$N$58)&lt;A54,"",INDEX(Items!$A$5:$A$58,MATCH(SMALL(Items!$N$5:$N$58,A54),Items!$N$5:$N$58,0)))</f>
         <v/>
       </c>
       <c r="C54" s="6">
-        <f>IF(B54="","",INDEX(Items!$I$5:$I$55,MATCH(B54,Items!$A$5:$A$55,0)))</f>
+        <f>IF(B54="","",INDEX(Items!$I$5:$I$58,MATCH(B54,Items!$A$5:$A$58,0)))</f>
         <v/>
       </c>
       <c r="D54">
-        <f>IF(B54="","",INDEX(Items!$B$5:$B$55,MATCH(B54,Items!$A$5:$A$55,0)))</f>
+        <f>IF(B54="","",INDEX(Items!$B$5:$B$58,MATCH(B54,Items!$A$5:$A$58,0)))</f>
         <v/>
       </c>
       <c r="E54">
-        <f>IF(B54="","",INDEX(Items!$E$5:$E$55,MATCH(B54,Items!$A$5:$A$55,0)))</f>
+        <f>IF(B54="","",INDEX(Items!$E$5:$E$58,MATCH(B54,Items!$A$5:$A$58,0)))</f>
         <v/>
       </c>
       <c r="F54">
-        <f>IF(B54="","",INDEX(Items!$M$5:$M$55,MATCH(B54,Items!$A$5:$A$55,0)))</f>
+        <f>IF(B54="","",INDEX(Items!$M$5:$M$58,MATCH(B54,Items!$A$5:$A$58,0)))</f>
         <v/>
       </c>
     </row>
@@ -8067,23 +8391,98 @@
         <v>51</v>
       </c>
       <c r="B55">
-        <f>IF(COUNT(Items!$N$5:$N$55)&lt;A55,"",INDEX(Items!$A$5:$A$55,MATCH(SMALL(Items!$N$5:$N$55,A55),Items!$N$5:$N$55,0)))</f>
+        <f>IF(COUNT(Items!$N$5:$N$58)&lt;A55,"",INDEX(Items!$A$5:$A$58,MATCH(SMALL(Items!$N$5:$N$58,A55),Items!$N$5:$N$58,0)))</f>
         <v/>
       </c>
       <c r="C55" s="6">
-        <f>IF(B55="","",INDEX(Items!$I$5:$I$55,MATCH(B55,Items!$A$5:$A$55,0)))</f>
+        <f>IF(B55="","",INDEX(Items!$I$5:$I$58,MATCH(B55,Items!$A$5:$A$58,0)))</f>
         <v/>
       </c>
       <c r="D55">
-        <f>IF(B55="","",INDEX(Items!$B$5:$B$55,MATCH(B55,Items!$A$5:$A$55,0)))</f>
+        <f>IF(B55="","",INDEX(Items!$B$5:$B$58,MATCH(B55,Items!$A$5:$A$58,0)))</f>
         <v/>
       </c>
       <c r="E55">
-        <f>IF(B55="","",INDEX(Items!$E$5:$E$55,MATCH(B55,Items!$A$5:$A$55,0)))</f>
+        <f>IF(B55="","",INDEX(Items!$E$5:$E$58,MATCH(B55,Items!$A$5:$A$58,0)))</f>
         <v/>
       </c>
       <c r="F55">
-        <f>IF(B55="","",INDEX(Items!$M$5:$M$55,MATCH(B55,Items!$A$5:$A$55,0)))</f>
+        <f>IF(B55="","",INDEX(Items!$M$5:$M$58,MATCH(B55,Items!$A$5:$A$58,0)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>52</v>
+      </c>
+      <c r="B56">
+        <f>IF(COUNT(Items!$N$5:$N$58)&lt;A56,"",INDEX(Items!$A$5:$A$58,MATCH(SMALL(Items!$N$5:$N$58,A56),Items!$N$5:$N$58,0)))</f>
+        <v/>
+      </c>
+      <c r="C56" s="6">
+        <f>IF(B56="","",INDEX(Items!$I$5:$I$58,MATCH(B56,Items!$A$5:$A$58,0)))</f>
+        <v/>
+      </c>
+      <c r="D56">
+        <f>IF(B56="","",INDEX(Items!$B$5:$B$58,MATCH(B56,Items!$A$5:$A$58,0)))</f>
+        <v/>
+      </c>
+      <c r="E56">
+        <f>IF(B56="","",INDEX(Items!$E$5:$E$58,MATCH(B56,Items!$A$5:$A$58,0)))</f>
+        <v/>
+      </c>
+      <c r="F56">
+        <f>IF(B56="","",INDEX(Items!$M$5:$M$58,MATCH(B56,Items!$A$5:$A$58,0)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>53</v>
+      </c>
+      <c r="B57">
+        <f>IF(COUNT(Items!$N$5:$N$58)&lt;A57,"",INDEX(Items!$A$5:$A$58,MATCH(SMALL(Items!$N$5:$N$58,A57),Items!$N$5:$N$58,0)))</f>
+        <v/>
+      </c>
+      <c r="C57" s="6">
+        <f>IF(B57="","",INDEX(Items!$I$5:$I$58,MATCH(B57,Items!$A$5:$A$58,0)))</f>
+        <v/>
+      </c>
+      <c r="D57">
+        <f>IF(B57="","",INDEX(Items!$B$5:$B$58,MATCH(B57,Items!$A$5:$A$58,0)))</f>
+        <v/>
+      </c>
+      <c r="E57">
+        <f>IF(B57="","",INDEX(Items!$E$5:$E$58,MATCH(B57,Items!$A$5:$A$58,0)))</f>
+        <v/>
+      </c>
+      <c r="F57">
+        <f>IF(B57="","",INDEX(Items!$M$5:$M$58,MATCH(B57,Items!$A$5:$A$58,0)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>54</v>
+      </c>
+      <c r="B58">
+        <f>IF(COUNT(Items!$N$5:$N$58)&lt;A58,"",INDEX(Items!$A$5:$A$58,MATCH(SMALL(Items!$N$5:$N$58,A58),Items!$N$5:$N$58,0)))</f>
+        <v/>
+      </c>
+      <c r="C58" s="6">
+        <f>IF(B58="","",INDEX(Items!$I$5:$I$58,MATCH(B58,Items!$A$5:$A$58,0)))</f>
+        <v/>
+      </c>
+      <c r="D58">
+        <f>IF(B58="","",INDEX(Items!$B$5:$B$58,MATCH(B58,Items!$A$5:$A$58,0)))</f>
+        <v/>
+      </c>
+      <c r="E58">
+        <f>IF(B58="","",INDEX(Items!$E$5:$E$58,MATCH(B58,Items!$A$5:$A$58,0)))</f>
+        <v/>
+      </c>
+      <c r="F58">
+        <f>IF(B58="","",INDEX(Items!$M$5:$M$58,MATCH(B58,Items!$A$5:$A$58,0)))</f>
         <v/>
       </c>
     </row>
@@ -8145,11 +8544,11 @@
         </is>
       </c>
       <c r="C5">
-        <f>COUNTIF(Items!$E$5:$E$55,A5)</f>
+        <f>COUNTIF(Items!$E$5:$E$58,A5)</f>
         <v/>
       </c>
       <c r="D5" s="6">
-        <f>IF(SUMPRODUCT((Items!$E$5:$E$55=A5)*Items!$H$5:$H$55)=0,"",SUMPRODUCT((Items!$E$5:$E$55=A5)*Items!$G$5:$G$55)/SUMPRODUCT((Items!$E$5:$E$55=A5)*Items!$H$5:$H$55))</f>
+        <f>IF(SUMPRODUCT((Items!$E$5:$E$58=A5)*Items!$H$5:$H$58)=0,"",SUMPRODUCT((Items!$E$5:$E$58=A5)*Items!$G$5:$G$58)/SUMPRODUCT((Items!$E$5:$E$58=A5)*Items!$H$5:$H$58))</f>
         <v/>
       </c>
     </row>
@@ -8165,11 +8564,11 @@
         </is>
       </c>
       <c r="C6">
-        <f>COUNTIF(Items!$E$5:$E$55,A6)</f>
+        <f>COUNTIF(Items!$E$5:$E$58,A6)</f>
         <v/>
       </c>
       <c r="D6" s="6">
-        <f>IF(SUMPRODUCT((Items!$E$5:$E$55=A6)*Items!$H$5:$H$55)=0,"",SUMPRODUCT((Items!$E$5:$E$55=A6)*Items!$G$5:$G$55)/SUMPRODUCT((Items!$E$5:$E$55=A6)*Items!$H$5:$H$55))</f>
+        <f>IF(SUMPRODUCT((Items!$E$5:$E$58=A6)*Items!$H$5:$H$58)=0,"",SUMPRODUCT((Items!$E$5:$E$58=A6)*Items!$G$5:$G$58)/SUMPRODUCT((Items!$E$5:$E$58=A6)*Items!$H$5:$H$58))</f>
         <v/>
       </c>
     </row>
@@ -8185,11 +8584,11 @@
         </is>
       </c>
       <c r="C7">
-        <f>COUNTIF(Items!$E$5:$E$55,A7)</f>
+        <f>COUNTIF(Items!$E$5:$E$58,A7)</f>
         <v/>
       </c>
       <c r="D7" s="6">
-        <f>IF(SUMPRODUCT((Items!$E$5:$E$55=A7)*Items!$H$5:$H$55)=0,"",SUMPRODUCT((Items!$E$5:$E$55=A7)*Items!$G$5:$G$55)/SUMPRODUCT((Items!$E$5:$E$55=A7)*Items!$H$5:$H$55))</f>
+        <f>IF(SUMPRODUCT((Items!$E$5:$E$58=A7)*Items!$H$5:$H$58)=0,"",SUMPRODUCT((Items!$E$5:$E$58=A7)*Items!$G$5:$G$58)/SUMPRODUCT((Items!$E$5:$E$58=A7)*Items!$H$5:$H$58))</f>
         <v/>
       </c>
     </row>
@@ -8205,11 +8604,11 @@
         </is>
       </c>
       <c r="C8">
-        <f>COUNTIF(Items!$E$5:$E$55,A8)</f>
+        <f>COUNTIF(Items!$E$5:$E$58,A8)</f>
         <v/>
       </c>
       <c r="D8" s="6">
-        <f>IF(SUMPRODUCT((Items!$E$5:$E$55=A8)*Items!$H$5:$H$55)=0,"",SUMPRODUCT((Items!$E$5:$E$55=A8)*Items!$G$5:$G$55)/SUMPRODUCT((Items!$E$5:$E$55=A8)*Items!$H$5:$H$55))</f>
+        <f>IF(SUMPRODUCT((Items!$E$5:$E$58=A8)*Items!$H$5:$H$58)=0,"",SUMPRODUCT((Items!$E$5:$E$58=A8)*Items!$G$5:$G$58)/SUMPRODUCT((Items!$E$5:$E$58=A8)*Items!$H$5:$H$58))</f>
         <v/>
       </c>
     </row>
@@ -8223,11 +8622,11 @@
         </is>
       </c>
       <c r="C9">
-        <f>COUNTIF(Items!$B$5:$B$55,A9)</f>
+        <f>COUNTIF(Items!$B$5:$B$58,A9)</f>
         <v/>
       </c>
       <c r="D9" s="6">
-        <f>IF(SUMPRODUCT((Items!$B$5:$B$55=A9)*Items!$H$5:$H$55)=0,"",SUMPRODUCT((Items!$B$5:$B$55=A9)*Items!$G$5:$G$55)/SUMPRODUCT((Items!$B$5:$B$55=A9)*Items!$H$5:$H$55))</f>
+        <f>IF(SUMPRODUCT((Items!$B$5:$B$58=A9)*Items!$H$5:$H$58)=0,"",SUMPRODUCT((Items!$B$5:$B$58=A9)*Items!$G$5:$G$58)/SUMPRODUCT((Items!$B$5:$B$58=A9)*Items!$H$5:$H$58))</f>
         <v/>
       </c>
     </row>
@@ -8241,11 +8640,11 @@
         </is>
       </c>
       <c r="C10">
-        <f>COUNTIF(Items!$B$5:$B$55,A10)</f>
+        <f>COUNTIF(Items!$B$5:$B$58,A10)</f>
         <v/>
       </c>
       <c r="D10" s="6">
-        <f>IF(SUMPRODUCT((Items!$B$5:$B$55=A10)*Items!$H$5:$H$55)=0,"",SUMPRODUCT((Items!$B$5:$B$55=A10)*Items!$G$5:$G$55)/SUMPRODUCT((Items!$B$5:$B$55=A10)*Items!$H$5:$H$55))</f>
+        <f>IF(SUMPRODUCT((Items!$B$5:$B$58=A10)*Items!$H$5:$H$58)=0,"",SUMPRODUCT((Items!$B$5:$B$58=A10)*Items!$G$5:$G$58)/SUMPRODUCT((Items!$B$5:$B$58=A10)*Items!$H$5:$H$58))</f>
         <v/>
       </c>
     </row>
@@ -8259,11 +8658,11 @@
         </is>
       </c>
       <c r="C11">
-        <f>COUNTIF(Items!$B$5:$B$55,A11)</f>
+        <f>COUNTIF(Items!$B$5:$B$58,A11)</f>
         <v/>
       </c>
       <c r="D11" s="6">
-        <f>IF(SUMPRODUCT((Items!$B$5:$B$55=A11)*Items!$H$5:$H$55)=0,"",SUMPRODUCT((Items!$B$5:$B$55=A11)*Items!$G$5:$G$55)/SUMPRODUCT((Items!$B$5:$B$55=A11)*Items!$H$5:$H$55))</f>
+        <f>IF(SUMPRODUCT((Items!$B$5:$B$58=A11)*Items!$H$5:$H$58)=0,"",SUMPRODUCT((Items!$B$5:$B$58=A11)*Items!$G$5:$G$58)/SUMPRODUCT((Items!$B$5:$B$58=A11)*Items!$H$5:$H$58))</f>
         <v/>
       </c>
     </row>
@@ -8277,11 +8676,11 @@
         </is>
       </c>
       <c r="C12">
-        <f>COUNTIF(Items!$B$5:$B$55,A12)</f>
+        <f>COUNTIF(Items!$B$5:$B$58,A12)</f>
         <v/>
       </c>
       <c r="D12" s="6">
-        <f>IF(SUMPRODUCT((Items!$B$5:$B$55=A12)*Items!$H$5:$H$55)=0,"",SUMPRODUCT((Items!$B$5:$B$55=A12)*Items!$G$5:$G$55)/SUMPRODUCT((Items!$B$5:$B$55=A12)*Items!$H$5:$H$55))</f>
+        <f>IF(SUMPRODUCT((Items!$B$5:$B$58=A12)*Items!$H$5:$H$58)=0,"",SUMPRODUCT((Items!$B$5:$B$58=A12)*Items!$G$5:$G$58)/SUMPRODUCT((Items!$B$5:$B$58=A12)*Items!$H$5:$H$58))</f>
         <v/>
       </c>
     </row>
@@ -8295,11 +8694,11 @@
         </is>
       </c>
       <c r="C13">
-        <f>COUNTIF(Items!$B$5:$B$55,A13)</f>
+        <f>COUNTIF(Items!$B$5:$B$58,A13)</f>
         <v/>
       </c>
       <c r="D13" s="6">
-        <f>IF(SUMPRODUCT((Items!$B$5:$B$55=A13)*Items!$H$5:$H$55)=0,"",SUMPRODUCT((Items!$B$5:$B$55=A13)*Items!$G$5:$G$55)/SUMPRODUCT((Items!$B$5:$B$55=A13)*Items!$H$5:$H$55))</f>
+        <f>IF(SUMPRODUCT((Items!$B$5:$B$58=A13)*Items!$H$5:$H$58)=0,"",SUMPRODUCT((Items!$B$5:$B$58=A13)*Items!$G$5:$G$58)/SUMPRODUCT((Items!$B$5:$B$58=A13)*Items!$H$5:$H$58))</f>
         <v/>
       </c>
     </row>
@@ -8313,11 +8712,11 @@
         </is>
       </c>
       <c r="C14">
-        <f>COUNTIF(Items!$B$5:$B$55,A14)</f>
+        <f>COUNTIF(Items!$B$5:$B$58,A14)</f>
         <v/>
       </c>
       <c r="D14" s="6">
-        <f>IF(SUMPRODUCT((Items!$B$5:$B$55=A14)*Items!$H$5:$H$55)=0,"",SUMPRODUCT((Items!$B$5:$B$55=A14)*Items!$G$5:$G$55)/SUMPRODUCT((Items!$B$5:$B$55=A14)*Items!$H$5:$H$55))</f>
+        <f>IF(SUMPRODUCT((Items!$B$5:$B$58=A14)*Items!$H$5:$H$58)=0,"",SUMPRODUCT((Items!$B$5:$B$58=A14)*Items!$G$5:$G$58)/SUMPRODUCT((Items!$B$5:$B$58=A14)*Items!$H$5:$H$58))</f>
         <v/>
       </c>
     </row>
@@ -8374,19 +8773,19 @@
         <v>1</v>
       </c>
       <c r="B5" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AZ$3=B$4)*ISNUMBER(Marks!$B$5:$AZ$5))=0,"",SUMPRODUCT((Marks!$B$3:$AZ$3=B$4)*(Marks!$B$5:$AZ$5=1))/SUMPRODUCT((Marks!$B$3:$AZ$3=B$4)*ISNUMBER(Marks!$B$5:$AZ$5)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=B$4)*ISNUMBER(Marks!$B$5:$BC$5))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=B$4)*(Marks!$B$5:$BC$5=1))/SUMPRODUCT((Marks!$B$3:$BC$3=B$4)*ISNUMBER(Marks!$B$5:$BC$5)))</f>
         <v/>
       </c>
       <c r="C5" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AZ$3=C$4)*ISNUMBER(Marks!$B$5:$AZ$5))=0,"",SUMPRODUCT((Marks!$B$3:$AZ$3=C$4)*(Marks!$B$5:$AZ$5=1))/SUMPRODUCT((Marks!$B$3:$AZ$3=C$4)*ISNUMBER(Marks!$B$5:$AZ$5)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=C$4)*ISNUMBER(Marks!$B$5:$BC$5))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=C$4)*(Marks!$B$5:$BC$5=1))/SUMPRODUCT((Marks!$B$3:$BC$3=C$4)*ISNUMBER(Marks!$B$5:$BC$5)))</f>
         <v/>
       </c>
       <c r="D5" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AZ$3=D$4)*ISNUMBER(Marks!$B$5:$AZ$5))=0,"",SUMPRODUCT((Marks!$B$3:$AZ$3=D$4)*(Marks!$B$5:$AZ$5=1))/SUMPRODUCT((Marks!$B$3:$AZ$3=D$4)*ISNUMBER(Marks!$B$5:$AZ$5)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=D$4)*ISNUMBER(Marks!$B$5:$BC$5))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=D$4)*(Marks!$B$5:$BC$5=1))/SUMPRODUCT((Marks!$B$3:$BC$3=D$4)*ISNUMBER(Marks!$B$5:$BC$5)))</f>
         <v/>
       </c>
       <c r="E5" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AZ$3=E$4)*ISNUMBER(Marks!$B$5:$AZ$5))=0,"",SUMPRODUCT((Marks!$B$3:$AZ$3=E$4)*(Marks!$B$5:$AZ$5=1))/SUMPRODUCT((Marks!$B$3:$AZ$3=E$4)*ISNUMBER(Marks!$B$5:$AZ$5)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=E$4)*ISNUMBER(Marks!$B$5:$BC$5))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=E$4)*(Marks!$B$5:$BC$5=1))/SUMPRODUCT((Marks!$B$3:$BC$3=E$4)*ISNUMBER(Marks!$B$5:$BC$5)))</f>
         <v/>
       </c>
     </row>
@@ -8395,19 +8794,19 @@
         <v>2</v>
       </c>
       <c r="B6" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AZ$3=B$4)*ISNUMBER(Marks!$B$6:$AZ$6))=0,"",SUMPRODUCT((Marks!$B$3:$AZ$3=B$4)*(Marks!$B$6:$AZ$6=1))/SUMPRODUCT((Marks!$B$3:$AZ$3=B$4)*ISNUMBER(Marks!$B$6:$AZ$6)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=B$4)*ISNUMBER(Marks!$B$6:$BC$6))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=B$4)*(Marks!$B$6:$BC$6=1))/SUMPRODUCT((Marks!$B$3:$BC$3=B$4)*ISNUMBER(Marks!$B$6:$BC$6)))</f>
         <v/>
       </c>
       <c r="C6" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AZ$3=C$4)*ISNUMBER(Marks!$B$6:$AZ$6))=0,"",SUMPRODUCT((Marks!$B$3:$AZ$3=C$4)*(Marks!$B$6:$AZ$6=1))/SUMPRODUCT((Marks!$B$3:$AZ$3=C$4)*ISNUMBER(Marks!$B$6:$AZ$6)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=C$4)*ISNUMBER(Marks!$B$6:$BC$6))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=C$4)*(Marks!$B$6:$BC$6=1))/SUMPRODUCT((Marks!$B$3:$BC$3=C$4)*ISNUMBER(Marks!$B$6:$BC$6)))</f>
         <v/>
       </c>
       <c r="D6" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AZ$3=D$4)*ISNUMBER(Marks!$B$6:$AZ$6))=0,"",SUMPRODUCT((Marks!$B$3:$AZ$3=D$4)*(Marks!$B$6:$AZ$6=1))/SUMPRODUCT((Marks!$B$3:$AZ$3=D$4)*ISNUMBER(Marks!$B$6:$AZ$6)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=D$4)*ISNUMBER(Marks!$B$6:$BC$6))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=D$4)*(Marks!$B$6:$BC$6=1))/SUMPRODUCT((Marks!$B$3:$BC$3=D$4)*ISNUMBER(Marks!$B$6:$BC$6)))</f>
         <v/>
       </c>
       <c r="E6" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AZ$3=E$4)*ISNUMBER(Marks!$B$6:$AZ$6))=0,"",SUMPRODUCT((Marks!$B$3:$AZ$3=E$4)*(Marks!$B$6:$AZ$6=1))/SUMPRODUCT((Marks!$B$3:$AZ$3=E$4)*ISNUMBER(Marks!$B$6:$AZ$6)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=E$4)*ISNUMBER(Marks!$B$6:$BC$6))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=E$4)*(Marks!$B$6:$BC$6=1))/SUMPRODUCT((Marks!$B$3:$BC$3=E$4)*ISNUMBER(Marks!$B$6:$BC$6)))</f>
         <v/>
       </c>
     </row>
@@ -8416,19 +8815,19 @@
         <v>3</v>
       </c>
       <c r="B7" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AZ$3=B$4)*ISNUMBER(Marks!$B$7:$AZ$7))=0,"",SUMPRODUCT((Marks!$B$3:$AZ$3=B$4)*(Marks!$B$7:$AZ$7=1))/SUMPRODUCT((Marks!$B$3:$AZ$3=B$4)*ISNUMBER(Marks!$B$7:$AZ$7)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=B$4)*ISNUMBER(Marks!$B$7:$BC$7))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=B$4)*(Marks!$B$7:$BC$7=1))/SUMPRODUCT((Marks!$B$3:$BC$3=B$4)*ISNUMBER(Marks!$B$7:$BC$7)))</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AZ$3=C$4)*ISNUMBER(Marks!$B$7:$AZ$7))=0,"",SUMPRODUCT((Marks!$B$3:$AZ$3=C$4)*(Marks!$B$7:$AZ$7=1))/SUMPRODUCT((Marks!$B$3:$AZ$3=C$4)*ISNUMBER(Marks!$B$7:$AZ$7)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=C$4)*ISNUMBER(Marks!$B$7:$BC$7))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=C$4)*(Marks!$B$7:$BC$7=1))/SUMPRODUCT((Marks!$B$3:$BC$3=C$4)*ISNUMBER(Marks!$B$7:$BC$7)))</f>
         <v/>
       </c>
       <c r="D7" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AZ$3=D$4)*ISNUMBER(Marks!$B$7:$AZ$7))=0,"",SUMPRODUCT((Marks!$B$3:$AZ$3=D$4)*(Marks!$B$7:$AZ$7=1))/SUMPRODUCT((Marks!$B$3:$AZ$3=D$4)*ISNUMBER(Marks!$B$7:$AZ$7)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=D$4)*ISNUMBER(Marks!$B$7:$BC$7))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=D$4)*(Marks!$B$7:$BC$7=1))/SUMPRODUCT((Marks!$B$3:$BC$3=D$4)*ISNUMBER(Marks!$B$7:$BC$7)))</f>
         <v/>
       </c>
       <c r="E7" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AZ$3=E$4)*ISNUMBER(Marks!$B$7:$AZ$7))=0,"",SUMPRODUCT((Marks!$B$3:$AZ$3=E$4)*(Marks!$B$7:$AZ$7=1))/SUMPRODUCT((Marks!$B$3:$AZ$3=E$4)*ISNUMBER(Marks!$B$7:$AZ$7)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=E$4)*ISNUMBER(Marks!$B$7:$BC$7))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=E$4)*(Marks!$B$7:$BC$7=1))/SUMPRODUCT((Marks!$B$3:$BC$3=E$4)*ISNUMBER(Marks!$B$7:$BC$7)))</f>
         <v/>
       </c>
     </row>
@@ -8437,19 +8836,19 @@
         <v>4</v>
       </c>
       <c r="B8" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AZ$3=B$4)*ISNUMBER(Marks!$B$8:$AZ$8))=0,"",SUMPRODUCT((Marks!$B$3:$AZ$3=B$4)*(Marks!$B$8:$AZ$8=1))/SUMPRODUCT((Marks!$B$3:$AZ$3=B$4)*ISNUMBER(Marks!$B$8:$AZ$8)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=B$4)*ISNUMBER(Marks!$B$8:$BC$8))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=B$4)*(Marks!$B$8:$BC$8=1))/SUMPRODUCT((Marks!$B$3:$BC$3=B$4)*ISNUMBER(Marks!$B$8:$BC$8)))</f>
         <v/>
       </c>
       <c r="C8" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AZ$3=C$4)*ISNUMBER(Marks!$B$8:$AZ$8))=0,"",SUMPRODUCT((Marks!$B$3:$AZ$3=C$4)*(Marks!$B$8:$AZ$8=1))/SUMPRODUCT((Marks!$B$3:$AZ$3=C$4)*ISNUMBER(Marks!$B$8:$AZ$8)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=C$4)*ISNUMBER(Marks!$B$8:$BC$8))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=C$4)*(Marks!$B$8:$BC$8=1))/SUMPRODUCT((Marks!$B$3:$BC$3=C$4)*ISNUMBER(Marks!$B$8:$BC$8)))</f>
         <v/>
       </c>
       <c r="D8" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AZ$3=D$4)*ISNUMBER(Marks!$B$8:$AZ$8))=0,"",SUMPRODUCT((Marks!$B$3:$AZ$3=D$4)*(Marks!$B$8:$AZ$8=1))/SUMPRODUCT((Marks!$B$3:$AZ$3=D$4)*ISNUMBER(Marks!$B$8:$AZ$8)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=D$4)*ISNUMBER(Marks!$B$8:$BC$8))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=D$4)*(Marks!$B$8:$BC$8=1))/SUMPRODUCT((Marks!$B$3:$BC$3=D$4)*ISNUMBER(Marks!$B$8:$BC$8)))</f>
         <v/>
       </c>
       <c r="E8" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AZ$3=E$4)*ISNUMBER(Marks!$B$8:$AZ$8))=0,"",SUMPRODUCT((Marks!$B$3:$AZ$3=E$4)*(Marks!$B$8:$AZ$8=1))/SUMPRODUCT((Marks!$B$3:$AZ$3=E$4)*ISNUMBER(Marks!$B$8:$AZ$8)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=E$4)*ISNUMBER(Marks!$B$8:$BC$8))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=E$4)*(Marks!$B$8:$BC$8=1))/SUMPRODUCT((Marks!$B$3:$BC$3=E$4)*ISNUMBER(Marks!$B$8:$BC$8)))</f>
         <v/>
       </c>
     </row>
@@ -8458,19 +8857,19 @@
         <v>5</v>
       </c>
       <c r="B9" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AZ$3=B$4)*ISNUMBER(Marks!$B$9:$AZ$9))=0,"",SUMPRODUCT((Marks!$B$3:$AZ$3=B$4)*(Marks!$B$9:$AZ$9=1))/SUMPRODUCT((Marks!$B$3:$AZ$3=B$4)*ISNUMBER(Marks!$B$9:$AZ$9)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=B$4)*ISNUMBER(Marks!$B$9:$BC$9))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=B$4)*(Marks!$B$9:$BC$9=1))/SUMPRODUCT((Marks!$B$3:$BC$3=B$4)*ISNUMBER(Marks!$B$9:$BC$9)))</f>
         <v/>
       </c>
       <c r="C9" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AZ$3=C$4)*ISNUMBER(Marks!$B$9:$AZ$9))=0,"",SUMPRODUCT((Marks!$B$3:$AZ$3=C$4)*(Marks!$B$9:$AZ$9=1))/SUMPRODUCT((Marks!$B$3:$AZ$3=C$4)*ISNUMBER(Marks!$B$9:$AZ$9)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=C$4)*ISNUMBER(Marks!$B$9:$BC$9))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=C$4)*(Marks!$B$9:$BC$9=1))/SUMPRODUCT((Marks!$B$3:$BC$3=C$4)*ISNUMBER(Marks!$B$9:$BC$9)))</f>
         <v/>
       </c>
       <c r="D9" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AZ$3=D$4)*ISNUMBER(Marks!$B$9:$AZ$9))=0,"",SUMPRODUCT((Marks!$B$3:$AZ$3=D$4)*(Marks!$B$9:$AZ$9=1))/SUMPRODUCT((Marks!$B$3:$AZ$3=D$4)*ISNUMBER(Marks!$B$9:$AZ$9)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=D$4)*ISNUMBER(Marks!$B$9:$BC$9))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=D$4)*(Marks!$B$9:$BC$9=1))/SUMPRODUCT((Marks!$B$3:$BC$3=D$4)*ISNUMBER(Marks!$B$9:$BC$9)))</f>
         <v/>
       </c>
       <c r="E9" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AZ$3=E$4)*ISNUMBER(Marks!$B$9:$AZ$9))=0,"",SUMPRODUCT((Marks!$B$3:$AZ$3=E$4)*(Marks!$B$9:$AZ$9=1))/SUMPRODUCT((Marks!$B$3:$AZ$3=E$4)*ISNUMBER(Marks!$B$9:$AZ$9)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=E$4)*ISNUMBER(Marks!$B$9:$BC$9))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=E$4)*(Marks!$B$9:$BC$9=1))/SUMPRODUCT((Marks!$B$3:$BC$3=E$4)*ISNUMBER(Marks!$B$9:$BC$9)))</f>
         <v/>
       </c>
     </row>
@@ -8479,19 +8878,19 @@
         <v>6</v>
       </c>
       <c r="B10" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AZ$3=B$4)*ISNUMBER(Marks!$B$10:$AZ$10))=0,"",SUMPRODUCT((Marks!$B$3:$AZ$3=B$4)*(Marks!$B$10:$AZ$10=1))/SUMPRODUCT((Marks!$B$3:$AZ$3=B$4)*ISNUMBER(Marks!$B$10:$AZ$10)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=B$4)*ISNUMBER(Marks!$B$10:$BC$10))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=B$4)*(Marks!$B$10:$BC$10=1))/SUMPRODUCT((Marks!$B$3:$BC$3=B$4)*ISNUMBER(Marks!$B$10:$BC$10)))</f>
         <v/>
       </c>
       <c r="C10" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AZ$3=C$4)*ISNUMBER(Marks!$B$10:$AZ$10))=0,"",SUMPRODUCT((Marks!$B$3:$AZ$3=C$4)*(Marks!$B$10:$AZ$10=1))/SUMPRODUCT((Marks!$B$3:$AZ$3=C$4)*ISNUMBER(Marks!$B$10:$AZ$10)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=C$4)*ISNUMBER(Marks!$B$10:$BC$10))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=C$4)*(Marks!$B$10:$BC$10=1))/SUMPRODUCT((Marks!$B$3:$BC$3=C$4)*ISNUMBER(Marks!$B$10:$BC$10)))</f>
         <v/>
       </c>
       <c r="D10" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AZ$3=D$4)*ISNUMBER(Marks!$B$10:$AZ$10))=0,"",SUMPRODUCT((Marks!$B$3:$AZ$3=D$4)*(Marks!$B$10:$AZ$10=1))/SUMPRODUCT((Marks!$B$3:$AZ$3=D$4)*ISNUMBER(Marks!$B$10:$AZ$10)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=D$4)*ISNUMBER(Marks!$B$10:$BC$10))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=D$4)*(Marks!$B$10:$BC$10=1))/SUMPRODUCT((Marks!$B$3:$BC$3=D$4)*ISNUMBER(Marks!$B$10:$BC$10)))</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AZ$3=E$4)*ISNUMBER(Marks!$B$10:$AZ$10))=0,"",SUMPRODUCT((Marks!$B$3:$AZ$3=E$4)*(Marks!$B$10:$AZ$10=1))/SUMPRODUCT((Marks!$B$3:$AZ$3=E$4)*ISNUMBER(Marks!$B$10:$AZ$10)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=E$4)*ISNUMBER(Marks!$B$10:$BC$10))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=E$4)*(Marks!$B$10:$BC$10=1))/SUMPRODUCT((Marks!$B$3:$BC$3=E$4)*ISNUMBER(Marks!$B$10:$BC$10)))</f>
         <v/>
       </c>
     </row>
@@ -8500,19 +8899,19 @@
         <v>7</v>
       </c>
       <c r="B11" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AZ$3=B$4)*ISNUMBER(Marks!$B$11:$AZ$11))=0,"",SUMPRODUCT((Marks!$B$3:$AZ$3=B$4)*(Marks!$B$11:$AZ$11=1))/SUMPRODUCT((Marks!$B$3:$AZ$3=B$4)*ISNUMBER(Marks!$B$11:$AZ$11)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=B$4)*ISNUMBER(Marks!$B$11:$BC$11))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=B$4)*(Marks!$B$11:$BC$11=1))/SUMPRODUCT((Marks!$B$3:$BC$3=B$4)*ISNUMBER(Marks!$B$11:$BC$11)))</f>
         <v/>
       </c>
       <c r="C11" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AZ$3=C$4)*ISNUMBER(Marks!$B$11:$AZ$11))=0,"",SUMPRODUCT((Marks!$B$3:$AZ$3=C$4)*(Marks!$B$11:$AZ$11=1))/SUMPRODUCT((Marks!$B$3:$AZ$3=C$4)*ISNUMBER(Marks!$B$11:$AZ$11)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=C$4)*ISNUMBER(Marks!$B$11:$BC$11))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=C$4)*(Marks!$B$11:$BC$11=1))/SUMPRODUCT((Marks!$B$3:$BC$3=C$4)*ISNUMBER(Marks!$B$11:$BC$11)))</f>
         <v/>
       </c>
       <c r="D11" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AZ$3=D$4)*ISNUMBER(Marks!$B$11:$AZ$11))=0,"",SUMPRODUCT((Marks!$B$3:$AZ$3=D$4)*(Marks!$B$11:$AZ$11=1))/SUMPRODUCT((Marks!$B$3:$AZ$3=D$4)*ISNUMBER(Marks!$B$11:$AZ$11)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=D$4)*ISNUMBER(Marks!$B$11:$BC$11))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=D$4)*(Marks!$B$11:$BC$11=1))/SUMPRODUCT((Marks!$B$3:$BC$3=D$4)*ISNUMBER(Marks!$B$11:$BC$11)))</f>
         <v/>
       </c>
       <c r="E11" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AZ$3=E$4)*ISNUMBER(Marks!$B$11:$AZ$11))=0,"",SUMPRODUCT((Marks!$B$3:$AZ$3=E$4)*(Marks!$B$11:$AZ$11=1))/SUMPRODUCT((Marks!$B$3:$AZ$3=E$4)*ISNUMBER(Marks!$B$11:$AZ$11)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=E$4)*ISNUMBER(Marks!$B$11:$BC$11))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=E$4)*(Marks!$B$11:$BC$11=1))/SUMPRODUCT((Marks!$B$3:$BC$3=E$4)*ISNUMBER(Marks!$B$11:$BC$11)))</f>
         <v/>
       </c>
     </row>
@@ -8521,19 +8920,19 @@
         <v>8</v>
       </c>
       <c r="B12" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AZ$3=B$4)*ISNUMBER(Marks!$B$12:$AZ$12))=0,"",SUMPRODUCT((Marks!$B$3:$AZ$3=B$4)*(Marks!$B$12:$AZ$12=1))/SUMPRODUCT((Marks!$B$3:$AZ$3=B$4)*ISNUMBER(Marks!$B$12:$AZ$12)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=B$4)*ISNUMBER(Marks!$B$12:$BC$12))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=B$4)*(Marks!$B$12:$BC$12=1))/SUMPRODUCT((Marks!$B$3:$BC$3=B$4)*ISNUMBER(Marks!$B$12:$BC$12)))</f>
         <v/>
       </c>
       <c r="C12" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AZ$3=C$4)*ISNUMBER(Marks!$B$12:$AZ$12))=0,"",SUMPRODUCT((Marks!$B$3:$AZ$3=C$4)*(Marks!$B$12:$AZ$12=1))/SUMPRODUCT((Marks!$B$3:$AZ$3=C$4)*ISNUMBER(Marks!$B$12:$AZ$12)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=C$4)*ISNUMBER(Marks!$B$12:$BC$12))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=C$4)*(Marks!$B$12:$BC$12=1))/SUMPRODUCT((Marks!$B$3:$BC$3=C$4)*ISNUMBER(Marks!$B$12:$BC$12)))</f>
         <v/>
       </c>
       <c r="D12" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AZ$3=D$4)*ISNUMBER(Marks!$B$12:$AZ$12))=0,"",SUMPRODUCT((Marks!$B$3:$AZ$3=D$4)*(Marks!$B$12:$AZ$12=1))/SUMPRODUCT((Marks!$B$3:$AZ$3=D$4)*ISNUMBER(Marks!$B$12:$AZ$12)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=D$4)*ISNUMBER(Marks!$B$12:$BC$12))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=D$4)*(Marks!$B$12:$BC$12=1))/SUMPRODUCT((Marks!$B$3:$BC$3=D$4)*ISNUMBER(Marks!$B$12:$BC$12)))</f>
         <v/>
       </c>
       <c r="E12" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AZ$3=E$4)*ISNUMBER(Marks!$B$12:$AZ$12))=0,"",SUMPRODUCT((Marks!$B$3:$AZ$3=E$4)*(Marks!$B$12:$AZ$12=1))/SUMPRODUCT((Marks!$B$3:$AZ$3=E$4)*ISNUMBER(Marks!$B$12:$AZ$12)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=E$4)*ISNUMBER(Marks!$B$12:$BC$12))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=E$4)*(Marks!$B$12:$BC$12=1))/SUMPRODUCT((Marks!$B$3:$BC$3=E$4)*ISNUMBER(Marks!$B$12:$BC$12)))</f>
         <v/>
       </c>
     </row>
@@ -8542,19 +8941,19 @@
         <v>9</v>
       </c>
       <c r="B13" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AZ$3=B$4)*ISNUMBER(Marks!$B$13:$AZ$13))=0,"",SUMPRODUCT((Marks!$B$3:$AZ$3=B$4)*(Marks!$B$13:$AZ$13=1))/SUMPRODUCT((Marks!$B$3:$AZ$3=B$4)*ISNUMBER(Marks!$B$13:$AZ$13)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=B$4)*ISNUMBER(Marks!$B$13:$BC$13))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=B$4)*(Marks!$B$13:$BC$13=1))/SUMPRODUCT((Marks!$B$3:$BC$3=B$4)*ISNUMBER(Marks!$B$13:$BC$13)))</f>
         <v/>
       </c>
       <c r="C13" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AZ$3=C$4)*ISNUMBER(Marks!$B$13:$AZ$13))=0,"",SUMPRODUCT((Marks!$B$3:$AZ$3=C$4)*(Marks!$B$13:$AZ$13=1))/SUMPRODUCT((Marks!$B$3:$AZ$3=C$4)*ISNUMBER(Marks!$B$13:$AZ$13)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=C$4)*ISNUMBER(Marks!$B$13:$BC$13))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=C$4)*(Marks!$B$13:$BC$13=1))/SUMPRODUCT((Marks!$B$3:$BC$3=C$4)*ISNUMBER(Marks!$B$13:$BC$13)))</f>
         <v/>
       </c>
       <c r="D13" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AZ$3=D$4)*ISNUMBER(Marks!$B$13:$AZ$13))=0,"",SUMPRODUCT((Marks!$B$3:$AZ$3=D$4)*(Marks!$B$13:$AZ$13=1))/SUMPRODUCT((Marks!$B$3:$AZ$3=D$4)*ISNUMBER(Marks!$B$13:$AZ$13)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=D$4)*ISNUMBER(Marks!$B$13:$BC$13))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=D$4)*(Marks!$B$13:$BC$13=1))/SUMPRODUCT((Marks!$B$3:$BC$3=D$4)*ISNUMBER(Marks!$B$13:$BC$13)))</f>
         <v/>
       </c>
       <c r="E13" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AZ$3=E$4)*ISNUMBER(Marks!$B$13:$AZ$13))=0,"",SUMPRODUCT((Marks!$B$3:$AZ$3=E$4)*(Marks!$B$13:$AZ$13=1))/SUMPRODUCT((Marks!$B$3:$AZ$3=E$4)*ISNUMBER(Marks!$B$13:$AZ$13)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=E$4)*ISNUMBER(Marks!$B$13:$BC$13))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=E$4)*(Marks!$B$13:$BC$13=1))/SUMPRODUCT((Marks!$B$3:$BC$3=E$4)*ISNUMBER(Marks!$B$13:$BC$13)))</f>
         <v/>
       </c>
     </row>
@@ -8563,19 +8962,19 @@
         <v>10</v>
       </c>
       <c r="B14" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AZ$3=B$4)*ISNUMBER(Marks!$B$14:$AZ$14))=0,"",SUMPRODUCT((Marks!$B$3:$AZ$3=B$4)*(Marks!$B$14:$AZ$14=1))/SUMPRODUCT((Marks!$B$3:$AZ$3=B$4)*ISNUMBER(Marks!$B$14:$AZ$14)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=B$4)*ISNUMBER(Marks!$B$14:$BC$14))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=B$4)*(Marks!$B$14:$BC$14=1))/SUMPRODUCT((Marks!$B$3:$BC$3=B$4)*ISNUMBER(Marks!$B$14:$BC$14)))</f>
         <v/>
       </c>
       <c r="C14" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AZ$3=C$4)*ISNUMBER(Marks!$B$14:$AZ$14))=0,"",SUMPRODUCT((Marks!$B$3:$AZ$3=C$4)*(Marks!$B$14:$AZ$14=1))/SUMPRODUCT((Marks!$B$3:$AZ$3=C$4)*ISNUMBER(Marks!$B$14:$AZ$14)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=C$4)*ISNUMBER(Marks!$B$14:$BC$14))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=C$4)*(Marks!$B$14:$BC$14=1))/SUMPRODUCT((Marks!$B$3:$BC$3=C$4)*ISNUMBER(Marks!$B$14:$BC$14)))</f>
         <v/>
       </c>
       <c r="D14" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AZ$3=D$4)*ISNUMBER(Marks!$B$14:$AZ$14))=0,"",SUMPRODUCT((Marks!$B$3:$AZ$3=D$4)*(Marks!$B$14:$AZ$14=1))/SUMPRODUCT((Marks!$B$3:$AZ$3=D$4)*ISNUMBER(Marks!$B$14:$AZ$14)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=D$4)*ISNUMBER(Marks!$B$14:$BC$14))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=D$4)*(Marks!$B$14:$BC$14=1))/SUMPRODUCT((Marks!$B$3:$BC$3=D$4)*ISNUMBER(Marks!$B$14:$BC$14)))</f>
         <v/>
       </c>
       <c r="E14" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AZ$3=E$4)*ISNUMBER(Marks!$B$14:$AZ$14))=0,"",SUMPRODUCT((Marks!$B$3:$AZ$3=E$4)*(Marks!$B$14:$AZ$14=1))/SUMPRODUCT((Marks!$B$3:$AZ$3=E$4)*ISNUMBER(Marks!$B$14:$AZ$14)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=E$4)*ISNUMBER(Marks!$B$14:$BC$14))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=E$4)*(Marks!$B$14:$BC$14=1))/SUMPRODUCT((Marks!$B$3:$BC$3=E$4)*ISNUMBER(Marks!$B$14:$BC$14)))</f>
         <v/>
       </c>
     </row>
@@ -8584,19 +8983,19 @@
         <v>11</v>
       </c>
       <c r="B15" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AZ$3=B$4)*ISNUMBER(Marks!$B$15:$AZ$15))=0,"",SUMPRODUCT((Marks!$B$3:$AZ$3=B$4)*(Marks!$B$15:$AZ$15=1))/SUMPRODUCT((Marks!$B$3:$AZ$3=B$4)*ISNUMBER(Marks!$B$15:$AZ$15)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=B$4)*ISNUMBER(Marks!$B$15:$BC$15))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=B$4)*(Marks!$B$15:$BC$15=1))/SUMPRODUCT((Marks!$B$3:$BC$3=B$4)*ISNUMBER(Marks!$B$15:$BC$15)))</f>
         <v/>
       </c>
       <c r="C15" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AZ$3=C$4)*ISNUMBER(Marks!$B$15:$AZ$15))=0,"",SUMPRODUCT((Marks!$B$3:$AZ$3=C$4)*(Marks!$B$15:$AZ$15=1))/SUMPRODUCT((Marks!$B$3:$AZ$3=C$4)*ISNUMBER(Marks!$B$15:$AZ$15)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=C$4)*ISNUMBER(Marks!$B$15:$BC$15))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=C$4)*(Marks!$B$15:$BC$15=1))/SUMPRODUCT((Marks!$B$3:$BC$3=C$4)*ISNUMBER(Marks!$B$15:$BC$15)))</f>
         <v/>
       </c>
       <c r="D15" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AZ$3=D$4)*ISNUMBER(Marks!$B$15:$AZ$15))=0,"",SUMPRODUCT((Marks!$B$3:$AZ$3=D$4)*(Marks!$B$15:$AZ$15=1))/SUMPRODUCT((Marks!$B$3:$AZ$3=D$4)*ISNUMBER(Marks!$B$15:$AZ$15)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=D$4)*ISNUMBER(Marks!$B$15:$BC$15))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=D$4)*(Marks!$B$15:$BC$15=1))/SUMPRODUCT((Marks!$B$3:$BC$3=D$4)*ISNUMBER(Marks!$B$15:$BC$15)))</f>
         <v/>
       </c>
       <c r="E15" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AZ$3=E$4)*ISNUMBER(Marks!$B$15:$AZ$15))=0,"",SUMPRODUCT((Marks!$B$3:$AZ$3=E$4)*(Marks!$B$15:$AZ$15=1))/SUMPRODUCT((Marks!$B$3:$AZ$3=E$4)*ISNUMBER(Marks!$B$15:$AZ$15)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=E$4)*ISNUMBER(Marks!$B$15:$BC$15))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=E$4)*(Marks!$B$15:$BC$15=1))/SUMPRODUCT((Marks!$B$3:$BC$3=E$4)*ISNUMBER(Marks!$B$15:$BC$15)))</f>
         <v/>
       </c>
     </row>
@@ -8605,19 +9004,19 @@
         <v>12</v>
       </c>
       <c r="B16" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AZ$3=B$4)*ISNUMBER(Marks!$B$16:$AZ$16))=0,"",SUMPRODUCT((Marks!$B$3:$AZ$3=B$4)*(Marks!$B$16:$AZ$16=1))/SUMPRODUCT((Marks!$B$3:$AZ$3=B$4)*ISNUMBER(Marks!$B$16:$AZ$16)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=B$4)*ISNUMBER(Marks!$B$16:$BC$16))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=B$4)*(Marks!$B$16:$BC$16=1))/SUMPRODUCT((Marks!$B$3:$BC$3=B$4)*ISNUMBER(Marks!$B$16:$BC$16)))</f>
         <v/>
       </c>
       <c r="C16" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AZ$3=C$4)*ISNUMBER(Marks!$B$16:$AZ$16))=0,"",SUMPRODUCT((Marks!$B$3:$AZ$3=C$4)*(Marks!$B$16:$AZ$16=1))/SUMPRODUCT((Marks!$B$3:$AZ$3=C$4)*ISNUMBER(Marks!$B$16:$AZ$16)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=C$4)*ISNUMBER(Marks!$B$16:$BC$16))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=C$4)*(Marks!$B$16:$BC$16=1))/SUMPRODUCT((Marks!$B$3:$BC$3=C$4)*ISNUMBER(Marks!$B$16:$BC$16)))</f>
         <v/>
       </c>
       <c r="D16" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AZ$3=D$4)*ISNUMBER(Marks!$B$16:$AZ$16))=0,"",SUMPRODUCT((Marks!$B$3:$AZ$3=D$4)*(Marks!$B$16:$AZ$16=1))/SUMPRODUCT((Marks!$B$3:$AZ$3=D$4)*ISNUMBER(Marks!$B$16:$AZ$16)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=D$4)*ISNUMBER(Marks!$B$16:$BC$16))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=D$4)*(Marks!$B$16:$BC$16=1))/SUMPRODUCT((Marks!$B$3:$BC$3=D$4)*ISNUMBER(Marks!$B$16:$BC$16)))</f>
         <v/>
       </c>
       <c r="E16" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AZ$3=E$4)*ISNUMBER(Marks!$B$16:$AZ$16))=0,"",SUMPRODUCT((Marks!$B$3:$AZ$3=E$4)*(Marks!$B$16:$AZ$16=1))/SUMPRODUCT((Marks!$B$3:$AZ$3=E$4)*ISNUMBER(Marks!$B$16:$AZ$16)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=E$4)*ISNUMBER(Marks!$B$16:$BC$16))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=E$4)*(Marks!$B$16:$BC$16=1))/SUMPRODUCT((Marks!$B$3:$BC$3=E$4)*ISNUMBER(Marks!$B$16:$BC$16)))</f>
         <v/>
       </c>
     </row>
@@ -8626,19 +9025,19 @@
         <v>13</v>
       </c>
       <c r="B17" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AZ$3=B$4)*ISNUMBER(Marks!$B$17:$AZ$17))=0,"",SUMPRODUCT((Marks!$B$3:$AZ$3=B$4)*(Marks!$B$17:$AZ$17=1))/SUMPRODUCT((Marks!$B$3:$AZ$3=B$4)*ISNUMBER(Marks!$B$17:$AZ$17)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=B$4)*ISNUMBER(Marks!$B$17:$BC$17))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=B$4)*(Marks!$B$17:$BC$17=1))/SUMPRODUCT((Marks!$B$3:$BC$3=B$4)*ISNUMBER(Marks!$B$17:$BC$17)))</f>
         <v/>
       </c>
       <c r="C17" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AZ$3=C$4)*ISNUMBER(Marks!$B$17:$AZ$17))=0,"",SUMPRODUCT((Marks!$B$3:$AZ$3=C$4)*(Marks!$B$17:$AZ$17=1))/SUMPRODUCT((Marks!$B$3:$AZ$3=C$4)*ISNUMBER(Marks!$B$17:$AZ$17)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=C$4)*ISNUMBER(Marks!$B$17:$BC$17))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=C$4)*(Marks!$B$17:$BC$17=1))/SUMPRODUCT((Marks!$B$3:$BC$3=C$4)*ISNUMBER(Marks!$B$17:$BC$17)))</f>
         <v/>
       </c>
       <c r="D17" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AZ$3=D$4)*ISNUMBER(Marks!$B$17:$AZ$17))=0,"",SUMPRODUCT((Marks!$B$3:$AZ$3=D$4)*(Marks!$B$17:$AZ$17=1))/SUMPRODUCT((Marks!$B$3:$AZ$3=D$4)*ISNUMBER(Marks!$B$17:$AZ$17)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=D$4)*ISNUMBER(Marks!$B$17:$BC$17))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=D$4)*(Marks!$B$17:$BC$17=1))/SUMPRODUCT((Marks!$B$3:$BC$3=D$4)*ISNUMBER(Marks!$B$17:$BC$17)))</f>
         <v/>
       </c>
       <c r="E17" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AZ$3=E$4)*ISNUMBER(Marks!$B$17:$AZ$17))=0,"",SUMPRODUCT((Marks!$B$3:$AZ$3=E$4)*(Marks!$B$17:$AZ$17=1))/SUMPRODUCT((Marks!$B$3:$AZ$3=E$4)*ISNUMBER(Marks!$B$17:$AZ$17)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=E$4)*ISNUMBER(Marks!$B$17:$BC$17))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=E$4)*(Marks!$B$17:$BC$17=1))/SUMPRODUCT((Marks!$B$3:$BC$3=E$4)*ISNUMBER(Marks!$B$17:$BC$17)))</f>
         <v/>
       </c>
     </row>
@@ -8647,19 +9046,19 @@
         <v>14</v>
       </c>
       <c r="B18" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AZ$3=B$4)*ISNUMBER(Marks!$B$18:$AZ$18))=0,"",SUMPRODUCT((Marks!$B$3:$AZ$3=B$4)*(Marks!$B$18:$AZ$18=1))/SUMPRODUCT((Marks!$B$3:$AZ$3=B$4)*ISNUMBER(Marks!$B$18:$AZ$18)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=B$4)*ISNUMBER(Marks!$B$18:$BC$18))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=B$4)*(Marks!$B$18:$BC$18=1))/SUMPRODUCT((Marks!$B$3:$BC$3=B$4)*ISNUMBER(Marks!$B$18:$BC$18)))</f>
         <v/>
       </c>
       <c r="C18" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AZ$3=C$4)*ISNUMBER(Marks!$B$18:$AZ$18))=0,"",SUMPRODUCT((Marks!$B$3:$AZ$3=C$4)*(Marks!$B$18:$AZ$18=1))/SUMPRODUCT((Marks!$B$3:$AZ$3=C$4)*ISNUMBER(Marks!$B$18:$AZ$18)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=C$4)*ISNUMBER(Marks!$B$18:$BC$18))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=C$4)*(Marks!$B$18:$BC$18=1))/SUMPRODUCT((Marks!$B$3:$BC$3=C$4)*ISNUMBER(Marks!$B$18:$BC$18)))</f>
         <v/>
       </c>
       <c r="D18" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AZ$3=D$4)*ISNUMBER(Marks!$B$18:$AZ$18))=0,"",SUMPRODUCT((Marks!$B$3:$AZ$3=D$4)*(Marks!$B$18:$AZ$18=1))/SUMPRODUCT((Marks!$B$3:$AZ$3=D$4)*ISNUMBER(Marks!$B$18:$AZ$18)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=D$4)*ISNUMBER(Marks!$B$18:$BC$18))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=D$4)*(Marks!$B$18:$BC$18=1))/SUMPRODUCT((Marks!$B$3:$BC$3=D$4)*ISNUMBER(Marks!$B$18:$BC$18)))</f>
         <v/>
       </c>
       <c r="E18" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AZ$3=E$4)*ISNUMBER(Marks!$B$18:$AZ$18))=0,"",SUMPRODUCT((Marks!$B$3:$AZ$3=E$4)*(Marks!$B$18:$AZ$18=1))/SUMPRODUCT((Marks!$B$3:$AZ$3=E$4)*ISNUMBER(Marks!$B$18:$AZ$18)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=E$4)*ISNUMBER(Marks!$B$18:$BC$18))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=E$4)*(Marks!$B$18:$BC$18=1))/SUMPRODUCT((Marks!$B$3:$BC$3=E$4)*ISNUMBER(Marks!$B$18:$BC$18)))</f>
         <v/>
       </c>
     </row>
@@ -8668,19 +9067,19 @@
         <v>15</v>
       </c>
       <c r="B19" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AZ$3=B$4)*ISNUMBER(Marks!$B$19:$AZ$19))=0,"",SUMPRODUCT((Marks!$B$3:$AZ$3=B$4)*(Marks!$B$19:$AZ$19=1))/SUMPRODUCT((Marks!$B$3:$AZ$3=B$4)*ISNUMBER(Marks!$B$19:$AZ$19)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=B$4)*ISNUMBER(Marks!$B$19:$BC$19))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=B$4)*(Marks!$B$19:$BC$19=1))/SUMPRODUCT((Marks!$B$3:$BC$3=B$4)*ISNUMBER(Marks!$B$19:$BC$19)))</f>
         <v/>
       </c>
       <c r="C19" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AZ$3=C$4)*ISNUMBER(Marks!$B$19:$AZ$19))=0,"",SUMPRODUCT((Marks!$B$3:$AZ$3=C$4)*(Marks!$B$19:$AZ$19=1))/SUMPRODUCT((Marks!$B$3:$AZ$3=C$4)*ISNUMBER(Marks!$B$19:$AZ$19)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=C$4)*ISNUMBER(Marks!$B$19:$BC$19))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=C$4)*(Marks!$B$19:$BC$19=1))/SUMPRODUCT((Marks!$B$3:$BC$3=C$4)*ISNUMBER(Marks!$B$19:$BC$19)))</f>
         <v/>
       </c>
       <c r="D19" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AZ$3=D$4)*ISNUMBER(Marks!$B$19:$AZ$19))=0,"",SUMPRODUCT((Marks!$B$3:$AZ$3=D$4)*(Marks!$B$19:$AZ$19=1))/SUMPRODUCT((Marks!$B$3:$AZ$3=D$4)*ISNUMBER(Marks!$B$19:$AZ$19)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=D$4)*ISNUMBER(Marks!$B$19:$BC$19))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=D$4)*(Marks!$B$19:$BC$19=1))/SUMPRODUCT((Marks!$B$3:$BC$3=D$4)*ISNUMBER(Marks!$B$19:$BC$19)))</f>
         <v/>
       </c>
       <c r="E19" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AZ$3=E$4)*ISNUMBER(Marks!$B$19:$AZ$19))=0,"",SUMPRODUCT((Marks!$B$3:$AZ$3=E$4)*(Marks!$B$19:$AZ$19=1))/SUMPRODUCT((Marks!$B$3:$AZ$3=E$4)*ISNUMBER(Marks!$B$19:$AZ$19)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=E$4)*ISNUMBER(Marks!$B$19:$BC$19))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=E$4)*(Marks!$B$19:$BC$19=1))/SUMPRODUCT((Marks!$B$3:$BC$3=E$4)*ISNUMBER(Marks!$B$19:$BC$19)))</f>
         <v/>
       </c>
     </row>
@@ -8689,19 +9088,19 @@
         <v>16</v>
       </c>
       <c r="B20" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AZ$3=B$4)*ISNUMBER(Marks!$B$20:$AZ$20))=0,"",SUMPRODUCT((Marks!$B$3:$AZ$3=B$4)*(Marks!$B$20:$AZ$20=1))/SUMPRODUCT((Marks!$B$3:$AZ$3=B$4)*ISNUMBER(Marks!$B$20:$AZ$20)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=B$4)*ISNUMBER(Marks!$B$20:$BC$20))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=B$4)*(Marks!$B$20:$BC$20=1))/SUMPRODUCT((Marks!$B$3:$BC$3=B$4)*ISNUMBER(Marks!$B$20:$BC$20)))</f>
         <v/>
       </c>
       <c r="C20" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AZ$3=C$4)*ISNUMBER(Marks!$B$20:$AZ$20))=0,"",SUMPRODUCT((Marks!$B$3:$AZ$3=C$4)*(Marks!$B$20:$AZ$20=1))/SUMPRODUCT((Marks!$B$3:$AZ$3=C$4)*ISNUMBER(Marks!$B$20:$AZ$20)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=C$4)*ISNUMBER(Marks!$B$20:$BC$20))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=C$4)*(Marks!$B$20:$BC$20=1))/SUMPRODUCT((Marks!$B$3:$BC$3=C$4)*ISNUMBER(Marks!$B$20:$BC$20)))</f>
         <v/>
       </c>
       <c r="D20" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AZ$3=D$4)*ISNUMBER(Marks!$B$20:$AZ$20))=0,"",SUMPRODUCT((Marks!$B$3:$AZ$3=D$4)*(Marks!$B$20:$AZ$20=1))/SUMPRODUCT((Marks!$B$3:$AZ$3=D$4)*ISNUMBER(Marks!$B$20:$AZ$20)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=D$4)*ISNUMBER(Marks!$B$20:$BC$20))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=D$4)*(Marks!$B$20:$BC$20=1))/SUMPRODUCT((Marks!$B$3:$BC$3=D$4)*ISNUMBER(Marks!$B$20:$BC$20)))</f>
         <v/>
       </c>
       <c r="E20" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AZ$3=E$4)*ISNUMBER(Marks!$B$20:$AZ$20))=0,"",SUMPRODUCT((Marks!$B$3:$AZ$3=E$4)*(Marks!$B$20:$AZ$20=1))/SUMPRODUCT((Marks!$B$3:$AZ$3=E$4)*ISNUMBER(Marks!$B$20:$AZ$20)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=E$4)*ISNUMBER(Marks!$B$20:$BC$20))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=E$4)*(Marks!$B$20:$BC$20=1))/SUMPRODUCT((Marks!$B$3:$BC$3=E$4)*ISNUMBER(Marks!$B$20:$BC$20)))</f>
         <v/>
       </c>
     </row>
@@ -8710,19 +9109,19 @@
         <v>17</v>
       </c>
       <c r="B21" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AZ$3=B$4)*ISNUMBER(Marks!$B$21:$AZ$21))=0,"",SUMPRODUCT((Marks!$B$3:$AZ$3=B$4)*(Marks!$B$21:$AZ$21=1))/SUMPRODUCT((Marks!$B$3:$AZ$3=B$4)*ISNUMBER(Marks!$B$21:$AZ$21)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=B$4)*ISNUMBER(Marks!$B$21:$BC$21))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=B$4)*(Marks!$B$21:$BC$21=1))/SUMPRODUCT((Marks!$B$3:$BC$3=B$4)*ISNUMBER(Marks!$B$21:$BC$21)))</f>
         <v/>
       </c>
       <c r="C21" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AZ$3=C$4)*ISNUMBER(Marks!$B$21:$AZ$21))=0,"",SUMPRODUCT((Marks!$B$3:$AZ$3=C$4)*(Marks!$B$21:$AZ$21=1))/SUMPRODUCT((Marks!$B$3:$AZ$3=C$4)*ISNUMBER(Marks!$B$21:$AZ$21)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=C$4)*ISNUMBER(Marks!$B$21:$BC$21))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=C$4)*(Marks!$B$21:$BC$21=1))/SUMPRODUCT((Marks!$B$3:$BC$3=C$4)*ISNUMBER(Marks!$B$21:$BC$21)))</f>
         <v/>
       </c>
       <c r="D21" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AZ$3=D$4)*ISNUMBER(Marks!$B$21:$AZ$21))=0,"",SUMPRODUCT((Marks!$B$3:$AZ$3=D$4)*(Marks!$B$21:$AZ$21=1))/SUMPRODUCT((Marks!$B$3:$AZ$3=D$4)*ISNUMBER(Marks!$B$21:$AZ$21)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=D$4)*ISNUMBER(Marks!$B$21:$BC$21))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=D$4)*(Marks!$B$21:$BC$21=1))/SUMPRODUCT((Marks!$B$3:$BC$3=D$4)*ISNUMBER(Marks!$B$21:$BC$21)))</f>
         <v/>
       </c>
       <c r="E21" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AZ$3=E$4)*ISNUMBER(Marks!$B$21:$AZ$21))=0,"",SUMPRODUCT((Marks!$B$3:$AZ$3=E$4)*(Marks!$B$21:$AZ$21=1))/SUMPRODUCT((Marks!$B$3:$AZ$3=E$4)*ISNUMBER(Marks!$B$21:$AZ$21)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=E$4)*ISNUMBER(Marks!$B$21:$BC$21))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=E$4)*(Marks!$B$21:$BC$21=1))/SUMPRODUCT((Marks!$B$3:$BC$3=E$4)*ISNUMBER(Marks!$B$21:$BC$21)))</f>
         <v/>
       </c>
     </row>
@@ -8731,19 +9130,19 @@
         <v>18</v>
       </c>
       <c r="B22" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AZ$3=B$4)*ISNUMBER(Marks!$B$22:$AZ$22))=0,"",SUMPRODUCT((Marks!$B$3:$AZ$3=B$4)*(Marks!$B$22:$AZ$22=1))/SUMPRODUCT((Marks!$B$3:$AZ$3=B$4)*ISNUMBER(Marks!$B$22:$AZ$22)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=B$4)*ISNUMBER(Marks!$B$22:$BC$22))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=B$4)*(Marks!$B$22:$BC$22=1))/SUMPRODUCT((Marks!$B$3:$BC$3=B$4)*ISNUMBER(Marks!$B$22:$BC$22)))</f>
         <v/>
       </c>
       <c r="C22" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AZ$3=C$4)*ISNUMBER(Marks!$B$22:$AZ$22))=0,"",SUMPRODUCT((Marks!$B$3:$AZ$3=C$4)*(Marks!$B$22:$AZ$22=1))/SUMPRODUCT((Marks!$B$3:$AZ$3=C$4)*ISNUMBER(Marks!$B$22:$AZ$22)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=C$4)*ISNUMBER(Marks!$B$22:$BC$22))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=C$4)*(Marks!$B$22:$BC$22=1))/SUMPRODUCT((Marks!$B$3:$BC$3=C$4)*ISNUMBER(Marks!$B$22:$BC$22)))</f>
         <v/>
       </c>
       <c r="D22" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AZ$3=D$4)*ISNUMBER(Marks!$B$22:$AZ$22))=0,"",SUMPRODUCT((Marks!$B$3:$AZ$3=D$4)*(Marks!$B$22:$AZ$22=1))/SUMPRODUCT((Marks!$B$3:$AZ$3=D$4)*ISNUMBER(Marks!$B$22:$AZ$22)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=D$4)*ISNUMBER(Marks!$B$22:$BC$22))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=D$4)*(Marks!$B$22:$BC$22=1))/SUMPRODUCT((Marks!$B$3:$BC$3=D$4)*ISNUMBER(Marks!$B$22:$BC$22)))</f>
         <v/>
       </c>
       <c r="E22" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AZ$3=E$4)*ISNUMBER(Marks!$B$22:$AZ$22))=0,"",SUMPRODUCT((Marks!$B$3:$AZ$3=E$4)*(Marks!$B$22:$AZ$22=1))/SUMPRODUCT((Marks!$B$3:$AZ$3=E$4)*ISNUMBER(Marks!$B$22:$AZ$22)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=E$4)*ISNUMBER(Marks!$B$22:$BC$22))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=E$4)*(Marks!$B$22:$BC$22=1))/SUMPRODUCT((Marks!$B$3:$BC$3=E$4)*ISNUMBER(Marks!$B$22:$BC$22)))</f>
         <v/>
       </c>
     </row>
@@ -8752,19 +9151,19 @@
         <v>19</v>
       </c>
       <c r="B23" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AZ$3=B$4)*ISNUMBER(Marks!$B$23:$AZ$23))=0,"",SUMPRODUCT((Marks!$B$3:$AZ$3=B$4)*(Marks!$B$23:$AZ$23=1))/SUMPRODUCT((Marks!$B$3:$AZ$3=B$4)*ISNUMBER(Marks!$B$23:$AZ$23)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=B$4)*ISNUMBER(Marks!$B$23:$BC$23))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=B$4)*(Marks!$B$23:$BC$23=1))/SUMPRODUCT((Marks!$B$3:$BC$3=B$4)*ISNUMBER(Marks!$B$23:$BC$23)))</f>
         <v/>
       </c>
       <c r="C23" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AZ$3=C$4)*ISNUMBER(Marks!$B$23:$AZ$23))=0,"",SUMPRODUCT((Marks!$B$3:$AZ$3=C$4)*(Marks!$B$23:$AZ$23=1))/SUMPRODUCT((Marks!$B$3:$AZ$3=C$4)*ISNUMBER(Marks!$B$23:$AZ$23)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=C$4)*ISNUMBER(Marks!$B$23:$BC$23))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=C$4)*(Marks!$B$23:$BC$23=1))/SUMPRODUCT((Marks!$B$3:$BC$3=C$4)*ISNUMBER(Marks!$B$23:$BC$23)))</f>
         <v/>
       </c>
       <c r="D23" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AZ$3=D$4)*ISNUMBER(Marks!$B$23:$AZ$23))=0,"",SUMPRODUCT((Marks!$B$3:$AZ$3=D$4)*(Marks!$B$23:$AZ$23=1))/SUMPRODUCT((Marks!$B$3:$AZ$3=D$4)*ISNUMBER(Marks!$B$23:$AZ$23)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=D$4)*ISNUMBER(Marks!$B$23:$BC$23))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=D$4)*(Marks!$B$23:$BC$23=1))/SUMPRODUCT((Marks!$B$3:$BC$3=D$4)*ISNUMBER(Marks!$B$23:$BC$23)))</f>
         <v/>
       </c>
       <c r="E23" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AZ$3=E$4)*ISNUMBER(Marks!$B$23:$AZ$23))=0,"",SUMPRODUCT((Marks!$B$3:$AZ$3=E$4)*(Marks!$B$23:$AZ$23=1))/SUMPRODUCT((Marks!$B$3:$AZ$3=E$4)*ISNUMBER(Marks!$B$23:$AZ$23)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=E$4)*ISNUMBER(Marks!$B$23:$BC$23))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=E$4)*(Marks!$B$23:$BC$23=1))/SUMPRODUCT((Marks!$B$3:$BC$3=E$4)*ISNUMBER(Marks!$B$23:$BC$23)))</f>
         <v/>
       </c>
     </row>
@@ -8773,19 +9172,19 @@
         <v>20</v>
       </c>
       <c r="B24" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AZ$3=B$4)*ISNUMBER(Marks!$B$24:$AZ$24))=0,"",SUMPRODUCT((Marks!$B$3:$AZ$3=B$4)*(Marks!$B$24:$AZ$24=1))/SUMPRODUCT((Marks!$B$3:$AZ$3=B$4)*ISNUMBER(Marks!$B$24:$AZ$24)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=B$4)*ISNUMBER(Marks!$B$24:$BC$24))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=B$4)*(Marks!$B$24:$BC$24=1))/SUMPRODUCT((Marks!$B$3:$BC$3=B$4)*ISNUMBER(Marks!$B$24:$BC$24)))</f>
         <v/>
       </c>
       <c r="C24" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AZ$3=C$4)*ISNUMBER(Marks!$B$24:$AZ$24))=0,"",SUMPRODUCT((Marks!$B$3:$AZ$3=C$4)*(Marks!$B$24:$AZ$24=1))/SUMPRODUCT((Marks!$B$3:$AZ$3=C$4)*ISNUMBER(Marks!$B$24:$AZ$24)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=C$4)*ISNUMBER(Marks!$B$24:$BC$24))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=C$4)*(Marks!$B$24:$BC$24=1))/SUMPRODUCT((Marks!$B$3:$BC$3=C$4)*ISNUMBER(Marks!$B$24:$BC$24)))</f>
         <v/>
       </c>
       <c r="D24" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AZ$3=D$4)*ISNUMBER(Marks!$B$24:$AZ$24))=0,"",SUMPRODUCT((Marks!$B$3:$AZ$3=D$4)*(Marks!$B$24:$AZ$24=1))/SUMPRODUCT((Marks!$B$3:$AZ$3=D$4)*ISNUMBER(Marks!$B$24:$AZ$24)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=D$4)*ISNUMBER(Marks!$B$24:$BC$24))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=D$4)*(Marks!$B$24:$BC$24=1))/SUMPRODUCT((Marks!$B$3:$BC$3=D$4)*ISNUMBER(Marks!$B$24:$BC$24)))</f>
         <v/>
       </c>
       <c r="E24" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AZ$3=E$4)*ISNUMBER(Marks!$B$24:$AZ$24))=0,"",SUMPRODUCT((Marks!$B$3:$AZ$3=E$4)*(Marks!$B$24:$AZ$24=1))/SUMPRODUCT((Marks!$B$3:$AZ$3=E$4)*ISNUMBER(Marks!$B$24:$AZ$24)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=E$4)*ISNUMBER(Marks!$B$24:$BC$24))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=E$4)*(Marks!$B$24:$BC$24=1))/SUMPRODUCT((Marks!$B$3:$BC$3=E$4)*ISNUMBER(Marks!$B$24:$BC$24)))</f>
         <v/>
       </c>
     </row>
@@ -8794,19 +9193,19 @@
         <v>21</v>
       </c>
       <c r="B25" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AZ$3=B$4)*ISNUMBER(Marks!$B$25:$AZ$25))=0,"",SUMPRODUCT((Marks!$B$3:$AZ$3=B$4)*(Marks!$B$25:$AZ$25=1))/SUMPRODUCT((Marks!$B$3:$AZ$3=B$4)*ISNUMBER(Marks!$B$25:$AZ$25)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=B$4)*ISNUMBER(Marks!$B$25:$BC$25))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=B$4)*(Marks!$B$25:$BC$25=1))/SUMPRODUCT((Marks!$B$3:$BC$3=B$4)*ISNUMBER(Marks!$B$25:$BC$25)))</f>
         <v/>
       </c>
       <c r="C25" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AZ$3=C$4)*ISNUMBER(Marks!$B$25:$AZ$25))=0,"",SUMPRODUCT((Marks!$B$3:$AZ$3=C$4)*(Marks!$B$25:$AZ$25=1))/SUMPRODUCT((Marks!$B$3:$AZ$3=C$4)*ISNUMBER(Marks!$B$25:$AZ$25)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=C$4)*ISNUMBER(Marks!$B$25:$BC$25))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=C$4)*(Marks!$B$25:$BC$25=1))/SUMPRODUCT((Marks!$B$3:$BC$3=C$4)*ISNUMBER(Marks!$B$25:$BC$25)))</f>
         <v/>
       </c>
       <c r="D25" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AZ$3=D$4)*ISNUMBER(Marks!$B$25:$AZ$25))=0,"",SUMPRODUCT((Marks!$B$3:$AZ$3=D$4)*(Marks!$B$25:$AZ$25=1))/SUMPRODUCT((Marks!$B$3:$AZ$3=D$4)*ISNUMBER(Marks!$B$25:$AZ$25)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=D$4)*ISNUMBER(Marks!$B$25:$BC$25))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=D$4)*(Marks!$B$25:$BC$25=1))/SUMPRODUCT((Marks!$B$3:$BC$3=D$4)*ISNUMBER(Marks!$B$25:$BC$25)))</f>
         <v/>
       </c>
       <c r="E25" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AZ$3=E$4)*ISNUMBER(Marks!$B$25:$AZ$25))=0,"",SUMPRODUCT((Marks!$B$3:$AZ$3=E$4)*(Marks!$B$25:$AZ$25=1))/SUMPRODUCT((Marks!$B$3:$AZ$3=E$4)*ISNUMBER(Marks!$B$25:$AZ$25)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=E$4)*ISNUMBER(Marks!$B$25:$BC$25))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=E$4)*(Marks!$B$25:$BC$25=1))/SUMPRODUCT((Marks!$B$3:$BC$3=E$4)*ISNUMBER(Marks!$B$25:$BC$25)))</f>
         <v/>
       </c>
     </row>
@@ -8815,19 +9214,19 @@
         <v>22</v>
       </c>
       <c r="B26" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AZ$3=B$4)*ISNUMBER(Marks!$B$26:$AZ$26))=0,"",SUMPRODUCT((Marks!$B$3:$AZ$3=B$4)*(Marks!$B$26:$AZ$26=1))/SUMPRODUCT((Marks!$B$3:$AZ$3=B$4)*ISNUMBER(Marks!$B$26:$AZ$26)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=B$4)*ISNUMBER(Marks!$B$26:$BC$26))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=B$4)*(Marks!$B$26:$BC$26=1))/SUMPRODUCT((Marks!$B$3:$BC$3=B$4)*ISNUMBER(Marks!$B$26:$BC$26)))</f>
         <v/>
       </c>
       <c r="C26" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AZ$3=C$4)*ISNUMBER(Marks!$B$26:$AZ$26))=0,"",SUMPRODUCT((Marks!$B$3:$AZ$3=C$4)*(Marks!$B$26:$AZ$26=1))/SUMPRODUCT((Marks!$B$3:$AZ$3=C$4)*ISNUMBER(Marks!$B$26:$AZ$26)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=C$4)*ISNUMBER(Marks!$B$26:$BC$26))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=C$4)*(Marks!$B$26:$BC$26=1))/SUMPRODUCT((Marks!$B$3:$BC$3=C$4)*ISNUMBER(Marks!$B$26:$BC$26)))</f>
         <v/>
       </c>
       <c r="D26" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AZ$3=D$4)*ISNUMBER(Marks!$B$26:$AZ$26))=0,"",SUMPRODUCT((Marks!$B$3:$AZ$3=D$4)*(Marks!$B$26:$AZ$26=1))/SUMPRODUCT((Marks!$B$3:$AZ$3=D$4)*ISNUMBER(Marks!$B$26:$AZ$26)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=D$4)*ISNUMBER(Marks!$B$26:$BC$26))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=D$4)*(Marks!$B$26:$BC$26=1))/SUMPRODUCT((Marks!$B$3:$BC$3=D$4)*ISNUMBER(Marks!$B$26:$BC$26)))</f>
         <v/>
       </c>
       <c r="E26" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AZ$3=E$4)*ISNUMBER(Marks!$B$26:$AZ$26))=0,"",SUMPRODUCT((Marks!$B$3:$AZ$3=E$4)*(Marks!$B$26:$AZ$26=1))/SUMPRODUCT((Marks!$B$3:$AZ$3=E$4)*ISNUMBER(Marks!$B$26:$AZ$26)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=E$4)*ISNUMBER(Marks!$B$26:$BC$26))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=E$4)*(Marks!$B$26:$BC$26=1))/SUMPRODUCT((Marks!$B$3:$BC$3=E$4)*ISNUMBER(Marks!$B$26:$BC$26)))</f>
         <v/>
       </c>
     </row>
@@ -8836,19 +9235,19 @@
         <v>23</v>
       </c>
       <c r="B27" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AZ$3=B$4)*ISNUMBER(Marks!$B$27:$AZ$27))=0,"",SUMPRODUCT((Marks!$B$3:$AZ$3=B$4)*(Marks!$B$27:$AZ$27=1))/SUMPRODUCT((Marks!$B$3:$AZ$3=B$4)*ISNUMBER(Marks!$B$27:$AZ$27)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=B$4)*ISNUMBER(Marks!$B$27:$BC$27))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=B$4)*(Marks!$B$27:$BC$27=1))/SUMPRODUCT((Marks!$B$3:$BC$3=B$4)*ISNUMBER(Marks!$B$27:$BC$27)))</f>
         <v/>
       </c>
       <c r="C27" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AZ$3=C$4)*ISNUMBER(Marks!$B$27:$AZ$27))=0,"",SUMPRODUCT((Marks!$B$3:$AZ$3=C$4)*(Marks!$B$27:$AZ$27=1))/SUMPRODUCT((Marks!$B$3:$AZ$3=C$4)*ISNUMBER(Marks!$B$27:$AZ$27)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=C$4)*ISNUMBER(Marks!$B$27:$BC$27))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=C$4)*(Marks!$B$27:$BC$27=1))/SUMPRODUCT((Marks!$B$3:$BC$3=C$4)*ISNUMBER(Marks!$B$27:$BC$27)))</f>
         <v/>
       </c>
       <c r="D27" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AZ$3=D$4)*ISNUMBER(Marks!$B$27:$AZ$27))=0,"",SUMPRODUCT((Marks!$B$3:$AZ$3=D$4)*(Marks!$B$27:$AZ$27=1))/SUMPRODUCT((Marks!$B$3:$AZ$3=D$4)*ISNUMBER(Marks!$B$27:$AZ$27)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=D$4)*ISNUMBER(Marks!$B$27:$BC$27))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=D$4)*(Marks!$B$27:$BC$27=1))/SUMPRODUCT((Marks!$B$3:$BC$3=D$4)*ISNUMBER(Marks!$B$27:$BC$27)))</f>
         <v/>
       </c>
       <c r="E27" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AZ$3=E$4)*ISNUMBER(Marks!$B$27:$AZ$27))=0,"",SUMPRODUCT((Marks!$B$3:$AZ$3=E$4)*(Marks!$B$27:$AZ$27=1))/SUMPRODUCT((Marks!$B$3:$AZ$3=E$4)*ISNUMBER(Marks!$B$27:$AZ$27)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=E$4)*ISNUMBER(Marks!$B$27:$BC$27))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=E$4)*(Marks!$B$27:$BC$27=1))/SUMPRODUCT((Marks!$B$3:$BC$3=E$4)*ISNUMBER(Marks!$B$27:$BC$27)))</f>
         <v/>
       </c>
     </row>
@@ -8857,19 +9256,19 @@
         <v>24</v>
       </c>
       <c r="B28" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AZ$3=B$4)*ISNUMBER(Marks!$B$28:$AZ$28))=0,"",SUMPRODUCT((Marks!$B$3:$AZ$3=B$4)*(Marks!$B$28:$AZ$28=1))/SUMPRODUCT((Marks!$B$3:$AZ$3=B$4)*ISNUMBER(Marks!$B$28:$AZ$28)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=B$4)*ISNUMBER(Marks!$B$28:$BC$28))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=B$4)*(Marks!$B$28:$BC$28=1))/SUMPRODUCT((Marks!$B$3:$BC$3=B$4)*ISNUMBER(Marks!$B$28:$BC$28)))</f>
         <v/>
       </c>
       <c r="C28" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AZ$3=C$4)*ISNUMBER(Marks!$B$28:$AZ$28))=0,"",SUMPRODUCT((Marks!$B$3:$AZ$3=C$4)*(Marks!$B$28:$AZ$28=1))/SUMPRODUCT((Marks!$B$3:$AZ$3=C$4)*ISNUMBER(Marks!$B$28:$AZ$28)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=C$4)*ISNUMBER(Marks!$B$28:$BC$28))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=C$4)*(Marks!$B$28:$BC$28=1))/SUMPRODUCT((Marks!$B$3:$BC$3=C$4)*ISNUMBER(Marks!$B$28:$BC$28)))</f>
         <v/>
       </c>
       <c r="D28" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AZ$3=D$4)*ISNUMBER(Marks!$B$28:$AZ$28))=0,"",SUMPRODUCT((Marks!$B$3:$AZ$3=D$4)*(Marks!$B$28:$AZ$28=1))/SUMPRODUCT((Marks!$B$3:$AZ$3=D$4)*ISNUMBER(Marks!$B$28:$AZ$28)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=D$4)*ISNUMBER(Marks!$B$28:$BC$28))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=D$4)*(Marks!$B$28:$BC$28=1))/SUMPRODUCT((Marks!$B$3:$BC$3=D$4)*ISNUMBER(Marks!$B$28:$BC$28)))</f>
         <v/>
       </c>
       <c r="E28" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AZ$3=E$4)*ISNUMBER(Marks!$B$28:$AZ$28))=0,"",SUMPRODUCT((Marks!$B$3:$AZ$3=E$4)*(Marks!$B$28:$AZ$28=1))/SUMPRODUCT((Marks!$B$3:$AZ$3=E$4)*ISNUMBER(Marks!$B$28:$AZ$28)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=E$4)*ISNUMBER(Marks!$B$28:$BC$28))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=E$4)*(Marks!$B$28:$BC$28=1))/SUMPRODUCT((Marks!$B$3:$BC$3=E$4)*ISNUMBER(Marks!$B$28:$BC$28)))</f>
         <v/>
       </c>
     </row>
@@ -8878,19 +9277,19 @@
         <v>25</v>
       </c>
       <c r="B29" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AZ$3=B$4)*ISNUMBER(Marks!$B$29:$AZ$29))=0,"",SUMPRODUCT((Marks!$B$3:$AZ$3=B$4)*(Marks!$B$29:$AZ$29=1))/SUMPRODUCT((Marks!$B$3:$AZ$3=B$4)*ISNUMBER(Marks!$B$29:$AZ$29)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=B$4)*ISNUMBER(Marks!$B$29:$BC$29))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=B$4)*(Marks!$B$29:$BC$29=1))/SUMPRODUCT((Marks!$B$3:$BC$3=B$4)*ISNUMBER(Marks!$B$29:$BC$29)))</f>
         <v/>
       </c>
       <c r="C29" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AZ$3=C$4)*ISNUMBER(Marks!$B$29:$AZ$29))=0,"",SUMPRODUCT((Marks!$B$3:$AZ$3=C$4)*(Marks!$B$29:$AZ$29=1))/SUMPRODUCT((Marks!$B$3:$AZ$3=C$4)*ISNUMBER(Marks!$B$29:$AZ$29)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=C$4)*ISNUMBER(Marks!$B$29:$BC$29))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=C$4)*(Marks!$B$29:$BC$29=1))/SUMPRODUCT((Marks!$B$3:$BC$3=C$4)*ISNUMBER(Marks!$B$29:$BC$29)))</f>
         <v/>
       </c>
       <c r="D29" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AZ$3=D$4)*ISNUMBER(Marks!$B$29:$AZ$29))=0,"",SUMPRODUCT((Marks!$B$3:$AZ$3=D$4)*(Marks!$B$29:$AZ$29=1))/SUMPRODUCT((Marks!$B$3:$AZ$3=D$4)*ISNUMBER(Marks!$B$29:$AZ$29)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=D$4)*ISNUMBER(Marks!$B$29:$BC$29))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=D$4)*(Marks!$B$29:$BC$29=1))/SUMPRODUCT((Marks!$B$3:$BC$3=D$4)*ISNUMBER(Marks!$B$29:$BC$29)))</f>
         <v/>
       </c>
       <c r="E29" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AZ$3=E$4)*ISNUMBER(Marks!$B$29:$AZ$29))=0,"",SUMPRODUCT((Marks!$B$3:$AZ$3=E$4)*(Marks!$B$29:$AZ$29=1))/SUMPRODUCT((Marks!$B$3:$AZ$3=E$4)*ISNUMBER(Marks!$B$29:$AZ$29)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=E$4)*ISNUMBER(Marks!$B$29:$BC$29))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=E$4)*(Marks!$B$29:$BC$29=1))/SUMPRODUCT((Marks!$B$3:$BC$3=E$4)*ISNUMBER(Marks!$B$29:$BC$29)))</f>
         <v/>
       </c>
     </row>
@@ -8899,19 +9298,19 @@
         <v>26</v>
       </c>
       <c r="B30" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AZ$3=B$4)*ISNUMBER(Marks!$B$30:$AZ$30))=0,"",SUMPRODUCT((Marks!$B$3:$AZ$3=B$4)*(Marks!$B$30:$AZ$30=1))/SUMPRODUCT((Marks!$B$3:$AZ$3=B$4)*ISNUMBER(Marks!$B$30:$AZ$30)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=B$4)*ISNUMBER(Marks!$B$30:$BC$30))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=B$4)*(Marks!$B$30:$BC$30=1))/SUMPRODUCT((Marks!$B$3:$BC$3=B$4)*ISNUMBER(Marks!$B$30:$BC$30)))</f>
         <v/>
       </c>
       <c r="C30" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AZ$3=C$4)*ISNUMBER(Marks!$B$30:$AZ$30))=0,"",SUMPRODUCT((Marks!$B$3:$AZ$3=C$4)*(Marks!$B$30:$AZ$30=1))/SUMPRODUCT((Marks!$B$3:$AZ$3=C$4)*ISNUMBER(Marks!$B$30:$AZ$30)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=C$4)*ISNUMBER(Marks!$B$30:$BC$30))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=C$4)*(Marks!$B$30:$BC$30=1))/SUMPRODUCT((Marks!$B$3:$BC$3=C$4)*ISNUMBER(Marks!$B$30:$BC$30)))</f>
         <v/>
       </c>
       <c r="D30" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AZ$3=D$4)*ISNUMBER(Marks!$B$30:$AZ$30))=0,"",SUMPRODUCT((Marks!$B$3:$AZ$3=D$4)*(Marks!$B$30:$AZ$30=1))/SUMPRODUCT((Marks!$B$3:$AZ$3=D$4)*ISNUMBER(Marks!$B$30:$AZ$30)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=D$4)*ISNUMBER(Marks!$B$30:$BC$30))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=D$4)*(Marks!$B$30:$BC$30=1))/SUMPRODUCT((Marks!$B$3:$BC$3=D$4)*ISNUMBER(Marks!$B$30:$BC$30)))</f>
         <v/>
       </c>
       <c r="E30" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AZ$3=E$4)*ISNUMBER(Marks!$B$30:$AZ$30))=0,"",SUMPRODUCT((Marks!$B$3:$AZ$3=E$4)*(Marks!$B$30:$AZ$30=1))/SUMPRODUCT((Marks!$B$3:$AZ$3=E$4)*ISNUMBER(Marks!$B$30:$AZ$30)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=E$4)*ISNUMBER(Marks!$B$30:$BC$30))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=E$4)*(Marks!$B$30:$BC$30=1))/SUMPRODUCT((Marks!$B$3:$BC$3=E$4)*ISNUMBER(Marks!$B$30:$BC$30)))</f>
         <v/>
       </c>
     </row>
@@ -8920,19 +9319,19 @@
         <v>27</v>
       </c>
       <c r="B31" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AZ$3=B$4)*ISNUMBER(Marks!$B$31:$AZ$31))=0,"",SUMPRODUCT((Marks!$B$3:$AZ$3=B$4)*(Marks!$B$31:$AZ$31=1))/SUMPRODUCT((Marks!$B$3:$AZ$3=B$4)*ISNUMBER(Marks!$B$31:$AZ$31)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=B$4)*ISNUMBER(Marks!$B$31:$BC$31))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=B$4)*(Marks!$B$31:$BC$31=1))/SUMPRODUCT((Marks!$B$3:$BC$3=B$4)*ISNUMBER(Marks!$B$31:$BC$31)))</f>
         <v/>
       </c>
       <c r="C31" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AZ$3=C$4)*ISNUMBER(Marks!$B$31:$AZ$31))=0,"",SUMPRODUCT((Marks!$B$3:$AZ$3=C$4)*(Marks!$B$31:$AZ$31=1))/SUMPRODUCT((Marks!$B$3:$AZ$3=C$4)*ISNUMBER(Marks!$B$31:$AZ$31)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=C$4)*ISNUMBER(Marks!$B$31:$BC$31))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=C$4)*(Marks!$B$31:$BC$31=1))/SUMPRODUCT((Marks!$B$3:$BC$3=C$4)*ISNUMBER(Marks!$B$31:$BC$31)))</f>
         <v/>
       </c>
       <c r="D31" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AZ$3=D$4)*ISNUMBER(Marks!$B$31:$AZ$31))=0,"",SUMPRODUCT((Marks!$B$3:$AZ$3=D$4)*(Marks!$B$31:$AZ$31=1))/SUMPRODUCT((Marks!$B$3:$AZ$3=D$4)*ISNUMBER(Marks!$B$31:$AZ$31)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=D$4)*ISNUMBER(Marks!$B$31:$BC$31))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=D$4)*(Marks!$B$31:$BC$31=1))/SUMPRODUCT((Marks!$B$3:$BC$3=D$4)*ISNUMBER(Marks!$B$31:$BC$31)))</f>
         <v/>
       </c>
       <c r="E31" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AZ$3=E$4)*ISNUMBER(Marks!$B$31:$AZ$31))=0,"",SUMPRODUCT((Marks!$B$3:$AZ$3=E$4)*(Marks!$B$31:$AZ$31=1))/SUMPRODUCT((Marks!$B$3:$AZ$3=E$4)*ISNUMBER(Marks!$B$31:$AZ$31)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=E$4)*ISNUMBER(Marks!$B$31:$BC$31))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=E$4)*(Marks!$B$31:$BC$31=1))/SUMPRODUCT((Marks!$B$3:$BC$3=E$4)*ISNUMBER(Marks!$B$31:$BC$31)))</f>
         <v/>
       </c>
     </row>
@@ -8941,19 +9340,19 @@
         <v>28</v>
       </c>
       <c r="B32" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AZ$3=B$4)*ISNUMBER(Marks!$B$32:$AZ$32))=0,"",SUMPRODUCT((Marks!$B$3:$AZ$3=B$4)*(Marks!$B$32:$AZ$32=1))/SUMPRODUCT((Marks!$B$3:$AZ$3=B$4)*ISNUMBER(Marks!$B$32:$AZ$32)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=B$4)*ISNUMBER(Marks!$B$32:$BC$32))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=B$4)*(Marks!$B$32:$BC$32=1))/SUMPRODUCT((Marks!$B$3:$BC$3=B$4)*ISNUMBER(Marks!$B$32:$BC$32)))</f>
         <v/>
       </c>
       <c r="C32" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AZ$3=C$4)*ISNUMBER(Marks!$B$32:$AZ$32))=0,"",SUMPRODUCT((Marks!$B$3:$AZ$3=C$4)*(Marks!$B$32:$AZ$32=1))/SUMPRODUCT((Marks!$B$3:$AZ$3=C$4)*ISNUMBER(Marks!$B$32:$AZ$32)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=C$4)*ISNUMBER(Marks!$B$32:$BC$32))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=C$4)*(Marks!$B$32:$BC$32=1))/SUMPRODUCT((Marks!$B$3:$BC$3=C$4)*ISNUMBER(Marks!$B$32:$BC$32)))</f>
         <v/>
       </c>
       <c r="D32" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AZ$3=D$4)*ISNUMBER(Marks!$B$32:$AZ$32))=0,"",SUMPRODUCT((Marks!$B$3:$AZ$3=D$4)*(Marks!$B$32:$AZ$32=1))/SUMPRODUCT((Marks!$B$3:$AZ$3=D$4)*ISNUMBER(Marks!$B$32:$AZ$32)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=D$4)*ISNUMBER(Marks!$B$32:$BC$32))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=D$4)*(Marks!$B$32:$BC$32=1))/SUMPRODUCT((Marks!$B$3:$BC$3=D$4)*ISNUMBER(Marks!$B$32:$BC$32)))</f>
         <v/>
       </c>
       <c r="E32" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AZ$3=E$4)*ISNUMBER(Marks!$B$32:$AZ$32))=0,"",SUMPRODUCT((Marks!$B$3:$AZ$3=E$4)*(Marks!$B$32:$AZ$32=1))/SUMPRODUCT((Marks!$B$3:$AZ$3=E$4)*ISNUMBER(Marks!$B$32:$AZ$32)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=E$4)*ISNUMBER(Marks!$B$32:$BC$32))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=E$4)*(Marks!$B$32:$BC$32=1))/SUMPRODUCT((Marks!$B$3:$BC$3=E$4)*ISNUMBER(Marks!$B$32:$BC$32)))</f>
         <v/>
       </c>
     </row>
@@ -8962,19 +9361,19 @@
         <v>29</v>
       </c>
       <c r="B33" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AZ$3=B$4)*ISNUMBER(Marks!$B$33:$AZ$33))=0,"",SUMPRODUCT((Marks!$B$3:$AZ$3=B$4)*(Marks!$B$33:$AZ$33=1))/SUMPRODUCT((Marks!$B$3:$AZ$3=B$4)*ISNUMBER(Marks!$B$33:$AZ$33)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=B$4)*ISNUMBER(Marks!$B$33:$BC$33))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=B$4)*(Marks!$B$33:$BC$33=1))/SUMPRODUCT((Marks!$B$3:$BC$3=B$4)*ISNUMBER(Marks!$B$33:$BC$33)))</f>
         <v/>
       </c>
       <c r="C33" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AZ$3=C$4)*ISNUMBER(Marks!$B$33:$AZ$33))=0,"",SUMPRODUCT((Marks!$B$3:$AZ$3=C$4)*(Marks!$B$33:$AZ$33=1))/SUMPRODUCT((Marks!$B$3:$AZ$3=C$4)*ISNUMBER(Marks!$B$33:$AZ$33)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=C$4)*ISNUMBER(Marks!$B$33:$BC$33))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=C$4)*(Marks!$B$33:$BC$33=1))/SUMPRODUCT((Marks!$B$3:$BC$3=C$4)*ISNUMBER(Marks!$B$33:$BC$33)))</f>
         <v/>
       </c>
       <c r="D33" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AZ$3=D$4)*ISNUMBER(Marks!$B$33:$AZ$33))=0,"",SUMPRODUCT((Marks!$B$3:$AZ$3=D$4)*(Marks!$B$33:$AZ$33=1))/SUMPRODUCT((Marks!$B$3:$AZ$3=D$4)*ISNUMBER(Marks!$B$33:$AZ$33)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=D$4)*ISNUMBER(Marks!$B$33:$BC$33))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=D$4)*(Marks!$B$33:$BC$33=1))/SUMPRODUCT((Marks!$B$3:$BC$3=D$4)*ISNUMBER(Marks!$B$33:$BC$33)))</f>
         <v/>
       </c>
       <c r="E33" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AZ$3=E$4)*ISNUMBER(Marks!$B$33:$AZ$33))=0,"",SUMPRODUCT((Marks!$B$3:$AZ$3=E$4)*(Marks!$B$33:$AZ$33=1))/SUMPRODUCT((Marks!$B$3:$AZ$3=E$4)*ISNUMBER(Marks!$B$33:$AZ$33)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=E$4)*ISNUMBER(Marks!$B$33:$BC$33))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=E$4)*(Marks!$B$33:$BC$33=1))/SUMPRODUCT((Marks!$B$3:$BC$3=E$4)*ISNUMBER(Marks!$B$33:$BC$33)))</f>
         <v/>
       </c>
     </row>
@@ -8983,19 +9382,19 @@
         <v>30</v>
       </c>
       <c r="B34" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AZ$3=B$4)*ISNUMBER(Marks!$B$34:$AZ$34))=0,"",SUMPRODUCT((Marks!$B$3:$AZ$3=B$4)*(Marks!$B$34:$AZ$34=1))/SUMPRODUCT((Marks!$B$3:$AZ$3=B$4)*ISNUMBER(Marks!$B$34:$AZ$34)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=B$4)*ISNUMBER(Marks!$B$34:$BC$34))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=B$4)*(Marks!$B$34:$BC$34=1))/SUMPRODUCT((Marks!$B$3:$BC$3=B$4)*ISNUMBER(Marks!$B$34:$BC$34)))</f>
         <v/>
       </c>
       <c r="C34" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AZ$3=C$4)*ISNUMBER(Marks!$B$34:$AZ$34))=0,"",SUMPRODUCT((Marks!$B$3:$AZ$3=C$4)*(Marks!$B$34:$AZ$34=1))/SUMPRODUCT((Marks!$B$3:$AZ$3=C$4)*ISNUMBER(Marks!$B$34:$AZ$34)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=C$4)*ISNUMBER(Marks!$B$34:$BC$34))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=C$4)*(Marks!$B$34:$BC$34=1))/SUMPRODUCT((Marks!$B$3:$BC$3=C$4)*ISNUMBER(Marks!$B$34:$BC$34)))</f>
         <v/>
       </c>
       <c r="D34" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AZ$3=D$4)*ISNUMBER(Marks!$B$34:$AZ$34))=0,"",SUMPRODUCT((Marks!$B$3:$AZ$3=D$4)*(Marks!$B$34:$AZ$34=1))/SUMPRODUCT((Marks!$B$3:$AZ$3=D$4)*ISNUMBER(Marks!$B$34:$AZ$34)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=D$4)*ISNUMBER(Marks!$B$34:$BC$34))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=D$4)*(Marks!$B$34:$BC$34=1))/SUMPRODUCT((Marks!$B$3:$BC$3=D$4)*ISNUMBER(Marks!$B$34:$BC$34)))</f>
         <v/>
       </c>
       <c r="E34" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AZ$3=E$4)*ISNUMBER(Marks!$B$34:$AZ$34))=0,"",SUMPRODUCT((Marks!$B$3:$AZ$3=E$4)*(Marks!$B$34:$AZ$34=1))/SUMPRODUCT((Marks!$B$3:$AZ$3=E$4)*ISNUMBER(Marks!$B$34:$AZ$34)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=E$4)*ISNUMBER(Marks!$B$34:$BC$34))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=E$4)*(Marks!$B$34:$BC$34=1))/SUMPRODUCT((Marks!$B$3:$BC$3=E$4)*ISNUMBER(Marks!$B$34:$BC$34)))</f>
         <v/>
       </c>
     </row>
@@ -9004,19 +9403,19 @@
         <v>31</v>
       </c>
       <c r="B35" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AZ$3=B$4)*ISNUMBER(Marks!$B$35:$AZ$35))=0,"",SUMPRODUCT((Marks!$B$3:$AZ$3=B$4)*(Marks!$B$35:$AZ$35=1))/SUMPRODUCT((Marks!$B$3:$AZ$3=B$4)*ISNUMBER(Marks!$B$35:$AZ$35)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=B$4)*ISNUMBER(Marks!$B$35:$BC$35))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=B$4)*(Marks!$B$35:$BC$35=1))/SUMPRODUCT((Marks!$B$3:$BC$3=B$4)*ISNUMBER(Marks!$B$35:$BC$35)))</f>
         <v/>
       </c>
       <c r="C35" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AZ$3=C$4)*ISNUMBER(Marks!$B$35:$AZ$35))=0,"",SUMPRODUCT((Marks!$B$3:$AZ$3=C$4)*(Marks!$B$35:$AZ$35=1))/SUMPRODUCT((Marks!$B$3:$AZ$3=C$4)*ISNUMBER(Marks!$B$35:$AZ$35)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=C$4)*ISNUMBER(Marks!$B$35:$BC$35))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=C$4)*(Marks!$B$35:$BC$35=1))/SUMPRODUCT((Marks!$B$3:$BC$3=C$4)*ISNUMBER(Marks!$B$35:$BC$35)))</f>
         <v/>
       </c>
       <c r="D35" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AZ$3=D$4)*ISNUMBER(Marks!$B$35:$AZ$35))=0,"",SUMPRODUCT((Marks!$B$3:$AZ$3=D$4)*(Marks!$B$35:$AZ$35=1))/SUMPRODUCT((Marks!$B$3:$AZ$3=D$4)*ISNUMBER(Marks!$B$35:$AZ$35)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=D$4)*ISNUMBER(Marks!$B$35:$BC$35))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=D$4)*(Marks!$B$35:$BC$35=1))/SUMPRODUCT((Marks!$B$3:$BC$3=D$4)*ISNUMBER(Marks!$B$35:$BC$35)))</f>
         <v/>
       </c>
       <c r="E35" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AZ$3=E$4)*ISNUMBER(Marks!$B$35:$AZ$35))=0,"",SUMPRODUCT((Marks!$B$3:$AZ$3=E$4)*(Marks!$B$35:$AZ$35=1))/SUMPRODUCT((Marks!$B$3:$AZ$3=E$4)*ISNUMBER(Marks!$B$35:$AZ$35)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=E$4)*ISNUMBER(Marks!$B$35:$BC$35))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=E$4)*(Marks!$B$35:$BC$35=1))/SUMPRODUCT((Marks!$B$3:$BC$3=E$4)*ISNUMBER(Marks!$B$35:$BC$35)))</f>
         <v/>
       </c>
     </row>
@@ -9025,19 +9424,19 @@
         <v>32</v>
       </c>
       <c r="B36" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AZ$3=B$4)*ISNUMBER(Marks!$B$36:$AZ$36))=0,"",SUMPRODUCT((Marks!$B$3:$AZ$3=B$4)*(Marks!$B$36:$AZ$36=1))/SUMPRODUCT((Marks!$B$3:$AZ$3=B$4)*ISNUMBER(Marks!$B$36:$AZ$36)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=B$4)*ISNUMBER(Marks!$B$36:$BC$36))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=B$4)*(Marks!$B$36:$BC$36=1))/SUMPRODUCT((Marks!$B$3:$BC$3=B$4)*ISNUMBER(Marks!$B$36:$BC$36)))</f>
         <v/>
       </c>
       <c r="C36" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AZ$3=C$4)*ISNUMBER(Marks!$B$36:$AZ$36))=0,"",SUMPRODUCT((Marks!$B$3:$AZ$3=C$4)*(Marks!$B$36:$AZ$36=1))/SUMPRODUCT((Marks!$B$3:$AZ$3=C$4)*ISNUMBER(Marks!$B$36:$AZ$36)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=C$4)*ISNUMBER(Marks!$B$36:$BC$36))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=C$4)*(Marks!$B$36:$BC$36=1))/SUMPRODUCT((Marks!$B$3:$BC$3=C$4)*ISNUMBER(Marks!$B$36:$BC$36)))</f>
         <v/>
       </c>
       <c r="D36" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AZ$3=D$4)*ISNUMBER(Marks!$B$36:$AZ$36))=0,"",SUMPRODUCT((Marks!$B$3:$AZ$3=D$4)*(Marks!$B$36:$AZ$36=1))/SUMPRODUCT((Marks!$B$3:$AZ$3=D$4)*ISNUMBER(Marks!$B$36:$AZ$36)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=D$4)*ISNUMBER(Marks!$B$36:$BC$36))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=D$4)*(Marks!$B$36:$BC$36=1))/SUMPRODUCT((Marks!$B$3:$BC$3=D$4)*ISNUMBER(Marks!$B$36:$BC$36)))</f>
         <v/>
       </c>
       <c r="E36" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AZ$3=E$4)*ISNUMBER(Marks!$B$36:$AZ$36))=0,"",SUMPRODUCT((Marks!$B$3:$AZ$3=E$4)*(Marks!$B$36:$AZ$36=1))/SUMPRODUCT((Marks!$B$3:$AZ$3=E$4)*ISNUMBER(Marks!$B$36:$AZ$36)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=E$4)*ISNUMBER(Marks!$B$36:$BC$36))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=E$4)*(Marks!$B$36:$BC$36=1))/SUMPRODUCT((Marks!$B$3:$BC$3=E$4)*ISNUMBER(Marks!$B$36:$BC$36)))</f>
         <v/>
       </c>
     </row>
@@ -9046,19 +9445,19 @@
         <v>33</v>
       </c>
       <c r="B37" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AZ$3=B$4)*ISNUMBER(Marks!$B$37:$AZ$37))=0,"",SUMPRODUCT((Marks!$B$3:$AZ$3=B$4)*(Marks!$B$37:$AZ$37=1))/SUMPRODUCT((Marks!$B$3:$AZ$3=B$4)*ISNUMBER(Marks!$B$37:$AZ$37)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=B$4)*ISNUMBER(Marks!$B$37:$BC$37))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=B$4)*(Marks!$B$37:$BC$37=1))/SUMPRODUCT((Marks!$B$3:$BC$3=B$4)*ISNUMBER(Marks!$B$37:$BC$37)))</f>
         <v/>
       </c>
       <c r="C37" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AZ$3=C$4)*ISNUMBER(Marks!$B$37:$AZ$37))=0,"",SUMPRODUCT((Marks!$B$3:$AZ$3=C$4)*(Marks!$B$37:$AZ$37=1))/SUMPRODUCT((Marks!$B$3:$AZ$3=C$4)*ISNUMBER(Marks!$B$37:$AZ$37)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=C$4)*ISNUMBER(Marks!$B$37:$BC$37))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=C$4)*(Marks!$B$37:$BC$37=1))/SUMPRODUCT((Marks!$B$3:$BC$3=C$4)*ISNUMBER(Marks!$B$37:$BC$37)))</f>
         <v/>
       </c>
       <c r="D37" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AZ$3=D$4)*ISNUMBER(Marks!$B$37:$AZ$37))=0,"",SUMPRODUCT((Marks!$B$3:$AZ$3=D$4)*(Marks!$B$37:$AZ$37=1))/SUMPRODUCT((Marks!$B$3:$AZ$3=D$4)*ISNUMBER(Marks!$B$37:$AZ$37)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=D$4)*ISNUMBER(Marks!$B$37:$BC$37))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=D$4)*(Marks!$B$37:$BC$37=1))/SUMPRODUCT((Marks!$B$3:$BC$3=D$4)*ISNUMBER(Marks!$B$37:$BC$37)))</f>
         <v/>
       </c>
       <c r="E37" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AZ$3=E$4)*ISNUMBER(Marks!$B$37:$AZ$37))=0,"",SUMPRODUCT((Marks!$B$3:$AZ$3=E$4)*(Marks!$B$37:$AZ$37=1))/SUMPRODUCT((Marks!$B$3:$AZ$3=E$4)*ISNUMBER(Marks!$B$37:$AZ$37)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=E$4)*ISNUMBER(Marks!$B$37:$BC$37))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=E$4)*(Marks!$B$37:$BC$37=1))/SUMPRODUCT((Marks!$B$3:$BC$3=E$4)*ISNUMBER(Marks!$B$37:$BC$37)))</f>
         <v/>
       </c>
     </row>
@@ -9067,19 +9466,19 @@
         <v>34</v>
       </c>
       <c r="B38" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AZ$3=B$4)*ISNUMBER(Marks!$B$38:$AZ$38))=0,"",SUMPRODUCT((Marks!$B$3:$AZ$3=B$4)*(Marks!$B$38:$AZ$38=1))/SUMPRODUCT((Marks!$B$3:$AZ$3=B$4)*ISNUMBER(Marks!$B$38:$AZ$38)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=B$4)*ISNUMBER(Marks!$B$38:$BC$38))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=B$4)*(Marks!$B$38:$BC$38=1))/SUMPRODUCT((Marks!$B$3:$BC$3=B$4)*ISNUMBER(Marks!$B$38:$BC$38)))</f>
         <v/>
       </c>
       <c r="C38" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AZ$3=C$4)*ISNUMBER(Marks!$B$38:$AZ$38))=0,"",SUMPRODUCT((Marks!$B$3:$AZ$3=C$4)*(Marks!$B$38:$AZ$38=1))/SUMPRODUCT((Marks!$B$3:$AZ$3=C$4)*ISNUMBER(Marks!$B$38:$AZ$38)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=C$4)*ISNUMBER(Marks!$B$38:$BC$38))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=C$4)*(Marks!$B$38:$BC$38=1))/SUMPRODUCT((Marks!$B$3:$BC$3=C$4)*ISNUMBER(Marks!$B$38:$BC$38)))</f>
         <v/>
       </c>
       <c r="D38" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AZ$3=D$4)*ISNUMBER(Marks!$B$38:$AZ$38))=0,"",SUMPRODUCT((Marks!$B$3:$AZ$3=D$4)*(Marks!$B$38:$AZ$38=1))/SUMPRODUCT((Marks!$B$3:$AZ$3=D$4)*ISNUMBER(Marks!$B$38:$AZ$38)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=D$4)*ISNUMBER(Marks!$B$38:$BC$38))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=D$4)*(Marks!$B$38:$BC$38=1))/SUMPRODUCT((Marks!$B$3:$BC$3=D$4)*ISNUMBER(Marks!$B$38:$BC$38)))</f>
         <v/>
       </c>
       <c r="E38" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AZ$3=E$4)*ISNUMBER(Marks!$B$38:$AZ$38))=0,"",SUMPRODUCT((Marks!$B$3:$AZ$3=E$4)*(Marks!$B$38:$AZ$38=1))/SUMPRODUCT((Marks!$B$3:$AZ$3=E$4)*ISNUMBER(Marks!$B$38:$AZ$38)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=E$4)*ISNUMBER(Marks!$B$38:$BC$38))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=E$4)*(Marks!$B$38:$BC$38=1))/SUMPRODUCT((Marks!$B$3:$BC$3=E$4)*ISNUMBER(Marks!$B$38:$BC$38)))</f>
         <v/>
       </c>
     </row>
@@ -9088,19 +9487,19 @@
         <v>35</v>
       </c>
       <c r="B39" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AZ$3=B$4)*ISNUMBER(Marks!$B$39:$AZ$39))=0,"",SUMPRODUCT((Marks!$B$3:$AZ$3=B$4)*(Marks!$B$39:$AZ$39=1))/SUMPRODUCT((Marks!$B$3:$AZ$3=B$4)*ISNUMBER(Marks!$B$39:$AZ$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=B$4)*ISNUMBER(Marks!$B$39:$BC$39))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=B$4)*(Marks!$B$39:$BC$39=1))/SUMPRODUCT((Marks!$B$3:$BC$3=B$4)*ISNUMBER(Marks!$B$39:$BC$39)))</f>
         <v/>
       </c>
       <c r="C39" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AZ$3=C$4)*ISNUMBER(Marks!$B$39:$AZ$39))=0,"",SUMPRODUCT((Marks!$B$3:$AZ$3=C$4)*(Marks!$B$39:$AZ$39=1))/SUMPRODUCT((Marks!$B$3:$AZ$3=C$4)*ISNUMBER(Marks!$B$39:$AZ$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=C$4)*ISNUMBER(Marks!$B$39:$BC$39))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=C$4)*(Marks!$B$39:$BC$39=1))/SUMPRODUCT((Marks!$B$3:$BC$3=C$4)*ISNUMBER(Marks!$B$39:$BC$39)))</f>
         <v/>
       </c>
       <c r="D39" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AZ$3=D$4)*ISNUMBER(Marks!$B$39:$AZ$39))=0,"",SUMPRODUCT((Marks!$B$3:$AZ$3=D$4)*(Marks!$B$39:$AZ$39=1))/SUMPRODUCT((Marks!$B$3:$AZ$3=D$4)*ISNUMBER(Marks!$B$39:$AZ$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=D$4)*ISNUMBER(Marks!$B$39:$BC$39))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=D$4)*(Marks!$B$39:$BC$39=1))/SUMPRODUCT((Marks!$B$3:$BC$3=D$4)*ISNUMBER(Marks!$B$39:$BC$39)))</f>
         <v/>
       </c>
       <c r="E39" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AZ$3=E$4)*ISNUMBER(Marks!$B$39:$AZ$39))=0,"",SUMPRODUCT((Marks!$B$3:$AZ$3=E$4)*(Marks!$B$39:$AZ$39=1))/SUMPRODUCT((Marks!$B$3:$AZ$3=E$4)*ISNUMBER(Marks!$B$39:$AZ$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=E$4)*ISNUMBER(Marks!$B$39:$BC$39))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=E$4)*(Marks!$B$39:$BC$39=1))/SUMPRODUCT((Marks!$B$3:$BC$3=E$4)*ISNUMBER(Marks!$B$39:$BC$39)))</f>
         <v/>
       </c>
     </row>

--- a/content/W01/SAT/answer-key/C2_W01_SAT_item_analysis_TRAINER.xlsx
+++ b/content/W01/SAT/answer-key/C2_W01_SAT_item_analysis_TRAINER.xlsx
@@ -13,6 +13,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Discussion" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tags" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Seats" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ratings" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -21,7 +22,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0"/>
+  </numFmts>
   <fonts count="4">
     <font>
       <name val="Calibri"/>
@@ -69,7 +72,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -81,6 +84,7 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -9506,4 +9510,1508 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N48"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="44" customWidth="1" min="1" max="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>Step one: each part's rating beside its score</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Type each seat's ratings, 1 to 4, from the answer sheet; the rates on the right are computed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E3" t="n">
+        <v>4</v>
+      </c>
+      <c r="F3" t="n">
+        <v>5</v>
+      </c>
+      <c r="G3" t="n">
+        <v>6</v>
+      </c>
+      <c r="I3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J3" t="n">
+        <v>2</v>
+      </c>
+      <c r="K3" t="n">
+        <v>3</v>
+      </c>
+      <c r="L3" t="n">
+        <v>4</v>
+      </c>
+      <c r="M3" t="n">
+        <v>5</v>
+      </c>
+      <c r="N3" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>Seat</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>Rating, part 1</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>Rating, part 2</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>Rating, part 3</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>Rating, part 4</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>Rating, part 5</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>Rating, part 6</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr">
+        <is>
+          <t>Right rate, part 1</t>
+        </is>
+      </c>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>Right rate, part 2</t>
+        </is>
+      </c>
+      <c r="K4" s="4" t="inlineStr">
+        <is>
+          <t>Right rate, part 3</t>
+        </is>
+      </c>
+      <c r="L4" s="4" t="inlineStr">
+        <is>
+          <t>Right rate, part 4</t>
+        </is>
+      </c>
+      <c r="M4" s="4" t="inlineStr">
+        <is>
+          <t>Right rate, part 5</t>
+        </is>
+      </c>
+      <c r="N4" s="4" t="inlineStr">
+        <is>
+          <t>Right rate, part 6</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="5" t="n"/>
+      <c r="C5" s="5" t="n"/>
+      <c r="D5" s="5" t="n"/>
+      <c r="E5" s="5" t="n"/>
+      <c r="F5" s="5" t="n"/>
+      <c r="G5" s="5" t="n"/>
+      <c r="I5" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=I$3)*ISNUMBER(Marks!$B$5:$BC$5))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=I$3)*(Marks!$B$5:$BC$5=1))/SUMPRODUCT((Marks!$B$2:$BC$2=I$3)*ISNUMBER(Marks!$B$5:$BC$5)))</f>
+        <v/>
+      </c>
+      <c r="J5" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=J$3)*ISNUMBER(Marks!$B$5:$BC$5))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=J$3)*(Marks!$B$5:$BC$5=1))/SUMPRODUCT((Marks!$B$2:$BC$2=J$3)*ISNUMBER(Marks!$B$5:$BC$5)))</f>
+        <v/>
+      </c>
+      <c r="K5" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=K$3)*ISNUMBER(Marks!$B$5:$BC$5))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=K$3)*(Marks!$B$5:$BC$5=1))/SUMPRODUCT((Marks!$B$2:$BC$2=K$3)*ISNUMBER(Marks!$B$5:$BC$5)))</f>
+        <v/>
+      </c>
+      <c r="L5" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=L$3)*ISNUMBER(Marks!$B$5:$BC$5))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=L$3)*(Marks!$B$5:$BC$5=1))/SUMPRODUCT((Marks!$B$2:$BC$2=L$3)*ISNUMBER(Marks!$B$5:$BC$5)))</f>
+        <v/>
+      </c>
+      <c r="M5" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=M$3)*ISNUMBER(Marks!$B$5:$BC$5))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=M$3)*(Marks!$B$5:$BC$5=1))/SUMPRODUCT((Marks!$B$2:$BC$2=M$3)*ISNUMBER(Marks!$B$5:$BC$5)))</f>
+        <v/>
+      </c>
+      <c r="N5" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=N$3)*ISNUMBER(Marks!$B$5:$BC$5))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=N$3)*(Marks!$B$5:$BC$5=1))/SUMPRODUCT((Marks!$B$2:$BC$2=N$3)*ISNUMBER(Marks!$B$5:$BC$5)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="5" t="n"/>
+      <c r="C6" s="5" t="n"/>
+      <c r="D6" s="5" t="n"/>
+      <c r="E6" s="5" t="n"/>
+      <c r="F6" s="5" t="n"/>
+      <c r="G6" s="5" t="n"/>
+      <c r="I6" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=I$3)*ISNUMBER(Marks!$B$6:$BC$6))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=I$3)*(Marks!$B$6:$BC$6=1))/SUMPRODUCT((Marks!$B$2:$BC$2=I$3)*ISNUMBER(Marks!$B$6:$BC$6)))</f>
+        <v/>
+      </c>
+      <c r="J6" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=J$3)*ISNUMBER(Marks!$B$6:$BC$6))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=J$3)*(Marks!$B$6:$BC$6=1))/SUMPRODUCT((Marks!$B$2:$BC$2=J$3)*ISNUMBER(Marks!$B$6:$BC$6)))</f>
+        <v/>
+      </c>
+      <c r="K6" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=K$3)*ISNUMBER(Marks!$B$6:$BC$6))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=K$3)*(Marks!$B$6:$BC$6=1))/SUMPRODUCT((Marks!$B$2:$BC$2=K$3)*ISNUMBER(Marks!$B$6:$BC$6)))</f>
+        <v/>
+      </c>
+      <c r="L6" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=L$3)*ISNUMBER(Marks!$B$6:$BC$6))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=L$3)*(Marks!$B$6:$BC$6=1))/SUMPRODUCT((Marks!$B$2:$BC$2=L$3)*ISNUMBER(Marks!$B$6:$BC$6)))</f>
+        <v/>
+      </c>
+      <c r="M6" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=M$3)*ISNUMBER(Marks!$B$6:$BC$6))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=M$3)*(Marks!$B$6:$BC$6=1))/SUMPRODUCT((Marks!$B$2:$BC$2=M$3)*ISNUMBER(Marks!$B$6:$BC$6)))</f>
+        <v/>
+      </c>
+      <c r="N6" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=N$3)*ISNUMBER(Marks!$B$6:$BC$6))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=N$3)*(Marks!$B$6:$BC$6=1))/SUMPRODUCT((Marks!$B$2:$BC$2=N$3)*ISNUMBER(Marks!$B$6:$BC$6)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" s="5" t="n"/>
+      <c r="C7" s="5" t="n"/>
+      <c r="D7" s="5" t="n"/>
+      <c r="E7" s="5" t="n"/>
+      <c r="F7" s="5" t="n"/>
+      <c r="G7" s="5" t="n"/>
+      <c r="I7" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=I$3)*ISNUMBER(Marks!$B$7:$BC$7))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=I$3)*(Marks!$B$7:$BC$7=1))/SUMPRODUCT((Marks!$B$2:$BC$2=I$3)*ISNUMBER(Marks!$B$7:$BC$7)))</f>
+        <v/>
+      </c>
+      <c r="J7" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=J$3)*ISNUMBER(Marks!$B$7:$BC$7))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=J$3)*(Marks!$B$7:$BC$7=1))/SUMPRODUCT((Marks!$B$2:$BC$2=J$3)*ISNUMBER(Marks!$B$7:$BC$7)))</f>
+        <v/>
+      </c>
+      <c r="K7" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=K$3)*ISNUMBER(Marks!$B$7:$BC$7))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=K$3)*(Marks!$B$7:$BC$7=1))/SUMPRODUCT((Marks!$B$2:$BC$2=K$3)*ISNUMBER(Marks!$B$7:$BC$7)))</f>
+        <v/>
+      </c>
+      <c r="L7" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=L$3)*ISNUMBER(Marks!$B$7:$BC$7))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=L$3)*(Marks!$B$7:$BC$7=1))/SUMPRODUCT((Marks!$B$2:$BC$2=L$3)*ISNUMBER(Marks!$B$7:$BC$7)))</f>
+        <v/>
+      </c>
+      <c r="M7" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=M$3)*ISNUMBER(Marks!$B$7:$BC$7))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=M$3)*(Marks!$B$7:$BC$7=1))/SUMPRODUCT((Marks!$B$2:$BC$2=M$3)*ISNUMBER(Marks!$B$7:$BC$7)))</f>
+        <v/>
+      </c>
+      <c r="N7" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=N$3)*ISNUMBER(Marks!$B$7:$BC$7))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=N$3)*(Marks!$B$7:$BC$7=1))/SUMPRODUCT((Marks!$B$2:$BC$2=N$3)*ISNUMBER(Marks!$B$7:$BC$7)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" s="5" t="n"/>
+      <c r="C8" s="5" t="n"/>
+      <c r="D8" s="5" t="n"/>
+      <c r="E8" s="5" t="n"/>
+      <c r="F8" s="5" t="n"/>
+      <c r="G8" s="5" t="n"/>
+      <c r="I8" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=I$3)*ISNUMBER(Marks!$B$8:$BC$8))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=I$3)*(Marks!$B$8:$BC$8=1))/SUMPRODUCT((Marks!$B$2:$BC$2=I$3)*ISNUMBER(Marks!$B$8:$BC$8)))</f>
+        <v/>
+      </c>
+      <c r="J8" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=J$3)*ISNUMBER(Marks!$B$8:$BC$8))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=J$3)*(Marks!$B$8:$BC$8=1))/SUMPRODUCT((Marks!$B$2:$BC$2=J$3)*ISNUMBER(Marks!$B$8:$BC$8)))</f>
+        <v/>
+      </c>
+      <c r="K8" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=K$3)*ISNUMBER(Marks!$B$8:$BC$8))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=K$3)*(Marks!$B$8:$BC$8=1))/SUMPRODUCT((Marks!$B$2:$BC$2=K$3)*ISNUMBER(Marks!$B$8:$BC$8)))</f>
+        <v/>
+      </c>
+      <c r="L8" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=L$3)*ISNUMBER(Marks!$B$8:$BC$8))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=L$3)*(Marks!$B$8:$BC$8=1))/SUMPRODUCT((Marks!$B$2:$BC$2=L$3)*ISNUMBER(Marks!$B$8:$BC$8)))</f>
+        <v/>
+      </c>
+      <c r="M8" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=M$3)*ISNUMBER(Marks!$B$8:$BC$8))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=M$3)*(Marks!$B$8:$BC$8=1))/SUMPRODUCT((Marks!$B$2:$BC$2=M$3)*ISNUMBER(Marks!$B$8:$BC$8)))</f>
+        <v/>
+      </c>
+      <c r="N8" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=N$3)*ISNUMBER(Marks!$B$8:$BC$8))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=N$3)*(Marks!$B$8:$BC$8=1))/SUMPRODUCT((Marks!$B$2:$BC$2=N$3)*ISNUMBER(Marks!$B$8:$BC$8)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>5</v>
+      </c>
+      <c r="B9" s="5" t="n"/>
+      <c r="C9" s="5" t="n"/>
+      <c r="D9" s="5" t="n"/>
+      <c r="E9" s="5" t="n"/>
+      <c r="F9" s="5" t="n"/>
+      <c r="G9" s="5" t="n"/>
+      <c r="I9" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=I$3)*ISNUMBER(Marks!$B$9:$BC$9))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=I$3)*(Marks!$B$9:$BC$9=1))/SUMPRODUCT((Marks!$B$2:$BC$2=I$3)*ISNUMBER(Marks!$B$9:$BC$9)))</f>
+        <v/>
+      </c>
+      <c r="J9" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=J$3)*ISNUMBER(Marks!$B$9:$BC$9))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=J$3)*(Marks!$B$9:$BC$9=1))/SUMPRODUCT((Marks!$B$2:$BC$2=J$3)*ISNUMBER(Marks!$B$9:$BC$9)))</f>
+        <v/>
+      </c>
+      <c r="K9" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=K$3)*ISNUMBER(Marks!$B$9:$BC$9))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=K$3)*(Marks!$B$9:$BC$9=1))/SUMPRODUCT((Marks!$B$2:$BC$2=K$3)*ISNUMBER(Marks!$B$9:$BC$9)))</f>
+        <v/>
+      </c>
+      <c r="L9" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=L$3)*ISNUMBER(Marks!$B$9:$BC$9))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=L$3)*(Marks!$B$9:$BC$9=1))/SUMPRODUCT((Marks!$B$2:$BC$2=L$3)*ISNUMBER(Marks!$B$9:$BC$9)))</f>
+        <v/>
+      </c>
+      <c r="M9" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=M$3)*ISNUMBER(Marks!$B$9:$BC$9))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=M$3)*(Marks!$B$9:$BC$9=1))/SUMPRODUCT((Marks!$B$2:$BC$2=M$3)*ISNUMBER(Marks!$B$9:$BC$9)))</f>
+        <v/>
+      </c>
+      <c r="N9" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=N$3)*ISNUMBER(Marks!$B$9:$BC$9))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=N$3)*(Marks!$B$9:$BC$9=1))/SUMPRODUCT((Marks!$B$2:$BC$2=N$3)*ISNUMBER(Marks!$B$9:$BC$9)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>6</v>
+      </c>
+      <c r="B10" s="5" t="n"/>
+      <c r="C10" s="5" t="n"/>
+      <c r="D10" s="5" t="n"/>
+      <c r="E10" s="5" t="n"/>
+      <c r="F10" s="5" t="n"/>
+      <c r="G10" s="5" t="n"/>
+      <c r="I10" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=I$3)*ISNUMBER(Marks!$B$10:$BC$10))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=I$3)*(Marks!$B$10:$BC$10=1))/SUMPRODUCT((Marks!$B$2:$BC$2=I$3)*ISNUMBER(Marks!$B$10:$BC$10)))</f>
+        <v/>
+      </c>
+      <c r="J10" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=J$3)*ISNUMBER(Marks!$B$10:$BC$10))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=J$3)*(Marks!$B$10:$BC$10=1))/SUMPRODUCT((Marks!$B$2:$BC$2=J$3)*ISNUMBER(Marks!$B$10:$BC$10)))</f>
+        <v/>
+      </c>
+      <c r="K10" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=K$3)*ISNUMBER(Marks!$B$10:$BC$10))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=K$3)*(Marks!$B$10:$BC$10=1))/SUMPRODUCT((Marks!$B$2:$BC$2=K$3)*ISNUMBER(Marks!$B$10:$BC$10)))</f>
+        <v/>
+      </c>
+      <c r="L10" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=L$3)*ISNUMBER(Marks!$B$10:$BC$10))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=L$3)*(Marks!$B$10:$BC$10=1))/SUMPRODUCT((Marks!$B$2:$BC$2=L$3)*ISNUMBER(Marks!$B$10:$BC$10)))</f>
+        <v/>
+      </c>
+      <c r="M10" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=M$3)*ISNUMBER(Marks!$B$10:$BC$10))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=M$3)*(Marks!$B$10:$BC$10=1))/SUMPRODUCT((Marks!$B$2:$BC$2=M$3)*ISNUMBER(Marks!$B$10:$BC$10)))</f>
+        <v/>
+      </c>
+      <c r="N10" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=N$3)*ISNUMBER(Marks!$B$10:$BC$10))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=N$3)*(Marks!$B$10:$BC$10=1))/SUMPRODUCT((Marks!$B$2:$BC$2=N$3)*ISNUMBER(Marks!$B$10:$BC$10)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>7</v>
+      </c>
+      <c r="B11" s="5" t="n"/>
+      <c r="C11" s="5" t="n"/>
+      <c r="D11" s="5" t="n"/>
+      <c r="E11" s="5" t="n"/>
+      <c r="F11" s="5" t="n"/>
+      <c r="G11" s="5" t="n"/>
+      <c r="I11" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=I$3)*ISNUMBER(Marks!$B$11:$BC$11))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=I$3)*(Marks!$B$11:$BC$11=1))/SUMPRODUCT((Marks!$B$2:$BC$2=I$3)*ISNUMBER(Marks!$B$11:$BC$11)))</f>
+        <v/>
+      </c>
+      <c r="J11" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=J$3)*ISNUMBER(Marks!$B$11:$BC$11))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=J$3)*(Marks!$B$11:$BC$11=1))/SUMPRODUCT((Marks!$B$2:$BC$2=J$3)*ISNUMBER(Marks!$B$11:$BC$11)))</f>
+        <v/>
+      </c>
+      <c r="K11" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=K$3)*ISNUMBER(Marks!$B$11:$BC$11))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=K$3)*(Marks!$B$11:$BC$11=1))/SUMPRODUCT((Marks!$B$2:$BC$2=K$3)*ISNUMBER(Marks!$B$11:$BC$11)))</f>
+        <v/>
+      </c>
+      <c r="L11" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=L$3)*ISNUMBER(Marks!$B$11:$BC$11))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=L$3)*(Marks!$B$11:$BC$11=1))/SUMPRODUCT((Marks!$B$2:$BC$2=L$3)*ISNUMBER(Marks!$B$11:$BC$11)))</f>
+        <v/>
+      </c>
+      <c r="M11" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=M$3)*ISNUMBER(Marks!$B$11:$BC$11))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=M$3)*(Marks!$B$11:$BC$11=1))/SUMPRODUCT((Marks!$B$2:$BC$2=M$3)*ISNUMBER(Marks!$B$11:$BC$11)))</f>
+        <v/>
+      </c>
+      <c r="N11" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=N$3)*ISNUMBER(Marks!$B$11:$BC$11))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=N$3)*(Marks!$B$11:$BC$11=1))/SUMPRODUCT((Marks!$B$2:$BC$2=N$3)*ISNUMBER(Marks!$B$11:$BC$11)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>8</v>
+      </c>
+      <c r="B12" s="5" t="n"/>
+      <c r="C12" s="5" t="n"/>
+      <c r="D12" s="5" t="n"/>
+      <c r="E12" s="5" t="n"/>
+      <c r="F12" s="5" t="n"/>
+      <c r="G12" s="5" t="n"/>
+      <c r="I12" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=I$3)*ISNUMBER(Marks!$B$12:$BC$12))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=I$3)*(Marks!$B$12:$BC$12=1))/SUMPRODUCT((Marks!$B$2:$BC$2=I$3)*ISNUMBER(Marks!$B$12:$BC$12)))</f>
+        <v/>
+      </c>
+      <c r="J12" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=J$3)*ISNUMBER(Marks!$B$12:$BC$12))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=J$3)*(Marks!$B$12:$BC$12=1))/SUMPRODUCT((Marks!$B$2:$BC$2=J$3)*ISNUMBER(Marks!$B$12:$BC$12)))</f>
+        <v/>
+      </c>
+      <c r="K12" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=K$3)*ISNUMBER(Marks!$B$12:$BC$12))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=K$3)*(Marks!$B$12:$BC$12=1))/SUMPRODUCT((Marks!$B$2:$BC$2=K$3)*ISNUMBER(Marks!$B$12:$BC$12)))</f>
+        <v/>
+      </c>
+      <c r="L12" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=L$3)*ISNUMBER(Marks!$B$12:$BC$12))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=L$3)*(Marks!$B$12:$BC$12=1))/SUMPRODUCT((Marks!$B$2:$BC$2=L$3)*ISNUMBER(Marks!$B$12:$BC$12)))</f>
+        <v/>
+      </c>
+      <c r="M12" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=M$3)*ISNUMBER(Marks!$B$12:$BC$12))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=M$3)*(Marks!$B$12:$BC$12=1))/SUMPRODUCT((Marks!$B$2:$BC$2=M$3)*ISNUMBER(Marks!$B$12:$BC$12)))</f>
+        <v/>
+      </c>
+      <c r="N12" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=N$3)*ISNUMBER(Marks!$B$12:$BC$12))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=N$3)*(Marks!$B$12:$BC$12=1))/SUMPRODUCT((Marks!$B$2:$BC$2=N$3)*ISNUMBER(Marks!$B$12:$BC$12)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>9</v>
+      </c>
+      <c r="B13" s="5" t="n"/>
+      <c r="C13" s="5" t="n"/>
+      <c r="D13" s="5" t="n"/>
+      <c r="E13" s="5" t="n"/>
+      <c r="F13" s="5" t="n"/>
+      <c r="G13" s="5" t="n"/>
+      <c r="I13" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=I$3)*ISNUMBER(Marks!$B$13:$BC$13))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=I$3)*(Marks!$B$13:$BC$13=1))/SUMPRODUCT((Marks!$B$2:$BC$2=I$3)*ISNUMBER(Marks!$B$13:$BC$13)))</f>
+        <v/>
+      </c>
+      <c r="J13" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=J$3)*ISNUMBER(Marks!$B$13:$BC$13))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=J$3)*(Marks!$B$13:$BC$13=1))/SUMPRODUCT((Marks!$B$2:$BC$2=J$3)*ISNUMBER(Marks!$B$13:$BC$13)))</f>
+        <v/>
+      </c>
+      <c r="K13" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=K$3)*ISNUMBER(Marks!$B$13:$BC$13))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=K$3)*(Marks!$B$13:$BC$13=1))/SUMPRODUCT((Marks!$B$2:$BC$2=K$3)*ISNUMBER(Marks!$B$13:$BC$13)))</f>
+        <v/>
+      </c>
+      <c r="L13" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=L$3)*ISNUMBER(Marks!$B$13:$BC$13))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=L$3)*(Marks!$B$13:$BC$13=1))/SUMPRODUCT((Marks!$B$2:$BC$2=L$3)*ISNUMBER(Marks!$B$13:$BC$13)))</f>
+        <v/>
+      </c>
+      <c r="M13" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=M$3)*ISNUMBER(Marks!$B$13:$BC$13))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=M$3)*(Marks!$B$13:$BC$13=1))/SUMPRODUCT((Marks!$B$2:$BC$2=M$3)*ISNUMBER(Marks!$B$13:$BC$13)))</f>
+        <v/>
+      </c>
+      <c r="N13" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=N$3)*ISNUMBER(Marks!$B$13:$BC$13))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=N$3)*(Marks!$B$13:$BC$13=1))/SUMPRODUCT((Marks!$B$2:$BC$2=N$3)*ISNUMBER(Marks!$B$13:$BC$13)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>10</v>
+      </c>
+      <c r="B14" s="5" t="n"/>
+      <c r="C14" s="5" t="n"/>
+      <c r="D14" s="5" t="n"/>
+      <c r="E14" s="5" t="n"/>
+      <c r="F14" s="5" t="n"/>
+      <c r="G14" s="5" t="n"/>
+      <c r="I14" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=I$3)*ISNUMBER(Marks!$B$14:$BC$14))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=I$3)*(Marks!$B$14:$BC$14=1))/SUMPRODUCT((Marks!$B$2:$BC$2=I$3)*ISNUMBER(Marks!$B$14:$BC$14)))</f>
+        <v/>
+      </c>
+      <c r="J14" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=J$3)*ISNUMBER(Marks!$B$14:$BC$14))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=J$3)*(Marks!$B$14:$BC$14=1))/SUMPRODUCT((Marks!$B$2:$BC$2=J$3)*ISNUMBER(Marks!$B$14:$BC$14)))</f>
+        <v/>
+      </c>
+      <c r="K14" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=K$3)*ISNUMBER(Marks!$B$14:$BC$14))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=K$3)*(Marks!$B$14:$BC$14=1))/SUMPRODUCT((Marks!$B$2:$BC$2=K$3)*ISNUMBER(Marks!$B$14:$BC$14)))</f>
+        <v/>
+      </c>
+      <c r="L14" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=L$3)*ISNUMBER(Marks!$B$14:$BC$14))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=L$3)*(Marks!$B$14:$BC$14=1))/SUMPRODUCT((Marks!$B$2:$BC$2=L$3)*ISNUMBER(Marks!$B$14:$BC$14)))</f>
+        <v/>
+      </c>
+      <c r="M14" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=M$3)*ISNUMBER(Marks!$B$14:$BC$14))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=M$3)*(Marks!$B$14:$BC$14=1))/SUMPRODUCT((Marks!$B$2:$BC$2=M$3)*ISNUMBER(Marks!$B$14:$BC$14)))</f>
+        <v/>
+      </c>
+      <c r="N14" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=N$3)*ISNUMBER(Marks!$B$14:$BC$14))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=N$3)*(Marks!$B$14:$BC$14=1))/SUMPRODUCT((Marks!$B$2:$BC$2=N$3)*ISNUMBER(Marks!$B$14:$BC$14)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>11</v>
+      </c>
+      <c r="B15" s="5" t="n"/>
+      <c r="C15" s="5" t="n"/>
+      <c r="D15" s="5" t="n"/>
+      <c r="E15" s="5" t="n"/>
+      <c r="F15" s="5" t="n"/>
+      <c r="G15" s="5" t="n"/>
+      <c r="I15" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=I$3)*ISNUMBER(Marks!$B$15:$BC$15))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=I$3)*(Marks!$B$15:$BC$15=1))/SUMPRODUCT((Marks!$B$2:$BC$2=I$3)*ISNUMBER(Marks!$B$15:$BC$15)))</f>
+        <v/>
+      </c>
+      <c r="J15" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=J$3)*ISNUMBER(Marks!$B$15:$BC$15))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=J$3)*(Marks!$B$15:$BC$15=1))/SUMPRODUCT((Marks!$B$2:$BC$2=J$3)*ISNUMBER(Marks!$B$15:$BC$15)))</f>
+        <v/>
+      </c>
+      <c r="K15" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=K$3)*ISNUMBER(Marks!$B$15:$BC$15))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=K$3)*(Marks!$B$15:$BC$15=1))/SUMPRODUCT((Marks!$B$2:$BC$2=K$3)*ISNUMBER(Marks!$B$15:$BC$15)))</f>
+        <v/>
+      </c>
+      <c r="L15" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=L$3)*ISNUMBER(Marks!$B$15:$BC$15))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=L$3)*(Marks!$B$15:$BC$15=1))/SUMPRODUCT((Marks!$B$2:$BC$2=L$3)*ISNUMBER(Marks!$B$15:$BC$15)))</f>
+        <v/>
+      </c>
+      <c r="M15" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=M$3)*ISNUMBER(Marks!$B$15:$BC$15))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=M$3)*(Marks!$B$15:$BC$15=1))/SUMPRODUCT((Marks!$B$2:$BC$2=M$3)*ISNUMBER(Marks!$B$15:$BC$15)))</f>
+        <v/>
+      </c>
+      <c r="N15" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=N$3)*ISNUMBER(Marks!$B$15:$BC$15))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=N$3)*(Marks!$B$15:$BC$15=1))/SUMPRODUCT((Marks!$B$2:$BC$2=N$3)*ISNUMBER(Marks!$B$15:$BC$15)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>12</v>
+      </c>
+      <c r="B16" s="5" t="n"/>
+      <c r="C16" s="5" t="n"/>
+      <c r="D16" s="5" t="n"/>
+      <c r="E16" s="5" t="n"/>
+      <c r="F16" s="5" t="n"/>
+      <c r="G16" s="5" t="n"/>
+      <c r="I16" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=I$3)*ISNUMBER(Marks!$B$16:$BC$16))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=I$3)*(Marks!$B$16:$BC$16=1))/SUMPRODUCT((Marks!$B$2:$BC$2=I$3)*ISNUMBER(Marks!$B$16:$BC$16)))</f>
+        <v/>
+      </c>
+      <c r="J16" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=J$3)*ISNUMBER(Marks!$B$16:$BC$16))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=J$3)*(Marks!$B$16:$BC$16=1))/SUMPRODUCT((Marks!$B$2:$BC$2=J$3)*ISNUMBER(Marks!$B$16:$BC$16)))</f>
+        <v/>
+      </c>
+      <c r="K16" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=K$3)*ISNUMBER(Marks!$B$16:$BC$16))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=K$3)*(Marks!$B$16:$BC$16=1))/SUMPRODUCT((Marks!$B$2:$BC$2=K$3)*ISNUMBER(Marks!$B$16:$BC$16)))</f>
+        <v/>
+      </c>
+      <c r="L16" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=L$3)*ISNUMBER(Marks!$B$16:$BC$16))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=L$3)*(Marks!$B$16:$BC$16=1))/SUMPRODUCT((Marks!$B$2:$BC$2=L$3)*ISNUMBER(Marks!$B$16:$BC$16)))</f>
+        <v/>
+      </c>
+      <c r="M16" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=M$3)*ISNUMBER(Marks!$B$16:$BC$16))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=M$3)*(Marks!$B$16:$BC$16=1))/SUMPRODUCT((Marks!$B$2:$BC$2=M$3)*ISNUMBER(Marks!$B$16:$BC$16)))</f>
+        <v/>
+      </c>
+      <c r="N16" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=N$3)*ISNUMBER(Marks!$B$16:$BC$16))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=N$3)*(Marks!$B$16:$BC$16=1))/SUMPRODUCT((Marks!$B$2:$BC$2=N$3)*ISNUMBER(Marks!$B$16:$BC$16)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>13</v>
+      </c>
+      <c r="B17" s="5" t="n"/>
+      <c r="C17" s="5" t="n"/>
+      <c r="D17" s="5" t="n"/>
+      <c r="E17" s="5" t="n"/>
+      <c r="F17" s="5" t="n"/>
+      <c r="G17" s="5" t="n"/>
+      <c r="I17" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=I$3)*ISNUMBER(Marks!$B$17:$BC$17))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=I$3)*(Marks!$B$17:$BC$17=1))/SUMPRODUCT((Marks!$B$2:$BC$2=I$3)*ISNUMBER(Marks!$B$17:$BC$17)))</f>
+        <v/>
+      </c>
+      <c r="J17" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=J$3)*ISNUMBER(Marks!$B$17:$BC$17))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=J$3)*(Marks!$B$17:$BC$17=1))/SUMPRODUCT((Marks!$B$2:$BC$2=J$3)*ISNUMBER(Marks!$B$17:$BC$17)))</f>
+        <v/>
+      </c>
+      <c r="K17" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=K$3)*ISNUMBER(Marks!$B$17:$BC$17))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=K$3)*(Marks!$B$17:$BC$17=1))/SUMPRODUCT((Marks!$B$2:$BC$2=K$3)*ISNUMBER(Marks!$B$17:$BC$17)))</f>
+        <v/>
+      </c>
+      <c r="L17" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=L$3)*ISNUMBER(Marks!$B$17:$BC$17))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=L$3)*(Marks!$B$17:$BC$17=1))/SUMPRODUCT((Marks!$B$2:$BC$2=L$3)*ISNUMBER(Marks!$B$17:$BC$17)))</f>
+        <v/>
+      </c>
+      <c r="M17" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=M$3)*ISNUMBER(Marks!$B$17:$BC$17))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=M$3)*(Marks!$B$17:$BC$17=1))/SUMPRODUCT((Marks!$B$2:$BC$2=M$3)*ISNUMBER(Marks!$B$17:$BC$17)))</f>
+        <v/>
+      </c>
+      <c r="N17" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=N$3)*ISNUMBER(Marks!$B$17:$BC$17))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=N$3)*(Marks!$B$17:$BC$17=1))/SUMPRODUCT((Marks!$B$2:$BC$2=N$3)*ISNUMBER(Marks!$B$17:$BC$17)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>14</v>
+      </c>
+      <c r="B18" s="5" t="n"/>
+      <c r="C18" s="5" t="n"/>
+      <c r="D18" s="5" t="n"/>
+      <c r="E18" s="5" t="n"/>
+      <c r="F18" s="5" t="n"/>
+      <c r="G18" s="5" t="n"/>
+      <c r="I18" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=I$3)*ISNUMBER(Marks!$B$18:$BC$18))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=I$3)*(Marks!$B$18:$BC$18=1))/SUMPRODUCT((Marks!$B$2:$BC$2=I$3)*ISNUMBER(Marks!$B$18:$BC$18)))</f>
+        <v/>
+      </c>
+      <c r="J18" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=J$3)*ISNUMBER(Marks!$B$18:$BC$18))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=J$3)*(Marks!$B$18:$BC$18=1))/SUMPRODUCT((Marks!$B$2:$BC$2=J$3)*ISNUMBER(Marks!$B$18:$BC$18)))</f>
+        <v/>
+      </c>
+      <c r="K18" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=K$3)*ISNUMBER(Marks!$B$18:$BC$18))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=K$3)*(Marks!$B$18:$BC$18=1))/SUMPRODUCT((Marks!$B$2:$BC$2=K$3)*ISNUMBER(Marks!$B$18:$BC$18)))</f>
+        <v/>
+      </c>
+      <c r="L18" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=L$3)*ISNUMBER(Marks!$B$18:$BC$18))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=L$3)*(Marks!$B$18:$BC$18=1))/SUMPRODUCT((Marks!$B$2:$BC$2=L$3)*ISNUMBER(Marks!$B$18:$BC$18)))</f>
+        <v/>
+      </c>
+      <c r="M18" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=M$3)*ISNUMBER(Marks!$B$18:$BC$18))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=M$3)*(Marks!$B$18:$BC$18=1))/SUMPRODUCT((Marks!$B$2:$BC$2=M$3)*ISNUMBER(Marks!$B$18:$BC$18)))</f>
+        <v/>
+      </c>
+      <c r="N18" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=N$3)*ISNUMBER(Marks!$B$18:$BC$18))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=N$3)*(Marks!$B$18:$BC$18=1))/SUMPRODUCT((Marks!$B$2:$BC$2=N$3)*ISNUMBER(Marks!$B$18:$BC$18)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>15</v>
+      </c>
+      <c r="B19" s="5" t="n"/>
+      <c r="C19" s="5" t="n"/>
+      <c r="D19" s="5" t="n"/>
+      <c r="E19" s="5" t="n"/>
+      <c r="F19" s="5" t="n"/>
+      <c r="G19" s="5" t="n"/>
+      <c r="I19" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=I$3)*ISNUMBER(Marks!$B$19:$BC$19))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=I$3)*(Marks!$B$19:$BC$19=1))/SUMPRODUCT((Marks!$B$2:$BC$2=I$3)*ISNUMBER(Marks!$B$19:$BC$19)))</f>
+        <v/>
+      </c>
+      <c r="J19" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=J$3)*ISNUMBER(Marks!$B$19:$BC$19))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=J$3)*(Marks!$B$19:$BC$19=1))/SUMPRODUCT((Marks!$B$2:$BC$2=J$3)*ISNUMBER(Marks!$B$19:$BC$19)))</f>
+        <v/>
+      </c>
+      <c r="K19" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=K$3)*ISNUMBER(Marks!$B$19:$BC$19))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=K$3)*(Marks!$B$19:$BC$19=1))/SUMPRODUCT((Marks!$B$2:$BC$2=K$3)*ISNUMBER(Marks!$B$19:$BC$19)))</f>
+        <v/>
+      </c>
+      <c r="L19" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=L$3)*ISNUMBER(Marks!$B$19:$BC$19))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=L$3)*(Marks!$B$19:$BC$19=1))/SUMPRODUCT((Marks!$B$2:$BC$2=L$3)*ISNUMBER(Marks!$B$19:$BC$19)))</f>
+        <v/>
+      </c>
+      <c r="M19" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=M$3)*ISNUMBER(Marks!$B$19:$BC$19))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=M$3)*(Marks!$B$19:$BC$19=1))/SUMPRODUCT((Marks!$B$2:$BC$2=M$3)*ISNUMBER(Marks!$B$19:$BC$19)))</f>
+        <v/>
+      </c>
+      <c r="N19" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=N$3)*ISNUMBER(Marks!$B$19:$BC$19))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=N$3)*(Marks!$B$19:$BC$19=1))/SUMPRODUCT((Marks!$B$2:$BC$2=N$3)*ISNUMBER(Marks!$B$19:$BC$19)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>16</v>
+      </c>
+      <c r="B20" s="5" t="n"/>
+      <c r="C20" s="5" t="n"/>
+      <c r="D20" s="5" t="n"/>
+      <c r="E20" s="5" t="n"/>
+      <c r="F20" s="5" t="n"/>
+      <c r="G20" s="5" t="n"/>
+      <c r="I20" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=I$3)*ISNUMBER(Marks!$B$20:$BC$20))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=I$3)*(Marks!$B$20:$BC$20=1))/SUMPRODUCT((Marks!$B$2:$BC$2=I$3)*ISNUMBER(Marks!$B$20:$BC$20)))</f>
+        <v/>
+      </c>
+      <c r="J20" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=J$3)*ISNUMBER(Marks!$B$20:$BC$20))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=J$3)*(Marks!$B$20:$BC$20=1))/SUMPRODUCT((Marks!$B$2:$BC$2=J$3)*ISNUMBER(Marks!$B$20:$BC$20)))</f>
+        <v/>
+      </c>
+      <c r="K20" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=K$3)*ISNUMBER(Marks!$B$20:$BC$20))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=K$3)*(Marks!$B$20:$BC$20=1))/SUMPRODUCT((Marks!$B$2:$BC$2=K$3)*ISNUMBER(Marks!$B$20:$BC$20)))</f>
+        <v/>
+      </c>
+      <c r="L20" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=L$3)*ISNUMBER(Marks!$B$20:$BC$20))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=L$3)*(Marks!$B$20:$BC$20=1))/SUMPRODUCT((Marks!$B$2:$BC$2=L$3)*ISNUMBER(Marks!$B$20:$BC$20)))</f>
+        <v/>
+      </c>
+      <c r="M20" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=M$3)*ISNUMBER(Marks!$B$20:$BC$20))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=M$3)*(Marks!$B$20:$BC$20=1))/SUMPRODUCT((Marks!$B$2:$BC$2=M$3)*ISNUMBER(Marks!$B$20:$BC$20)))</f>
+        <v/>
+      </c>
+      <c r="N20" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=N$3)*ISNUMBER(Marks!$B$20:$BC$20))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=N$3)*(Marks!$B$20:$BC$20=1))/SUMPRODUCT((Marks!$B$2:$BC$2=N$3)*ISNUMBER(Marks!$B$20:$BC$20)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>17</v>
+      </c>
+      <c r="B21" s="5" t="n"/>
+      <c r="C21" s="5" t="n"/>
+      <c r="D21" s="5" t="n"/>
+      <c r="E21" s="5" t="n"/>
+      <c r="F21" s="5" t="n"/>
+      <c r="G21" s="5" t="n"/>
+      <c r="I21" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=I$3)*ISNUMBER(Marks!$B$21:$BC$21))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=I$3)*(Marks!$B$21:$BC$21=1))/SUMPRODUCT((Marks!$B$2:$BC$2=I$3)*ISNUMBER(Marks!$B$21:$BC$21)))</f>
+        <v/>
+      </c>
+      <c r="J21" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=J$3)*ISNUMBER(Marks!$B$21:$BC$21))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=J$3)*(Marks!$B$21:$BC$21=1))/SUMPRODUCT((Marks!$B$2:$BC$2=J$3)*ISNUMBER(Marks!$B$21:$BC$21)))</f>
+        <v/>
+      </c>
+      <c r="K21" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=K$3)*ISNUMBER(Marks!$B$21:$BC$21))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=K$3)*(Marks!$B$21:$BC$21=1))/SUMPRODUCT((Marks!$B$2:$BC$2=K$3)*ISNUMBER(Marks!$B$21:$BC$21)))</f>
+        <v/>
+      </c>
+      <c r="L21" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=L$3)*ISNUMBER(Marks!$B$21:$BC$21))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=L$3)*(Marks!$B$21:$BC$21=1))/SUMPRODUCT((Marks!$B$2:$BC$2=L$3)*ISNUMBER(Marks!$B$21:$BC$21)))</f>
+        <v/>
+      </c>
+      <c r="M21" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=M$3)*ISNUMBER(Marks!$B$21:$BC$21))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=M$3)*(Marks!$B$21:$BC$21=1))/SUMPRODUCT((Marks!$B$2:$BC$2=M$3)*ISNUMBER(Marks!$B$21:$BC$21)))</f>
+        <v/>
+      </c>
+      <c r="N21" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=N$3)*ISNUMBER(Marks!$B$21:$BC$21))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=N$3)*(Marks!$B$21:$BC$21=1))/SUMPRODUCT((Marks!$B$2:$BC$2=N$3)*ISNUMBER(Marks!$B$21:$BC$21)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>18</v>
+      </c>
+      <c r="B22" s="5" t="n"/>
+      <c r="C22" s="5" t="n"/>
+      <c r="D22" s="5" t="n"/>
+      <c r="E22" s="5" t="n"/>
+      <c r="F22" s="5" t="n"/>
+      <c r="G22" s="5" t="n"/>
+      <c r="I22" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=I$3)*ISNUMBER(Marks!$B$22:$BC$22))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=I$3)*(Marks!$B$22:$BC$22=1))/SUMPRODUCT((Marks!$B$2:$BC$2=I$3)*ISNUMBER(Marks!$B$22:$BC$22)))</f>
+        <v/>
+      </c>
+      <c r="J22" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=J$3)*ISNUMBER(Marks!$B$22:$BC$22))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=J$3)*(Marks!$B$22:$BC$22=1))/SUMPRODUCT((Marks!$B$2:$BC$2=J$3)*ISNUMBER(Marks!$B$22:$BC$22)))</f>
+        <v/>
+      </c>
+      <c r="K22" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=K$3)*ISNUMBER(Marks!$B$22:$BC$22))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=K$3)*(Marks!$B$22:$BC$22=1))/SUMPRODUCT((Marks!$B$2:$BC$2=K$3)*ISNUMBER(Marks!$B$22:$BC$22)))</f>
+        <v/>
+      </c>
+      <c r="L22" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=L$3)*ISNUMBER(Marks!$B$22:$BC$22))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=L$3)*(Marks!$B$22:$BC$22=1))/SUMPRODUCT((Marks!$B$2:$BC$2=L$3)*ISNUMBER(Marks!$B$22:$BC$22)))</f>
+        <v/>
+      </c>
+      <c r="M22" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=M$3)*ISNUMBER(Marks!$B$22:$BC$22))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=M$3)*(Marks!$B$22:$BC$22=1))/SUMPRODUCT((Marks!$B$2:$BC$2=M$3)*ISNUMBER(Marks!$B$22:$BC$22)))</f>
+        <v/>
+      </c>
+      <c r="N22" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=N$3)*ISNUMBER(Marks!$B$22:$BC$22))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=N$3)*(Marks!$B$22:$BC$22=1))/SUMPRODUCT((Marks!$B$2:$BC$2=N$3)*ISNUMBER(Marks!$B$22:$BC$22)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>19</v>
+      </c>
+      <c r="B23" s="5" t="n"/>
+      <c r="C23" s="5" t="n"/>
+      <c r="D23" s="5" t="n"/>
+      <c r="E23" s="5" t="n"/>
+      <c r="F23" s="5" t="n"/>
+      <c r="G23" s="5" t="n"/>
+      <c r="I23" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=I$3)*ISNUMBER(Marks!$B$23:$BC$23))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=I$3)*(Marks!$B$23:$BC$23=1))/SUMPRODUCT((Marks!$B$2:$BC$2=I$3)*ISNUMBER(Marks!$B$23:$BC$23)))</f>
+        <v/>
+      </c>
+      <c r="J23" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=J$3)*ISNUMBER(Marks!$B$23:$BC$23))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=J$3)*(Marks!$B$23:$BC$23=1))/SUMPRODUCT((Marks!$B$2:$BC$2=J$3)*ISNUMBER(Marks!$B$23:$BC$23)))</f>
+        <v/>
+      </c>
+      <c r="K23" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=K$3)*ISNUMBER(Marks!$B$23:$BC$23))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=K$3)*(Marks!$B$23:$BC$23=1))/SUMPRODUCT((Marks!$B$2:$BC$2=K$3)*ISNUMBER(Marks!$B$23:$BC$23)))</f>
+        <v/>
+      </c>
+      <c r="L23" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=L$3)*ISNUMBER(Marks!$B$23:$BC$23))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=L$3)*(Marks!$B$23:$BC$23=1))/SUMPRODUCT((Marks!$B$2:$BC$2=L$3)*ISNUMBER(Marks!$B$23:$BC$23)))</f>
+        <v/>
+      </c>
+      <c r="M23" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=M$3)*ISNUMBER(Marks!$B$23:$BC$23))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=M$3)*(Marks!$B$23:$BC$23=1))/SUMPRODUCT((Marks!$B$2:$BC$2=M$3)*ISNUMBER(Marks!$B$23:$BC$23)))</f>
+        <v/>
+      </c>
+      <c r="N23" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=N$3)*ISNUMBER(Marks!$B$23:$BC$23))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=N$3)*(Marks!$B$23:$BC$23=1))/SUMPRODUCT((Marks!$B$2:$BC$2=N$3)*ISNUMBER(Marks!$B$23:$BC$23)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>20</v>
+      </c>
+      <c r="B24" s="5" t="n"/>
+      <c r="C24" s="5" t="n"/>
+      <c r="D24" s="5" t="n"/>
+      <c r="E24" s="5" t="n"/>
+      <c r="F24" s="5" t="n"/>
+      <c r="G24" s="5" t="n"/>
+      <c r="I24" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=I$3)*ISNUMBER(Marks!$B$24:$BC$24))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=I$3)*(Marks!$B$24:$BC$24=1))/SUMPRODUCT((Marks!$B$2:$BC$2=I$3)*ISNUMBER(Marks!$B$24:$BC$24)))</f>
+        <v/>
+      </c>
+      <c r="J24" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=J$3)*ISNUMBER(Marks!$B$24:$BC$24))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=J$3)*(Marks!$B$24:$BC$24=1))/SUMPRODUCT((Marks!$B$2:$BC$2=J$3)*ISNUMBER(Marks!$B$24:$BC$24)))</f>
+        <v/>
+      </c>
+      <c r="K24" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=K$3)*ISNUMBER(Marks!$B$24:$BC$24))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=K$3)*(Marks!$B$24:$BC$24=1))/SUMPRODUCT((Marks!$B$2:$BC$2=K$3)*ISNUMBER(Marks!$B$24:$BC$24)))</f>
+        <v/>
+      </c>
+      <c r="L24" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=L$3)*ISNUMBER(Marks!$B$24:$BC$24))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=L$3)*(Marks!$B$24:$BC$24=1))/SUMPRODUCT((Marks!$B$2:$BC$2=L$3)*ISNUMBER(Marks!$B$24:$BC$24)))</f>
+        <v/>
+      </c>
+      <c r="M24" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=M$3)*ISNUMBER(Marks!$B$24:$BC$24))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=M$3)*(Marks!$B$24:$BC$24=1))/SUMPRODUCT((Marks!$B$2:$BC$2=M$3)*ISNUMBER(Marks!$B$24:$BC$24)))</f>
+        <v/>
+      </c>
+      <c r="N24" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=N$3)*ISNUMBER(Marks!$B$24:$BC$24))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=N$3)*(Marks!$B$24:$BC$24=1))/SUMPRODUCT((Marks!$B$2:$BC$2=N$3)*ISNUMBER(Marks!$B$24:$BC$24)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>21</v>
+      </c>
+      <c r="B25" s="5" t="n"/>
+      <c r="C25" s="5" t="n"/>
+      <c r="D25" s="5" t="n"/>
+      <c r="E25" s="5" t="n"/>
+      <c r="F25" s="5" t="n"/>
+      <c r="G25" s="5" t="n"/>
+      <c r="I25" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=I$3)*ISNUMBER(Marks!$B$25:$BC$25))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=I$3)*(Marks!$B$25:$BC$25=1))/SUMPRODUCT((Marks!$B$2:$BC$2=I$3)*ISNUMBER(Marks!$B$25:$BC$25)))</f>
+        <v/>
+      </c>
+      <c r="J25" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=J$3)*ISNUMBER(Marks!$B$25:$BC$25))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=J$3)*(Marks!$B$25:$BC$25=1))/SUMPRODUCT((Marks!$B$2:$BC$2=J$3)*ISNUMBER(Marks!$B$25:$BC$25)))</f>
+        <v/>
+      </c>
+      <c r="K25" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=K$3)*ISNUMBER(Marks!$B$25:$BC$25))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=K$3)*(Marks!$B$25:$BC$25=1))/SUMPRODUCT((Marks!$B$2:$BC$2=K$3)*ISNUMBER(Marks!$B$25:$BC$25)))</f>
+        <v/>
+      </c>
+      <c r="L25" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=L$3)*ISNUMBER(Marks!$B$25:$BC$25))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=L$3)*(Marks!$B$25:$BC$25=1))/SUMPRODUCT((Marks!$B$2:$BC$2=L$3)*ISNUMBER(Marks!$B$25:$BC$25)))</f>
+        <v/>
+      </c>
+      <c r="M25" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=M$3)*ISNUMBER(Marks!$B$25:$BC$25))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=M$3)*(Marks!$B$25:$BC$25=1))/SUMPRODUCT((Marks!$B$2:$BC$2=M$3)*ISNUMBER(Marks!$B$25:$BC$25)))</f>
+        <v/>
+      </c>
+      <c r="N25" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=N$3)*ISNUMBER(Marks!$B$25:$BC$25))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=N$3)*(Marks!$B$25:$BC$25=1))/SUMPRODUCT((Marks!$B$2:$BC$2=N$3)*ISNUMBER(Marks!$B$25:$BC$25)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>22</v>
+      </c>
+      <c r="B26" s="5" t="n"/>
+      <c r="C26" s="5" t="n"/>
+      <c r="D26" s="5" t="n"/>
+      <c r="E26" s="5" t="n"/>
+      <c r="F26" s="5" t="n"/>
+      <c r="G26" s="5" t="n"/>
+      <c r="I26" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=I$3)*ISNUMBER(Marks!$B$26:$BC$26))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=I$3)*(Marks!$B$26:$BC$26=1))/SUMPRODUCT((Marks!$B$2:$BC$2=I$3)*ISNUMBER(Marks!$B$26:$BC$26)))</f>
+        <v/>
+      </c>
+      <c r="J26" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=J$3)*ISNUMBER(Marks!$B$26:$BC$26))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=J$3)*(Marks!$B$26:$BC$26=1))/SUMPRODUCT((Marks!$B$2:$BC$2=J$3)*ISNUMBER(Marks!$B$26:$BC$26)))</f>
+        <v/>
+      </c>
+      <c r="K26" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=K$3)*ISNUMBER(Marks!$B$26:$BC$26))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=K$3)*(Marks!$B$26:$BC$26=1))/SUMPRODUCT((Marks!$B$2:$BC$2=K$3)*ISNUMBER(Marks!$B$26:$BC$26)))</f>
+        <v/>
+      </c>
+      <c r="L26" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=L$3)*ISNUMBER(Marks!$B$26:$BC$26))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=L$3)*(Marks!$B$26:$BC$26=1))/SUMPRODUCT((Marks!$B$2:$BC$2=L$3)*ISNUMBER(Marks!$B$26:$BC$26)))</f>
+        <v/>
+      </c>
+      <c r="M26" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=M$3)*ISNUMBER(Marks!$B$26:$BC$26))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=M$3)*(Marks!$B$26:$BC$26=1))/SUMPRODUCT((Marks!$B$2:$BC$2=M$3)*ISNUMBER(Marks!$B$26:$BC$26)))</f>
+        <v/>
+      </c>
+      <c r="N26" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=N$3)*ISNUMBER(Marks!$B$26:$BC$26))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=N$3)*(Marks!$B$26:$BC$26=1))/SUMPRODUCT((Marks!$B$2:$BC$2=N$3)*ISNUMBER(Marks!$B$26:$BC$26)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>23</v>
+      </c>
+      <c r="B27" s="5" t="n"/>
+      <c r="C27" s="5" t="n"/>
+      <c r="D27" s="5" t="n"/>
+      <c r="E27" s="5" t="n"/>
+      <c r="F27" s="5" t="n"/>
+      <c r="G27" s="5" t="n"/>
+      <c r="I27" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=I$3)*ISNUMBER(Marks!$B$27:$BC$27))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=I$3)*(Marks!$B$27:$BC$27=1))/SUMPRODUCT((Marks!$B$2:$BC$2=I$3)*ISNUMBER(Marks!$B$27:$BC$27)))</f>
+        <v/>
+      </c>
+      <c r="J27" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=J$3)*ISNUMBER(Marks!$B$27:$BC$27))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=J$3)*(Marks!$B$27:$BC$27=1))/SUMPRODUCT((Marks!$B$2:$BC$2=J$3)*ISNUMBER(Marks!$B$27:$BC$27)))</f>
+        <v/>
+      </c>
+      <c r="K27" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=K$3)*ISNUMBER(Marks!$B$27:$BC$27))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=K$3)*(Marks!$B$27:$BC$27=1))/SUMPRODUCT((Marks!$B$2:$BC$2=K$3)*ISNUMBER(Marks!$B$27:$BC$27)))</f>
+        <v/>
+      </c>
+      <c r="L27" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=L$3)*ISNUMBER(Marks!$B$27:$BC$27))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=L$3)*(Marks!$B$27:$BC$27=1))/SUMPRODUCT((Marks!$B$2:$BC$2=L$3)*ISNUMBER(Marks!$B$27:$BC$27)))</f>
+        <v/>
+      </c>
+      <c r="M27" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=M$3)*ISNUMBER(Marks!$B$27:$BC$27))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=M$3)*(Marks!$B$27:$BC$27=1))/SUMPRODUCT((Marks!$B$2:$BC$2=M$3)*ISNUMBER(Marks!$B$27:$BC$27)))</f>
+        <v/>
+      </c>
+      <c r="N27" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=N$3)*ISNUMBER(Marks!$B$27:$BC$27))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=N$3)*(Marks!$B$27:$BC$27=1))/SUMPRODUCT((Marks!$B$2:$BC$2=N$3)*ISNUMBER(Marks!$B$27:$BC$27)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>24</v>
+      </c>
+      <c r="B28" s="5" t="n"/>
+      <c r="C28" s="5" t="n"/>
+      <c r="D28" s="5" t="n"/>
+      <c r="E28" s="5" t="n"/>
+      <c r="F28" s="5" t="n"/>
+      <c r="G28" s="5" t="n"/>
+      <c r="I28" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=I$3)*ISNUMBER(Marks!$B$28:$BC$28))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=I$3)*(Marks!$B$28:$BC$28=1))/SUMPRODUCT((Marks!$B$2:$BC$2=I$3)*ISNUMBER(Marks!$B$28:$BC$28)))</f>
+        <v/>
+      </c>
+      <c r="J28" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=J$3)*ISNUMBER(Marks!$B$28:$BC$28))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=J$3)*(Marks!$B$28:$BC$28=1))/SUMPRODUCT((Marks!$B$2:$BC$2=J$3)*ISNUMBER(Marks!$B$28:$BC$28)))</f>
+        <v/>
+      </c>
+      <c r="K28" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=K$3)*ISNUMBER(Marks!$B$28:$BC$28))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=K$3)*(Marks!$B$28:$BC$28=1))/SUMPRODUCT((Marks!$B$2:$BC$2=K$3)*ISNUMBER(Marks!$B$28:$BC$28)))</f>
+        <v/>
+      </c>
+      <c r="L28" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=L$3)*ISNUMBER(Marks!$B$28:$BC$28))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=L$3)*(Marks!$B$28:$BC$28=1))/SUMPRODUCT((Marks!$B$2:$BC$2=L$3)*ISNUMBER(Marks!$B$28:$BC$28)))</f>
+        <v/>
+      </c>
+      <c r="M28" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=M$3)*ISNUMBER(Marks!$B$28:$BC$28))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=M$3)*(Marks!$B$28:$BC$28=1))/SUMPRODUCT((Marks!$B$2:$BC$2=M$3)*ISNUMBER(Marks!$B$28:$BC$28)))</f>
+        <v/>
+      </c>
+      <c r="N28" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=N$3)*ISNUMBER(Marks!$B$28:$BC$28))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=N$3)*(Marks!$B$28:$BC$28=1))/SUMPRODUCT((Marks!$B$2:$BC$2=N$3)*ISNUMBER(Marks!$B$28:$BC$28)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>25</v>
+      </c>
+      <c r="B29" s="5" t="n"/>
+      <c r="C29" s="5" t="n"/>
+      <c r="D29" s="5" t="n"/>
+      <c r="E29" s="5" t="n"/>
+      <c r="F29" s="5" t="n"/>
+      <c r="G29" s="5" t="n"/>
+      <c r="I29" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=I$3)*ISNUMBER(Marks!$B$29:$BC$29))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=I$3)*(Marks!$B$29:$BC$29=1))/SUMPRODUCT((Marks!$B$2:$BC$2=I$3)*ISNUMBER(Marks!$B$29:$BC$29)))</f>
+        <v/>
+      </c>
+      <c r="J29" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=J$3)*ISNUMBER(Marks!$B$29:$BC$29))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=J$3)*(Marks!$B$29:$BC$29=1))/SUMPRODUCT((Marks!$B$2:$BC$2=J$3)*ISNUMBER(Marks!$B$29:$BC$29)))</f>
+        <v/>
+      </c>
+      <c r="K29" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=K$3)*ISNUMBER(Marks!$B$29:$BC$29))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=K$3)*(Marks!$B$29:$BC$29=1))/SUMPRODUCT((Marks!$B$2:$BC$2=K$3)*ISNUMBER(Marks!$B$29:$BC$29)))</f>
+        <v/>
+      </c>
+      <c r="L29" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=L$3)*ISNUMBER(Marks!$B$29:$BC$29))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=L$3)*(Marks!$B$29:$BC$29=1))/SUMPRODUCT((Marks!$B$2:$BC$2=L$3)*ISNUMBER(Marks!$B$29:$BC$29)))</f>
+        <v/>
+      </c>
+      <c r="M29" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=M$3)*ISNUMBER(Marks!$B$29:$BC$29))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=M$3)*(Marks!$B$29:$BC$29=1))/SUMPRODUCT((Marks!$B$2:$BC$2=M$3)*ISNUMBER(Marks!$B$29:$BC$29)))</f>
+        <v/>
+      </c>
+      <c r="N29" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=N$3)*ISNUMBER(Marks!$B$29:$BC$29))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=N$3)*(Marks!$B$29:$BC$29=1))/SUMPRODUCT((Marks!$B$2:$BC$2=N$3)*ISNUMBER(Marks!$B$29:$BC$29)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>26</v>
+      </c>
+      <c r="B30" s="5" t="n"/>
+      <c r="C30" s="5" t="n"/>
+      <c r="D30" s="5" t="n"/>
+      <c r="E30" s="5" t="n"/>
+      <c r="F30" s="5" t="n"/>
+      <c r="G30" s="5" t="n"/>
+      <c r="I30" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=I$3)*ISNUMBER(Marks!$B$30:$BC$30))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=I$3)*(Marks!$B$30:$BC$30=1))/SUMPRODUCT((Marks!$B$2:$BC$2=I$3)*ISNUMBER(Marks!$B$30:$BC$30)))</f>
+        <v/>
+      </c>
+      <c r="J30" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=J$3)*ISNUMBER(Marks!$B$30:$BC$30))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=J$3)*(Marks!$B$30:$BC$30=1))/SUMPRODUCT((Marks!$B$2:$BC$2=J$3)*ISNUMBER(Marks!$B$30:$BC$30)))</f>
+        <v/>
+      </c>
+      <c r="K30" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=K$3)*ISNUMBER(Marks!$B$30:$BC$30))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=K$3)*(Marks!$B$30:$BC$30=1))/SUMPRODUCT((Marks!$B$2:$BC$2=K$3)*ISNUMBER(Marks!$B$30:$BC$30)))</f>
+        <v/>
+      </c>
+      <c r="L30" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=L$3)*ISNUMBER(Marks!$B$30:$BC$30))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=L$3)*(Marks!$B$30:$BC$30=1))/SUMPRODUCT((Marks!$B$2:$BC$2=L$3)*ISNUMBER(Marks!$B$30:$BC$30)))</f>
+        <v/>
+      </c>
+      <c r="M30" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=M$3)*ISNUMBER(Marks!$B$30:$BC$30))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=M$3)*(Marks!$B$30:$BC$30=1))/SUMPRODUCT((Marks!$B$2:$BC$2=M$3)*ISNUMBER(Marks!$B$30:$BC$30)))</f>
+        <v/>
+      </c>
+      <c r="N30" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=N$3)*ISNUMBER(Marks!$B$30:$BC$30))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=N$3)*(Marks!$B$30:$BC$30=1))/SUMPRODUCT((Marks!$B$2:$BC$2=N$3)*ISNUMBER(Marks!$B$30:$BC$30)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>27</v>
+      </c>
+      <c r="B31" s="5" t="n"/>
+      <c r="C31" s="5" t="n"/>
+      <c r="D31" s="5" t="n"/>
+      <c r="E31" s="5" t="n"/>
+      <c r="F31" s="5" t="n"/>
+      <c r="G31" s="5" t="n"/>
+      <c r="I31" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=I$3)*ISNUMBER(Marks!$B$31:$BC$31))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=I$3)*(Marks!$B$31:$BC$31=1))/SUMPRODUCT((Marks!$B$2:$BC$2=I$3)*ISNUMBER(Marks!$B$31:$BC$31)))</f>
+        <v/>
+      </c>
+      <c r="J31" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=J$3)*ISNUMBER(Marks!$B$31:$BC$31))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=J$3)*(Marks!$B$31:$BC$31=1))/SUMPRODUCT((Marks!$B$2:$BC$2=J$3)*ISNUMBER(Marks!$B$31:$BC$31)))</f>
+        <v/>
+      </c>
+      <c r="K31" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=K$3)*ISNUMBER(Marks!$B$31:$BC$31))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=K$3)*(Marks!$B$31:$BC$31=1))/SUMPRODUCT((Marks!$B$2:$BC$2=K$3)*ISNUMBER(Marks!$B$31:$BC$31)))</f>
+        <v/>
+      </c>
+      <c r="L31" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=L$3)*ISNUMBER(Marks!$B$31:$BC$31))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=L$3)*(Marks!$B$31:$BC$31=1))/SUMPRODUCT((Marks!$B$2:$BC$2=L$3)*ISNUMBER(Marks!$B$31:$BC$31)))</f>
+        <v/>
+      </c>
+      <c r="M31" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=M$3)*ISNUMBER(Marks!$B$31:$BC$31))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=M$3)*(Marks!$B$31:$BC$31=1))/SUMPRODUCT((Marks!$B$2:$BC$2=M$3)*ISNUMBER(Marks!$B$31:$BC$31)))</f>
+        <v/>
+      </c>
+      <c r="N31" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=N$3)*ISNUMBER(Marks!$B$31:$BC$31))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=N$3)*(Marks!$B$31:$BC$31=1))/SUMPRODUCT((Marks!$B$2:$BC$2=N$3)*ISNUMBER(Marks!$B$31:$BC$31)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>28</v>
+      </c>
+      <c r="B32" s="5" t="n"/>
+      <c r="C32" s="5" t="n"/>
+      <c r="D32" s="5" t="n"/>
+      <c r="E32" s="5" t="n"/>
+      <c r="F32" s="5" t="n"/>
+      <c r="G32" s="5" t="n"/>
+      <c r="I32" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=I$3)*ISNUMBER(Marks!$B$32:$BC$32))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=I$3)*(Marks!$B$32:$BC$32=1))/SUMPRODUCT((Marks!$B$2:$BC$2=I$3)*ISNUMBER(Marks!$B$32:$BC$32)))</f>
+        <v/>
+      </c>
+      <c r="J32" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=J$3)*ISNUMBER(Marks!$B$32:$BC$32))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=J$3)*(Marks!$B$32:$BC$32=1))/SUMPRODUCT((Marks!$B$2:$BC$2=J$3)*ISNUMBER(Marks!$B$32:$BC$32)))</f>
+        <v/>
+      </c>
+      <c r="K32" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=K$3)*ISNUMBER(Marks!$B$32:$BC$32))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=K$3)*(Marks!$B$32:$BC$32=1))/SUMPRODUCT((Marks!$B$2:$BC$2=K$3)*ISNUMBER(Marks!$B$32:$BC$32)))</f>
+        <v/>
+      </c>
+      <c r="L32" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=L$3)*ISNUMBER(Marks!$B$32:$BC$32))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=L$3)*(Marks!$B$32:$BC$32=1))/SUMPRODUCT((Marks!$B$2:$BC$2=L$3)*ISNUMBER(Marks!$B$32:$BC$32)))</f>
+        <v/>
+      </c>
+      <c r="M32" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=M$3)*ISNUMBER(Marks!$B$32:$BC$32))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=M$3)*(Marks!$B$32:$BC$32=1))/SUMPRODUCT((Marks!$B$2:$BC$2=M$3)*ISNUMBER(Marks!$B$32:$BC$32)))</f>
+        <v/>
+      </c>
+      <c r="N32" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=N$3)*ISNUMBER(Marks!$B$32:$BC$32))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=N$3)*(Marks!$B$32:$BC$32=1))/SUMPRODUCT((Marks!$B$2:$BC$2=N$3)*ISNUMBER(Marks!$B$32:$BC$32)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>29</v>
+      </c>
+      <c r="B33" s="5" t="n"/>
+      <c r="C33" s="5" t="n"/>
+      <c r="D33" s="5" t="n"/>
+      <c r="E33" s="5" t="n"/>
+      <c r="F33" s="5" t="n"/>
+      <c r="G33" s="5" t="n"/>
+      <c r="I33" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=I$3)*ISNUMBER(Marks!$B$33:$BC$33))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=I$3)*(Marks!$B$33:$BC$33=1))/SUMPRODUCT((Marks!$B$2:$BC$2=I$3)*ISNUMBER(Marks!$B$33:$BC$33)))</f>
+        <v/>
+      </c>
+      <c r="J33" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=J$3)*ISNUMBER(Marks!$B$33:$BC$33))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=J$3)*(Marks!$B$33:$BC$33=1))/SUMPRODUCT((Marks!$B$2:$BC$2=J$3)*ISNUMBER(Marks!$B$33:$BC$33)))</f>
+        <v/>
+      </c>
+      <c r="K33" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=K$3)*ISNUMBER(Marks!$B$33:$BC$33))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=K$3)*(Marks!$B$33:$BC$33=1))/SUMPRODUCT((Marks!$B$2:$BC$2=K$3)*ISNUMBER(Marks!$B$33:$BC$33)))</f>
+        <v/>
+      </c>
+      <c r="L33" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=L$3)*ISNUMBER(Marks!$B$33:$BC$33))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=L$3)*(Marks!$B$33:$BC$33=1))/SUMPRODUCT((Marks!$B$2:$BC$2=L$3)*ISNUMBER(Marks!$B$33:$BC$33)))</f>
+        <v/>
+      </c>
+      <c r="M33" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=M$3)*ISNUMBER(Marks!$B$33:$BC$33))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=M$3)*(Marks!$B$33:$BC$33=1))/SUMPRODUCT((Marks!$B$2:$BC$2=M$3)*ISNUMBER(Marks!$B$33:$BC$33)))</f>
+        <v/>
+      </c>
+      <c r="N33" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=N$3)*ISNUMBER(Marks!$B$33:$BC$33))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=N$3)*(Marks!$B$33:$BC$33=1))/SUMPRODUCT((Marks!$B$2:$BC$2=N$3)*ISNUMBER(Marks!$B$33:$BC$33)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>30</v>
+      </c>
+      <c r="B34" s="5" t="n"/>
+      <c r="C34" s="5" t="n"/>
+      <c r="D34" s="5" t="n"/>
+      <c r="E34" s="5" t="n"/>
+      <c r="F34" s="5" t="n"/>
+      <c r="G34" s="5" t="n"/>
+      <c r="I34" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=I$3)*ISNUMBER(Marks!$B$34:$BC$34))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=I$3)*(Marks!$B$34:$BC$34=1))/SUMPRODUCT((Marks!$B$2:$BC$2=I$3)*ISNUMBER(Marks!$B$34:$BC$34)))</f>
+        <v/>
+      </c>
+      <c r="J34" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=J$3)*ISNUMBER(Marks!$B$34:$BC$34))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=J$3)*(Marks!$B$34:$BC$34=1))/SUMPRODUCT((Marks!$B$2:$BC$2=J$3)*ISNUMBER(Marks!$B$34:$BC$34)))</f>
+        <v/>
+      </c>
+      <c r="K34" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=K$3)*ISNUMBER(Marks!$B$34:$BC$34))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=K$3)*(Marks!$B$34:$BC$34=1))/SUMPRODUCT((Marks!$B$2:$BC$2=K$3)*ISNUMBER(Marks!$B$34:$BC$34)))</f>
+        <v/>
+      </c>
+      <c r="L34" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=L$3)*ISNUMBER(Marks!$B$34:$BC$34))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=L$3)*(Marks!$B$34:$BC$34=1))/SUMPRODUCT((Marks!$B$2:$BC$2=L$3)*ISNUMBER(Marks!$B$34:$BC$34)))</f>
+        <v/>
+      </c>
+      <c r="M34" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=M$3)*ISNUMBER(Marks!$B$34:$BC$34))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=M$3)*(Marks!$B$34:$BC$34=1))/SUMPRODUCT((Marks!$B$2:$BC$2=M$3)*ISNUMBER(Marks!$B$34:$BC$34)))</f>
+        <v/>
+      </c>
+      <c r="N34" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=N$3)*ISNUMBER(Marks!$B$34:$BC$34))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=N$3)*(Marks!$B$34:$BC$34=1))/SUMPRODUCT((Marks!$B$2:$BC$2=N$3)*ISNUMBER(Marks!$B$34:$BC$34)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>31</v>
+      </c>
+      <c r="B35" s="5" t="n"/>
+      <c r="C35" s="5" t="n"/>
+      <c r="D35" s="5" t="n"/>
+      <c r="E35" s="5" t="n"/>
+      <c r="F35" s="5" t="n"/>
+      <c r="G35" s="5" t="n"/>
+      <c r="I35" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=I$3)*ISNUMBER(Marks!$B$35:$BC$35))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=I$3)*(Marks!$B$35:$BC$35=1))/SUMPRODUCT((Marks!$B$2:$BC$2=I$3)*ISNUMBER(Marks!$B$35:$BC$35)))</f>
+        <v/>
+      </c>
+      <c r="J35" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=J$3)*ISNUMBER(Marks!$B$35:$BC$35))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=J$3)*(Marks!$B$35:$BC$35=1))/SUMPRODUCT((Marks!$B$2:$BC$2=J$3)*ISNUMBER(Marks!$B$35:$BC$35)))</f>
+        <v/>
+      </c>
+      <c r="K35" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=K$3)*ISNUMBER(Marks!$B$35:$BC$35))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=K$3)*(Marks!$B$35:$BC$35=1))/SUMPRODUCT((Marks!$B$2:$BC$2=K$3)*ISNUMBER(Marks!$B$35:$BC$35)))</f>
+        <v/>
+      </c>
+      <c r="L35" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=L$3)*ISNUMBER(Marks!$B$35:$BC$35))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=L$3)*(Marks!$B$35:$BC$35=1))/SUMPRODUCT((Marks!$B$2:$BC$2=L$3)*ISNUMBER(Marks!$B$35:$BC$35)))</f>
+        <v/>
+      </c>
+      <c r="M35" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=M$3)*ISNUMBER(Marks!$B$35:$BC$35))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=M$3)*(Marks!$B$35:$BC$35=1))/SUMPRODUCT((Marks!$B$2:$BC$2=M$3)*ISNUMBER(Marks!$B$35:$BC$35)))</f>
+        <v/>
+      </c>
+      <c r="N35" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=N$3)*ISNUMBER(Marks!$B$35:$BC$35))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=N$3)*(Marks!$B$35:$BC$35=1))/SUMPRODUCT((Marks!$B$2:$BC$2=N$3)*ISNUMBER(Marks!$B$35:$BC$35)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>32</v>
+      </c>
+      <c r="B36" s="5" t="n"/>
+      <c r="C36" s="5" t="n"/>
+      <c r="D36" s="5" t="n"/>
+      <c r="E36" s="5" t="n"/>
+      <c r="F36" s="5" t="n"/>
+      <c r="G36" s="5" t="n"/>
+      <c r="I36" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=I$3)*ISNUMBER(Marks!$B$36:$BC$36))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=I$3)*(Marks!$B$36:$BC$36=1))/SUMPRODUCT((Marks!$B$2:$BC$2=I$3)*ISNUMBER(Marks!$B$36:$BC$36)))</f>
+        <v/>
+      </c>
+      <c r="J36" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=J$3)*ISNUMBER(Marks!$B$36:$BC$36))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=J$3)*(Marks!$B$36:$BC$36=1))/SUMPRODUCT((Marks!$B$2:$BC$2=J$3)*ISNUMBER(Marks!$B$36:$BC$36)))</f>
+        <v/>
+      </c>
+      <c r="K36" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=K$3)*ISNUMBER(Marks!$B$36:$BC$36))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=K$3)*(Marks!$B$36:$BC$36=1))/SUMPRODUCT((Marks!$B$2:$BC$2=K$3)*ISNUMBER(Marks!$B$36:$BC$36)))</f>
+        <v/>
+      </c>
+      <c r="L36" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=L$3)*ISNUMBER(Marks!$B$36:$BC$36))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=L$3)*(Marks!$B$36:$BC$36=1))/SUMPRODUCT((Marks!$B$2:$BC$2=L$3)*ISNUMBER(Marks!$B$36:$BC$36)))</f>
+        <v/>
+      </c>
+      <c r="M36" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=M$3)*ISNUMBER(Marks!$B$36:$BC$36))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=M$3)*(Marks!$B$36:$BC$36=1))/SUMPRODUCT((Marks!$B$2:$BC$2=M$3)*ISNUMBER(Marks!$B$36:$BC$36)))</f>
+        <v/>
+      </c>
+      <c r="N36" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=N$3)*ISNUMBER(Marks!$B$36:$BC$36))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=N$3)*(Marks!$B$36:$BC$36=1))/SUMPRODUCT((Marks!$B$2:$BC$2=N$3)*ISNUMBER(Marks!$B$36:$BC$36)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>33</v>
+      </c>
+      <c r="B37" s="5" t="n"/>
+      <c r="C37" s="5" t="n"/>
+      <c r="D37" s="5" t="n"/>
+      <c r="E37" s="5" t="n"/>
+      <c r="F37" s="5" t="n"/>
+      <c r="G37" s="5" t="n"/>
+      <c r="I37" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=I$3)*ISNUMBER(Marks!$B$37:$BC$37))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=I$3)*(Marks!$B$37:$BC$37=1))/SUMPRODUCT((Marks!$B$2:$BC$2=I$3)*ISNUMBER(Marks!$B$37:$BC$37)))</f>
+        <v/>
+      </c>
+      <c r="J37" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=J$3)*ISNUMBER(Marks!$B$37:$BC$37))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=J$3)*(Marks!$B$37:$BC$37=1))/SUMPRODUCT((Marks!$B$2:$BC$2=J$3)*ISNUMBER(Marks!$B$37:$BC$37)))</f>
+        <v/>
+      </c>
+      <c r="K37" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=K$3)*ISNUMBER(Marks!$B$37:$BC$37))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=K$3)*(Marks!$B$37:$BC$37=1))/SUMPRODUCT((Marks!$B$2:$BC$2=K$3)*ISNUMBER(Marks!$B$37:$BC$37)))</f>
+        <v/>
+      </c>
+      <c r="L37" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=L$3)*ISNUMBER(Marks!$B$37:$BC$37))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=L$3)*(Marks!$B$37:$BC$37=1))/SUMPRODUCT((Marks!$B$2:$BC$2=L$3)*ISNUMBER(Marks!$B$37:$BC$37)))</f>
+        <v/>
+      </c>
+      <c r="M37" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=M$3)*ISNUMBER(Marks!$B$37:$BC$37))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=M$3)*(Marks!$B$37:$BC$37=1))/SUMPRODUCT((Marks!$B$2:$BC$2=M$3)*ISNUMBER(Marks!$B$37:$BC$37)))</f>
+        <v/>
+      </c>
+      <c r="N37" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=N$3)*ISNUMBER(Marks!$B$37:$BC$37))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=N$3)*(Marks!$B$37:$BC$37=1))/SUMPRODUCT((Marks!$B$2:$BC$2=N$3)*ISNUMBER(Marks!$B$37:$BC$37)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>34</v>
+      </c>
+      <c r="B38" s="5" t="n"/>
+      <c r="C38" s="5" t="n"/>
+      <c r="D38" s="5" t="n"/>
+      <c r="E38" s="5" t="n"/>
+      <c r="F38" s="5" t="n"/>
+      <c r="G38" s="5" t="n"/>
+      <c r="I38" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=I$3)*ISNUMBER(Marks!$B$38:$BC$38))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=I$3)*(Marks!$B$38:$BC$38=1))/SUMPRODUCT((Marks!$B$2:$BC$2=I$3)*ISNUMBER(Marks!$B$38:$BC$38)))</f>
+        <v/>
+      </c>
+      <c r="J38" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=J$3)*ISNUMBER(Marks!$B$38:$BC$38))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=J$3)*(Marks!$B$38:$BC$38=1))/SUMPRODUCT((Marks!$B$2:$BC$2=J$3)*ISNUMBER(Marks!$B$38:$BC$38)))</f>
+        <v/>
+      </c>
+      <c r="K38" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=K$3)*ISNUMBER(Marks!$B$38:$BC$38))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=K$3)*(Marks!$B$38:$BC$38=1))/SUMPRODUCT((Marks!$B$2:$BC$2=K$3)*ISNUMBER(Marks!$B$38:$BC$38)))</f>
+        <v/>
+      </c>
+      <c r="L38" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=L$3)*ISNUMBER(Marks!$B$38:$BC$38))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=L$3)*(Marks!$B$38:$BC$38=1))/SUMPRODUCT((Marks!$B$2:$BC$2=L$3)*ISNUMBER(Marks!$B$38:$BC$38)))</f>
+        <v/>
+      </c>
+      <c r="M38" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=M$3)*ISNUMBER(Marks!$B$38:$BC$38))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=M$3)*(Marks!$B$38:$BC$38=1))/SUMPRODUCT((Marks!$B$2:$BC$2=M$3)*ISNUMBER(Marks!$B$38:$BC$38)))</f>
+        <v/>
+      </c>
+      <c r="N38" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=N$3)*ISNUMBER(Marks!$B$38:$BC$38))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=N$3)*(Marks!$B$38:$BC$38=1))/SUMPRODUCT((Marks!$B$2:$BC$2=N$3)*ISNUMBER(Marks!$B$38:$BC$38)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>35</v>
+      </c>
+      <c r="B39" s="5" t="n"/>
+      <c r="C39" s="5" t="n"/>
+      <c r="D39" s="5" t="n"/>
+      <c r="E39" s="5" t="n"/>
+      <c r="F39" s="5" t="n"/>
+      <c r="G39" s="5" t="n"/>
+      <c r="I39" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=I$3)*ISNUMBER(Marks!$B$39:$BC$39))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=I$3)*(Marks!$B$39:$BC$39=1))/SUMPRODUCT((Marks!$B$2:$BC$2=I$3)*ISNUMBER(Marks!$B$39:$BC$39)))</f>
+        <v/>
+      </c>
+      <c r="J39" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=J$3)*ISNUMBER(Marks!$B$39:$BC$39))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=J$3)*(Marks!$B$39:$BC$39=1))/SUMPRODUCT((Marks!$B$2:$BC$2=J$3)*ISNUMBER(Marks!$B$39:$BC$39)))</f>
+        <v/>
+      </c>
+      <c r="K39" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=K$3)*ISNUMBER(Marks!$B$39:$BC$39))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=K$3)*(Marks!$B$39:$BC$39=1))/SUMPRODUCT((Marks!$B$2:$BC$2=K$3)*ISNUMBER(Marks!$B$39:$BC$39)))</f>
+        <v/>
+      </c>
+      <c r="L39" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=L$3)*ISNUMBER(Marks!$B$39:$BC$39))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=L$3)*(Marks!$B$39:$BC$39=1))/SUMPRODUCT((Marks!$B$2:$BC$2=L$3)*ISNUMBER(Marks!$B$39:$BC$39)))</f>
+        <v/>
+      </c>
+      <c r="M39" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=M$3)*ISNUMBER(Marks!$B$39:$BC$39))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=M$3)*(Marks!$B$39:$BC$39=1))/SUMPRODUCT((Marks!$B$2:$BC$2=M$3)*ISNUMBER(Marks!$B$39:$BC$39)))</f>
+        <v/>
+      </c>
+      <c r="N39" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=N$3)*ISNUMBER(Marks!$B$39:$BC$39))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=N$3)*(Marks!$B$39:$BC$39=1))/SUMPRODUCT((Marks!$B$2:$BC$2=N$3)*ISNUMBER(Marks!$B$39:$BC$39)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>The room</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>Part</t>
+        </is>
+      </c>
+      <c r="B42" s="4" t="inlineStr">
+        <is>
+          <t>Mean rating</t>
+        </is>
+      </c>
+      <c r="C42" s="4" t="inlineStr">
+        <is>
+          <t>Right rate</t>
+        </is>
+      </c>
+      <c r="D42" s="4" t="inlineStr">
+        <is>
+          <t>Rated 3 or 4, under half right</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Part 1. The week's rules, cold</t>
+        </is>
+      </c>
+      <c r="B43" s="7">
+        <f>IF(COUNT(B5:B39)=0,"",AVERAGE(B5:B39))</f>
+        <v/>
+      </c>
+      <c r="C43" s="6">
+        <f>IFERROR(INDEX(Tags!$D$5:$D$14,MATCH(1,Tags!$A$5:$A$14,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D43">
+        <f>SUMPRODUCT((B5:B39&gt;=3)*ISNUMBER(I5:I39)*(I5:I39&lt;0.5))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Part 2. Where did the revenue go</t>
+        </is>
+      </c>
+      <c r="B44" s="7">
+        <f>IF(COUNT(C5:C39)=0,"",AVERAGE(C5:C39))</f>
+        <v/>
+      </c>
+      <c r="C44" s="6">
+        <f>IFERROR(INDEX(Tags!$D$5:$D$14,MATCH(2,Tags!$A$5:$A$14,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D44">
+        <f>SUMPRODUCT((C5:C39&gt;=3)*ISNUMBER(J5:J39)*(J5:J39&lt;0.5))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Part 3. Rows you can trust</t>
+        </is>
+      </c>
+      <c r="B45" s="7">
+        <f>IF(COUNT(D5:D39)=0,"",AVERAGE(D5:D39))</f>
+        <v/>
+      </c>
+      <c r="C45" s="6">
+        <f>IFERROR(INDEX(Tags!$D$5:$D$14,MATCH(3,Tags!$A$5:$A$14,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D45">
+        <f>SUMPRODUCT((D5:D39&gt;=3)*ISNUMBER(K5:K39)*(K5:K39&lt;0.5))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Part 4. Read the code, read the data</t>
+        </is>
+      </c>
+      <c r="B46" s="7">
+        <f>IF(COUNT(E5:E39)=0,"",AVERAGE(E5:E39))</f>
+        <v/>
+      </c>
+      <c r="C46" s="6">
+        <f>IFERROR(INDEX(Tags!$D$5:$D$14,MATCH(4,Tags!$A$5:$A$14,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D46">
+        <f>SUMPRODUCT((E5:E39&gt;=3)*ISNUMBER(L5:L39)*(L5:L39&lt;0.5))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Part 5. Chance and a fair test</t>
+        </is>
+      </c>
+      <c r="B47" s="7">
+        <f>IF(COUNT(F5:F39)=0,"",AVERAGE(F5:F39))</f>
+        <v/>
+      </c>
+      <c r="C47" s="6">
+        <f>IFERROR(INDEX(Tags!$D$5:$D$14,MATCH(5,Tags!$A$5:$A$14,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D47">
+        <f>SUMPRODUCT((F5:F39&gt;=3)*ISNUMBER(M5:M39)*(M5:M39&lt;0.5))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Part 6. The numbers</t>
+        </is>
+      </c>
+      <c r="B48" s="7">
+        <f>IF(COUNT(G5:G39)=0,"",AVERAGE(G5:G39))</f>
+        <v/>
+      </c>
+      <c r="C48" s="6">
+        <f>IFERROR(INDEX(Tags!$D$5:$D$14,MATCH(6,Tags!$A$5:$A$14,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D48">
+        <f>SUMPRODUCT((G5:G39&gt;=3)*ISNUMBER(N5:N39)*(N5:N39&lt;0.5))</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/content/W01/SAT/answer-key/C2_W01_SAT_item_analysis_TRAINER.xlsx
+++ b/content/W01/SAT/answer-key/C2_W01_SAT_item_analysis_TRAINER.xlsx
@@ -4762,7 +4762,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>a, b, c</t>
+          <t>b, c, d</t>
         </is>
       </c>
       <c r="G20">
@@ -5362,7 +5362,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>a, b, c</t>
+          <t>a, c, d</t>
         </is>
       </c>
       <c r="G30">
@@ -6442,7 +6442,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>a, b, c</t>
+          <t>b, c, d</t>
         </is>
       </c>
       <c r="G48">
@@ -6502,7 +6502,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>a, b, d</t>
+          <t>a, c, d</t>
         </is>
       </c>
       <c r="G49">

--- a/content/W01/SAT/answer-key/C2_W01_SAT_item_analysis_TRAINER.xlsx
+++ b/content/W01/SAT/answer-key/C2_W01_SAT_item_analysis_TRAINER.xlsx
@@ -509,7 +509,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BF39"/>
+  <dimension ref="A1:AN39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -550,7 +550,7 @@
         <v>1</v>
       </c>
       <c r="J2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K2" t="n">
         <v>2</v>
@@ -574,118 +574,64 @@
         <v>2</v>
       </c>
       <c r="R2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W2" t="n">
         <v>3</v>
       </c>
       <c r="X2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Y2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Z2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AA2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AB2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AC2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AD2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AE2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AF2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AG2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AH2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AI2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AJ2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AK2" t="n">
-        <v>4</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>4</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>4</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>4</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>4</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>4</v>
-      </c>
-      <c r="AQ2" t="n">
         <v>5</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>5</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>5</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>5</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>5</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>5</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>5</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>6</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>6</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>6</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>6</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>6</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>6</v>
       </c>
     </row>
     <row r="3">
@@ -711,255 +657,165 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
+          <t>[F]</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
           <t>[S]</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>[S]</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>[D]</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>[S]</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
         <is>
           <t>[F]</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>[SV]</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>[D]</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
         <is>
           <t>[F]</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>[F]</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>[F]</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>[S]</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>[F]</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>[S]</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>[S]</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>[F]</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
         <is>
           <t>[D]</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>[D]</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>[F]</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
         <is>
           <t>[S]</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>[F]</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
         <is>
           <t>[S]</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>[F]</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
         <is>
           <t>[S]</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>[S]</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
         <is>
           <t>[F]</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>[D]</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>[SV]</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
         <is>
           <t>[S]</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="AG3" t="inlineStr">
         <is>
           <t>[S]</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>[F]</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
         <is>
           <t>[S]</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="AJ3" t="inlineStr">
         <is>
           <t>[S]</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>[F]</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>[D]</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>[S]</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>[F]</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>[F]</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>[F]</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>[S]</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>[S]</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>[F]</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>[F]</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>[F]</t>
-        </is>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>[S]</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>[F]</t>
-        </is>
-      </c>
-      <c r="AG3" t="inlineStr">
-        <is>
-          <t>[SV]</t>
-        </is>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>[F]</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>[D]</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>[S]</t>
-        </is>
-      </c>
       <c r="AK3" t="inlineStr">
-        <is>
-          <t>[S]</t>
-        </is>
-      </c>
-      <c r="AL3" t="inlineStr">
-        <is>
-          <t>[D]</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>[S]</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>[F]</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>[F]</t>
-        </is>
-      </c>
-      <c r="AP3" t="inlineStr">
-        <is>
-          <t>[F]</t>
-        </is>
-      </c>
-      <c r="AQ3" t="inlineStr">
-        <is>
-          <t>[S]</t>
-        </is>
-      </c>
-      <c r="AR3" t="inlineStr">
-        <is>
-          <t>[F]</t>
-        </is>
-      </c>
-      <c r="AS3" t="inlineStr">
-        <is>
-          <t>[F]</t>
-        </is>
-      </c>
-      <c r="AT3" t="inlineStr">
-        <is>
-          <t>[S]</t>
-        </is>
-      </c>
-      <c r="AU3" t="inlineStr">
-        <is>
-          <t>[D]</t>
-        </is>
-      </c>
-      <c r="AV3" t="inlineStr">
-        <is>
-          <t>[F]</t>
-        </is>
-      </c>
-      <c r="AW3" t="inlineStr">
-        <is>
-          <t>[D]</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>[S]</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>[F]</t>
-        </is>
-      </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>[S]</t>
-        </is>
-      </c>
-      <c r="BA3" t="inlineStr">
-        <is>
-          <t>[S]</t>
-        </is>
-      </c>
-      <c r="BB3" t="inlineStr">
-        <is>
-          <t>[S]</t>
-        </is>
-      </c>
-      <c r="BC3" t="inlineStr">
         <is>
           <t>[S]</t>
         </is>
@@ -1153,105 +1009,15 @@
       </c>
       <c r="AL4" s="4" t="inlineStr">
         <is>
-          <t>Q37</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="AM4" s="4" t="inlineStr">
         <is>
-          <t>Q38</t>
+          <t>Answered</t>
         </is>
       </c>
       <c r="AN4" s="4" t="inlineStr">
-        <is>
-          <t>Q39</t>
-        </is>
-      </c>
-      <c r="AO4" s="4" t="inlineStr">
-        <is>
-          <t>Q40</t>
-        </is>
-      </c>
-      <c r="AP4" s="4" t="inlineStr">
-        <is>
-          <t>Q41</t>
-        </is>
-      </c>
-      <c r="AQ4" s="4" t="inlineStr">
-        <is>
-          <t>Q42</t>
-        </is>
-      </c>
-      <c r="AR4" s="4" t="inlineStr">
-        <is>
-          <t>Q43</t>
-        </is>
-      </c>
-      <c r="AS4" s="4" t="inlineStr">
-        <is>
-          <t>Q44</t>
-        </is>
-      </c>
-      <c r="AT4" s="4" t="inlineStr">
-        <is>
-          <t>Q45</t>
-        </is>
-      </c>
-      <c r="AU4" s="4" t="inlineStr">
-        <is>
-          <t>Q46</t>
-        </is>
-      </c>
-      <c r="AV4" s="4" t="inlineStr">
-        <is>
-          <t>Q47</t>
-        </is>
-      </c>
-      <c r="AW4" s="4" t="inlineStr">
-        <is>
-          <t>Q48</t>
-        </is>
-      </c>
-      <c r="AX4" s="4" t="inlineStr">
-        <is>
-          <t>Q49</t>
-        </is>
-      </c>
-      <c r="AY4" s="4" t="inlineStr">
-        <is>
-          <t>Q50</t>
-        </is>
-      </c>
-      <c r="AZ4" s="4" t="inlineStr">
-        <is>
-          <t>Q51</t>
-        </is>
-      </c>
-      <c r="BA4" s="4" t="inlineStr">
-        <is>
-          <t>Q52</t>
-        </is>
-      </c>
-      <c r="BB4" s="4" t="inlineStr">
-        <is>
-          <t>Q53</t>
-        </is>
-      </c>
-      <c r="BC4" s="4" t="inlineStr">
-        <is>
-          <t>Q54</t>
-        </is>
-      </c>
-      <c r="BD4" s="4" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="BE4" s="4" t="inlineStr">
-        <is>
-          <t>Answered</t>
-        </is>
-      </c>
-      <c r="BF4" s="4" t="inlineStr">
         <is>
           <t>Band</t>
         </is>
@@ -1297,34 +1063,16 @@
       <c r="AI5" s="5" t="n"/>
       <c r="AJ5" s="5" t="n"/>
       <c r="AK5" s="5" t="n"/>
-      <c r="AL5" s="5" t="n"/>
-      <c r="AM5" s="5" t="n"/>
-      <c r="AN5" s="5" t="n"/>
-      <c r="AO5" s="5" t="n"/>
-      <c r="AP5" s="5" t="n"/>
-      <c r="AQ5" s="5" t="n"/>
-      <c r="AR5" s="5" t="n"/>
-      <c r="AS5" s="5" t="n"/>
-      <c r="AT5" s="5" t="n"/>
-      <c r="AU5" s="5" t="n"/>
-      <c r="AV5" s="5" t="n"/>
-      <c r="AW5" s="5" t="n"/>
-      <c r="AX5" s="5" t="n"/>
-      <c r="AY5" s="5" t="n"/>
-      <c r="AZ5" s="5" t="n"/>
-      <c r="BA5" s="5" t="n"/>
-      <c r="BB5" s="5" t="n"/>
-      <c r="BC5" s="5" t="n"/>
-      <c r="BD5">
-        <f>IF(COUNT(B5:BC5)=0,"",SUM(B5:BC5))</f>
-        <v/>
-      </c>
-      <c r="BE5">
-        <f>COUNT(B5:BC5)</f>
-        <v/>
-      </c>
-      <c r="BF5">
-        <f>IF(OR(BD5="",COUNT($BD$5:$BD$39)&lt;3),"",IF(RANK(BD5,$BD$5:$BD$39,0)&lt;=ROUND(COUNT($BD$5:$BD$39)/3,0),"top",IF(RANK(BD5,$BD$5:$BD$39,1)&lt;=ROUND(COUNT($BD$5:$BD$39)/3,0),"bottom","middle")))</f>
+      <c r="AL5">
+        <f>IF(COUNT(B5:AK5)=0,"",SUM(B5:AK5))</f>
+        <v/>
+      </c>
+      <c r="AM5">
+        <f>COUNT(B5:AK5)</f>
+        <v/>
+      </c>
+      <c r="AN5">
+        <f>IF(OR(AL5="",COUNT($AL$5:$AL$39)&lt;3),"",IF(RANK(AL5,$AL$5:$AL$39,0)&lt;=ROUND(COUNT($AL$5:$AL$39)/3,0),"top",IF(RANK(AL5,$AL$5:$AL$39,1)&lt;=ROUND(COUNT($AL$5:$AL$39)/3,0),"bottom","middle")))</f>
         <v/>
       </c>
     </row>
@@ -1368,34 +1116,16 @@
       <c r="AI6" s="5" t="n"/>
       <c r="AJ6" s="5" t="n"/>
       <c r="AK6" s="5" t="n"/>
-      <c r="AL6" s="5" t="n"/>
-      <c r="AM6" s="5" t="n"/>
-      <c r="AN6" s="5" t="n"/>
-      <c r="AO6" s="5" t="n"/>
-      <c r="AP6" s="5" t="n"/>
-      <c r="AQ6" s="5" t="n"/>
-      <c r="AR6" s="5" t="n"/>
-      <c r="AS6" s="5" t="n"/>
-      <c r="AT6" s="5" t="n"/>
-      <c r="AU6" s="5" t="n"/>
-      <c r="AV6" s="5" t="n"/>
-      <c r="AW6" s="5" t="n"/>
-      <c r="AX6" s="5" t="n"/>
-      <c r="AY6" s="5" t="n"/>
-      <c r="AZ6" s="5" t="n"/>
-      <c r="BA6" s="5" t="n"/>
-      <c r="BB6" s="5" t="n"/>
-      <c r="BC6" s="5" t="n"/>
-      <c r="BD6">
-        <f>IF(COUNT(B6:BC6)=0,"",SUM(B6:BC6))</f>
-        <v/>
-      </c>
-      <c r="BE6">
-        <f>COUNT(B6:BC6)</f>
-        <v/>
-      </c>
-      <c r="BF6">
-        <f>IF(OR(BD6="",COUNT($BD$5:$BD$39)&lt;3),"",IF(RANK(BD6,$BD$5:$BD$39,0)&lt;=ROUND(COUNT($BD$5:$BD$39)/3,0),"top",IF(RANK(BD6,$BD$5:$BD$39,1)&lt;=ROUND(COUNT($BD$5:$BD$39)/3,0),"bottom","middle")))</f>
+      <c r="AL6">
+        <f>IF(COUNT(B6:AK6)=0,"",SUM(B6:AK6))</f>
+        <v/>
+      </c>
+      <c r="AM6">
+        <f>COUNT(B6:AK6)</f>
+        <v/>
+      </c>
+      <c r="AN6">
+        <f>IF(OR(AL6="",COUNT($AL$5:$AL$39)&lt;3),"",IF(RANK(AL6,$AL$5:$AL$39,0)&lt;=ROUND(COUNT($AL$5:$AL$39)/3,0),"top",IF(RANK(AL6,$AL$5:$AL$39,1)&lt;=ROUND(COUNT($AL$5:$AL$39)/3,0),"bottom","middle")))</f>
         <v/>
       </c>
     </row>
@@ -1439,34 +1169,16 @@
       <c r="AI7" s="5" t="n"/>
       <c r="AJ7" s="5" t="n"/>
       <c r="AK7" s="5" t="n"/>
-      <c r="AL7" s="5" t="n"/>
-      <c r="AM7" s="5" t="n"/>
-      <c r="AN7" s="5" t="n"/>
-      <c r="AO7" s="5" t="n"/>
-      <c r="AP7" s="5" t="n"/>
-      <c r="AQ7" s="5" t="n"/>
-      <c r="AR7" s="5" t="n"/>
-      <c r="AS7" s="5" t="n"/>
-      <c r="AT7" s="5" t="n"/>
-      <c r="AU7" s="5" t="n"/>
-      <c r="AV7" s="5" t="n"/>
-      <c r="AW7" s="5" t="n"/>
-      <c r="AX7" s="5" t="n"/>
-      <c r="AY7" s="5" t="n"/>
-      <c r="AZ7" s="5" t="n"/>
-      <c r="BA7" s="5" t="n"/>
-      <c r="BB7" s="5" t="n"/>
-      <c r="BC7" s="5" t="n"/>
-      <c r="BD7">
-        <f>IF(COUNT(B7:BC7)=0,"",SUM(B7:BC7))</f>
-        <v/>
-      </c>
-      <c r="BE7">
-        <f>COUNT(B7:BC7)</f>
-        <v/>
-      </c>
-      <c r="BF7">
-        <f>IF(OR(BD7="",COUNT($BD$5:$BD$39)&lt;3),"",IF(RANK(BD7,$BD$5:$BD$39,0)&lt;=ROUND(COUNT($BD$5:$BD$39)/3,0),"top",IF(RANK(BD7,$BD$5:$BD$39,1)&lt;=ROUND(COUNT($BD$5:$BD$39)/3,0),"bottom","middle")))</f>
+      <c r="AL7">
+        <f>IF(COUNT(B7:AK7)=0,"",SUM(B7:AK7))</f>
+        <v/>
+      </c>
+      <c r="AM7">
+        <f>COUNT(B7:AK7)</f>
+        <v/>
+      </c>
+      <c r="AN7">
+        <f>IF(OR(AL7="",COUNT($AL$5:$AL$39)&lt;3),"",IF(RANK(AL7,$AL$5:$AL$39,0)&lt;=ROUND(COUNT($AL$5:$AL$39)/3,0),"top",IF(RANK(AL7,$AL$5:$AL$39,1)&lt;=ROUND(COUNT($AL$5:$AL$39)/3,0),"bottom","middle")))</f>
         <v/>
       </c>
     </row>
@@ -1510,34 +1222,16 @@
       <c r="AI8" s="5" t="n"/>
       <c r="AJ8" s="5" t="n"/>
       <c r="AK8" s="5" t="n"/>
-      <c r="AL8" s="5" t="n"/>
-      <c r="AM8" s="5" t="n"/>
-      <c r="AN8" s="5" t="n"/>
-      <c r="AO8" s="5" t="n"/>
-      <c r="AP8" s="5" t="n"/>
-      <c r="AQ8" s="5" t="n"/>
-      <c r="AR8" s="5" t="n"/>
-      <c r="AS8" s="5" t="n"/>
-      <c r="AT8" s="5" t="n"/>
-      <c r="AU8" s="5" t="n"/>
-      <c r="AV8" s="5" t="n"/>
-      <c r="AW8" s="5" t="n"/>
-      <c r="AX8" s="5" t="n"/>
-      <c r="AY8" s="5" t="n"/>
-      <c r="AZ8" s="5" t="n"/>
-      <c r="BA8" s="5" t="n"/>
-      <c r="BB8" s="5" t="n"/>
-      <c r="BC8" s="5" t="n"/>
-      <c r="BD8">
-        <f>IF(COUNT(B8:BC8)=0,"",SUM(B8:BC8))</f>
-        <v/>
-      </c>
-      <c r="BE8">
-        <f>COUNT(B8:BC8)</f>
-        <v/>
-      </c>
-      <c r="BF8">
-        <f>IF(OR(BD8="",COUNT($BD$5:$BD$39)&lt;3),"",IF(RANK(BD8,$BD$5:$BD$39,0)&lt;=ROUND(COUNT($BD$5:$BD$39)/3,0),"top",IF(RANK(BD8,$BD$5:$BD$39,1)&lt;=ROUND(COUNT($BD$5:$BD$39)/3,0),"bottom","middle")))</f>
+      <c r="AL8">
+        <f>IF(COUNT(B8:AK8)=0,"",SUM(B8:AK8))</f>
+        <v/>
+      </c>
+      <c r="AM8">
+        <f>COUNT(B8:AK8)</f>
+        <v/>
+      </c>
+      <c r="AN8">
+        <f>IF(OR(AL8="",COUNT($AL$5:$AL$39)&lt;3),"",IF(RANK(AL8,$AL$5:$AL$39,0)&lt;=ROUND(COUNT($AL$5:$AL$39)/3,0),"top",IF(RANK(AL8,$AL$5:$AL$39,1)&lt;=ROUND(COUNT($AL$5:$AL$39)/3,0),"bottom","middle")))</f>
         <v/>
       </c>
     </row>
@@ -1581,34 +1275,16 @@
       <c r="AI9" s="5" t="n"/>
       <c r="AJ9" s="5" t="n"/>
       <c r="AK9" s="5" t="n"/>
-      <c r="AL9" s="5" t="n"/>
-      <c r="AM9" s="5" t="n"/>
-      <c r="AN9" s="5" t="n"/>
-      <c r="AO9" s="5" t="n"/>
-      <c r="AP9" s="5" t="n"/>
-      <c r="AQ9" s="5" t="n"/>
-      <c r="AR9" s="5" t="n"/>
-      <c r="AS9" s="5" t="n"/>
-      <c r="AT9" s="5" t="n"/>
-      <c r="AU9" s="5" t="n"/>
-      <c r="AV9" s="5" t="n"/>
-      <c r="AW9" s="5" t="n"/>
-      <c r="AX9" s="5" t="n"/>
-      <c r="AY9" s="5" t="n"/>
-      <c r="AZ9" s="5" t="n"/>
-      <c r="BA9" s="5" t="n"/>
-      <c r="BB9" s="5" t="n"/>
-      <c r="BC9" s="5" t="n"/>
-      <c r="BD9">
-        <f>IF(COUNT(B9:BC9)=0,"",SUM(B9:BC9))</f>
-        <v/>
-      </c>
-      <c r="BE9">
-        <f>COUNT(B9:BC9)</f>
-        <v/>
-      </c>
-      <c r="BF9">
-        <f>IF(OR(BD9="",COUNT($BD$5:$BD$39)&lt;3),"",IF(RANK(BD9,$BD$5:$BD$39,0)&lt;=ROUND(COUNT($BD$5:$BD$39)/3,0),"top",IF(RANK(BD9,$BD$5:$BD$39,1)&lt;=ROUND(COUNT($BD$5:$BD$39)/3,0),"bottom","middle")))</f>
+      <c r="AL9">
+        <f>IF(COUNT(B9:AK9)=0,"",SUM(B9:AK9))</f>
+        <v/>
+      </c>
+      <c r="AM9">
+        <f>COUNT(B9:AK9)</f>
+        <v/>
+      </c>
+      <c r="AN9">
+        <f>IF(OR(AL9="",COUNT($AL$5:$AL$39)&lt;3),"",IF(RANK(AL9,$AL$5:$AL$39,0)&lt;=ROUND(COUNT($AL$5:$AL$39)/3,0),"top",IF(RANK(AL9,$AL$5:$AL$39,1)&lt;=ROUND(COUNT($AL$5:$AL$39)/3,0),"bottom","middle")))</f>
         <v/>
       </c>
     </row>
@@ -1652,34 +1328,16 @@
       <c r="AI10" s="5" t="n"/>
       <c r="AJ10" s="5" t="n"/>
       <c r="AK10" s="5" t="n"/>
-      <c r="AL10" s="5" t="n"/>
-      <c r="AM10" s="5" t="n"/>
-      <c r="AN10" s="5" t="n"/>
-      <c r="AO10" s="5" t="n"/>
-      <c r="AP10" s="5" t="n"/>
-      <c r="AQ10" s="5" t="n"/>
-      <c r="AR10" s="5" t="n"/>
-      <c r="AS10" s="5" t="n"/>
-      <c r="AT10" s="5" t="n"/>
-      <c r="AU10" s="5" t="n"/>
-      <c r="AV10" s="5" t="n"/>
-      <c r="AW10" s="5" t="n"/>
-      <c r="AX10" s="5" t="n"/>
-      <c r="AY10" s="5" t="n"/>
-      <c r="AZ10" s="5" t="n"/>
-      <c r="BA10" s="5" t="n"/>
-      <c r="BB10" s="5" t="n"/>
-      <c r="BC10" s="5" t="n"/>
-      <c r="BD10">
-        <f>IF(COUNT(B10:BC10)=0,"",SUM(B10:BC10))</f>
-        <v/>
-      </c>
-      <c r="BE10">
-        <f>COUNT(B10:BC10)</f>
-        <v/>
-      </c>
-      <c r="BF10">
-        <f>IF(OR(BD10="",COUNT($BD$5:$BD$39)&lt;3),"",IF(RANK(BD10,$BD$5:$BD$39,0)&lt;=ROUND(COUNT($BD$5:$BD$39)/3,0),"top",IF(RANK(BD10,$BD$5:$BD$39,1)&lt;=ROUND(COUNT($BD$5:$BD$39)/3,0),"bottom","middle")))</f>
+      <c r="AL10">
+        <f>IF(COUNT(B10:AK10)=0,"",SUM(B10:AK10))</f>
+        <v/>
+      </c>
+      <c r="AM10">
+        <f>COUNT(B10:AK10)</f>
+        <v/>
+      </c>
+      <c r="AN10">
+        <f>IF(OR(AL10="",COUNT($AL$5:$AL$39)&lt;3),"",IF(RANK(AL10,$AL$5:$AL$39,0)&lt;=ROUND(COUNT($AL$5:$AL$39)/3,0),"top",IF(RANK(AL10,$AL$5:$AL$39,1)&lt;=ROUND(COUNT($AL$5:$AL$39)/3,0),"bottom","middle")))</f>
         <v/>
       </c>
     </row>
@@ -1723,34 +1381,16 @@
       <c r="AI11" s="5" t="n"/>
       <c r="AJ11" s="5" t="n"/>
       <c r="AK11" s="5" t="n"/>
-      <c r="AL11" s="5" t="n"/>
-      <c r="AM11" s="5" t="n"/>
-      <c r="AN11" s="5" t="n"/>
-      <c r="AO11" s="5" t="n"/>
-      <c r="AP11" s="5" t="n"/>
-      <c r="AQ11" s="5" t="n"/>
-      <c r="AR11" s="5" t="n"/>
-      <c r="AS11" s="5" t="n"/>
-      <c r="AT11" s="5" t="n"/>
-      <c r="AU11" s="5" t="n"/>
-      <c r="AV11" s="5" t="n"/>
-      <c r="AW11" s="5" t="n"/>
-      <c r="AX11" s="5" t="n"/>
-      <c r="AY11" s="5" t="n"/>
-      <c r="AZ11" s="5" t="n"/>
-      <c r="BA11" s="5" t="n"/>
-      <c r="BB11" s="5" t="n"/>
-      <c r="BC11" s="5" t="n"/>
-      <c r="BD11">
-        <f>IF(COUNT(B11:BC11)=0,"",SUM(B11:BC11))</f>
-        <v/>
-      </c>
-      <c r="BE11">
-        <f>COUNT(B11:BC11)</f>
-        <v/>
-      </c>
-      <c r="BF11">
-        <f>IF(OR(BD11="",COUNT($BD$5:$BD$39)&lt;3),"",IF(RANK(BD11,$BD$5:$BD$39,0)&lt;=ROUND(COUNT($BD$5:$BD$39)/3,0),"top",IF(RANK(BD11,$BD$5:$BD$39,1)&lt;=ROUND(COUNT($BD$5:$BD$39)/3,0),"bottom","middle")))</f>
+      <c r="AL11">
+        <f>IF(COUNT(B11:AK11)=0,"",SUM(B11:AK11))</f>
+        <v/>
+      </c>
+      <c r="AM11">
+        <f>COUNT(B11:AK11)</f>
+        <v/>
+      </c>
+      <c r="AN11">
+        <f>IF(OR(AL11="",COUNT($AL$5:$AL$39)&lt;3),"",IF(RANK(AL11,$AL$5:$AL$39,0)&lt;=ROUND(COUNT($AL$5:$AL$39)/3,0),"top",IF(RANK(AL11,$AL$5:$AL$39,1)&lt;=ROUND(COUNT($AL$5:$AL$39)/3,0),"bottom","middle")))</f>
         <v/>
       </c>
     </row>
@@ -1794,34 +1434,16 @@
       <c r="AI12" s="5" t="n"/>
       <c r="AJ12" s="5" t="n"/>
       <c r="AK12" s="5" t="n"/>
-      <c r="AL12" s="5" t="n"/>
-      <c r="AM12" s="5" t="n"/>
-      <c r="AN12" s="5" t="n"/>
-      <c r="AO12" s="5" t="n"/>
-      <c r="AP12" s="5" t="n"/>
-      <c r="AQ12" s="5" t="n"/>
-      <c r="AR12" s="5" t="n"/>
-      <c r="AS12" s="5" t="n"/>
-      <c r="AT12" s="5" t="n"/>
-      <c r="AU12" s="5" t="n"/>
-      <c r="AV12" s="5" t="n"/>
-      <c r="AW12" s="5" t="n"/>
-      <c r="AX12" s="5" t="n"/>
-      <c r="AY12" s="5" t="n"/>
-      <c r="AZ12" s="5" t="n"/>
-      <c r="BA12" s="5" t="n"/>
-      <c r="BB12" s="5" t="n"/>
-      <c r="BC12" s="5" t="n"/>
-      <c r="BD12">
-        <f>IF(COUNT(B12:BC12)=0,"",SUM(B12:BC12))</f>
-        <v/>
-      </c>
-      <c r="BE12">
-        <f>COUNT(B12:BC12)</f>
-        <v/>
-      </c>
-      <c r="BF12">
-        <f>IF(OR(BD12="",COUNT($BD$5:$BD$39)&lt;3),"",IF(RANK(BD12,$BD$5:$BD$39,0)&lt;=ROUND(COUNT($BD$5:$BD$39)/3,0),"top",IF(RANK(BD12,$BD$5:$BD$39,1)&lt;=ROUND(COUNT($BD$5:$BD$39)/3,0),"bottom","middle")))</f>
+      <c r="AL12">
+        <f>IF(COUNT(B12:AK12)=0,"",SUM(B12:AK12))</f>
+        <v/>
+      </c>
+      <c r="AM12">
+        <f>COUNT(B12:AK12)</f>
+        <v/>
+      </c>
+      <c r="AN12">
+        <f>IF(OR(AL12="",COUNT($AL$5:$AL$39)&lt;3),"",IF(RANK(AL12,$AL$5:$AL$39,0)&lt;=ROUND(COUNT($AL$5:$AL$39)/3,0),"top",IF(RANK(AL12,$AL$5:$AL$39,1)&lt;=ROUND(COUNT($AL$5:$AL$39)/3,0),"bottom","middle")))</f>
         <v/>
       </c>
     </row>
@@ -1865,34 +1487,16 @@
       <c r="AI13" s="5" t="n"/>
       <c r="AJ13" s="5" t="n"/>
       <c r="AK13" s="5" t="n"/>
-      <c r="AL13" s="5" t="n"/>
-      <c r="AM13" s="5" t="n"/>
-      <c r="AN13" s="5" t="n"/>
-      <c r="AO13" s="5" t="n"/>
-      <c r="AP13" s="5" t="n"/>
-      <c r="AQ13" s="5" t="n"/>
-      <c r="AR13" s="5" t="n"/>
-      <c r="AS13" s="5" t="n"/>
-      <c r="AT13" s="5" t="n"/>
-      <c r="AU13" s="5" t="n"/>
-      <c r="AV13" s="5" t="n"/>
-      <c r="AW13" s="5" t="n"/>
-      <c r="AX13" s="5" t="n"/>
-      <c r="AY13" s="5" t="n"/>
-      <c r="AZ13" s="5" t="n"/>
-      <c r="BA13" s="5" t="n"/>
-      <c r="BB13" s="5" t="n"/>
-      <c r="BC13" s="5" t="n"/>
-      <c r="BD13">
-        <f>IF(COUNT(B13:BC13)=0,"",SUM(B13:BC13))</f>
-        <v/>
-      </c>
-      <c r="BE13">
-        <f>COUNT(B13:BC13)</f>
-        <v/>
-      </c>
-      <c r="BF13">
-        <f>IF(OR(BD13="",COUNT($BD$5:$BD$39)&lt;3),"",IF(RANK(BD13,$BD$5:$BD$39,0)&lt;=ROUND(COUNT($BD$5:$BD$39)/3,0),"top",IF(RANK(BD13,$BD$5:$BD$39,1)&lt;=ROUND(COUNT($BD$5:$BD$39)/3,0),"bottom","middle")))</f>
+      <c r="AL13">
+        <f>IF(COUNT(B13:AK13)=0,"",SUM(B13:AK13))</f>
+        <v/>
+      </c>
+      <c r="AM13">
+        <f>COUNT(B13:AK13)</f>
+        <v/>
+      </c>
+      <c r="AN13">
+        <f>IF(OR(AL13="",COUNT($AL$5:$AL$39)&lt;3),"",IF(RANK(AL13,$AL$5:$AL$39,0)&lt;=ROUND(COUNT($AL$5:$AL$39)/3,0),"top",IF(RANK(AL13,$AL$5:$AL$39,1)&lt;=ROUND(COUNT($AL$5:$AL$39)/3,0),"bottom","middle")))</f>
         <v/>
       </c>
     </row>
@@ -1936,34 +1540,16 @@
       <c r="AI14" s="5" t="n"/>
       <c r="AJ14" s="5" t="n"/>
       <c r="AK14" s="5" t="n"/>
-      <c r="AL14" s="5" t="n"/>
-      <c r="AM14" s="5" t="n"/>
-      <c r="AN14" s="5" t="n"/>
-      <c r="AO14" s="5" t="n"/>
-      <c r="AP14" s="5" t="n"/>
-      <c r="AQ14" s="5" t="n"/>
-      <c r="AR14" s="5" t="n"/>
-      <c r="AS14" s="5" t="n"/>
-      <c r="AT14" s="5" t="n"/>
-      <c r="AU14" s="5" t="n"/>
-      <c r="AV14" s="5" t="n"/>
-      <c r="AW14" s="5" t="n"/>
-      <c r="AX14" s="5" t="n"/>
-      <c r="AY14" s="5" t="n"/>
-      <c r="AZ14" s="5" t="n"/>
-      <c r="BA14" s="5" t="n"/>
-      <c r="BB14" s="5" t="n"/>
-      <c r="BC14" s="5" t="n"/>
-      <c r="BD14">
-        <f>IF(COUNT(B14:BC14)=0,"",SUM(B14:BC14))</f>
-        <v/>
-      </c>
-      <c r="BE14">
-        <f>COUNT(B14:BC14)</f>
-        <v/>
-      </c>
-      <c r="BF14">
-        <f>IF(OR(BD14="",COUNT($BD$5:$BD$39)&lt;3),"",IF(RANK(BD14,$BD$5:$BD$39,0)&lt;=ROUND(COUNT($BD$5:$BD$39)/3,0),"top",IF(RANK(BD14,$BD$5:$BD$39,1)&lt;=ROUND(COUNT($BD$5:$BD$39)/3,0),"bottom","middle")))</f>
+      <c r="AL14">
+        <f>IF(COUNT(B14:AK14)=0,"",SUM(B14:AK14))</f>
+        <v/>
+      </c>
+      <c r="AM14">
+        <f>COUNT(B14:AK14)</f>
+        <v/>
+      </c>
+      <c r="AN14">
+        <f>IF(OR(AL14="",COUNT($AL$5:$AL$39)&lt;3),"",IF(RANK(AL14,$AL$5:$AL$39,0)&lt;=ROUND(COUNT($AL$5:$AL$39)/3,0),"top",IF(RANK(AL14,$AL$5:$AL$39,1)&lt;=ROUND(COUNT($AL$5:$AL$39)/3,0),"bottom","middle")))</f>
         <v/>
       </c>
     </row>
@@ -2007,34 +1593,16 @@
       <c r="AI15" s="5" t="n"/>
       <c r="AJ15" s="5" t="n"/>
       <c r="AK15" s="5" t="n"/>
-      <c r="AL15" s="5" t="n"/>
-      <c r="AM15" s="5" t="n"/>
-      <c r="AN15" s="5" t="n"/>
-      <c r="AO15" s="5" t="n"/>
-      <c r="AP15" s="5" t="n"/>
-      <c r="AQ15" s="5" t="n"/>
-      <c r="AR15" s="5" t="n"/>
-      <c r="AS15" s="5" t="n"/>
-      <c r="AT15" s="5" t="n"/>
-      <c r="AU15" s="5" t="n"/>
-      <c r="AV15" s="5" t="n"/>
-      <c r="AW15" s="5" t="n"/>
-      <c r="AX15" s="5" t="n"/>
-      <c r="AY15" s="5" t="n"/>
-      <c r="AZ15" s="5" t="n"/>
-      <c r="BA15" s="5" t="n"/>
-      <c r="BB15" s="5" t="n"/>
-      <c r="BC15" s="5" t="n"/>
-      <c r="BD15">
-        <f>IF(COUNT(B15:BC15)=0,"",SUM(B15:BC15))</f>
-        <v/>
-      </c>
-      <c r="BE15">
-        <f>COUNT(B15:BC15)</f>
-        <v/>
-      </c>
-      <c r="BF15">
-        <f>IF(OR(BD15="",COUNT($BD$5:$BD$39)&lt;3),"",IF(RANK(BD15,$BD$5:$BD$39,0)&lt;=ROUND(COUNT($BD$5:$BD$39)/3,0),"top",IF(RANK(BD15,$BD$5:$BD$39,1)&lt;=ROUND(COUNT($BD$5:$BD$39)/3,0),"bottom","middle")))</f>
+      <c r="AL15">
+        <f>IF(COUNT(B15:AK15)=0,"",SUM(B15:AK15))</f>
+        <v/>
+      </c>
+      <c r="AM15">
+        <f>COUNT(B15:AK15)</f>
+        <v/>
+      </c>
+      <c r="AN15">
+        <f>IF(OR(AL15="",COUNT($AL$5:$AL$39)&lt;3),"",IF(RANK(AL15,$AL$5:$AL$39,0)&lt;=ROUND(COUNT($AL$5:$AL$39)/3,0),"top",IF(RANK(AL15,$AL$5:$AL$39,1)&lt;=ROUND(COUNT($AL$5:$AL$39)/3,0),"bottom","middle")))</f>
         <v/>
       </c>
     </row>
@@ -2078,34 +1646,16 @@
       <c r="AI16" s="5" t="n"/>
       <c r="AJ16" s="5" t="n"/>
       <c r="AK16" s="5" t="n"/>
-      <c r="AL16" s="5" t="n"/>
-      <c r="AM16" s="5" t="n"/>
-      <c r="AN16" s="5" t="n"/>
-      <c r="AO16" s="5" t="n"/>
-      <c r="AP16" s="5" t="n"/>
-      <c r="AQ16" s="5" t="n"/>
-      <c r="AR16" s="5" t="n"/>
-      <c r="AS16" s="5" t="n"/>
-      <c r="AT16" s="5" t="n"/>
-      <c r="AU16" s="5" t="n"/>
-      <c r="AV16" s="5" t="n"/>
-      <c r="AW16" s="5" t="n"/>
-      <c r="AX16" s="5" t="n"/>
-      <c r="AY16" s="5" t="n"/>
-      <c r="AZ16" s="5" t="n"/>
-      <c r="BA16" s="5" t="n"/>
-      <c r="BB16" s="5" t="n"/>
-      <c r="BC16" s="5" t="n"/>
-      <c r="BD16">
-        <f>IF(COUNT(B16:BC16)=0,"",SUM(B16:BC16))</f>
-        <v/>
-      </c>
-      <c r="BE16">
-        <f>COUNT(B16:BC16)</f>
-        <v/>
-      </c>
-      <c r="BF16">
-        <f>IF(OR(BD16="",COUNT($BD$5:$BD$39)&lt;3),"",IF(RANK(BD16,$BD$5:$BD$39,0)&lt;=ROUND(COUNT($BD$5:$BD$39)/3,0),"top",IF(RANK(BD16,$BD$5:$BD$39,1)&lt;=ROUND(COUNT($BD$5:$BD$39)/3,0),"bottom","middle")))</f>
+      <c r="AL16">
+        <f>IF(COUNT(B16:AK16)=0,"",SUM(B16:AK16))</f>
+        <v/>
+      </c>
+      <c r="AM16">
+        <f>COUNT(B16:AK16)</f>
+        <v/>
+      </c>
+      <c r="AN16">
+        <f>IF(OR(AL16="",COUNT($AL$5:$AL$39)&lt;3),"",IF(RANK(AL16,$AL$5:$AL$39,0)&lt;=ROUND(COUNT($AL$5:$AL$39)/3,0),"top",IF(RANK(AL16,$AL$5:$AL$39,1)&lt;=ROUND(COUNT($AL$5:$AL$39)/3,0),"bottom","middle")))</f>
         <v/>
       </c>
     </row>
@@ -2149,34 +1699,16 @@
       <c r="AI17" s="5" t="n"/>
       <c r="AJ17" s="5" t="n"/>
       <c r="AK17" s="5" t="n"/>
-      <c r="AL17" s="5" t="n"/>
-      <c r="AM17" s="5" t="n"/>
-      <c r="AN17" s="5" t="n"/>
-      <c r="AO17" s="5" t="n"/>
-      <c r="AP17" s="5" t="n"/>
-      <c r="AQ17" s="5" t="n"/>
-      <c r="AR17" s="5" t="n"/>
-      <c r="AS17" s="5" t="n"/>
-      <c r="AT17" s="5" t="n"/>
-      <c r="AU17" s="5" t="n"/>
-      <c r="AV17" s="5" t="n"/>
-      <c r="AW17" s="5" t="n"/>
-      <c r="AX17" s="5" t="n"/>
-      <c r="AY17" s="5" t="n"/>
-      <c r="AZ17" s="5" t="n"/>
-      <c r="BA17" s="5" t="n"/>
-      <c r="BB17" s="5" t="n"/>
-      <c r="BC17" s="5" t="n"/>
-      <c r="BD17">
-        <f>IF(COUNT(B17:BC17)=0,"",SUM(B17:BC17))</f>
-        <v/>
-      </c>
-      <c r="BE17">
-        <f>COUNT(B17:BC17)</f>
-        <v/>
-      </c>
-      <c r="BF17">
-        <f>IF(OR(BD17="",COUNT($BD$5:$BD$39)&lt;3),"",IF(RANK(BD17,$BD$5:$BD$39,0)&lt;=ROUND(COUNT($BD$5:$BD$39)/3,0),"top",IF(RANK(BD17,$BD$5:$BD$39,1)&lt;=ROUND(COUNT($BD$5:$BD$39)/3,0),"bottom","middle")))</f>
+      <c r="AL17">
+        <f>IF(COUNT(B17:AK17)=0,"",SUM(B17:AK17))</f>
+        <v/>
+      </c>
+      <c r="AM17">
+        <f>COUNT(B17:AK17)</f>
+        <v/>
+      </c>
+      <c r="AN17">
+        <f>IF(OR(AL17="",COUNT($AL$5:$AL$39)&lt;3),"",IF(RANK(AL17,$AL$5:$AL$39,0)&lt;=ROUND(COUNT($AL$5:$AL$39)/3,0),"top",IF(RANK(AL17,$AL$5:$AL$39,1)&lt;=ROUND(COUNT($AL$5:$AL$39)/3,0),"bottom","middle")))</f>
         <v/>
       </c>
     </row>
@@ -2220,34 +1752,16 @@
       <c r="AI18" s="5" t="n"/>
       <c r="AJ18" s="5" t="n"/>
       <c r="AK18" s="5" t="n"/>
-      <c r="AL18" s="5" t="n"/>
-      <c r="AM18" s="5" t="n"/>
-      <c r="AN18" s="5" t="n"/>
-      <c r="AO18" s="5" t="n"/>
-      <c r="AP18" s="5" t="n"/>
-      <c r="AQ18" s="5" t="n"/>
-      <c r="AR18" s="5" t="n"/>
-      <c r="AS18" s="5" t="n"/>
-      <c r="AT18" s="5" t="n"/>
-      <c r="AU18" s="5" t="n"/>
-      <c r="AV18" s="5" t="n"/>
-      <c r="AW18" s="5" t="n"/>
-      <c r="AX18" s="5" t="n"/>
-      <c r="AY18" s="5" t="n"/>
-      <c r="AZ18" s="5" t="n"/>
-      <c r="BA18" s="5" t="n"/>
-      <c r="BB18" s="5" t="n"/>
-      <c r="BC18" s="5" t="n"/>
-      <c r="BD18">
-        <f>IF(COUNT(B18:BC18)=0,"",SUM(B18:BC18))</f>
-        <v/>
-      </c>
-      <c r="BE18">
-        <f>COUNT(B18:BC18)</f>
-        <v/>
-      </c>
-      <c r="BF18">
-        <f>IF(OR(BD18="",COUNT($BD$5:$BD$39)&lt;3),"",IF(RANK(BD18,$BD$5:$BD$39,0)&lt;=ROUND(COUNT($BD$5:$BD$39)/3,0),"top",IF(RANK(BD18,$BD$5:$BD$39,1)&lt;=ROUND(COUNT($BD$5:$BD$39)/3,0),"bottom","middle")))</f>
+      <c r="AL18">
+        <f>IF(COUNT(B18:AK18)=0,"",SUM(B18:AK18))</f>
+        <v/>
+      </c>
+      <c r="AM18">
+        <f>COUNT(B18:AK18)</f>
+        <v/>
+      </c>
+      <c r="AN18">
+        <f>IF(OR(AL18="",COUNT($AL$5:$AL$39)&lt;3),"",IF(RANK(AL18,$AL$5:$AL$39,0)&lt;=ROUND(COUNT($AL$5:$AL$39)/3,0),"top",IF(RANK(AL18,$AL$5:$AL$39,1)&lt;=ROUND(COUNT($AL$5:$AL$39)/3,0),"bottom","middle")))</f>
         <v/>
       </c>
     </row>
@@ -2291,34 +1805,16 @@
       <c r="AI19" s="5" t="n"/>
       <c r="AJ19" s="5" t="n"/>
       <c r="AK19" s="5" t="n"/>
-      <c r="AL19" s="5" t="n"/>
-      <c r="AM19" s="5" t="n"/>
-      <c r="AN19" s="5" t="n"/>
-      <c r="AO19" s="5" t="n"/>
-      <c r="AP19" s="5" t="n"/>
-      <c r="AQ19" s="5" t="n"/>
-      <c r="AR19" s="5" t="n"/>
-      <c r="AS19" s="5" t="n"/>
-      <c r="AT19" s="5" t="n"/>
-      <c r="AU19" s="5" t="n"/>
-      <c r="AV19" s="5" t="n"/>
-      <c r="AW19" s="5" t="n"/>
-      <c r="AX19" s="5" t="n"/>
-      <c r="AY19" s="5" t="n"/>
-      <c r="AZ19" s="5" t="n"/>
-      <c r="BA19" s="5" t="n"/>
-      <c r="BB19" s="5" t="n"/>
-      <c r="BC19" s="5" t="n"/>
-      <c r="BD19">
-        <f>IF(COUNT(B19:BC19)=0,"",SUM(B19:BC19))</f>
-        <v/>
-      </c>
-      <c r="BE19">
-        <f>COUNT(B19:BC19)</f>
-        <v/>
-      </c>
-      <c r="BF19">
-        <f>IF(OR(BD19="",COUNT($BD$5:$BD$39)&lt;3),"",IF(RANK(BD19,$BD$5:$BD$39,0)&lt;=ROUND(COUNT($BD$5:$BD$39)/3,0),"top",IF(RANK(BD19,$BD$5:$BD$39,1)&lt;=ROUND(COUNT($BD$5:$BD$39)/3,0),"bottom","middle")))</f>
+      <c r="AL19">
+        <f>IF(COUNT(B19:AK19)=0,"",SUM(B19:AK19))</f>
+        <v/>
+      </c>
+      <c r="AM19">
+        <f>COUNT(B19:AK19)</f>
+        <v/>
+      </c>
+      <c r="AN19">
+        <f>IF(OR(AL19="",COUNT($AL$5:$AL$39)&lt;3),"",IF(RANK(AL19,$AL$5:$AL$39,0)&lt;=ROUND(COUNT($AL$5:$AL$39)/3,0),"top",IF(RANK(AL19,$AL$5:$AL$39,1)&lt;=ROUND(COUNT($AL$5:$AL$39)/3,0),"bottom","middle")))</f>
         <v/>
       </c>
     </row>
@@ -2362,34 +1858,16 @@
       <c r="AI20" s="5" t="n"/>
       <c r="AJ20" s="5" t="n"/>
       <c r="AK20" s="5" t="n"/>
-      <c r="AL20" s="5" t="n"/>
-      <c r="AM20" s="5" t="n"/>
-      <c r="AN20" s="5" t="n"/>
-      <c r="AO20" s="5" t="n"/>
-      <c r="AP20" s="5" t="n"/>
-      <c r="AQ20" s="5" t="n"/>
-      <c r="AR20" s="5" t="n"/>
-      <c r="AS20" s="5" t="n"/>
-      <c r="AT20" s="5" t="n"/>
-      <c r="AU20" s="5" t="n"/>
-      <c r="AV20" s="5" t="n"/>
-      <c r="AW20" s="5" t="n"/>
-      <c r="AX20" s="5" t="n"/>
-      <c r="AY20" s="5" t="n"/>
-      <c r="AZ20" s="5" t="n"/>
-      <c r="BA20" s="5" t="n"/>
-      <c r="BB20" s="5" t="n"/>
-      <c r="BC20" s="5" t="n"/>
-      <c r="BD20">
-        <f>IF(COUNT(B20:BC20)=0,"",SUM(B20:BC20))</f>
-        <v/>
-      </c>
-      <c r="BE20">
-        <f>COUNT(B20:BC20)</f>
-        <v/>
-      </c>
-      <c r="BF20">
-        <f>IF(OR(BD20="",COUNT($BD$5:$BD$39)&lt;3),"",IF(RANK(BD20,$BD$5:$BD$39,0)&lt;=ROUND(COUNT($BD$5:$BD$39)/3,0),"top",IF(RANK(BD20,$BD$5:$BD$39,1)&lt;=ROUND(COUNT($BD$5:$BD$39)/3,0),"bottom","middle")))</f>
+      <c r="AL20">
+        <f>IF(COUNT(B20:AK20)=0,"",SUM(B20:AK20))</f>
+        <v/>
+      </c>
+      <c r="AM20">
+        <f>COUNT(B20:AK20)</f>
+        <v/>
+      </c>
+      <c r="AN20">
+        <f>IF(OR(AL20="",COUNT($AL$5:$AL$39)&lt;3),"",IF(RANK(AL20,$AL$5:$AL$39,0)&lt;=ROUND(COUNT($AL$5:$AL$39)/3,0),"top",IF(RANK(AL20,$AL$5:$AL$39,1)&lt;=ROUND(COUNT($AL$5:$AL$39)/3,0),"bottom","middle")))</f>
         <v/>
       </c>
     </row>
@@ -2433,34 +1911,16 @@
       <c r="AI21" s="5" t="n"/>
       <c r="AJ21" s="5" t="n"/>
       <c r="AK21" s="5" t="n"/>
-      <c r="AL21" s="5" t="n"/>
-      <c r="AM21" s="5" t="n"/>
-      <c r="AN21" s="5" t="n"/>
-      <c r="AO21" s="5" t="n"/>
-      <c r="AP21" s="5" t="n"/>
-      <c r="AQ21" s="5" t="n"/>
-      <c r="AR21" s="5" t="n"/>
-      <c r="AS21" s="5" t="n"/>
-      <c r="AT21" s="5" t="n"/>
-      <c r="AU21" s="5" t="n"/>
-      <c r="AV21" s="5" t="n"/>
-      <c r="AW21" s="5" t="n"/>
-      <c r="AX21" s="5" t="n"/>
-      <c r="AY21" s="5" t="n"/>
-      <c r="AZ21" s="5" t="n"/>
-      <c r="BA21" s="5" t="n"/>
-      <c r="BB21" s="5" t="n"/>
-      <c r="BC21" s="5" t="n"/>
-      <c r="BD21">
-        <f>IF(COUNT(B21:BC21)=0,"",SUM(B21:BC21))</f>
-        <v/>
-      </c>
-      <c r="BE21">
-        <f>COUNT(B21:BC21)</f>
-        <v/>
-      </c>
-      <c r="BF21">
-        <f>IF(OR(BD21="",COUNT($BD$5:$BD$39)&lt;3),"",IF(RANK(BD21,$BD$5:$BD$39,0)&lt;=ROUND(COUNT($BD$5:$BD$39)/3,0),"top",IF(RANK(BD21,$BD$5:$BD$39,1)&lt;=ROUND(COUNT($BD$5:$BD$39)/3,0),"bottom","middle")))</f>
+      <c r="AL21">
+        <f>IF(COUNT(B21:AK21)=0,"",SUM(B21:AK21))</f>
+        <v/>
+      </c>
+      <c r="AM21">
+        <f>COUNT(B21:AK21)</f>
+        <v/>
+      </c>
+      <c r="AN21">
+        <f>IF(OR(AL21="",COUNT($AL$5:$AL$39)&lt;3),"",IF(RANK(AL21,$AL$5:$AL$39,0)&lt;=ROUND(COUNT($AL$5:$AL$39)/3,0),"top",IF(RANK(AL21,$AL$5:$AL$39,1)&lt;=ROUND(COUNT($AL$5:$AL$39)/3,0),"bottom","middle")))</f>
         <v/>
       </c>
     </row>
@@ -2504,34 +1964,16 @@
       <c r="AI22" s="5" t="n"/>
       <c r="AJ22" s="5" t="n"/>
       <c r="AK22" s="5" t="n"/>
-      <c r="AL22" s="5" t="n"/>
-      <c r="AM22" s="5" t="n"/>
-      <c r="AN22" s="5" t="n"/>
-      <c r="AO22" s="5" t="n"/>
-      <c r="AP22" s="5" t="n"/>
-      <c r="AQ22" s="5" t="n"/>
-      <c r="AR22" s="5" t="n"/>
-      <c r="AS22" s="5" t="n"/>
-      <c r="AT22" s="5" t="n"/>
-      <c r="AU22" s="5" t="n"/>
-      <c r="AV22" s="5" t="n"/>
-      <c r="AW22" s="5" t="n"/>
-      <c r="AX22" s="5" t="n"/>
-      <c r="AY22" s="5" t="n"/>
-      <c r="AZ22" s="5" t="n"/>
-      <c r="BA22" s="5" t="n"/>
-      <c r="BB22" s="5" t="n"/>
-      <c r="BC22" s="5" t="n"/>
-      <c r="BD22">
-        <f>IF(COUNT(B22:BC22)=0,"",SUM(B22:BC22))</f>
-        <v/>
-      </c>
-      <c r="BE22">
-        <f>COUNT(B22:BC22)</f>
-        <v/>
-      </c>
-      <c r="BF22">
-        <f>IF(OR(BD22="",COUNT($BD$5:$BD$39)&lt;3),"",IF(RANK(BD22,$BD$5:$BD$39,0)&lt;=ROUND(COUNT($BD$5:$BD$39)/3,0),"top",IF(RANK(BD22,$BD$5:$BD$39,1)&lt;=ROUND(COUNT($BD$5:$BD$39)/3,0),"bottom","middle")))</f>
+      <c r="AL22">
+        <f>IF(COUNT(B22:AK22)=0,"",SUM(B22:AK22))</f>
+        <v/>
+      </c>
+      <c r="AM22">
+        <f>COUNT(B22:AK22)</f>
+        <v/>
+      </c>
+      <c r="AN22">
+        <f>IF(OR(AL22="",COUNT($AL$5:$AL$39)&lt;3),"",IF(RANK(AL22,$AL$5:$AL$39,0)&lt;=ROUND(COUNT($AL$5:$AL$39)/3,0),"top",IF(RANK(AL22,$AL$5:$AL$39,1)&lt;=ROUND(COUNT($AL$5:$AL$39)/3,0),"bottom","middle")))</f>
         <v/>
       </c>
     </row>
@@ -2575,34 +2017,16 @@
       <c r="AI23" s="5" t="n"/>
       <c r="AJ23" s="5" t="n"/>
       <c r="AK23" s="5" t="n"/>
-      <c r="AL23" s="5" t="n"/>
-      <c r="AM23" s="5" t="n"/>
-      <c r="AN23" s="5" t="n"/>
-      <c r="AO23" s="5" t="n"/>
-      <c r="AP23" s="5" t="n"/>
-      <c r="AQ23" s="5" t="n"/>
-      <c r="AR23" s="5" t="n"/>
-      <c r="AS23" s="5" t="n"/>
-      <c r="AT23" s="5" t="n"/>
-      <c r="AU23" s="5" t="n"/>
-      <c r="AV23" s="5" t="n"/>
-      <c r="AW23" s="5" t="n"/>
-      <c r="AX23" s="5" t="n"/>
-      <c r="AY23" s="5" t="n"/>
-      <c r="AZ23" s="5" t="n"/>
-      <c r="BA23" s="5" t="n"/>
-      <c r="BB23" s="5" t="n"/>
-      <c r="BC23" s="5" t="n"/>
-      <c r="BD23">
-        <f>IF(COUNT(B23:BC23)=0,"",SUM(B23:BC23))</f>
-        <v/>
-      </c>
-      <c r="BE23">
-        <f>COUNT(B23:BC23)</f>
-        <v/>
-      </c>
-      <c r="BF23">
-        <f>IF(OR(BD23="",COUNT($BD$5:$BD$39)&lt;3),"",IF(RANK(BD23,$BD$5:$BD$39,0)&lt;=ROUND(COUNT($BD$5:$BD$39)/3,0),"top",IF(RANK(BD23,$BD$5:$BD$39,1)&lt;=ROUND(COUNT($BD$5:$BD$39)/3,0),"bottom","middle")))</f>
+      <c r="AL23">
+        <f>IF(COUNT(B23:AK23)=0,"",SUM(B23:AK23))</f>
+        <v/>
+      </c>
+      <c r="AM23">
+        <f>COUNT(B23:AK23)</f>
+        <v/>
+      </c>
+      <c r="AN23">
+        <f>IF(OR(AL23="",COUNT($AL$5:$AL$39)&lt;3),"",IF(RANK(AL23,$AL$5:$AL$39,0)&lt;=ROUND(COUNT($AL$5:$AL$39)/3,0),"top",IF(RANK(AL23,$AL$5:$AL$39,1)&lt;=ROUND(COUNT($AL$5:$AL$39)/3,0),"bottom","middle")))</f>
         <v/>
       </c>
     </row>
@@ -2646,34 +2070,16 @@
       <c r="AI24" s="5" t="n"/>
       <c r="AJ24" s="5" t="n"/>
       <c r="AK24" s="5" t="n"/>
-      <c r="AL24" s="5" t="n"/>
-      <c r="AM24" s="5" t="n"/>
-      <c r="AN24" s="5" t="n"/>
-      <c r="AO24" s="5" t="n"/>
-      <c r="AP24" s="5" t="n"/>
-      <c r="AQ24" s="5" t="n"/>
-      <c r="AR24" s="5" t="n"/>
-      <c r="AS24" s="5" t="n"/>
-      <c r="AT24" s="5" t="n"/>
-      <c r="AU24" s="5" t="n"/>
-      <c r="AV24" s="5" t="n"/>
-      <c r="AW24" s="5" t="n"/>
-      <c r="AX24" s="5" t="n"/>
-      <c r="AY24" s="5" t="n"/>
-      <c r="AZ24" s="5" t="n"/>
-      <c r="BA24" s="5" t="n"/>
-      <c r="BB24" s="5" t="n"/>
-      <c r="BC24" s="5" t="n"/>
-      <c r="BD24">
-        <f>IF(COUNT(B24:BC24)=0,"",SUM(B24:BC24))</f>
-        <v/>
-      </c>
-      <c r="BE24">
-        <f>COUNT(B24:BC24)</f>
-        <v/>
-      </c>
-      <c r="BF24">
-        <f>IF(OR(BD24="",COUNT($BD$5:$BD$39)&lt;3),"",IF(RANK(BD24,$BD$5:$BD$39,0)&lt;=ROUND(COUNT($BD$5:$BD$39)/3,0),"top",IF(RANK(BD24,$BD$5:$BD$39,1)&lt;=ROUND(COUNT($BD$5:$BD$39)/3,0),"bottom","middle")))</f>
+      <c r="AL24">
+        <f>IF(COUNT(B24:AK24)=0,"",SUM(B24:AK24))</f>
+        <v/>
+      </c>
+      <c r="AM24">
+        <f>COUNT(B24:AK24)</f>
+        <v/>
+      </c>
+      <c r="AN24">
+        <f>IF(OR(AL24="",COUNT($AL$5:$AL$39)&lt;3),"",IF(RANK(AL24,$AL$5:$AL$39,0)&lt;=ROUND(COUNT($AL$5:$AL$39)/3,0),"top",IF(RANK(AL24,$AL$5:$AL$39,1)&lt;=ROUND(COUNT($AL$5:$AL$39)/3,0),"bottom","middle")))</f>
         <v/>
       </c>
     </row>
@@ -2717,34 +2123,16 @@
       <c r="AI25" s="5" t="n"/>
       <c r="AJ25" s="5" t="n"/>
       <c r="AK25" s="5" t="n"/>
-      <c r="AL25" s="5" t="n"/>
-      <c r="AM25" s="5" t="n"/>
-      <c r="AN25" s="5" t="n"/>
-      <c r="AO25" s="5" t="n"/>
-      <c r="AP25" s="5" t="n"/>
-      <c r="AQ25" s="5" t="n"/>
-      <c r="AR25" s="5" t="n"/>
-      <c r="AS25" s="5" t="n"/>
-      <c r="AT25" s="5" t="n"/>
-      <c r="AU25" s="5" t="n"/>
-      <c r="AV25" s="5" t="n"/>
-      <c r="AW25" s="5" t="n"/>
-      <c r="AX25" s="5" t="n"/>
-      <c r="AY25" s="5" t="n"/>
-      <c r="AZ25" s="5" t="n"/>
-      <c r="BA25" s="5" t="n"/>
-      <c r="BB25" s="5" t="n"/>
-      <c r="BC25" s="5" t="n"/>
-      <c r="BD25">
-        <f>IF(COUNT(B25:BC25)=0,"",SUM(B25:BC25))</f>
-        <v/>
-      </c>
-      <c r="BE25">
-        <f>COUNT(B25:BC25)</f>
-        <v/>
-      </c>
-      <c r="BF25">
-        <f>IF(OR(BD25="",COUNT($BD$5:$BD$39)&lt;3),"",IF(RANK(BD25,$BD$5:$BD$39,0)&lt;=ROUND(COUNT($BD$5:$BD$39)/3,0),"top",IF(RANK(BD25,$BD$5:$BD$39,1)&lt;=ROUND(COUNT($BD$5:$BD$39)/3,0),"bottom","middle")))</f>
+      <c r="AL25">
+        <f>IF(COUNT(B25:AK25)=0,"",SUM(B25:AK25))</f>
+        <v/>
+      </c>
+      <c r="AM25">
+        <f>COUNT(B25:AK25)</f>
+        <v/>
+      </c>
+      <c r="AN25">
+        <f>IF(OR(AL25="",COUNT($AL$5:$AL$39)&lt;3),"",IF(RANK(AL25,$AL$5:$AL$39,0)&lt;=ROUND(COUNT($AL$5:$AL$39)/3,0),"top",IF(RANK(AL25,$AL$5:$AL$39,1)&lt;=ROUND(COUNT($AL$5:$AL$39)/3,0),"bottom","middle")))</f>
         <v/>
       </c>
     </row>
@@ -2788,34 +2176,16 @@
       <c r="AI26" s="5" t="n"/>
       <c r="AJ26" s="5" t="n"/>
       <c r="AK26" s="5" t="n"/>
-      <c r="AL26" s="5" t="n"/>
-      <c r="AM26" s="5" t="n"/>
-      <c r="AN26" s="5" t="n"/>
-      <c r="AO26" s="5" t="n"/>
-      <c r="AP26" s="5" t="n"/>
-      <c r="AQ26" s="5" t="n"/>
-      <c r="AR26" s="5" t="n"/>
-      <c r="AS26" s="5" t="n"/>
-      <c r="AT26" s="5" t="n"/>
-      <c r="AU26" s="5" t="n"/>
-      <c r="AV26" s="5" t="n"/>
-      <c r="AW26" s="5" t="n"/>
-      <c r="AX26" s="5" t="n"/>
-      <c r="AY26" s="5" t="n"/>
-      <c r="AZ26" s="5" t="n"/>
-      <c r="BA26" s="5" t="n"/>
-      <c r="BB26" s="5" t="n"/>
-      <c r="BC26" s="5" t="n"/>
-      <c r="BD26">
-        <f>IF(COUNT(B26:BC26)=0,"",SUM(B26:BC26))</f>
-        <v/>
-      </c>
-      <c r="BE26">
-        <f>COUNT(B26:BC26)</f>
-        <v/>
-      </c>
-      <c r="BF26">
-        <f>IF(OR(BD26="",COUNT($BD$5:$BD$39)&lt;3),"",IF(RANK(BD26,$BD$5:$BD$39,0)&lt;=ROUND(COUNT($BD$5:$BD$39)/3,0),"top",IF(RANK(BD26,$BD$5:$BD$39,1)&lt;=ROUND(COUNT($BD$5:$BD$39)/3,0),"bottom","middle")))</f>
+      <c r="AL26">
+        <f>IF(COUNT(B26:AK26)=0,"",SUM(B26:AK26))</f>
+        <v/>
+      </c>
+      <c r="AM26">
+        <f>COUNT(B26:AK26)</f>
+        <v/>
+      </c>
+      <c r="AN26">
+        <f>IF(OR(AL26="",COUNT($AL$5:$AL$39)&lt;3),"",IF(RANK(AL26,$AL$5:$AL$39,0)&lt;=ROUND(COUNT($AL$5:$AL$39)/3,0),"top",IF(RANK(AL26,$AL$5:$AL$39,1)&lt;=ROUND(COUNT($AL$5:$AL$39)/3,0),"bottom","middle")))</f>
         <v/>
       </c>
     </row>
@@ -2859,34 +2229,16 @@
       <c r="AI27" s="5" t="n"/>
       <c r="AJ27" s="5" t="n"/>
       <c r="AK27" s="5" t="n"/>
-      <c r="AL27" s="5" t="n"/>
-      <c r="AM27" s="5" t="n"/>
-      <c r="AN27" s="5" t="n"/>
-      <c r="AO27" s="5" t="n"/>
-      <c r="AP27" s="5" t="n"/>
-      <c r="AQ27" s="5" t="n"/>
-      <c r="AR27" s="5" t="n"/>
-      <c r="AS27" s="5" t="n"/>
-      <c r="AT27" s="5" t="n"/>
-      <c r="AU27" s="5" t="n"/>
-      <c r="AV27" s="5" t="n"/>
-      <c r="AW27" s="5" t="n"/>
-      <c r="AX27" s="5" t="n"/>
-      <c r="AY27" s="5" t="n"/>
-      <c r="AZ27" s="5" t="n"/>
-      <c r="BA27" s="5" t="n"/>
-      <c r="BB27" s="5" t="n"/>
-      <c r="BC27" s="5" t="n"/>
-      <c r="BD27">
-        <f>IF(COUNT(B27:BC27)=0,"",SUM(B27:BC27))</f>
-        <v/>
-      </c>
-      <c r="BE27">
-        <f>COUNT(B27:BC27)</f>
-        <v/>
-      </c>
-      <c r="BF27">
-        <f>IF(OR(BD27="",COUNT($BD$5:$BD$39)&lt;3),"",IF(RANK(BD27,$BD$5:$BD$39,0)&lt;=ROUND(COUNT($BD$5:$BD$39)/3,0),"top",IF(RANK(BD27,$BD$5:$BD$39,1)&lt;=ROUND(COUNT($BD$5:$BD$39)/3,0),"bottom","middle")))</f>
+      <c r="AL27">
+        <f>IF(COUNT(B27:AK27)=0,"",SUM(B27:AK27))</f>
+        <v/>
+      </c>
+      <c r="AM27">
+        <f>COUNT(B27:AK27)</f>
+        <v/>
+      </c>
+      <c r="AN27">
+        <f>IF(OR(AL27="",COUNT($AL$5:$AL$39)&lt;3),"",IF(RANK(AL27,$AL$5:$AL$39,0)&lt;=ROUND(COUNT($AL$5:$AL$39)/3,0),"top",IF(RANK(AL27,$AL$5:$AL$39,1)&lt;=ROUND(COUNT($AL$5:$AL$39)/3,0),"bottom","middle")))</f>
         <v/>
       </c>
     </row>
@@ -2930,34 +2282,16 @@
       <c r="AI28" s="5" t="n"/>
       <c r="AJ28" s="5" t="n"/>
       <c r="AK28" s="5" t="n"/>
-      <c r="AL28" s="5" t="n"/>
-      <c r="AM28" s="5" t="n"/>
-      <c r="AN28" s="5" t="n"/>
-      <c r="AO28" s="5" t="n"/>
-      <c r="AP28" s="5" t="n"/>
-      <c r="AQ28" s="5" t="n"/>
-      <c r="AR28" s="5" t="n"/>
-      <c r="AS28" s="5" t="n"/>
-      <c r="AT28" s="5" t="n"/>
-      <c r="AU28" s="5" t="n"/>
-      <c r="AV28" s="5" t="n"/>
-      <c r="AW28" s="5" t="n"/>
-      <c r="AX28" s="5" t="n"/>
-      <c r="AY28" s="5" t="n"/>
-      <c r="AZ28" s="5" t="n"/>
-      <c r="BA28" s="5" t="n"/>
-      <c r="BB28" s="5" t="n"/>
-      <c r="BC28" s="5" t="n"/>
-      <c r="BD28">
-        <f>IF(COUNT(B28:BC28)=0,"",SUM(B28:BC28))</f>
-        <v/>
-      </c>
-      <c r="BE28">
-        <f>COUNT(B28:BC28)</f>
-        <v/>
-      </c>
-      <c r="BF28">
-        <f>IF(OR(BD28="",COUNT($BD$5:$BD$39)&lt;3),"",IF(RANK(BD28,$BD$5:$BD$39,0)&lt;=ROUND(COUNT($BD$5:$BD$39)/3,0),"top",IF(RANK(BD28,$BD$5:$BD$39,1)&lt;=ROUND(COUNT($BD$5:$BD$39)/3,0),"bottom","middle")))</f>
+      <c r="AL28">
+        <f>IF(COUNT(B28:AK28)=0,"",SUM(B28:AK28))</f>
+        <v/>
+      </c>
+      <c r="AM28">
+        <f>COUNT(B28:AK28)</f>
+        <v/>
+      </c>
+      <c r="AN28">
+        <f>IF(OR(AL28="",COUNT($AL$5:$AL$39)&lt;3),"",IF(RANK(AL28,$AL$5:$AL$39,0)&lt;=ROUND(COUNT($AL$5:$AL$39)/3,0),"top",IF(RANK(AL28,$AL$5:$AL$39,1)&lt;=ROUND(COUNT($AL$5:$AL$39)/3,0),"bottom","middle")))</f>
         <v/>
       </c>
     </row>
@@ -3001,34 +2335,16 @@
       <c r="AI29" s="5" t="n"/>
       <c r="AJ29" s="5" t="n"/>
       <c r="AK29" s="5" t="n"/>
-      <c r="AL29" s="5" t="n"/>
-      <c r="AM29" s="5" t="n"/>
-      <c r="AN29" s="5" t="n"/>
-      <c r="AO29" s="5" t="n"/>
-      <c r="AP29" s="5" t="n"/>
-      <c r="AQ29" s="5" t="n"/>
-      <c r="AR29" s="5" t="n"/>
-      <c r="AS29" s="5" t="n"/>
-      <c r="AT29" s="5" t="n"/>
-      <c r="AU29" s="5" t="n"/>
-      <c r="AV29" s="5" t="n"/>
-      <c r="AW29" s="5" t="n"/>
-      <c r="AX29" s="5" t="n"/>
-      <c r="AY29" s="5" t="n"/>
-      <c r="AZ29" s="5" t="n"/>
-      <c r="BA29" s="5" t="n"/>
-      <c r="BB29" s="5" t="n"/>
-      <c r="BC29" s="5" t="n"/>
-      <c r="BD29">
-        <f>IF(COUNT(B29:BC29)=0,"",SUM(B29:BC29))</f>
-        <v/>
-      </c>
-      <c r="BE29">
-        <f>COUNT(B29:BC29)</f>
-        <v/>
-      </c>
-      <c r="BF29">
-        <f>IF(OR(BD29="",COUNT($BD$5:$BD$39)&lt;3),"",IF(RANK(BD29,$BD$5:$BD$39,0)&lt;=ROUND(COUNT($BD$5:$BD$39)/3,0),"top",IF(RANK(BD29,$BD$5:$BD$39,1)&lt;=ROUND(COUNT($BD$5:$BD$39)/3,0),"bottom","middle")))</f>
+      <c r="AL29">
+        <f>IF(COUNT(B29:AK29)=0,"",SUM(B29:AK29))</f>
+        <v/>
+      </c>
+      <c r="AM29">
+        <f>COUNT(B29:AK29)</f>
+        <v/>
+      </c>
+      <c r="AN29">
+        <f>IF(OR(AL29="",COUNT($AL$5:$AL$39)&lt;3),"",IF(RANK(AL29,$AL$5:$AL$39,0)&lt;=ROUND(COUNT($AL$5:$AL$39)/3,0),"top",IF(RANK(AL29,$AL$5:$AL$39,1)&lt;=ROUND(COUNT($AL$5:$AL$39)/3,0),"bottom","middle")))</f>
         <v/>
       </c>
     </row>
@@ -3072,34 +2388,16 @@
       <c r="AI30" s="5" t="n"/>
       <c r="AJ30" s="5" t="n"/>
       <c r="AK30" s="5" t="n"/>
-      <c r="AL30" s="5" t="n"/>
-      <c r="AM30" s="5" t="n"/>
-      <c r="AN30" s="5" t="n"/>
-      <c r="AO30" s="5" t="n"/>
-      <c r="AP30" s="5" t="n"/>
-      <c r="AQ30" s="5" t="n"/>
-      <c r="AR30" s="5" t="n"/>
-      <c r="AS30" s="5" t="n"/>
-      <c r="AT30" s="5" t="n"/>
-      <c r="AU30" s="5" t="n"/>
-      <c r="AV30" s="5" t="n"/>
-      <c r="AW30" s="5" t="n"/>
-      <c r="AX30" s="5" t="n"/>
-      <c r="AY30" s="5" t="n"/>
-      <c r="AZ30" s="5" t="n"/>
-      <c r="BA30" s="5" t="n"/>
-      <c r="BB30" s="5" t="n"/>
-      <c r="BC30" s="5" t="n"/>
-      <c r="BD30">
-        <f>IF(COUNT(B30:BC30)=0,"",SUM(B30:BC30))</f>
-        <v/>
-      </c>
-      <c r="BE30">
-        <f>COUNT(B30:BC30)</f>
-        <v/>
-      </c>
-      <c r="BF30">
-        <f>IF(OR(BD30="",COUNT($BD$5:$BD$39)&lt;3),"",IF(RANK(BD30,$BD$5:$BD$39,0)&lt;=ROUND(COUNT($BD$5:$BD$39)/3,0),"top",IF(RANK(BD30,$BD$5:$BD$39,1)&lt;=ROUND(COUNT($BD$5:$BD$39)/3,0),"bottom","middle")))</f>
+      <c r="AL30">
+        <f>IF(COUNT(B30:AK30)=0,"",SUM(B30:AK30))</f>
+        <v/>
+      </c>
+      <c r="AM30">
+        <f>COUNT(B30:AK30)</f>
+        <v/>
+      </c>
+      <c r="AN30">
+        <f>IF(OR(AL30="",COUNT($AL$5:$AL$39)&lt;3),"",IF(RANK(AL30,$AL$5:$AL$39,0)&lt;=ROUND(COUNT($AL$5:$AL$39)/3,0),"top",IF(RANK(AL30,$AL$5:$AL$39,1)&lt;=ROUND(COUNT($AL$5:$AL$39)/3,0),"bottom","middle")))</f>
         <v/>
       </c>
     </row>
@@ -3143,34 +2441,16 @@
       <c r="AI31" s="5" t="n"/>
       <c r="AJ31" s="5" t="n"/>
       <c r="AK31" s="5" t="n"/>
-      <c r="AL31" s="5" t="n"/>
-      <c r="AM31" s="5" t="n"/>
-      <c r="AN31" s="5" t="n"/>
-      <c r="AO31" s="5" t="n"/>
-      <c r="AP31" s="5" t="n"/>
-      <c r="AQ31" s="5" t="n"/>
-      <c r="AR31" s="5" t="n"/>
-      <c r="AS31" s="5" t="n"/>
-      <c r="AT31" s="5" t="n"/>
-      <c r="AU31" s="5" t="n"/>
-      <c r="AV31" s="5" t="n"/>
-      <c r="AW31" s="5" t="n"/>
-      <c r="AX31" s="5" t="n"/>
-      <c r="AY31" s="5" t="n"/>
-      <c r="AZ31" s="5" t="n"/>
-      <c r="BA31" s="5" t="n"/>
-      <c r="BB31" s="5" t="n"/>
-      <c r="BC31" s="5" t="n"/>
-      <c r="BD31">
-        <f>IF(COUNT(B31:BC31)=0,"",SUM(B31:BC31))</f>
-        <v/>
-      </c>
-      <c r="BE31">
-        <f>COUNT(B31:BC31)</f>
-        <v/>
-      </c>
-      <c r="BF31">
-        <f>IF(OR(BD31="",COUNT($BD$5:$BD$39)&lt;3),"",IF(RANK(BD31,$BD$5:$BD$39,0)&lt;=ROUND(COUNT($BD$5:$BD$39)/3,0),"top",IF(RANK(BD31,$BD$5:$BD$39,1)&lt;=ROUND(COUNT($BD$5:$BD$39)/3,0),"bottom","middle")))</f>
+      <c r="AL31">
+        <f>IF(COUNT(B31:AK31)=0,"",SUM(B31:AK31))</f>
+        <v/>
+      </c>
+      <c r="AM31">
+        <f>COUNT(B31:AK31)</f>
+        <v/>
+      </c>
+      <c r="AN31">
+        <f>IF(OR(AL31="",COUNT($AL$5:$AL$39)&lt;3),"",IF(RANK(AL31,$AL$5:$AL$39,0)&lt;=ROUND(COUNT($AL$5:$AL$39)/3,0),"top",IF(RANK(AL31,$AL$5:$AL$39,1)&lt;=ROUND(COUNT($AL$5:$AL$39)/3,0),"bottom","middle")))</f>
         <v/>
       </c>
     </row>
@@ -3214,34 +2494,16 @@
       <c r="AI32" s="5" t="n"/>
       <c r="AJ32" s="5" t="n"/>
       <c r="AK32" s="5" t="n"/>
-      <c r="AL32" s="5" t="n"/>
-      <c r="AM32" s="5" t="n"/>
-      <c r="AN32" s="5" t="n"/>
-      <c r="AO32" s="5" t="n"/>
-      <c r="AP32" s="5" t="n"/>
-      <c r="AQ32" s="5" t="n"/>
-      <c r="AR32" s="5" t="n"/>
-      <c r="AS32" s="5" t="n"/>
-      <c r="AT32" s="5" t="n"/>
-      <c r="AU32" s="5" t="n"/>
-      <c r="AV32" s="5" t="n"/>
-      <c r="AW32" s="5" t="n"/>
-      <c r="AX32" s="5" t="n"/>
-      <c r="AY32" s="5" t="n"/>
-      <c r="AZ32" s="5" t="n"/>
-      <c r="BA32" s="5" t="n"/>
-      <c r="BB32" s="5" t="n"/>
-      <c r="BC32" s="5" t="n"/>
-      <c r="BD32">
-        <f>IF(COUNT(B32:BC32)=0,"",SUM(B32:BC32))</f>
-        <v/>
-      </c>
-      <c r="BE32">
-        <f>COUNT(B32:BC32)</f>
-        <v/>
-      </c>
-      <c r="BF32">
-        <f>IF(OR(BD32="",COUNT($BD$5:$BD$39)&lt;3),"",IF(RANK(BD32,$BD$5:$BD$39,0)&lt;=ROUND(COUNT($BD$5:$BD$39)/3,0),"top",IF(RANK(BD32,$BD$5:$BD$39,1)&lt;=ROUND(COUNT($BD$5:$BD$39)/3,0),"bottom","middle")))</f>
+      <c r="AL32">
+        <f>IF(COUNT(B32:AK32)=0,"",SUM(B32:AK32))</f>
+        <v/>
+      </c>
+      <c r="AM32">
+        <f>COUNT(B32:AK32)</f>
+        <v/>
+      </c>
+      <c r="AN32">
+        <f>IF(OR(AL32="",COUNT($AL$5:$AL$39)&lt;3),"",IF(RANK(AL32,$AL$5:$AL$39,0)&lt;=ROUND(COUNT($AL$5:$AL$39)/3,0),"top",IF(RANK(AL32,$AL$5:$AL$39,1)&lt;=ROUND(COUNT($AL$5:$AL$39)/3,0),"bottom","middle")))</f>
         <v/>
       </c>
     </row>
@@ -3285,34 +2547,16 @@
       <c r="AI33" s="5" t="n"/>
       <c r="AJ33" s="5" t="n"/>
       <c r="AK33" s="5" t="n"/>
-      <c r="AL33" s="5" t="n"/>
-      <c r="AM33" s="5" t="n"/>
-      <c r="AN33" s="5" t="n"/>
-      <c r="AO33" s="5" t="n"/>
-      <c r="AP33" s="5" t="n"/>
-      <c r="AQ33" s="5" t="n"/>
-      <c r="AR33" s="5" t="n"/>
-      <c r="AS33" s="5" t="n"/>
-      <c r="AT33" s="5" t="n"/>
-      <c r="AU33" s="5" t="n"/>
-      <c r="AV33" s="5" t="n"/>
-      <c r="AW33" s="5" t="n"/>
-      <c r="AX33" s="5" t="n"/>
-      <c r="AY33" s="5" t="n"/>
-      <c r="AZ33" s="5" t="n"/>
-      <c r="BA33" s="5" t="n"/>
-      <c r="BB33" s="5" t="n"/>
-      <c r="BC33" s="5" t="n"/>
-      <c r="BD33">
-        <f>IF(COUNT(B33:BC33)=0,"",SUM(B33:BC33))</f>
-        <v/>
-      </c>
-      <c r="BE33">
-        <f>COUNT(B33:BC33)</f>
-        <v/>
-      </c>
-      <c r="BF33">
-        <f>IF(OR(BD33="",COUNT($BD$5:$BD$39)&lt;3),"",IF(RANK(BD33,$BD$5:$BD$39,0)&lt;=ROUND(COUNT($BD$5:$BD$39)/3,0),"top",IF(RANK(BD33,$BD$5:$BD$39,1)&lt;=ROUND(COUNT($BD$5:$BD$39)/3,0),"bottom","middle")))</f>
+      <c r="AL33">
+        <f>IF(COUNT(B33:AK33)=0,"",SUM(B33:AK33))</f>
+        <v/>
+      </c>
+      <c r="AM33">
+        <f>COUNT(B33:AK33)</f>
+        <v/>
+      </c>
+      <c r="AN33">
+        <f>IF(OR(AL33="",COUNT($AL$5:$AL$39)&lt;3),"",IF(RANK(AL33,$AL$5:$AL$39,0)&lt;=ROUND(COUNT($AL$5:$AL$39)/3,0),"top",IF(RANK(AL33,$AL$5:$AL$39,1)&lt;=ROUND(COUNT($AL$5:$AL$39)/3,0),"bottom","middle")))</f>
         <v/>
       </c>
     </row>
@@ -3356,34 +2600,16 @@
       <c r="AI34" s="5" t="n"/>
       <c r="AJ34" s="5" t="n"/>
       <c r="AK34" s="5" t="n"/>
-      <c r="AL34" s="5" t="n"/>
-      <c r="AM34" s="5" t="n"/>
-      <c r="AN34" s="5" t="n"/>
-      <c r="AO34" s="5" t="n"/>
-      <c r="AP34" s="5" t="n"/>
-      <c r="AQ34" s="5" t="n"/>
-      <c r="AR34" s="5" t="n"/>
-      <c r="AS34" s="5" t="n"/>
-      <c r="AT34" s="5" t="n"/>
-      <c r="AU34" s="5" t="n"/>
-      <c r="AV34" s="5" t="n"/>
-      <c r="AW34" s="5" t="n"/>
-      <c r="AX34" s="5" t="n"/>
-      <c r="AY34" s="5" t="n"/>
-      <c r="AZ34" s="5" t="n"/>
-      <c r="BA34" s="5" t="n"/>
-      <c r="BB34" s="5" t="n"/>
-      <c r="BC34" s="5" t="n"/>
-      <c r="BD34">
-        <f>IF(COUNT(B34:BC34)=0,"",SUM(B34:BC34))</f>
-        <v/>
-      </c>
-      <c r="BE34">
-        <f>COUNT(B34:BC34)</f>
-        <v/>
-      </c>
-      <c r="BF34">
-        <f>IF(OR(BD34="",COUNT($BD$5:$BD$39)&lt;3),"",IF(RANK(BD34,$BD$5:$BD$39,0)&lt;=ROUND(COUNT($BD$5:$BD$39)/3,0),"top",IF(RANK(BD34,$BD$5:$BD$39,1)&lt;=ROUND(COUNT($BD$5:$BD$39)/3,0),"bottom","middle")))</f>
+      <c r="AL34">
+        <f>IF(COUNT(B34:AK34)=0,"",SUM(B34:AK34))</f>
+        <v/>
+      </c>
+      <c r="AM34">
+        <f>COUNT(B34:AK34)</f>
+        <v/>
+      </c>
+      <c r="AN34">
+        <f>IF(OR(AL34="",COUNT($AL$5:$AL$39)&lt;3),"",IF(RANK(AL34,$AL$5:$AL$39,0)&lt;=ROUND(COUNT($AL$5:$AL$39)/3,0),"top",IF(RANK(AL34,$AL$5:$AL$39,1)&lt;=ROUND(COUNT($AL$5:$AL$39)/3,0),"bottom","middle")))</f>
         <v/>
       </c>
     </row>
@@ -3427,34 +2653,16 @@
       <c r="AI35" s="5" t="n"/>
       <c r="AJ35" s="5" t="n"/>
       <c r="AK35" s="5" t="n"/>
-      <c r="AL35" s="5" t="n"/>
-      <c r="AM35" s="5" t="n"/>
-      <c r="AN35" s="5" t="n"/>
-      <c r="AO35" s="5" t="n"/>
-      <c r="AP35" s="5" t="n"/>
-      <c r="AQ35" s="5" t="n"/>
-      <c r="AR35" s="5" t="n"/>
-      <c r="AS35" s="5" t="n"/>
-      <c r="AT35" s="5" t="n"/>
-      <c r="AU35" s="5" t="n"/>
-      <c r="AV35" s="5" t="n"/>
-      <c r="AW35" s="5" t="n"/>
-      <c r="AX35" s="5" t="n"/>
-      <c r="AY35" s="5" t="n"/>
-      <c r="AZ35" s="5" t="n"/>
-      <c r="BA35" s="5" t="n"/>
-      <c r="BB35" s="5" t="n"/>
-      <c r="BC35" s="5" t="n"/>
-      <c r="BD35">
-        <f>IF(COUNT(B35:BC35)=0,"",SUM(B35:BC35))</f>
-        <v/>
-      </c>
-      <c r="BE35">
-        <f>COUNT(B35:BC35)</f>
-        <v/>
-      </c>
-      <c r="BF35">
-        <f>IF(OR(BD35="",COUNT($BD$5:$BD$39)&lt;3),"",IF(RANK(BD35,$BD$5:$BD$39,0)&lt;=ROUND(COUNT($BD$5:$BD$39)/3,0),"top",IF(RANK(BD35,$BD$5:$BD$39,1)&lt;=ROUND(COUNT($BD$5:$BD$39)/3,0),"bottom","middle")))</f>
+      <c r="AL35">
+        <f>IF(COUNT(B35:AK35)=0,"",SUM(B35:AK35))</f>
+        <v/>
+      </c>
+      <c r="AM35">
+        <f>COUNT(B35:AK35)</f>
+        <v/>
+      </c>
+      <c r="AN35">
+        <f>IF(OR(AL35="",COUNT($AL$5:$AL$39)&lt;3),"",IF(RANK(AL35,$AL$5:$AL$39,0)&lt;=ROUND(COUNT($AL$5:$AL$39)/3,0),"top",IF(RANK(AL35,$AL$5:$AL$39,1)&lt;=ROUND(COUNT($AL$5:$AL$39)/3,0),"bottom","middle")))</f>
         <v/>
       </c>
     </row>
@@ -3498,34 +2706,16 @@
       <c r="AI36" s="5" t="n"/>
       <c r="AJ36" s="5" t="n"/>
       <c r="AK36" s="5" t="n"/>
-      <c r="AL36" s="5" t="n"/>
-      <c r="AM36" s="5" t="n"/>
-      <c r="AN36" s="5" t="n"/>
-      <c r="AO36" s="5" t="n"/>
-      <c r="AP36" s="5" t="n"/>
-      <c r="AQ36" s="5" t="n"/>
-      <c r="AR36" s="5" t="n"/>
-      <c r="AS36" s="5" t="n"/>
-      <c r="AT36" s="5" t="n"/>
-      <c r="AU36" s="5" t="n"/>
-      <c r="AV36" s="5" t="n"/>
-      <c r="AW36" s="5" t="n"/>
-      <c r="AX36" s="5" t="n"/>
-      <c r="AY36" s="5" t="n"/>
-      <c r="AZ36" s="5" t="n"/>
-      <c r="BA36" s="5" t="n"/>
-      <c r="BB36" s="5" t="n"/>
-      <c r="BC36" s="5" t="n"/>
-      <c r="BD36">
-        <f>IF(COUNT(B36:BC36)=0,"",SUM(B36:BC36))</f>
-        <v/>
-      </c>
-      <c r="BE36">
-        <f>COUNT(B36:BC36)</f>
-        <v/>
-      </c>
-      <c r="BF36">
-        <f>IF(OR(BD36="",COUNT($BD$5:$BD$39)&lt;3),"",IF(RANK(BD36,$BD$5:$BD$39,0)&lt;=ROUND(COUNT($BD$5:$BD$39)/3,0),"top",IF(RANK(BD36,$BD$5:$BD$39,1)&lt;=ROUND(COUNT($BD$5:$BD$39)/3,0),"bottom","middle")))</f>
+      <c r="AL36">
+        <f>IF(COUNT(B36:AK36)=0,"",SUM(B36:AK36))</f>
+        <v/>
+      </c>
+      <c r="AM36">
+        <f>COUNT(B36:AK36)</f>
+        <v/>
+      </c>
+      <c r="AN36">
+        <f>IF(OR(AL36="",COUNT($AL$5:$AL$39)&lt;3),"",IF(RANK(AL36,$AL$5:$AL$39,0)&lt;=ROUND(COUNT($AL$5:$AL$39)/3,0),"top",IF(RANK(AL36,$AL$5:$AL$39,1)&lt;=ROUND(COUNT($AL$5:$AL$39)/3,0),"bottom","middle")))</f>
         <v/>
       </c>
     </row>
@@ -3569,34 +2759,16 @@
       <c r="AI37" s="5" t="n"/>
       <c r="AJ37" s="5" t="n"/>
       <c r="AK37" s="5" t="n"/>
-      <c r="AL37" s="5" t="n"/>
-      <c r="AM37" s="5" t="n"/>
-      <c r="AN37" s="5" t="n"/>
-      <c r="AO37" s="5" t="n"/>
-      <c r="AP37" s="5" t="n"/>
-      <c r="AQ37" s="5" t="n"/>
-      <c r="AR37" s="5" t="n"/>
-      <c r="AS37" s="5" t="n"/>
-      <c r="AT37" s="5" t="n"/>
-      <c r="AU37" s="5" t="n"/>
-      <c r="AV37" s="5" t="n"/>
-      <c r="AW37" s="5" t="n"/>
-      <c r="AX37" s="5" t="n"/>
-      <c r="AY37" s="5" t="n"/>
-      <c r="AZ37" s="5" t="n"/>
-      <c r="BA37" s="5" t="n"/>
-      <c r="BB37" s="5" t="n"/>
-      <c r="BC37" s="5" t="n"/>
-      <c r="BD37">
-        <f>IF(COUNT(B37:BC37)=0,"",SUM(B37:BC37))</f>
-        <v/>
-      </c>
-      <c r="BE37">
-        <f>COUNT(B37:BC37)</f>
-        <v/>
-      </c>
-      <c r="BF37">
-        <f>IF(OR(BD37="",COUNT($BD$5:$BD$39)&lt;3),"",IF(RANK(BD37,$BD$5:$BD$39,0)&lt;=ROUND(COUNT($BD$5:$BD$39)/3,0),"top",IF(RANK(BD37,$BD$5:$BD$39,1)&lt;=ROUND(COUNT($BD$5:$BD$39)/3,0),"bottom","middle")))</f>
+      <c r="AL37">
+        <f>IF(COUNT(B37:AK37)=0,"",SUM(B37:AK37))</f>
+        <v/>
+      </c>
+      <c r="AM37">
+        <f>COUNT(B37:AK37)</f>
+        <v/>
+      </c>
+      <c r="AN37">
+        <f>IF(OR(AL37="",COUNT($AL$5:$AL$39)&lt;3),"",IF(RANK(AL37,$AL$5:$AL$39,0)&lt;=ROUND(COUNT($AL$5:$AL$39)/3,0),"top",IF(RANK(AL37,$AL$5:$AL$39,1)&lt;=ROUND(COUNT($AL$5:$AL$39)/3,0),"bottom","middle")))</f>
         <v/>
       </c>
     </row>
@@ -3640,34 +2812,16 @@
       <c r="AI38" s="5" t="n"/>
       <c r="AJ38" s="5" t="n"/>
       <c r="AK38" s="5" t="n"/>
-      <c r="AL38" s="5" t="n"/>
-      <c r="AM38" s="5" t="n"/>
-      <c r="AN38" s="5" t="n"/>
-      <c r="AO38" s="5" t="n"/>
-      <c r="AP38" s="5" t="n"/>
-      <c r="AQ38" s="5" t="n"/>
-      <c r="AR38" s="5" t="n"/>
-      <c r="AS38" s="5" t="n"/>
-      <c r="AT38" s="5" t="n"/>
-      <c r="AU38" s="5" t="n"/>
-      <c r="AV38" s="5" t="n"/>
-      <c r="AW38" s="5" t="n"/>
-      <c r="AX38" s="5" t="n"/>
-      <c r="AY38" s="5" t="n"/>
-      <c r="AZ38" s="5" t="n"/>
-      <c r="BA38" s="5" t="n"/>
-      <c r="BB38" s="5" t="n"/>
-      <c r="BC38" s="5" t="n"/>
-      <c r="BD38">
-        <f>IF(COUNT(B38:BC38)=0,"",SUM(B38:BC38))</f>
-        <v/>
-      </c>
-      <c r="BE38">
-        <f>COUNT(B38:BC38)</f>
-        <v/>
-      </c>
-      <c r="BF38">
-        <f>IF(OR(BD38="",COUNT($BD$5:$BD$39)&lt;3),"",IF(RANK(BD38,$BD$5:$BD$39,0)&lt;=ROUND(COUNT($BD$5:$BD$39)/3,0),"top",IF(RANK(BD38,$BD$5:$BD$39,1)&lt;=ROUND(COUNT($BD$5:$BD$39)/3,0),"bottom","middle")))</f>
+      <c r="AL38">
+        <f>IF(COUNT(B38:AK38)=0,"",SUM(B38:AK38))</f>
+        <v/>
+      </c>
+      <c r="AM38">
+        <f>COUNT(B38:AK38)</f>
+        <v/>
+      </c>
+      <c r="AN38">
+        <f>IF(OR(AL38="",COUNT($AL$5:$AL$39)&lt;3),"",IF(RANK(AL38,$AL$5:$AL$39,0)&lt;=ROUND(COUNT($AL$5:$AL$39)/3,0),"top",IF(RANK(AL38,$AL$5:$AL$39,1)&lt;=ROUND(COUNT($AL$5:$AL$39)/3,0),"bottom","middle")))</f>
         <v/>
       </c>
     </row>
@@ -3711,34 +2865,16 @@
       <c r="AI39" s="5" t="n"/>
       <c r="AJ39" s="5" t="n"/>
       <c r="AK39" s="5" t="n"/>
-      <c r="AL39" s="5" t="n"/>
-      <c r="AM39" s="5" t="n"/>
-      <c r="AN39" s="5" t="n"/>
-      <c r="AO39" s="5" t="n"/>
-      <c r="AP39" s="5" t="n"/>
-      <c r="AQ39" s="5" t="n"/>
-      <c r="AR39" s="5" t="n"/>
-      <c r="AS39" s="5" t="n"/>
-      <c r="AT39" s="5" t="n"/>
-      <c r="AU39" s="5" t="n"/>
-      <c r="AV39" s="5" t="n"/>
-      <c r="AW39" s="5" t="n"/>
-      <c r="AX39" s="5" t="n"/>
-      <c r="AY39" s="5" t="n"/>
-      <c r="AZ39" s="5" t="n"/>
-      <c r="BA39" s="5" t="n"/>
-      <c r="BB39" s="5" t="n"/>
-      <c r="BC39" s="5" t="n"/>
-      <c r="BD39">
-        <f>IF(COUNT(B39:BC39)=0,"",SUM(B39:BC39))</f>
-        <v/>
-      </c>
-      <c r="BE39">
-        <f>COUNT(B39:BC39)</f>
-        <v/>
-      </c>
-      <c r="BF39">
-        <f>IF(OR(BD39="",COUNT($BD$5:$BD$39)&lt;3),"",IF(RANK(BD39,$BD$5:$BD$39,0)&lt;=ROUND(COUNT($BD$5:$BD$39)/3,0),"top",IF(RANK(BD39,$BD$5:$BD$39,1)&lt;=ROUND(COUNT($BD$5:$BD$39)/3,0),"bottom","middle")))</f>
+      <c r="AL39">
+        <f>IF(COUNT(B39:AK39)=0,"",SUM(B39:AK39))</f>
+        <v/>
+      </c>
+      <c r="AM39">
+        <f>COUNT(B39:AK39)</f>
+        <v/>
+      </c>
+      <c r="AN39">
+        <f>IF(OR(AL39="",COUNT($AL$5:$AL$39)&lt;3),"",IF(RANK(AL39,$AL$5:$AL$39,0)&lt;=ROUND(COUNT($AL$5:$AL$39)/3,0),"top",IF(RANK(AL39,$AL$5:$AL$39,1)&lt;=ROUND(COUNT($AL$5:$AL$39)/3,0),"bottom","middle")))</f>
         <v/>
       </c>
     </row>
@@ -3753,7 +2889,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N58"/>
+  <dimension ref="A1:N40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="13" max="13"/>
@@ -3847,12 +2983,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Fill in the blank</t>
+          <t>Applied maths</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Easy</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -3862,7 +2998,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>large (or extreme)</t>
+          <t>Median Rs 1,400; mean Rs 97,080.</t>
         </is>
       </c>
       <c r="G5">
@@ -3878,11 +3014,11 @@
         <v/>
       </c>
       <c r="J5" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BF$5:$BF$39="top")*ISNUMBER(Marks!B$5:B$39))=0,"",SUMPRODUCT((Marks!$BF$5:$BF$39="top")*(Marks!B$5:B$39=1))/SUMPRODUCT((Marks!$BF$5:$BF$39="top")*ISNUMBER(Marks!B$5:B$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AN$5:$AN$39="top")*ISNUMBER(Marks!B$5:B$39))=0,"",SUMPRODUCT((Marks!$AN$5:$AN$39="top")*(Marks!B$5:B$39=1))/SUMPRODUCT((Marks!$AN$5:$AN$39="top")*ISNUMBER(Marks!B$5:B$39)))</f>
         <v/>
       </c>
       <c r="K5" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*ISNUMBER(Marks!B$5:B$39))=0,"",SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*(Marks!B$5:B$39=1))/SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*ISNUMBER(Marks!B$5:B$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AN$5:$AN$39="bottom")*ISNUMBER(Marks!B$5:B$39))=0,"",SUMPRODUCT((Marks!$AN$5:$AN$39="bottom")*(Marks!B$5:B$39=1))/SUMPRODUCT((Marks!$AN$5:$AN$39="bottom")*ISNUMBER(Marks!B$5:B$39)))</f>
         <v/>
       </c>
       <c r="L5" s="6">
@@ -3907,12 +3043,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Fill in the blank</t>
+          <t>One correct option</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Hard</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -3922,7 +3058,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>confounder</t>
+          <t>c</t>
         </is>
       </c>
       <c r="G6">
@@ -3938,11 +3074,11 @@
         <v/>
       </c>
       <c r="J6" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BF$5:$BF$39="top")*ISNUMBER(Marks!C$5:C$39))=0,"",SUMPRODUCT((Marks!$BF$5:$BF$39="top")*(Marks!C$5:C$39=1))/SUMPRODUCT((Marks!$BF$5:$BF$39="top")*ISNUMBER(Marks!C$5:C$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AN$5:$AN$39="top")*ISNUMBER(Marks!C$5:C$39))=0,"",SUMPRODUCT((Marks!$AN$5:$AN$39="top")*(Marks!C$5:C$39=1))/SUMPRODUCT((Marks!$AN$5:$AN$39="top")*ISNUMBER(Marks!C$5:C$39)))</f>
         <v/>
       </c>
       <c r="K6" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*ISNUMBER(Marks!C$5:C$39))=0,"",SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*(Marks!C$5:C$39=1))/SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*ISNUMBER(Marks!C$5:C$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AN$5:$AN$39="bottom")*ISNUMBER(Marks!C$5:C$39))=0,"",SUMPRODUCT((Marks!$AN$5:$AN$39="bottom")*(Marks!C$5:C$39=1))/SUMPRODUCT((Marks!$AN$5:$AN$39="bottom")*ISNUMBER(Marks!C$5:C$39)))</f>
         <v/>
       </c>
       <c r="L6" s="6">
@@ -3967,12 +3103,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>True or false</t>
+          <t>One correct option</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Hard</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3982,7 +3118,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>b</t>
         </is>
       </c>
       <c r="G7">
@@ -3998,11 +3134,11 @@
         <v/>
       </c>
       <c r="J7" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BF$5:$BF$39="top")*ISNUMBER(Marks!D$5:D$39))=0,"",SUMPRODUCT((Marks!$BF$5:$BF$39="top")*(Marks!D$5:D$39=1))/SUMPRODUCT((Marks!$BF$5:$BF$39="top")*ISNUMBER(Marks!D$5:D$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AN$5:$AN$39="top")*ISNUMBER(Marks!D$5:D$39))=0,"",SUMPRODUCT((Marks!$AN$5:$AN$39="top")*(Marks!D$5:D$39=1))/SUMPRODUCT((Marks!$AN$5:$AN$39="top")*ISNUMBER(Marks!D$5:D$39)))</f>
         <v/>
       </c>
       <c r="K7" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*ISNUMBER(Marks!D$5:D$39))=0,"",SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*(Marks!D$5:D$39=1))/SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*ISNUMBER(Marks!D$5:D$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AN$5:$AN$39="bottom")*ISNUMBER(Marks!D$5:D$39))=0,"",SUMPRODUCT((Marks!$AN$5:$AN$39="bottom")*(Marks!D$5:D$39=1))/SUMPRODUCT((Marks!$AN$5:$AN$39="bottom")*ISNUMBER(Marks!D$5:D$39)))</f>
         <v/>
       </c>
       <c r="L7" s="6">
@@ -4027,22 +3163,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>True or false</t>
+          <t>Applied maths</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>Hard</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>[S]</t>
+          <t>[F]</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Revenue falls by 6.5 percent (1.10 x 0.85 = 0.935).</t>
         </is>
       </c>
       <c r="G8">
@@ -4058,11 +3194,11 @@
         <v/>
       </c>
       <c r="J8" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BF$5:$BF$39="top")*ISNUMBER(Marks!E$5:E$39))=0,"",SUMPRODUCT((Marks!$BF$5:$BF$39="top")*(Marks!E$5:E$39=1))/SUMPRODUCT((Marks!$BF$5:$BF$39="top")*ISNUMBER(Marks!E$5:E$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AN$5:$AN$39="top")*ISNUMBER(Marks!E$5:E$39))=0,"",SUMPRODUCT((Marks!$AN$5:$AN$39="top")*(Marks!E$5:E$39=1))/SUMPRODUCT((Marks!$AN$5:$AN$39="top")*ISNUMBER(Marks!E$5:E$39)))</f>
         <v/>
       </c>
       <c r="K8" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*ISNUMBER(Marks!E$5:E$39))=0,"",SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*(Marks!E$5:E$39=1))/SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*ISNUMBER(Marks!E$5:E$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AN$5:$AN$39="bottom")*ISNUMBER(Marks!E$5:E$39))=0,"",SUMPRODUCT((Marks!$AN$5:$AN$39="bottom")*(Marks!E$5:E$39=1))/SUMPRODUCT((Marks!$AN$5:$AN$39="bottom")*ISNUMBER(Marks!E$5:E$39)))</f>
         <v/>
       </c>
       <c r="L8" s="6">
@@ -4087,22 +3223,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>True or false</t>
+          <t>One correct option</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>Hard</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>[F]</t>
+          <t>[S]</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>d</t>
         </is>
       </c>
       <c r="G9">
@@ -4118,11 +3254,11 @@
         <v/>
       </c>
       <c r="J9" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BF$5:$BF$39="top")*ISNUMBER(Marks!F$5:F$39))=0,"",SUMPRODUCT((Marks!$BF$5:$BF$39="top")*(Marks!F$5:F$39=1))/SUMPRODUCT((Marks!$BF$5:$BF$39="top")*ISNUMBER(Marks!F$5:F$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AN$5:$AN$39="top")*ISNUMBER(Marks!F$5:F$39))=0,"",SUMPRODUCT((Marks!$AN$5:$AN$39="top")*(Marks!F$5:F$39=1))/SUMPRODUCT((Marks!$AN$5:$AN$39="top")*ISNUMBER(Marks!F$5:F$39)))</f>
         <v/>
       </c>
       <c r="K9" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*ISNUMBER(Marks!F$5:F$39))=0,"",SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*(Marks!F$5:F$39=1))/SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*ISNUMBER(Marks!F$5:F$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AN$5:$AN$39="bottom")*ISNUMBER(Marks!F$5:F$39))=0,"",SUMPRODUCT((Marks!$AN$5:$AN$39="bottom")*(Marks!F$5:F$39=1))/SUMPRODUCT((Marks!$AN$5:$AN$39="bottom")*ISNUMBER(Marks!F$5:F$39)))</f>
         <v/>
       </c>
       <c r="L9" s="6">
@@ -4147,7 +3283,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>True or false</t>
+          <t>One correct option</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -4157,12 +3293,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>[F]</t>
+          <t>[S]</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>a</t>
         </is>
       </c>
       <c r="G10">
@@ -4178,11 +3314,11 @@
         <v/>
       </c>
       <c r="J10" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BF$5:$BF$39="top")*ISNUMBER(Marks!G$5:G$39))=0,"",SUMPRODUCT((Marks!$BF$5:$BF$39="top")*(Marks!G$5:G$39=1))/SUMPRODUCT((Marks!$BF$5:$BF$39="top")*ISNUMBER(Marks!G$5:G$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AN$5:$AN$39="top")*ISNUMBER(Marks!G$5:G$39))=0,"",SUMPRODUCT((Marks!$AN$5:$AN$39="top")*(Marks!G$5:G$39=1))/SUMPRODUCT((Marks!$AN$5:$AN$39="top")*ISNUMBER(Marks!G$5:G$39)))</f>
         <v/>
       </c>
       <c r="K10" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*ISNUMBER(Marks!G$5:G$39))=0,"",SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*(Marks!G$5:G$39=1))/SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*ISNUMBER(Marks!G$5:G$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AN$5:$AN$39="bottom")*ISNUMBER(Marks!G$5:G$39))=0,"",SUMPRODUCT((Marks!$AN$5:$AN$39="bottom")*(Marks!G$5:G$39=1))/SUMPRODUCT((Marks!$AN$5:$AN$39="bottom")*ISNUMBER(Marks!G$5:G$39)))</f>
         <v/>
       </c>
       <c r="L10" s="6">
@@ -4207,22 +3343,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>True or false</t>
+          <t>One correct option</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>Hard</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>[F]</t>
+          <t>[D]</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>d</t>
         </is>
       </c>
       <c r="G11">
@@ -4238,11 +3374,11 @@
         <v/>
       </c>
       <c r="J11" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BF$5:$BF$39="top")*ISNUMBER(Marks!H$5:H$39))=0,"",SUMPRODUCT((Marks!$BF$5:$BF$39="top")*(Marks!H$5:H$39=1))/SUMPRODUCT((Marks!$BF$5:$BF$39="top")*ISNUMBER(Marks!H$5:H$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AN$5:$AN$39="top")*ISNUMBER(Marks!H$5:H$39))=0,"",SUMPRODUCT((Marks!$AN$5:$AN$39="top")*(Marks!H$5:H$39=1))/SUMPRODUCT((Marks!$AN$5:$AN$39="top")*ISNUMBER(Marks!H$5:H$39)))</f>
         <v/>
       </c>
       <c r="K11" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*ISNUMBER(Marks!H$5:H$39))=0,"",SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*(Marks!H$5:H$39=1))/SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*ISNUMBER(Marks!H$5:H$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AN$5:$AN$39="bottom")*ISNUMBER(Marks!H$5:H$39))=0,"",SUMPRODUCT((Marks!$AN$5:$AN$39="bottom")*(Marks!H$5:H$39=1))/SUMPRODUCT((Marks!$AN$5:$AN$39="bottom")*ISNUMBER(Marks!H$5:H$39)))</f>
         <v/>
       </c>
       <c r="L11" s="6">
@@ -4267,22 +3403,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>True or false</t>
+          <t>Order the steps</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>[F]</t>
+          <t>[S]</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>b, d, e, a, c</t>
         </is>
       </c>
       <c r="G12">
@@ -4298,11 +3434,11 @@
         <v/>
       </c>
       <c r="J12" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BF$5:$BF$39="top")*ISNUMBER(Marks!I$5:I$39))=0,"",SUMPRODUCT((Marks!$BF$5:$BF$39="top")*(Marks!I$5:I$39=1))/SUMPRODUCT((Marks!$BF$5:$BF$39="top")*ISNUMBER(Marks!I$5:I$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AN$5:$AN$39="top")*ISNUMBER(Marks!I$5:I$39))=0,"",SUMPRODUCT((Marks!$AN$5:$AN$39="top")*(Marks!I$5:I$39=1))/SUMPRODUCT((Marks!$AN$5:$AN$39="top")*ISNUMBER(Marks!I$5:I$39)))</f>
         <v/>
       </c>
       <c r="K12" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*ISNUMBER(Marks!I$5:I$39))=0,"",SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*(Marks!I$5:I$39=1))/SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*ISNUMBER(Marks!I$5:I$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AN$5:$AN$39="bottom")*ISNUMBER(Marks!I$5:I$39))=0,"",SUMPRODUCT((Marks!$AN$5:$AN$39="bottom")*(Marks!I$5:I$39=1))/SUMPRODUCT((Marks!$AN$5:$AN$39="bottom")*ISNUMBER(Marks!I$5:I$39)))</f>
         <v/>
       </c>
       <c r="L12" s="6">
@@ -4323,11 +3459,11 @@
         <v>9</v>
       </c>
       <c r="B13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>True or false</t>
+          <t>One correct option</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -4337,12 +3473,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>[D]</t>
+          <t>[F]</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>b</t>
         </is>
       </c>
       <c r="G13">
@@ -4358,11 +3494,11 @@
         <v/>
       </c>
       <c r="J13" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BF$5:$BF$39="top")*ISNUMBER(Marks!J$5:J$39))=0,"",SUMPRODUCT((Marks!$BF$5:$BF$39="top")*(Marks!J$5:J$39=1))/SUMPRODUCT((Marks!$BF$5:$BF$39="top")*ISNUMBER(Marks!J$5:J$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AN$5:$AN$39="top")*ISNUMBER(Marks!J$5:J$39))=0,"",SUMPRODUCT((Marks!$AN$5:$AN$39="top")*(Marks!J$5:J$39=1))/SUMPRODUCT((Marks!$AN$5:$AN$39="top")*ISNUMBER(Marks!J$5:J$39)))</f>
         <v/>
       </c>
       <c r="K13" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*ISNUMBER(Marks!J$5:J$39))=0,"",SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*(Marks!J$5:J$39=1))/SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*ISNUMBER(Marks!J$5:J$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AN$5:$AN$39="bottom")*ISNUMBER(Marks!J$5:J$39))=0,"",SUMPRODUCT((Marks!$AN$5:$AN$39="bottom")*(Marks!J$5:J$39=1))/SUMPRODUCT((Marks!$AN$5:$AN$39="bottom")*ISNUMBER(Marks!J$5:J$39)))</f>
         <v/>
       </c>
       <c r="L13" s="6">
@@ -4387,22 +3523,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>One correct option</t>
+          <t>True or false</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>[S]</t>
+          <t>[SV]</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>c</t>
+          <t>False</t>
         </is>
       </c>
       <c r="G14">
@@ -4418,11 +3554,11 @@
         <v/>
       </c>
       <c r="J14" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BF$5:$BF$39="top")*ISNUMBER(Marks!K$5:K$39))=0,"",SUMPRODUCT((Marks!$BF$5:$BF$39="top")*(Marks!K$5:K$39=1))/SUMPRODUCT((Marks!$BF$5:$BF$39="top")*ISNUMBER(Marks!K$5:K$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AN$5:$AN$39="top")*ISNUMBER(Marks!K$5:K$39))=0,"",SUMPRODUCT((Marks!$AN$5:$AN$39="top")*(Marks!K$5:K$39=1))/SUMPRODUCT((Marks!$AN$5:$AN$39="top")*ISNUMBER(Marks!K$5:K$39)))</f>
         <v/>
       </c>
       <c r="K14" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*ISNUMBER(Marks!K$5:K$39))=0,"",SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*(Marks!K$5:K$39=1))/SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*ISNUMBER(Marks!K$5:K$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AN$5:$AN$39="bottom")*ISNUMBER(Marks!K$5:K$39))=0,"",SUMPRODUCT((Marks!$AN$5:$AN$39="bottom")*(Marks!K$5:K$39=1))/SUMPRODUCT((Marks!$AN$5:$AN$39="bottom")*ISNUMBER(Marks!K$5:K$39)))</f>
         <v/>
       </c>
       <c r="L14" s="6">
@@ -4447,22 +3583,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>One correct option</t>
+          <t>True or false</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>Hard</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>[S]</t>
+          <t>[D]</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>a</t>
+          <t>c</t>
         </is>
       </c>
       <c r="G15">
@@ -4478,11 +3614,11 @@
         <v/>
       </c>
       <c r="J15" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BF$5:$BF$39="top")*ISNUMBER(Marks!L$5:L$39))=0,"",SUMPRODUCT((Marks!$BF$5:$BF$39="top")*(Marks!L$5:L$39=1))/SUMPRODUCT((Marks!$BF$5:$BF$39="top")*ISNUMBER(Marks!L$5:L$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AN$5:$AN$39="top")*ISNUMBER(Marks!L$5:L$39))=0,"",SUMPRODUCT((Marks!$AN$5:$AN$39="top")*(Marks!L$5:L$39=1))/SUMPRODUCT((Marks!$AN$5:$AN$39="top")*ISNUMBER(Marks!L$5:L$39)))</f>
         <v/>
       </c>
       <c r="K15" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*ISNUMBER(Marks!L$5:L$39))=0,"",SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*(Marks!L$5:L$39=1))/SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*ISNUMBER(Marks!L$5:L$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AN$5:$AN$39="bottom")*ISNUMBER(Marks!L$5:L$39))=0,"",SUMPRODUCT((Marks!$AN$5:$AN$39="bottom")*(Marks!L$5:L$39=1))/SUMPRODUCT((Marks!$AN$5:$AN$39="bottom")*ISNUMBER(Marks!L$5:L$39)))</f>
         <v/>
       </c>
       <c r="L15" s="6">
@@ -4507,22 +3643,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>One correct option</t>
+          <t>More than one correct</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>Hard</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>[S]</t>
+          <t>[F]</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>a</t>
+          <t>b, d</t>
         </is>
       </c>
       <c r="G16">
@@ -4538,11 +3674,11 @@
         <v/>
       </c>
       <c r="J16" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BF$5:$BF$39="top")*ISNUMBER(Marks!M$5:M$39))=0,"",SUMPRODUCT((Marks!$BF$5:$BF$39="top")*(Marks!M$5:M$39=1))/SUMPRODUCT((Marks!$BF$5:$BF$39="top")*ISNUMBER(Marks!M$5:M$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AN$5:$AN$39="top")*ISNUMBER(Marks!M$5:M$39))=0,"",SUMPRODUCT((Marks!$AN$5:$AN$39="top")*(Marks!M$5:M$39=1))/SUMPRODUCT((Marks!$AN$5:$AN$39="top")*ISNUMBER(Marks!M$5:M$39)))</f>
         <v/>
       </c>
       <c r="K16" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*ISNUMBER(Marks!M$5:M$39))=0,"",SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*(Marks!M$5:M$39=1))/SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*ISNUMBER(Marks!M$5:M$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AN$5:$AN$39="bottom")*ISNUMBER(Marks!M$5:M$39))=0,"",SUMPRODUCT((Marks!$AN$5:$AN$39="bottom")*(Marks!M$5:M$39=1))/SUMPRODUCT((Marks!$AN$5:$AN$39="bottom")*ISNUMBER(Marks!M$5:M$39)))</f>
         <v/>
       </c>
       <c r="L16" s="6">
@@ -4582,7 +3718,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>d</t>
+          <t>b</t>
         </is>
       </c>
       <c r="G17">
@@ -4598,11 +3734,11 @@
         <v/>
       </c>
       <c r="J17" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BF$5:$BF$39="top")*ISNUMBER(Marks!N$5:N$39))=0,"",SUMPRODUCT((Marks!$BF$5:$BF$39="top")*(Marks!N$5:N$39=1))/SUMPRODUCT((Marks!$BF$5:$BF$39="top")*ISNUMBER(Marks!N$5:N$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AN$5:$AN$39="top")*ISNUMBER(Marks!N$5:N$39))=0,"",SUMPRODUCT((Marks!$AN$5:$AN$39="top")*(Marks!N$5:N$39=1))/SUMPRODUCT((Marks!$AN$5:$AN$39="top")*ISNUMBER(Marks!N$5:N$39)))</f>
         <v/>
       </c>
       <c r="K17" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*ISNUMBER(Marks!N$5:N$39))=0,"",SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*(Marks!N$5:N$39=1))/SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*ISNUMBER(Marks!N$5:N$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AN$5:$AN$39="bottom")*ISNUMBER(Marks!N$5:N$39))=0,"",SUMPRODUCT((Marks!$AN$5:$AN$39="bottom")*(Marks!N$5:N$39=1))/SUMPRODUCT((Marks!$AN$5:$AN$39="bottom")*ISNUMBER(Marks!N$5:N$39)))</f>
         <v/>
       </c>
       <c r="L17" s="6">
@@ -4627,7 +3763,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>One correct option</t>
+          <t>Scenario set</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -4637,12 +3773,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>[D]</t>
+          <t>[F]</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>c</t>
+          <t>d</t>
         </is>
       </c>
       <c r="G18">
@@ -4658,11 +3794,11 @@
         <v/>
       </c>
       <c r="J18" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BF$5:$BF$39="top")*ISNUMBER(Marks!O$5:O$39))=0,"",SUMPRODUCT((Marks!$BF$5:$BF$39="top")*(Marks!O$5:O$39=1))/SUMPRODUCT((Marks!$BF$5:$BF$39="top")*ISNUMBER(Marks!O$5:O$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AN$5:$AN$39="top")*ISNUMBER(Marks!O$5:O$39))=0,"",SUMPRODUCT((Marks!$AN$5:$AN$39="top")*(Marks!O$5:O$39=1))/SUMPRODUCT((Marks!$AN$5:$AN$39="top")*ISNUMBER(Marks!O$5:O$39)))</f>
         <v/>
       </c>
       <c r="K18" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*ISNUMBER(Marks!O$5:O$39))=0,"",SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*(Marks!O$5:O$39=1))/SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*ISNUMBER(Marks!O$5:O$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AN$5:$AN$39="bottom")*ISNUMBER(Marks!O$5:O$39))=0,"",SUMPRODUCT((Marks!$AN$5:$AN$39="bottom")*(Marks!O$5:O$39=1))/SUMPRODUCT((Marks!$AN$5:$AN$39="bottom")*ISNUMBER(Marks!O$5:O$39)))</f>
         <v/>
       </c>
       <c r="L18" s="6">
@@ -4687,12 +3823,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>More than one correct</t>
+          <t>Scenario set</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>Hard</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -4702,7 +3838,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>a, b, d</t>
+          <t>A fall of 35.0 percent.</t>
         </is>
       </c>
       <c r="G19">
@@ -4718,11 +3854,11 @@
         <v/>
       </c>
       <c r="J19" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BF$5:$BF$39="top")*ISNUMBER(Marks!P$5:P$39))=0,"",SUMPRODUCT((Marks!$BF$5:$BF$39="top")*(Marks!P$5:P$39=1))/SUMPRODUCT((Marks!$BF$5:$BF$39="top")*ISNUMBER(Marks!P$5:P$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AN$5:$AN$39="top")*ISNUMBER(Marks!P$5:P$39))=0,"",SUMPRODUCT((Marks!$AN$5:$AN$39="top")*(Marks!P$5:P$39=1))/SUMPRODUCT((Marks!$AN$5:$AN$39="top")*ISNUMBER(Marks!P$5:P$39)))</f>
         <v/>
       </c>
       <c r="K19" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*ISNUMBER(Marks!P$5:P$39))=0,"",SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*(Marks!P$5:P$39=1))/SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*ISNUMBER(Marks!P$5:P$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AN$5:$AN$39="bottom")*ISNUMBER(Marks!P$5:P$39))=0,"",SUMPRODUCT((Marks!$AN$5:$AN$39="bottom")*(Marks!P$5:P$39=1))/SUMPRODUCT((Marks!$AN$5:$AN$39="bottom")*ISNUMBER(Marks!P$5:P$39)))</f>
         <v/>
       </c>
       <c r="L19" s="6">
@@ -4747,7 +3883,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>More than one correct</t>
+          <t>Order the steps</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4757,12 +3893,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>[S]</t>
+          <t>[F]</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>b, c, d</t>
+          <t>b, d, a, c</t>
         </is>
       </c>
       <c r="G20">
@@ -4778,11 +3914,11 @@
         <v/>
       </c>
       <c r="J20" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BF$5:$BF$39="top")*ISNUMBER(Marks!Q$5:Q$39))=0,"",SUMPRODUCT((Marks!$BF$5:$BF$39="top")*(Marks!Q$5:Q$39=1))/SUMPRODUCT((Marks!$BF$5:$BF$39="top")*ISNUMBER(Marks!Q$5:Q$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AN$5:$AN$39="top")*ISNUMBER(Marks!Q$5:Q$39))=0,"",SUMPRODUCT((Marks!$AN$5:$AN$39="top")*(Marks!Q$5:Q$39=1))/SUMPRODUCT((Marks!$AN$5:$AN$39="top")*ISNUMBER(Marks!Q$5:Q$39)))</f>
         <v/>
       </c>
       <c r="K20" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*ISNUMBER(Marks!Q$5:Q$39))=0,"",SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*(Marks!Q$5:Q$39=1))/SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*ISNUMBER(Marks!Q$5:Q$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AN$5:$AN$39="bottom")*ISNUMBER(Marks!Q$5:Q$39))=0,"",SUMPRODUCT((Marks!$AN$5:$AN$39="bottom")*(Marks!Q$5:Q$39=1))/SUMPRODUCT((Marks!$AN$5:$AN$39="bottom")*ISNUMBER(Marks!Q$5:Q$39)))</f>
         <v/>
       </c>
       <c r="L20" s="6">
@@ -4803,16 +3939,16 @@
         <v>17</v>
       </c>
       <c r="B21" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Scenario set</t>
+          <t>More than one correct</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>Hard</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -4822,7 +3958,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>a, c, d</t>
         </is>
       </c>
       <c r="G21">
@@ -4838,11 +3974,11 @@
         <v/>
       </c>
       <c r="J21" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BF$5:$BF$39="top")*ISNUMBER(Marks!R$5:R$39))=0,"",SUMPRODUCT((Marks!$BF$5:$BF$39="top")*(Marks!R$5:R$39=1))/SUMPRODUCT((Marks!$BF$5:$BF$39="top")*ISNUMBER(Marks!R$5:R$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AN$5:$AN$39="top")*ISNUMBER(Marks!R$5:R$39))=0,"",SUMPRODUCT((Marks!$AN$5:$AN$39="top")*(Marks!R$5:R$39=1))/SUMPRODUCT((Marks!$AN$5:$AN$39="top")*ISNUMBER(Marks!R$5:R$39)))</f>
         <v/>
       </c>
       <c r="K21" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*ISNUMBER(Marks!R$5:R$39))=0,"",SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*(Marks!R$5:R$39=1))/SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*ISNUMBER(Marks!R$5:R$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AN$5:$AN$39="bottom")*ISNUMBER(Marks!R$5:R$39))=0,"",SUMPRODUCT((Marks!$AN$5:$AN$39="bottom")*(Marks!R$5:R$39=1))/SUMPRODUCT((Marks!$AN$5:$AN$39="bottom")*ISNUMBER(Marks!R$5:R$39)))</f>
         <v/>
       </c>
       <c r="L21" s="6">
@@ -4863,16 +3999,16 @@
         <v>18</v>
       </c>
       <c r="B22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Scenario set</t>
+          <t>One correct option</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Hard</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -4882,7 +4018,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>c</t>
         </is>
       </c>
       <c r="G22">
@@ -4898,11 +4034,11 @@
         <v/>
       </c>
       <c r="J22" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BF$5:$BF$39="top")*ISNUMBER(Marks!S$5:S$39))=0,"",SUMPRODUCT((Marks!$BF$5:$BF$39="top")*(Marks!S$5:S$39=1))/SUMPRODUCT((Marks!$BF$5:$BF$39="top")*ISNUMBER(Marks!S$5:S$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AN$5:$AN$39="top")*ISNUMBER(Marks!S$5:S$39))=0,"",SUMPRODUCT((Marks!$AN$5:$AN$39="top")*(Marks!S$5:S$39=1))/SUMPRODUCT((Marks!$AN$5:$AN$39="top")*ISNUMBER(Marks!S$5:S$39)))</f>
         <v/>
       </c>
       <c r="K22" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*ISNUMBER(Marks!S$5:S$39))=0,"",SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*(Marks!S$5:S$39=1))/SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*ISNUMBER(Marks!S$5:S$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AN$5:$AN$39="bottom")*ISNUMBER(Marks!S$5:S$39))=0,"",SUMPRODUCT((Marks!$AN$5:$AN$39="bottom")*(Marks!S$5:S$39=1))/SUMPRODUCT((Marks!$AN$5:$AN$39="bottom")*ISNUMBER(Marks!S$5:S$39)))</f>
         <v/>
       </c>
       <c r="L22" s="6">
@@ -4923,16 +4059,16 @@
         <v>19</v>
       </c>
       <c r="B23" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Scenario set</t>
+          <t>One correct option</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Hard</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -4942,7 +4078,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>b</t>
         </is>
       </c>
       <c r="G23">
@@ -4958,11 +4094,11 @@
         <v/>
       </c>
       <c r="J23" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BF$5:$BF$39="top")*ISNUMBER(Marks!T$5:T$39))=0,"",SUMPRODUCT((Marks!$BF$5:$BF$39="top")*(Marks!T$5:T$39=1))/SUMPRODUCT((Marks!$BF$5:$BF$39="top")*ISNUMBER(Marks!T$5:T$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AN$5:$AN$39="top")*ISNUMBER(Marks!T$5:T$39))=0,"",SUMPRODUCT((Marks!$AN$5:$AN$39="top")*(Marks!T$5:T$39=1))/SUMPRODUCT((Marks!$AN$5:$AN$39="top")*ISNUMBER(Marks!T$5:T$39)))</f>
         <v/>
       </c>
       <c r="K23" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*ISNUMBER(Marks!T$5:T$39))=0,"",SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*(Marks!T$5:T$39=1))/SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*ISNUMBER(Marks!T$5:T$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AN$5:$AN$39="bottom")*ISNUMBER(Marks!T$5:T$39))=0,"",SUMPRODUCT((Marks!$AN$5:$AN$39="bottom")*(Marks!T$5:T$39=1))/SUMPRODUCT((Marks!$AN$5:$AN$39="bottom")*ISNUMBER(Marks!T$5:T$39)))</f>
         <v/>
       </c>
       <c r="L23" s="6">
@@ -4983,7 +4119,7 @@
         <v>20</v>
       </c>
       <c r="B24" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -5018,11 +4154,11 @@
         <v/>
       </c>
       <c r="J24" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BF$5:$BF$39="top")*ISNUMBER(Marks!U$5:U$39))=0,"",SUMPRODUCT((Marks!$BF$5:$BF$39="top")*(Marks!U$5:U$39=1))/SUMPRODUCT((Marks!$BF$5:$BF$39="top")*ISNUMBER(Marks!U$5:U$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AN$5:$AN$39="top")*ISNUMBER(Marks!U$5:U$39))=0,"",SUMPRODUCT((Marks!$AN$5:$AN$39="top")*(Marks!U$5:U$39=1))/SUMPRODUCT((Marks!$AN$5:$AN$39="top")*ISNUMBER(Marks!U$5:U$39)))</f>
         <v/>
       </c>
       <c r="K24" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*ISNUMBER(Marks!U$5:U$39))=0,"",SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*(Marks!U$5:U$39=1))/SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*ISNUMBER(Marks!U$5:U$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AN$5:$AN$39="bottom")*ISNUMBER(Marks!U$5:U$39))=0,"",SUMPRODUCT((Marks!$AN$5:$AN$39="bottom")*(Marks!U$5:U$39=1))/SUMPRODUCT((Marks!$AN$5:$AN$39="bottom")*ISNUMBER(Marks!U$5:U$39)))</f>
         <v/>
       </c>
       <c r="L24" s="6">
@@ -5043,26 +4179,26 @@
         <v>21</v>
       </c>
       <c r="B25" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Order the steps</t>
+          <t>Scenario set</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Hard</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>[S]</t>
+          <t>[D]</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>b, d, e, a, c</t>
+          <t>d</t>
         </is>
       </c>
       <c r="G25">
@@ -5078,11 +4214,11 @@
         <v/>
       </c>
       <c r="J25" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BF$5:$BF$39="top")*ISNUMBER(Marks!V$5:V$39))=0,"",SUMPRODUCT((Marks!$BF$5:$BF$39="top")*(Marks!V$5:V$39=1))/SUMPRODUCT((Marks!$BF$5:$BF$39="top")*ISNUMBER(Marks!V$5:V$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AN$5:$AN$39="top")*ISNUMBER(Marks!V$5:V$39))=0,"",SUMPRODUCT((Marks!$AN$5:$AN$39="top")*(Marks!V$5:V$39=1))/SUMPRODUCT((Marks!$AN$5:$AN$39="top")*ISNUMBER(Marks!V$5:V$39)))</f>
         <v/>
       </c>
       <c r="K25" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*ISNUMBER(Marks!V$5:V$39))=0,"",SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*(Marks!V$5:V$39=1))/SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*ISNUMBER(Marks!V$5:V$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AN$5:$AN$39="bottom")*ISNUMBER(Marks!V$5:V$39))=0,"",SUMPRODUCT((Marks!$AN$5:$AN$39="bottom")*(Marks!V$5:V$39=1))/SUMPRODUCT((Marks!$AN$5:$AN$39="bottom")*ISNUMBER(Marks!V$5:V$39)))</f>
         <v/>
       </c>
       <c r="L25" s="6">
@@ -5107,7 +4243,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>One correct option</t>
+          <t>Scenario set</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5122,7 +4258,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>d</t>
+          <t>c</t>
         </is>
       </c>
       <c r="G26">
@@ -5138,11 +4274,11 @@
         <v/>
       </c>
       <c r="J26" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BF$5:$BF$39="top")*ISNUMBER(Marks!W$5:W$39))=0,"",SUMPRODUCT((Marks!$BF$5:$BF$39="top")*(Marks!W$5:W$39=1))/SUMPRODUCT((Marks!$BF$5:$BF$39="top")*ISNUMBER(Marks!W$5:W$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AN$5:$AN$39="top")*ISNUMBER(Marks!W$5:W$39))=0,"",SUMPRODUCT((Marks!$AN$5:$AN$39="top")*(Marks!W$5:W$39=1))/SUMPRODUCT((Marks!$AN$5:$AN$39="top")*ISNUMBER(Marks!W$5:W$39)))</f>
         <v/>
       </c>
       <c r="K26" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*ISNUMBER(Marks!W$5:W$39))=0,"",SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*(Marks!W$5:W$39=1))/SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*ISNUMBER(Marks!W$5:W$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AN$5:$AN$39="bottom")*ISNUMBER(Marks!W$5:W$39))=0,"",SUMPRODUCT((Marks!$AN$5:$AN$39="bottom")*(Marks!W$5:W$39=1))/SUMPRODUCT((Marks!$AN$5:$AN$39="bottom")*ISNUMBER(Marks!W$5:W$39)))</f>
         <v/>
       </c>
       <c r="L26" s="6">
@@ -5163,26 +4299,26 @@
         <v>23</v>
       </c>
       <c r="B27" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>One correct option</t>
+          <t>Scenario set</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Hard</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>[F]</t>
+          <t>[S]</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>a</t>
         </is>
       </c>
       <c r="G27">
@@ -5198,11 +4334,11 @@
         <v/>
       </c>
       <c r="J27" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BF$5:$BF$39="top")*ISNUMBER(Marks!X$5:X$39))=0,"",SUMPRODUCT((Marks!$BF$5:$BF$39="top")*(Marks!X$5:X$39=1))/SUMPRODUCT((Marks!$BF$5:$BF$39="top")*ISNUMBER(Marks!X$5:X$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AN$5:$AN$39="top")*ISNUMBER(Marks!X$5:X$39))=0,"",SUMPRODUCT((Marks!$AN$5:$AN$39="top")*(Marks!X$5:X$39=1))/SUMPRODUCT((Marks!$AN$5:$AN$39="top")*ISNUMBER(Marks!X$5:X$39)))</f>
         <v/>
       </c>
       <c r="K27" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*ISNUMBER(Marks!X$5:X$39))=0,"",SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*(Marks!X$5:X$39=1))/SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*ISNUMBER(Marks!X$5:X$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AN$5:$AN$39="bottom")*ISNUMBER(Marks!X$5:X$39))=0,"",SUMPRODUCT((Marks!$AN$5:$AN$39="bottom")*(Marks!X$5:X$39=1))/SUMPRODUCT((Marks!$AN$5:$AN$39="bottom")*ISNUMBER(Marks!X$5:X$39)))</f>
         <v/>
       </c>
       <c r="L27" s="6">
@@ -5223,11 +4359,11 @@
         <v>24</v>
       </c>
       <c r="B28" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>One correct option</t>
+          <t>Scenario set</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5258,11 +4394,11 @@
         <v/>
       </c>
       <c r="J28" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BF$5:$BF$39="top")*ISNUMBER(Marks!Y$5:Y$39))=0,"",SUMPRODUCT((Marks!$BF$5:$BF$39="top")*(Marks!Y$5:Y$39=1))/SUMPRODUCT((Marks!$BF$5:$BF$39="top")*ISNUMBER(Marks!Y$5:Y$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AN$5:$AN$39="top")*ISNUMBER(Marks!Y$5:Y$39))=0,"",SUMPRODUCT((Marks!$AN$5:$AN$39="top")*(Marks!Y$5:Y$39=1))/SUMPRODUCT((Marks!$AN$5:$AN$39="top")*ISNUMBER(Marks!Y$5:Y$39)))</f>
         <v/>
       </c>
       <c r="K28" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*ISNUMBER(Marks!Y$5:Y$39))=0,"",SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*(Marks!Y$5:Y$39=1))/SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*ISNUMBER(Marks!Y$5:Y$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AN$5:$AN$39="bottom")*ISNUMBER(Marks!Y$5:Y$39))=0,"",SUMPRODUCT((Marks!$AN$5:$AN$39="bottom")*(Marks!Y$5:Y$39=1))/SUMPRODUCT((Marks!$AN$5:$AN$39="bottom")*ISNUMBER(Marks!Y$5:Y$39)))</f>
         <v/>
       </c>
       <c r="L28" s="6">
@@ -5283,7 +4419,7 @@
         <v>25</v>
       </c>
       <c r="B29" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -5302,7 +4438,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>d</t>
+          <t>c</t>
         </is>
       </c>
       <c r="G29">
@@ -5318,11 +4454,11 @@
         <v/>
       </c>
       <c r="J29" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BF$5:$BF$39="top")*ISNUMBER(Marks!Z$5:Z$39))=0,"",SUMPRODUCT((Marks!$BF$5:$BF$39="top")*(Marks!Z$5:Z$39=1))/SUMPRODUCT((Marks!$BF$5:$BF$39="top")*ISNUMBER(Marks!Z$5:Z$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AN$5:$AN$39="top")*ISNUMBER(Marks!Z$5:Z$39))=0,"",SUMPRODUCT((Marks!$AN$5:$AN$39="top")*(Marks!Z$5:Z$39=1))/SUMPRODUCT((Marks!$AN$5:$AN$39="top")*ISNUMBER(Marks!Z$5:Z$39)))</f>
         <v/>
       </c>
       <c r="K29" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*ISNUMBER(Marks!Z$5:Z$39))=0,"",SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*(Marks!Z$5:Z$39=1))/SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*ISNUMBER(Marks!Z$5:Z$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AN$5:$AN$39="bottom")*ISNUMBER(Marks!Z$5:Z$39))=0,"",SUMPRODUCT((Marks!$AN$5:$AN$39="bottom")*(Marks!Z$5:Z$39=1))/SUMPRODUCT((Marks!$AN$5:$AN$39="bottom")*ISNUMBER(Marks!Z$5:Z$39)))</f>
         <v/>
       </c>
       <c r="L29" s="6">
@@ -5343,7 +4479,7 @@
         <v>26</v>
       </c>
       <c r="B30" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -5352,17 +4488,17 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>Hard</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>[S]</t>
+          <t>[F]</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>a, c, d</t>
+          <t>b, e</t>
         </is>
       </c>
       <c r="G30">
@@ -5378,11 +4514,11 @@
         <v/>
       </c>
       <c r="J30" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BF$5:$BF$39="top")*ISNUMBER(Marks!AA$5:AA$39))=0,"",SUMPRODUCT((Marks!$BF$5:$BF$39="top")*(Marks!AA$5:AA$39=1))/SUMPRODUCT((Marks!$BF$5:$BF$39="top")*ISNUMBER(Marks!AA$5:AA$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AN$5:$AN$39="top")*ISNUMBER(Marks!AA$5:AA$39))=0,"",SUMPRODUCT((Marks!$AN$5:$AN$39="top")*(Marks!AA$5:AA$39=1))/SUMPRODUCT((Marks!$AN$5:$AN$39="top")*ISNUMBER(Marks!AA$5:AA$39)))</f>
         <v/>
       </c>
       <c r="K30" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*ISNUMBER(Marks!AA$5:AA$39))=0,"",SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*(Marks!AA$5:AA$39=1))/SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*ISNUMBER(Marks!AA$5:AA$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AN$5:$AN$39="bottom")*ISNUMBER(Marks!AA$5:AA$39))=0,"",SUMPRODUCT((Marks!$AN$5:$AN$39="bottom")*(Marks!AA$5:AA$39=1))/SUMPRODUCT((Marks!$AN$5:$AN$39="bottom")*ISNUMBER(Marks!AA$5:AA$39)))</f>
         <v/>
       </c>
       <c r="L30" s="6">
@@ -5403,26 +4539,26 @@
         <v>27</v>
       </c>
       <c r="B31" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>More than one correct</t>
+          <t>One correct option</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>Hard</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>[F]</t>
+          <t>[S]</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>a, b, c</t>
+          <t>b</t>
         </is>
       </c>
       <c r="G31">
@@ -5438,11 +4574,11 @@
         <v/>
       </c>
       <c r="J31" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BF$5:$BF$39="top")*ISNUMBER(Marks!AB$5:AB$39))=0,"",SUMPRODUCT((Marks!$BF$5:$BF$39="top")*(Marks!AB$5:AB$39=1))/SUMPRODUCT((Marks!$BF$5:$BF$39="top")*ISNUMBER(Marks!AB$5:AB$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AN$5:$AN$39="top")*ISNUMBER(Marks!AB$5:AB$39))=0,"",SUMPRODUCT((Marks!$AN$5:$AN$39="top")*(Marks!AB$5:AB$39=1))/SUMPRODUCT((Marks!$AN$5:$AN$39="top")*ISNUMBER(Marks!AB$5:AB$39)))</f>
         <v/>
       </c>
       <c r="K31" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*ISNUMBER(Marks!AB$5:AB$39))=0,"",SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*(Marks!AB$5:AB$39=1))/SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*ISNUMBER(Marks!AB$5:AB$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AN$5:$AN$39="bottom")*ISNUMBER(Marks!AB$5:AB$39))=0,"",SUMPRODUCT((Marks!$AN$5:$AN$39="bottom")*(Marks!AB$5:AB$39=1))/SUMPRODUCT((Marks!$AN$5:$AN$39="bottom")*ISNUMBER(Marks!AB$5:AB$39)))</f>
         <v/>
       </c>
       <c r="L31" s="6">
@@ -5463,26 +4599,26 @@
         <v>28</v>
       </c>
       <c r="B32" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Scenario set</t>
+          <t>True or false</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>Hard</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>[F]</t>
+          <t>[S]</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>197</t>
+          <t>c</t>
         </is>
       </c>
       <c r="G32">
@@ -5498,11 +4634,11 @@
         <v/>
       </c>
       <c r="J32" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BF$5:$BF$39="top")*ISNUMBER(Marks!AC$5:AC$39))=0,"",SUMPRODUCT((Marks!$BF$5:$BF$39="top")*(Marks!AC$5:AC$39=1))/SUMPRODUCT((Marks!$BF$5:$BF$39="top")*ISNUMBER(Marks!AC$5:AC$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AN$5:$AN$39="top")*ISNUMBER(Marks!AC$5:AC$39))=0,"",SUMPRODUCT((Marks!$AN$5:$AN$39="top")*(Marks!AC$5:AC$39=1))/SUMPRODUCT((Marks!$AN$5:$AN$39="top")*ISNUMBER(Marks!AC$5:AC$39)))</f>
         <v/>
       </c>
       <c r="K32" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*ISNUMBER(Marks!AC$5:AC$39))=0,"",SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*(Marks!AC$5:AC$39=1))/SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*ISNUMBER(Marks!AC$5:AC$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AN$5:$AN$39="bottom")*ISNUMBER(Marks!AC$5:AC$39))=0,"",SUMPRODUCT((Marks!$AN$5:$AN$39="bottom")*(Marks!AC$5:AC$39=1))/SUMPRODUCT((Marks!$AN$5:$AN$39="bottom")*ISNUMBER(Marks!AC$5:AC$39)))</f>
         <v/>
       </c>
       <c r="L32" s="6">
@@ -5523,16 +4659,16 @@
         <v>29</v>
       </c>
       <c r="B33" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Scenario set</t>
+          <t>One correct option</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Hard</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -5542,7 +4678,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>b</t>
         </is>
       </c>
       <c r="G33">
@@ -5558,11 +4694,11 @@
         <v/>
       </c>
       <c r="J33" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BF$5:$BF$39="top")*ISNUMBER(Marks!AD$5:AD$39))=0,"",SUMPRODUCT((Marks!$BF$5:$BF$39="top")*(Marks!AD$5:AD$39=1))/SUMPRODUCT((Marks!$BF$5:$BF$39="top")*ISNUMBER(Marks!AD$5:AD$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AN$5:$AN$39="top")*ISNUMBER(Marks!AD$5:AD$39))=0,"",SUMPRODUCT((Marks!$AN$5:$AN$39="top")*(Marks!AD$5:AD$39=1))/SUMPRODUCT((Marks!$AN$5:$AN$39="top")*ISNUMBER(Marks!AD$5:AD$39)))</f>
         <v/>
       </c>
       <c r="K33" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*ISNUMBER(Marks!AD$5:AD$39))=0,"",SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*(Marks!AD$5:AD$39=1))/SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*ISNUMBER(Marks!AD$5:AD$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AN$5:$AN$39="bottom")*ISNUMBER(Marks!AD$5:AD$39))=0,"",SUMPRODUCT((Marks!$AN$5:$AN$39="bottom")*(Marks!AD$5:AD$39=1))/SUMPRODUCT((Marks!$AN$5:$AN$39="bottom")*ISNUMBER(Marks!AD$5:AD$39)))</f>
         <v/>
       </c>
       <c r="L33" s="6">
@@ -5583,26 +4719,26 @@
         <v>30</v>
       </c>
       <c r="B34" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Scenario set</t>
+          <t>One correct option</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Hard</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>[S]</t>
+          <t>[SV]</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>c</t>
+          <t>a</t>
         </is>
       </c>
       <c r="G34">
@@ -5618,11 +4754,11 @@
         <v/>
       </c>
       <c r="J34" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BF$5:$BF$39="top")*ISNUMBER(Marks!AE$5:AE$39))=0,"",SUMPRODUCT((Marks!$BF$5:$BF$39="top")*(Marks!AE$5:AE$39=1))/SUMPRODUCT((Marks!$BF$5:$BF$39="top")*ISNUMBER(Marks!AE$5:AE$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AN$5:$AN$39="top")*ISNUMBER(Marks!AE$5:AE$39))=0,"",SUMPRODUCT((Marks!$AN$5:$AN$39="top")*(Marks!AE$5:AE$39=1))/SUMPRODUCT((Marks!$AN$5:$AN$39="top")*ISNUMBER(Marks!AE$5:AE$39)))</f>
         <v/>
       </c>
       <c r="K34" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*ISNUMBER(Marks!AE$5:AE$39))=0,"",SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*(Marks!AE$5:AE$39=1))/SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*ISNUMBER(Marks!AE$5:AE$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AN$5:$AN$39="bottom")*ISNUMBER(Marks!AE$5:AE$39))=0,"",SUMPRODUCT((Marks!$AN$5:$AN$39="bottom")*(Marks!AE$5:AE$39=1))/SUMPRODUCT((Marks!$AN$5:$AN$39="bottom")*ISNUMBER(Marks!AE$5:AE$39)))</f>
         <v/>
       </c>
       <c r="L34" s="6">
@@ -5643,26 +4779,26 @@
         <v>31</v>
       </c>
       <c r="B35" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Order the steps</t>
+          <t>One correct option</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Hard</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>[F]</t>
+          <t>[S]</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>b, d, a, c</t>
+          <t>d</t>
         </is>
       </c>
       <c r="G35">
@@ -5678,11 +4814,11 @@
         <v/>
       </c>
       <c r="J35" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BF$5:$BF$39="top")*ISNUMBER(Marks!AF$5:AF$39))=0,"",SUMPRODUCT((Marks!$BF$5:$BF$39="top")*(Marks!AF$5:AF$39=1))/SUMPRODUCT((Marks!$BF$5:$BF$39="top")*ISNUMBER(Marks!AF$5:AF$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AN$5:$AN$39="top")*ISNUMBER(Marks!AF$5:AF$39))=0,"",SUMPRODUCT((Marks!$AN$5:$AN$39="top")*(Marks!AF$5:AF$39=1))/SUMPRODUCT((Marks!$AN$5:$AN$39="top")*ISNUMBER(Marks!AF$5:AF$39)))</f>
         <v/>
       </c>
       <c r="K35" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*ISNUMBER(Marks!AF$5:AF$39))=0,"",SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*(Marks!AF$5:AF$39=1))/SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*ISNUMBER(Marks!AF$5:AF$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AN$5:$AN$39="bottom")*ISNUMBER(Marks!AF$5:AF$39))=0,"",SUMPRODUCT((Marks!$AN$5:$AN$39="bottom")*(Marks!AF$5:AF$39=1))/SUMPRODUCT((Marks!$AN$5:$AN$39="bottom")*ISNUMBER(Marks!AF$5:AF$39)))</f>
         <v/>
       </c>
       <c r="L35" s="6">
@@ -5703,11 +4839,11 @@
         <v>32</v>
       </c>
       <c r="B36" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>True or false</t>
+          <t>Fill in the blank</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5717,12 +4853,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>[SV]</t>
+          <t>[S]</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>d</t>
         </is>
       </c>
       <c r="G36">
@@ -5738,11 +4874,11 @@
         <v/>
       </c>
       <c r="J36" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BF$5:$BF$39="top")*ISNUMBER(Marks!AG$5:AG$39))=0,"",SUMPRODUCT((Marks!$BF$5:$BF$39="top")*(Marks!AG$5:AG$39=1))/SUMPRODUCT((Marks!$BF$5:$BF$39="top")*ISNUMBER(Marks!AG$5:AG$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AN$5:$AN$39="top")*ISNUMBER(Marks!AG$5:AG$39))=0,"",SUMPRODUCT((Marks!$AN$5:$AN$39="top")*(Marks!AG$5:AG$39=1))/SUMPRODUCT((Marks!$AN$5:$AN$39="top")*ISNUMBER(Marks!AG$5:AG$39)))</f>
         <v/>
       </c>
       <c r="K36" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*ISNUMBER(Marks!AG$5:AG$39))=0,"",SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*(Marks!AG$5:AG$39=1))/SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*ISNUMBER(Marks!AG$5:AG$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AN$5:$AN$39="bottom")*ISNUMBER(Marks!AG$5:AG$39))=0,"",SUMPRODUCT((Marks!$AN$5:$AN$39="bottom")*(Marks!AG$5:AG$39=1))/SUMPRODUCT((Marks!$AN$5:$AN$39="bottom")*ISNUMBER(Marks!AG$5:AG$39)))</f>
         <v/>
       </c>
       <c r="L36" s="6">
@@ -5763,11 +4899,11 @@
         <v>33</v>
       </c>
       <c r="B37" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Scenario set</t>
+          <t>Fill in the blank</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5782,7 +4918,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>d</t>
+          <t>b</t>
         </is>
       </c>
       <c r="G37">
@@ -5798,11 +4934,11 @@
         <v/>
       </c>
       <c r="J37" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BF$5:$BF$39="top")*ISNUMBER(Marks!AH$5:AH$39))=0,"",SUMPRODUCT((Marks!$BF$5:$BF$39="top")*(Marks!AH$5:AH$39=1))/SUMPRODUCT((Marks!$BF$5:$BF$39="top")*ISNUMBER(Marks!AH$5:AH$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AN$5:$AN$39="top")*ISNUMBER(Marks!AH$5:AH$39))=0,"",SUMPRODUCT((Marks!$AN$5:$AN$39="top")*(Marks!AH$5:AH$39=1))/SUMPRODUCT((Marks!$AN$5:$AN$39="top")*ISNUMBER(Marks!AH$5:AH$39)))</f>
         <v/>
       </c>
       <c r="K37" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*ISNUMBER(Marks!AH$5:AH$39))=0,"",SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*(Marks!AH$5:AH$39=1))/SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*ISNUMBER(Marks!AH$5:AH$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AN$5:$AN$39="bottom")*ISNUMBER(Marks!AH$5:AH$39))=0,"",SUMPRODUCT((Marks!$AN$5:$AN$39="bottom")*(Marks!AH$5:AH$39=1))/SUMPRODUCT((Marks!$AN$5:$AN$39="bottom")*ISNUMBER(Marks!AH$5:AH$39)))</f>
         <v/>
       </c>
       <c r="L37" s="6">
@@ -5823,26 +4959,26 @@
         <v>34</v>
       </c>
       <c r="B38" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Scenario set</t>
+          <t>Match the following</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Hard</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>[D]</t>
+          <t>[S]</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>c</t>
         </is>
       </c>
       <c r="G38">
@@ -5858,11 +4994,11 @@
         <v/>
       </c>
       <c r="J38" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BF$5:$BF$39="top")*ISNUMBER(Marks!AI$5:AI$39))=0,"",SUMPRODUCT((Marks!$BF$5:$BF$39="top")*(Marks!AI$5:AI$39=1))/SUMPRODUCT((Marks!$BF$5:$BF$39="top")*ISNUMBER(Marks!AI$5:AI$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AN$5:$AN$39="top")*ISNUMBER(Marks!AI$5:AI$39))=0,"",SUMPRODUCT((Marks!$AN$5:$AN$39="top")*(Marks!AI$5:AI$39=1))/SUMPRODUCT((Marks!$AN$5:$AN$39="top")*ISNUMBER(Marks!AI$5:AI$39)))</f>
         <v/>
       </c>
       <c r="K38" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*ISNUMBER(Marks!AI$5:AI$39))=0,"",SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*(Marks!AI$5:AI$39=1))/SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*ISNUMBER(Marks!AI$5:AI$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AN$5:$AN$39="bottom")*ISNUMBER(Marks!AI$5:AI$39))=0,"",SUMPRODUCT((Marks!$AN$5:$AN$39="bottom")*(Marks!AI$5:AI$39=1))/SUMPRODUCT((Marks!$AN$5:$AN$39="bottom")*ISNUMBER(Marks!AI$5:AI$39)))</f>
         <v/>
       </c>
       <c r="L38" s="6">
@@ -5883,16 +5019,16 @@
         <v>35</v>
       </c>
       <c r="B39" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Scenario set</t>
+          <t>Match the following</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -5902,7 +5038,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2.00 (or 2)</t>
+          <t>f</t>
         </is>
       </c>
       <c r="G39">
@@ -5918,11 +5054,11 @@
         <v/>
       </c>
       <c r="J39" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BF$5:$BF$39="top")*ISNUMBER(Marks!AJ$5:AJ$39))=0,"",SUMPRODUCT((Marks!$BF$5:$BF$39="top")*(Marks!AJ$5:AJ$39=1))/SUMPRODUCT((Marks!$BF$5:$BF$39="top")*ISNUMBER(Marks!AJ$5:AJ$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AN$5:$AN$39="top")*ISNUMBER(Marks!AJ$5:AJ$39))=0,"",SUMPRODUCT((Marks!$AN$5:$AN$39="top")*(Marks!AJ$5:AJ$39=1))/SUMPRODUCT((Marks!$AN$5:$AN$39="top")*ISNUMBER(Marks!AJ$5:AJ$39)))</f>
         <v/>
       </c>
       <c r="K39" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*ISNUMBER(Marks!AJ$5:AJ$39))=0,"",SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*(Marks!AJ$5:AJ$39=1))/SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*ISNUMBER(Marks!AJ$5:AJ$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AN$5:$AN$39="bottom")*ISNUMBER(Marks!AJ$5:AJ$39))=0,"",SUMPRODUCT((Marks!$AN$5:$AN$39="bottom")*(Marks!AJ$5:AJ$39=1))/SUMPRODUCT((Marks!$AN$5:$AN$39="bottom")*ISNUMBER(Marks!AJ$5:AJ$39)))</f>
         <v/>
       </c>
       <c r="L39" s="6">
@@ -5943,11 +5079,11 @@
         <v>36</v>
       </c>
       <c r="B40" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Scenario set</t>
+          <t>Match the following</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5962,7 +5098,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>4,000 (Rs 4,000)</t>
+          <t>a</t>
         </is>
       </c>
       <c r="G40">
@@ -5978,11 +5114,11 @@
         <v/>
       </c>
       <c r="J40" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BF$5:$BF$39="top")*ISNUMBER(Marks!AK$5:AK$39))=0,"",SUMPRODUCT((Marks!$BF$5:$BF$39="top")*(Marks!AK$5:AK$39=1))/SUMPRODUCT((Marks!$BF$5:$BF$39="top")*ISNUMBER(Marks!AK$5:AK$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AN$5:$AN$39="top")*ISNUMBER(Marks!AK$5:AK$39))=0,"",SUMPRODUCT((Marks!$AN$5:$AN$39="top")*(Marks!AK$5:AK$39=1))/SUMPRODUCT((Marks!$AN$5:$AN$39="top")*ISNUMBER(Marks!AK$5:AK$39)))</f>
         <v/>
       </c>
       <c r="K40" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*ISNUMBER(Marks!AK$5:AK$39))=0,"",SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*(Marks!AK$5:AK$39=1))/SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*ISNUMBER(Marks!AK$5:AK$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AN$5:$AN$39="bottom")*ISNUMBER(Marks!AK$5:AK$39))=0,"",SUMPRODUCT((Marks!$AN$5:$AN$39="bottom")*(Marks!AK$5:AK$39=1))/SUMPRODUCT((Marks!$AN$5:$AN$39="bottom")*ISNUMBER(Marks!AK$5:AK$39)))</f>
         <v/>
       </c>
       <c r="L40" s="6">
@@ -5995,1086 +5131,6 @@
       </c>
       <c r="N40">
         <f>IF(H40=0,"",I40+ROW()/1000000)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="n">
-        <v>37</v>
-      </c>
-      <c r="B41" t="n">
-        <v>4</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Scenario set</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>[D]</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>c</t>
-        </is>
-      </c>
-      <c r="G41">
-        <f>COUNTIF(Marks!AL$5:AL$39,1)</f>
-        <v/>
-      </c>
-      <c r="H41">
-        <f>COUNT(Marks!AL$5:AL$39)</f>
-        <v/>
-      </c>
-      <c r="I41" s="6">
-        <f>IF(H41=0,"",G41/H41)</f>
-        <v/>
-      </c>
-      <c r="J41" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BF$5:$BF$39="top")*ISNUMBER(Marks!AL$5:AL$39))=0,"",SUMPRODUCT((Marks!$BF$5:$BF$39="top")*(Marks!AL$5:AL$39=1))/SUMPRODUCT((Marks!$BF$5:$BF$39="top")*ISNUMBER(Marks!AL$5:AL$39)))</f>
-        <v/>
-      </c>
-      <c r="K41" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*ISNUMBER(Marks!AL$5:AL$39))=0,"",SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*(Marks!AL$5:AL$39=1))/SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*ISNUMBER(Marks!AL$5:AL$39)))</f>
-        <v/>
-      </c>
-      <c r="L41" s="6">
-        <f>IF(OR(J41="",K41=""),"",J41-K41)</f>
-        <v/>
-      </c>
-      <c r="M41">
-        <f>IF(H41=0,"",IF(I41&lt;0.2,"Check the item: fewer than one in five got it right",IF(AND(L41&lt;&gt;"",N(L41)&lt;0),"Check the item: the bottom third beat the top third","")))</f>
-        <v/>
-      </c>
-      <c r="N41">
-        <f>IF(H41=0,"",I41+ROW()/1000000)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="n">
-        <v>38</v>
-      </c>
-      <c r="B42" t="n">
-        <v>4</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>One correct option</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>[S]</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>d</t>
-        </is>
-      </c>
-      <c r="G42">
-        <f>COUNTIF(Marks!AM$5:AM$39,1)</f>
-        <v/>
-      </c>
-      <c r="H42">
-        <f>COUNT(Marks!AM$5:AM$39)</f>
-        <v/>
-      </c>
-      <c r="I42" s="6">
-        <f>IF(H42=0,"",G42/H42)</f>
-        <v/>
-      </c>
-      <c r="J42" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BF$5:$BF$39="top")*ISNUMBER(Marks!AM$5:AM$39))=0,"",SUMPRODUCT((Marks!$BF$5:$BF$39="top")*(Marks!AM$5:AM$39=1))/SUMPRODUCT((Marks!$BF$5:$BF$39="top")*ISNUMBER(Marks!AM$5:AM$39)))</f>
-        <v/>
-      </c>
-      <c r="K42" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*ISNUMBER(Marks!AM$5:AM$39))=0,"",SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*(Marks!AM$5:AM$39=1))/SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*ISNUMBER(Marks!AM$5:AM$39)))</f>
-        <v/>
-      </c>
-      <c r="L42" s="6">
-        <f>IF(OR(J42="",K42=""),"",J42-K42)</f>
-        <v/>
-      </c>
-      <c r="M42">
-        <f>IF(H42=0,"",IF(I42&lt;0.2,"Check the item: fewer than one in five got it right",IF(AND(L42&lt;&gt;"",N(L42)&lt;0),"Check the item: the bottom third beat the top third","")))</f>
-        <v/>
-      </c>
-      <c r="N42">
-        <f>IF(H42=0,"",I42+ROW()/1000000)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="n">
-        <v>39</v>
-      </c>
-      <c r="B43" t="n">
-        <v>4</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>One correct option</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>[F]</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>c</t>
-        </is>
-      </c>
-      <c r="G43">
-        <f>COUNTIF(Marks!AN$5:AN$39,1)</f>
-        <v/>
-      </c>
-      <c r="H43">
-        <f>COUNT(Marks!AN$5:AN$39)</f>
-        <v/>
-      </c>
-      <c r="I43" s="6">
-        <f>IF(H43=0,"",G43/H43)</f>
-        <v/>
-      </c>
-      <c r="J43" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BF$5:$BF$39="top")*ISNUMBER(Marks!AN$5:AN$39))=0,"",SUMPRODUCT((Marks!$BF$5:$BF$39="top")*(Marks!AN$5:AN$39=1))/SUMPRODUCT((Marks!$BF$5:$BF$39="top")*ISNUMBER(Marks!AN$5:AN$39)))</f>
-        <v/>
-      </c>
-      <c r="K43" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*ISNUMBER(Marks!AN$5:AN$39))=0,"",SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*(Marks!AN$5:AN$39=1))/SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*ISNUMBER(Marks!AN$5:AN$39)))</f>
-        <v/>
-      </c>
-      <c r="L43" s="6">
-        <f>IF(OR(J43="",K43=""),"",J43-K43)</f>
-        <v/>
-      </c>
-      <c r="M43">
-        <f>IF(H43=0,"",IF(I43&lt;0.2,"Check the item: fewer than one in five got it right",IF(AND(L43&lt;&gt;"",N(L43)&lt;0),"Check the item: the bottom third beat the top third","")))</f>
-        <v/>
-      </c>
-      <c r="N43">
-        <f>IF(H43=0,"",I43+ROW()/1000000)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="n">
-        <v>40</v>
-      </c>
-      <c r="B44" t="n">
-        <v>4</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>One correct option</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>[F]</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>b</t>
-        </is>
-      </c>
-      <c r="G44">
-        <f>COUNTIF(Marks!AO$5:AO$39,1)</f>
-        <v/>
-      </c>
-      <c r="H44">
-        <f>COUNT(Marks!AO$5:AO$39)</f>
-        <v/>
-      </c>
-      <c r="I44" s="6">
-        <f>IF(H44=0,"",G44/H44)</f>
-        <v/>
-      </c>
-      <c r="J44" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BF$5:$BF$39="top")*ISNUMBER(Marks!AO$5:AO$39))=0,"",SUMPRODUCT((Marks!$BF$5:$BF$39="top")*(Marks!AO$5:AO$39=1))/SUMPRODUCT((Marks!$BF$5:$BF$39="top")*ISNUMBER(Marks!AO$5:AO$39)))</f>
-        <v/>
-      </c>
-      <c r="K44" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*ISNUMBER(Marks!AO$5:AO$39))=0,"",SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*(Marks!AO$5:AO$39=1))/SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*ISNUMBER(Marks!AO$5:AO$39)))</f>
-        <v/>
-      </c>
-      <c r="L44" s="6">
-        <f>IF(OR(J44="",K44=""),"",J44-K44)</f>
-        <v/>
-      </c>
-      <c r="M44">
-        <f>IF(H44=0,"",IF(I44&lt;0.2,"Check the item: fewer than one in five got it right",IF(AND(L44&lt;&gt;"",N(L44)&lt;0),"Check the item: the bottom third beat the top third","")))</f>
-        <v/>
-      </c>
-      <c r="N44">
-        <f>IF(H44=0,"",I44+ROW()/1000000)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="n">
-        <v>41</v>
-      </c>
-      <c r="B45" t="n">
-        <v>4</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>One correct option</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>[F]</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
-      <c r="G45">
-        <f>COUNTIF(Marks!AP$5:AP$39,1)</f>
-        <v/>
-      </c>
-      <c r="H45">
-        <f>COUNT(Marks!AP$5:AP$39)</f>
-        <v/>
-      </c>
-      <c r="I45" s="6">
-        <f>IF(H45=0,"",G45/H45)</f>
-        <v/>
-      </c>
-      <c r="J45" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BF$5:$BF$39="top")*ISNUMBER(Marks!AP$5:AP$39))=0,"",SUMPRODUCT((Marks!$BF$5:$BF$39="top")*(Marks!AP$5:AP$39=1))/SUMPRODUCT((Marks!$BF$5:$BF$39="top")*ISNUMBER(Marks!AP$5:AP$39)))</f>
-        <v/>
-      </c>
-      <c r="K45" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*ISNUMBER(Marks!AP$5:AP$39))=0,"",SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*(Marks!AP$5:AP$39=1))/SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*ISNUMBER(Marks!AP$5:AP$39)))</f>
-        <v/>
-      </c>
-      <c r="L45" s="6">
-        <f>IF(OR(J45="",K45=""),"",J45-K45)</f>
-        <v/>
-      </c>
-      <c r="M45">
-        <f>IF(H45=0,"",IF(I45&lt;0.2,"Check the item: fewer than one in five got it right",IF(AND(L45&lt;&gt;"",N(L45)&lt;0),"Check the item: the bottom third beat the top third","")))</f>
-        <v/>
-      </c>
-      <c r="N45">
-        <f>IF(H45=0,"",I45+ROW()/1000000)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="n">
-        <v>42</v>
-      </c>
-      <c r="B46" t="n">
-        <v>5</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>One correct option</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>[S]</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>c</t>
-        </is>
-      </c>
-      <c r="G46">
-        <f>COUNTIF(Marks!AQ$5:AQ$39,1)</f>
-        <v/>
-      </c>
-      <c r="H46">
-        <f>COUNT(Marks!AQ$5:AQ$39)</f>
-        <v/>
-      </c>
-      <c r="I46" s="6">
-        <f>IF(H46=0,"",G46/H46)</f>
-        <v/>
-      </c>
-      <c r="J46" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BF$5:$BF$39="top")*ISNUMBER(Marks!AQ$5:AQ$39))=0,"",SUMPRODUCT((Marks!$BF$5:$BF$39="top")*(Marks!AQ$5:AQ$39=1))/SUMPRODUCT((Marks!$BF$5:$BF$39="top")*ISNUMBER(Marks!AQ$5:AQ$39)))</f>
-        <v/>
-      </c>
-      <c r="K46" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*ISNUMBER(Marks!AQ$5:AQ$39))=0,"",SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*(Marks!AQ$5:AQ$39=1))/SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*ISNUMBER(Marks!AQ$5:AQ$39)))</f>
-        <v/>
-      </c>
-      <c r="L46" s="6">
-        <f>IF(OR(J46="",K46=""),"",J46-K46)</f>
-        <v/>
-      </c>
-      <c r="M46">
-        <f>IF(H46=0,"",IF(I46&lt;0.2,"Check the item: fewer than one in five got it right",IF(AND(L46&lt;&gt;"",N(L46)&lt;0),"Check the item: the bottom third beat the top third","")))</f>
-        <v/>
-      </c>
-      <c r="N46">
-        <f>IF(H46=0,"",I46+ROW()/1000000)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="n">
-        <v>43</v>
-      </c>
-      <c r="B47" t="n">
-        <v>5</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>One correct option</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>[F]</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>b</t>
-        </is>
-      </c>
-      <c r="G47">
-        <f>COUNTIF(Marks!AR$5:AR$39,1)</f>
-        <v/>
-      </c>
-      <c r="H47">
-        <f>COUNT(Marks!AR$5:AR$39)</f>
-        <v/>
-      </c>
-      <c r="I47" s="6">
-        <f>IF(H47=0,"",G47/H47)</f>
-        <v/>
-      </c>
-      <c r="J47" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BF$5:$BF$39="top")*ISNUMBER(Marks!AR$5:AR$39))=0,"",SUMPRODUCT((Marks!$BF$5:$BF$39="top")*(Marks!AR$5:AR$39=1))/SUMPRODUCT((Marks!$BF$5:$BF$39="top")*ISNUMBER(Marks!AR$5:AR$39)))</f>
-        <v/>
-      </c>
-      <c r="K47" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*ISNUMBER(Marks!AR$5:AR$39))=0,"",SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*(Marks!AR$5:AR$39=1))/SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*ISNUMBER(Marks!AR$5:AR$39)))</f>
-        <v/>
-      </c>
-      <c r="L47" s="6">
-        <f>IF(OR(J47="",K47=""),"",J47-K47)</f>
-        <v/>
-      </c>
-      <c r="M47">
-        <f>IF(H47=0,"",IF(I47&lt;0.2,"Check the item: fewer than one in five got it right",IF(AND(L47&lt;&gt;"",N(L47)&lt;0),"Check the item: the bottom third beat the top third","")))</f>
-        <v/>
-      </c>
-      <c r="N47">
-        <f>IF(H47=0,"",I47+ROW()/1000000)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="n">
-        <v>44</v>
-      </c>
-      <c r="B48" t="n">
-        <v>5</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>More than one correct</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>[F]</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>b, c, d</t>
-        </is>
-      </c>
-      <c r="G48">
-        <f>COUNTIF(Marks!AS$5:AS$39,1)</f>
-        <v/>
-      </c>
-      <c r="H48">
-        <f>COUNT(Marks!AS$5:AS$39)</f>
-        <v/>
-      </c>
-      <c r="I48" s="6">
-        <f>IF(H48=0,"",G48/H48)</f>
-        <v/>
-      </c>
-      <c r="J48" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BF$5:$BF$39="top")*ISNUMBER(Marks!AS$5:AS$39))=0,"",SUMPRODUCT((Marks!$BF$5:$BF$39="top")*(Marks!AS$5:AS$39=1))/SUMPRODUCT((Marks!$BF$5:$BF$39="top")*ISNUMBER(Marks!AS$5:AS$39)))</f>
-        <v/>
-      </c>
-      <c r="K48" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*ISNUMBER(Marks!AS$5:AS$39))=0,"",SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*(Marks!AS$5:AS$39=1))/SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*ISNUMBER(Marks!AS$5:AS$39)))</f>
-        <v/>
-      </c>
-      <c r="L48" s="6">
-        <f>IF(OR(J48="",K48=""),"",J48-K48)</f>
-        <v/>
-      </c>
-      <c r="M48">
-        <f>IF(H48=0,"",IF(I48&lt;0.2,"Check the item: fewer than one in five got it right",IF(AND(L48&lt;&gt;"",N(L48)&lt;0),"Check the item: the bottom third beat the top third","")))</f>
-        <v/>
-      </c>
-      <c r="N48">
-        <f>IF(H48=0,"",I48+ROW()/1000000)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="n">
-        <v>45</v>
-      </c>
-      <c r="B49" t="n">
-        <v>5</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>More than one correct</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>[S]</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>a, c, d</t>
-        </is>
-      </c>
-      <c r="G49">
-        <f>COUNTIF(Marks!AT$5:AT$39,1)</f>
-        <v/>
-      </c>
-      <c r="H49">
-        <f>COUNT(Marks!AT$5:AT$39)</f>
-        <v/>
-      </c>
-      <c r="I49" s="6">
-        <f>IF(H49=0,"",G49/H49)</f>
-        <v/>
-      </c>
-      <c r="J49" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BF$5:$BF$39="top")*ISNUMBER(Marks!AT$5:AT$39))=0,"",SUMPRODUCT((Marks!$BF$5:$BF$39="top")*(Marks!AT$5:AT$39=1))/SUMPRODUCT((Marks!$BF$5:$BF$39="top")*ISNUMBER(Marks!AT$5:AT$39)))</f>
-        <v/>
-      </c>
-      <c r="K49" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*ISNUMBER(Marks!AT$5:AT$39))=0,"",SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*(Marks!AT$5:AT$39=1))/SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*ISNUMBER(Marks!AT$5:AT$39)))</f>
-        <v/>
-      </c>
-      <c r="L49" s="6">
-        <f>IF(OR(J49="",K49=""),"",J49-K49)</f>
-        <v/>
-      </c>
-      <c r="M49">
-        <f>IF(H49=0,"",IF(I49&lt;0.2,"Check the item: fewer than one in five got it right",IF(AND(L49&lt;&gt;"",N(L49)&lt;0),"Check the item: the bottom third beat the top third","")))</f>
-        <v/>
-      </c>
-      <c r="N49">
-        <f>IF(H49=0,"",I49+ROW()/1000000)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="n">
-        <v>46</v>
-      </c>
-      <c r="B50" t="n">
-        <v>5</v>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Scenario set</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>[D]</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
-      <c r="G50">
-        <f>COUNTIF(Marks!AU$5:AU$39,1)</f>
-        <v/>
-      </c>
-      <c r="H50">
-        <f>COUNT(Marks!AU$5:AU$39)</f>
-        <v/>
-      </c>
-      <c r="I50" s="6">
-        <f>IF(H50=0,"",G50/H50)</f>
-        <v/>
-      </c>
-      <c r="J50" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BF$5:$BF$39="top")*ISNUMBER(Marks!AU$5:AU$39))=0,"",SUMPRODUCT((Marks!$BF$5:$BF$39="top")*(Marks!AU$5:AU$39=1))/SUMPRODUCT((Marks!$BF$5:$BF$39="top")*ISNUMBER(Marks!AU$5:AU$39)))</f>
-        <v/>
-      </c>
-      <c r="K50" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*ISNUMBER(Marks!AU$5:AU$39))=0,"",SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*(Marks!AU$5:AU$39=1))/SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*ISNUMBER(Marks!AU$5:AU$39)))</f>
-        <v/>
-      </c>
-      <c r="L50" s="6">
-        <f>IF(OR(J50="",K50=""),"",J50-K50)</f>
-        <v/>
-      </c>
-      <c r="M50">
-        <f>IF(H50=0,"",IF(I50&lt;0.2,"Check the item: fewer than one in five got it right",IF(AND(L50&lt;&gt;"",N(L50)&lt;0),"Check the item: the bottom third beat the top third","")))</f>
-        <v/>
-      </c>
-      <c r="N50">
-        <f>IF(H50=0,"",I50+ROW()/1000000)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="n">
-        <v>47</v>
-      </c>
-      <c r="B51" t="n">
-        <v>5</v>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Scenario set</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>[F]</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="G51">
-        <f>COUNTIF(Marks!AV$5:AV$39,1)</f>
-        <v/>
-      </c>
-      <c r="H51">
-        <f>COUNT(Marks!AV$5:AV$39)</f>
-        <v/>
-      </c>
-      <c r="I51" s="6">
-        <f>IF(H51=0,"",G51/H51)</f>
-        <v/>
-      </c>
-      <c r="J51" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BF$5:$BF$39="top")*ISNUMBER(Marks!AV$5:AV$39))=0,"",SUMPRODUCT((Marks!$BF$5:$BF$39="top")*(Marks!AV$5:AV$39=1))/SUMPRODUCT((Marks!$BF$5:$BF$39="top")*ISNUMBER(Marks!AV$5:AV$39)))</f>
-        <v/>
-      </c>
-      <c r="K51" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*ISNUMBER(Marks!AV$5:AV$39))=0,"",SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*(Marks!AV$5:AV$39=1))/SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*ISNUMBER(Marks!AV$5:AV$39)))</f>
-        <v/>
-      </c>
-      <c r="L51" s="6">
-        <f>IF(OR(J51="",K51=""),"",J51-K51)</f>
-        <v/>
-      </c>
-      <c r="M51">
-        <f>IF(H51=0,"",IF(I51&lt;0.2,"Check the item: fewer than one in five got it right",IF(AND(L51&lt;&gt;"",N(L51)&lt;0),"Check the item: the bottom third beat the top third","")))</f>
-        <v/>
-      </c>
-      <c r="N51">
-        <f>IF(H51=0,"",I51+ROW()/1000000)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="n">
-        <v>48</v>
-      </c>
-      <c r="B52" t="n">
-        <v>5</v>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Scenario set</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>[D]</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>d</t>
-        </is>
-      </c>
-      <c r="G52">
-        <f>COUNTIF(Marks!AW$5:AW$39,1)</f>
-        <v/>
-      </c>
-      <c r="H52">
-        <f>COUNT(Marks!AW$5:AW$39)</f>
-        <v/>
-      </c>
-      <c r="I52" s="6">
-        <f>IF(H52=0,"",G52/H52)</f>
-        <v/>
-      </c>
-      <c r="J52" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BF$5:$BF$39="top")*ISNUMBER(Marks!AW$5:AW$39))=0,"",SUMPRODUCT((Marks!$BF$5:$BF$39="top")*(Marks!AW$5:AW$39=1))/SUMPRODUCT((Marks!$BF$5:$BF$39="top")*ISNUMBER(Marks!AW$5:AW$39)))</f>
-        <v/>
-      </c>
-      <c r="K52" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*ISNUMBER(Marks!AW$5:AW$39))=0,"",SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*(Marks!AW$5:AW$39=1))/SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*ISNUMBER(Marks!AW$5:AW$39)))</f>
-        <v/>
-      </c>
-      <c r="L52" s="6">
-        <f>IF(OR(J52="",K52=""),"",J52-K52)</f>
-        <v/>
-      </c>
-      <c r="M52">
-        <f>IF(H52=0,"",IF(I52&lt;0.2,"Check the item: fewer than one in five got it right",IF(AND(L52&lt;&gt;"",N(L52)&lt;0),"Check the item: the bottom third beat the top third","")))</f>
-        <v/>
-      </c>
-      <c r="N52">
-        <f>IF(H52=0,"",I52+ROW()/1000000)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="n">
-        <v>49</v>
-      </c>
-      <c r="B53" t="n">
-        <v>6</v>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>One correct option</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>[S]</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>d</t>
-        </is>
-      </c>
-      <c r="G53">
-        <f>COUNTIF(Marks!AX$5:AX$39,1)</f>
-        <v/>
-      </c>
-      <c r="H53">
-        <f>COUNT(Marks!AX$5:AX$39)</f>
-        <v/>
-      </c>
-      <c r="I53" s="6">
-        <f>IF(H53=0,"",G53/H53)</f>
-        <v/>
-      </c>
-      <c r="J53" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BF$5:$BF$39="top")*ISNUMBER(Marks!AX$5:AX$39))=0,"",SUMPRODUCT((Marks!$BF$5:$BF$39="top")*(Marks!AX$5:AX$39=1))/SUMPRODUCT((Marks!$BF$5:$BF$39="top")*ISNUMBER(Marks!AX$5:AX$39)))</f>
-        <v/>
-      </c>
-      <c r="K53" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*ISNUMBER(Marks!AX$5:AX$39))=0,"",SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*(Marks!AX$5:AX$39=1))/SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*ISNUMBER(Marks!AX$5:AX$39)))</f>
-        <v/>
-      </c>
-      <c r="L53" s="6">
-        <f>IF(OR(J53="",K53=""),"",J53-K53)</f>
-        <v/>
-      </c>
-      <c r="M53">
-        <f>IF(H53=0,"",IF(I53&lt;0.2,"Check the item: fewer than one in five got it right",IF(AND(L53&lt;&gt;"",N(L53)&lt;0),"Check the item: the bottom third beat the top third","")))</f>
-        <v/>
-      </c>
-      <c r="N53">
-        <f>IF(H53=0,"",I53+ROW()/1000000)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="n">
-        <v>50</v>
-      </c>
-      <c r="B54" t="n">
-        <v>6</v>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Applied maths</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>[F]</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>Revenue falls by 6.5 percent (1.10 x 0.85 = 0.935).</t>
-        </is>
-      </c>
-      <c r="G54">
-        <f>COUNTIF(Marks!AY$5:AY$39,1)</f>
-        <v/>
-      </c>
-      <c r="H54">
-        <f>COUNT(Marks!AY$5:AY$39)</f>
-        <v/>
-      </c>
-      <c r="I54" s="6">
-        <f>IF(H54=0,"",G54/H54)</f>
-        <v/>
-      </c>
-      <c r="J54" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BF$5:$BF$39="top")*ISNUMBER(Marks!AY$5:AY$39))=0,"",SUMPRODUCT((Marks!$BF$5:$BF$39="top")*(Marks!AY$5:AY$39=1))/SUMPRODUCT((Marks!$BF$5:$BF$39="top")*ISNUMBER(Marks!AY$5:AY$39)))</f>
-        <v/>
-      </c>
-      <c r="K54" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*ISNUMBER(Marks!AY$5:AY$39))=0,"",SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*(Marks!AY$5:AY$39=1))/SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*ISNUMBER(Marks!AY$5:AY$39)))</f>
-        <v/>
-      </c>
-      <c r="L54" s="6">
-        <f>IF(OR(J54="",K54=""),"",J54-K54)</f>
-        <v/>
-      </c>
-      <c r="M54">
-        <f>IF(H54=0,"",IF(I54&lt;0.2,"Check the item: fewer than one in five got it right",IF(AND(L54&lt;&gt;"",N(L54)&lt;0),"Check the item: the bottom third beat the top third","")))</f>
-        <v/>
-      </c>
-      <c r="N54">
-        <f>IF(H54=0,"",I54+ROW()/1000000)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="n">
-        <v>51</v>
-      </c>
-      <c r="B55" t="n">
-        <v>6</v>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Applied maths</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>[S]</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>Median Rs 1,400; mean Rs 97,080.</t>
-        </is>
-      </c>
-      <c r="G55">
-        <f>COUNTIF(Marks!AZ$5:AZ$39,1)</f>
-        <v/>
-      </c>
-      <c r="H55">
-        <f>COUNT(Marks!AZ$5:AZ$39)</f>
-        <v/>
-      </c>
-      <c r="I55" s="6">
-        <f>IF(H55=0,"",G55/H55)</f>
-        <v/>
-      </c>
-      <c r="J55" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BF$5:$BF$39="top")*ISNUMBER(Marks!AZ$5:AZ$39))=0,"",SUMPRODUCT((Marks!$BF$5:$BF$39="top")*(Marks!AZ$5:AZ$39=1))/SUMPRODUCT((Marks!$BF$5:$BF$39="top")*ISNUMBER(Marks!AZ$5:AZ$39)))</f>
-        <v/>
-      </c>
-      <c r="K55" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*ISNUMBER(Marks!AZ$5:AZ$39))=0,"",SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*(Marks!AZ$5:AZ$39=1))/SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*ISNUMBER(Marks!AZ$5:AZ$39)))</f>
-        <v/>
-      </c>
-      <c r="L55" s="6">
-        <f>IF(OR(J55="",K55=""),"",J55-K55)</f>
-        <v/>
-      </c>
-      <c r="M55">
-        <f>IF(H55=0,"",IF(I55&lt;0.2,"Check the item: fewer than one in five got it right",IF(AND(L55&lt;&gt;"",N(L55)&lt;0),"Check the item: the bottom third beat the top third","")))</f>
-        <v/>
-      </c>
-      <c r="N55">
-        <f>IF(H55=0,"",I55+ROW()/1000000)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="n">
-        <v>52</v>
-      </c>
-      <c r="B56" t="n">
-        <v>6</v>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Applied maths</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>[S]</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>A fall of 9.5 percent ((1.9 - 2.1) / 2.1).</t>
-        </is>
-      </c>
-      <c r="G56">
-        <f>COUNTIF(Marks!BA$5:BA$39,1)</f>
-        <v/>
-      </c>
-      <c r="H56">
-        <f>COUNT(Marks!BA$5:BA$39)</f>
-        <v/>
-      </c>
-      <c r="I56" s="6">
-        <f>IF(H56=0,"",G56/H56)</f>
-        <v/>
-      </c>
-      <c r="J56" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BF$5:$BF$39="top")*ISNUMBER(Marks!BA$5:BA$39))=0,"",SUMPRODUCT((Marks!$BF$5:$BF$39="top")*(Marks!BA$5:BA$39=1))/SUMPRODUCT((Marks!$BF$5:$BF$39="top")*ISNUMBER(Marks!BA$5:BA$39)))</f>
-        <v/>
-      </c>
-      <c r="K56" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*ISNUMBER(Marks!BA$5:BA$39))=0,"",SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*(Marks!BA$5:BA$39=1))/SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*ISNUMBER(Marks!BA$5:BA$39)))</f>
-        <v/>
-      </c>
-      <c r="L56" s="6">
-        <f>IF(OR(J56="",K56=""),"",J56-K56)</f>
-        <v/>
-      </c>
-      <c r="M56">
-        <f>IF(H56=0,"",IF(I56&lt;0.2,"Check the item: fewer than one in five got it right",IF(AND(L56&lt;&gt;"",N(L56)&lt;0),"Check the item: the bottom third beat the top third","")))</f>
-        <v/>
-      </c>
-      <c r="N56">
-        <f>IF(H56=0,"",I56+ROW()/1000000)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="n">
-        <v>53</v>
-      </c>
-      <c r="B57" t="n">
-        <v>6</v>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Applied maths</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>[S]</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>0.028 (140 / 5,000).</t>
-        </is>
-      </c>
-      <c r="G57">
-        <f>COUNTIF(Marks!BB$5:BB$39,1)</f>
-        <v/>
-      </c>
-      <c r="H57">
-        <f>COUNT(Marks!BB$5:BB$39)</f>
-        <v/>
-      </c>
-      <c r="I57" s="6">
-        <f>IF(H57=0,"",G57/H57)</f>
-        <v/>
-      </c>
-      <c r="J57" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BF$5:$BF$39="top")*ISNUMBER(Marks!BB$5:BB$39))=0,"",SUMPRODUCT((Marks!$BF$5:$BF$39="top")*(Marks!BB$5:BB$39=1))/SUMPRODUCT((Marks!$BF$5:$BF$39="top")*ISNUMBER(Marks!BB$5:BB$39)))</f>
-        <v/>
-      </c>
-      <c r="K57" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*ISNUMBER(Marks!BB$5:BB$39))=0,"",SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*(Marks!BB$5:BB$39=1))/SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*ISNUMBER(Marks!BB$5:BB$39)))</f>
-        <v/>
-      </c>
-      <c r="L57" s="6">
-        <f>IF(OR(J57="",K57=""),"",J57-K57)</f>
-        <v/>
-      </c>
-      <c r="M57">
-        <f>IF(H57=0,"",IF(I57&lt;0.2,"Check the item: fewer than one in five got it right",IF(AND(L57&lt;&gt;"",N(L57)&lt;0),"Check the item: the bottom third beat the top third","")))</f>
-        <v/>
-      </c>
-      <c r="N57">
-        <f>IF(H57=0,"",I57+ROW()/1000000)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="n">
-        <v>54</v>
-      </c>
-      <c r="B58" t="n">
-        <v>6</v>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Applied maths</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>[S]</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>Rs 11 crore (Rs 12 crore before discounts).</t>
-        </is>
-      </c>
-      <c r="G58">
-        <f>COUNTIF(Marks!BC$5:BC$39,1)</f>
-        <v/>
-      </c>
-      <c r="H58">
-        <f>COUNT(Marks!BC$5:BC$39)</f>
-        <v/>
-      </c>
-      <c r="I58" s="6">
-        <f>IF(H58=0,"",G58/H58)</f>
-        <v/>
-      </c>
-      <c r="J58" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BF$5:$BF$39="top")*ISNUMBER(Marks!BC$5:BC$39))=0,"",SUMPRODUCT((Marks!$BF$5:$BF$39="top")*(Marks!BC$5:BC$39=1))/SUMPRODUCT((Marks!$BF$5:$BF$39="top")*ISNUMBER(Marks!BC$5:BC$39)))</f>
-        <v/>
-      </c>
-      <c r="K58" s="6">
-        <f>IF(SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*ISNUMBER(Marks!BC$5:BC$39))=0,"",SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*(Marks!BC$5:BC$39=1))/SUMPRODUCT((Marks!$BF$5:$BF$39="bottom")*ISNUMBER(Marks!BC$5:BC$39)))</f>
-        <v/>
-      </c>
-      <c r="L58" s="6">
-        <f>IF(OR(J58="",K58=""),"",J58-K58)</f>
-        <v/>
-      </c>
-      <c r="M58">
-        <f>IF(H58=0,"",IF(I58&lt;0.2,"Check the item: fewer than one in five got it right",IF(AND(L58&lt;&gt;"",N(L58)&lt;0),"Check the item: the bottom third beat the top third","")))</f>
-        <v/>
-      </c>
-      <c r="N58">
-        <f>IF(H58=0,"",I58+ROW()/1000000)</f>
         <v/>
       </c>
     </row>
@@ -7089,7 +5145,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F58"/>
+  <dimension ref="A1:F40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="6" max="6"/>
@@ -7104,7 +5160,7 @@
     </row>
     <row r="2">
       <c r="B2">
-        <f>IF(SUM(Items!H5:H58)=0,"No marks entered yet.","Most-missed first: take the items from the top.")</f>
+        <f>IF(SUM(Items!H5:H40)=0,"No marks entered yet.","Most-missed first: take the items from the top.")</f>
         <v/>
       </c>
     </row>
@@ -7145,23 +5201,23 @@
         <v>1</v>
       </c>
       <c r="B5">
-        <f>IF(COUNT(Items!$N$5:$N$58)&lt;A5,"",INDEX(Items!$A$5:$A$58,MATCH(SMALL(Items!$N$5:$N$58,A5),Items!$N$5:$N$58,0)))</f>
+        <f>IF(COUNT(Items!$N$5:$N$40)&lt;A5,"",INDEX(Items!$A$5:$A$40,MATCH(SMALL(Items!$N$5:$N$40,A5),Items!$N$5:$N$40,0)))</f>
         <v/>
       </c>
       <c r="C5" s="6">
-        <f>IF(B5="","",INDEX(Items!$I$5:$I$58,MATCH(B5,Items!$A$5:$A$58,0)))</f>
+        <f>IF(B5="","",INDEX(Items!$I$5:$I$40,MATCH(B5,Items!$A$5:$A$40,0)))</f>
         <v/>
       </c>
       <c r="D5">
-        <f>IF(B5="","",INDEX(Items!$B$5:$B$58,MATCH(B5,Items!$A$5:$A$58,0)))</f>
+        <f>IF(B5="","",INDEX(Items!$B$5:$B$40,MATCH(B5,Items!$A$5:$A$40,0)))</f>
         <v/>
       </c>
       <c r="E5">
-        <f>IF(B5="","",INDEX(Items!$E$5:$E$58,MATCH(B5,Items!$A$5:$A$58,0)))</f>
+        <f>IF(B5="","",INDEX(Items!$E$5:$E$40,MATCH(B5,Items!$A$5:$A$40,0)))</f>
         <v/>
       </c>
       <c r="F5">
-        <f>IF(B5="","",INDEX(Items!$M$5:$M$58,MATCH(B5,Items!$A$5:$A$58,0)))</f>
+        <f>IF(B5="","",INDEX(Items!$M$5:$M$40,MATCH(B5,Items!$A$5:$A$40,0)))</f>
         <v/>
       </c>
     </row>
@@ -7170,23 +5226,23 @@
         <v>2</v>
       </c>
       <c r="B6">
-        <f>IF(COUNT(Items!$N$5:$N$58)&lt;A6,"",INDEX(Items!$A$5:$A$58,MATCH(SMALL(Items!$N$5:$N$58,A6),Items!$N$5:$N$58,0)))</f>
+        <f>IF(COUNT(Items!$N$5:$N$40)&lt;A6,"",INDEX(Items!$A$5:$A$40,MATCH(SMALL(Items!$N$5:$N$40,A6),Items!$N$5:$N$40,0)))</f>
         <v/>
       </c>
       <c r="C6" s="6">
-        <f>IF(B6="","",INDEX(Items!$I$5:$I$58,MATCH(B6,Items!$A$5:$A$58,0)))</f>
+        <f>IF(B6="","",INDEX(Items!$I$5:$I$40,MATCH(B6,Items!$A$5:$A$40,0)))</f>
         <v/>
       </c>
       <c r="D6">
-        <f>IF(B6="","",INDEX(Items!$B$5:$B$58,MATCH(B6,Items!$A$5:$A$58,0)))</f>
+        <f>IF(B6="","",INDEX(Items!$B$5:$B$40,MATCH(B6,Items!$A$5:$A$40,0)))</f>
         <v/>
       </c>
       <c r="E6">
-        <f>IF(B6="","",INDEX(Items!$E$5:$E$58,MATCH(B6,Items!$A$5:$A$58,0)))</f>
+        <f>IF(B6="","",INDEX(Items!$E$5:$E$40,MATCH(B6,Items!$A$5:$A$40,0)))</f>
         <v/>
       </c>
       <c r="F6">
-        <f>IF(B6="","",INDEX(Items!$M$5:$M$58,MATCH(B6,Items!$A$5:$A$58,0)))</f>
+        <f>IF(B6="","",INDEX(Items!$M$5:$M$40,MATCH(B6,Items!$A$5:$A$40,0)))</f>
         <v/>
       </c>
     </row>
@@ -7195,23 +5251,23 @@
         <v>3</v>
       </c>
       <c r="B7">
-        <f>IF(COUNT(Items!$N$5:$N$58)&lt;A7,"",INDEX(Items!$A$5:$A$58,MATCH(SMALL(Items!$N$5:$N$58,A7),Items!$N$5:$N$58,0)))</f>
+        <f>IF(COUNT(Items!$N$5:$N$40)&lt;A7,"",INDEX(Items!$A$5:$A$40,MATCH(SMALL(Items!$N$5:$N$40,A7),Items!$N$5:$N$40,0)))</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>IF(B7="","",INDEX(Items!$I$5:$I$58,MATCH(B7,Items!$A$5:$A$58,0)))</f>
+        <f>IF(B7="","",INDEX(Items!$I$5:$I$40,MATCH(B7,Items!$A$5:$A$40,0)))</f>
         <v/>
       </c>
       <c r="D7">
-        <f>IF(B7="","",INDEX(Items!$B$5:$B$58,MATCH(B7,Items!$A$5:$A$58,0)))</f>
+        <f>IF(B7="","",INDEX(Items!$B$5:$B$40,MATCH(B7,Items!$A$5:$A$40,0)))</f>
         <v/>
       </c>
       <c r="E7">
-        <f>IF(B7="","",INDEX(Items!$E$5:$E$58,MATCH(B7,Items!$A$5:$A$58,0)))</f>
+        <f>IF(B7="","",INDEX(Items!$E$5:$E$40,MATCH(B7,Items!$A$5:$A$40,0)))</f>
         <v/>
       </c>
       <c r="F7">
-        <f>IF(B7="","",INDEX(Items!$M$5:$M$58,MATCH(B7,Items!$A$5:$A$58,0)))</f>
+        <f>IF(B7="","",INDEX(Items!$M$5:$M$40,MATCH(B7,Items!$A$5:$A$40,0)))</f>
         <v/>
       </c>
     </row>
@@ -7220,23 +5276,23 @@
         <v>4</v>
       </c>
       <c r="B8">
-        <f>IF(COUNT(Items!$N$5:$N$58)&lt;A8,"",INDEX(Items!$A$5:$A$58,MATCH(SMALL(Items!$N$5:$N$58,A8),Items!$N$5:$N$58,0)))</f>
+        <f>IF(COUNT(Items!$N$5:$N$40)&lt;A8,"",INDEX(Items!$A$5:$A$40,MATCH(SMALL(Items!$N$5:$N$40,A8),Items!$N$5:$N$40,0)))</f>
         <v/>
       </c>
       <c r="C8" s="6">
-        <f>IF(B8="","",INDEX(Items!$I$5:$I$58,MATCH(B8,Items!$A$5:$A$58,0)))</f>
+        <f>IF(B8="","",INDEX(Items!$I$5:$I$40,MATCH(B8,Items!$A$5:$A$40,0)))</f>
         <v/>
       </c>
       <c r="D8">
-        <f>IF(B8="","",INDEX(Items!$B$5:$B$58,MATCH(B8,Items!$A$5:$A$58,0)))</f>
+        <f>IF(B8="","",INDEX(Items!$B$5:$B$40,MATCH(B8,Items!$A$5:$A$40,0)))</f>
         <v/>
       </c>
       <c r="E8">
-        <f>IF(B8="","",INDEX(Items!$E$5:$E$58,MATCH(B8,Items!$A$5:$A$58,0)))</f>
+        <f>IF(B8="","",INDEX(Items!$E$5:$E$40,MATCH(B8,Items!$A$5:$A$40,0)))</f>
         <v/>
       </c>
       <c r="F8">
-        <f>IF(B8="","",INDEX(Items!$M$5:$M$58,MATCH(B8,Items!$A$5:$A$58,0)))</f>
+        <f>IF(B8="","",INDEX(Items!$M$5:$M$40,MATCH(B8,Items!$A$5:$A$40,0)))</f>
         <v/>
       </c>
     </row>
@@ -7245,23 +5301,23 @@
         <v>5</v>
       </c>
       <c r="B9">
-        <f>IF(COUNT(Items!$N$5:$N$58)&lt;A9,"",INDEX(Items!$A$5:$A$58,MATCH(SMALL(Items!$N$5:$N$58,A9),Items!$N$5:$N$58,0)))</f>
+        <f>IF(COUNT(Items!$N$5:$N$40)&lt;A9,"",INDEX(Items!$A$5:$A$40,MATCH(SMALL(Items!$N$5:$N$40,A9),Items!$N$5:$N$40,0)))</f>
         <v/>
       </c>
       <c r="C9" s="6">
-        <f>IF(B9="","",INDEX(Items!$I$5:$I$58,MATCH(B9,Items!$A$5:$A$58,0)))</f>
+        <f>IF(B9="","",INDEX(Items!$I$5:$I$40,MATCH(B9,Items!$A$5:$A$40,0)))</f>
         <v/>
       </c>
       <c r="D9">
-        <f>IF(B9="","",INDEX(Items!$B$5:$B$58,MATCH(B9,Items!$A$5:$A$58,0)))</f>
+        <f>IF(B9="","",INDEX(Items!$B$5:$B$40,MATCH(B9,Items!$A$5:$A$40,0)))</f>
         <v/>
       </c>
       <c r="E9">
-        <f>IF(B9="","",INDEX(Items!$E$5:$E$58,MATCH(B9,Items!$A$5:$A$58,0)))</f>
+        <f>IF(B9="","",INDEX(Items!$E$5:$E$40,MATCH(B9,Items!$A$5:$A$40,0)))</f>
         <v/>
       </c>
       <c r="F9">
-        <f>IF(B9="","",INDEX(Items!$M$5:$M$58,MATCH(B9,Items!$A$5:$A$58,0)))</f>
+        <f>IF(B9="","",INDEX(Items!$M$5:$M$40,MATCH(B9,Items!$A$5:$A$40,0)))</f>
         <v/>
       </c>
     </row>
@@ -7270,23 +5326,23 @@
         <v>6</v>
       </c>
       <c r="B10">
-        <f>IF(COUNT(Items!$N$5:$N$58)&lt;A10,"",INDEX(Items!$A$5:$A$58,MATCH(SMALL(Items!$N$5:$N$58,A10),Items!$N$5:$N$58,0)))</f>
+        <f>IF(COUNT(Items!$N$5:$N$40)&lt;A10,"",INDEX(Items!$A$5:$A$40,MATCH(SMALL(Items!$N$5:$N$40,A10),Items!$N$5:$N$40,0)))</f>
         <v/>
       </c>
       <c r="C10" s="6">
-        <f>IF(B10="","",INDEX(Items!$I$5:$I$58,MATCH(B10,Items!$A$5:$A$58,0)))</f>
+        <f>IF(B10="","",INDEX(Items!$I$5:$I$40,MATCH(B10,Items!$A$5:$A$40,0)))</f>
         <v/>
       </c>
       <c r="D10">
-        <f>IF(B10="","",INDEX(Items!$B$5:$B$58,MATCH(B10,Items!$A$5:$A$58,0)))</f>
+        <f>IF(B10="","",INDEX(Items!$B$5:$B$40,MATCH(B10,Items!$A$5:$A$40,0)))</f>
         <v/>
       </c>
       <c r="E10">
-        <f>IF(B10="","",INDEX(Items!$E$5:$E$58,MATCH(B10,Items!$A$5:$A$58,0)))</f>
+        <f>IF(B10="","",INDEX(Items!$E$5:$E$40,MATCH(B10,Items!$A$5:$A$40,0)))</f>
         <v/>
       </c>
       <c r="F10">
-        <f>IF(B10="","",INDEX(Items!$M$5:$M$58,MATCH(B10,Items!$A$5:$A$58,0)))</f>
+        <f>IF(B10="","",INDEX(Items!$M$5:$M$40,MATCH(B10,Items!$A$5:$A$40,0)))</f>
         <v/>
       </c>
     </row>
@@ -7295,23 +5351,23 @@
         <v>7</v>
       </c>
       <c r="B11">
-        <f>IF(COUNT(Items!$N$5:$N$58)&lt;A11,"",INDEX(Items!$A$5:$A$58,MATCH(SMALL(Items!$N$5:$N$58,A11),Items!$N$5:$N$58,0)))</f>
+        <f>IF(COUNT(Items!$N$5:$N$40)&lt;A11,"",INDEX(Items!$A$5:$A$40,MATCH(SMALL(Items!$N$5:$N$40,A11),Items!$N$5:$N$40,0)))</f>
         <v/>
       </c>
       <c r="C11" s="6">
-        <f>IF(B11="","",INDEX(Items!$I$5:$I$58,MATCH(B11,Items!$A$5:$A$58,0)))</f>
+        <f>IF(B11="","",INDEX(Items!$I$5:$I$40,MATCH(B11,Items!$A$5:$A$40,0)))</f>
         <v/>
       </c>
       <c r="D11">
-        <f>IF(B11="","",INDEX(Items!$B$5:$B$58,MATCH(B11,Items!$A$5:$A$58,0)))</f>
+        <f>IF(B11="","",INDEX(Items!$B$5:$B$40,MATCH(B11,Items!$A$5:$A$40,0)))</f>
         <v/>
       </c>
       <c r="E11">
-        <f>IF(B11="","",INDEX(Items!$E$5:$E$58,MATCH(B11,Items!$A$5:$A$58,0)))</f>
+        <f>IF(B11="","",INDEX(Items!$E$5:$E$40,MATCH(B11,Items!$A$5:$A$40,0)))</f>
         <v/>
       </c>
       <c r="F11">
-        <f>IF(B11="","",INDEX(Items!$M$5:$M$58,MATCH(B11,Items!$A$5:$A$58,0)))</f>
+        <f>IF(B11="","",INDEX(Items!$M$5:$M$40,MATCH(B11,Items!$A$5:$A$40,0)))</f>
         <v/>
       </c>
     </row>
@@ -7320,23 +5376,23 @@
         <v>8</v>
       </c>
       <c r="B12">
-        <f>IF(COUNT(Items!$N$5:$N$58)&lt;A12,"",INDEX(Items!$A$5:$A$58,MATCH(SMALL(Items!$N$5:$N$58,A12),Items!$N$5:$N$58,0)))</f>
+        <f>IF(COUNT(Items!$N$5:$N$40)&lt;A12,"",INDEX(Items!$A$5:$A$40,MATCH(SMALL(Items!$N$5:$N$40,A12),Items!$N$5:$N$40,0)))</f>
         <v/>
       </c>
       <c r="C12" s="6">
-        <f>IF(B12="","",INDEX(Items!$I$5:$I$58,MATCH(B12,Items!$A$5:$A$58,0)))</f>
+        <f>IF(B12="","",INDEX(Items!$I$5:$I$40,MATCH(B12,Items!$A$5:$A$40,0)))</f>
         <v/>
       </c>
       <c r="D12">
-        <f>IF(B12="","",INDEX(Items!$B$5:$B$58,MATCH(B12,Items!$A$5:$A$58,0)))</f>
+        <f>IF(B12="","",INDEX(Items!$B$5:$B$40,MATCH(B12,Items!$A$5:$A$40,0)))</f>
         <v/>
       </c>
       <c r="E12">
-        <f>IF(B12="","",INDEX(Items!$E$5:$E$58,MATCH(B12,Items!$A$5:$A$58,0)))</f>
+        <f>IF(B12="","",INDEX(Items!$E$5:$E$40,MATCH(B12,Items!$A$5:$A$40,0)))</f>
         <v/>
       </c>
       <c r="F12">
-        <f>IF(B12="","",INDEX(Items!$M$5:$M$58,MATCH(B12,Items!$A$5:$A$58,0)))</f>
+        <f>IF(B12="","",INDEX(Items!$M$5:$M$40,MATCH(B12,Items!$A$5:$A$40,0)))</f>
         <v/>
       </c>
     </row>
@@ -7345,23 +5401,23 @@
         <v>9</v>
       </c>
       <c r="B13">
-        <f>IF(COUNT(Items!$N$5:$N$58)&lt;A13,"",INDEX(Items!$A$5:$A$58,MATCH(SMALL(Items!$N$5:$N$58,A13),Items!$N$5:$N$58,0)))</f>
+        <f>IF(COUNT(Items!$N$5:$N$40)&lt;A13,"",INDEX(Items!$A$5:$A$40,MATCH(SMALL(Items!$N$5:$N$40,A13),Items!$N$5:$N$40,0)))</f>
         <v/>
       </c>
       <c r="C13" s="6">
-        <f>IF(B13="","",INDEX(Items!$I$5:$I$58,MATCH(B13,Items!$A$5:$A$58,0)))</f>
+        <f>IF(B13="","",INDEX(Items!$I$5:$I$40,MATCH(B13,Items!$A$5:$A$40,0)))</f>
         <v/>
       </c>
       <c r="D13">
-        <f>IF(B13="","",INDEX(Items!$B$5:$B$58,MATCH(B13,Items!$A$5:$A$58,0)))</f>
+        <f>IF(B13="","",INDEX(Items!$B$5:$B$40,MATCH(B13,Items!$A$5:$A$40,0)))</f>
         <v/>
       </c>
       <c r="E13">
-        <f>IF(B13="","",INDEX(Items!$E$5:$E$58,MATCH(B13,Items!$A$5:$A$58,0)))</f>
+        <f>IF(B13="","",INDEX(Items!$E$5:$E$40,MATCH(B13,Items!$A$5:$A$40,0)))</f>
         <v/>
       </c>
       <c r="F13">
-        <f>IF(B13="","",INDEX(Items!$M$5:$M$58,MATCH(B13,Items!$A$5:$A$58,0)))</f>
+        <f>IF(B13="","",INDEX(Items!$M$5:$M$40,MATCH(B13,Items!$A$5:$A$40,0)))</f>
         <v/>
       </c>
     </row>
@@ -7370,23 +5426,23 @@
         <v>10</v>
       </c>
       <c r="B14">
-        <f>IF(COUNT(Items!$N$5:$N$58)&lt;A14,"",INDEX(Items!$A$5:$A$58,MATCH(SMALL(Items!$N$5:$N$58,A14),Items!$N$5:$N$58,0)))</f>
+        <f>IF(COUNT(Items!$N$5:$N$40)&lt;A14,"",INDEX(Items!$A$5:$A$40,MATCH(SMALL(Items!$N$5:$N$40,A14),Items!$N$5:$N$40,0)))</f>
         <v/>
       </c>
       <c r="C14" s="6">
-        <f>IF(B14="","",INDEX(Items!$I$5:$I$58,MATCH(B14,Items!$A$5:$A$58,0)))</f>
+        <f>IF(B14="","",INDEX(Items!$I$5:$I$40,MATCH(B14,Items!$A$5:$A$40,0)))</f>
         <v/>
       </c>
       <c r="D14">
-        <f>IF(B14="","",INDEX(Items!$B$5:$B$58,MATCH(B14,Items!$A$5:$A$58,0)))</f>
+        <f>IF(B14="","",INDEX(Items!$B$5:$B$40,MATCH(B14,Items!$A$5:$A$40,0)))</f>
         <v/>
       </c>
       <c r="E14">
-        <f>IF(B14="","",INDEX(Items!$E$5:$E$58,MATCH(B14,Items!$A$5:$A$58,0)))</f>
+        <f>IF(B14="","",INDEX(Items!$E$5:$E$40,MATCH(B14,Items!$A$5:$A$40,0)))</f>
         <v/>
       </c>
       <c r="F14">
-        <f>IF(B14="","",INDEX(Items!$M$5:$M$58,MATCH(B14,Items!$A$5:$A$58,0)))</f>
+        <f>IF(B14="","",INDEX(Items!$M$5:$M$40,MATCH(B14,Items!$A$5:$A$40,0)))</f>
         <v/>
       </c>
     </row>
@@ -7395,23 +5451,23 @@
         <v>11</v>
       </c>
       <c r="B15">
-        <f>IF(COUNT(Items!$N$5:$N$58)&lt;A15,"",INDEX(Items!$A$5:$A$58,MATCH(SMALL(Items!$N$5:$N$58,A15),Items!$N$5:$N$58,0)))</f>
+        <f>IF(COUNT(Items!$N$5:$N$40)&lt;A15,"",INDEX(Items!$A$5:$A$40,MATCH(SMALL(Items!$N$5:$N$40,A15),Items!$N$5:$N$40,0)))</f>
         <v/>
       </c>
       <c r="C15" s="6">
-        <f>IF(B15="","",INDEX(Items!$I$5:$I$58,MATCH(B15,Items!$A$5:$A$58,0)))</f>
+        <f>IF(B15="","",INDEX(Items!$I$5:$I$40,MATCH(B15,Items!$A$5:$A$40,0)))</f>
         <v/>
       </c>
       <c r="D15">
-        <f>IF(B15="","",INDEX(Items!$B$5:$B$58,MATCH(B15,Items!$A$5:$A$58,0)))</f>
+        <f>IF(B15="","",INDEX(Items!$B$5:$B$40,MATCH(B15,Items!$A$5:$A$40,0)))</f>
         <v/>
       </c>
       <c r="E15">
-        <f>IF(B15="","",INDEX(Items!$E$5:$E$58,MATCH(B15,Items!$A$5:$A$58,0)))</f>
+        <f>IF(B15="","",INDEX(Items!$E$5:$E$40,MATCH(B15,Items!$A$5:$A$40,0)))</f>
         <v/>
       </c>
       <c r="F15">
-        <f>IF(B15="","",INDEX(Items!$M$5:$M$58,MATCH(B15,Items!$A$5:$A$58,0)))</f>
+        <f>IF(B15="","",INDEX(Items!$M$5:$M$40,MATCH(B15,Items!$A$5:$A$40,0)))</f>
         <v/>
       </c>
     </row>
@@ -7420,23 +5476,23 @@
         <v>12</v>
       </c>
       <c r="B16">
-        <f>IF(COUNT(Items!$N$5:$N$58)&lt;A16,"",INDEX(Items!$A$5:$A$58,MATCH(SMALL(Items!$N$5:$N$58,A16),Items!$N$5:$N$58,0)))</f>
+        <f>IF(COUNT(Items!$N$5:$N$40)&lt;A16,"",INDEX(Items!$A$5:$A$40,MATCH(SMALL(Items!$N$5:$N$40,A16),Items!$N$5:$N$40,0)))</f>
         <v/>
       </c>
       <c r="C16" s="6">
-        <f>IF(B16="","",INDEX(Items!$I$5:$I$58,MATCH(B16,Items!$A$5:$A$58,0)))</f>
+        <f>IF(B16="","",INDEX(Items!$I$5:$I$40,MATCH(B16,Items!$A$5:$A$40,0)))</f>
         <v/>
       </c>
       <c r="D16">
-        <f>IF(B16="","",INDEX(Items!$B$5:$B$58,MATCH(B16,Items!$A$5:$A$58,0)))</f>
+        <f>IF(B16="","",INDEX(Items!$B$5:$B$40,MATCH(B16,Items!$A$5:$A$40,0)))</f>
         <v/>
       </c>
       <c r="E16">
-        <f>IF(B16="","",INDEX(Items!$E$5:$E$58,MATCH(B16,Items!$A$5:$A$58,0)))</f>
+        <f>IF(B16="","",INDEX(Items!$E$5:$E$40,MATCH(B16,Items!$A$5:$A$40,0)))</f>
         <v/>
       </c>
       <c r="F16">
-        <f>IF(B16="","",INDEX(Items!$M$5:$M$58,MATCH(B16,Items!$A$5:$A$58,0)))</f>
+        <f>IF(B16="","",INDEX(Items!$M$5:$M$40,MATCH(B16,Items!$A$5:$A$40,0)))</f>
         <v/>
       </c>
     </row>
@@ -7445,23 +5501,23 @@
         <v>13</v>
       </c>
       <c r="B17">
-        <f>IF(COUNT(Items!$N$5:$N$58)&lt;A17,"",INDEX(Items!$A$5:$A$58,MATCH(SMALL(Items!$N$5:$N$58,A17),Items!$N$5:$N$58,0)))</f>
+        <f>IF(COUNT(Items!$N$5:$N$40)&lt;A17,"",INDEX(Items!$A$5:$A$40,MATCH(SMALL(Items!$N$5:$N$40,A17),Items!$N$5:$N$40,0)))</f>
         <v/>
       </c>
       <c r="C17" s="6">
-        <f>IF(B17="","",INDEX(Items!$I$5:$I$58,MATCH(B17,Items!$A$5:$A$58,0)))</f>
+        <f>IF(B17="","",INDEX(Items!$I$5:$I$40,MATCH(B17,Items!$A$5:$A$40,0)))</f>
         <v/>
       </c>
       <c r="D17">
-        <f>IF(B17="","",INDEX(Items!$B$5:$B$58,MATCH(B17,Items!$A$5:$A$58,0)))</f>
+        <f>IF(B17="","",INDEX(Items!$B$5:$B$40,MATCH(B17,Items!$A$5:$A$40,0)))</f>
         <v/>
       </c>
       <c r="E17">
-        <f>IF(B17="","",INDEX(Items!$E$5:$E$58,MATCH(B17,Items!$A$5:$A$58,0)))</f>
+        <f>IF(B17="","",INDEX(Items!$E$5:$E$40,MATCH(B17,Items!$A$5:$A$40,0)))</f>
         <v/>
       </c>
       <c r="F17">
-        <f>IF(B17="","",INDEX(Items!$M$5:$M$58,MATCH(B17,Items!$A$5:$A$58,0)))</f>
+        <f>IF(B17="","",INDEX(Items!$M$5:$M$40,MATCH(B17,Items!$A$5:$A$40,0)))</f>
         <v/>
       </c>
     </row>
@@ -7470,23 +5526,23 @@
         <v>14</v>
       </c>
       <c r="B18">
-        <f>IF(COUNT(Items!$N$5:$N$58)&lt;A18,"",INDEX(Items!$A$5:$A$58,MATCH(SMALL(Items!$N$5:$N$58,A18),Items!$N$5:$N$58,0)))</f>
+        <f>IF(COUNT(Items!$N$5:$N$40)&lt;A18,"",INDEX(Items!$A$5:$A$40,MATCH(SMALL(Items!$N$5:$N$40,A18),Items!$N$5:$N$40,0)))</f>
         <v/>
       </c>
       <c r="C18" s="6">
-        <f>IF(B18="","",INDEX(Items!$I$5:$I$58,MATCH(B18,Items!$A$5:$A$58,0)))</f>
+        <f>IF(B18="","",INDEX(Items!$I$5:$I$40,MATCH(B18,Items!$A$5:$A$40,0)))</f>
         <v/>
       </c>
       <c r="D18">
-        <f>IF(B18="","",INDEX(Items!$B$5:$B$58,MATCH(B18,Items!$A$5:$A$58,0)))</f>
+        <f>IF(B18="","",INDEX(Items!$B$5:$B$40,MATCH(B18,Items!$A$5:$A$40,0)))</f>
         <v/>
       </c>
       <c r="E18">
-        <f>IF(B18="","",INDEX(Items!$E$5:$E$58,MATCH(B18,Items!$A$5:$A$58,0)))</f>
+        <f>IF(B18="","",INDEX(Items!$E$5:$E$40,MATCH(B18,Items!$A$5:$A$40,0)))</f>
         <v/>
       </c>
       <c r="F18">
-        <f>IF(B18="","",INDEX(Items!$M$5:$M$58,MATCH(B18,Items!$A$5:$A$58,0)))</f>
+        <f>IF(B18="","",INDEX(Items!$M$5:$M$40,MATCH(B18,Items!$A$5:$A$40,0)))</f>
         <v/>
       </c>
     </row>
@@ -7495,23 +5551,23 @@
         <v>15</v>
       </c>
       <c r="B19">
-        <f>IF(COUNT(Items!$N$5:$N$58)&lt;A19,"",INDEX(Items!$A$5:$A$58,MATCH(SMALL(Items!$N$5:$N$58,A19),Items!$N$5:$N$58,0)))</f>
+        <f>IF(COUNT(Items!$N$5:$N$40)&lt;A19,"",INDEX(Items!$A$5:$A$40,MATCH(SMALL(Items!$N$5:$N$40,A19),Items!$N$5:$N$40,0)))</f>
         <v/>
       </c>
       <c r="C19" s="6">
-        <f>IF(B19="","",INDEX(Items!$I$5:$I$58,MATCH(B19,Items!$A$5:$A$58,0)))</f>
+        <f>IF(B19="","",INDEX(Items!$I$5:$I$40,MATCH(B19,Items!$A$5:$A$40,0)))</f>
         <v/>
       </c>
       <c r="D19">
-        <f>IF(B19="","",INDEX(Items!$B$5:$B$58,MATCH(B19,Items!$A$5:$A$58,0)))</f>
+        <f>IF(B19="","",INDEX(Items!$B$5:$B$40,MATCH(B19,Items!$A$5:$A$40,0)))</f>
         <v/>
       </c>
       <c r="E19">
-        <f>IF(B19="","",INDEX(Items!$E$5:$E$58,MATCH(B19,Items!$A$5:$A$58,0)))</f>
+        <f>IF(B19="","",INDEX(Items!$E$5:$E$40,MATCH(B19,Items!$A$5:$A$40,0)))</f>
         <v/>
       </c>
       <c r="F19">
-        <f>IF(B19="","",INDEX(Items!$M$5:$M$58,MATCH(B19,Items!$A$5:$A$58,0)))</f>
+        <f>IF(B19="","",INDEX(Items!$M$5:$M$40,MATCH(B19,Items!$A$5:$A$40,0)))</f>
         <v/>
       </c>
     </row>
@@ -7520,23 +5576,23 @@
         <v>16</v>
       </c>
       <c r="B20">
-        <f>IF(COUNT(Items!$N$5:$N$58)&lt;A20,"",INDEX(Items!$A$5:$A$58,MATCH(SMALL(Items!$N$5:$N$58,A20),Items!$N$5:$N$58,0)))</f>
+        <f>IF(COUNT(Items!$N$5:$N$40)&lt;A20,"",INDEX(Items!$A$5:$A$40,MATCH(SMALL(Items!$N$5:$N$40,A20),Items!$N$5:$N$40,0)))</f>
         <v/>
       </c>
       <c r="C20" s="6">
-        <f>IF(B20="","",INDEX(Items!$I$5:$I$58,MATCH(B20,Items!$A$5:$A$58,0)))</f>
+        <f>IF(B20="","",INDEX(Items!$I$5:$I$40,MATCH(B20,Items!$A$5:$A$40,0)))</f>
         <v/>
       </c>
       <c r="D20">
-        <f>IF(B20="","",INDEX(Items!$B$5:$B$58,MATCH(B20,Items!$A$5:$A$58,0)))</f>
+        <f>IF(B20="","",INDEX(Items!$B$5:$B$40,MATCH(B20,Items!$A$5:$A$40,0)))</f>
         <v/>
       </c>
       <c r="E20">
-        <f>IF(B20="","",INDEX(Items!$E$5:$E$58,MATCH(B20,Items!$A$5:$A$58,0)))</f>
+        <f>IF(B20="","",INDEX(Items!$E$5:$E$40,MATCH(B20,Items!$A$5:$A$40,0)))</f>
         <v/>
       </c>
       <c r="F20">
-        <f>IF(B20="","",INDEX(Items!$M$5:$M$58,MATCH(B20,Items!$A$5:$A$58,0)))</f>
+        <f>IF(B20="","",INDEX(Items!$M$5:$M$40,MATCH(B20,Items!$A$5:$A$40,0)))</f>
         <v/>
       </c>
     </row>
@@ -7545,23 +5601,23 @@
         <v>17</v>
       </c>
       <c r="B21">
-        <f>IF(COUNT(Items!$N$5:$N$58)&lt;A21,"",INDEX(Items!$A$5:$A$58,MATCH(SMALL(Items!$N$5:$N$58,A21),Items!$N$5:$N$58,0)))</f>
+        <f>IF(COUNT(Items!$N$5:$N$40)&lt;A21,"",INDEX(Items!$A$5:$A$40,MATCH(SMALL(Items!$N$5:$N$40,A21),Items!$N$5:$N$40,0)))</f>
         <v/>
       </c>
       <c r="C21" s="6">
-        <f>IF(B21="","",INDEX(Items!$I$5:$I$58,MATCH(B21,Items!$A$5:$A$58,0)))</f>
+        <f>IF(B21="","",INDEX(Items!$I$5:$I$40,MATCH(B21,Items!$A$5:$A$40,0)))</f>
         <v/>
       </c>
       <c r="D21">
-        <f>IF(B21="","",INDEX(Items!$B$5:$B$58,MATCH(B21,Items!$A$5:$A$58,0)))</f>
+        <f>IF(B21="","",INDEX(Items!$B$5:$B$40,MATCH(B21,Items!$A$5:$A$40,0)))</f>
         <v/>
       </c>
       <c r="E21">
-        <f>IF(B21="","",INDEX(Items!$E$5:$E$58,MATCH(B21,Items!$A$5:$A$58,0)))</f>
+        <f>IF(B21="","",INDEX(Items!$E$5:$E$40,MATCH(B21,Items!$A$5:$A$40,0)))</f>
         <v/>
       </c>
       <c r="F21">
-        <f>IF(B21="","",INDEX(Items!$M$5:$M$58,MATCH(B21,Items!$A$5:$A$58,0)))</f>
+        <f>IF(B21="","",INDEX(Items!$M$5:$M$40,MATCH(B21,Items!$A$5:$A$40,0)))</f>
         <v/>
       </c>
     </row>
@@ -7570,23 +5626,23 @@
         <v>18</v>
       </c>
       <c r="B22">
-        <f>IF(COUNT(Items!$N$5:$N$58)&lt;A22,"",INDEX(Items!$A$5:$A$58,MATCH(SMALL(Items!$N$5:$N$58,A22),Items!$N$5:$N$58,0)))</f>
+        <f>IF(COUNT(Items!$N$5:$N$40)&lt;A22,"",INDEX(Items!$A$5:$A$40,MATCH(SMALL(Items!$N$5:$N$40,A22),Items!$N$5:$N$40,0)))</f>
         <v/>
       </c>
       <c r="C22" s="6">
-        <f>IF(B22="","",INDEX(Items!$I$5:$I$58,MATCH(B22,Items!$A$5:$A$58,0)))</f>
+        <f>IF(B22="","",INDEX(Items!$I$5:$I$40,MATCH(B22,Items!$A$5:$A$40,0)))</f>
         <v/>
       </c>
       <c r="D22">
-        <f>IF(B22="","",INDEX(Items!$B$5:$B$58,MATCH(B22,Items!$A$5:$A$58,0)))</f>
+        <f>IF(B22="","",INDEX(Items!$B$5:$B$40,MATCH(B22,Items!$A$5:$A$40,0)))</f>
         <v/>
       </c>
       <c r="E22">
-        <f>IF(B22="","",INDEX(Items!$E$5:$E$58,MATCH(B22,Items!$A$5:$A$58,0)))</f>
+        <f>IF(B22="","",INDEX(Items!$E$5:$E$40,MATCH(B22,Items!$A$5:$A$40,0)))</f>
         <v/>
       </c>
       <c r="F22">
-        <f>IF(B22="","",INDEX(Items!$M$5:$M$58,MATCH(B22,Items!$A$5:$A$58,0)))</f>
+        <f>IF(B22="","",INDEX(Items!$M$5:$M$40,MATCH(B22,Items!$A$5:$A$40,0)))</f>
         <v/>
       </c>
     </row>
@@ -7595,23 +5651,23 @@
         <v>19</v>
       </c>
       <c r="B23">
-        <f>IF(COUNT(Items!$N$5:$N$58)&lt;A23,"",INDEX(Items!$A$5:$A$58,MATCH(SMALL(Items!$N$5:$N$58,A23),Items!$N$5:$N$58,0)))</f>
+        <f>IF(COUNT(Items!$N$5:$N$40)&lt;A23,"",INDEX(Items!$A$5:$A$40,MATCH(SMALL(Items!$N$5:$N$40,A23),Items!$N$5:$N$40,0)))</f>
         <v/>
       </c>
       <c r="C23" s="6">
-        <f>IF(B23="","",INDEX(Items!$I$5:$I$58,MATCH(B23,Items!$A$5:$A$58,0)))</f>
+        <f>IF(B23="","",INDEX(Items!$I$5:$I$40,MATCH(B23,Items!$A$5:$A$40,0)))</f>
         <v/>
       </c>
       <c r="D23">
-        <f>IF(B23="","",INDEX(Items!$B$5:$B$58,MATCH(B23,Items!$A$5:$A$58,0)))</f>
+        <f>IF(B23="","",INDEX(Items!$B$5:$B$40,MATCH(B23,Items!$A$5:$A$40,0)))</f>
         <v/>
       </c>
       <c r="E23">
-        <f>IF(B23="","",INDEX(Items!$E$5:$E$58,MATCH(B23,Items!$A$5:$A$58,0)))</f>
+        <f>IF(B23="","",INDEX(Items!$E$5:$E$40,MATCH(B23,Items!$A$5:$A$40,0)))</f>
         <v/>
       </c>
       <c r="F23">
-        <f>IF(B23="","",INDEX(Items!$M$5:$M$58,MATCH(B23,Items!$A$5:$A$58,0)))</f>
+        <f>IF(B23="","",INDEX(Items!$M$5:$M$40,MATCH(B23,Items!$A$5:$A$40,0)))</f>
         <v/>
       </c>
     </row>
@@ -7620,23 +5676,23 @@
         <v>20</v>
       </c>
       <c r="B24">
-        <f>IF(COUNT(Items!$N$5:$N$58)&lt;A24,"",INDEX(Items!$A$5:$A$58,MATCH(SMALL(Items!$N$5:$N$58,A24),Items!$N$5:$N$58,0)))</f>
+        <f>IF(COUNT(Items!$N$5:$N$40)&lt;A24,"",INDEX(Items!$A$5:$A$40,MATCH(SMALL(Items!$N$5:$N$40,A24),Items!$N$5:$N$40,0)))</f>
         <v/>
       </c>
       <c r="C24" s="6">
-        <f>IF(B24="","",INDEX(Items!$I$5:$I$58,MATCH(B24,Items!$A$5:$A$58,0)))</f>
+        <f>IF(B24="","",INDEX(Items!$I$5:$I$40,MATCH(B24,Items!$A$5:$A$40,0)))</f>
         <v/>
       </c>
       <c r="D24">
-        <f>IF(B24="","",INDEX(Items!$B$5:$B$58,MATCH(B24,Items!$A$5:$A$58,0)))</f>
+        <f>IF(B24="","",INDEX(Items!$B$5:$B$40,MATCH(B24,Items!$A$5:$A$40,0)))</f>
         <v/>
       </c>
       <c r="E24">
-        <f>IF(B24="","",INDEX(Items!$E$5:$E$58,MATCH(B24,Items!$A$5:$A$58,0)))</f>
+        <f>IF(B24="","",INDEX(Items!$E$5:$E$40,MATCH(B24,Items!$A$5:$A$40,0)))</f>
         <v/>
       </c>
       <c r="F24">
-        <f>IF(B24="","",INDEX(Items!$M$5:$M$58,MATCH(B24,Items!$A$5:$A$58,0)))</f>
+        <f>IF(B24="","",INDEX(Items!$M$5:$M$40,MATCH(B24,Items!$A$5:$A$40,0)))</f>
         <v/>
       </c>
     </row>
@@ -7645,23 +5701,23 @@
         <v>21</v>
       </c>
       <c r="B25">
-        <f>IF(COUNT(Items!$N$5:$N$58)&lt;A25,"",INDEX(Items!$A$5:$A$58,MATCH(SMALL(Items!$N$5:$N$58,A25),Items!$N$5:$N$58,0)))</f>
+        <f>IF(COUNT(Items!$N$5:$N$40)&lt;A25,"",INDEX(Items!$A$5:$A$40,MATCH(SMALL(Items!$N$5:$N$40,A25),Items!$N$5:$N$40,0)))</f>
         <v/>
       </c>
       <c r="C25" s="6">
-        <f>IF(B25="","",INDEX(Items!$I$5:$I$58,MATCH(B25,Items!$A$5:$A$58,0)))</f>
+        <f>IF(B25="","",INDEX(Items!$I$5:$I$40,MATCH(B25,Items!$A$5:$A$40,0)))</f>
         <v/>
       </c>
       <c r="D25">
-        <f>IF(B25="","",INDEX(Items!$B$5:$B$58,MATCH(B25,Items!$A$5:$A$58,0)))</f>
+        <f>IF(B25="","",INDEX(Items!$B$5:$B$40,MATCH(B25,Items!$A$5:$A$40,0)))</f>
         <v/>
       </c>
       <c r="E25">
-        <f>IF(B25="","",INDEX(Items!$E$5:$E$58,MATCH(B25,Items!$A$5:$A$58,0)))</f>
+        <f>IF(B25="","",INDEX(Items!$E$5:$E$40,MATCH(B25,Items!$A$5:$A$40,0)))</f>
         <v/>
       </c>
       <c r="F25">
-        <f>IF(B25="","",INDEX(Items!$M$5:$M$58,MATCH(B25,Items!$A$5:$A$58,0)))</f>
+        <f>IF(B25="","",INDEX(Items!$M$5:$M$40,MATCH(B25,Items!$A$5:$A$40,0)))</f>
         <v/>
       </c>
     </row>
@@ -7670,23 +5726,23 @@
         <v>22</v>
       </c>
       <c r="B26">
-        <f>IF(COUNT(Items!$N$5:$N$58)&lt;A26,"",INDEX(Items!$A$5:$A$58,MATCH(SMALL(Items!$N$5:$N$58,A26),Items!$N$5:$N$58,0)))</f>
+        <f>IF(COUNT(Items!$N$5:$N$40)&lt;A26,"",INDEX(Items!$A$5:$A$40,MATCH(SMALL(Items!$N$5:$N$40,A26),Items!$N$5:$N$40,0)))</f>
         <v/>
       </c>
       <c r="C26" s="6">
-        <f>IF(B26="","",INDEX(Items!$I$5:$I$58,MATCH(B26,Items!$A$5:$A$58,0)))</f>
+        <f>IF(B26="","",INDEX(Items!$I$5:$I$40,MATCH(B26,Items!$A$5:$A$40,0)))</f>
         <v/>
       </c>
       <c r="D26">
-        <f>IF(B26="","",INDEX(Items!$B$5:$B$58,MATCH(B26,Items!$A$5:$A$58,0)))</f>
+        <f>IF(B26="","",INDEX(Items!$B$5:$B$40,MATCH(B26,Items!$A$5:$A$40,0)))</f>
         <v/>
       </c>
       <c r="E26">
-        <f>IF(B26="","",INDEX(Items!$E$5:$E$58,MATCH(B26,Items!$A$5:$A$58,0)))</f>
+        <f>IF(B26="","",INDEX(Items!$E$5:$E$40,MATCH(B26,Items!$A$5:$A$40,0)))</f>
         <v/>
       </c>
       <c r="F26">
-        <f>IF(B26="","",INDEX(Items!$M$5:$M$58,MATCH(B26,Items!$A$5:$A$58,0)))</f>
+        <f>IF(B26="","",INDEX(Items!$M$5:$M$40,MATCH(B26,Items!$A$5:$A$40,0)))</f>
         <v/>
       </c>
     </row>
@@ -7695,23 +5751,23 @@
         <v>23</v>
       </c>
       <c r="B27">
-        <f>IF(COUNT(Items!$N$5:$N$58)&lt;A27,"",INDEX(Items!$A$5:$A$58,MATCH(SMALL(Items!$N$5:$N$58,A27),Items!$N$5:$N$58,0)))</f>
+        <f>IF(COUNT(Items!$N$5:$N$40)&lt;A27,"",INDEX(Items!$A$5:$A$40,MATCH(SMALL(Items!$N$5:$N$40,A27),Items!$N$5:$N$40,0)))</f>
         <v/>
       </c>
       <c r="C27" s="6">
-        <f>IF(B27="","",INDEX(Items!$I$5:$I$58,MATCH(B27,Items!$A$5:$A$58,0)))</f>
+        <f>IF(B27="","",INDEX(Items!$I$5:$I$40,MATCH(B27,Items!$A$5:$A$40,0)))</f>
         <v/>
       </c>
       <c r="D27">
-        <f>IF(B27="","",INDEX(Items!$B$5:$B$58,MATCH(B27,Items!$A$5:$A$58,0)))</f>
+        <f>IF(B27="","",INDEX(Items!$B$5:$B$40,MATCH(B27,Items!$A$5:$A$40,0)))</f>
         <v/>
       </c>
       <c r="E27">
-        <f>IF(B27="","",INDEX(Items!$E$5:$E$58,MATCH(B27,Items!$A$5:$A$58,0)))</f>
+        <f>IF(B27="","",INDEX(Items!$E$5:$E$40,MATCH(B27,Items!$A$5:$A$40,0)))</f>
         <v/>
       </c>
       <c r="F27">
-        <f>IF(B27="","",INDEX(Items!$M$5:$M$58,MATCH(B27,Items!$A$5:$A$58,0)))</f>
+        <f>IF(B27="","",INDEX(Items!$M$5:$M$40,MATCH(B27,Items!$A$5:$A$40,0)))</f>
         <v/>
       </c>
     </row>
@@ -7720,23 +5776,23 @@
         <v>24</v>
       </c>
       <c r="B28">
-        <f>IF(COUNT(Items!$N$5:$N$58)&lt;A28,"",INDEX(Items!$A$5:$A$58,MATCH(SMALL(Items!$N$5:$N$58,A28),Items!$N$5:$N$58,0)))</f>
+        <f>IF(COUNT(Items!$N$5:$N$40)&lt;A28,"",INDEX(Items!$A$5:$A$40,MATCH(SMALL(Items!$N$5:$N$40,A28),Items!$N$5:$N$40,0)))</f>
         <v/>
       </c>
       <c r="C28" s="6">
-        <f>IF(B28="","",INDEX(Items!$I$5:$I$58,MATCH(B28,Items!$A$5:$A$58,0)))</f>
+        <f>IF(B28="","",INDEX(Items!$I$5:$I$40,MATCH(B28,Items!$A$5:$A$40,0)))</f>
         <v/>
       </c>
       <c r="D28">
-        <f>IF(B28="","",INDEX(Items!$B$5:$B$58,MATCH(B28,Items!$A$5:$A$58,0)))</f>
+        <f>IF(B28="","",INDEX(Items!$B$5:$B$40,MATCH(B28,Items!$A$5:$A$40,0)))</f>
         <v/>
       </c>
       <c r="E28">
-        <f>IF(B28="","",INDEX(Items!$E$5:$E$58,MATCH(B28,Items!$A$5:$A$58,0)))</f>
+        <f>IF(B28="","",INDEX(Items!$E$5:$E$40,MATCH(B28,Items!$A$5:$A$40,0)))</f>
         <v/>
       </c>
       <c r="F28">
-        <f>IF(B28="","",INDEX(Items!$M$5:$M$58,MATCH(B28,Items!$A$5:$A$58,0)))</f>
+        <f>IF(B28="","",INDEX(Items!$M$5:$M$40,MATCH(B28,Items!$A$5:$A$40,0)))</f>
         <v/>
       </c>
     </row>
@@ -7745,23 +5801,23 @@
         <v>25</v>
       </c>
       <c r="B29">
-        <f>IF(COUNT(Items!$N$5:$N$58)&lt;A29,"",INDEX(Items!$A$5:$A$58,MATCH(SMALL(Items!$N$5:$N$58,A29),Items!$N$5:$N$58,0)))</f>
+        <f>IF(COUNT(Items!$N$5:$N$40)&lt;A29,"",INDEX(Items!$A$5:$A$40,MATCH(SMALL(Items!$N$5:$N$40,A29),Items!$N$5:$N$40,0)))</f>
         <v/>
       </c>
       <c r="C29" s="6">
-        <f>IF(B29="","",INDEX(Items!$I$5:$I$58,MATCH(B29,Items!$A$5:$A$58,0)))</f>
+        <f>IF(B29="","",INDEX(Items!$I$5:$I$40,MATCH(B29,Items!$A$5:$A$40,0)))</f>
         <v/>
       </c>
       <c r="D29">
-        <f>IF(B29="","",INDEX(Items!$B$5:$B$58,MATCH(B29,Items!$A$5:$A$58,0)))</f>
+        <f>IF(B29="","",INDEX(Items!$B$5:$B$40,MATCH(B29,Items!$A$5:$A$40,0)))</f>
         <v/>
       </c>
       <c r="E29">
-        <f>IF(B29="","",INDEX(Items!$E$5:$E$58,MATCH(B29,Items!$A$5:$A$58,0)))</f>
+        <f>IF(B29="","",INDEX(Items!$E$5:$E$40,MATCH(B29,Items!$A$5:$A$40,0)))</f>
         <v/>
       </c>
       <c r="F29">
-        <f>IF(B29="","",INDEX(Items!$M$5:$M$58,MATCH(B29,Items!$A$5:$A$58,0)))</f>
+        <f>IF(B29="","",INDEX(Items!$M$5:$M$40,MATCH(B29,Items!$A$5:$A$40,0)))</f>
         <v/>
       </c>
     </row>
@@ -7770,23 +5826,23 @@
         <v>26</v>
       </c>
       <c r="B30">
-        <f>IF(COUNT(Items!$N$5:$N$58)&lt;A30,"",INDEX(Items!$A$5:$A$58,MATCH(SMALL(Items!$N$5:$N$58,A30),Items!$N$5:$N$58,0)))</f>
+        <f>IF(COUNT(Items!$N$5:$N$40)&lt;A30,"",INDEX(Items!$A$5:$A$40,MATCH(SMALL(Items!$N$5:$N$40,A30),Items!$N$5:$N$40,0)))</f>
         <v/>
       </c>
       <c r="C30" s="6">
-        <f>IF(B30="","",INDEX(Items!$I$5:$I$58,MATCH(B30,Items!$A$5:$A$58,0)))</f>
+        <f>IF(B30="","",INDEX(Items!$I$5:$I$40,MATCH(B30,Items!$A$5:$A$40,0)))</f>
         <v/>
       </c>
       <c r="D30">
-        <f>IF(B30="","",INDEX(Items!$B$5:$B$58,MATCH(B30,Items!$A$5:$A$58,0)))</f>
+        <f>IF(B30="","",INDEX(Items!$B$5:$B$40,MATCH(B30,Items!$A$5:$A$40,0)))</f>
         <v/>
       </c>
       <c r="E30">
-        <f>IF(B30="","",INDEX(Items!$E$5:$E$58,MATCH(B30,Items!$A$5:$A$58,0)))</f>
+        <f>IF(B30="","",INDEX(Items!$E$5:$E$40,MATCH(B30,Items!$A$5:$A$40,0)))</f>
         <v/>
       </c>
       <c r="F30">
-        <f>IF(B30="","",INDEX(Items!$M$5:$M$58,MATCH(B30,Items!$A$5:$A$58,0)))</f>
+        <f>IF(B30="","",INDEX(Items!$M$5:$M$40,MATCH(B30,Items!$A$5:$A$40,0)))</f>
         <v/>
       </c>
     </row>
@@ -7795,23 +5851,23 @@
         <v>27</v>
       </c>
       <c r="B31">
-        <f>IF(COUNT(Items!$N$5:$N$58)&lt;A31,"",INDEX(Items!$A$5:$A$58,MATCH(SMALL(Items!$N$5:$N$58,A31),Items!$N$5:$N$58,0)))</f>
+        <f>IF(COUNT(Items!$N$5:$N$40)&lt;A31,"",INDEX(Items!$A$5:$A$40,MATCH(SMALL(Items!$N$5:$N$40,A31),Items!$N$5:$N$40,0)))</f>
         <v/>
       </c>
       <c r="C31" s="6">
-        <f>IF(B31="","",INDEX(Items!$I$5:$I$58,MATCH(B31,Items!$A$5:$A$58,0)))</f>
+        <f>IF(B31="","",INDEX(Items!$I$5:$I$40,MATCH(B31,Items!$A$5:$A$40,0)))</f>
         <v/>
       </c>
       <c r="D31">
-        <f>IF(B31="","",INDEX(Items!$B$5:$B$58,MATCH(B31,Items!$A$5:$A$58,0)))</f>
+        <f>IF(B31="","",INDEX(Items!$B$5:$B$40,MATCH(B31,Items!$A$5:$A$40,0)))</f>
         <v/>
       </c>
       <c r="E31">
-        <f>IF(B31="","",INDEX(Items!$E$5:$E$58,MATCH(B31,Items!$A$5:$A$58,0)))</f>
+        <f>IF(B31="","",INDEX(Items!$E$5:$E$40,MATCH(B31,Items!$A$5:$A$40,0)))</f>
         <v/>
       </c>
       <c r="F31">
-        <f>IF(B31="","",INDEX(Items!$M$5:$M$58,MATCH(B31,Items!$A$5:$A$58,0)))</f>
+        <f>IF(B31="","",INDEX(Items!$M$5:$M$40,MATCH(B31,Items!$A$5:$A$40,0)))</f>
         <v/>
       </c>
     </row>
@@ -7820,23 +5876,23 @@
         <v>28</v>
       </c>
       <c r="B32">
-        <f>IF(COUNT(Items!$N$5:$N$58)&lt;A32,"",INDEX(Items!$A$5:$A$58,MATCH(SMALL(Items!$N$5:$N$58,A32),Items!$N$5:$N$58,0)))</f>
+        <f>IF(COUNT(Items!$N$5:$N$40)&lt;A32,"",INDEX(Items!$A$5:$A$40,MATCH(SMALL(Items!$N$5:$N$40,A32),Items!$N$5:$N$40,0)))</f>
         <v/>
       </c>
       <c r="C32" s="6">
-        <f>IF(B32="","",INDEX(Items!$I$5:$I$58,MATCH(B32,Items!$A$5:$A$58,0)))</f>
+        <f>IF(B32="","",INDEX(Items!$I$5:$I$40,MATCH(B32,Items!$A$5:$A$40,0)))</f>
         <v/>
       </c>
       <c r="D32">
-        <f>IF(B32="","",INDEX(Items!$B$5:$B$58,MATCH(B32,Items!$A$5:$A$58,0)))</f>
+        <f>IF(B32="","",INDEX(Items!$B$5:$B$40,MATCH(B32,Items!$A$5:$A$40,0)))</f>
         <v/>
       </c>
       <c r="E32">
-        <f>IF(B32="","",INDEX(Items!$E$5:$E$58,MATCH(B32,Items!$A$5:$A$58,0)))</f>
+        <f>IF(B32="","",INDEX(Items!$E$5:$E$40,MATCH(B32,Items!$A$5:$A$40,0)))</f>
         <v/>
       </c>
       <c r="F32">
-        <f>IF(B32="","",INDEX(Items!$M$5:$M$58,MATCH(B32,Items!$A$5:$A$58,0)))</f>
+        <f>IF(B32="","",INDEX(Items!$M$5:$M$40,MATCH(B32,Items!$A$5:$A$40,0)))</f>
         <v/>
       </c>
     </row>
@@ -7845,23 +5901,23 @@
         <v>29</v>
       </c>
       <c r="B33">
-        <f>IF(COUNT(Items!$N$5:$N$58)&lt;A33,"",INDEX(Items!$A$5:$A$58,MATCH(SMALL(Items!$N$5:$N$58,A33),Items!$N$5:$N$58,0)))</f>
+        <f>IF(COUNT(Items!$N$5:$N$40)&lt;A33,"",INDEX(Items!$A$5:$A$40,MATCH(SMALL(Items!$N$5:$N$40,A33),Items!$N$5:$N$40,0)))</f>
         <v/>
       </c>
       <c r="C33" s="6">
-        <f>IF(B33="","",INDEX(Items!$I$5:$I$58,MATCH(B33,Items!$A$5:$A$58,0)))</f>
+        <f>IF(B33="","",INDEX(Items!$I$5:$I$40,MATCH(B33,Items!$A$5:$A$40,0)))</f>
         <v/>
       </c>
       <c r="D33">
-        <f>IF(B33="","",INDEX(Items!$B$5:$B$58,MATCH(B33,Items!$A$5:$A$58,0)))</f>
+        <f>IF(B33="","",INDEX(Items!$B$5:$B$40,MATCH(B33,Items!$A$5:$A$40,0)))</f>
         <v/>
       </c>
       <c r="E33">
-        <f>IF(B33="","",INDEX(Items!$E$5:$E$58,MATCH(B33,Items!$A$5:$A$58,0)))</f>
+        <f>IF(B33="","",INDEX(Items!$E$5:$E$40,MATCH(B33,Items!$A$5:$A$40,0)))</f>
         <v/>
       </c>
       <c r="F33">
-        <f>IF(B33="","",INDEX(Items!$M$5:$M$58,MATCH(B33,Items!$A$5:$A$58,0)))</f>
+        <f>IF(B33="","",INDEX(Items!$M$5:$M$40,MATCH(B33,Items!$A$5:$A$40,0)))</f>
         <v/>
       </c>
     </row>
@@ -7870,23 +5926,23 @@
         <v>30</v>
       </c>
       <c r="B34">
-        <f>IF(COUNT(Items!$N$5:$N$58)&lt;A34,"",INDEX(Items!$A$5:$A$58,MATCH(SMALL(Items!$N$5:$N$58,A34),Items!$N$5:$N$58,0)))</f>
+        <f>IF(COUNT(Items!$N$5:$N$40)&lt;A34,"",INDEX(Items!$A$5:$A$40,MATCH(SMALL(Items!$N$5:$N$40,A34),Items!$N$5:$N$40,0)))</f>
         <v/>
       </c>
       <c r="C34" s="6">
-        <f>IF(B34="","",INDEX(Items!$I$5:$I$58,MATCH(B34,Items!$A$5:$A$58,0)))</f>
+        <f>IF(B34="","",INDEX(Items!$I$5:$I$40,MATCH(B34,Items!$A$5:$A$40,0)))</f>
         <v/>
       </c>
       <c r="D34">
-        <f>IF(B34="","",INDEX(Items!$B$5:$B$58,MATCH(B34,Items!$A$5:$A$58,0)))</f>
+        <f>IF(B34="","",INDEX(Items!$B$5:$B$40,MATCH(B34,Items!$A$5:$A$40,0)))</f>
         <v/>
       </c>
       <c r="E34">
-        <f>IF(B34="","",INDEX(Items!$E$5:$E$58,MATCH(B34,Items!$A$5:$A$58,0)))</f>
+        <f>IF(B34="","",INDEX(Items!$E$5:$E$40,MATCH(B34,Items!$A$5:$A$40,0)))</f>
         <v/>
       </c>
       <c r="F34">
-        <f>IF(B34="","",INDEX(Items!$M$5:$M$58,MATCH(B34,Items!$A$5:$A$58,0)))</f>
+        <f>IF(B34="","",INDEX(Items!$M$5:$M$40,MATCH(B34,Items!$A$5:$A$40,0)))</f>
         <v/>
       </c>
     </row>
@@ -7895,23 +5951,23 @@
         <v>31</v>
       </c>
       <c r="B35">
-        <f>IF(COUNT(Items!$N$5:$N$58)&lt;A35,"",INDEX(Items!$A$5:$A$58,MATCH(SMALL(Items!$N$5:$N$58,A35),Items!$N$5:$N$58,0)))</f>
+        <f>IF(COUNT(Items!$N$5:$N$40)&lt;A35,"",INDEX(Items!$A$5:$A$40,MATCH(SMALL(Items!$N$5:$N$40,A35),Items!$N$5:$N$40,0)))</f>
         <v/>
       </c>
       <c r="C35" s="6">
-        <f>IF(B35="","",INDEX(Items!$I$5:$I$58,MATCH(B35,Items!$A$5:$A$58,0)))</f>
+        <f>IF(B35="","",INDEX(Items!$I$5:$I$40,MATCH(B35,Items!$A$5:$A$40,0)))</f>
         <v/>
       </c>
       <c r="D35">
-        <f>IF(B35="","",INDEX(Items!$B$5:$B$58,MATCH(B35,Items!$A$5:$A$58,0)))</f>
+        <f>IF(B35="","",INDEX(Items!$B$5:$B$40,MATCH(B35,Items!$A$5:$A$40,0)))</f>
         <v/>
       </c>
       <c r="E35">
-        <f>IF(B35="","",INDEX(Items!$E$5:$E$58,MATCH(B35,Items!$A$5:$A$58,0)))</f>
+        <f>IF(B35="","",INDEX(Items!$E$5:$E$40,MATCH(B35,Items!$A$5:$A$40,0)))</f>
         <v/>
       </c>
       <c r="F35">
-        <f>IF(B35="","",INDEX(Items!$M$5:$M$58,MATCH(B35,Items!$A$5:$A$58,0)))</f>
+        <f>IF(B35="","",INDEX(Items!$M$5:$M$40,MATCH(B35,Items!$A$5:$A$40,0)))</f>
         <v/>
       </c>
     </row>
@@ -7920,23 +5976,23 @@
         <v>32</v>
       </c>
       <c r="B36">
-        <f>IF(COUNT(Items!$N$5:$N$58)&lt;A36,"",INDEX(Items!$A$5:$A$58,MATCH(SMALL(Items!$N$5:$N$58,A36),Items!$N$5:$N$58,0)))</f>
+        <f>IF(COUNT(Items!$N$5:$N$40)&lt;A36,"",INDEX(Items!$A$5:$A$40,MATCH(SMALL(Items!$N$5:$N$40,A36),Items!$N$5:$N$40,0)))</f>
         <v/>
       </c>
       <c r="C36" s="6">
-        <f>IF(B36="","",INDEX(Items!$I$5:$I$58,MATCH(B36,Items!$A$5:$A$58,0)))</f>
+        <f>IF(B36="","",INDEX(Items!$I$5:$I$40,MATCH(B36,Items!$A$5:$A$40,0)))</f>
         <v/>
       </c>
       <c r="D36">
-        <f>IF(B36="","",INDEX(Items!$B$5:$B$58,MATCH(B36,Items!$A$5:$A$58,0)))</f>
+        <f>IF(B36="","",INDEX(Items!$B$5:$B$40,MATCH(B36,Items!$A$5:$A$40,0)))</f>
         <v/>
       </c>
       <c r="E36">
-        <f>IF(B36="","",INDEX(Items!$E$5:$E$58,MATCH(B36,Items!$A$5:$A$58,0)))</f>
+        <f>IF(B36="","",INDEX(Items!$E$5:$E$40,MATCH(B36,Items!$A$5:$A$40,0)))</f>
         <v/>
       </c>
       <c r="F36">
-        <f>IF(B36="","",INDEX(Items!$M$5:$M$58,MATCH(B36,Items!$A$5:$A$58,0)))</f>
+        <f>IF(B36="","",INDEX(Items!$M$5:$M$40,MATCH(B36,Items!$A$5:$A$40,0)))</f>
         <v/>
       </c>
     </row>
@@ -7945,23 +6001,23 @@
         <v>33</v>
       </c>
       <c r="B37">
-        <f>IF(COUNT(Items!$N$5:$N$58)&lt;A37,"",INDEX(Items!$A$5:$A$58,MATCH(SMALL(Items!$N$5:$N$58,A37),Items!$N$5:$N$58,0)))</f>
+        <f>IF(COUNT(Items!$N$5:$N$40)&lt;A37,"",INDEX(Items!$A$5:$A$40,MATCH(SMALL(Items!$N$5:$N$40,A37),Items!$N$5:$N$40,0)))</f>
         <v/>
       </c>
       <c r="C37" s="6">
-        <f>IF(B37="","",INDEX(Items!$I$5:$I$58,MATCH(B37,Items!$A$5:$A$58,0)))</f>
+        <f>IF(B37="","",INDEX(Items!$I$5:$I$40,MATCH(B37,Items!$A$5:$A$40,0)))</f>
         <v/>
       </c>
       <c r="D37">
-        <f>IF(B37="","",INDEX(Items!$B$5:$B$58,MATCH(B37,Items!$A$5:$A$58,0)))</f>
+        <f>IF(B37="","",INDEX(Items!$B$5:$B$40,MATCH(B37,Items!$A$5:$A$40,0)))</f>
         <v/>
       </c>
       <c r="E37">
-        <f>IF(B37="","",INDEX(Items!$E$5:$E$58,MATCH(B37,Items!$A$5:$A$58,0)))</f>
+        <f>IF(B37="","",INDEX(Items!$E$5:$E$40,MATCH(B37,Items!$A$5:$A$40,0)))</f>
         <v/>
       </c>
       <c r="F37">
-        <f>IF(B37="","",INDEX(Items!$M$5:$M$58,MATCH(B37,Items!$A$5:$A$58,0)))</f>
+        <f>IF(B37="","",INDEX(Items!$M$5:$M$40,MATCH(B37,Items!$A$5:$A$40,0)))</f>
         <v/>
       </c>
     </row>
@@ -7970,23 +6026,23 @@
         <v>34</v>
       </c>
       <c r="B38">
-        <f>IF(COUNT(Items!$N$5:$N$58)&lt;A38,"",INDEX(Items!$A$5:$A$58,MATCH(SMALL(Items!$N$5:$N$58,A38),Items!$N$5:$N$58,0)))</f>
+        <f>IF(COUNT(Items!$N$5:$N$40)&lt;A38,"",INDEX(Items!$A$5:$A$40,MATCH(SMALL(Items!$N$5:$N$40,A38),Items!$N$5:$N$40,0)))</f>
         <v/>
       </c>
       <c r="C38" s="6">
-        <f>IF(B38="","",INDEX(Items!$I$5:$I$58,MATCH(B38,Items!$A$5:$A$58,0)))</f>
+        <f>IF(B38="","",INDEX(Items!$I$5:$I$40,MATCH(B38,Items!$A$5:$A$40,0)))</f>
         <v/>
       </c>
       <c r="D38">
-        <f>IF(B38="","",INDEX(Items!$B$5:$B$58,MATCH(B38,Items!$A$5:$A$58,0)))</f>
+        <f>IF(B38="","",INDEX(Items!$B$5:$B$40,MATCH(B38,Items!$A$5:$A$40,0)))</f>
         <v/>
       </c>
       <c r="E38">
-        <f>IF(B38="","",INDEX(Items!$E$5:$E$58,MATCH(B38,Items!$A$5:$A$58,0)))</f>
+        <f>IF(B38="","",INDEX(Items!$E$5:$E$40,MATCH(B38,Items!$A$5:$A$40,0)))</f>
         <v/>
       </c>
       <c r="F38">
-        <f>IF(B38="","",INDEX(Items!$M$5:$M$58,MATCH(B38,Items!$A$5:$A$58,0)))</f>
+        <f>IF(B38="","",INDEX(Items!$M$5:$M$40,MATCH(B38,Items!$A$5:$A$40,0)))</f>
         <v/>
       </c>
     </row>
@@ -7995,23 +6051,23 @@
         <v>35</v>
       </c>
       <c r="B39">
-        <f>IF(COUNT(Items!$N$5:$N$58)&lt;A39,"",INDEX(Items!$A$5:$A$58,MATCH(SMALL(Items!$N$5:$N$58,A39),Items!$N$5:$N$58,0)))</f>
+        <f>IF(COUNT(Items!$N$5:$N$40)&lt;A39,"",INDEX(Items!$A$5:$A$40,MATCH(SMALL(Items!$N$5:$N$40,A39),Items!$N$5:$N$40,0)))</f>
         <v/>
       </c>
       <c r="C39" s="6">
-        <f>IF(B39="","",INDEX(Items!$I$5:$I$58,MATCH(B39,Items!$A$5:$A$58,0)))</f>
+        <f>IF(B39="","",INDEX(Items!$I$5:$I$40,MATCH(B39,Items!$A$5:$A$40,0)))</f>
         <v/>
       </c>
       <c r="D39">
-        <f>IF(B39="","",INDEX(Items!$B$5:$B$58,MATCH(B39,Items!$A$5:$A$58,0)))</f>
+        <f>IF(B39="","",INDEX(Items!$B$5:$B$40,MATCH(B39,Items!$A$5:$A$40,0)))</f>
         <v/>
       </c>
       <c r="E39">
-        <f>IF(B39="","",INDEX(Items!$E$5:$E$58,MATCH(B39,Items!$A$5:$A$58,0)))</f>
+        <f>IF(B39="","",INDEX(Items!$E$5:$E$40,MATCH(B39,Items!$A$5:$A$40,0)))</f>
         <v/>
       </c>
       <c r="F39">
-        <f>IF(B39="","",INDEX(Items!$M$5:$M$58,MATCH(B39,Items!$A$5:$A$58,0)))</f>
+        <f>IF(B39="","",INDEX(Items!$M$5:$M$40,MATCH(B39,Items!$A$5:$A$40,0)))</f>
         <v/>
       </c>
     </row>
@@ -8020,473 +6076,23 @@
         <v>36</v>
       </c>
       <c r="B40">
-        <f>IF(COUNT(Items!$N$5:$N$58)&lt;A40,"",INDEX(Items!$A$5:$A$58,MATCH(SMALL(Items!$N$5:$N$58,A40),Items!$N$5:$N$58,0)))</f>
+        <f>IF(COUNT(Items!$N$5:$N$40)&lt;A40,"",INDEX(Items!$A$5:$A$40,MATCH(SMALL(Items!$N$5:$N$40,A40),Items!$N$5:$N$40,0)))</f>
         <v/>
       </c>
       <c r="C40" s="6">
-        <f>IF(B40="","",INDEX(Items!$I$5:$I$58,MATCH(B40,Items!$A$5:$A$58,0)))</f>
+        <f>IF(B40="","",INDEX(Items!$I$5:$I$40,MATCH(B40,Items!$A$5:$A$40,0)))</f>
         <v/>
       </c>
       <c r="D40">
-        <f>IF(B40="","",INDEX(Items!$B$5:$B$58,MATCH(B40,Items!$A$5:$A$58,0)))</f>
+        <f>IF(B40="","",INDEX(Items!$B$5:$B$40,MATCH(B40,Items!$A$5:$A$40,0)))</f>
         <v/>
       </c>
       <c r="E40">
-        <f>IF(B40="","",INDEX(Items!$E$5:$E$58,MATCH(B40,Items!$A$5:$A$58,0)))</f>
+        <f>IF(B40="","",INDEX(Items!$E$5:$E$40,MATCH(B40,Items!$A$5:$A$40,0)))</f>
         <v/>
       </c>
       <c r="F40">
-        <f>IF(B40="","",INDEX(Items!$M$5:$M$58,MATCH(B40,Items!$A$5:$A$58,0)))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="n">
-        <v>37</v>
-      </c>
-      <c r="B41">
-        <f>IF(COUNT(Items!$N$5:$N$58)&lt;A41,"",INDEX(Items!$A$5:$A$58,MATCH(SMALL(Items!$N$5:$N$58,A41),Items!$N$5:$N$58,0)))</f>
-        <v/>
-      </c>
-      <c r="C41" s="6">
-        <f>IF(B41="","",INDEX(Items!$I$5:$I$58,MATCH(B41,Items!$A$5:$A$58,0)))</f>
-        <v/>
-      </c>
-      <c r="D41">
-        <f>IF(B41="","",INDEX(Items!$B$5:$B$58,MATCH(B41,Items!$A$5:$A$58,0)))</f>
-        <v/>
-      </c>
-      <c r="E41">
-        <f>IF(B41="","",INDEX(Items!$E$5:$E$58,MATCH(B41,Items!$A$5:$A$58,0)))</f>
-        <v/>
-      </c>
-      <c r="F41">
-        <f>IF(B41="","",INDEX(Items!$M$5:$M$58,MATCH(B41,Items!$A$5:$A$58,0)))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="n">
-        <v>38</v>
-      </c>
-      <c r="B42">
-        <f>IF(COUNT(Items!$N$5:$N$58)&lt;A42,"",INDEX(Items!$A$5:$A$58,MATCH(SMALL(Items!$N$5:$N$58,A42),Items!$N$5:$N$58,0)))</f>
-        <v/>
-      </c>
-      <c r="C42" s="6">
-        <f>IF(B42="","",INDEX(Items!$I$5:$I$58,MATCH(B42,Items!$A$5:$A$58,0)))</f>
-        <v/>
-      </c>
-      <c r="D42">
-        <f>IF(B42="","",INDEX(Items!$B$5:$B$58,MATCH(B42,Items!$A$5:$A$58,0)))</f>
-        <v/>
-      </c>
-      <c r="E42">
-        <f>IF(B42="","",INDEX(Items!$E$5:$E$58,MATCH(B42,Items!$A$5:$A$58,0)))</f>
-        <v/>
-      </c>
-      <c r="F42">
-        <f>IF(B42="","",INDEX(Items!$M$5:$M$58,MATCH(B42,Items!$A$5:$A$58,0)))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="n">
-        <v>39</v>
-      </c>
-      <c r="B43">
-        <f>IF(COUNT(Items!$N$5:$N$58)&lt;A43,"",INDEX(Items!$A$5:$A$58,MATCH(SMALL(Items!$N$5:$N$58,A43),Items!$N$5:$N$58,0)))</f>
-        <v/>
-      </c>
-      <c r="C43" s="6">
-        <f>IF(B43="","",INDEX(Items!$I$5:$I$58,MATCH(B43,Items!$A$5:$A$58,0)))</f>
-        <v/>
-      </c>
-      <c r="D43">
-        <f>IF(B43="","",INDEX(Items!$B$5:$B$58,MATCH(B43,Items!$A$5:$A$58,0)))</f>
-        <v/>
-      </c>
-      <c r="E43">
-        <f>IF(B43="","",INDEX(Items!$E$5:$E$58,MATCH(B43,Items!$A$5:$A$58,0)))</f>
-        <v/>
-      </c>
-      <c r="F43">
-        <f>IF(B43="","",INDEX(Items!$M$5:$M$58,MATCH(B43,Items!$A$5:$A$58,0)))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="n">
-        <v>40</v>
-      </c>
-      <c r="B44">
-        <f>IF(COUNT(Items!$N$5:$N$58)&lt;A44,"",INDEX(Items!$A$5:$A$58,MATCH(SMALL(Items!$N$5:$N$58,A44),Items!$N$5:$N$58,0)))</f>
-        <v/>
-      </c>
-      <c r="C44" s="6">
-        <f>IF(B44="","",INDEX(Items!$I$5:$I$58,MATCH(B44,Items!$A$5:$A$58,0)))</f>
-        <v/>
-      </c>
-      <c r="D44">
-        <f>IF(B44="","",INDEX(Items!$B$5:$B$58,MATCH(B44,Items!$A$5:$A$58,0)))</f>
-        <v/>
-      </c>
-      <c r="E44">
-        <f>IF(B44="","",INDEX(Items!$E$5:$E$58,MATCH(B44,Items!$A$5:$A$58,0)))</f>
-        <v/>
-      </c>
-      <c r="F44">
-        <f>IF(B44="","",INDEX(Items!$M$5:$M$58,MATCH(B44,Items!$A$5:$A$58,0)))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="n">
-        <v>41</v>
-      </c>
-      <c r="B45">
-        <f>IF(COUNT(Items!$N$5:$N$58)&lt;A45,"",INDEX(Items!$A$5:$A$58,MATCH(SMALL(Items!$N$5:$N$58,A45),Items!$N$5:$N$58,0)))</f>
-        <v/>
-      </c>
-      <c r="C45" s="6">
-        <f>IF(B45="","",INDEX(Items!$I$5:$I$58,MATCH(B45,Items!$A$5:$A$58,0)))</f>
-        <v/>
-      </c>
-      <c r="D45">
-        <f>IF(B45="","",INDEX(Items!$B$5:$B$58,MATCH(B45,Items!$A$5:$A$58,0)))</f>
-        <v/>
-      </c>
-      <c r="E45">
-        <f>IF(B45="","",INDEX(Items!$E$5:$E$58,MATCH(B45,Items!$A$5:$A$58,0)))</f>
-        <v/>
-      </c>
-      <c r="F45">
-        <f>IF(B45="","",INDEX(Items!$M$5:$M$58,MATCH(B45,Items!$A$5:$A$58,0)))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="n">
-        <v>42</v>
-      </c>
-      <c r="B46">
-        <f>IF(COUNT(Items!$N$5:$N$58)&lt;A46,"",INDEX(Items!$A$5:$A$58,MATCH(SMALL(Items!$N$5:$N$58,A46),Items!$N$5:$N$58,0)))</f>
-        <v/>
-      </c>
-      <c r="C46" s="6">
-        <f>IF(B46="","",INDEX(Items!$I$5:$I$58,MATCH(B46,Items!$A$5:$A$58,0)))</f>
-        <v/>
-      </c>
-      <c r="D46">
-        <f>IF(B46="","",INDEX(Items!$B$5:$B$58,MATCH(B46,Items!$A$5:$A$58,0)))</f>
-        <v/>
-      </c>
-      <c r="E46">
-        <f>IF(B46="","",INDEX(Items!$E$5:$E$58,MATCH(B46,Items!$A$5:$A$58,0)))</f>
-        <v/>
-      </c>
-      <c r="F46">
-        <f>IF(B46="","",INDEX(Items!$M$5:$M$58,MATCH(B46,Items!$A$5:$A$58,0)))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="n">
-        <v>43</v>
-      </c>
-      <c r="B47">
-        <f>IF(COUNT(Items!$N$5:$N$58)&lt;A47,"",INDEX(Items!$A$5:$A$58,MATCH(SMALL(Items!$N$5:$N$58,A47),Items!$N$5:$N$58,0)))</f>
-        <v/>
-      </c>
-      <c r="C47" s="6">
-        <f>IF(B47="","",INDEX(Items!$I$5:$I$58,MATCH(B47,Items!$A$5:$A$58,0)))</f>
-        <v/>
-      </c>
-      <c r="D47">
-        <f>IF(B47="","",INDEX(Items!$B$5:$B$58,MATCH(B47,Items!$A$5:$A$58,0)))</f>
-        <v/>
-      </c>
-      <c r="E47">
-        <f>IF(B47="","",INDEX(Items!$E$5:$E$58,MATCH(B47,Items!$A$5:$A$58,0)))</f>
-        <v/>
-      </c>
-      <c r="F47">
-        <f>IF(B47="","",INDEX(Items!$M$5:$M$58,MATCH(B47,Items!$A$5:$A$58,0)))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="n">
-        <v>44</v>
-      </c>
-      <c r="B48">
-        <f>IF(COUNT(Items!$N$5:$N$58)&lt;A48,"",INDEX(Items!$A$5:$A$58,MATCH(SMALL(Items!$N$5:$N$58,A48),Items!$N$5:$N$58,0)))</f>
-        <v/>
-      </c>
-      <c r="C48" s="6">
-        <f>IF(B48="","",INDEX(Items!$I$5:$I$58,MATCH(B48,Items!$A$5:$A$58,0)))</f>
-        <v/>
-      </c>
-      <c r="D48">
-        <f>IF(B48="","",INDEX(Items!$B$5:$B$58,MATCH(B48,Items!$A$5:$A$58,0)))</f>
-        <v/>
-      </c>
-      <c r="E48">
-        <f>IF(B48="","",INDEX(Items!$E$5:$E$58,MATCH(B48,Items!$A$5:$A$58,0)))</f>
-        <v/>
-      </c>
-      <c r="F48">
-        <f>IF(B48="","",INDEX(Items!$M$5:$M$58,MATCH(B48,Items!$A$5:$A$58,0)))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="n">
-        <v>45</v>
-      </c>
-      <c r="B49">
-        <f>IF(COUNT(Items!$N$5:$N$58)&lt;A49,"",INDEX(Items!$A$5:$A$58,MATCH(SMALL(Items!$N$5:$N$58,A49),Items!$N$5:$N$58,0)))</f>
-        <v/>
-      </c>
-      <c r="C49" s="6">
-        <f>IF(B49="","",INDEX(Items!$I$5:$I$58,MATCH(B49,Items!$A$5:$A$58,0)))</f>
-        <v/>
-      </c>
-      <c r="D49">
-        <f>IF(B49="","",INDEX(Items!$B$5:$B$58,MATCH(B49,Items!$A$5:$A$58,0)))</f>
-        <v/>
-      </c>
-      <c r="E49">
-        <f>IF(B49="","",INDEX(Items!$E$5:$E$58,MATCH(B49,Items!$A$5:$A$58,0)))</f>
-        <v/>
-      </c>
-      <c r="F49">
-        <f>IF(B49="","",INDEX(Items!$M$5:$M$58,MATCH(B49,Items!$A$5:$A$58,0)))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="n">
-        <v>46</v>
-      </c>
-      <c r="B50">
-        <f>IF(COUNT(Items!$N$5:$N$58)&lt;A50,"",INDEX(Items!$A$5:$A$58,MATCH(SMALL(Items!$N$5:$N$58,A50),Items!$N$5:$N$58,0)))</f>
-        <v/>
-      </c>
-      <c r="C50" s="6">
-        <f>IF(B50="","",INDEX(Items!$I$5:$I$58,MATCH(B50,Items!$A$5:$A$58,0)))</f>
-        <v/>
-      </c>
-      <c r="D50">
-        <f>IF(B50="","",INDEX(Items!$B$5:$B$58,MATCH(B50,Items!$A$5:$A$58,0)))</f>
-        <v/>
-      </c>
-      <c r="E50">
-        <f>IF(B50="","",INDEX(Items!$E$5:$E$58,MATCH(B50,Items!$A$5:$A$58,0)))</f>
-        <v/>
-      </c>
-      <c r="F50">
-        <f>IF(B50="","",INDEX(Items!$M$5:$M$58,MATCH(B50,Items!$A$5:$A$58,0)))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="n">
-        <v>47</v>
-      </c>
-      <c r="B51">
-        <f>IF(COUNT(Items!$N$5:$N$58)&lt;A51,"",INDEX(Items!$A$5:$A$58,MATCH(SMALL(Items!$N$5:$N$58,A51),Items!$N$5:$N$58,0)))</f>
-        <v/>
-      </c>
-      <c r="C51" s="6">
-        <f>IF(B51="","",INDEX(Items!$I$5:$I$58,MATCH(B51,Items!$A$5:$A$58,0)))</f>
-        <v/>
-      </c>
-      <c r="D51">
-        <f>IF(B51="","",INDEX(Items!$B$5:$B$58,MATCH(B51,Items!$A$5:$A$58,0)))</f>
-        <v/>
-      </c>
-      <c r="E51">
-        <f>IF(B51="","",INDEX(Items!$E$5:$E$58,MATCH(B51,Items!$A$5:$A$58,0)))</f>
-        <v/>
-      </c>
-      <c r="F51">
-        <f>IF(B51="","",INDEX(Items!$M$5:$M$58,MATCH(B51,Items!$A$5:$A$58,0)))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="n">
-        <v>48</v>
-      </c>
-      <c r="B52">
-        <f>IF(COUNT(Items!$N$5:$N$58)&lt;A52,"",INDEX(Items!$A$5:$A$58,MATCH(SMALL(Items!$N$5:$N$58,A52),Items!$N$5:$N$58,0)))</f>
-        <v/>
-      </c>
-      <c r="C52" s="6">
-        <f>IF(B52="","",INDEX(Items!$I$5:$I$58,MATCH(B52,Items!$A$5:$A$58,0)))</f>
-        <v/>
-      </c>
-      <c r="D52">
-        <f>IF(B52="","",INDEX(Items!$B$5:$B$58,MATCH(B52,Items!$A$5:$A$58,0)))</f>
-        <v/>
-      </c>
-      <c r="E52">
-        <f>IF(B52="","",INDEX(Items!$E$5:$E$58,MATCH(B52,Items!$A$5:$A$58,0)))</f>
-        <v/>
-      </c>
-      <c r="F52">
-        <f>IF(B52="","",INDEX(Items!$M$5:$M$58,MATCH(B52,Items!$A$5:$A$58,0)))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="n">
-        <v>49</v>
-      </c>
-      <c r="B53">
-        <f>IF(COUNT(Items!$N$5:$N$58)&lt;A53,"",INDEX(Items!$A$5:$A$58,MATCH(SMALL(Items!$N$5:$N$58,A53),Items!$N$5:$N$58,0)))</f>
-        <v/>
-      </c>
-      <c r="C53" s="6">
-        <f>IF(B53="","",INDEX(Items!$I$5:$I$58,MATCH(B53,Items!$A$5:$A$58,0)))</f>
-        <v/>
-      </c>
-      <c r="D53">
-        <f>IF(B53="","",INDEX(Items!$B$5:$B$58,MATCH(B53,Items!$A$5:$A$58,0)))</f>
-        <v/>
-      </c>
-      <c r="E53">
-        <f>IF(B53="","",INDEX(Items!$E$5:$E$58,MATCH(B53,Items!$A$5:$A$58,0)))</f>
-        <v/>
-      </c>
-      <c r="F53">
-        <f>IF(B53="","",INDEX(Items!$M$5:$M$58,MATCH(B53,Items!$A$5:$A$58,0)))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="n">
-        <v>50</v>
-      </c>
-      <c r="B54">
-        <f>IF(COUNT(Items!$N$5:$N$58)&lt;A54,"",INDEX(Items!$A$5:$A$58,MATCH(SMALL(Items!$N$5:$N$58,A54),Items!$N$5:$N$58,0)))</f>
-        <v/>
-      </c>
-      <c r="C54" s="6">
-        <f>IF(B54="","",INDEX(Items!$I$5:$I$58,MATCH(B54,Items!$A$5:$A$58,0)))</f>
-        <v/>
-      </c>
-      <c r="D54">
-        <f>IF(B54="","",INDEX(Items!$B$5:$B$58,MATCH(B54,Items!$A$5:$A$58,0)))</f>
-        <v/>
-      </c>
-      <c r="E54">
-        <f>IF(B54="","",INDEX(Items!$E$5:$E$58,MATCH(B54,Items!$A$5:$A$58,0)))</f>
-        <v/>
-      </c>
-      <c r="F54">
-        <f>IF(B54="","",INDEX(Items!$M$5:$M$58,MATCH(B54,Items!$A$5:$A$58,0)))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="n">
-        <v>51</v>
-      </c>
-      <c r="B55">
-        <f>IF(COUNT(Items!$N$5:$N$58)&lt;A55,"",INDEX(Items!$A$5:$A$58,MATCH(SMALL(Items!$N$5:$N$58,A55),Items!$N$5:$N$58,0)))</f>
-        <v/>
-      </c>
-      <c r="C55" s="6">
-        <f>IF(B55="","",INDEX(Items!$I$5:$I$58,MATCH(B55,Items!$A$5:$A$58,0)))</f>
-        <v/>
-      </c>
-      <c r="D55">
-        <f>IF(B55="","",INDEX(Items!$B$5:$B$58,MATCH(B55,Items!$A$5:$A$58,0)))</f>
-        <v/>
-      </c>
-      <c r="E55">
-        <f>IF(B55="","",INDEX(Items!$E$5:$E$58,MATCH(B55,Items!$A$5:$A$58,0)))</f>
-        <v/>
-      </c>
-      <c r="F55">
-        <f>IF(B55="","",INDEX(Items!$M$5:$M$58,MATCH(B55,Items!$A$5:$A$58,0)))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="n">
-        <v>52</v>
-      </c>
-      <c r="B56">
-        <f>IF(COUNT(Items!$N$5:$N$58)&lt;A56,"",INDEX(Items!$A$5:$A$58,MATCH(SMALL(Items!$N$5:$N$58,A56),Items!$N$5:$N$58,0)))</f>
-        <v/>
-      </c>
-      <c r="C56" s="6">
-        <f>IF(B56="","",INDEX(Items!$I$5:$I$58,MATCH(B56,Items!$A$5:$A$58,0)))</f>
-        <v/>
-      </c>
-      <c r="D56">
-        <f>IF(B56="","",INDEX(Items!$B$5:$B$58,MATCH(B56,Items!$A$5:$A$58,0)))</f>
-        <v/>
-      </c>
-      <c r="E56">
-        <f>IF(B56="","",INDEX(Items!$E$5:$E$58,MATCH(B56,Items!$A$5:$A$58,0)))</f>
-        <v/>
-      </c>
-      <c r="F56">
-        <f>IF(B56="","",INDEX(Items!$M$5:$M$58,MATCH(B56,Items!$A$5:$A$58,0)))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="n">
-        <v>53</v>
-      </c>
-      <c r="B57">
-        <f>IF(COUNT(Items!$N$5:$N$58)&lt;A57,"",INDEX(Items!$A$5:$A$58,MATCH(SMALL(Items!$N$5:$N$58,A57),Items!$N$5:$N$58,0)))</f>
-        <v/>
-      </c>
-      <c r="C57" s="6">
-        <f>IF(B57="","",INDEX(Items!$I$5:$I$58,MATCH(B57,Items!$A$5:$A$58,0)))</f>
-        <v/>
-      </c>
-      <c r="D57">
-        <f>IF(B57="","",INDEX(Items!$B$5:$B$58,MATCH(B57,Items!$A$5:$A$58,0)))</f>
-        <v/>
-      </c>
-      <c r="E57">
-        <f>IF(B57="","",INDEX(Items!$E$5:$E$58,MATCH(B57,Items!$A$5:$A$58,0)))</f>
-        <v/>
-      </c>
-      <c r="F57">
-        <f>IF(B57="","",INDEX(Items!$M$5:$M$58,MATCH(B57,Items!$A$5:$A$58,0)))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="n">
-        <v>54</v>
-      </c>
-      <c r="B58">
-        <f>IF(COUNT(Items!$N$5:$N$58)&lt;A58,"",INDEX(Items!$A$5:$A$58,MATCH(SMALL(Items!$N$5:$N$58,A58),Items!$N$5:$N$58,0)))</f>
-        <v/>
-      </c>
-      <c r="C58" s="6">
-        <f>IF(B58="","",INDEX(Items!$I$5:$I$58,MATCH(B58,Items!$A$5:$A$58,0)))</f>
-        <v/>
-      </c>
-      <c r="D58">
-        <f>IF(B58="","",INDEX(Items!$B$5:$B$58,MATCH(B58,Items!$A$5:$A$58,0)))</f>
-        <v/>
-      </c>
-      <c r="E58">
-        <f>IF(B58="","",INDEX(Items!$E$5:$E$58,MATCH(B58,Items!$A$5:$A$58,0)))</f>
-        <v/>
-      </c>
-      <c r="F58">
-        <f>IF(B58="","",INDEX(Items!$M$5:$M$58,MATCH(B58,Items!$A$5:$A$58,0)))</f>
+        <f>IF(B40="","",INDEX(Items!$M$5:$M$40,MATCH(B40,Items!$A$5:$A$40,0)))</f>
         <v/>
       </c>
     </row>
@@ -8501,7 +6107,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D14"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="2" max="2"/>
@@ -8548,11 +6154,11 @@
         </is>
       </c>
       <c r="C5">
-        <f>COUNTIF(Items!$E$5:$E$58,A5)</f>
+        <f>COUNTIF(Items!$E$5:$E$40,A5)</f>
         <v/>
       </c>
       <c r="D5" s="6">
-        <f>IF(SUMPRODUCT((Items!$E$5:$E$58=A5)*Items!$H$5:$H$58)=0,"",SUMPRODUCT((Items!$E$5:$E$58=A5)*Items!$G$5:$G$58)/SUMPRODUCT((Items!$E$5:$E$58=A5)*Items!$H$5:$H$58))</f>
+        <f>IF(SUMPRODUCT((Items!$E$5:$E$40=A5)*Items!$H$5:$H$40)=0,"",SUMPRODUCT((Items!$E$5:$E$40=A5)*Items!$G$5:$G$40)/SUMPRODUCT((Items!$E$5:$E$40=A5)*Items!$H$5:$H$40))</f>
         <v/>
       </c>
     </row>
@@ -8568,11 +6174,11 @@
         </is>
       </c>
       <c r="C6">
-        <f>COUNTIF(Items!$E$5:$E$58,A6)</f>
+        <f>COUNTIF(Items!$E$5:$E$40,A6)</f>
         <v/>
       </c>
       <c r="D6" s="6">
-        <f>IF(SUMPRODUCT((Items!$E$5:$E$58=A6)*Items!$H$5:$H$58)=0,"",SUMPRODUCT((Items!$E$5:$E$58=A6)*Items!$G$5:$G$58)/SUMPRODUCT((Items!$E$5:$E$58=A6)*Items!$H$5:$H$58))</f>
+        <f>IF(SUMPRODUCT((Items!$E$5:$E$40=A6)*Items!$H$5:$H$40)=0,"",SUMPRODUCT((Items!$E$5:$E$40=A6)*Items!$G$5:$G$40)/SUMPRODUCT((Items!$E$5:$E$40=A6)*Items!$H$5:$H$40))</f>
         <v/>
       </c>
     </row>
@@ -8588,11 +6194,11 @@
         </is>
       </c>
       <c r="C7">
-        <f>COUNTIF(Items!$E$5:$E$58,A7)</f>
+        <f>COUNTIF(Items!$E$5:$E$40,A7)</f>
         <v/>
       </c>
       <c r="D7" s="6">
-        <f>IF(SUMPRODUCT((Items!$E$5:$E$58=A7)*Items!$H$5:$H$58)=0,"",SUMPRODUCT((Items!$E$5:$E$58=A7)*Items!$G$5:$G$58)/SUMPRODUCT((Items!$E$5:$E$58=A7)*Items!$H$5:$H$58))</f>
+        <f>IF(SUMPRODUCT((Items!$E$5:$E$40=A7)*Items!$H$5:$H$40)=0,"",SUMPRODUCT((Items!$E$5:$E$40=A7)*Items!$G$5:$G$40)/SUMPRODUCT((Items!$E$5:$E$40=A7)*Items!$H$5:$H$40))</f>
         <v/>
       </c>
     </row>
@@ -8608,11 +6214,11 @@
         </is>
       </c>
       <c r="C8">
-        <f>COUNTIF(Items!$E$5:$E$58,A8)</f>
+        <f>COUNTIF(Items!$E$5:$E$40,A8)</f>
         <v/>
       </c>
       <c r="D8" s="6">
-        <f>IF(SUMPRODUCT((Items!$E$5:$E$58=A8)*Items!$H$5:$H$58)=0,"",SUMPRODUCT((Items!$E$5:$E$58=A8)*Items!$G$5:$G$58)/SUMPRODUCT((Items!$E$5:$E$58=A8)*Items!$H$5:$H$58))</f>
+        <f>IF(SUMPRODUCT((Items!$E$5:$E$40=A8)*Items!$H$5:$H$40)=0,"",SUMPRODUCT((Items!$E$5:$E$40=A8)*Items!$G$5:$G$40)/SUMPRODUCT((Items!$E$5:$E$40=A8)*Items!$H$5:$H$40))</f>
         <v/>
       </c>
     </row>
@@ -8622,15 +6228,15 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Part 1. The week's rules, cold</t>
+          <t>Part 1. Where the revenue went</t>
         </is>
       </c>
       <c r="C9">
-        <f>COUNTIF(Items!$B$5:$B$58,A9)</f>
+        <f>COUNTIF(Items!$B$5:$B$40,A9)</f>
         <v/>
       </c>
       <c r="D9" s="6">
-        <f>IF(SUMPRODUCT((Items!$B$5:$B$58=A9)*Items!$H$5:$H$58)=0,"",SUMPRODUCT((Items!$B$5:$B$58=A9)*Items!$G$5:$G$58)/SUMPRODUCT((Items!$B$5:$B$58=A9)*Items!$H$5:$H$58))</f>
+        <f>IF(SUMPRODUCT((Items!$B$5:$B$40=A9)*Items!$H$5:$H$40)=0,"",SUMPRODUCT((Items!$B$5:$B$40=A9)*Items!$G$5:$G$40)/SUMPRODUCT((Items!$B$5:$B$40=A9)*Items!$H$5:$H$40))</f>
         <v/>
       </c>
     </row>
@@ -8640,15 +6246,15 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Part 2. Where did the revenue go</t>
+          <t>Part 2. Which Q1 figure is right</t>
         </is>
       </c>
       <c r="C10">
-        <f>COUNTIF(Items!$B$5:$B$58,A10)</f>
+        <f>COUNTIF(Items!$B$5:$B$40,A10)</f>
         <v/>
       </c>
       <c r="D10" s="6">
-        <f>IF(SUMPRODUCT((Items!$B$5:$B$58=A10)*Items!$H$5:$H$58)=0,"",SUMPRODUCT((Items!$B$5:$B$58=A10)*Items!$G$5:$G$58)/SUMPRODUCT((Items!$B$5:$B$58=A10)*Items!$H$5:$H$58))</f>
+        <f>IF(SUMPRODUCT((Items!$B$5:$B$40=A10)*Items!$H$5:$H$40)=0,"",SUMPRODUCT((Items!$B$5:$B$40=A10)*Items!$G$5:$G$40)/SUMPRODUCT((Items!$B$5:$B$40=A10)*Items!$H$5:$H$40))</f>
         <v/>
       </c>
     </row>
@@ -8658,15 +6264,15 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Part 3. Rows you can trust</t>
+          <t>Part 3. Real, worth it, and caused</t>
         </is>
       </c>
       <c r="C11">
-        <f>COUNTIF(Items!$B$5:$B$58,A11)</f>
+        <f>COUNTIF(Items!$B$5:$B$40,A11)</f>
         <v/>
       </c>
       <c r="D11" s="6">
-        <f>IF(SUMPRODUCT((Items!$B$5:$B$58=A11)*Items!$H$5:$H$58)=0,"",SUMPRODUCT((Items!$B$5:$B$58=A11)*Items!$G$5:$G$58)/SUMPRODUCT((Items!$B$5:$B$58=A11)*Items!$H$5:$H$58))</f>
+        <f>IF(SUMPRODUCT((Items!$B$5:$B$40=A11)*Items!$H$5:$H$40)=0,"",SUMPRODUCT((Items!$B$5:$B$40=A11)*Items!$G$5:$G$40)/SUMPRODUCT((Items!$B$5:$B$40=A11)*Items!$H$5:$H$40))</f>
         <v/>
       </c>
     </row>
@@ -8676,15 +6282,15 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Part 4. Read the code, read the data</t>
+          <t>Part 4. The same traps, in public</t>
         </is>
       </c>
       <c r="C12">
-        <f>COUNTIF(Items!$B$5:$B$58,A12)</f>
+        <f>COUNTIF(Items!$B$5:$B$40,A12)</f>
         <v/>
       </c>
       <c r="D12" s="6">
-        <f>IF(SUMPRODUCT((Items!$B$5:$B$58=A12)*Items!$H$5:$H$58)=0,"",SUMPRODUCT((Items!$B$5:$B$58=A12)*Items!$G$5:$G$58)/SUMPRODUCT((Items!$B$5:$B$58=A12)*Items!$H$5:$H$58))</f>
+        <f>IF(SUMPRODUCT((Items!$B$5:$B$40=A12)*Items!$H$5:$H$40)=0,"",SUMPRODUCT((Items!$B$5:$B$40=A12)*Items!$G$5:$G$40)/SUMPRODUCT((Items!$B$5:$B$40=A12)*Items!$H$5:$H$40))</f>
         <v/>
       </c>
     </row>
@@ -8694,33 +6300,15 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Part 5. Chance and a fair test</t>
+          <t>Part 5. The agent's bill and its logs</t>
         </is>
       </c>
       <c r="C13">
-        <f>COUNTIF(Items!$B$5:$B$58,A13)</f>
+        <f>COUNTIF(Items!$B$5:$B$40,A13)</f>
         <v/>
       </c>
       <c r="D13" s="6">
-        <f>IF(SUMPRODUCT((Items!$B$5:$B$58=A13)*Items!$H$5:$H$58)=0,"",SUMPRODUCT((Items!$B$5:$B$58=A13)*Items!$G$5:$G$58)/SUMPRODUCT((Items!$B$5:$B$58=A13)*Items!$H$5:$H$58))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>6</v>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Part 6. The numbers</t>
-        </is>
-      </c>
-      <c r="C14">
-        <f>COUNTIF(Items!$B$5:$B$58,A14)</f>
-        <v/>
-      </c>
-      <c r="D14" s="6">
-        <f>IF(SUMPRODUCT((Items!$B$5:$B$58=A14)*Items!$H$5:$H$58)=0,"",SUMPRODUCT((Items!$B$5:$B$58=A14)*Items!$G$5:$G$58)/SUMPRODUCT((Items!$B$5:$B$58=A14)*Items!$H$5:$H$58))</f>
+        <f>IF(SUMPRODUCT((Items!$B$5:$B$40=A13)*Items!$H$5:$H$40)=0,"",SUMPRODUCT((Items!$B$5:$B$40=A13)*Items!$G$5:$G$40)/SUMPRODUCT((Items!$B$5:$B$40=A13)*Items!$H$5:$H$40))</f>
         <v/>
       </c>
     </row>
@@ -8777,19 +6365,19 @@
         <v>1</v>
       </c>
       <c r="B5" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=B$4)*ISNUMBER(Marks!$B$5:$BC$5))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=B$4)*(Marks!$B$5:$BC$5=1))/SUMPRODUCT((Marks!$B$3:$BC$3=B$4)*ISNUMBER(Marks!$B$5:$BC$5)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=B$4)*ISNUMBER(Marks!$B$5:$AK$5))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=B$4)*(Marks!$B$5:$AK$5=1))/SUMPRODUCT((Marks!$B$3:$AK$3=B$4)*ISNUMBER(Marks!$B$5:$AK$5)))</f>
         <v/>
       </c>
       <c r="C5" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=C$4)*ISNUMBER(Marks!$B$5:$BC$5))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=C$4)*(Marks!$B$5:$BC$5=1))/SUMPRODUCT((Marks!$B$3:$BC$3=C$4)*ISNUMBER(Marks!$B$5:$BC$5)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=C$4)*ISNUMBER(Marks!$B$5:$AK$5))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=C$4)*(Marks!$B$5:$AK$5=1))/SUMPRODUCT((Marks!$B$3:$AK$3=C$4)*ISNUMBER(Marks!$B$5:$AK$5)))</f>
         <v/>
       </c>
       <c r="D5" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=D$4)*ISNUMBER(Marks!$B$5:$BC$5))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=D$4)*(Marks!$B$5:$BC$5=1))/SUMPRODUCT((Marks!$B$3:$BC$3=D$4)*ISNUMBER(Marks!$B$5:$BC$5)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=D$4)*ISNUMBER(Marks!$B$5:$AK$5))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=D$4)*(Marks!$B$5:$AK$5=1))/SUMPRODUCT((Marks!$B$3:$AK$3=D$4)*ISNUMBER(Marks!$B$5:$AK$5)))</f>
         <v/>
       </c>
       <c r="E5" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=E$4)*ISNUMBER(Marks!$B$5:$BC$5))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=E$4)*(Marks!$B$5:$BC$5=1))/SUMPRODUCT((Marks!$B$3:$BC$3=E$4)*ISNUMBER(Marks!$B$5:$BC$5)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=E$4)*ISNUMBER(Marks!$B$5:$AK$5))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=E$4)*(Marks!$B$5:$AK$5=1))/SUMPRODUCT((Marks!$B$3:$AK$3=E$4)*ISNUMBER(Marks!$B$5:$AK$5)))</f>
         <v/>
       </c>
     </row>
@@ -8798,19 +6386,19 @@
         <v>2</v>
       </c>
       <c r="B6" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=B$4)*ISNUMBER(Marks!$B$6:$BC$6))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=B$4)*(Marks!$B$6:$BC$6=1))/SUMPRODUCT((Marks!$B$3:$BC$3=B$4)*ISNUMBER(Marks!$B$6:$BC$6)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=B$4)*ISNUMBER(Marks!$B$6:$AK$6))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=B$4)*(Marks!$B$6:$AK$6=1))/SUMPRODUCT((Marks!$B$3:$AK$3=B$4)*ISNUMBER(Marks!$B$6:$AK$6)))</f>
         <v/>
       </c>
       <c r="C6" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=C$4)*ISNUMBER(Marks!$B$6:$BC$6))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=C$4)*(Marks!$B$6:$BC$6=1))/SUMPRODUCT((Marks!$B$3:$BC$3=C$4)*ISNUMBER(Marks!$B$6:$BC$6)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=C$4)*ISNUMBER(Marks!$B$6:$AK$6))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=C$4)*(Marks!$B$6:$AK$6=1))/SUMPRODUCT((Marks!$B$3:$AK$3=C$4)*ISNUMBER(Marks!$B$6:$AK$6)))</f>
         <v/>
       </c>
       <c r="D6" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=D$4)*ISNUMBER(Marks!$B$6:$BC$6))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=D$4)*(Marks!$B$6:$BC$6=1))/SUMPRODUCT((Marks!$B$3:$BC$3=D$4)*ISNUMBER(Marks!$B$6:$BC$6)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=D$4)*ISNUMBER(Marks!$B$6:$AK$6))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=D$4)*(Marks!$B$6:$AK$6=1))/SUMPRODUCT((Marks!$B$3:$AK$3=D$4)*ISNUMBER(Marks!$B$6:$AK$6)))</f>
         <v/>
       </c>
       <c r="E6" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=E$4)*ISNUMBER(Marks!$B$6:$BC$6))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=E$4)*(Marks!$B$6:$BC$6=1))/SUMPRODUCT((Marks!$B$3:$BC$3=E$4)*ISNUMBER(Marks!$B$6:$BC$6)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=E$4)*ISNUMBER(Marks!$B$6:$AK$6))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=E$4)*(Marks!$B$6:$AK$6=1))/SUMPRODUCT((Marks!$B$3:$AK$3=E$4)*ISNUMBER(Marks!$B$6:$AK$6)))</f>
         <v/>
       </c>
     </row>
@@ -8819,19 +6407,19 @@
         <v>3</v>
       </c>
       <c r="B7" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=B$4)*ISNUMBER(Marks!$B$7:$BC$7))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=B$4)*(Marks!$B$7:$BC$7=1))/SUMPRODUCT((Marks!$B$3:$BC$3=B$4)*ISNUMBER(Marks!$B$7:$BC$7)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=B$4)*ISNUMBER(Marks!$B$7:$AK$7))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=B$4)*(Marks!$B$7:$AK$7=1))/SUMPRODUCT((Marks!$B$3:$AK$3=B$4)*ISNUMBER(Marks!$B$7:$AK$7)))</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=C$4)*ISNUMBER(Marks!$B$7:$BC$7))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=C$4)*(Marks!$B$7:$BC$7=1))/SUMPRODUCT((Marks!$B$3:$BC$3=C$4)*ISNUMBER(Marks!$B$7:$BC$7)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=C$4)*ISNUMBER(Marks!$B$7:$AK$7))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=C$4)*(Marks!$B$7:$AK$7=1))/SUMPRODUCT((Marks!$B$3:$AK$3=C$4)*ISNUMBER(Marks!$B$7:$AK$7)))</f>
         <v/>
       </c>
       <c r="D7" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=D$4)*ISNUMBER(Marks!$B$7:$BC$7))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=D$4)*(Marks!$B$7:$BC$7=1))/SUMPRODUCT((Marks!$B$3:$BC$3=D$4)*ISNUMBER(Marks!$B$7:$BC$7)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=D$4)*ISNUMBER(Marks!$B$7:$AK$7))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=D$4)*(Marks!$B$7:$AK$7=1))/SUMPRODUCT((Marks!$B$3:$AK$3=D$4)*ISNUMBER(Marks!$B$7:$AK$7)))</f>
         <v/>
       </c>
       <c r="E7" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=E$4)*ISNUMBER(Marks!$B$7:$BC$7))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=E$4)*(Marks!$B$7:$BC$7=1))/SUMPRODUCT((Marks!$B$3:$BC$3=E$4)*ISNUMBER(Marks!$B$7:$BC$7)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=E$4)*ISNUMBER(Marks!$B$7:$AK$7))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=E$4)*(Marks!$B$7:$AK$7=1))/SUMPRODUCT((Marks!$B$3:$AK$3=E$4)*ISNUMBER(Marks!$B$7:$AK$7)))</f>
         <v/>
       </c>
     </row>
@@ -8840,19 +6428,19 @@
         <v>4</v>
       </c>
       <c r="B8" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=B$4)*ISNUMBER(Marks!$B$8:$BC$8))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=B$4)*(Marks!$B$8:$BC$8=1))/SUMPRODUCT((Marks!$B$3:$BC$3=B$4)*ISNUMBER(Marks!$B$8:$BC$8)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=B$4)*ISNUMBER(Marks!$B$8:$AK$8))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=B$4)*(Marks!$B$8:$AK$8=1))/SUMPRODUCT((Marks!$B$3:$AK$3=B$4)*ISNUMBER(Marks!$B$8:$AK$8)))</f>
         <v/>
       </c>
       <c r="C8" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=C$4)*ISNUMBER(Marks!$B$8:$BC$8))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=C$4)*(Marks!$B$8:$BC$8=1))/SUMPRODUCT((Marks!$B$3:$BC$3=C$4)*ISNUMBER(Marks!$B$8:$BC$8)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=C$4)*ISNUMBER(Marks!$B$8:$AK$8))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=C$4)*(Marks!$B$8:$AK$8=1))/SUMPRODUCT((Marks!$B$3:$AK$3=C$4)*ISNUMBER(Marks!$B$8:$AK$8)))</f>
         <v/>
       </c>
       <c r="D8" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=D$4)*ISNUMBER(Marks!$B$8:$BC$8))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=D$4)*(Marks!$B$8:$BC$8=1))/SUMPRODUCT((Marks!$B$3:$BC$3=D$4)*ISNUMBER(Marks!$B$8:$BC$8)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=D$4)*ISNUMBER(Marks!$B$8:$AK$8))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=D$4)*(Marks!$B$8:$AK$8=1))/SUMPRODUCT((Marks!$B$3:$AK$3=D$4)*ISNUMBER(Marks!$B$8:$AK$8)))</f>
         <v/>
       </c>
       <c r="E8" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=E$4)*ISNUMBER(Marks!$B$8:$BC$8))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=E$4)*(Marks!$B$8:$BC$8=1))/SUMPRODUCT((Marks!$B$3:$BC$3=E$4)*ISNUMBER(Marks!$B$8:$BC$8)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=E$4)*ISNUMBER(Marks!$B$8:$AK$8))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=E$4)*(Marks!$B$8:$AK$8=1))/SUMPRODUCT((Marks!$B$3:$AK$3=E$4)*ISNUMBER(Marks!$B$8:$AK$8)))</f>
         <v/>
       </c>
     </row>
@@ -8861,19 +6449,19 @@
         <v>5</v>
       </c>
       <c r="B9" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=B$4)*ISNUMBER(Marks!$B$9:$BC$9))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=B$4)*(Marks!$B$9:$BC$9=1))/SUMPRODUCT((Marks!$B$3:$BC$3=B$4)*ISNUMBER(Marks!$B$9:$BC$9)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=B$4)*ISNUMBER(Marks!$B$9:$AK$9))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=B$4)*(Marks!$B$9:$AK$9=1))/SUMPRODUCT((Marks!$B$3:$AK$3=B$4)*ISNUMBER(Marks!$B$9:$AK$9)))</f>
         <v/>
       </c>
       <c r="C9" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=C$4)*ISNUMBER(Marks!$B$9:$BC$9))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=C$4)*(Marks!$B$9:$BC$9=1))/SUMPRODUCT((Marks!$B$3:$BC$3=C$4)*ISNUMBER(Marks!$B$9:$BC$9)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=C$4)*ISNUMBER(Marks!$B$9:$AK$9))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=C$4)*(Marks!$B$9:$AK$9=1))/SUMPRODUCT((Marks!$B$3:$AK$3=C$4)*ISNUMBER(Marks!$B$9:$AK$9)))</f>
         <v/>
       </c>
       <c r="D9" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=D$4)*ISNUMBER(Marks!$B$9:$BC$9))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=D$4)*(Marks!$B$9:$BC$9=1))/SUMPRODUCT((Marks!$B$3:$BC$3=D$4)*ISNUMBER(Marks!$B$9:$BC$9)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=D$4)*ISNUMBER(Marks!$B$9:$AK$9))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=D$4)*(Marks!$B$9:$AK$9=1))/SUMPRODUCT((Marks!$B$3:$AK$3=D$4)*ISNUMBER(Marks!$B$9:$AK$9)))</f>
         <v/>
       </c>
       <c r="E9" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=E$4)*ISNUMBER(Marks!$B$9:$BC$9))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=E$4)*(Marks!$B$9:$BC$9=1))/SUMPRODUCT((Marks!$B$3:$BC$3=E$4)*ISNUMBER(Marks!$B$9:$BC$9)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=E$4)*ISNUMBER(Marks!$B$9:$AK$9))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=E$4)*(Marks!$B$9:$AK$9=1))/SUMPRODUCT((Marks!$B$3:$AK$3=E$4)*ISNUMBER(Marks!$B$9:$AK$9)))</f>
         <v/>
       </c>
     </row>
@@ -8882,19 +6470,19 @@
         <v>6</v>
       </c>
       <c r="B10" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=B$4)*ISNUMBER(Marks!$B$10:$BC$10))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=B$4)*(Marks!$B$10:$BC$10=1))/SUMPRODUCT((Marks!$B$3:$BC$3=B$4)*ISNUMBER(Marks!$B$10:$BC$10)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=B$4)*ISNUMBER(Marks!$B$10:$AK$10))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=B$4)*(Marks!$B$10:$AK$10=1))/SUMPRODUCT((Marks!$B$3:$AK$3=B$4)*ISNUMBER(Marks!$B$10:$AK$10)))</f>
         <v/>
       </c>
       <c r="C10" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=C$4)*ISNUMBER(Marks!$B$10:$BC$10))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=C$4)*(Marks!$B$10:$BC$10=1))/SUMPRODUCT((Marks!$B$3:$BC$3=C$4)*ISNUMBER(Marks!$B$10:$BC$10)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=C$4)*ISNUMBER(Marks!$B$10:$AK$10))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=C$4)*(Marks!$B$10:$AK$10=1))/SUMPRODUCT((Marks!$B$3:$AK$3=C$4)*ISNUMBER(Marks!$B$10:$AK$10)))</f>
         <v/>
       </c>
       <c r="D10" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=D$4)*ISNUMBER(Marks!$B$10:$BC$10))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=D$4)*(Marks!$B$10:$BC$10=1))/SUMPRODUCT((Marks!$B$3:$BC$3=D$4)*ISNUMBER(Marks!$B$10:$BC$10)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=D$4)*ISNUMBER(Marks!$B$10:$AK$10))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=D$4)*(Marks!$B$10:$AK$10=1))/SUMPRODUCT((Marks!$B$3:$AK$3=D$4)*ISNUMBER(Marks!$B$10:$AK$10)))</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=E$4)*ISNUMBER(Marks!$B$10:$BC$10))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=E$4)*(Marks!$B$10:$BC$10=1))/SUMPRODUCT((Marks!$B$3:$BC$3=E$4)*ISNUMBER(Marks!$B$10:$BC$10)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=E$4)*ISNUMBER(Marks!$B$10:$AK$10))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=E$4)*(Marks!$B$10:$AK$10=1))/SUMPRODUCT((Marks!$B$3:$AK$3=E$4)*ISNUMBER(Marks!$B$10:$AK$10)))</f>
         <v/>
       </c>
     </row>
@@ -8903,19 +6491,19 @@
         <v>7</v>
       </c>
       <c r="B11" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=B$4)*ISNUMBER(Marks!$B$11:$BC$11))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=B$4)*(Marks!$B$11:$BC$11=1))/SUMPRODUCT((Marks!$B$3:$BC$3=B$4)*ISNUMBER(Marks!$B$11:$BC$11)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=B$4)*ISNUMBER(Marks!$B$11:$AK$11))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=B$4)*(Marks!$B$11:$AK$11=1))/SUMPRODUCT((Marks!$B$3:$AK$3=B$4)*ISNUMBER(Marks!$B$11:$AK$11)))</f>
         <v/>
       </c>
       <c r="C11" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=C$4)*ISNUMBER(Marks!$B$11:$BC$11))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=C$4)*(Marks!$B$11:$BC$11=1))/SUMPRODUCT((Marks!$B$3:$BC$3=C$4)*ISNUMBER(Marks!$B$11:$BC$11)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=C$4)*ISNUMBER(Marks!$B$11:$AK$11))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=C$4)*(Marks!$B$11:$AK$11=1))/SUMPRODUCT((Marks!$B$3:$AK$3=C$4)*ISNUMBER(Marks!$B$11:$AK$11)))</f>
         <v/>
       </c>
       <c r="D11" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=D$4)*ISNUMBER(Marks!$B$11:$BC$11))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=D$4)*(Marks!$B$11:$BC$11=1))/SUMPRODUCT((Marks!$B$3:$BC$3=D$4)*ISNUMBER(Marks!$B$11:$BC$11)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=D$4)*ISNUMBER(Marks!$B$11:$AK$11))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=D$4)*(Marks!$B$11:$AK$11=1))/SUMPRODUCT((Marks!$B$3:$AK$3=D$4)*ISNUMBER(Marks!$B$11:$AK$11)))</f>
         <v/>
       </c>
       <c r="E11" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=E$4)*ISNUMBER(Marks!$B$11:$BC$11))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=E$4)*(Marks!$B$11:$BC$11=1))/SUMPRODUCT((Marks!$B$3:$BC$3=E$4)*ISNUMBER(Marks!$B$11:$BC$11)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=E$4)*ISNUMBER(Marks!$B$11:$AK$11))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=E$4)*(Marks!$B$11:$AK$11=1))/SUMPRODUCT((Marks!$B$3:$AK$3=E$4)*ISNUMBER(Marks!$B$11:$AK$11)))</f>
         <v/>
       </c>
     </row>
@@ -8924,19 +6512,19 @@
         <v>8</v>
       </c>
       <c r="B12" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=B$4)*ISNUMBER(Marks!$B$12:$BC$12))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=B$4)*(Marks!$B$12:$BC$12=1))/SUMPRODUCT((Marks!$B$3:$BC$3=B$4)*ISNUMBER(Marks!$B$12:$BC$12)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=B$4)*ISNUMBER(Marks!$B$12:$AK$12))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=B$4)*(Marks!$B$12:$AK$12=1))/SUMPRODUCT((Marks!$B$3:$AK$3=B$4)*ISNUMBER(Marks!$B$12:$AK$12)))</f>
         <v/>
       </c>
       <c r="C12" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=C$4)*ISNUMBER(Marks!$B$12:$BC$12))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=C$4)*(Marks!$B$12:$BC$12=1))/SUMPRODUCT((Marks!$B$3:$BC$3=C$4)*ISNUMBER(Marks!$B$12:$BC$12)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=C$4)*ISNUMBER(Marks!$B$12:$AK$12))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=C$4)*(Marks!$B$12:$AK$12=1))/SUMPRODUCT((Marks!$B$3:$AK$3=C$4)*ISNUMBER(Marks!$B$12:$AK$12)))</f>
         <v/>
       </c>
       <c r="D12" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=D$4)*ISNUMBER(Marks!$B$12:$BC$12))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=D$4)*(Marks!$B$12:$BC$12=1))/SUMPRODUCT((Marks!$B$3:$BC$3=D$4)*ISNUMBER(Marks!$B$12:$BC$12)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=D$4)*ISNUMBER(Marks!$B$12:$AK$12))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=D$4)*(Marks!$B$12:$AK$12=1))/SUMPRODUCT((Marks!$B$3:$AK$3=D$4)*ISNUMBER(Marks!$B$12:$AK$12)))</f>
         <v/>
       </c>
       <c r="E12" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=E$4)*ISNUMBER(Marks!$B$12:$BC$12))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=E$4)*(Marks!$B$12:$BC$12=1))/SUMPRODUCT((Marks!$B$3:$BC$3=E$4)*ISNUMBER(Marks!$B$12:$BC$12)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=E$4)*ISNUMBER(Marks!$B$12:$AK$12))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=E$4)*(Marks!$B$12:$AK$12=1))/SUMPRODUCT((Marks!$B$3:$AK$3=E$4)*ISNUMBER(Marks!$B$12:$AK$12)))</f>
         <v/>
       </c>
     </row>
@@ -8945,19 +6533,19 @@
         <v>9</v>
       </c>
       <c r="B13" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=B$4)*ISNUMBER(Marks!$B$13:$BC$13))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=B$4)*(Marks!$B$13:$BC$13=1))/SUMPRODUCT((Marks!$B$3:$BC$3=B$4)*ISNUMBER(Marks!$B$13:$BC$13)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=B$4)*ISNUMBER(Marks!$B$13:$AK$13))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=B$4)*(Marks!$B$13:$AK$13=1))/SUMPRODUCT((Marks!$B$3:$AK$3=B$4)*ISNUMBER(Marks!$B$13:$AK$13)))</f>
         <v/>
       </c>
       <c r="C13" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=C$4)*ISNUMBER(Marks!$B$13:$BC$13))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=C$4)*(Marks!$B$13:$BC$13=1))/SUMPRODUCT((Marks!$B$3:$BC$3=C$4)*ISNUMBER(Marks!$B$13:$BC$13)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=C$4)*ISNUMBER(Marks!$B$13:$AK$13))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=C$4)*(Marks!$B$13:$AK$13=1))/SUMPRODUCT((Marks!$B$3:$AK$3=C$4)*ISNUMBER(Marks!$B$13:$AK$13)))</f>
         <v/>
       </c>
       <c r="D13" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=D$4)*ISNUMBER(Marks!$B$13:$BC$13))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=D$4)*(Marks!$B$13:$BC$13=1))/SUMPRODUCT((Marks!$B$3:$BC$3=D$4)*ISNUMBER(Marks!$B$13:$BC$13)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=D$4)*ISNUMBER(Marks!$B$13:$AK$13))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=D$4)*(Marks!$B$13:$AK$13=1))/SUMPRODUCT((Marks!$B$3:$AK$3=D$4)*ISNUMBER(Marks!$B$13:$AK$13)))</f>
         <v/>
       </c>
       <c r="E13" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=E$4)*ISNUMBER(Marks!$B$13:$BC$13))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=E$4)*(Marks!$B$13:$BC$13=1))/SUMPRODUCT((Marks!$B$3:$BC$3=E$4)*ISNUMBER(Marks!$B$13:$BC$13)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=E$4)*ISNUMBER(Marks!$B$13:$AK$13))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=E$4)*(Marks!$B$13:$AK$13=1))/SUMPRODUCT((Marks!$B$3:$AK$3=E$4)*ISNUMBER(Marks!$B$13:$AK$13)))</f>
         <v/>
       </c>
     </row>
@@ -8966,19 +6554,19 @@
         <v>10</v>
       </c>
       <c r="B14" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=B$4)*ISNUMBER(Marks!$B$14:$BC$14))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=B$4)*(Marks!$B$14:$BC$14=1))/SUMPRODUCT((Marks!$B$3:$BC$3=B$4)*ISNUMBER(Marks!$B$14:$BC$14)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=B$4)*ISNUMBER(Marks!$B$14:$AK$14))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=B$4)*(Marks!$B$14:$AK$14=1))/SUMPRODUCT((Marks!$B$3:$AK$3=B$4)*ISNUMBER(Marks!$B$14:$AK$14)))</f>
         <v/>
       </c>
       <c r="C14" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=C$4)*ISNUMBER(Marks!$B$14:$BC$14))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=C$4)*(Marks!$B$14:$BC$14=1))/SUMPRODUCT((Marks!$B$3:$BC$3=C$4)*ISNUMBER(Marks!$B$14:$BC$14)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=C$4)*ISNUMBER(Marks!$B$14:$AK$14))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=C$4)*(Marks!$B$14:$AK$14=1))/SUMPRODUCT((Marks!$B$3:$AK$3=C$4)*ISNUMBER(Marks!$B$14:$AK$14)))</f>
         <v/>
       </c>
       <c r="D14" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=D$4)*ISNUMBER(Marks!$B$14:$BC$14))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=D$4)*(Marks!$B$14:$BC$14=1))/SUMPRODUCT((Marks!$B$3:$BC$3=D$4)*ISNUMBER(Marks!$B$14:$BC$14)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=D$4)*ISNUMBER(Marks!$B$14:$AK$14))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=D$4)*(Marks!$B$14:$AK$14=1))/SUMPRODUCT((Marks!$B$3:$AK$3=D$4)*ISNUMBER(Marks!$B$14:$AK$14)))</f>
         <v/>
       </c>
       <c r="E14" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=E$4)*ISNUMBER(Marks!$B$14:$BC$14))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=E$4)*(Marks!$B$14:$BC$14=1))/SUMPRODUCT((Marks!$B$3:$BC$3=E$4)*ISNUMBER(Marks!$B$14:$BC$14)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=E$4)*ISNUMBER(Marks!$B$14:$AK$14))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=E$4)*(Marks!$B$14:$AK$14=1))/SUMPRODUCT((Marks!$B$3:$AK$3=E$4)*ISNUMBER(Marks!$B$14:$AK$14)))</f>
         <v/>
       </c>
     </row>
@@ -8987,19 +6575,19 @@
         <v>11</v>
       </c>
       <c r="B15" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=B$4)*ISNUMBER(Marks!$B$15:$BC$15))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=B$4)*(Marks!$B$15:$BC$15=1))/SUMPRODUCT((Marks!$B$3:$BC$3=B$4)*ISNUMBER(Marks!$B$15:$BC$15)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=B$4)*ISNUMBER(Marks!$B$15:$AK$15))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=B$4)*(Marks!$B$15:$AK$15=1))/SUMPRODUCT((Marks!$B$3:$AK$3=B$4)*ISNUMBER(Marks!$B$15:$AK$15)))</f>
         <v/>
       </c>
       <c r="C15" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=C$4)*ISNUMBER(Marks!$B$15:$BC$15))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=C$4)*(Marks!$B$15:$BC$15=1))/SUMPRODUCT((Marks!$B$3:$BC$3=C$4)*ISNUMBER(Marks!$B$15:$BC$15)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=C$4)*ISNUMBER(Marks!$B$15:$AK$15))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=C$4)*(Marks!$B$15:$AK$15=1))/SUMPRODUCT((Marks!$B$3:$AK$3=C$4)*ISNUMBER(Marks!$B$15:$AK$15)))</f>
         <v/>
       </c>
       <c r="D15" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=D$4)*ISNUMBER(Marks!$B$15:$BC$15))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=D$4)*(Marks!$B$15:$BC$15=1))/SUMPRODUCT((Marks!$B$3:$BC$3=D$4)*ISNUMBER(Marks!$B$15:$BC$15)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=D$4)*ISNUMBER(Marks!$B$15:$AK$15))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=D$4)*(Marks!$B$15:$AK$15=1))/SUMPRODUCT((Marks!$B$3:$AK$3=D$4)*ISNUMBER(Marks!$B$15:$AK$15)))</f>
         <v/>
       </c>
       <c r="E15" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=E$4)*ISNUMBER(Marks!$B$15:$BC$15))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=E$4)*(Marks!$B$15:$BC$15=1))/SUMPRODUCT((Marks!$B$3:$BC$3=E$4)*ISNUMBER(Marks!$B$15:$BC$15)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=E$4)*ISNUMBER(Marks!$B$15:$AK$15))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=E$4)*(Marks!$B$15:$AK$15=1))/SUMPRODUCT((Marks!$B$3:$AK$3=E$4)*ISNUMBER(Marks!$B$15:$AK$15)))</f>
         <v/>
       </c>
     </row>
@@ -9008,19 +6596,19 @@
         <v>12</v>
       </c>
       <c r="B16" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=B$4)*ISNUMBER(Marks!$B$16:$BC$16))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=B$4)*(Marks!$B$16:$BC$16=1))/SUMPRODUCT((Marks!$B$3:$BC$3=B$4)*ISNUMBER(Marks!$B$16:$BC$16)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=B$4)*ISNUMBER(Marks!$B$16:$AK$16))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=B$4)*(Marks!$B$16:$AK$16=1))/SUMPRODUCT((Marks!$B$3:$AK$3=B$4)*ISNUMBER(Marks!$B$16:$AK$16)))</f>
         <v/>
       </c>
       <c r="C16" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=C$4)*ISNUMBER(Marks!$B$16:$BC$16))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=C$4)*(Marks!$B$16:$BC$16=1))/SUMPRODUCT((Marks!$B$3:$BC$3=C$4)*ISNUMBER(Marks!$B$16:$BC$16)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=C$4)*ISNUMBER(Marks!$B$16:$AK$16))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=C$4)*(Marks!$B$16:$AK$16=1))/SUMPRODUCT((Marks!$B$3:$AK$3=C$4)*ISNUMBER(Marks!$B$16:$AK$16)))</f>
         <v/>
       </c>
       <c r="D16" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=D$4)*ISNUMBER(Marks!$B$16:$BC$16))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=D$4)*(Marks!$B$16:$BC$16=1))/SUMPRODUCT((Marks!$B$3:$BC$3=D$4)*ISNUMBER(Marks!$B$16:$BC$16)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=D$4)*ISNUMBER(Marks!$B$16:$AK$16))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=D$4)*(Marks!$B$16:$AK$16=1))/SUMPRODUCT((Marks!$B$3:$AK$3=D$4)*ISNUMBER(Marks!$B$16:$AK$16)))</f>
         <v/>
       </c>
       <c r="E16" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=E$4)*ISNUMBER(Marks!$B$16:$BC$16))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=E$4)*(Marks!$B$16:$BC$16=1))/SUMPRODUCT((Marks!$B$3:$BC$3=E$4)*ISNUMBER(Marks!$B$16:$BC$16)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=E$4)*ISNUMBER(Marks!$B$16:$AK$16))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=E$4)*(Marks!$B$16:$AK$16=1))/SUMPRODUCT((Marks!$B$3:$AK$3=E$4)*ISNUMBER(Marks!$B$16:$AK$16)))</f>
         <v/>
       </c>
     </row>
@@ -9029,19 +6617,19 @@
         <v>13</v>
       </c>
       <c r="B17" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=B$4)*ISNUMBER(Marks!$B$17:$BC$17))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=B$4)*(Marks!$B$17:$BC$17=1))/SUMPRODUCT((Marks!$B$3:$BC$3=B$4)*ISNUMBER(Marks!$B$17:$BC$17)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=B$4)*ISNUMBER(Marks!$B$17:$AK$17))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=B$4)*(Marks!$B$17:$AK$17=1))/SUMPRODUCT((Marks!$B$3:$AK$3=B$4)*ISNUMBER(Marks!$B$17:$AK$17)))</f>
         <v/>
       </c>
       <c r="C17" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=C$4)*ISNUMBER(Marks!$B$17:$BC$17))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=C$4)*(Marks!$B$17:$BC$17=1))/SUMPRODUCT((Marks!$B$3:$BC$3=C$4)*ISNUMBER(Marks!$B$17:$BC$17)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=C$4)*ISNUMBER(Marks!$B$17:$AK$17))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=C$4)*(Marks!$B$17:$AK$17=1))/SUMPRODUCT((Marks!$B$3:$AK$3=C$4)*ISNUMBER(Marks!$B$17:$AK$17)))</f>
         <v/>
       </c>
       <c r="D17" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=D$4)*ISNUMBER(Marks!$B$17:$BC$17))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=D$4)*(Marks!$B$17:$BC$17=1))/SUMPRODUCT((Marks!$B$3:$BC$3=D$4)*ISNUMBER(Marks!$B$17:$BC$17)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=D$4)*ISNUMBER(Marks!$B$17:$AK$17))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=D$4)*(Marks!$B$17:$AK$17=1))/SUMPRODUCT((Marks!$B$3:$AK$3=D$4)*ISNUMBER(Marks!$B$17:$AK$17)))</f>
         <v/>
       </c>
       <c r="E17" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=E$4)*ISNUMBER(Marks!$B$17:$BC$17))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=E$4)*(Marks!$B$17:$BC$17=1))/SUMPRODUCT((Marks!$B$3:$BC$3=E$4)*ISNUMBER(Marks!$B$17:$BC$17)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=E$4)*ISNUMBER(Marks!$B$17:$AK$17))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=E$4)*(Marks!$B$17:$AK$17=1))/SUMPRODUCT((Marks!$B$3:$AK$3=E$4)*ISNUMBER(Marks!$B$17:$AK$17)))</f>
         <v/>
       </c>
     </row>
@@ -9050,19 +6638,19 @@
         <v>14</v>
       </c>
       <c r="B18" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=B$4)*ISNUMBER(Marks!$B$18:$BC$18))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=B$4)*(Marks!$B$18:$BC$18=1))/SUMPRODUCT((Marks!$B$3:$BC$3=B$4)*ISNUMBER(Marks!$B$18:$BC$18)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=B$4)*ISNUMBER(Marks!$B$18:$AK$18))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=B$4)*(Marks!$B$18:$AK$18=1))/SUMPRODUCT((Marks!$B$3:$AK$3=B$4)*ISNUMBER(Marks!$B$18:$AK$18)))</f>
         <v/>
       </c>
       <c r="C18" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=C$4)*ISNUMBER(Marks!$B$18:$BC$18))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=C$4)*(Marks!$B$18:$BC$18=1))/SUMPRODUCT((Marks!$B$3:$BC$3=C$4)*ISNUMBER(Marks!$B$18:$BC$18)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=C$4)*ISNUMBER(Marks!$B$18:$AK$18))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=C$4)*(Marks!$B$18:$AK$18=1))/SUMPRODUCT((Marks!$B$3:$AK$3=C$4)*ISNUMBER(Marks!$B$18:$AK$18)))</f>
         <v/>
       </c>
       <c r="D18" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=D$4)*ISNUMBER(Marks!$B$18:$BC$18))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=D$4)*(Marks!$B$18:$BC$18=1))/SUMPRODUCT((Marks!$B$3:$BC$3=D$4)*ISNUMBER(Marks!$B$18:$BC$18)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=D$4)*ISNUMBER(Marks!$B$18:$AK$18))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=D$4)*(Marks!$B$18:$AK$18=1))/SUMPRODUCT((Marks!$B$3:$AK$3=D$4)*ISNUMBER(Marks!$B$18:$AK$18)))</f>
         <v/>
       </c>
       <c r="E18" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=E$4)*ISNUMBER(Marks!$B$18:$BC$18))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=E$4)*(Marks!$B$18:$BC$18=1))/SUMPRODUCT((Marks!$B$3:$BC$3=E$4)*ISNUMBER(Marks!$B$18:$BC$18)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=E$4)*ISNUMBER(Marks!$B$18:$AK$18))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=E$4)*(Marks!$B$18:$AK$18=1))/SUMPRODUCT((Marks!$B$3:$AK$3=E$4)*ISNUMBER(Marks!$B$18:$AK$18)))</f>
         <v/>
       </c>
     </row>
@@ -9071,19 +6659,19 @@
         <v>15</v>
       </c>
       <c r="B19" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=B$4)*ISNUMBER(Marks!$B$19:$BC$19))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=B$4)*(Marks!$B$19:$BC$19=1))/SUMPRODUCT((Marks!$B$3:$BC$3=B$4)*ISNUMBER(Marks!$B$19:$BC$19)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=B$4)*ISNUMBER(Marks!$B$19:$AK$19))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=B$4)*(Marks!$B$19:$AK$19=1))/SUMPRODUCT((Marks!$B$3:$AK$3=B$4)*ISNUMBER(Marks!$B$19:$AK$19)))</f>
         <v/>
       </c>
       <c r="C19" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=C$4)*ISNUMBER(Marks!$B$19:$BC$19))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=C$4)*(Marks!$B$19:$BC$19=1))/SUMPRODUCT((Marks!$B$3:$BC$3=C$4)*ISNUMBER(Marks!$B$19:$BC$19)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=C$4)*ISNUMBER(Marks!$B$19:$AK$19))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=C$4)*(Marks!$B$19:$AK$19=1))/SUMPRODUCT((Marks!$B$3:$AK$3=C$4)*ISNUMBER(Marks!$B$19:$AK$19)))</f>
         <v/>
       </c>
       <c r="D19" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=D$4)*ISNUMBER(Marks!$B$19:$BC$19))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=D$4)*(Marks!$B$19:$BC$19=1))/SUMPRODUCT((Marks!$B$3:$BC$3=D$4)*ISNUMBER(Marks!$B$19:$BC$19)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=D$4)*ISNUMBER(Marks!$B$19:$AK$19))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=D$4)*(Marks!$B$19:$AK$19=1))/SUMPRODUCT((Marks!$B$3:$AK$3=D$4)*ISNUMBER(Marks!$B$19:$AK$19)))</f>
         <v/>
       </c>
       <c r="E19" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=E$4)*ISNUMBER(Marks!$B$19:$BC$19))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=E$4)*(Marks!$B$19:$BC$19=1))/SUMPRODUCT((Marks!$B$3:$BC$3=E$4)*ISNUMBER(Marks!$B$19:$BC$19)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=E$4)*ISNUMBER(Marks!$B$19:$AK$19))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=E$4)*(Marks!$B$19:$AK$19=1))/SUMPRODUCT((Marks!$B$3:$AK$3=E$4)*ISNUMBER(Marks!$B$19:$AK$19)))</f>
         <v/>
       </c>
     </row>
@@ -9092,19 +6680,19 @@
         <v>16</v>
       </c>
       <c r="B20" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=B$4)*ISNUMBER(Marks!$B$20:$BC$20))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=B$4)*(Marks!$B$20:$BC$20=1))/SUMPRODUCT((Marks!$B$3:$BC$3=B$4)*ISNUMBER(Marks!$B$20:$BC$20)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=B$4)*ISNUMBER(Marks!$B$20:$AK$20))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=B$4)*(Marks!$B$20:$AK$20=1))/SUMPRODUCT((Marks!$B$3:$AK$3=B$4)*ISNUMBER(Marks!$B$20:$AK$20)))</f>
         <v/>
       </c>
       <c r="C20" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=C$4)*ISNUMBER(Marks!$B$20:$BC$20))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=C$4)*(Marks!$B$20:$BC$20=1))/SUMPRODUCT((Marks!$B$3:$BC$3=C$4)*ISNUMBER(Marks!$B$20:$BC$20)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=C$4)*ISNUMBER(Marks!$B$20:$AK$20))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=C$4)*(Marks!$B$20:$AK$20=1))/SUMPRODUCT((Marks!$B$3:$AK$3=C$4)*ISNUMBER(Marks!$B$20:$AK$20)))</f>
         <v/>
       </c>
       <c r="D20" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=D$4)*ISNUMBER(Marks!$B$20:$BC$20))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=D$4)*(Marks!$B$20:$BC$20=1))/SUMPRODUCT((Marks!$B$3:$BC$3=D$4)*ISNUMBER(Marks!$B$20:$BC$20)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=D$4)*ISNUMBER(Marks!$B$20:$AK$20))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=D$4)*(Marks!$B$20:$AK$20=1))/SUMPRODUCT((Marks!$B$3:$AK$3=D$4)*ISNUMBER(Marks!$B$20:$AK$20)))</f>
         <v/>
       </c>
       <c r="E20" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=E$4)*ISNUMBER(Marks!$B$20:$BC$20))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=E$4)*(Marks!$B$20:$BC$20=1))/SUMPRODUCT((Marks!$B$3:$BC$3=E$4)*ISNUMBER(Marks!$B$20:$BC$20)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=E$4)*ISNUMBER(Marks!$B$20:$AK$20))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=E$4)*(Marks!$B$20:$AK$20=1))/SUMPRODUCT((Marks!$B$3:$AK$3=E$4)*ISNUMBER(Marks!$B$20:$AK$20)))</f>
         <v/>
       </c>
     </row>
@@ -9113,19 +6701,19 @@
         <v>17</v>
       </c>
       <c r="B21" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=B$4)*ISNUMBER(Marks!$B$21:$BC$21))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=B$4)*(Marks!$B$21:$BC$21=1))/SUMPRODUCT((Marks!$B$3:$BC$3=B$4)*ISNUMBER(Marks!$B$21:$BC$21)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=B$4)*ISNUMBER(Marks!$B$21:$AK$21))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=B$4)*(Marks!$B$21:$AK$21=1))/SUMPRODUCT((Marks!$B$3:$AK$3=B$4)*ISNUMBER(Marks!$B$21:$AK$21)))</f>
         <v/>
       </c>
       <c r="C21" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=C$4)*ISNUMBER(Marks!$B$21:$BC$21))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=C$4)*(Marks!$B$21:$BC$21=1))/SUMPRODUCT((Marks!$B$3:$BC$3=C$4)*ISNUMBER(Marks!$B$21:$BC$21)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=C$4)*ISNUMBER(Marks!$B$21:$AK$21))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=C$4)*(Marks!$B$21:$AK$21=1))/SUMPRODUCT((Marks!$B$3:$AK$3=C$4)*ISNUMBER(Marks!$B$21:$AK$21)))</f>
         <v/>
       </c>
       <c r="D21" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=D$4)*ISNUMBER(Marks!$B$21:$BC$21))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=D$4)*(Marks!$B$21:$BC$21=1))/SUMPRODUCT((Marks!$B$3:$BC$3=D$4)*ISNUMBER(Marks!$B$21:$BC$21)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=D$4)*ISNUMBER(Marks!$B$21:$AK$21))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=D$4)*(Marks!$B$21:$AK$21=1))/SUMPRODUCT((Marks!$B$3:$AK$3=D$4)*ISNUMBER(Marks!$B$21:$AK$21)))</f>
         <v/>
       </c>
       <c r="E21" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=E$4)*ISNUMBER(Marks!$B$21:$BC$21))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=E$4)*(Marks!$B$21:$BC$21=1))/SUMPRODUCT((Marks!$B$3:$BC$3=E$4)*ISNUMBER(Marks!$B$21:$BC$21)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=E$4)*ISNUMBER(Marks!$B$21:$AK$21))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=E$4)*(Marks!$B$21:$AK$21=1))/SUMPRODUCT((Marks!$B$3:$AK$3=E$4)*ISNUMBER(Marks!$B$21:$AK$21)))</f>
         <v/>
       </c>
     </row>
@@ -9134,19 +6722,19 @@
         <v>18</v>
       </c>
       <c r="B22" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=B$4)*ISNUMBER(Marks!$B$22:$BC$22))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=B$4)*(Marks!$B$22:$BC$22=1))/SUMPRODUCT((Marks!$B$3:$BC$3=B$4)*ISNUMBER(Marks!$B$22:$BC$22)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=B$4)*ISNUMBER(Marks!$B$22:$AK$22))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=B$4)*(Marks!$B$22:$AK$22=1))/SUMPRODUCT((Marks!$B$3:$AK$3=B$4)*ISNUMBER(Marks!$B$22:$AK$22)))</f>
         <v/>
       </c>
       <c r="C22" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=C$4)*ISNUMBER(Marks!$B$22:$BC$22))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=C$4)*(Marks!$B$22:$BC$22=1))/SUMPRODUCT((Marks!$B$3:$BC$3=C$4)*ISNUMBER(Marks!$B$22:$BC$22)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=C$4)*ISNUMBER(Marks!$B$22:$AK$22))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=C$4)*(Marks!$B$22:$AK$22=1))/SUMPRODUCT((Marks!$B$3:$AK$3=C$4)*ISNUMBER(Marks!$B$22:$AK$22)))</f>
         <v/>
       </c>
       <c r="D22" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=D$4)*ISNUMBER(Marks!$B$22:$BC$22))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=D$4)*(Marks!$B$22:$BC$22=1))/SUMPRODUCT((Marks!$B$3:$BC$3=D$4)*ISNUMBER(Marks!$B$22:$BC$22)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=D$4)*ISNUMBER(Marks!$B$22:$AK$22))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=D$4)*(Marks!$B$22:$AK$22=1))/SUMPRODUCT((Marks!$B$3:$AK$3=D$4)*ISNUMBER(Marks!$B$22:$AK$22)))</f>
         <v/>
       </c>
       <c r="E22" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=E$4)*ISNUMBER(Marks!$B$22:$BC$22))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=E$4)*(Marks!$B$22:$BC$22=1))/SUMPRODUCT((Marks!$B$3:$BC$3=E$4)*ISNUMBER(Marks!$B$22:$BC$22)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=E$4)*ISNUMBER(Marks!$B$22:$AK$22))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=E$4)*(Marks!$B$22:$AK$22=1))/SUMPRODUCT((Marks!$B$3:$AK$3=E$4)*ISNUMBER(Marks!$B$22:$AK$22)))</f>
         <v/>
       </c>
     </row>
@@ -9155,19 +6743,19 @@
         <v>19</v>
       </c>
       <c r="B23" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=B$4)*ISNUMBER(Marks!$B$23:$BC$23))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=B$4)*(Marks!$B$23:$BC$23=1))/SUMPRODUCT((Marks!$B$3:$BC$3=B$4)*ISNUMBER(Marks!$B$23:$BC$23)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=B$4)*ISNUMBER(Marks!$B$23:$AK$23))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=B$4)*(Marks!$B$23:$AK$23=1))/SUMPRODUCT((Marks!$B$3:$AK$3=B$4)*ISNUMBER(Marks!$B$23:$AK$23)))</f>
         <v/>
       </c>
       <c r="C23" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=C$4)*ISNUMBER(Marks!$B$23:$BC$23))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=C$4)*(Marks!$B$23:$BC$23=1))/SUMPRODUCT((Marks!$B$3:$BC$3=C$4)*ISNUMBER(Marks!$B$23:$BC$23)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=C$4)*ISNUMBER(Marks!$B$23:$AK$23))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=C$4)*(Marks!$B$23:$AK$23=1))/SUMPRODUCT((Marks!$B$3:$AK$3=C$4)*ISNUMBER(Marks!$B$23:$AK$23)))</f>
         <v/>
       </c>
       <c r="D23" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=D$4)*ISNUMBER(Marks!$B$23:$BC$23))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=D$4)*(Marks!$B$23:$BC$23=1))/SUMPRODUCT((Marks!$B$3:$BC$3=D$4)*ISNUMBER(Marks!$B$23:$BC$23)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=D$4)*ISNUMBER(Marks!$B$23:$AK$23))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=D$4)*(Marks!$B$23:$AK$23=1))/SUMPRODUCT((Marks!$B$3:$AK$3=D$4)*ISNUMBER(Marks!$B$23:$AK$23)))</f>
         <v/>
       </c>
       <c r="E23" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=E$4)*ISNUMBER(Marks!$B$23:$BC$23))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=E$4)*(Marks!$B$23:$BC$23=1))/SUMPRODUCT((Marks!$B$3:$BC$3=E$4)*ISNUMBER(Marks!$B$23:$BC$23)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=E$4)*ISNUMBER(Marks!$B$23:$AK$23))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=E$4)*(Marks!$B$23:$AK$23=1))/SUMPRODUCT((Marks!$B$3:$AK$3=E$4)*ISNUMBER(Marks!$B$23:$AK$23)))</f>
         <v/>
       </c>
     </row>
@@ -9176,19 +6764,19 @@
         <v>20</v>
       </c>
       <c r="B24" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=B$4)*ISNUMBER(Marks!$B$24:$BC$24))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=B$4)*(Marks!$B$24:$BC$24=1))/SUMPRODUCT((Marks!$B$3:$BC$3=B$4)*ISNUMBER(Marks!$B$24:$BC$24)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=B$4)*ISNUMBER(Marks!$B$24:$AK$24))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=B$4)*(Marks!$B$24:$AK$24=1))/SUMPRODUCT((Marks!$B$3:$AK$3=B$4)*ISNUMBER(Marks!$B$24:$AK$24)))</f>
         <v/>
       </c>
       <c r="C24" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=C$4)*ISNUMBER(Marks!$B$24:$BC$24))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=C$4)*(Marks!$B$24:$BC$24=1))/SUMPRODUCT((Marks!$B$3:$BC$3=C$4)*ISNUMBER(Marks!$B$24:$BC$24)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=C$4)*ISNUMBER(Marks!$B$24:$AK$24))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=C$4)*(Marks!$B$24:$AK$24=1))/SUMPRODUCT((Marks!$B$3:$AK$3=C$4)*ISNUMBER(Marks!$B$24:$AK$24)))</f>
         <v/>
       </c>
       <c r="D24" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=D$4)*ISNUMBER(Marks!$B$24:$BC$24))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=D$4)*(Marks!$B$24:$BC$24=1))/SUMPRODUCT((Marks!$B$3:$BC$3=D$4)*ISNUMBER(Marks!$B$24:$BC$24)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=D$4)*ISNUMBER(Marks!$B$24:$AK$24))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=D$4)*(Marks!$B$24:$AK$24=1))/SUMPRODUCT((Marks!$B$3:$AK$3=D$4)*ISNUMBER(Marks!$B$24:$AK$24)))</f>
         <v/>
       </c>
       <c r="E24" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=E$4)*ISNUMBER(Marks!$B$24:$BC$24))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=E$4)*(Marks!$B$24:$BC$24=1))/SUMPRODUCT((Marks!$B$3:$BC$3=E$4)*ISNUMBER(Marks!$B$24:$BC$24)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=E$4)*ISNUMBER(Marks!$B$24:$AK$24))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=E$4)*(Marks!$B$24:$AK$24=1))/SUMPRODUCT((Marks!$B$3:$AK$3=E$4)*ISNUMBER(Marks!$B$24:$AK$24)))</f>
         <v/>
       </c>
     </row>
@@ -9197,19 +6785,19 @@
         <v>21</v>
       </c>
       <c r="B25" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=B$4)*ISNUMBER(Marks!$B$25:$BC$25))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=B$4)*(Marks!$B$25:$BC$25=1))/SUMPRODUCT((Marks!$B$3:$BC$3=B$4)*ISNUMBER(Marks!$B$25:$BC$25)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=B$4)*ISNUMBER(Marks!$B$25:$AK$25))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=B$4)*(Marks!$B$25:$AK$25=1))/SUMPRODUCT((Marks!$B$3:$AK$3=B$4)*ISNUMBER(Marks!$B$25:$AK$25)))</f>
         <v/>
       </c>
       <c r="C25" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=C$4)*ISNUMBER(Marks!$B$25:$BC$25))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=C$4)*(Marks!$B$25:$BC$25=1))/SUMPRODUCT((Marks!$B$3:$BC$3=C$4)*ISNUMBER(Marks!$B$25:$BC$25)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=C$4)*ISNUMBER(Marks!$B$25:$AK$25))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=C$4)*(Marks!$B$25:$AK$25=1))/SUMPRODUCT((Marks!$B$3:$AK$3=C$4)*ISNUMBER(Marks!$B$25:$AK$25)))</f>
         <v/>
       </c>
       <c r="D25" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=D$4)*ISNUMBER(Marks!$B$25:$BC$25))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=D$4)*(Marks!$B$25:$BC$25=1))/SUMPRODUCT((Marks!$B$3:$BC$3=D$4)*ISNUMBER(Marks!$B$25:$BC$25)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=D$4)*ISNUMBER(Marks!$B$25:$AK$25))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=D$4)*(Marks!$B$25:$AK$25=1))/SUMPRODUCT((Marks!$B$3:$AK$3=D$4)*ISNUMBER(Marks!$B$25:$AK$25)))</f>
         <v/>
       </c>
       <c r="E25" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=E$4)*ISNUMBER(Marks!$B$25:$BC$25))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=E$4)*(Marks!$B$25:$BC$25=1))/SUMPRODUCT((Marks!$B$3:$BC$3=E$4)*ISNUMBER(Marks!$B$25:$BC$25)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=E$4)*ISNUMBER(Marks!$B$25:$AK$25))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=E$4)*(Marks!$B$25:$AK$25=1))/SUMPRODUCT((Marks!$B$3:$AK$3=E$4)*ISNUMBER(Marks!$B$25:$AK$25)))</f>
         <v/>
       </c>
     </row>
@@ -9218,19 +6806,19 @@
         <v>22</v>
       </c>
       <c r="B26" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=B$4)*ISNUMBER(Marks!$B$26:$BC$26))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=B$4)*(Marks!$B$26:$BC$26=1))/SUMPRODUCT((Marks!$B$3:$BC$3=B$4)*ISNUMBER(Marks!$B$26:$BC$26)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=B$4)*ISNUMBER(Marks!$B$26:$AK$26))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=B$4)*(Marks!$B$26:$AK$26=1))/SUMPRODUCT((Marks!$B$3:$AK$3=B$4)*ISNUMBER(Marks!$B$26:$AK$26)))</f>
         <v/>
       </c>
       <c r="C26" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=C$4)*ISNUMBER(Marks!$B$26:$BC$26))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=C$4)*(Marks!$B$26:$BC$26=1))/SUMPRODUCT((Marks!$B$3:$BC$3=C$4)*ISNUMBER(Marks!$B$26:$BC$26)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=C$4)*ISNUMBER(Marks!$B$26:$AK$26))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=C$4)*(Marks!$B$26:$AK$26=1))/SUMPRODUCT((Marks!$B$3:$AK$3=C$4)*ISNUMBER(Marks!$B$26:$AK$26)))</f>
         <v/>
       </c>
       <c r="D26" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=D$4)*ISNUMBER(Marks!$B$26:$BC$26))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=D$4)*(Marks!$B$26:$BC$26=1))/SUMPRODUCT((Marks!$B$3:$BC$3=D$4)*ISNUMBER(Marks!$B$26:$BC$26)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=D$4)*ISNUMBER(Marks!$B$26:$AK$26))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=D$4)*(Marks!$B$26:$AK$26=1))/SUMPRODUCT((Marks!$B$3:$AK$3=D$4)*ISNUMBER(Marks!$B$26:$AK$26)))</f>
         <v/>
       </c>
       <c r="E26" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=E$4)*ISNUMBER(Marks!$B$26:$BC$26))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=E$4)*(Marks!$B$26:$BC$26=1))/SUMPRODUCT((Marks!$B$3:$BC$3=E$4)*ISNUMBER(Marks!$B$26:$BC$26)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=E$4)*ISNUMBER(Marks!$B$26:$AK$26))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=E$4)*(Marks!$B$26:$AK$26=1))/SUMPRODUCT((Marks!$B$3:$AK$3=E$4)*ISNUMBER(Marks!$B$26:$AK$26)))</f>
         <v/>
       </c>
     </row>
@@ -9239,19 +6827,19 @@
         <v>23</v>
       </c>
       <c r="B27" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=B$4)*ISNUMBER(Marks!$B$27:$BC$27))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=B$4)*(Marks!$B$27:$BC$27=1))/SUMPRODUCT((Marks!$B$3:$BC$3=B$4)*ISNUMBER(Marks!$B$27:$BC$27)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=B$4)*ISNUMBER(Marks!$B$27:$AK$27))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=B$4)*(Marks!$B$27:$AK$27=1))/SUMPRODUCT((Marks!$B$3:$AK$3=B$4)*ISNUMBER(Marks!$B$27:$AK$27)))</f>
         <v/>
       </c>
       <c r="C27" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=C$4)*ISNUMBER(Marks!$B$27:$BC$27))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=C$4)*(Marks!$B$27:$BC$27=1))/SUMPRODUCT((Marks!$B$3:$BC$3=C$4)*ISNUMBER(Marks!$B$27:$BC$27)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=C$4)*ISNUMBER(Marks!$B$27:$AK$27))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=C$4)*(Marks!$B$27:$AK$27=1))/SUMPRODUCT((Marks!$B$3:$AK$3=C$4)*ISNUMBER(Marks!$B$27:$AK$27)))</f>
         <v/>
       </c>
       <c r="D27" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=D$4)*ISNUMBER(Marks!$B$27:$BC$27))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=D$4)*(Marks!$B$27:$BC$27=1))/SUMPRODUCT((Marks!$B$3:$BC$3=D$4)*ISNUMBER(Marks!$B$27:$BC$27)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=D$4)*ISNUMBER(Marks!$B$27:$AK$27))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=D$4)*(Marks!$B$27:$AK$27=1))/SUMPRODUCT((Marks!$B$3:$AK$3=D$4)*ISNUMBER(Marks!$B$27:$AK$27)))</f>
         <v/>
       </c>
       <c r="E27" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=E$4)*ISNUMBER(Marks!$B$27:$BC$27))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=E$4)*(Marks!$B$27:$BC$27=1))/SUMPRODUCT((Marks!$B$3:$BC$3=E$4)*ISNUMBER(Marks!$B$27:$BC$27)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=E$4)*ISNUMBER(Marks!$B$27:$AK$27))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=E$4)*(Marks!$B$27:$AK$27=1))/SUMPRODUCT((Marks!$B$3:$AK$3=E$4)*ISNUMBER(Marks!$B$27:$AK$27)))</f>
         <v/>
       </c>
     </row>
@@ -9260,19 +6848,19 @@
         <v>24</v>
       </c>
       <c r="B28" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=B$4)*ISNUMBER(Marks!$B$28:$BC$28))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=B$4)*(Marks!$B$28:$BC$28=1))/SUMPRODUCT((Marks!$B$3:$BC$3=B$4)*ISNUMBER(Marks!$B$28:$BC$28)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=B$4)*ISNUMBER(Marks!$B$28:$AK$28))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=B$4)*(Marks!$B$28:$AK$28=1))/SUMPRODUCT((Marks!$B$3:$AK$3=B$4)*ISNUMBER(Marks!$B$28:$AK$28)))</f>
         <v/>
       </c>
       <c r="C28" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=C$4)*ISNUMBER(Marks!$B$28:$BC$28))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=C$4)*(Marks!$B$28:$BC$28=1))/SUMPRODUCT((Marks!$B$3:$BC$3=C$4)*ISNUMBER(Marks!$B$28:$BC$28)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=C$4)*ISNUMBER(Marks!$B$28:$AK$28))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=C$4)*(Marks!$B$28:$AK$28=1))/SUMPRODUCT((Marks!$B$3:$AK$3=C$4)*ISNUMBER(Marks!$B$28:$AK$28)))</f>
         <v/>
       </c>
       <c r="D28" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=D$4)*ISNUMBER(Marks!$B$28:$BC$28))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=D$4)*(Marks!$B$28:$BC$28=1))/SUMPRODUCT((Marks!$B$3:$BC$3=D$4)*ISNUMBER(Marks!$B$28:$BC$28)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=D$4)*ISNUMBER(Marks!$B$28:$AK$28))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=D$4)*(Marks!$B$28:$AK$28=1))/SUMPRODUCT((Marks!$B$3:$AK$3=D$4)*ISNUMBER(Marks!$B$28:$AK$28)))</f>
         <v/>
       </c>
       <c r="E28" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=E$4)*ISNUMBER(Marks!$B$28:$BC$28))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=E$4)*(Marks!$B$28:$BC$28=1))/SUMPRODUCT((Marks!$B$3:$BC$3=E$4)*ISNUMBER(Marks!$B$28:$BC$28)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=E$4)*ISNUMBER(Marks!$B$28:$AK$28))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=E$4)*(Marks!$B$28:$AK$28=1))/SUMPRODUCT((Marks!$B$3:$AK$3=E$4)*ISNUMBER(Marks!$B$28:$AK$28)))</f>
         <v/>
       </c>
     </row>
@@ -9281,19 +6869,19 @@
         <v>25</v>
       </c>
       <c r="B29" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=B$4)*ISNUMBER(Marks!$B$29:$BC$29))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=B$4)*(Marks!$B$29:$BC$29=1))/SUMPRODUCT((Marks!$B$3:$BC$3=B$4)*ISNUMBER(Marks!$B$29:$BC$29)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=B$4)*ISNUMBER(Marks!$B$29:$AK$29))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=B$4)*(Marks!$B$29:$AK$29=1))/SUMPRODUCT((Marks!$B$3:$AK$3=B$4)*ISNUMBER(Marks!$B$29:$AK$29)))</f>
         <v/>
       </c>
       <c r="C29" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=C$4)*ISNUMBER(Marks!$B$29:$BC$29))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=C$4)*(Marks!$B$29:$BC$29=1))/SUMPRODUCT((Marks!$B$3:$BC$3=C$4)*ISNUMBER(Marks!$B$29:$BC$29)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=C$4)*ISNUMBER(Marks!$B$29:$AK$29))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=C$4)*(Marks!$B$29:$AK$29=1))/SUMPRODUCT((Marks!$B$3:$AK$3=C$4)*ISNUMBER(Marks!$B$29:$AK$29)))</f>
         <v/>
       </c>
       <c r="D29" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=D$4)*ISNUMBER(Marks!$B$29:$BC$29))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=D$4)*(Marks!$B$29:$BC$29=1))/SUMPRODUCT((Marks!$B$3:$BC$3=D$4)*ISNUMBER(Marks!$B$29:$BC$29)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=D$4)*ISNUMBER(Marks!$B$29:$AK$29))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=D$4)*(Marks!$B$29:$AK$29=1))/SUMPRODUCT((Marks!$B$3:$AK$3=D$4)*ISNUMBER(Marks!$B$29:$AK$29)))</f>
         <v/>
       </c>
       <c r="E29" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=E$4)*ISNUMBER(Marks!$B$29:$BC$29))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=E$4)*(Marks!$B$29:$BC$29=1))/SUMPRODUCT((Marks!$B$3:$BC$3=E$4)*ISNUMBER(Marks!$B$29:$BC$29)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=E$4)*ISNUMBER(Marks!$B$29:$AK$29))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=E$4)*(Marks!$B$29:$AK$29=1))/SUMPRODUCT((Marks!$B$3:$AK$3=E$4)*ISNUMBER(Marks!$B$29:$AK$29)))</f>
         <v/>
       </c>
     </row>
@@ -9302,19 +6890,19 @@
         <v>26</v>
       </c>
       <c r="B30" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=B$4)*ISNUMBER(Marks!$B$30:$BC$30))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=B$4)*(Marks!$B$30:$BC$30=1))/SUMPRODUCT((Marks!$B$3:$BC$3=B$4)*ISNUMBER(Marks!$B$30:$BC$30)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=B$4)*ISNUMBER(Marks!$B$30:$AK$30))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=B$4)*(Marks!$B$30:$AK$30=1))/SUMPRODUCT((Marks!$B$3:$AK$3=B$4)*ISNUMBER(Marks!$B$30:$AK$30)))</f>
         <v/>
       </c>
       <c r="C30" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=C$4)*ISNUMBER(Marks!$B$30:$BC$30))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=C$4)*(Marks!$B$30:$BC$30=1))/SUMPRODUCT((Marks!$B$3:$BC$3=C$4)*ISNUMBER(Marks!$B$30:$BC$30)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=C$4)*ISNUMBER(Marks!$B$30:$AK$30))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=C$4)*(Marks!$B$30:$AK$30=1))/SUMPRODUCT((Marks!$B$3:$AK$3=C$4)*ISNUMBER(Marks!$B$30:$AK$30)))</f>
         <v/>
       </c>
       <c r="D30" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=D$4)*ISNUMBER(Marks!$B$30:$BC$30))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=D$4)*(Marks!$B$30:$BC$30=1))/SUMPRODUCT((Marks!$B$3:$BC$3=D$4)*ISNUMBER(Marks!$B$30:$BC$30)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=D$4)*ISNUMBER(Marks!$B$30:$AK$30))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=D$4)*(Marks!$B$30:$AK$30=1))/SUMPRODUCT((Marks!$B$3:$AK$3=D$4)*ISNUMBER(Marks!$B$30:$AK$30)))</f>
         <v/>
       </c>
       <c r="E30" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=E$4)*ISNUMBER(Marks!$B$30:$BC$30))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=E$4)*(Marks!$B$30:$BC$30=1))/SUMPRODUCT((Marks!$B$3:$BC$3=E$4)*ISNUMBER(Marks!$B$30:$BC$30)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=E$4)*ISNUMBER(Marks!$B$30:$AK$30))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=E$4)*(Marks!$B$30:$AK$30=1))/SUMPRODUCT((Marks!$B$3:$AK$3=E$4)*ISNUMBER(Marks!$B$30:$AK$30)))</f>
         <v/>
       </c>
     </row>
@@ -9323,19 +6911,19 @@
         <v>27</v>
       </c>
       <c r="B31" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=B$4)*ISNUMBER(Marks!$B$31:$BC$31))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=B$4)*(Marks!$B$31:$BC$31=1))/SUMPRODUCT((Marks!$B$3:$BC$3=B$4)*ISNUMBER(Marks!$B$31:$BC$31)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=B$4)*ISNUMBER(Marks!$B$31:$AK$31))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=B$4)*(Marks!$B$31:$AK$31=1))/SUMPRODUCT((Marks!$B$3:$AK$3=B$4)*ISNUMBER(Marks!$B$31:$AK$31)))</f>
         <v/>
       </c>
       <c r="C31" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=C$4)*ISNUMBER(Marks!$B$31:$BC$31))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=C$4)*(Marks!$B$31:$BC$31=1))/SUMPRODUCT((Marks!$B$3:$BC$3=C$4)*ISNUMBER(Marks!$B$31:$BC$31)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=C$4)*ISNUMBER(Marks!$B$31:$AK$31))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=C$4)*(Marks!$B$31:$AK$31=1))/SUMPRODUCT((Marks!$B$3:$AK$3=C$4)*ISNUMBER(Marks!$B$31:$AK$31)))</f>
         <v/>
       </c>
       <c r="D31" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=D$4)*ISNUMBER(Marks!$B$31:$BC$31))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=D$4)*(Marks!$B$31:$BC$31=1))/SUMPRODUCT((Marks!$B$3:$BC$3=D$4)*ISNUMBER(Marks!$B$31:$BC$31)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=D$4)*ISNUMBER(Marks!$B$31:$AK$31))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=D$4)*(Marks!$B$31:$AK$31=1))/SUMPRODUCT((Marks!$B$3:$AK$3=D$4)*ISNUMBER(Marks!$B$31:$AK$31)))</f>
         <v/>
       </c>
       <c r="E31" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=E$4)*ISNUMBER(Marks!$B$31:$BC$31))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=E$4)*(Marks!$B$31:$BC$31=1))/SUMPRODUCT((Marks!$B$3:$BC$3=E$4)*ISNUMBER(Marks!$B$31:$BC$31)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=E$4)*ISNUMBER(Marks!$B$31:$AK$31))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=E$4)*(Marks!$B$31:$AK$31=1))/SUMPRODUCT((Marks!$B$3:$AK$3=E$4)*ISNUMBER(Marks!$B$31:$AK$31)))</f>
         <v/>
       </c>
     </row>
@@ -9344,19 +6932,19 @@
         <v>28</v>
       </c>
       <c r="B32" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=B$4)*ISNUMBER(Marks!$B$32:$BC$32))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=B$4)*(Marks!$B$32:$BC$32=1))/SUMPRODUCT((Marks!$B$3:$BC$3=B$4)*ISNUMBER(Marks!$B$32:$BC$32)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=B$4)*ISNUMBER(Marks!$B$32:$AK$32))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=B$4)*(Marks!$B$32:$AK$32=1))/SUMPRODUCT((Marks!$B$3:$AK$3=B$4)*ISNUMBER(Marks!$B$32:$AK$32)))</f>
         <v/>
       </c>
       <c r="C32" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=C$4)*ISNUMBER(Marks!$B$32:$BC$32))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=C$4)*(Marks!$B$32:$BC$32=1))/SUMPRODUCT((Marks!$B$3:$BC$3=C$4)*ISNUMBER(Marks!$B$32:$BC$32)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=C$4)*ISNUMBER(Marks!$B$32:$AK$32))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=C$4)*(Marks!$B$32:$AK$32=1))/SUMPRODUCT((Marks!$B$3:$AK$3=C$4)*ISNUMBER(Marks!$B$32:$AK$32)))</f>
         <v/>
       </c>
       <c r="D32" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=D$4)*ISNUMBER(Marks!$B$32:$BC$32))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=D$4)*(Marks!$B$32:$BC$32=1))/SUMPRODUCT((Marks!$B$3:$BC$3=D$4)*ISNUMBER(Marks!$B$32:$BC$32)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=D$4)*ISNUMBER(Marks!$B$32:$AK$32))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=D$4)*(Marks!$B$32:$AK$32=1))/SUMPRODUCT((Marks!$B$3:$AK$3=D$4)*ISNUMBER(Marks!$B$32:$AK$32)))</f>
         <v/>
       </c>
       <c r="E32" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=E$4)*ISNUMBER(Marks!$B$32:$BC$32))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=E$4)*(Marks!$B$32:$BC$32=1))/SUMPRODUCT((Marks!$B$3:$BC$3=E$4)*ISNUMBER(Marks!$B$32:$BC$32)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=E$4)*ISNUMBER(Marks!$B$32:$AK$32))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=E$4)*(Marks!$B$32:$AK$32=1))/SUMPRODUCT((Marks!$B$3:$AK$3=E$4)*ISNUMBER(Marks!$B$32:$AK$32)))</f>
         <v/>
       </c>
     </row>
@@ -9365,19 +6953,19 @@
         <v>29</v>
       </c>
       <c r="B33" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=B$4)*ISNUMBER(Marks!$B$33:$BC$33))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=B$4)*(Marks!$B$33:$BC$33=1))/SUMPRODUCT((Marks!$B$3:$BC$3=B$4)*ISNUMBER(Marks!$B$33:$BC$33)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=B$4)*ISNUMBER(Marks!$B$33:$AK$33))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=B$4)*(Marks!$B$33:$AK$33=1))/SUMPRODUCT((Marks!$B$3:$AK$3=B$4)*ISNUMBER(Marks!$B$33:$AK$33)))</f>
         <v/>
       </c>
       <c r="C33" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=C$4)*ISNUMBER(Marks!$B$33:$BC$33))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=C$4)*(Marks!$B$33:$BC$33=1))/SUMPRODUCT((Marks!$B$3:$BC$3=C$4)*ISNUMBER(Marks!$B$33:$BC$33)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=C$4)*ISNUMBER(Marks!$B$33:$AK$33))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=C$4)*(Marks!$B$33:$AK$33=1))/SUMPRODUCT((Marks!$B$3:$AK$3=C$4)*ISNUMBER(Marks!$B$33:$AK$33)))</f>
         <v/>
       </c>
       <c r="D33" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=D$4)*ISNUMBER(Marks!$B$33:$BC$33))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=D$4)*(Marks!$B$33:$BC$33=1))/SUMPRODUCT((Marks!$B$3:$BC$3=D$4)*ISNUMBER(Marks!$B$33:$BC$33)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=D$4)*ISNUMBER(Marks!$B$33:$AK$33))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=D$4)*(Marks!$B$33:$AK$33=1))/SUMPRODUCT((Marks!$B$3:$AK$3=D$4)*ISNUMBER(Marks!$B$33:$AK$33)))</f>
         <v/>
       </c>
       <c r="E33" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=E$4)*ISNUMBER(Marks!$B$33:$BC$33))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=E$4)*(Marks!$B$33:$BC$33=1))/SUMPRODUCT((Marks!$B$3:$BC$3=E$4)*ISNUMBER(Marks!$B$33:$BC$33)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=E$4)*ISNUMBER(Marks!$B$33:$AK$33))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=E$4)*(Marks!$B$33:$AK$33=1))/SUMPRODUCT((Marks!$B$3:$AK$3=E$4)*ISNUMBER(Marks!$B$33:$AK$33)))</f>
         <v/>
       </c>
     </row>
@@ -9386,19 +6974,19 @@
         <v>30</v>
       </c>
       <c r="B34" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=B$4)*ISNUMBER(Marks!$B$34:$BC$34))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=B$4)*(Marks!$B$34:$BC$34=1))/SUMPRODUCT((Marks!$B$3:$BC$3=B$4)*ISNUMBER(Marks!$B$34:$BC$34)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=B$4)*ISNUMBER(Marks!$B$34:$AK$34))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=B$4)*(Marks!$B$34:$AK$34=1))/SUMPRODUCT((Marks!$B$3:$AK$3=B$4)*ISNUMBER(Marks!$B$34:$AK$34)))</f>
         <v/>
       </c>
       <c r="C34" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=C$4)*ISNUMBER(Marks!$B$34:$BC$34))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=C$4)*(Marks!$B$34:$BC$34=1))/SUMPRODUCT((Marks!$B$3:$BC$3=C$4)*ISNUMBER(Marks!$B$34:$BC$34)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=C$4)*ISNUMBER(Marks!$B$34:$AK$34))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=C$4)*(Marks!$B$34:$AK$34=1))/SUMPRODUCT((Marks!$B$3:$AK$3=C$4)*ISNUMBER(Marks!$B$34:$AK$34)))</f>
         <v/>
       </c>
       <c r="D34" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=D$4)*ISNUMBER(Marks!$B$34:$BC$34))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=D$4)*(Marks!$B$34:$BC$34=1))/SUMPRODUCT((Marks!$B$3:$BC$3=D$4)*ISNUMBER(Marks!$B$34:$BC$34)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=D$4)*ISNUMBER(Marks!$B$34:$AK$34))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=D$4)*(Marks!$B$34:$AK$34=1))/SUMPRODUCT((Marks!$B$3:$AK$3=D$4)*ISNUMBER(Marks!$B$34:$AK$34)))</f>
         <v/>
       </c>
       <c r="E34" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=E$4)*ISNUMBER(Marks!$B$34:$BC$34))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=E$4)*(Marks!$B$34:$BC$34=1))/SUMPRODUCT((Marks!$B$3:$BC$3=E$4)*ISNUMBER(Marks!$B$34:$BC$34)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=E$4)*ISNUMBER(Marks!$B$34:$AK$34))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=E$4)*(Marks!$B$34:$AK$34=1))/SUMPRODUCT((Marks!$B$3:$AK$3=E$4)*ISNUMBER(Marks!$B$34:$AK$34)))</f>
         <v/>
       </c>
     </row>
@@ -9407,19 +6995,19 @@
         <v>31</v>
       </c>
       <c r="B35" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=B$4)*ISNUMBER(Marks!$B$35:$BC$35))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=B$4)*(Marks!$B$35:$BC$35=1))/SUMPRODUCT((Marks!$B$3:$BC$3=B$4)*ISNUMBER(Marks!$B$35:$BC$35)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=B$4)*ISNUMBER(Marks!$B$35:$AK$35))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=B$4)*(Marks!$B$35:$AK$35=1))/SUMPRODUCT((Marks!$B$3:$AK$3=B$4)*ISNUMBER(Marks!$B$35:$AK$35)))</f>
         <v/>
       </c>
       <c r="C35" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=C$4)*ISNUMBER(Marks!$B$35:$BC$35))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=C$4)*(Marks!$B$35:$BC$35=1))/SUMPRODUCT((Marks!$B$3:$BC$3=C$4)*ISNUMBER(Marks!$B$35:$BC$35)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=C$4)*ISNUMBER(Marks!$B$35:$AK$35))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=C$4)*(Marks!$B$35:$AK$35=1))/SUMPRODUCT((Marks!$B$3:$AK$3=C$4)*ISNUMBER(Marks!$B$35:$AK$35)))</f>
         <v/>
       </c>
       <c r="D35" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=D$4)*ISNUMBER(Marks!$B$35:$BC$35))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=D$4)*(Marks!$B$35:$BC$35=1))/SUMPRODUCT((Marks!$B$3:$BC$3=D$4)*ISNUMBER(Marks!$B$35:$BC$35)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=D$4)*ISNUMBER(Marks!$B$35:$AK$35))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=D$4)*(Marks!$B$35:$AK$35=1))/SUMPRODUCT((Marks!$B$3:$AK$3=D$4)*ISNUMBER(Marks!$B$35:$AK$35)))</f>
         <v/>
       </c>
       <c r="E35" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=E$4)*ISNUMBER(Marks!$B$35:$BC$35))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=E$4)*(Marks!$B$35:$BC$35=1))/SUMPRODUCT((Marks!$B$3:$BC$3=E$4)*ISNUMBER(Marks!$B$35:$BC$35)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=E$4)*ISNUMBER(Marks!$B$35:$AK$35))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=E$4)*(Marks!$B$35:$AK$35=1))/SUMPRODUCT((Marks!$B$3:$AK$3=E$4)*ISNUMBER(Marks!$B$35:$AK$35)))</f>
         <v/>
       </c>
     </row>
@@ -9428,19 +7016,19 @@
         <v>32</v>
       </c>
       <c r="B36" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=B$4)*ISNUMBER(Marks!$B$36:$BC$36))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=B$4)*(Marks!$B$36:$BC$36=1))/SUMPRODUCT((Marks!$B$3:$BC$3=B$4)*ISNUMBER(Marks!$B$36:$BC$36)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=B$4)*ISNUMBER(Marks!$B$36:$AK$36))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=B$4)*(Marks!$B$36:$AK$36=1))/SUMPRODUCT((Marks!$B$3:$AK$3=B$4)*ISNUMBER(Marks!$B$36:$AK$36)))</f>
         <v/>
       </c>
       <c r="C36" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=C$4)*ISNUMBER(Marks!$B$36:$BC$36))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=C$4)*(Marks!$B$36:$BC$36=1))/SUMPRODUCT((Marks!$B$3:$BC$3=C$4)*ISNUMBER(Marks!$B$36:$BC$36)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=C$4)*ISNUMBER(Marks!$B$36:$AK$36))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=C$4)*(Marks!$B$36:$AK$36=1))/SUMPRODUCT((Marks!$B$3:$AK$3=C$4)*ISNUMBER(Marks!$B$36:$AK$36)))</f>
         <v/>
       </c>
       <c r="D36" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=D$4)*ISNUMBER(Marks!$B$36:$BC$36))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=D$4)*(Marks!$B$36:$BC$36=1))/SUMPRODUCT((Marks!$B$3:$BC$3=D$4)*ISNUMBER(Marks!$B$36:$BC$36)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=D$4)*ISNUMBER(Marks!$B$36:$AK$36))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=D$4)*(Marks!$B$36:$AK$36=1))/SUMPRODUCT((Marks!$B$3:$AK$3=D$4)*ISNUMBER(Marks!$B$36:$AK$36)))</f>
         <v/>
       </c>
       <c r="E36" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=E$4)*ISNUMBER(Marks!$B$36:$BC$36))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=E$4)*(Marks!$B$36:$BC$36=1))/SUMPRODUCT((Marks!$B$3:$BC$3=E$4)*ISNUMBER(Marks!$B$36:$BC$36)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=E$4)*ISNUMBER(Marks!$B$36:$AK$36))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=E$4)*(Marks!$B$36:$AK$36=1))/SUMPRODUCT((Marks!$B$3:$AK$3=E$4)*ISNUMBER(Marks!$B$36:$AK$36)))</f>
         <v/>
       </c>
     </row>
@@ -9449,19 +7037,19 @@
         <v>33</v>
       </c>
       <c r="B37" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=B$4)*ISNUMBER(Marks!$B$37:$BC$37))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=B$4)*(Marks!$B$37:$BC$37=1))/SUMPRODUCT((Marks!$B$3:$BC$3=B$4)*ISNUMBER(Marks!$B$37:$BC$37)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=B$4)*ISNUMBER(Marks!$B$37:$AK$37))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=B$4)*(Marks!$B$37:$AK$37=1))/SUMPRODUCT((Marks!$B$3:$AK$3=B$4)*ISNUMBER(Marks!$B$37:$AK$37)))</f>
         <v/>
       </c>
       <c r="C37" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=C$4)*ISNUMBER(Marks!$B$37:$BC$37))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=C$4)*(Marks!$B$37:$BC$37=1))/SUMPRODUCT((Marks!$B$3:$BC$3=C$4)*ISNUMBER(Marks!$B$37:$BC$37)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=C$4)*ISNUMBER(Marks!$B$37:$AK$37))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=C$4)*(Marks!$B$37:$AK$37=1))/SUMPRODUCT((Marks!$B$3:$AK$3=C$4)*ISNUMBER(Marks!$B$37:$AK$37)))</f>
         <v/>
       </c>
       <c r="D37" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=D$4)*ISNUMBER(Marks!$B$37:$BC$37))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=D$4)*(Marks!$B$37:$BC$37=1))/SUMPRODUCT((Marks!$B$3:$BC$3=D$4)*ISNUMBER(Marks!$B$37:$BC$37)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=D$4)*ISNUMBER(Marks!$B$37:$AK$37))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=D$4)*(Marks!$B$37:$AK$37=1))/SUMPRODUCT((Marks!$B$3:$AK$3=D$4)*ISNUMBER(Marks!$B$37:$AK$37)))</f>
         <v/>
       </c>
       <c r="E37" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=E$4)*ISNUMBER(Marks!$B$37:$BC$37))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=E$4)*(Marks!$B$37:$BC$37=1))/SUMPRODUCT((Marks!$B$3:$BC$3=E$4)*ISNUMBER(Marks!$B$37:$BC$37)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=E$4)*ISNUMBER(Marks!$B$37:$AK$37))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=E$4)*(Marks!$B$37:$AK$37=1))/SUMPRODUCT((Marks!$B$3:$AK$3=E$4)*ISNUMBER(Marks!$B$37:$AK$37)))</f>
         <v/>
       </c>
     </row>
@@ -9470,19 +7058,19 @@
         <v>34</v>
       </c>
       <c r="B38" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=B$4)*ISNUMBER(Marks!$B$38:$BC$38))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=B$4)*(Marks!$B$38:$BC$38=1))/SUMPRODUCT((Marks!$B$3:$BC$3=B$4)*ISNUMBER(Marks!$B$38:$BC$38)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=B$4)*ISNUMBER(Marks!$B$38:$AK$38))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=B$4)*(Marks!$B$38:$AK$38=1))/SUMPRODUCT((Marks!$B$3:$AK$3=B$4)*ISNUMBER(Marks!$B$38:$AK$38)))</f>
         <v/>
       </c>
       <c r="C38" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=C$4)*ISNUMBER(Marks!$B$38:$BC$38))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=C$4)*(Marks!$B$38:$BC$38=1))/SUMPRODUCT((Marks!$B$3:$BC$3=C$4)*ISNUMBER(Marks!$B$38:$BC$38)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=C$4)*ISNUMBER(Marks!$B$38:$AK$38))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=C$4)*(Marks!$B$38:$AK$38=1))/SUMPRODUCT((Marks!$B$3:$AK$3=C$4)*ISNUMBER(Marks!$B$38:$AK$38)))</f>
         <v/>
       </c>
       <c r="D38" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=D$4)*ISNUMBER(Marks!$B$38:$BC$38))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=D$4)*(Marks!$B$38:$BC$38=1))/SUMPRODUCT((Marks!$B$3:$BC$3=D$4)*ISNUMBER(Marks!$B$38:$BC$38)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=D$4)*ISNUMBER(Marks!$B$38:$AK$38))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=D$4)*(Marks!$B$38:$AK$38=1))/SUMPRODUCT((Marks!$B$3:$AK$3=D$4)*ISNUMBER(Marks!$B$38:$AK$38)))</f>
         <v/>
       </c>
       <c r="E38" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=E$4)*ISNUMBER(Marks!$B$38:$BC$38))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=E$4)*(Marks!$B$38:$BC$38=1))/SUMPRODUCT((Marks!$B$3:$BC$3=E$4)*ISNUMBER(Marks!$B$38:$BC$38)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=E$4)*ISNUMBER(Marks!$B$38:$AK$38))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=E$4)*(Marks!$B$38:$AK$38=1))/SUMPRODUCT((Marks!$B$3:$AK$3=E$4)*ISNUMBER(Marks!$B$38:$AK$38)))</f>
         <v/>
       </c>
     </row>
@@ -9491,19 +7079,19 @@
         <v>35</v>
       </c>
       <c r="B39" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=B$4)*ISNUMBER(Marks!$B$39:$BC$39))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=B$4)*(Marks!$B$39:$BC$39=1))/SUMPRODUCT((Marks!$B$3:$BC$3=B$4)*ISNUMBER(Marks!$B$39:$BC$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=B$4)*ISNUMBER(Marks!$B$39:$AK$39))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=B$4)*(Marks!$B$39:$AK$39=1))/SUMPRODUCT((Marks!$B$3:$AK$3=B$4)*ISNUMBER(Marks!$B$39:$AK$39)))</f>
         <v/>
       </c>
       <c r="C39" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=C$4)*ISNUMBER(Marks!$B$39:$BC$39))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=C$4)*(Marks!$B$39:$BC$39=1))/SUMPRODUCT((Marks!$B$3:$BC$3=C$4)*ISNUMBER(Marks!$B$39:$BC$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=C$4)*ISNUMBER(Marks!$B$39:$AK$39))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=C$4)*(Marks!$B$39:$AK$39=1))/SUMPRODUCT((Marks!$B$3:$AK$3=C$4)*ISNUMBER(Marks!$B$39:$AK$39)))</f>
         <v/>
       </c>
       <c r="D39" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=D$4)*ISNUMBER(Marks!$B$39:$BC$39))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=D$4)*(Marks!$B$39:$BC$39=1))/SUMPRODUCT((Marks!$B$3:$BC$3=D$4)*ISNUMBER(Marks!$B$39:$BC$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=D$4)*ISNUMBER(Marks!$B$39:$AK$39))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=D$4)*(Marks!$B$39:$AK$39=1))/SUMPRODUCT((Marks!$B$3:$AK$3=D$4)*ISNUMBER(Marks!$B$39:$AK$39)))</f>
         <v/>
       </c>
       <c r="E39" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$BC$3=E$4)*ISNUMBER(Marks!$B$39:$BC$39))=0,"",SUMPRODUCT((Marks!$B$3:$BC$3=E$4)*(Marks!$B$39:$BC$39=1))/SUMPRODUCT((Marks!$B$3:$BC$3=E$4)*ISNUMBER(Marks!$B$39:$BC$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=E$4)*ISNUMBER(Marks!$B$39:$AK$39))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=E$4)*(Marks!$B$39:$AK$39=1))/SUMPRODUCT((Marks!$B$3:$AK$3=E$4)*ISNUMBER(Marks!$B$39:$AK$39)))</f>
         <v/>
       </c>
     </row>
@@ -9518,7 +7106,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N48"/>
+  <dimension ref="A1:L47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -9554,26 +7142,20 @@
       <c r="F3" t="n">
         <v>5</v>
       </c>
-      <c r="G3" t="n">
-        <v>6</v>
+      <c r="H3" t="n">
+        <v>1</v>
       </c>
       <c r="I3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L3" t="n">
-        <v>4</v>
-      </c>
-      <c r="M3" t="n">
         <v>5</v>
-      </c>
-      <c r="N3" t="n">
-        <v>6</v>
       </c>
     </row>
     <row r="4">
@@ -9607,39 +7189,29 @@
           <t>Rating, part 5</t>
         </is>
       </c>
-      <c r="G4" s="4" t="inlineStr">
-        <is>
-          <t>Rating, part 6</t>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>Right rate, part 1</t>
         </is>
       </c>
       <c r="I4" s="4" t="inlineStr">
         <is>
-          <t>Right rate, part 1</t>
+          <t>Right rate, part 2</t>
         </is>
       </c>
       <c r="J4" s="4" t="inlineStr">
         <is>
-          <t>Right rate, part 2</t>
+          <t>Right rate, part 3</t>
         </is>
       </c>
       <c r="K4" s="4" t="inlineStr">
         <is>
-          <t>Right rate, part 3</t>
+          <t>Right rate, part 4</t>
         </is>
       </c>
       <c r="L4" s="4" t="inlineStr">
         <is>
-          <t>Right rate, part 4</t>
-        </is>
-      </c>
-      <c r="M4" s="4" t="inlineStr">
-        <is>
           <t>Right rate, part 5</t>
-        </is>
-      </c>
-      <c r="N4" s="4" t="inlineStr">
-        <is>
-          <t>Right rate, part 6</t>
         </is>
       </c>
     </row>
@@ -9652,29 +7224,24 @@
       <c r="D5" s="5" t="n"/>
       <c r="E5" s="5" t="n"/>
       <c r="F5" s="5" t="n"/>
-      <c r="G5" s="5" t="n"/>
+      <c r="H5" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=H$3)*ISNUMBER(Marks!$B$5:$AK$5))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=H$3)*(Marks!$B$5:$AK$5=1))/SUMPRODUCT((Marks!$B$2:$AK$2=H$3)*ISNUMBER(Marks!$B$5:$AK$5)))</f>
+        <v/>
+      </c>
       <c r="I5" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=I$3)*ISNUMBER(Marks!$B$5:$BC$5))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=I$3)*(Marks!$B$5:$BC$5=1))/SUMPRODUCT((Marks!$B$2:$BC$2=I$3)*ISNUMBER(Marks!$B$5:$BC$5)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=I$3)*ISNUMBER(Marks!$B$5:$AK$5))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=I$3)*(Marks!$B$5:$AK$5=1))/SUMPRODUCT((Marks!$B$2:$AK$2=I$3)*ISNUMBER(Marks!$B$5:$AK$5)))</f>
         <v/>
       </c>
       <c r="J5" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=J$3)*ISNUMBER(Marks!$B$5:$BC$5))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=J$3)*(Marks!$B$5:$BC$5=1))/SUMPRODUCT((Marks!$B$2:$BC$2=J$3)*ISNUMBER(Marks!$B$5:$BC$5)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=J$3)*ISNUMBER(Marks!$B$5:$AK$5))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=J$3)*(Marks!$B$5:$AK$5=1))/SUMPRODUCT((Marks!$B$2:$AK$2=J$3)*ISNUMBER(Marks!$B$5:$AK$5)))</f>
         <v/>
       </c>
       <c r="K5" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=K$3)*ISNUMBER(Marks!$B$5:$BC$5))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=K$3)*(Marks!$B$5:$BC$5=1))/SUMPRODUCT((Marks!$B$2:$BC$2=K$3)*ISNUMBER(Marks!$B$5:$BC$5)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=K$3)*ISNUMBER(Marks!$B$5:$AK$5))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=K$3)*(Marks!$B$5:$AK$5=1))/SUMPRODUCT((Marks!$B$2:$AK$2=K$3)*ISNUMBER(Marks!$B$5:$AK$5)))</f>
         <v/>
       </c>
       <c r="L5" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=L$3)*ISNUMBER(Marks!$B$5:$BC$5))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=L$3)*(Marks!$B$5:$BC$5=1))/SUMPRODUCT((Marks!$B$2:$BC$2=L$3)*ISNUMBER(Marks!$B$5:$BC$5)))</f>
-        <v/>
-      </c>
-      <c r="M5" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=M$3)*ISNUMBER(Marks!$B$5:$BC$5))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=M$3)*(Marks!$B$5:$BC$5=1))/SUMPRODUCT((Marks!$B$2:$BC$2=M$3)*ISNUMBER(Marks!$B$5:$BC$5)))</f>
-        <v/>
-      </c>
-      <c r="N5" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=N$3)*ISNUMBER(Marks!$B$5:$BC$5))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=N$3)*(Marks!$B$5:$BC$5=1))/SUMPRODUCT((Marks!$B$2:$BC$2=N$3)*ISNUMBER(Marks!$B$5:$BC$5)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=L$3)*ISNUMBER(Marks!$B$5:$AK$5))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=L$3)*(Marks!$B$5:$AK$5=1))/SUMPRODUCT((Marks!$B$2:$AK$2=L$3)*ISNUMBER(Marks!$B$5:$AK$5)))</f>
         <v/>
       </c>
     </row>
@@ -9687,29 +7254,24 @@
       <c r="D6" s="5" t="n"/>
       <c r="E6" s="5" t="n"/>
       <c r="F6" s="5" t="n"/>
-      <c r="G6" s="5" t="n"/>
+      <c r="H6" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=H$3)*ISNUMBER(Marks!$B$6:$AK$6))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=H$3)*(Marks!$B$6:$AK$6=1))/SUMPRODUCT((Marks!$B$2:$AK$2=H$3)*ISNUMBER(Marks!$B$6:$AK$6)))</f>
+        <v/>
+      </c>
       <c r="I6" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=I$3)*ISNUMBER(Marks!$B$6:$BC$6))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=I$3)*(Marks!$B$6:$BC$6=1))/SUMPRODUCT((Marks!$B$2:$BC$2=I$3)*ISNUMBER(Marks!$B$6:$BC$6)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=I$3)*ISNUMBER(Marks!$B$6:$AK$6))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=I$3)*(Marks!$B$6:$AK$6=1))/SUMPRODUCT((Marks!$B$2:$AK$2=I$3)*ISNUMBER(Marks!$B$6:$AK$6)))</f>
         <v/>
       </c>
       <c r="J6" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=J$3)*ISNUMBER(Marks!$B$6:$BC$6))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=J$3)*(Marks!$B$6:$BC$6=1))/SUMPRODUCT((Marks!$B$2:$BC$2=J$3)*ISNUMBER(Marks!$B$6:$BC$6)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=J$3)*ISNUMBER(Marks!$B$6:$AK$6))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=J$3)*(Marks!$B$6:$AK$6=1))/SUMPRODUCT((Marks!$B$2:$AK$2=J$3)*ISNUMBER(Marks!$B$6:$AK$6)))</f>
         <v/>
       </c>
       <c r="K6" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=K$3)*ISNUMBER(Marks!$B$6:$BC$6))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=K$3)*(Marks!$B$6:$BC$6=1))/SUMPRODUCT((Marks!$B$2:$BC$2=K$3)*ISNUMBER(Marks!$B$6:$BC$6)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=K$3)*ISNUMBER(Marks!$B$6:$AK$6))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=K$3)*(Marks!$B$6:$AK$6=1))/SUMPRODUCT((Marks!$B$2:$AK$2=K$3)*ISNUMBER(Marks!$B$6:$AK$6)))</f>
         <v/>
       </c>
       <c r="L6" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=L$3)*ISNUMBER(Marks!$B$6:$BC$6))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=L$3)*(Marks!$B$6:$BC$6=1))/SUMPRODUCT((Marks!$B$2:$BC$2=L$3)*ISNUMBER(Marks!$B$6:$BC$6)))</f>
-        <v/>
-      </c>
-      <c r="M6" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=M$3)*ISNUMBER(Marks!$B$6:$BC$6))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=M$3)*(Marks!$B$6:$BC$6=1))/SUMPRODUCT((Marks!$B$2:$BC$2=M$3)*ISNUMBER(Marks!$B$6:$BC$6)))</f>
-        <v/>
-      </c>
-      <c r="N6" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=N$3)*ISNUMBER(Marks!$B$6:$BC$6))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=N$3)*(Marks!$B$6:$BC$6=1))/SUMPRODUCT((Marks!$B$2:$BC$2=N$3)*ISNUMBER(Marks!$B$6:$BC$6)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=L$3)*ISNUMBER(Marks!$B$6:$AK$6))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=L$3)*(Marks!$B$6:$AK$6=1))/SUMPRODUCT((Marks!$B$2:$AK$2=L$3)*ISNUMBER(Marks!$B$6:$AK$6)))</f>
         <v/>
       </c>
     </row>
@@ -9722,29 +7284,24 @@
       <c r="D7" s="5" t="n"/>
       <c r="E7" s="5" t="n"/>
       <c r="F7" s="5" t="n"/>
-      <c r="G7" s="5" t="n"/>
+      <c r="H7" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=H$3)*ISNUMBER(Marks!$B$7:$AK$7))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=H$3)*(Marks!$B$7:$AK$7=1))/SUMPRODUCT((Marks!$B$2:$AK$2=H$3)*ISNUMBER(Marks!$B$7:$AK$7)))</f>
+        <v/>
+      </c>
       <c r="I7" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=I$3)*ISNUMBER(Marks!$B$7:$BC$7))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=I$3)*(Marks!$B$7:$BC$7=1))/SUMPRODUCT((Marks!$B$2:$BC$2=I$3)*ISNUMBER(Marks!$B$7:$BC$7)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=I$3)*ISNUMBER(Marks!$B$7:$AK$7))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=I$3)*(Marks!$B$7:$AK$7=1))/SUMPRODUCT((Marks!$B$2:$AK$2=I$3)*ISNUMBER(Marks!$B$7:$AK$7)))</f>
         <v/>
       </c>
       <c r="J7" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=J$3)*ISNUMBER(Marks!$B$7:$BC$7))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=J$3)*(Marks!$B$7:$BC$7=1))/SUMPRODUCT((Marks!$B$2:$BC$2=J$3)*ISNUMBER(Marks!$B$7:$BC$7)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=J$3)*ISNUMBER(Marks!$B$7:$AK$7))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=J$3)*(Marks!$B$7:$AK$7=1))/SUMPRODUCT((Marks!$B$2:$AK$2=J$3)*ISNUMBER(Marks!$B$7:$AK$7)))</f>
         <v/>
       </c>
       <c r="K7" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=K$3)*ISNUMBER(Marks!$B$7:$BC$7))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=K$3)*(Marks!$B$7:$BC$7=1))/SUMPRODUCT((Marks!$B$2:$BC$2=K$3)*ISNUMBER(Marks!$B$7:$BC$7)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=K$3)*ISNUMBER(Marks!$B$7:$AK$7))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=K$3)*(Marks!$B$7:$AK$7=1))/SUMPRODUCT((Marks!$B$2:$AK$2=K$3)*ISNUMBER(Marks!$B$7:$AK$7)))</f>
         <v/>
       </c>
       <c r="L7" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=L$3)*ISNUMBER(Marks!$B$7:$BC$7))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=L$3)*(Marks!$B$7:$BC$7=1))/SUMPRODUCT((Marks!$B$2:$BC$2=L$3)*ISNUMBER(Marks!$B$7:$BC$7)))</f>
-        <v/>
-      </c>
-      <c r="M7" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=M$3)*ISNUMBER(Marks!$B$7:$BC$7))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=M$3)*(Marks!$B$7:$BC$7=1))/SUMPRODUCT((Marks!$B$2:$BC$2=M$3)*ISNUMBER(Marks!$B$7:$BC$7)))</f>
-        <v/>
-      </c>
-      <c r="N7" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=N$3)*ISNUMBER(Marks!$B$7:$BC$7))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=N$3)*(Marks!$B$7:$BC$7=1))/SUMPRODUCT((Marks!$B$2:$BC$2=N$3)*ISNUMBER(Marks!$B$7:$BC$7)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=L$3)*ISNUMBER(Marks!$B$7:$AK$7))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=L$3)*(Marks!$B$7:$AK$7=1))/SUMPRODUCT((Marks!$B$2:$AK$2=L$3)*ISNUMBER(Marks!$B$7:$AK$7)))</f>
         <v/>
       </c>
     </row>
@@ -9757,29 +7314,24 @@
       <c r="D8" s="5" t="n"/>
       <c r="E8" s="5" t="n"/>
       <c r="F8" s="5" t="n"/>
-      <c r="G8" s="5" t="n"/>
+      <c r="H8" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=H$3)*ISNUMBER(Marks!$B$8:$AK$8))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=H$3)*(Marks!$B$8:$AK$8=1))/SUMPRODUCT((Marks!$B$2:$AK$2=H$3)*ISNUMBER(Marks!$B$8:$AK$8)))</f>
+        <v/>
+      </c>
       <c r="I8" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=I$3)*ISNUMBER(Marks!$B$8:$BC$8))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=I$3)*(Marks!$B$8:$BC$8=1))/SUMPRODUCT((Marks!$B$2:$BC$2=I$3)*ISNUMBER(Marks!$B$8:$BC$8)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=I$3)*ISNUMBER(Marks!$B$8:$AK$8))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=I$3)*(Marks!$B$8:$AK$8=1))/SUMPRODUCT((Marks!$B$2:$AK$2=I$3)*ISNUMBER(Marks!$B$8:$AK$8)))</f>
         <v/>
       </c>
       <c r="J8" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=J$3)*ISNUMBER(Marks!$B$8:$BC$8))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=J$3)*(Marks!$B$8:$BC$8=1))/SUMPRODUCT((Marks!$B$2:$BC$2=J$3)*ISNUMBER(Marks!$B$8:$BC$8)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=J$3)*ISNUMBER(Marks!$B$8:$AK$8))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=J$3)*(Marks!$B$8:$AK$8=1))/SUMPRODUCT((Marks!$B$2:$AK$2=J$3)*ISNUMBER(Marks!$B$8:$AK$8)))</f>
         <v/>
       </c>
       <c r="K8" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=K$3)*ISNUMBER(Marks!$B$8:$BC$8))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=K$3)*(Marks!$B$8:$BC$8=1))/SUMPRODUCT((Marks!$B$2:$BC$2=K$3)*ISNUMBER(Marks!$B$8:$BC$8)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=K$3)*ISNUMBER(Marks!$B$8:$AK$8))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=K$3)*(Marks!$B$8:$AK$8=1))/SUMPRODUCT((Marks!$B$2:$AK$2=K$3)*ISNUMBER(Marks!$B$8:$AK$8)))</f>
         <v/>
       </c>
       <c r="L8" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=L$3)*ISNUMBER(Marks!$B$8:$BC$8))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=L$3)*(Marks!$B$8:$BC$8=1))/SUMPRODUCT((Marks!$B$2:$BC$2=L$3)*ISNUMBER(Marks!$B$8:$BC$8)))</f>
-        <v/>
-      </c>
-      <c r="M8" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=M$3)*ISNUMBER(Marks!$B$8:$BC$8))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=M$3)*(Marks!$B$8:$BC$8=1))/SUMPRODUCT((Marks!$B$2:$BC$2=M$3)*ISNUMBER(Marks!$B$8:$BC$8)))</f>
-        <v/>
-      </c>
-      <c r="N8" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=N$3)*ISNUMBER(Marks!$B$8:$BC$8))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=N$3)*(Marks!$B$8:$BC$8=1))/SUMPRODUCT((Marks!$B$2:$BC$2=N$3)*ISNUMBER(Marks!$B$8:$BC$8)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=L$3)*ISNUMBER(Marks!$B$8:$AK$8))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=L$3)*(Marks!$B$8:$AK$8=1))/SUMPRODUCT((Marks!$B$2:$AK$2=L$3)*ISNUMBER(Marks!$B$8:$AK$8)))</f>
         <v/>
       </c>
     </row>
@@ -9792,29 +7344,24 @@
       <c r="D9" s="5" t="n"/>
       <c r="E9" s="5" t="n"/>
       <c r="F9" s="5" t="n"/>
-      <c r="G9" s="5" t="n"/>
+      <c r="H9" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=H$3)*ISNUMBER(Marks!$B$9:$AK$9))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=H$3)*(Marks!$B$9:$AK$9=1))/SUMPRODUCT((Marks!$B$2:$AK$2=H$3)*ISNUMBER(Marks!$B$9:$AK$9)))</f>
+        <v/>
+      </c>
       <c r="I9" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=I$3)*ISNUMBER(Marks!$B$9:$BC$9))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=I$3)*(Marks!$B$9:$BC$9=1))/SUMPRODUCT((Marks!$B$2:$BC$2=I$3)*ISNUMBER(Marks!$B$9:$BC$9)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=I$3)*ISNUMBER(Marks!$B$9:$AK$9))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=I$3)*(Marks!$B$9:$AK$9=1))/SUMPRODUCT((Marks!$B$2:$AK$2=I$3)*ISNUMBER(Marks!$B$9:$AK$9)))</f>
         <v/>
       </c>
       <c r="J9" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=J$3)*ISNUMBER(Marks!$B$9:$BC$9))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=J$3)*(Marks!$B$9:$BC$9=1))/SUMPRODUCT((Marks!$B$2:$BC$2=J$3)*ISNUMBER(Marks!$B$9:$BC$9)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=J$3)*ISNUMBER(Marks!$B$9:$AK$9))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=J$3)*(Marks!$B$9:$AK$9=1))/SUMPRODUCT((Marks!$B$2:$AK$2=J$3)*ISNUMBER(Marks!$B$9:$AK$9)))</f>
         <v/>
       </c>
       <c r="K9" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=K$3)*ISNUMBER(Marks!$B$9:$BC$9))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=K$3)*(Marks!$B$9:$BC$9=1))/SUMPRODUCT((Marks!$B$2:$BC$2=K$3)*ISNUMBER(Marks!$B$9:$BC$9)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=K$3)*ISNUMBER(Marks!$B$9:$AK$9))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=K$3)*(Marks!$B$9:$AK$9=1))/SUMPRODUCT((Marks!$B$2:$AK$2=K$3)*ISNUMBER(Marks!$B$9:$AK$9)))</f>
         <v/>
       </c>
       <c r="L9" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=L$3)*ISNUMBER(Marks!$B$9:$BC$9))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=L$3)*(Marks!$B$9:$BC$9=1))/SUMPRODUCT((Marks!$B$2:$BC$2=L$3)*ISNUMBER(Marks!$B$9:$BC$9)))</f>
-        <v/>
-      </c>
-      <c r="M9" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=M$3)*ISNUMBER(Marks!$B$9:$BC$9))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=M$3)*(Marks!$B$9:$BC$9=1))/SUMPRODUCT((Marks!$B$2:$BC$2=M$3)*ISNUMBER(Marks!$B$9:$BC$9)))</f>
-        <v/>
-      </c>
-      <c r="N9" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=N$3)*ISNUMBER(Marks!$B$9:$BC$9))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=N$3)*(Marks!$B$9:$BC$9=1))/SUMPRODUCT((Marks!$B$2:$BC$2=N$3)*ISNUMBER(Marks!$B$9:$BC$9)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=L$3)*ISNUMBER(Marks!$B$9:$AK$9))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=L$3)*(Marks!$B$9:$AK$9=1))/SUMPRODUCT((Marks!$B$2:$AK$2=L$3)*ISNUMBER(Marks!$B$9:$AK$9)))</f>
         <v/>
       </c>
     </row>
@@ -9827,29 +7374,24 @@
       <c r="D10" s="5" t="n"/>
       <c r="E10" s="5" t="n"/>
       <c r="F10" s="5" t="n"/>
-      <c r="G10" s="5" t="n"/>
+      <c r="H10" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=H$3)*ISNUMBER(Marks!$B$10:$AK$10))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=H$3)*(Marks!$B$10:$AK$10=1))/SUMPRODUCT((Marks!$B$2:$AK$2=H$3)*ISNUMBER(Marks!$B$10:$AK$10)))</f>
+        <v/>
+      </c>
       <c r="I10" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=I$3)*ISNUMBER(Marks!$B$10:$BC$10))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=I$3)*(Marks!$B$10:$BC$10=1))/SUMPRODUCT((Marks!$B$2:$BC$2=I$3)*ISNUMBER(Marks!$B$10:$BC$10)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=I$3)*ISNUMBER(Marks!$B$10:$AK$10))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=I$3)*(Marks!$B$10:$AK$10=1))/SUMPRODUCT((Marks!$B$2:$AK$2=I$3)*ISNUMBER(Marks!$B$10:$AK$10)))</f>
         <v/>
       </c>
       <c r="J10" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=J$3)*ISNUMBER(Marks!$B$10:$BC$10))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=J$3)*(Marks!$B$10:$BC$10=1))/SUMPRODUCT((Marks!$B$2:$BC$2=J$3)*ISNUMBER(Marks!$B$10:$BC$10)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=J$3)*ISNUMBER(Marks!$B$10:$AK$10))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=J$3)*(Marks!$B$10:$AK$10=1))/SUMPRODUCT((Marks!$B$2:$AK$2=J$3)*ISNUMBER(Marks!$B$10:$AK$10)))</f>
         <v/>
       </c>
       <c r="K10" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=K$3)*ISNUMBER(Marks!$B$10:$BC$10))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=K$3)*(Marks!$B$10:$BC$10=1))/SUMPRODUCT((Marks!$B$2:$BC$2=K$3)*ISNUMBER(Marks!$B$10:$BC$10)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=K$3)*ISNUMBER(Marks!$B$10:$AK$10))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=K$3)*(Marks!$B$10:$AK$10=1))/SUMPRODUCT((Marks!$B$2:$AK$2=K$3)*ISNUMBER(Marks!$B$10:$AK$10)))</f>
         <v/>
       </c>
       <c r="L10" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=L$3)*ISNUMBER(Marks!$B$10:$BC$10))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=L$3)*(Marks!$B$10:$BC$10=1))/SUMPRODUCT((Marks!$B$2:$BC$2=L$3)*ISNUMBER(Marks!$B$10:$BC$10)))</f>
-        <v/>
-      </c>
-      <c r="M10" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=M$3)*ISNUMBER(Marks!$B$10:$BC$10))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=M$3)*(Marks!$B$10:$BC$10=1))/SUMPRODUCT((Marks!$B$2:$BC$2=M$3)*ISNUMBER(Marks!$B$10:$BC$10)))</f>
-        <v/>
-      </c>
-      <c r="N10" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=N$3)*ISNUMBER(Marks!$B$10:$BC$10))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=N$3)*(Marks!$B$10:$BC$10=1))/SUMPRODUCT((Marks!$B$2:$BC$2=N$3)*ISNUMBER(Marks!$B$10:$BC$10)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=L$3)*ISNUMBER(Marks!$B$10:$AK$10))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=L$3)*(Marks!$B$10:$AK$10=1))/SUMPRODUCT((Marks!$B$2:$AK$2=L$3)*ISNUMBER(Marks!$B$10:$AK$10)))</f>
         <v/>
       </c>
     </row>
@@ -9862,29 +7404,24 @@
       <c r="D11" s="5" t="n"/>
       <c r="E11" s="5" t="n"/>
       <c r="F11" s="5" t="n"/>
-      <c r="G11" s="5" t="n"/>
+      <c r="H11" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=H$3)*ISNUMBER(Marks!$B$11:$AK$11))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=H$3)*(Marks!$B$11:$AK$11=1))/SUMPRODUCT((Marks!$B$2:$AK$2=H$3)*ISNUMBER(Marks!$B$11:$AK$11)))</f>
+        <v/>
+      </c>
       <c r="I11" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=I$3)*ISNUMBER(Marks!$B$11:$BC$11))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=I$3)*(Marks!$B$11:$BC$11=1))/SUMPRODUCT((Marks!$B$2:$BC$2=I$3)*ISNUMBER(Marks!$B$11:$BC$11)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=I$3)*ISNUMBER(Marks!$B$11:$AK$11))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=I$3)*(Marks!$B$11:$AK$11=1))/SUMPRODUCT((Marks!$B$2:$AK$2=I$3)*ISNUMBER(Marks!$B$11:$AK$11)))</f>
         <v/>
       </c>
       <c r="J11" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=J$3)*ISNUMBER(Marks!$B$11:$BC$11))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=J$3)*(Marks!$B$11:$BC$11=1))/SUMPRODUCT((Marks!$B$2:$BC$2=J$3)*ISNUMBER(Marks!$B$11:$BC$11)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=J$3)*ISNUMBER(Marks!$B$11:$AK$11))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=J$3)*(Marks!$B$11:$AK$11=1))/SUMPRODUCT((Marks!$B$2:$AK$2=J$3)*ISNUMBER(Marks!$B$11:$AK$11)))</f>
         <v/>
       </c>
       <c r="K11" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=K$3)*ISNUMBER(Marks!$B$11:$BC$11))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=K$3)*(Marks!$B$11:$BC$11=1))/SUMPRODUCT((Marks!$B$2:$BC$2=K$3)*ISNUMBER(Marks!$B$11:$BC$11)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=K$3)*ISNUMBER(Marks!$B$11:$AK$11))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=K$3)*(Marks!$B$11:$AK$11=1))/SUMPRODUCT((Marks!$B$2:$AK$2=K$3)*ISNUMBER(Marks!$B$11:$AK$11)))</f>
         <v/>
       </c>
       <c r="L11" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=L$3)*ISNUMBER(Marks!$B$11:$BC$11))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=L$3)*(Marks!$B$11:$BC$11=1))/SUMPRODUCT((Marks!$B$2:$BC$2=L$3)*ISNUMBER(Marks!$B$11:$BC$11)))</f>
-        <v/>
-      </c>
-      <c r="M11" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=M$3)*ISNUMBER(Marks!$B$11:$BC$11))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=M$3)*(Marks!$B$11:$BC$11=1))/SUMPRODUCT((Marks!$B$2:$BC$2=M$3)*ISNUMBER(Marks!$B$11:$BC$11)))</f>
-        <v/>
-      </c>
-      <c r="N11" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=N$3)*ISNUMBER(Marks!$B$11:$BC$11))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=N$3)*(Marks!$B$11:$BC$11=1))/SUMPRODUCT((Marks!$B$2:$BC$2=N$3)*ISNUMBER(Marks!$B$11:$BC$11)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=L$3)*ISNUMBER(Marks!$B$11:$AK$11))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=L$3)*(Marks!$B$11:$AK$11=1))/SUMPRODUCT((Marks!$B$2:$AK$2=L$3)*ISNUMBER(Marks!$B$11:$AK$11)))</f>
         <v/>
       </c>
     </row>
@@ -9897,29 +7434,24 @@
       <c r="D12" s="5" t="n"/>
       <c r="E12" s="5" t="n"/>
       <c r="F12" s="5" t="n"/>
-      <c r="G12" s="5" t="n"/>
+      <c r="H12" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=H$3)*ISNUMBER(Marks!$B$12:$AK$12))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=H$3)*(Marks!$B$12:$AK$12=1))/SUMPRODUCT((Marks!$B$2:$AK$2=H$3)*ISNUMBER(Marks!$B$12:$AK$12)))</f>
+        <v/>
+      </c>
       <c r="I12" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=I$3)*ISNUMBER(Marks!$B$12:$BC$12))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=I$3)*(Marks!$B$12:$BC$12=1))/SUMPRODUCT((Marks!$B$2:$BC$2=I$3)*ISNUMBER(Marks!$B$12:$BC$12)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=I$3)*ISNUMBER(Marks!$B$12:$AK$12))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=I$3)*(Marks!$B$12:$AK$12=1))/SUMPRODUCT((Marks!$B$2:$AK$2=I$3)*ISNUMBER(Marks!$B$12:$AK$12)))</f>
         <v/>
       </c>
       <c r="J12" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=J$3)*ISNUMBER(Marks!$B$12:$BC$12))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=J$3)*(Marks!$B$12:$BC$12=1))/SUMPRODUCT((Marks!$B$2:$BC$2=J$3)*ISNUMBER(Marks!$B$12:$BC$12)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=J$3)*ISNUMBER(Marks!$B$12:$AK$12))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=J$3)*(Marks!$B$12:$AK$12=1))/SUMPRODUCT((Marks!$B$2:$AK$2=J$3)*ISNUMBER(Marks!$B$12:$AK$12)))</f>
         <v/>
       </c>
       <c r="K12" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=K$3)*ISNUMBER(Marks!$B$12:$BC$12))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=K$3)*(Marks!$B$12:$BC$12=1))/SUMPRODUCT((Marks!$B$2:$BC$2=K$3)*ISNUMBER(Marks!$B$12:$BC$12)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=K$3)*ISNUMBER(Marks!$B$12:$AK$12))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=K$3)*(Marks!$B$12:$AK$12=1))/SUMPRODUCT((Marks!$B$2:$AK$2=K$3)*ISNUMBER(Marks!$B$12:$AK$12)))</f>
         <v/>
       </c>
       <c r="L12" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=L$3)*ISNUMBER(Marks!$B$12:$BC$12))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=L$3)*(Marks!$B$12:$BC$12=1))/SUMPRODUCT((Marks!$B$2:$BC$2=L$3)*ISNUMBER(Marks!$B$12:$BC$12)))</f>
-        <v/>
-      </c>
-      <c r="M12" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=M$3)*ISNUMBER(Marks!$B$12:$BC$12))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=M$3)*(Marks!$B$12:$BC$12=1))/SUMPRODUCT((Marks!$B$2:$BC$2=M$3)*ISNUMBER(Marks!$B$12:$BC$12)))</f>
-        <v/>
-      </c>
-      <c r="N12" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=N$3)*ISNUMBER(Marks!$B$12:$BC$12))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=N$3)*(Marks!$B$12:$BC$12=1))/SUMPRODUCT((Marks!$B$2:$BC$2=N$3)*ISNUMBER(Marks!$B$12:$BC$12)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=L$3)*ISNUMBER(Marks!$B$12:$AK$12))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=L$3)*(Marks!$B$12:$AK$12=1))/SUMPRODUCT((Marks!$B$2:$AK$2=L$3)*ISNUMBER(Marks!$B$12:$AK$12)))</f>
         <v/>
       </c>
     </row>
@@ -9932,29 +7464,24 @@
       <c r="D13" s="5" t="n"/>
       <c r="E13" s="5" t="n"/>
       <c r="F13" s="5" t="n"/>
-      <c r="G13" s="5" t="n"/>
+      <c r="H13" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=H$3)*ISNUMBER(Marks!$B$13:$AK$13))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=H$3)*(Marks!$B$13:$AK$13=1))/SUMPRODUCT((Marks!$B$2:$AK$2=H$3)*ISNUMBER(Marks!$B$13:$AK$13)))</f>
+        <v/>
+      </c>
       <c r="I13" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=I$3)*ISNUMBER(Marks!$B$13:$BC$13))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=I$3)*(Marks!$B$13:$BC$13=1))/SUMPRODUCT((Marks!$B$2:$BC$2=I$3)*ISNUMBER(Marks!$B$13:$BC$13)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=I$3)*ISNUMBER(Marks!$B$13:$AK$13))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=I$3)*(Marks!$B$13:$AK$13=1))/SUMPRODUCT((Marks!$B$2:$AK$2=I$3)*ISNUMBER(Marks!$B$13:$AK$13)))</f>
         <v/>
       </c>
       <c r="J13" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=J$3)*ISNUMBER(Marks!$B$13:$BC$13))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=J$3)*(Marks!$B$13:$BC$13=1))/SUMPRODUCT((Marks!$B$2:$BC$2=J$3)*ISNUMBER(Marks!$B$13:$BC$13)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=J$3)*ISNUMBER(Marks!$B$13:$AK$13))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=J$3)*(Marks!$B$13:$AK$13=1))/SUMPRODUCT((Marks!$B$2:$AK$2=J$3)*ISNUMBER(Marks!$B$13:$AK$13)))</f>
         <v/>
       </c>
       <c r="K13" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=K$3)*ISNUMBER(Marks!$B$13:$BC$13))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=K$3)*(Marks!$B$13:$BC$13=1))/SUMPRODUCT((Marks!$B$2:$BC$2=K$3)*ISNUMBER(Marks!$B$13:$BC$13)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=K$3)*ISNUMBER(Marks!$B$13:$AK$13))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=K$3)*(Marks!$B$13:$AK$13=1))/SUMPRODUCT((Marks!$B$2:$AK$2=K$3)*ISNUMBER(Marks!$B$13:$AK$13)))</f>
         <v/>
       </c>
       <c r="L13" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=L$3)*ISNUMBER(Marks!$B$13:$BC$13))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=L$3)*(Marks!$B$13:$BC$13=1))/SUMPRODUCT((Marks!$B$2:$BC$2=L$3)*ISNUMBER(Marks!$B$13:$BC$13)))</f>
-        <v/>
-      </c>
-      <c r="M13" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=M$3)*ISNUMBER(Marks!$B$13:$BC$13))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=M$3)*(Marks!$B$13:$BC$13=1))/SUMPRODUCT((Marks!$B$2:$BC$2=M$3)*ISNUMBER(Marks!$B$13:$BC$13)))</f>
-        <v/>
-      </c>
-      <c r="N13" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=N$3)*ISNUMBER(Marks!$B$13:$BC$13))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=N$3)*(Marks!$B$13:$BC$13=1))/SUMPRODUCT((Marks!$B$2:$BC$2=N$3)*ISNUMBER(Marks!$B$13:$BC$13)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=L$3)*ISNUMBER(Marks!$B$13:$AK$13))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=L$3)*(Marks!$B$13:$AK$13=1))/SUMPRODUCT((Marks!$B$2:$AK$2=L$3)*ISNUMBER(Marks!$B$13:$AK$13)))</f>
         <v/>
       </c>
     </row>
@@ -9967,29 +7494,24 @@
       <c r="D14" s="5" t="n"/>
       <c r="E14" s="5" t="n"/>
       <c r="F14" s="5" t="n"/>
-      <c r="G14" s="5" t="n"/>
+      <c r="H14" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=H$3)*ISNUMBER(Marks!$B$14:$AK$14))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=H$3)*(Marks!$B$14:$AK$14=1))/SUMPRODUCT((Marks!$B$2:$AK$2=H$3)*ISNUMBER(Marks!$B$14:$AK$14)))</f>
+        <v/>
+      </c>
       <c r="I14" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=I$3)*ISNUMBER(Marks!$B$14:$BC$14))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=I$3)*(Marks!$B$14:$BC$14=1))/SUMPRODUCT((Marks!$B$2:$BC$2=I$3)*ISNUMBER(Marks!$B$14:$BC$14)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=I$3)*ISNUMBER(Marks!$B$14:$AK$14))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=I$3)*(Marks!$B$14:$AK$14=1))/SUMPRODUCT((Marks!$B$2:$AK$2=I$3)*ISNUMBER(Marks!$B$14:$AK$14)))</f>
         <v/>
       </c>
       <c r="J14" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=J$3)*ISNUMBER(Marks!$B$14:$BC$14))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=J$3)*(Marks!$B$14:$BC$14=1))/SUMPRODUCT((Marks!$B$2:$BC$2=J$3)*ISNUMBER(Marks!$B$14:$BC$14)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=J$3)*ISNUMBER(Marks!$B$14:$AK$14))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=J$3)*(Marks!$B$14:$AK$14=1))/SUMPRODUCT((Marks!$B$2:$AK$2=J$3)*ISNUMBER(Marks!$B$14:$AK$14)))</f>
         <v/>
       </c>
       <c r="K14" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=K$3)*ISNUMBER(Marks!$B$14:$BC$14))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=K$3)*(Marks!$B$14:$BC$14=1))/SUMPRODUCT((Marks!$B$2:$BC$2=K$3)*ISNUMBER(Marks!$B$14:$BC$14)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=K$3)*ISNUMBER(Marks!$B$14:$AK$14))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=K$3)*(Marks!$B$14:$AK$14=1))/SUMPRODUCT((Marks!$B$2:$AK$2=K$3)*ISNUMBER(Marks!$B$14:$AK$14)))</f>
         <v/>
       </c>
       <c r="L14" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=L$3)*ISNUMBER(Marks!$B$14:$BC$14))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=L$3)*(Marks!$B$14:$BC$14=1))/SUMPRODUCT((Marks!$B$2:$BC$2=L$3)*ISNUMBER(Marks!$B$14:$BC$14)))</f>
-        <v/>
-      </c>
-      <c r="M14" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=M$3)*ISNUMBER(Marks!$B$14:$BC$14))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=M$3)*(Marks!$B$14:$BC$14=1))/SUMPRODUCT((Marks!$B$2:$BC$2=M$3)*ISNUMBER(Marks!$B$14:$BC$14)))</f>
-        <v/>
-      </c>
-      <c r="N14" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=N$3)*ISNUMBER(Marks!$B$14:$BC$14))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=N$3)*(Marks!$B$14:$BC$14=1))/SUMPRODUCT((Marks!$B$2:$BC$2=N$3)*ISNUMBER(Marks!$B$14:$BC$14)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=L$3)*ISNUMBER(Marks!$B$14:$AK$14))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=L$3)*(Marks!$B$14:$AK$14=1))/SUMPRODUCT((Marks!$B$2:$AK$2=L$3)*ISNUMBER(Marks!$B$14:$AK$14)))</f>
         <v/>
       </c>
     </row>
@@ -10002,29 +7524,24 @@
       <c r="D15" s="5" t="n"/>
       <c r="E15" s="5" t="n"/>
       <c r="F15" s="5" t="n"/>
-      <c r="G15" s="5" t="n"/>
+      <c r="H15" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=H$3)*ISNUMBER(Marks!$B$15:$AK$15))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=H$3)*(Marks!$B$15:$AK$15=1))/SUMPRODUCT((Marks!$B$2:$AK$2=H$3)*ISNUMBER(Marks!$B$15:$AK$15)))</f>
+        <v/>
+      </c>
       <c r="I15" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=I$3)*ISNUMBER(Marks!$B$15:$BC$15))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=I$3)*(Marks!$B$15:$BC$15=1))/SUMPRODUCT((Marks!$B$2:$BC$2=I$3)*ISNUMBER(Marks!$B$15:$BC$15)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=I$3)*ISNUMBER(Marks!$B$15:$AK$15))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=I$3)*(Marks!$B$15:$AK$15=1))/SUMPRODUCT((Marks!$B$2:$AK$2=I$3)*ISNUMBER(Marks!$B$15:$AK$15)))</f>
         <v/>
       </c>
       <c r="J15" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=J$3)*ISNUMBER(Marks!$B$15:$BC$15))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=J$3)*(Marks!$B$15:$BC$15=1))/SUMPRODUCT((Marks!$B$2:$BC$2=J$3)*ISNUMBER(Marks!$B$15:$BC$15)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=J$3)*ISNUMBER(Marks!$B$15:$AK$15))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=J$3)*(Marks!$B$15:$AK$15=1))/SUMPRODUCT((Marks!$B$2:$AK$2=J$3)*ISNUMBER(Marks!$B$15:$AK$15)))</f>
         <v/>
       </c>
       <c r="K15" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=K$3)*ISNUMBER(Marks!$B$15:$BC$15))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=K$3)*(Marks!$B$15:$BC$15=1))/SUMPRODUCT((Marks!$B$2:$BC$2=K$3)*ISNUMBER(Marks!$B$15:$BC$15)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=K$3)*ISNUMBER(Marks!$B$15:$AK$15))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=K$3)*(Marks!$B$15:$AK$15=1))/SUMPRODUCT((Marks!$B$2:$AK$2=K$3)*ISNUMBER(Marks!$B$15:$AK$15)))</f>
         <v/>
       </c>
       <c r="L15" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=L$3)*ISNUMBER(Marks!$B$15:$BC$15))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=L$3)*(Marks!$B$15:$BC$15=1))/SUMPRODUCT((Marks!$B$2:$BC$2=L$3)*ISNUMBER(Marks!$B$15:$BC$15)))</f>
-        <v/>
-      </c>
-      <c r="M15" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=M$3)*ISNUMBER(Marks!$B$15:$BC$15))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=M$3)*(Marks!$B$15:$BC$15=1))/SUMPRODUCT((Marks!$B$2:$BC$2=M$3)*ISNUMBER(Marks!$B$15:$BC$15)))</f>
-        <v/>
-      </c>
-      <c r="N15" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=N$3)*ISNUMBER(Marks!$B$15:$BC$15))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=N$3)*(Marks!$B$15:$BC$15=1))/SUMPRODUCT((Marks!$B$2:$BC$2=N$3)*ISNUMBER(Marks!$B$15:$BC$15)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=L$3)*ISNUMBER(Marks!$B$15:$AK$15))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=L$3)*(Marks!$B$15:$AK$15=1))/SUMPRODUCT((Marks!$B$2:$AK$2=L$3)*ISNUMBER(Marks!$B$15:$AK$15)))</f>
         <v/>
       </c>
     </row>
@@ -10037,29 +7554,24 @@
       <c r="D16" s="5" t="n"/>
       <c r="E16" s="5" t="n"/>
       <c r="F16" s="5" t="n"/>
-      <c r="G16" s="5" t="n"/>
+      <c r="H16" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=H$3)*ISNUMBER(Marks!$B$16:$AK$16))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=H$3)*(Marks!$B$16:$AK$16=1))/SUMPRODUCT((Marks!$B$2:$AK$2=H$3)*ISNUMBER(Marks!$B$16:$AK$16)))</f>
+        <v/>
+      </c>
       <c r="I16" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=I$3)*ISNUMBER(Marks!$B$16:$BC$16))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=I$3)*(Marks!$B$16:$BC$16=1))/SUMPRODUCT((Marks!$B$2:$BC$2=I$3)*ISNUMBER(Marks!$B$16:$BC$16)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=I$3)*ISNUMBER(Marks!$B$16:$AK$16))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=I$3)*(Marks!$B$16:$AK$16=1))/SUMPRODUCT((Marks!$B$2:$AK$2=I$3)*ISNUMBER(Marks!$B$16:$AK$16)))</f>
         <v/>
       </c>
       <c r="J16" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=J$3)*ISNUMBER(Marks!$B$16:$BC$16))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=J$3)*(Marks!$B$16:$BC$16=1))/SUMPRODUCT((Marks!$B$2:$BC$2=J$3)*ISNUMBER(Marks!$B$16:$BC$16)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=J$3)*ISNUMBER(Marks!$B$16:$AK$16))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=J$3)*(Marks!$B$16:$AK$16=1))/SUMPRODUCT((Marks!$B$2:$AK$2=J$3)*ISNUMBER(Marks!$B$16:$AK$16)))</f>
         <v/>
       </c>
       <c r="K16" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=K$3)*ISNUMBER(Marks!$B$16:$BC$16))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=K$3)*(Marks!$B$16:$BC$16=1))/SUMPRODUCT((Marks!$B$2:$BC$2=K$3)*ISNUMBER(Marks!$B$16:$BC$16)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=K$3)*ISNUMBER(Marks!$B$16:$AK$16))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=K$3)*(Marks!$B$16:$AK$16=1))/SUMPRODUCT((Marks!$B$2:$AK$2=K$3)*ISNUMBER(Marks!$B$16:$AK$16)))</f>
         <v/>
       </c>
       <c r="L16" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=L$3)*ISNUMBER(Marks!$B$16:$BC$16))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=L$3)*(Marks!$B$16:$BC$16=1))/SUMPRODUCT((Marks!$B$2:$BC$2=L$3)*ISNUMBER(Marks!$B$16:$BC$16)))</f>
-        <v/>
-      </c>
-      <c r="M16" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=M$3)*ISNUMBER(Marks!$B$16:$BC$16))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=M$3)*(Marks!$B$16:$BC$16=1))/SUMPRODUCT((Marks!$B$2:$BC$2=M$3)*ISNUMBER(Marks!$B$16:$BC$16)))</f>
-        <v/>
-      </c>
-      <c r="N16" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=N$3)*ISNUMBER(Marks!$B$16:$BC$16))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=N$3)*(Marks!$B$16:$BC$16=1))/SUMPRODUCT((Marks!$B$2:$BC$2=N$3)*ISNUMBER(Marks!$B$16:$BC$16)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=L$3)*ISNUMBER(Marks!$B$16:$AK$16))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=L$3)*(Marks!$B$16:$AK$16=1))/SUMPRODUCT((Marks!$B$2:$AK$2=L$3)*ISNUMBER(Marks!$B$16:$AK$16)))</f>
         <v/>
       </c>
     </row>
@@ -10072,29 +7584,24 @@
       <c r="D17" s="5" t="n"/>
       <c r="E17" s="5" t="n"/>
       <c r="F17" s="5" t="n"/>
-      <c r="G17" s="5" t="n"/>
+      <c r="H17" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=H$3)*ISNUMBER(Marks!$B$17:$AK$17))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=H$3)*(Marks!$B$17:$AK$17=1))/SUMPRODUCT((Marks!$B$2:$AK$2=H$3)*ISNUMBER(Marks!$B$17:$AK$17)))</f>
+        <v/>
+      </c>
       <c r="I17" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=I$3)*ISNUMBER(Marks!$B$17:$BC$17))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=I$3)*(Marks!$B$17:$BC$17=1))/SUMPRODUCT((Marks!$B$2:$BC$2=I$3)*ISNUMBER(Marks!$B$17:$BC$17)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=I$3)*ISNUMBER(Marks!$B$17:$AK$17))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=I$3)*(Marks!$B$17:$AK$17=1))/SUMPRODUCT((Marks!$B$2:$AK$2=I$3)*ISNUMBER(Marks!$B$17:$AK$17)))</f>
         <v/>
       </c>
       <c r="J17" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=J$3)*ISNUMBER(Marks!$B$17:$BC$17))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=J$3)*(Marks!$B$17:$BC$17=1))/SUMPRODUCT((Marks!$B$2:$BC$2=J$3)*ISNUMBER(Marks!$B$17:$BC$17)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=J$3)*ISNUMBER(Marks!$B$17:$AK$17))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=J$3)*(Marks!$B$17:$AK$17=1))/SUMPRODUCT((Marks!$B$2:$AK$2=J$3)*ISNUMBER(Marks!$B$17:$AK$17)))</f>
         <v/>
       </c>
       <c r="K17" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=K$3)*ISNUMBER(Marks!$B$17:$BC$17))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=K$3)*(Marks!$B$17:$BC$17=1))/SUMPRODUCT((Marks!$B$2:$BC$2=K$3)*ISNUMBER(Marks!$B$17:$BC$17)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=K$3)*ISNUMBER(Marks!$B$17:$AK$17))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=K$3)*(Marks!$B$17:$AK$17=1))/SUMPRODUCT((Marks!$B$2:$AK$2=K$3)*ISNUMBER(Marks!$B$17:$AK$17)))</f>
         <v/>
       </c>
       <c r="L17" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=L$3)*ISNUMBER(Marks!$B$17:$BC$17))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=L$3)*(Marks!$B$17:$BC$17=1))/SUMPRODUCT((Marks!$B$2:$BC$2=L$3)*ISNUMBER(Marks!$B$17:$BC$17)))</f>
-        <v/>
-      </c>
-      <c r="M17" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=M$3)*ISNUMBER(Marks!$B$17:$BC$17))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=M$3)*(Marks!$B$17:$BC$17=1))/SUMPRODUCT((Marks!$B$2:$BC$2=M$3)*ISNUMBER(Marks!$B$17:$BC$17)))</f>
-        <v/>
-      </c>
-      <c r="N17" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=N$3)*ISNUMBER(Marks!$B$17:$BC$17))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=N$3)*(Marks!$B$17:$BC$17=1))/SUMPRODUCT((Marks!$B$2:$BC$2=N$3)*ISNUMBER(Marks!$B$17:$BC$17)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=L$3)*ISNUMBER(Marks!$B$17:$AK$17))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=L$3)*(Marks!$B$17:$AK$17=1))/SUMPRODUCT((Marks!$B$2:$AK$2=L$3)*ISNUMBER(Marks!$B$17:$AK$17)))</f>
         <v/>
       </c>
     </row>
@@ -10107,29 +7614,24 @@
       <c r="D18" s="5" t="n"/>
       <c r="E18" s="5" t="n"/>
       <c r="F18" s="5" t="n"/>
-      <c r="G18" s="5" t="n"/>
+      <c r="H18" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=H$3)*ISNUMBER(Marks!$B$18:$AK$18))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=H$3)*(Marks!$B$18:$AK$18=1))/SUMPRODUCT((Marks!$B$2:$AK$2=H$3)*ISNUMBER(Marks!$B$18:$AK$18)))</f>
+        <v/>
+      </c>
       <c r="I18" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=I$3)*ISNUMBER(Marks!$B$18:$BC$18))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=I$3)*(Marks!$B$18:$BC$18=1))/SUMPRODUCT((Marks!$B$2:$BC$2=I$3)*ISNUMBER(Marks!$B$18:$BC$18)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=I$3)*ISNUMBER(Marks!$B$18:$AK$18))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=I$3)*(Marks!$B$18:$AK$18=1))/SUMPRODUCT((Marks!$B$2:$AK$2=I$3)*ISNUMBER(Marks!$B$18:$AK$18)))</f>
         <v/>
       </c>
       <c r="J18" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=J$3)*ISNUMBER(Marks!$B$18:$BC$18))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=J$3)*(Marks!$B$18:$BC$18=1))/SUMPRODUCT((Marks!$B$2:$BC$2=J$3)*ISNUMBER(Marks!$B$18:$BC$18)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=J$3)*ISNUMBER(Marks!$B$18:$AK$18))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=J$3)*(Marks!$B$18:$AK$18=1))/SUMPRODUCT((Marks!$B$2:$AK$2=J$3)*ISNUMBER(Marks!$B$18:$AK$18)))</f>
         <v/>
       </c>
       <c r="K18" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=K$3)*ISNUMBER(Marks!$B$18:$BC$18))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=K$3)*(Marks!$B$18:$BC$18=1))/SUMPRODUCT((Marks!$B$2:$BC$2=K$3)*ISNUMBER(Marks!$B$18:$BC$18)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=K$3)*ISNUMBER(Marks!$B$18:$AK$18))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=K$3)*(Marks!$B$18:$AK$18=1))/SUMPRODUCT((Marks!$B$2:$AK$2=K$3)*ISNUMBER(Marks!$B$18:$AK$18)))</f>
         <v/>
       </c>
       <c r="L18" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=L$3)*ISNUMBER(Marks!$B$18:$BC$18))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=L$3)*(Marks!$B$18:$BC$18=1))/SUMPRODUCT((Marks!$B$2:$BC$2=L$3)*ISNUMBER(Marks!$B$18:$BC$18)))</f>
-        <v/>
-      </c>
-      <c r="M18" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=M$3)*ISNUMBER(Marks!$B$18:$BC$18))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=M$3)*(Marks!$B$18:$BC$18=1))/SUMPRODUCT((Marks!$B$2:$BC$2=M$3)*ISNUMBER(Marks!$B$18:$BC$18)))</f>
-        <v/>
-      </c>
-      <c r="N18" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=N$3)*ISNUMBER(Marks!$B$18:$BC$18))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=N$3)*(Marks!$B$18:$BC$18=1))/SUMPRODUCT((Marks!$B$2:$BC$2=N$3)*ISNUMBER(Marks!$B$18:$BC$18)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=L$3)*ISNUMBER(Marks!$B$18:$AK$18))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=L$3)*(Marks!$B$18:$AK$18=1))/SUMPRODUCT((Marks!$B$2:$AK$2=L$3)*ISNUMBER(Marks!$B$18:$AK$18)))</f>
         <v/>
       </c>
     </row>
@@ -10142,29 +7644,24 @@
       <c r="D19" s="5" t="n"/>
       <c r="E19" s="5" t="n"/>
       <c r="F19" s="5" t="n"/>
-      <c r="G19" s="5" t="n"/>
+      <c r="H19" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=H$3)*ISNUMBER(Marks!$B$19:$AK$19))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=H$3)*(Marks!$B$19:$AK$19=1))/SUMPRODUCT((Marks!$B$2:$AK$2=H$3)*ISNUMBER(Marks!$B$19:$AK$19)))</f>
+        <v/>
+      </c>
       <c r="I19" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=I$3)*ISNUMBER(Marks!$B$19:$BC$19))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=I$3)*(Marks!$B$19:$BC$19=1))/SUMPRODUCT((Marks!$B$2:$BC$2=I$3)*ISNUMBER(Marks!$B$19:$BC$19)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=I$3)*ISNUMBER(Marks!$B$19:$AK$19))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=I$3)*(Marks!$B$19:$AK$19=1))/SUMPRODUCT((Marks!$B$2:$AK$2=I$3)*ISNUMBER(Marks!$B$19:$AK$19)))</f>
         <v/>
       </c>
       <c r="J19" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=J$3)*ISNUMBER(Marks!$B$19:$BC$19))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=J$3)*(Marks!$B$19:$BC$19=1))/SUMPRODUCT((Marks!$B$2:$BC$2=J$3)*ISNUMBER(Marks!$B$19:$BC$19)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=J$3)*ISNUMBER(Marks!$B$19:$AK$19))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=J$3)*(Marks!$B$19:$AK$19=1))/SUMPRODUCT((Marks!$B$2:$AK$2=J$3)*ISNUMBER(Marks!$B$19:$AK$19)))</f>
         <v/>
       </c>
       <c r="K19" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=K$3)*ISNUMBER(Marks!$B$19:$BC$19))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=K$3)*(Marks!$B$19:$BC$19=1))/SUMPRODUCT((Marks!$B$2:$BC$2=K$3)*ISNUMBER(Marks!$B$19:$BC$19)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=K$3)*ISNUMBER(Marks!$B$19:$AK$19))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=K$3)*(Marks!$B$19:$AK$19=1))/SUMPRODUCT((Marks!$B$2:$AK$2=K$3)*ISNUMBER(Marks!$B$19:$AK$19)))</f>
         <v/>
       </c>
       <c r="L19" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=L$3)*ISNUMBER(Marks!$B$19:$BC$19))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=L$3)*(Marks!$B$19:$BC$19=1))/SUMPRODUCT((Marks!$B$2:$BC$2=L$3)*ISNUMBER(Marks!$B$19:$BC$19)))</f>
-        <v/>
-      </c>
-      <c r="M19" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=M$3)*ISNUMBER(Marks!$B$19:$BC$19))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=M$3)*(Marks!$B$19:$BC$19=1))/SUMPRODUCT((Marks!$B$2:$BC$2=M$3)*ISNUMBER(Marks!$B$19:$BC$19)))</f>
-        <v/>
-      </c>
-      <c r="N19" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=N$3)*ISNUMBER(Marks!$B$19:$BC$19))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=N$3)*(Marks!$B$19:$BC$19=1))/SUMPRODUCT((Marks!$B$2:$BC$2=N$3)*ISNUMBER(Marks!$B$19:$BC$19)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=L$3)*ISNUMBER(Marks!$B$19:$AK$19))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=L$3)*(Marks!$B$19:$AK$19=1))/SUMPRODUCT((Marks!$B$2:$AK$2=L$3)*ISNUMBER(Marks!$B$19:$AK$19)))</f>
         <v/>
       </c>
     </row>
@@ -10177,29 +7674,24 @@
       <c r="D20" s="5" t="n"/>
       <c r="E20" s="5" t="n"/>
       <c r="F20" s="5" t="n"/>
-      <c r="G20" s="5" t="n"/>
+      <c r="H20" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=H$3)*ISNUMBER(Marks!$B$20:$AK$20))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=H$3)*(Marks!$B$20:$AK$20=1))/SUMPRODUCT((Marks!$B$2:$AK$2=H$3)*ISNUMBER(Marks!$B$20:$AK$20)))</f>
+        <v/>
+      </c>
       <c r="I20" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=I$3)*ISNUMBER(Marks!$B$20:$BC$20))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=I$3)*(Marks!$B$20:$BC$20=1))/SUMPRODUCT((Marks!$B$2:$BC$2=I$3)*ISNUMBER(Marks!$B$20:$BC$20)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=I$3)*ISNUMBER(Marks!$B$20:$AK$20))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=I$3)*(Marks!$B$20:$AK$20=1))/SUMPRODUCT((Marks!$B$2:$AK$2=I$3)*ISNUMBER(Marks!$B$20:$AK$20)))</f>
         <v/>
       </c>
       <c r="J20" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=J$3)*ISNUMBER(Marks!$B$20:$BC$20))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=J$3)*(Marks!$B$20:$BC$20=1))/SUMPRODUCT((Marks!$B$2:$BC$2=J$3)*ISNUMBER(Marks!$B$20:$BC$20)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=J$3)*ISNUMBER(Marks!$B$20:$AK$20))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=J$3)*(Marks!$B$20:$AK$20=1))/SUMPRODUCT((Marks!$B$2:$AK$2=J$3)*ISNUMBER(Marks!$B$20:$AK$20)))</f>
         <v/>
       </c>
       <c r="K20" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=K$3)*ISNUMBER(Marks!$B$20:$BC$20))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=K$3)*(Marks!$B$20:$BC$20=1))/SUMPRODUCT((Marks!$B$2:$BC$2=K$3)*ISNUMBER(Marks!$B$20:$BC$20)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=K$3)*ISNUMBER(Marks!$B$20:$AK$20))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=K$3)*(Marks!$B$20:$AK$20=1))/SUMPRODUCT((Marks!$B$2:$AK$2=K$3)*ISNUMBER(Marks!$B$20:$AK$20)))</f>
         <v/>
       </c>
       <c r="L20" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=L$3)*ISNUMBER(Marks!$B$20:$BC$20))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=L$3)*(Marks!$B$20:$BC$20=1))/SUMPRODUCT((Marks!$B$2:$BC$2=L$3)*ISNUMBER(Marks!$B$20:$BC$20)))</f>
-        <v/>
-      </c>
-      <c r="M20" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=M$3)*ISNUMBER(Marks!$B$20:$BC$20))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=M$3)*(Marks!$B$20:$BC$20=1))/SUMPRODUCT((Marks!$B$2:$BC$2=M$3)*ISNUMBER(Marks!$B$20:$BC$20)))</f>
-        <v/>
-      </c>
-      <c r="N20" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=N$3)*ISNUMBER(Marks!$B$20:$BC$20))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=N$3)*(Marks!$B$20:$BC$20=1))/SUMPRODUCT((Marks!$B$2:$BC$2=N$3)*ISNUMBER(Marks!$B$20:$BC$20)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=L$3)*ISNUMBER(Marks!$B$20:$AK$20))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=L$3)*(Marks!$B$20:$AK$20=1))/SUMPRODUCT((Marks!$B$2:$AK$2=L$3)*ISNUMBER(Marks!$B$20:$AK$20)))</f>
         <v/>
       </c>
     </row>
@@ -10212,29 +7704,24 @@
       <c r="D21" s="5" t="n"/>
       <c r="E21" s="5" t="n"/>
       <c r="F21" s="5" t="n"/>
-      <c r="G21" s="5" t="n"/>
+      <c r="H21" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=H$3)*ISNUMBER(Marks!$B$21:$AK$21))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=H$3)*(Marks!$B$21:$AK$21=1))/SUMPRODUCT((Marks!$B$2:$AK$2=H$3)*ISNUMBER(Marks!$B$21:$AK$21)))</f>
+        <v/>
+      </c>
       <c r="I21" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=I$3)*ISNUMBER(Marks!$B$21:$BC$21))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=I$3)*(Marks!$B$21:$BC$21=1))/SUMPRODUCT((Marks!$B$2:$BC$2=I$3)*ISNUMBER(Marks!$B$21:$BC$21)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=I$3)*ISNUMBER(Marks!$B$21:$AK$21))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=I$3)*(Marks!$B$21:$AK$21=1))/SUMPRODUCT((Marks!$B$2:$AK$2=I$3)*ISNUMBER(Marks!$B$21:$AK$21)))</f>
         <v/>
       </c>
       <c r="J21" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=J$3)*ISNUMBER(Marks!$B$21:$BC$21))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=J$3)*(Marks!$B$21:$BC$21=1))/SUMPRODUCT((Marks!$B$2:$BC$2=J$3)*ISNUMBER(Marks!$B$21:$BC$21)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=J$3)*ISNUMBER(Marks!$B$21:$AK$21))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=J$3)*(Marks!$B$21:$AK$21=1))/SUMPRODUCT((Marks!$B$2:$AK$2=J$3)*ISNUMBER(Marks!$B$21:$AK$21)))</f>
         <v/>
       </c>
       <c r="K21" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=K$3)*ISNUMBER(Marks!$B$21:$BC$21))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=K$3)*(Marks!$B$21:$BC$21=1))/SUMPRODUCT((Marks!$B$2:$BC$2=K$3)*ISNUMBER(Marks!$B$21:$BC$21)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=K$3)*ISNUMBER(Marks!$B$21:$AK$21))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=K$3)*(Marks!$B$21:$AK$21=1))/SUMPRODUCT((Marks!$B$2:$AK$2=K$3)*ISNUMBER(Marks!$B$21:$AK$21)))</f>
         <v/>
       </c>
       <c r="L21" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=L$3)*ISNUMBER(Marks!$B$21:$BC$21))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=L$3)*(Marks!$B$21:$BC$21=1))/SUMPRODUCT((Marks!$B$2:$BC$2=L$3)*ISNUMBER(Marks!$B$21:$BC$21)))</f>
-        <v/>
-      </c>
-      <c r="M21" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=M$3)*ISNUMBER(Marks!$B$21:$BC$21))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=M$3)*(Marks!$B$21:$BC$21=1))/SUMPRODUCT((Marks!$B$2:$BC$2=M$3)*ISNUMBER(Marks!$B$21:$BC$21)))</f>
-        <v/>
-      </c>
-      <c r="N21" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=N$3)*ISNUMBER(Marks!$B$21:$BC$21))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=N$3)*(Marks!$B$21:$BC$21=1))/SUMPRODUCT((Marks!$B$2:$BC$2=N$3)*ISNUMBER(Marks!$B$21:$BC$21)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=L$3)*ISNUMBER(Marks!$B$21:$AK$21))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=L$3)*(Marks!$B$21:$AK$21=1))/SUMPRODUCT((Marks!$B$2:$AK$2=L$3)*ISNUMBER(Marks!$B$21:$AK$21)))</f>
         <v/>
       </c>
     </row>
@@ -10247,29 +7734,24 @@
       <c r="D22" s="5" t="n"/>
       <c r="E22" s="5" t="n"/>
       <c r="F22" s="5" t="n"/>
-      <c r="G22" s="5" t="n"/>
+      <c r="H22" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=H$3)*ISNUMBER(Marks!$B$22:$AK$22))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=H$3)*(Marks!$B$22:$AK$22=1))/SUMPRODUCT((Marks!$B$2:$AK$2=H$3)*ISNUMBER(Marks!$B$22:$AK$22)))</f>
+        <v/>
+      </c>
       <c r="I22" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=I$3)*ISNUMBER(Marks!$B$22:$BC$22))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=I$3)*(Marks!$B$22:$BC$22=1))/SUMPRODUCT((Marks!$B$2:$BC$2=I$3)*ISNUMBER(Marks!$B$22:$BC$22)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=I$3)*ISNUMBER(Marks!$B$22:$AK$22))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=I$3)*(Marks!$B$22:$AK$22=1))/SUMPRODUCT((Marks!$B$2:$AK$2=I$3)*ISNUMBER(Marks!$B$22:$AK$22)))</f>
         <v/>
       </c>
       <c r="J22" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=J$3)*ISNUMBER(Marks!$B$22:$BC$22))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=J$3)*(Marks!$B$22:$BC$22=1))/SUMPRODUCT((Marks!$B$2:$BC$2=J$3)*ISNUMBER(Marks!$B$22:$BC$22)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=J$3)*ISNUMBER(Marks!$B$22:$AK$22))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=J$3)*(Marks!$B$22:$AK$22=1))/SUMPRODUCT((Marks!$B$2:$AK$2=J$3)*ISNUMBER(Marks!$B$22:$AK$22)))</f>
         <v/>
       </c>
       <c r="K22" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=K$3)*ISNUMBER(Marks!$B$22:$BC$22))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=K$3)*(Marks!$B$22:$BC$22=1))/SUMPRODUCT((Marks!$B$2:$BC$2=K$3)*ISNUMBER(Marks!$B$22:$BC$22)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=K$3)*ISNUMBER(Marks!$B$22:$AK$22))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=K$3)*(Marks!$B$22:$AK$22=1))/SUMPRODUCT((Marks!$B$2:$AK$2=K$3)*ISNUMBER(Marks!$B$22:$AK$22)))</f>
         <v/>
       </c>
       <c r="L22" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=L$3)*ISNUMBER(Marks!$B$22:$BC$22))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=L$3)*(Marks!$B$22:$BC$22=1))/SUMPRODUCT((Marks!$B$2:$BC$2=L$3)*ISNUMBER(Marks!$B$22:$BC$22)))</f>
-        <v/>
-      </c>
-      <c r="M22" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=M$3)*ISNUMBER(Marks!$B$22:$BC$22))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=M$3)*(Marks!$B$22:$BC$22=1))/SUMPRODUCT((Marks!$B$2:$BC$2=M$3)*ISNUMBER(Marks!$B$22:$BC$22)))</f>
-        <v/>
-      </c>
-      <c r="N22" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=N$3)*ISNUMBER(Marks!$B$22:$BC$22))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=N$3)*(Marks!$B$22:$BC$22=1))/SUMPRODUCT((Marks!$B$2:$BC$2=N$3)*ISNUMBER(Marks!$B$22:$BC$22)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=L$3)*ISNUMBER(Marks!$B$22:$AK$22))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=L$3)*(Marks!$B$22:$AK$22=1))/SUMPRODUCT((Marks!$B$2:$AK$2=L$3)*ISNUMBER(Marks!$B$22:$AK$22)))</f>
         <v/>
       </c>
     </row>
@@ -10282,29 +7764,24 @@
       <c r="D23" s="5" t="n"/>
       <c r="E23" s="5" t="n"/>
       <c r="F23" s="5" t="n"/>
-      <c r="G23" s="5" t="n"/>
+      <c r="H23" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=H$3)*ISNUMBER(Marks!$B$23:$AK$23))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=H$3)*(Marks!$B$23:$AK$23=1))/SUMPRODUCT((Marks!$B$2:$AK$2=H$3)*ISNUMBER(Marks!$B$23:$AK$23)))</f>
+        <v/>
+      </c>
       <c r="I23" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=I$3)*ISNUMBER(Marks!$B$23:$BC$23))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=I$3)*(Marks!$B$23:$BC$23=1))/SUMPRODUCT((Marks!$B$2:$BC$2=I$3)*ISNUMBER(Marks!$B$23:$BC$23)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=I$3)*ISNUMBER(Marks!$B$23:$AK$23))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=I$3)*(Marks!$B$23:$AK$23=1))/SUMPRODUCT((Marks!$B$2:$AK$2=I$3)*ISNUMBER(Marks!$B$23:$AK$23)))</f>
         <v/>
       </c>
       <c r="J23" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=J$3)*ISNUMBER(Marks!$B$23:$BC$23))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=J$3)*(Marks!$B$23:$BC$23=1))/SUMPRODUCT((Marks!$B$2:$BC$2=J$3)*ISNUMBER(Marks!$B$23:$BC$23)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=J$3)*ISNUMBER(Marks!$B$23:$AK$23))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=J$3)*(Marks!$B$23:$AK$23=1))/SUMPRODUCT((Marks!$B$2:$AK$2=J$3)*ISNUMBER(Marks!$B$23:$AK$23)))</f>
         <v/>
       </c>
       <c r="K23" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=K$3)*ISNUMBER(Marks!$B$23:$BC$23))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=K$3)*(Marks!$B$23:$BC$23=1))/SUMPRODUCT((Marks!$B$2:$BC$2=K$3)*ISNUMBER(Marks!$B$23:$BC$23)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=K$3)*ISNUMBER(Marks!$B$23:$AK$23))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=K$3)*(Marks!$B$23:$AK$23=1))/SUMPRODUCT((Marks!$B$2:$AK$2=K$3)*ISNUMBER(Marks!$B$23:$AK$23)))</f>
         <v/>
       </c>
       <c r="L23" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=L$3)*ISNUMBER(Marks!$B$23:$BC$23))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=L$3)*(Marks!$B$23:$BC$23=1))/SUMPRODUCT((Marks!$B$2:$BC$2=L$3)*ISNUMBER(Marks!$B$23:$BC$23)))</f>
-        <v/>
-      </c>
-      <c r="M23" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=M$3)*ISNUMBER(Marks!$B$23:$BC$23))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=M$3)*(Marks!$B$23:$BC$23=1))/SUMPRODUCT((Marks!$B$2:$BC$2=M$3)*ISNUMBER(Marks!$B$23:$BC$23)))</f>
-        <v/>
-      </c>
-      <c r="N23" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=N$3)*ISNUMBER(Marks!$B$23:$BC$23))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=N$3)*(Marks!$B$23:$BC$23=1))/SUMPRODUCT((Marks!$B$2:$BC$2=N$3)*ISNUMBER(Marks!$B$23:$BC$23)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=L$3)*ISNUMBER(Marks!$B$23:$AK$23))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=L$3)*(Marks!$B$23:$AK$23=1))/SUMPRODUCT((Marks!$B$2:$AK$2=L$3)*ISNUMBER(Marks!$B$23:$AK$23)))</f>
         <v/>
       </c>
     </row>
@@ -10317,29 +7794,24 @@
       <c r="D24" s="5" t="n"/>
       <c r="E24" s="5" t="n"/>
       <c r="F24" s="5" t="n"/>
-      <c r="G24" s="5" t="n"/>
+      <c r="H24" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=H$3)*ISNUMBER(Marks!$B$24:$AK$24))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=H$3)*(Marks!$B$24:$AK$24=1))/SUMPRODUCT((Marks!$B$2:$AK$2=H$3)*ISNUMBER(Marks!$B$24:$AK$24)))</f>
+        <v/>
+      </c>
       <c r="I24" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=I$3)*ISNUMBER(Marks!$B$24:$BC$24))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=I$3)*(Marks!$B$24:$BC$24=1))/SUMPRODUCT((Marks!$B$2:$BC$2=I$3)*ISNUMBER(Marks!$B$24:$BC$24)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=I$3)*ISNUMBER(Marks!$B$24:$AK$24))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=I$3)*(Marks!$B$24:$AK$24=1))/SUMPRODUCT((Marks!$B$2:$AK$2=I$3)*ISNUMBER(Marks!$B$24:$AK$24)))</f>
         <v/>
       </c>
       <c r="J24" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=J$3)*ISNUMBER(Marks!$B$24:$BC$24))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=J$3)*(Marks!$B$24:$BC$24=1))/SUMPRODUCT((Marks!$B$2:$BC$2=J$3)*ISNUMBER(Marks!$B$24:$BC$24)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=J$3)*ISNUMBER(Marks!$B$24:$AK$24))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=J$3)*(Marks!$B$24:$AK$24=1))/SUMPRODUCT((Marks!$B$2:$AK$2=J$3)*ISNUMBER(Marks!$B$24:$AK$24)))</f>
         <v/>
       </c>
       <c r="K24" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=K$3)*ISNUMBER(Marks!$B$24:$BC$24))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=K$3)*(Marks!$B$24:$BC$24=1))/SUMPRODUCT((Marks!$B$2:$BC$2=K$3)*ISNUMBER(Marks!$B$24:$BC$24)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=K$3)*ISNUMBER(Marks!$B$24:$AK$24))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=K$3)*(Marks!$B$24:$AK$24=1))/SUMPRODUCT((Marks!$B$2:$AK$2=K$3)*ISNUMBER(Marks!$B$24:$AK$24)))</f>
         <v/>
       </c>
       <c r="L24" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=L$3)*ISNUMBER(Marks!$B$24:$BC$24))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=L$3)*(Marks!$B$24:$BC$24=1))/SUMPRODUCT((Marks!$B$2:$BC$2=L$3)*ISNUMBER(Marks!$B$24:$BC$24)))</f>
-        <v/>
-      </c>
-      <c r="M24" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=M$3)*ISNUMBER(Marks!$B$24:$BC$24))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=M$3)*(Marks!$B$24:$BC$24=1))/SUMPRODUCT((Marks!$B$2:$BC$2=M$3)*ISNUMBER(Marks!$B$24:$BC$24)))</f>
-        <v/>
-      </c>
-      <c r="N24" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=N$3)*ISNUMBER(Marks!$B$24:$BC$24))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=N$3)*(Marks!$B$24:$BC$24=1))/SUMPRODUCT((Marks!$B$2:$BC$2=N$3)*ISNUMBER(Marks!$B$24:$BC$24)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=L$3)*ISNUMBER(Marks!$B$24:$AK$24))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=L$3)*(Marks!$B$24:$AK$24=1))/SUMPRODUCT((Marks!$B$2:$AK$2=L$3)*ISNUMBER(Marks!$B$24:$AK$24)))</f>
         <v/>
       </c>
     </row>
@@ -10352,29 +7824,24 @@
       <c r="D25" s="5" t="n"/>
       <c r="E25" s="5" t="n"/>
       <c r="F25" s="5" t="n"/>
-      <c r="G25" s="5" t="n"/>
+      <c r="H25" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=H$3)*ISNUMBER(Marks!$B$25:$AK$25))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=H$3)*(Marks!$B$25:$AK$25=1))/SUMPRODUCT((Marks!$B$2:$AK$2=H$3)*ISNUMBER(Marks!$B$25:$AK$25)))</f>
+        <v/>
+      </c>
       <c r="I25" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=I$3)*ISNUMBER(Marks!$B$25:$BC$25))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=I$3)*(Marks!$B$25:$BC$25=1))/SUMPRODUCT((Marks!$B$2:$BC$2=I$3)*ISNUMBER(Marks!$B$25:$BC$25)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=I$3)*ISNUMBER(Marks!$B$25:$AK$25))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=I$3)*(Marks!$B$25:$AK$25=1))/SUMPRODUCT((Marks!$B$2:$AK$2=I$3)*ISNUMBER(Marks!$B$25:$AK$25)))</f>
         <v/>
       </c>
       <c r="J25" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=J$3)*ISNUMBER(Marks!$B$25:$BC$25))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=J$3)*(Marks!$B$25:$BC$25=1))/SUMPRODUCT((Marks!$B$2:$BC$2=J$3)*ISNUMBER(Marks!$B$25:$BC$25)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=J$3)*ISNUMBER(Marks!$B$25:$AK$25))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=J$3)*(Marks!$B$25:$AK$25=1))/SUMPRODUCT((Marks!$B$2:$AK$2=J$3)*ISNUMBER(Marks!$B$25:$AK$25)))</f>
         <v/>
       </c>
       <c r="K25" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=K$3)*ISNUMBER(Marks!$B$25:$BC$25))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=K$3)*(Marks!$B$25:$BC$25=1))/SUMPRODUCT((Marks!$B$2:$BC$2=K$3)*ISNUMBER(Marks!$B$25:$BC$25)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=K$3)*ISNUMBER(Marks!$B$25:$AK$25))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=K$3)*(Marks!$B$25:$AK$25=1))/SUMPRODUCT((Marks!$B$2:$AK$2=K$3)*ISNUMBER(Marks!$B$25:$AK$25)))</f>
         <v/>
       </c>
       <c r="L25" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=L$3)*ISNUMBER(Marks!$B$25:$BC$25))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=L$3)*(Marks!$B$25:$BC$25=1))/SUMPRODUCT((Marks!$B$2:$BC$2=L$3)*ISNUMBER(Marks!$B$25:$BC$25)))</f>
-        <v/>
-      </c>
-      <c r="M25" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=M$3)*ISNUMBER(Marks!$B$25:$BC$25))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=M$3)*(Marks!$B$25:$BC$25=1))/SUMPRODUCT((Marks!$B$2:$BC$2=M$3)*ISNUMBER(Marks!$B$25:$BC$25)))</f>
-        <v/>
-      </c>
-      <c r="N25" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=N$3)*ISNUMBER(Marks!$B$25:$BC$25))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=N$3)*(Marks!$B$25:$BC$25=1))/SUMPRODUCT((Marks!$B$2:$BC$2=N$3)*ISNUMBER(Marks!$B$25:$BC$25)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=L$3)*ISNUMBER(Marks!$B$25:$AK$25))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=L$3)*(Marks!$B$25:$AK$25=1))/SUMPRODUCT((Marks!$B$2:$AK$2=L$3)*ISNUMBER(Marks!$B$25:$AK$25)))</f>
         <v/>
       </c>
     </row>
@@ -10387,29 +7854,24 @@
       <c r="D26" s="5" t="n"/>
       <c r="E26" s="5" t="n"/>
       <c r="F26" s="5" t="n"/>
-      <c r="G26" s="5" t="n"/>
+      <c r="H26" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=H$3)*ISNUMBER(Marks!$B$26:$AK$26))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=H$3)*(Marks!$B$26:$AK$26=1))/SUMPRODUCT((Marks!$B$2:$AK$2=H$3)*ISNUMBER(Marks!$B$26:$AK$26)))</f>
+        <v/>
+      </c>
       <c r="I26" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=I$3)*ISNUMBER(Marks!$B$26:$BC$26))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=I$3)*(Marks!$B$26:$BC$26=1))/SUMPRODUCT((Marks!$B$2:$BC$2=I$3)*ISNUMBER(Marks!$B$26:$BC$26)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=I$3)*ISNUMBER(Marks!$B$26:$AK$26))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=I$3)*(Marks!$B$26:$AK$26=1))/SUMPRODUCT((Marks!$B$2:$AK$2=I$3)*ISNUMBER(Marks!$B$26:$AK$26)))</f>
         <v/>
       </c>
       <c r="J26" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=J$3)*ISNUMBER(Marks!$B$26:$BC$26))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=J$3)*(Marks!$B$26:$BC$26=1))/SUMPRODUCT((Marks!$B$2:$BC$2=J$3)*ISNUMBER(Marks!$B$26:$BC$26)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=J$3)*ISNUMBER(Marks!$B$26:$AK$26))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=J$3)*(Marks!$B$26:$AK$26=1))/SUMPRODUCT((Marks!$B$2:$AK$2=J$3)*ISNUMBER(Marks!$B$26:$AK$26)))</f>
         <v/>
       </c>
       <c r="K26" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=K$3)*ISNUMBER(Marks!$B$26:$BC$26))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=K$3)*(Marks!$B$26:$BC$26=1))/SUMPRODUCT((Marks!$B$2:$BC$2=K$3)*ISNUMBER(Marks!$B$26:$BC$26)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=K$3)*ISNUMBER(Marks!$B$26:$AK$26))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=K$3)*(Marks!$B$26:$AK$26=1))/SUMPRODUCT((Marks!$B$2:$AK$2=K$3)*ISNUMBER(Marks!$B$26:$AK$26)))</f>
         <v/>
       </c>
       <c r="L26" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=L$3)*ISNUMBER(Marks!$B$26:$BC$26))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=L$3)*(Marks!$B$26:$BC$26=1))/SUMPRODUCT((Marks!$B$2:$BC$2=L$3)*ISNUMBER(Marks!$B$26:$BC$26)))</f>
-        <v/>
-      </c>
-      <c r="M26" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=M$3)*ISNUMBER(Marks!$B$26:$BC$26))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=M$3)*(Marks!$B$26:$BC$26=1))/SUMPRODUCT((Marks!$B$2:$BC$2=M$3)*ISNUMBER(Marks!$B$26:$BC$26)))</f>
-        <v/>
-      </c>
-      <c r="N26" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=N$3)*ISNUMBER(Marks!$B$26:$BC$26))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=N$3)*(Marks!$B$26:$BC$26=1))/SUMPRODUCT((Marks!$B$2:$BC$2=N$3)*ISNUMBER(Marks!$B$26:$BC$26)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=L$3)*ISNUMBER(Marks!$B$26:$AK$26))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=L$3)*(Marks!$B$26:$AK$26=1))/SUMPRODUCT((Marks!$B$2:$AK$2=L$3)*ISNUMBER(Marks!$B$26:$AK$26)))</f>
         <v/>
       </c>
     </row>
@@ -10422,29 +7884,24 @@
       <c r="D27" s="5" t="n"/>
       <c r="E27" s="5" t="n"/>
       <c r="F27" s="5" t="n"/>
-      <c r="G27" s="5" t="n"/>
+      <c r="H27" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=H$3)*ISNUMBER(Marks!$B$27:$AK$27))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=H$3)*(Marks!$B$27:$AK$27=1))/SUMPRODUCT((Marks!$B$2:$AK$2=H$3)*ISNUMBER(Marks!$B$27:$AK$27)))</f>
+        <v/>
+      </c>
       <c r="I27" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=I$3)*ISNUMBER(Marks!$B$27:$BC$27))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=I$3)*(Marks!$B$27:$BC$27=1))/SUMPRODUCT((Marks!$B$2:$BC$2=I$3)*ISNUMBER(Marks!$B$27:$BC$27)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=I$3)*ISNUMBER(Marks!$B$27:$AK$27))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=I$3)*(Marks!$B$27:$AK$27=1))/SUMPRODUCT((Marks!$B$2:$AK$2=I$3)*ISNUMBER(Marks!$B$27:$AK$27)))</f>
         <v/>
       </c>
       <c r="J27" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=J$3)*ISNUMBER(Marks!$B$27:$BC$27))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=J$3)*(Marks!$B$27:$BC$27=1))/SUMPRODUCT((Marks!$B$2:$BC$2=J$3)*ISNUMBER(Marks!$B$27:$BC$27)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=J$3)*ISNUMBER(Marks!$B$27:$AK$27))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=J$3)*(Marks!$B$27:$AK$27=1))/SUMPRODUCT((Marks!$B$2:$AK$2=J$3)*ISNUMBER(Marks!$B$27:$AK$27)))</f>
         <v/>
       </c>
       <c r="K27" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=K$3)*ISNUMBER(Marks!$B$27:$BC$27))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=K$3)*(Marks!$B$27:$BC$27=1))/SUMPRODUCT((Marks!$B$2:$BC$2=K$3)*ISNUMBER(Marks!$B$27:$BC$27)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=K$3)*ISNUMBER(Marks!$B$27:$AK$27))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=K$3)*(Marks!$B$27:$AK$27=1))/SUMPRODUCT((Marks!$B$2:$AK$2=K$3)*ISNUMBER(Marks!$B$27:$AK$27)))</f>
         <v/>
       </c>
       <c r="L27" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=L$3)*ISNUMBER(Marks!$B$27:$BC$27))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=L$3)*(Marks!$B$27:$BC$27=1))/SUMPRODUCT((Marks!$B$2:$BC$2=L$3)*ISNUMBER(Marks!$B$27:$BC$27)))</f>
-        <v/>
-      </c>
-      <c r="M27" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=M$3)*ISNUMBER(Marks!$B$27:$BC$27))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=M$3)*(Marks!$B$27:$BC$27=1))/SUMPRODUCT((Marks!$B$2:$BC$2=M$3)*ISNUMBER(Marks!$B$27:$BC$27)))</f>
-        <v/>
-      </c>
-      <c r="N27" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=N$3)*ISNUMBER(Marks!$B$27:$BC$27))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=N$3)*(Marks!$B$27:$BC$27=1))/SUMPRODUCT((Marks!$B$2:$BC$2=N$3)*ISNUMBER(Marks!$B$27:$BC$27)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=L$3)*ISNUMBER(Marks!$B$27:$AK$27))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=L$3)*(Marks!$B$27:$AK$27=1))/SUMPRODUCT((Marks!$B$2:$AK$2=L$3)*ISNUMBER(Marks!$B$27:$AK$27)))</f>
         <v/>
       </c>
     </row>
@@ -10457,29 +7914,24 @@
       <c r="D28" s="5" t="n"/>
       <c r="E28" s="5" t="n"/>
       <c r="F28" s="5" t="n"/>
-      <c r="G28" s="5" t="n"/>
+      <c r="H28" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=H$3)*ISNUMBER(Marks!$B$28:$AK$28))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=H$3)*(Marks!$B$28:$AK$28=1))/SUMPRODUCT((Marks!$B$2:$AK$2=H$3)*ISNUMBER(Marks!$B$28:$AK$28)))</f>
+        <v/>
+      </c>
       <c r="I28" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=I$3)*ISNUMBER(Marks!$B$28:$BC$28))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=I$3)*(Marks!$B$28:$BC$28=1))/SUMPRODUCT((Marks!$B$2:$BC$2=I$3)*ISNUMBER(Marks!$B$28:$BC$28)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=I$3)*ISNUMBER(Marks!$B$28:$AK$28))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=I$3)*(Marks!$B$28:$AK$28=1))/SUMPRODUCT((Marks!$B$2:$AK$2=I$3)*ISNUMBER(Marks!$B$28:$AK$28)))</f>
         <v/>
       </c>
       <c r="J28" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=J$3)*ISNUMBER(Marks!$B$28:$BC$28))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=J$3)*(Marks!$B$28:$BC$28=1))/SUMPRODUCT((Marks!$B$2:$BC$2=J$3)*ISNUMBER(Marks!$B$28:$BC$28)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=J$3)*ISNUMBER(Marks!$B$28:$AK$28))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=J$3)*(Marks!$B$28:$AK$28=1))/SUMPRODUCT((Marks!$B$2:$AK$2=J$3)*ISNUMBER(Marks!$B$28:$AK$28)))</f>
         <v/>
       </c>
       <c r="K28" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=K$3)*ISNUMBER(Marks!$B$28:$BC$28))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=K$3)*(Marks!$B$28:$BC$28=1))/SUMPRODUCT((Marks!$B$2:$BC$2=K$3)*ISNUMBER(Marks!$B$28:$BC$28)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=K$3)*ISNUMBER(Marks!$B$28:$AK$28))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=K$3)*(Marks!$B$28:$AK$28=1))/SUMPRODUCT((Marks!$B$2:$AK$2=K$3)*ISNUMBER(Marks!$B$28:$AK$28)))</f>
         <v/>
       </c>
       <c r="L28" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=L$3)*ISNUMBER(Marks!$B$28:$BC$28))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=L$3)*(Marks!$B$28:$BC$28=1))/SUMPRODUCT((Marks!$B$2:$BC$2=L$3)*ISNUMBER(Marks!$B$28:$BC$28)))</f>
-        <v/>
-      </c>
-      <c r="M28" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=M$3)*ISNUMBER(Marks!$B$28:$BC$28))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=M$3)*(Marks!$B$28:$BC$28=1))/SUMPRODUCT((Marks!$B$2:$BC$2=M$3)*ISNUMBER(Marks!$B$28:$BC$28)))</f>
-        <v/>
-      </c>
-      <c r="N28" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=N$3)*ISNUMBER(Marks!$B$28:$BC$28))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=N$3)*(Marks!$B$28:$BC$28=1))/SUMPRODUCT((Marks!$B$2:$BC$2=N$3)*ISNUMBER(Marks!$B$28:$BC$28)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=L$3)*ISNUMBER(Marks!$B$28:$AK$28))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=L$3)*(Marks!$B$28:$AK$28=1))/SUMPRODUCT((Marks!$B$2:$AK$2=L$3)*ISNUMBER(Marks!$B$28:$AK$28)))</f>
         <v/>
       </c>
     </row>
@@ -10492,29 +7944,24 @@
       <c r="D29" s="5" t="n"/>
       <c r="E29" s="5" t="n"/>
       <c r="F29" s="5" t="n"/>
-      <c r="G29" s="5" t="n"/>
+      <c r="H29" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=H$3)*ISNUMBER(Marks!$B$29:$AK$29))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=H$3)*(Marks!$B$29:$AK$29=1))/SUMPRODUCT((Marks!$B$2:$AK$2=H$3)*ISNUMBER(Marks!$B$29:$AK$29)))</f>
+        <v/>
+      </c>
       <c r="I29" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=I$3)*ISNUMBER(Marks!$B$29:$BC$29))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=I$3)*(Marks!$B$29:$BC$29=1))/SUMPRODUCT((Marks!$B$2:$BC$2=I$3)*ISNUMBER(Marks!$B$29:$BC$29)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=I$3)*ISNUMBER(Marks!$B$29:$AK$29))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=I$3)*(Marks!$B$29:$AK$29=1))/SUMPRODUCT((Marks!$B$2:$AK$2=I$3)*ISNUMBER(Marks!$B$29:$AK$29)))</f>
         <v/>
       </c>
       <c r="J29" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=J$3)*ISNUMBER(Marks!$B$29:$BC$29))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=J$3)*(Marks!$B$29:$BC$29=1))/SUMPRODUCT((Marks!$B$2:$BC$2=J$3)*ISNUMBER(Marks!$B$29:$BC$29)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=J$3)*ISNUMBER(Marks!$B$29:$AK$29))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=J$3)*(Marks!$B$29:$AK$29=1))/SUMPRODUCT((Marks!$B$2:$AK$2=J$3)*ISNUMBER(Marks!$B$29:$AK$29)))</f>
         <v/>
       </c>
       <c r="K29" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=K$3)*ISNUMBER(Marks!$B$29:$BC$29))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=K$3)*(Marks!$B$29:$BC$29=1))/SUMPRODUCT((Marks!$B$2:$BC$2=K$3)*ISNUMBER(Marks!$B$29:$BC$29)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=K$3)*ISNUMBER(Marks!$B$29:$AK$29))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=K$3)*(Marks!$B$29:$AK$29=1))/SUMPRODUCT((Marks!$B$2:$AK$2=K$3)*ISNUMBER(Marks!$B$29:$AK$29)))</f>
         <v/>
       </c>
       <c r="L29" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=L$3)*ISNUMBER(Marks!$B$29:$BC$29))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=L$3)*(Marks!$B$29:$BC$29=1))/SUMPRODUCT((Marks!$B$2:$BC$2=L$3)*ISNUMBER(Marks!$B$29:$BC$29)))</f>
-        <v/>
-      </c>
-      <c r="M29" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=M$3)*ISNUMBER(Marks!$B$29:$BC$29))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=M$3)*(Marks!$B$29:$BC$29=1))/SUMPRODUCT((Marks!$B$2:$BC$2=M$3)*ISNUMBER(Marks!$B$29:$BC$29)))</f>
-        <v/>
-      </c>
-      <c r="N29" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=N$3)*ISNUMBER(Marks!$B$29:$BC$29))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=N$3)*(Marks!$B$29:$BC$29=1))/SUMPRODUCT((Marks!$B$2:$BC$2=N$3)*ISNUMBER(Marks!$B$29:$BC$29)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=L$3)*ISNUMBER(Marks!$B$29:$AK$29))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=L$3)*(Marks!$B$29:$AK$29=1))/SUMPRODUCT((Marks!$B$2:$AK$2=L$3)*ISNUMBER(Marks!$B$29:$AK$29)))</f>
         <v/>
       </c>
     </row>
@@ -10527,29 +7974,24 @@
       <c r="D30" s="5" t="n"/>
       <c r="E30" s="5" t="n"/>
       <c r="F30" s="5" t="n"/>
-      <c r="G30" s="5" t="n"/>
+      <c r="H30" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=H$3)*ISNUMBER(Marks!$B$30:$AK$30))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=H$3)*(Marks!$B$30:$AK$30=1))/SUMPRODUCT((Marks!$B$2:$AK$2=H$3)*ISNUMBER(Marks!$B$30:$AK$30)))</f>
+        <v/>
+      </c>
       <c r="I30" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=I$3)*ISNUMBER(Marks!$B$30:$BC$30))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=I$3)*(Marks!$B$30:$BC$30=1))/SUMPRODUCT((Marks!$B$2:$BC$2=I$3)*ISNUMBER(Marks!$B$30:$BC$30)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=I$3)*ISNUMBER(Marks!$B$30:$AK$30))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=I$3)*(Marks!$B$30:$AK$30=1))/SUMPRODUCT((Marks!$B$2:$AK$2=I$3)*ISNUMBER(Marks!$B$30:$AK$30)))</f>
         <v/>
       </c>
       <c r="J30" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=J$3)*ISNUMBER(Marks!$B$30:$BC$30))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=J$3)*(Marks!$B$30:$BC$30=1))/SUMPRODUCT((Marks!$B$2:$BC$2=J$3)*ISNUMBER(Marks!$B$30:$BC$30)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=J$3)*ISNUMBER(Marks!$B$30:$AK$30))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=J$3)*(Marks!$B$30:$AK$30=1))/SUMPRODUCT((Marks!$B$2:$AK$2=J$3)*ISNUMBER(Marks!$B$30:$AK$30)))</f>
         <v/>
       </c>
       <c r="K30" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=K$3)*ISNUMBER(Marks!$B$30:$BC$30))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=K$3)*(Marks!$B$30:$BC$30=1))/SUMPRODUCT((Marks!$B$2:$BC$2=K$3)*ISNUMBER(Marks!$B$30:$BC$30)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=K$3)*ISNUMBER(Marks!$B$30:$AK$30))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=K$3)*(Marks!$B$30:$AK$30=1))/SUMPRODUCT((Marks!$B$2:$AK$2=K$3)*ISNUMBER(Marks!$B$30:$AK$30)))</f>
         <v/>
       </c>
       <c r="L30" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=L$3)*ISNUMBER(Marks!$B$30:$BC$30))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=L$3)*(Marks!$B$30:$BC$30=1))/SUMPRODUCT((Marks!$B$2:$BC$2=L$3)*ISNUMBER(Marks!$B$30:$BC$30)))</f>
-        <v/>
-      </c>
-      <c r="M30" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=M$3)*ISNUMBER(Marks!$B$30:$BC$30))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=M$3)*(Marks!$B$30:$BC$30=1))/SUMPRODUCT((Marks!$B$2:$BC$2=M$3)*ISNUMBER(Marks!$B$30:$BC$30)))</f>
-        <v/>
-      </c>
-      <c r="N30" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=N$3)*ISNUMBER(Marks!$B$30:$BC$30))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=N$3)*(Marks!$B$30:$BC$30=1))/SUMPRODUCT((Marks!$B$2:$BC$2=N$3)*ISNUMBER(Marks!$B$30:$BC$30)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=L$3)*ISNUMBER(Marks!$B$30:$AK$30))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=L$3)*(Marks!$B$30:$AK$30=1))/SUMPRODUCT((Marks!$B$2:$AK$2=L$3)*ISNUMBER(Marks!$B$30:$AK$30)))</f>
         <v/>
       </c>
     </row>
@@ -10562,29 +8004,24 @@
       <c r="D31" s="5" t="n"/>
       <c r="E31" s="5" t="n"/>
       <c r="F31" s="5" t="n"/>
-      <c r="G31" s="5" t="n"/>
+      <c r="H31" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=H$3)*ISNUMBER(Marks!$B$31:$AK$31))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=H$3)*(Marks!$B$31:$AK$31=1))/SUMPRODUCT((Marks!$B$2:$AK$2=H$3)*ISNUMBER(Marks!$B$31:$AK$31)))</f>
+        <v/>
+      </c>
       <c r="I31" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=I$3)*ISNUMBER(Marks!$B$31:$BC$31))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=I$3)*(Marks!$B$31:$BC$31=1))/SUMPRODUCT((Marks!$B$2:$BC$2=I$3)*ISNUMBER(Marks!$B$31:$BC$31)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=I$3)*ISNUMBER(Marks!$B$31:$AK$31))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=I$3)*(Marks!$B$31:$AK$31=1))/SUMPRODUCT((Marks!$B$2:$AK$2=I$3)*ISNUMBER(Marks!$B$31:$AK$31)))</f>
         <v/>
       </c>
       <c r="J31" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=J$3)*ISNUMBER(Marks!$B$31:$BC$31))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=J$3)*(Marks!$B$31:$BC$31=1))/SUMPRODUCT((Marks!$B$2:$BC$2=J$3)*ISNUMBER(Marks!$B$31:$BC$31)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=J$3)*ISNUMBER(Marks!$B$31:$AK$31))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=J$3)*(Marks!$B$31:$AK$31=1))/SUMPRODUCT((Marks!$B$2:$AK$2=J$3)*ISNUMBER(Marks!$B$31:$AK$31)))</f>
         <v/>
       </c>
       <c r="K31" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=K$3)*ISNUMBER(Marks!$B$31:$BC$31))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=K$3)*(Marks!$B$31:$BC$31=1))/SUMPRODUCT((Marks!$B$2:$BC$2=K$3)*ISNUMBER(Marks!$B$31:$BC$31)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=K$3)*ISNUMBER(Marks!$B$31:$AK$31))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=K$3)*(Marks!$B$31:$AK$31=1))/SUMPRODUCT((Marks!$B$2:$AK$2=K$3)*ISNUMBER(Marks!$B$31:$AK$31)))</f>
         <v/>
       </c>
       <c r="L31" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=L$3)*ISNUMBER(Marks!$B$31:$BC$31))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=L$3)*(Marks!$B$31:$BC$31=1))/SUMPRODUCT((Marks!$B$2:$BC$2=L$3)*ISNUMBER(Marks!$B$31:$BC$31)))</f>
-        <v/>
-      </c>
-      <c r="M31" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=M$3)*ISNUMBER(Marks!$B$31:$BC$31))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=M$3)*(Marks!$B$31:$BC$31=1))/SUMPRODUCT((Marks!$B$2:$BC$2=M$3)*ISNUMBER(Marks!$B$31:$BC$31)))</f>
-        <v/>
-      </c>
-      <c r="N31" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=N$3)*ISNUMBER(Marks!$B$31:$BC$31))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=N$3)*(Marks!$B$31:$BC$31=1))/SUMPRODUCT((Marks!$B$2:$BC$2=N$3)*ISNUMBER(Marks!$B$31:$BC$31)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=L$3)*ISNUMBER(Marks!$B$31:$AK$31))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=L$3)*(Marks!$B$31:$AK$31=1))/SUMPRODUCT((Marks!$B$2:$AK$2=L$3)*ISNUMBER(Marks!$B$31:$AK$31)))</f>
         <v/>
       </c>
     </row>
@@ -10597,29 +8034,24 @@
       <c r="D32" s="5" t="n"/>
       <c r="E32" s="5" t="n"/>
       <c r="F32" s="5" t="n"/>
-      <c r="G32" s="5" t="n"/>
+      <c r="H32" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=H$3)*ISNUMBER(Marks!$B$32:$AK$32))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=H$3)*(Marks!$B$32:$AK$32=1))/SUMPRODUCT((Marks!$B$2:$AK$2=H$3)*ISNUMBER(Marks!$B$32:$AK$32)))</f>
+        <v/>
+      </c>
       <c r="I32" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=I$3)*ISNUMBER(Marks!$B$32:$BC$32))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=I$3)*(Marks!$B$32:$BC$32=1))/SUMPRODUCT((Marks!$B$2:$BC$2=I$3)*ISNUMBER(Marks!$B$32:$BC$32)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=I$3)*ISNUMBER(Marks!$B$32:$AK$32))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=I$3)*(Marks!$B$32:$AK$32=1))/SUMPRODUCT((Marks!$B$2:$AK$2=I$3)*ISNUMBER(Marks!$B$32:$AK$32)))</f>
         <v/>
       </c>
       <c r="J32" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=J$3)*ISNUMBER(Marks!$B$32:$BC$32))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=J$3)*(Marks!$B$32:$BC$32=1))/SUMPRODUCT((Marks!$B$2:$BC$2=J$3)*ISNUMBER(Marks!$B$32:$BC$32)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=J$3)*ISNUMBER(Marks!$B$32:$AK$32))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=J$3)*(Marks!$B$32:$AK$32=1))/SUMPRODUCT((Marks!$B$2:$AK$2=J$3)*ISNUMBER(Marks!$B$32:$AK$32)))</f>
         <v/>
       </c>
       <c r="K32" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=K$3)*ISNUMBER(Marks!$B$32:$BC$32))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=K$3)*(Marks!$B$32:$BC$32=1))/SUMPRODUCT((Marks!$B$2:$BC$2=K$3)*ISNUMBER(Marks!$B$32:$BC$32)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=K$3)*ISNUMBER(Marks!$B$32:$AK$32))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=K$3)*(Marks!$B$32:$AK$32=1))/SUMPRODUCT((Marks!$B$2:$AK$2=K$3)*ISNUMBER(Marks!$B$32:$AK$32)))</f>
         <v/>
       </c>
       <c r="L32" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=L$3)*ISNUMBER(Marks!$B$32:$BC$32))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=L$3)*(Marks!$B$32:$BC$32=1))/SUMPRODUCT((Marks!$B$2:$BC$2=L$3)*ISNUMBER(Marks!$B$32:$BC$32)))</f>
-        <v/>
-      </c>
-      <c r="M32" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=M$3)*ISNUMBER(Marks!$B$32:$BC$32))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=M$3)*(Marks!$B$32:$BC$32=1))/SUMPRODUCT((Marks!$B$2:$BC$2=M$3)*ISNUMBER(Marks!$B$32:$BC$32)))</f>
-        <v/>
-      </c>
-      <c r="N32" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=N$3)*ISNUMBER(Marks!$B$32:$BC$32))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=N$3)*(Marks!$B$32:$BC$32=1))/SUMPRODUCT((Marks!$B$2:$BC$2=N$3)*ISNUMBER(Marks!$B$32:$BC$32)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=L$3)*ISNUMBER(Marks!$B$32:$AK$32))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=L$3)*(Marks!$B$32:$AK$32=1))/SUMPRODUCT((Marks!$B$2:$AK$2=L$3)*ISNUMBER(Marks!$B$32:$AK$32)))</f>
         <v/>
       </c>
     </row>
@@ -10632,29 +8064,24 @@
       <c r="D33" s="5" t="n"/>
       <c r="E33" s="5" t="n"/>
       <c r="F33" s="5" t="n"/>
-      <c r="G33" s="5" t="n"/>
+      <c r="H33" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=H$3)*ISNUMBER(Marks!$B$33:$AK$33))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=H$3)*(Marks!$B$33:$AK$33=1))/SUMPRODUCT((Marks!$B$2:$AK$2=H$3)*ISNUMBER(Marks!$B$33:$AK$33)))</f>
+        <v/>
+      </c>
       <c r="I33" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=I$3)*ISNUMBER(Marks!$B$33:$BC$33))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=I$3)*(Marks!$B$33:$BC$33=1))/SUMPRODUCT((Marks!$B$2:$BC$2=I$3)*ISNUMBER(Marks!$B$33:$BC$33)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=I$3)*ISNUMBER(Marks!$B$33:$AK$33))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=I$3)*(Marks!$B$33:$AK$33=1))/SUMPRODUCT((Marks!$B$2:$AK$2=I$3)*ISNUMBER(Marks!$B$33:$AK$33)))</f>
         <v/>
       </c>
       <c r="J33" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=J$3)*ISNUMBER(Marks!$B$33:$BC$33))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=J$3)*(Marks!$B$33:$BC$33=1))/SUMPRODUCT((Marks!$B$2:$BC$2=J$3)*ISNUMBER(Marks!$B$33:$BC$33)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=J$3)*ISNUMBER(Marks!$B$33:$AK$33))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=J$3)*(Marks!$B$33:$AK$33=1))/SUMPRODUCT((Marks!$B$2:$AK$2=J$3)*ISNUMBER(Marks!$B$33:$AK$33)))</f>
         <v/>
       </c>
       <c r="K33" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=K$3)*ISNUMBER(Marks!$B$33:$BC$33))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=K$3)*(Marks!$B$33:$BC$33=1))/SUMPRODUCT((Marks!$B$2:$BC$2=K$3)*ISNUMBER(Marks!$B$33:$BC$33)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=K$3)*ISNUMBER(Marks!$B$33:$AK$33))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=K$3)*(Marks!$B$33:$AK$33=1))/SUMPRODUCT((Marks!$B$2:$AK$2=K$3)*ISNUMBER(Marks!$B$33:$AK$33)))</f>
         <v/>
       </c>
       <c r="L33" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=L$3)*ISNUMBER(Marks!$B$33:$BC$33))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=L$3)*(Marks!$B$33:$BC$33=1))/SUMPRODUCT((Marks!$B$2:$BC$2=L$3)*ISNUMBER(Marks!$B$33:$BC$33)))</f>
-        <v/>
-      </c>
-      <c r="M33" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=M$3)*ISNUMBER(Marks!$B$33:$BC$33))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=M$3)*(Marks!$B$33:$BC$33=1))/SUMPRODUCT((Marks!$B$2:$BC$2=M$3)*ISNUMBER(Marks!$B$33:$BC$33)))</f>
-        <v/>
-      </c>
-      <c r="N33" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=N$3)*ISNUMBER(Marks!$B$33:$BC$33))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=N$3)*(Marks!$B$33:$BC$33=1))/SUMPRODUCT((Marks!$B$2:$BC$2=N$3)*ISNUMBER(Marks!$B$33:$BC$33)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=L$3)*ISNUMBER(Marks!$B$33:$AK$33))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=L$3)*(Marks!$B$33:$AK$33=1))/SUMPRODUCT((Marks!$B$2:$AK$2=L$3)*ISNUMBER(Marks!$B$33:$AK$33)))</f>
         <v/>
       </c>
     </row>
@@ -10667,29 +8094,24 @@
       <c r="D34" s="5" t="n"/>
       <c r="E34" s="5" t="n"/>
       <c r="F34" s="5" t="n"/>
-      <c r="G34" s="5" t="n"/>
+      <c r="H34" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=H$3)*ISNUMBER(Marks!$B$34:$AK$34))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=H$3)*(Marks!$B$34:$AK$34=1))/SUMPRODUCT((Marks!$B$2:$AK$2=H$3)*ISNUMBER(Marks!$B$34:$AK$34)))</f>
+        <v/>
+      </c>
       <c r="I34" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=I$3)*ISNUMBER(Marks!$B$34:$BC$34))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=I$3)*(Marks!$B$34:$BC$34=1))/SUMPRODUCT((Marks!$B$2:$BC$2=I$3)*ISNUMBER(Marks!$B$34:$BC$34)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=I$3)*ISNUMBER(Marks!$B$34:$AK$34))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=I$3)*(Marks!$B$34:$AK$34=1))/SUMPRODUCT((Marks!$B$2:$AK$2=I$3)*ISNUMBER(Marks!$B$34:$AK$34)))</f>
         <v/>
       </c>
       <c r="J34" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=J$3)*ISNUMBER(Marks!$B$34:$BC$34))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=J$3)*(Marks!$B$34:$BC$34=1))/SUMPRODUCT((Marks!$B$2:$BC$2=J$3)*ISNUMBER(Marks!$B$34:$BC$34)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=J$3)*ISNUMBER(Marks!$B$34:$AK$34))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=J$3)*(Marks!$B$34:$AK$34=1))/SUMPRODUCT((Marks!$B$2:$AK$2=J$3)*ISNUMBER(Marks!$B$34:$AK$34)))</f>
         <v/>
       </c>
       <c r="K34" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=K$3)*ISNUMBER(Marks!$B$34:$BC$34))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=K$3)*(Marks!$B$34:$BC$34=1))/SUMPRODUCT((Marks!$B$2:$BC$2=K$3)*ISNUMBER(Marks!$B$34:$BC$34)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=K$3)*ISNUMBER(Marks!$B$34:$AK$34))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=K$3)*(Marks!$B$34:$AK$34=1))/SUMPRODUCT((Marks!$B$2:$AK$2=K$3)*ISNUMBER(Marks!$B$34:$AK$34)))</f>
         <v/>
       </c>
       <c r="L34" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=L$3)*ISNUMBER(Marks!$B$34:$BC$34))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=L$3)*(Marks!$B$34:$BC$34=1))/SUMPRODUCT((Marks!$B$2:$BC$2=L$3)*ISNUMBER(Marks!$B$34:$BC$34)))</f>
-        <v/>
-      </c>
-      <c r="M34" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=M$3)*ISNUMBER(Marks!$B$34:$BC$34))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=M$3)*(Marks!$B$34:$BC$34=1))/SUMPRODUCT((Marks!$B$2:$BC$2=M$3)*ISNUMBER(Marks!$B$34:$BC$34)))</f>
-        <v/>
-      </c>
-      <c r="N34" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=N$3)*ISNUMBER(Marks!$B$34:$BC$34))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=N$3)*(Marks!$B$34:$BC$34=1))/SUMPRODUCT((Marks!$B$2:$BC$2=N$3)*ISNUMBER(Marks!$B$34:$BC$34)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=L$3)*ISNUMBER(Marks!$B$34:$AK$34))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=L$3)*(Marks!$B$34:$AK$34=1))/SUMPRODUCT((Marks!$B$2:$AK$2=L$3)*ISNUMBER(Marks!$B$34:$AK$34)))</f>
         <v/>
       </c>
     </row>
@@ -10702,29 +8124,24 @@
       <c r="D35" s="5" t="n"/>
       <c r="E35" s="5" t="n"/>
       <c r="F35" s="5" t="n"/>
-      <c r="G35" s="5" t="n"/>
+      <c r="H35" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=H$3)*ISNUMBER(Marks!$B$35:$AK$35))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=H$3)*(Marks!$B$35:$AK$35=1))/SUMPRODUCT((Marks!$B$2:$AK$2=H$3)*ISNUMBER(Marks!$B$35:$AK$35)))</f>
+        <v/>
+      </c>
       <c r="I35" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=I$3)*ISNUMBER(Marks!$B$35:$BC$35))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=I$3)*(Marks!$B$35:$BC$35=1))/SUMPRODUCT((Marks!$B$2:$BC$2=I$3)*ISNUMBER(Marks!$B$35:$BC$35)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=I$3)*ISNUMBER(Marks!$B$35:$AK$35))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=I$3)*(Marks!$B$35:$AK$35=1))/SUMPRODUCT((Marks!$B$2:$AK$2=I$3)*ISNUMBER(Marks!$B$35:$AK$35)))</f>
         <v/>
       </c>
       <c r="J35" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=J$3)*ISNUMBER(Marks!$B$35:$BC$35))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=J$3)*(Marks!$B$35:$BC$35=1))/SUMPRODUCT((Marks!$B$2:$BC$2=J$3)*ISNUMBER(Marks!$B$35:$BC$35)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=J$3)*ISNUMBER(Marks!$B$35:$AK$35))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=J$3)*(Marks!$B$35:$AK$35=1))/SUMPRODUCT((Marks!$B$2:$AK$2=J$3)*ISNUMBER(Marks!$B$35:$AK$35)))</f>
         <v/>
       </c>
       <c r="K35" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=K$3)*ISNUMBER(Marks!$B$35:$BC$35))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=K$3)*(Marks!$B$35:$BC$35=1))/SUMPRODUCT((Marks!$B$2:$BC$2=K$3)*ISNUMBER(Marks!$B$35:$BC$35)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=K$3)*ISNUMBER(Marks!$B$35:$AK$35))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=K$3)*(Marks!$B$35:$AK$35=1))/SUMPRODUCT((Marks!$B$2:$AK$2=K$3)*ISNUMBER(Marks!$B$35:$AK$35)))</f>
         <v/>
       </c>
       <c r="L35" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=L$3)*ISNUMBER(Marks!$B$35:$BC$35))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=L$3)*(Marks!$B$35:$BC$35=1))/SUMPRODUCT((Marks!$B$2:$BC$2=L$3)*ISNUMBER(Marks!$B$35:$BC$35)))</f>
-        <v/>
-      </c>
-      <c r="M35" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=M$3)*ISNUMBER(Marks!$B$35:$BC$35))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=M$3)*(Marks!$B$35:$BC$35=1))/SUMPRODUCT((Marks!$B$2:$BC$2=M$3)*ISNUMBER(Marks!$B$35:$BC$35)))</f>
-        <v/>
-      </c>
-      <c r="N35" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=N$3)*ISNUMBER(Marks!$B$35:$BC$35))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=N$3)*(Marks!$B$35:$BC$35=1))/SUMPRODUCT((Marks!$B$2:$BC$2=N$3)*ISNUMBER(Marks!$B$35:$BC$35)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=L$3)*ISNUMBER(Marks!$B$35:$AK$35))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=L$3)*(Marks!$B$35:$AK$35=1))/SUMPRODUCT((Marks!$B$2:$AK$2=L$3)*ISNUMBER(Marks!$B$35:$AK$35)))</f>
         <v/>
       </c>
     </row>
@@ -10737,29 +8154,24 @@
       <c r="D36" s="5" t="n"/>
       <c r="E36" s="5" t="n"/>
       <c r="F36" s="5" t="n"/>
-      <c r="G36" s="5" t="n"/>
+      <c r="H36" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=H$3)*ISNUMBER(Marks!$B$36:$AK$36))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=H$3)*(Marks!$B$36:$AK$36=1))/SUMPRODUCT((Marks!$B$2:$AK$2=H$3)*ISNUMBER(Marks!$B$36:$AK$36)))</f>
+        <v/>
+      </c>
       <c r="I36" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=I$3)*ISNUMBER(Marks!$B$36:$BC$36))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=I$3)*(Marks!$B$36:$BC$36=1))/SUMPRODUCT((Marks!$B$2:$BC$2=I$3)*ISNUMBER(Marks!$B$36:$BC$36)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=I$3)*ISNUMBER(Marks!$B$36:$AK$36))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=I$3)*(Marks!$B$36:$AK$36=1))/SUMPRODUCT((Marks!$B$2:$AK$2=I$3)*ISNUMBER(Marks!$B$36:$AK$36)))</f>
         <v/>
       </c>
       <c r="J36" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=J$3)*ISNUMBER(Marks!$B$36:$BC$36))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=J$3)*(Marks!$B$36:$BC$36=1))/SUMPRODUCT((Marks!$B$2:$BC$2=J$3)*ISNUMBER(Marks!$B$36:$BC$36)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=J$3)*ISNUMBER(Marks!$B$36:$AK$36))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=J$3)*(Marks!$B$36:$AK$36=1))/SUMPRODUCT((Marks!$B$2:$AK$2=J$3)*ISNUMBER(Marks!$B$36:$AK$36)))</f>
         <v/>
       </c>
       <c r="K36" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=K$3)*ISNUMBER(Marks!$B$36:$BC$36))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=K$3)*(Marks!$B$36:$BC$36=1))/SUMPRODUCT((Marks!$B$2:$BC$2=K$3)*ISNUMBER(Marks!$B$36:$BC$36)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=K$3)*ISNUMBER(Marks!$B$36:$AK$36))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=K$3)*(Marks!$B$36:$AK$36=1))/SUMPRODUCT((Marks!$B$2:$AK$2=K$3)*ISNUMBER(Marks!$B$36:$AK$36)))</f>
         <v/>
       </c>
       <c r="L36" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=L$3)*ISNUMBER(Marks!$B$36:$BC$36))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=L$3)*(Marks!$B$36:$BC$36=1))/SUMPRODUCT((Marks!$B$2:$BC$2=L$3)*ISNUMBER(Marks!$B$36:$BC$36)))</f>
-        <v/>
-      </c>
-      <c r="M36" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=M$3)*ISNUMBER(Marks!$B$36:$BC$36))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=M$3)*(Marks!$B$36:$BC$36=1))/SUMPRODUCT((Marks!$B$2:$BC$2=M$3)*ISNUMBER(Marks!$B$36:$BC$36)))</f>
-        <v/>
-      </c>
-      <c r="N36" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=N$3)*ISNUMBER(Marks!$B$36:$BC$36))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=N$3)*(Marks!$B$36:$BC$36=1))/SUMPRODUCT((Marks!$B$2:$BC$2=N$3)*ISNUMBER(Marks!$B$36:$BC$36)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=L$3)*ISNUMBER(Marks!$B$36:$AK$36))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=L$3)*(Marks!$B$36:$AK$36=1))/SUMPRODUCT((Marks!$B$2:$AK$2=L$3)*ISNUMBER(Marks!$B$36:$AK$36)))</f>
         <v/>
       </c>
     </row>
@@ -10772,29 +8184,24 @@
       <c r="D37" s="5" t="n"/>
       <c r="E37" s="5" t="n"/>
       <c r="F37" s="5" t="n"/>
-      <c r="G37" s="5" t="n"/>
+      <c r="H37" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=H$3)*ISNUMBER(Marks!$B$37:$AK$37))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=H$3)*(Marks!$B$37:$AK$37=1))/SUMPRODUCT((Marks!$B$2:$AK$2=H$3)*ISNUMBER(Marks!$B$37:$AK$37)))</f>
+        <v/>
+      </c>
       <c r="I37" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=I$3)*ISNUMBER(Marks!$B$37:$BC$37))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=I$3)*(Marks!$B$37:$BC$37=1))/SUMPRODUCT((Marks!$B$2:$BC$2=I$3)*ISNUMBER(Marks!$B$37:$BC$37)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=I$3)*ISNUMBER(Marks!$B$37:$AK$37))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=I$3)*(Marks!$B$37:$AK$37=1))/SUMPRODUCT((Marks!$B$2:$AK$2=I$3)*ISNUMBER(Marks!$B$37:$AK$37)))</f>
         <v/>
       </c>
       <c r="J37" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=J$3)*ISNUMBER(Marks!$B$37:$BC$37))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=J$3)*(Marks!$B$37:$BC$37=1))/SUMPRODUCT((Marks!$B$2:$BC$2=J$3)*ISNUMBER(Marks!$B$37:$BC$37)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=J$3)*ISNUMBER(Marks!$B$37:$AK$37))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=J$3)*(Marks!$B$37:$AK$37=1))/SUMPRODUCT((Marks!$B$2:$AK$2=J$3)*ISNUMBER(Marks!$B$37:$AK$37)))</f>
         <v/>
       </c>
       <c r="K37" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=K$3)*ISNUMBER(Marks!$B$37:$BC$37))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=K$3)*(Marks!$B$37:$BC$37=1))/SUMPRODUCT((Marks!$B$2:$BC$2=K$3)*ISNUMBER(Marks!$B$37:$BC$37)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=K$3)*ISNUMBER(Marks!$B$37:$AK$37))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=K$3)*(Marks!$B$37:$AK$37=1))/SUMPRODUCT((Marks!$B$2:$AK$2=K$3)*ISNUMBER(Marks!$B$37:$AK$37)))</f>
         <v/>
       </c>
       <c r="L37" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=L$3)*ISNUMBER(Marks!$B$37:$BC$37))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=L$3)*(Marks!$B$37:$BC$37=1))/SUMPRODUCT((Marks!$B$2:$BC$2=L$3)*ISNUMBER(Marks!$B$37:$BC$37)))</f>
-        <v/>
-      </c>
-      <c r="M37" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=M$3)*ISNUMBER(Marks!$B$37:$BC$37))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=M$3)*(Marks!$B$37:$BC$37=1))/SUMPRODUCT((Marks!$B$2:$BC$2=M$3)*ISNUMBER(Marks!$B$37:$BC$37)))</f>
-        <v/>
-      </c>
-      <c r="N37" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=N$3)*ISNUMBER(Marks!$B$37:$BC$37))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=N$3)*(Marks!$B$37:$BC$37=1))/SUMPRODUCT((Marks!$B$2:$BC$2=N$3)*ISNUMBER(Marks!$B$37:$BC$37)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=L$3)*ISNUMBER(Marks!$B$37:$AK$37))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=L$3)*(Marks!$B$37:$AK$37=1))/SUMPRODUCT((Marks!$B$2:$AK$2=L$3)*ISNUMBER(Marks!$B$37:$AK$37)))</f>
         <v/>
       </c>
     </row>
@@ -10807,29 +8214,24 @@
       <c r="D38" s="5" t="n"/>
       <c r="E38" s="5" t="n"/>
       <c r="F38" s="5" t="n"/>
-      <c r="G38" s="5" t="n"/>
+      <c r="H38" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=H$3)*ISNUMBER(Marks!$B$38:$AK$38))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=H$3)*(Marks!$B$38:$AK$38=1))/SUMPRODUCT((Marks!$B$2:$AK$2=H$3)*ISNUMBER(Marks!$B$38:$AK$38)))</f>
+        <v/>
+      </c>
       <c r="I38" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=I$3)*ISNUMBER(Marks!$B$38:$BC$38))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=I$3)*(Marks!$B$38:$BC$38=1))/SUMPRODUCT((Marks!$B$2:$BC$2=I$3)*ISNUMBER(Marks!$B$38:$BC$38)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=I$3)*ISNUMBER(Marks!$B$38:$AK$38))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=I$3)*(Marks!$B$38:$AK$38=1))/SUMPRODUCT((Marks!$B$2:$AK$2=I$3)*ISNUMBER(Marks!$B$38:$AK$38)))</f>
         <v/>
       </c>
       <c r="J38" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=J$3)*ISNUMBER(Marks!$B$38:$BC$38))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=J$3)*(Marks!$B$38:$BC$38=1))/SUMPRODUCT((Marks!$B$2:$BC$2=J$3)*ISNUMBER(Marks!$B$38:$BC$38)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=J$3)*ISNUMBER(Marks!$B$38:$AK$38))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=J$3)*(Marks!$B$38:$AK$38=1))/SUMPRODUCT((Marks!$B$2:$AK$2=J$3)*ISNUMBER(Marks!$B$38:$AK$38)))</f>
         <v/>
       </c>
       <c r="K38" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=K$3)*ISNUMBER(Marks!$B$38:$BC$38))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=K$3)*(Marks!$B$38:$BC$38=1))/SUMPRODUCT((Marks!$B$2:$BC$2=K$3)*ISNUMBER(Marks!$B$38:$BC$38)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=K$3)*ISNUMBER(Marks!$B$38:$AK$38))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=K$3)*(Marks!$B$38:$AK$38=1))/SUMPRODUCT((Marks!$B$2:$AK$2=K$3)*ISNUMBER(Marks!$B$38:$AK$38)))</f>
         <v/>
       </c>
       <c r="L38" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=L$3)*ISNUMBER(Marks!$B$38:$BC$38))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=L$3)*(Marks!$B$38:$BC$38=1))/SUMPRODUCT((Marks!$B$2:$BC$2=L$3)*ISNUMBER(Marks!$B$38:$BC$38)))</f>
-        <v/>
-      </c>
-      <c r="M38" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=M$3)*ISNUMBER(Marks!$B$38:$BC$38))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=M$3)*(Marks!$B$38:$BC$38=1))/SUMPRODUCT((Marks!$B$2:$BC$2=M$3)*ISNUMBER(Marks!$B$38:$BC$38)))</f>
-        <v/>
-      </c>
-      <c r="N38" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=N$3)*ISNUMBER(Marks!$B$38:$BC$38))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=N$3)*(Marks!$B$38:$BC$38=1))/SUMPRODUCT((Marks!$B$2:$BC$2=N$3)*ISNUMBER(Marks!$B$38:$BC$38)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=L$3)*ISNUMBER(Marks!$B$38:$AK$38))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=L$3)*(Marks!$B$38:$AK$38=1))/SUMPRODUCT((Marks!$B$2:$AK$2=L$3)*ISNUMBER(Marks!$B$38:$AK$38)))</f>
         <v/>
       </c>
     </row>
@@ -10842,29 +8244,24 @@
       <c r="D39" s="5" t="n"/>
       <c r="E39" s="5" t="n"/>
       <c r="F39" s="5" t="n"/>
-      <c r="G39" s="5" t="n"/>
+      <c r="H39" s="6">
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=H$3)*ISNUMBER(Marks!$B$39:$AK$39))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=H$3)*(Marks!$B$39:$AK$39=1))/SUMPRODUCT((Marks!$B$2:$AK$2=H$3)*ISNUMBER(Marks!$B$39:$AK$39)))</f>
+        <v/>
+      </c>
       <c r="I39" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=I$3)*ISNUMBER(Marks!$B$39:$BC$39))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=I$3)*(Marks!$B$39:$BC$39=1))/SUMPRODUCT((Marks!$B$2:$BC$2=I$3)*ISNUMBER(Marks!$B$39:$BC$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=I$3)*ISNUMBER(Marks!$B$39:$AK$39))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=I$3)*(Marks!$B$39:$AK$39=1))/SUMPRODUCT((Marks!$B$2:$AK$2=I$3)*ISNUMBER(Marks!$B$39:$AK$39)))</f>
         <v/>
       </c>
       <c r="J39" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=J$3)*ISNUMBER(Marks!$B$39:$BC$39))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=J$3)*(Marks!$B$39:$BC$39=1))/SUMPRODUCT((Marks!$B$2:$BC$2=J$3)*ISNUMBER(Marks!$B$39:$BC$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=J$3)*ISNUMBER(Marks!$B$39:$AK$39))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=J$3)*(Marks!$B$39:$AK$39=1))/SUMPRODUCT((Marks!$B$2:$AK$2=J$3)*ISNUMBER(Marks!$B$39:$AK$39)))</f>
         <v/>
       </c>
       <c r="K39" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=K$3)*ISNUMBER(Marks!$B$39:$BC$39))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=K$3)*(Marks!$B$39:$BC$39=1))/SUMPRODUCT((Marks!$B$2:$BC$2=K$3)*ISNUMBER(Marks!$B$39:$BC$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=K$3)*ISNUMBER(Marks!$B$39:$AK$39))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=K$3)*(Marks!$B$39:$AK$39=1))/SUMPRODUCT((Marks!$B$2:$AK$2=K$3)*ISNUMBER(Marks!$B$39:$AK$39)))</f>
         <v/>
       </c>
       <c r="L39" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=L$3)*ISNUMBER(Marks!$B$39:$BC$39))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=L$3)*(Marks!$B$39:$BC$39=1))/SUMPRODUCT((Marks!$B$2:$BC$2=L$3)*ISNUMBER(Marks!$B$39:$BC$39)))</f>
-        <v/>
-      </c>
-      <c r="M39" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=M$3)*ISNUMBER(Marks!$B$39:$BC$39))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=M$3)*(Marks!$B$39:$BC$39=1))/SUMPRODUCT((Marks!$B$2:$BC$2=M$3)*ISNUMBER(Marks!$B$39:$BC$39)))</f>
-        <v/>
-      </c>
-      <c r="N39" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$BC$2=N$3)*ISNUMBER(Marks!$B$39:$BC$39))=0,"",SUMPRODUCT((Marks!$B$2:$BC$2=N$3)*(Marks!$B$39:$BC$39=1))/SUMPRODUCT((Marks!$B$2:$BC$2=N$3)*ISNUMBER(Marks!$B$39:$BC$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=L$3)*ISNUMBER(Marks!$B$39:$AK$39))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=L$3)*(Marks!$B$39:$AK$39=1))/SUMPRODUCT((Marks!$B$2:$AK$2=L$3)*ISNUMBER(Marks!$B$39:$AK$39)))</f>
         <v/>
       </c>
     </row>
@@ -10900,7 +8297,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Part 1. The week's rules, cold</t>
+          <t>Part 1. Where the revenue went</t>
         </is>
       </c>
       <c r="B43" s="7">
@@ -10908,18 +8305,18 @@
         <v/>
       </c>
       <c r="C43" s="6">
-        <f>IFERROR(INDEX(Tags!$D$5:$D$14,MATCH(1,Tags!$A$5:$A$14,0)),"")</f>
+        <f>IFERROR(INDEX(Tags!$D$5:$D$13,MATCH(1,Tags!$A$5:$A$13,0)),"")</f>
         <v/>
       </c>
       <c r="D43">
-        <f>SUMPRODUCT((B5:B39&gt;=3)*ISNUMBER(I5:I39)*(I5:I39&lt;0.5))</f>
+        <f>SUMPRODUCT((B5:B39&gt;=3)*ISNUMBER(H5:H39)*(H5:H39&lt;0.5))</f>
         <v/>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Part 2. Where did the revenue go</t>
+          <t>Part 2. Which Q1 figure is right</t>
         </is>
       </c>
       <c r="B44" s="7">
@@ -10927,18 +8324,18 @@
         <v/>
       </c>
       <c r="C44" s="6">
-        <f>IFERROR(INDEX(Tags!$D$5:$D$14,MATCH(2,Tags!$A$5:$A$14,0)),"")</f>
+        <f>IFERROR(INDEX(Tags!$D$5:$D$13,MATCH(2,Tags!$A$5:$A$13,0)),"")</f>
         <v/>
       </c>
       <c r="D44">
-        <f>SUMPRODUCT((C5:C39&gt;=3)*ISNUMBER(J5:J39)*(J5:J39&lt;0.5))</f>
+        <f>SUMPRODUCT((C5:C39&gt;=3)*ISNUMBER(I5:I39)*(I5:I39&lt;0.5))</f>
         <v/>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Part 3. Rows you can trust</t>
+          <t>Part 3. Real, worth it, and caused</t>
         </is>
       </c>
       <c r="B45" s="7">
@@ -10946,18 +8343,18 @@
         <v/>
       </c>
       <c r="C45" s="6">
-        <f>IFERROR(INDEX(Tags!$D$5:$D$14,MATCH(3,Tags!$A$5:$A$14,0)),"")</f>
+        <f>IFERROR(INDEX(Tags!$D$5:$D$13,MATCH(3,Tags!$A$5:$A$13,0)),"")</f>
         <v/>
       </c>
       <c r="D45">
-        <f>SUMPRODUCT((D5:D39&gt;=3)*ISNUMBER(K5:K39)*(K5:K39&lt;0.5))</f>
+        <f>SUMPRODUCT((D5:D39&gt;=3)*ISNUMBER(J5:J39)*(J5:J39&lt;0.5))</f>
         <v/>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Part 4. Read the code, read the data</t>
+          <t>Part 4. The same traps, in public</t>
         </is>
       </c>
       <c r="B46" s="7">
@@ -10965,18 +8362,18 @@
         <v/>
       </c>
       <c r="C46" s="6">
-        <f>IFERROR(INDEX(Tags!$D$5:$D$14,MATCH(4,Tags!$A$5:$A$14,0)),"")</f>
+        <f>IFERROR(INDEX(Tags!$D$5:$D$13,MATCH(4,Tags!$A$5:$A$13,0)),"")</f>
         <v/>
       </c>
       <c r="D46">
-        <f>SUMPRODUCT((E5:E39&gt;=3)*ISNUMBER(L5:L39)*(L5:L39&lt;0.5))</f>
+        <f>SUMPRODUCT((E5:E39&gt;=3)*ISNUMBER(K5:K39)*(K5:K39&lt;0.5))</f>
         <v/>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Part 5. Chance and a fair test</t>
+          <t>Part 5. The agent's bill and its logs</t>
         </is>
       </c>
       <c r="B47" s="7">
@@ -10984,30 +8381,11 @@
         <v/>
       </c>
       <c r="C47" s="6">
-        <f>IFERROR(INDEX(Tags!$D$5:$D$14,MATCH(5,Tags!$A$5:$A$14,0)),"")</f>
+        <f>IFERROR(INDEX(Tags!$D$5:$D$13,MATCH(5,Tags!$A$5:$A$13,0)),"")</f>
         <v/>
       </c>
       <c r="D47">
-        <f>SUMPRODUCT((F5:F39&gt;=3)*ISNUMBER(M5:M39)*(M5:M39&lt;0.5))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>Part 6. The numbers</t>
-        </is>
-      </c>
-      <c r="B48" s="7">
-        <f>IF(COUNT(G5:G39)=0,"",AVERAGE(G5:G39))</f>
-        <v/>
-      </c>
-      <c r="C48" s="6">
-        <f>IFERROR(INDEX(Tags!$D$5:$D$14,MATCH(6,Tags!$A$5:$A$14,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D48">
-        <f>SUMPRODUCT((G5:G39&gt;=3)*ISNUMBER(N5:N39)*(N5:N39&lt;0.5))</f>
+        <f>SUMPRODUCT((F5:F39&gt;=3)*ISNUMBER(L5:L39)*(L5:L39&lt;0.5))</f>
         <v/>
       </c>
     </row>

--- a/content/W01/SAT/answer-key/C2_W01_SAT_item_analysis_TRAINER.xlsx
+++ b/content/W01/SAT/answer-key/C2_W01_SAT_item_analysis_TRAINER.xlsx
@@ -509,7 +509,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN39"/>
+  <dimension ref="A1:AM39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -547,7 +547,7 @@
         <v>1</v>
       </c>
       <c r="I2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J2" t="n">
         <v>2</v>
@@ -571,7 +571,7 @@
         <v>2</v>
       </c>
       <c r="Q2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R2" t="n">
         <v>3</v>
@@ -586,10 +586,10 @@
         <v>3</v>
       </c>
       <c r="V2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="W2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="X2" t="n">
         <v>4</v>
@@ -604,10 +604,10 @@
         <v>4</v>
       </c>
       <c r="AB2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AC2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AD2" t="n">
         <v>5</v>
@@ -630,9 +630,6 @@
       <c r="AJ2" t="n">
         <v>5</v>
       </c>
-      <c r="AK2" t="n">
-        <v>5</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -657,165 +654,160 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
+          <t>[S]</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>[S]</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>[D]</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>[S]</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
           <t>[F]</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>[SV]</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>[D]</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>[F]</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>[F]</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>[F]</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
         <is>
           <t>[S]</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>[F]</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
         <is>
           <t>[S]</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>[S]</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>[S]</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>[F]</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>[F]</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>[S]</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>[F]</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>[S]</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>[S]</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>[F]</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>[S]</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
         <is>
           <t>[D]</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>[D]</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>[F]</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>[SV]</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
         <is>
           <t>[S]</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>[F]</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>[SV]</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>[D]</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>[F]</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>[F]</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>[F]</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
+      <c r="AG3" t="inlineStr">
         <is>
           <t>[S]</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>[F]</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
+      <c r="AH3" t="inlineStr">
         <is>
           <t>[S]</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="AI3" t="inlineStr">
         <is>
           <t>[S]</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>[F]</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>[D]</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>[D]</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>[F]</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>[S]</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>[F]</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>[S]</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>[F]</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>[S]</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>[S]</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>[F]</t>
-        </is>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>[SV]</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>[S]</t>
-        </is>
-      </c>
-      <c r="AG3" t="inlineStr">
-        <is>
-          <t>[S]</t>
-        </is>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>[F]</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>[S]</t>
-        </is>
-      </c>
       <c r="AJ3" t="inlineStr">
-        <is>
-          <t>[S]</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
         <is>
           <t>[S]</t>
         </is>
@@ -1004,20 +996,15 @@
       </c>
       <c r="AK4" s="4" t="inlineStr">
         <is>
-          <t>Q36</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="AL4" s="4" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Answered</t>
         </is>
       </c>
       <c r="AM4" s="4" t="inlineStr">
-        <is>
-          <t>Answered</t>
-        </is>
-      </c>
-      <c r="AN4" s="4" t="inlineStr">
         <is>
           <t>Band</t>
         </is>
@@ -1062,17 +1049,16 @@
       <c r="AH5" s="5" t="n"/>
       <c r="AI5" s="5" t="n"/>
       <c r="AJ5" s="5" t="n"/>
-      <c r="AK5" s="5" t="n"/>
+      <c r="AK5">
+        <f>IF(COUNT(B5:AJ5)=0,"",SUM(B5:AJ5))</f>
+        <v/>
+      </c>
       <c r="AL5">
-        <f>IF(COUNT(B5:AK5)=0,"",SUM(B5:AK5))</f>
+        <f>COUNT(B5:AJ5)</f>
         <v/>
       </c>
       <c r="AM5">
-        <f>COUNT(B5:AK5)</f>
-        <v/>
-      </c>
-      <c r="AN5">
-        <f>IF(OR(AL5="",COUNT($AL$5:$AL$39)&lt;3),"",IF(RANK(AL5,$AL$5:$AL$39,0)&lt;=ROUND(COUNT($AL$5:$AL$39)/3,0),"top",IF(RANK(AL5,$AL$5:$AL$39,1)&lt;=ROUND(COUNT($AL$5:$AL$39)/3,0),"bottom","middle")))</f>
+        <f>IF(OR(AK5="",COUNT($AK$5:$AK$39)&lt;3),"",IF(RANK(AK5,$AK$5:$AK$39,0)&lt;=ROUND(COUNT($AK$5:$AK$39)/3,0),"top",IF(RANK(AK5,$AK$5:$AK$39,1)&lt;=ROUND(COUNT($AK$5:$AK$39)/3,0),"bottom","middle")))</f>
         <v/>
       </c>
     </row>
@@ -1115,17 +1101,16 @@
       <c r="AH6" s="5" t="n"/>
       <c r="AI6" s="5" t="n"/>
       <c r="AJ6" s="5" t="n"/>
-      <c r="AK6" s="5" t="n"/>
+      <c r="AK6">
+        <f>IF(COUNT(B6:AJ6)=0,"",SUM(B6:AJ6))</f>
+        <v/>
+      </c>
       <c r="AL6">
-        <f>IF(COUNT(B6:AK6)=0,"",SUM(B6:AK6))</f>
+        <f>COUNT(B6:AJ6)</f>
         <v/>
       </c>
       <c r="AM6">
-        <f>COUNT(B6:AK6)</f>
-        <v/>
-      </c>
-      <c r="AN6">
-        <f>IF(OR(AL6="",COUNT($AL$5:$AL$39)&lt;3),"",IF(RANK(AL6,$AL$5:$AL$39,0)&lt;=ROUND(COUNT($AL$5:$AL$39)/3,0),"top",IF(RANK(AL6,$AL$5:$AL$39,1)&lt;=ROUND(COUNT($AL$5:$AL$39)/3,0),"bottom","middle")))</f>
+        <f>IF(OR(AK6="",COUNT($AK$5:$AK$39)&lt;3),"",IF(RANK(AK6,$AK$5:$AK$39,0)&lt;=ROUND(COUNT($AK$5:$AK$39)/3,0),"top",IF(RANK(AK6,$AK$5:$AK$39,1)&lt;=ROUND(COUNT($AK$5:$AK$39)/3,0),"bottom","middle")))</f>
         <v/>
       </c>
     </row>
@@ -1168,17 +1153,16 @@
       <c r="AH7" s="5" t="n"/>
       <c r="AI7" s="5" t="n"/>
       <c r="AJ7" s="5" t="n"/>
-      <c r="AK7" s="5" t="n"/>
+      <c r="AK7">
+        <f>IF(COUNT(B7:AJ7)=0,"",SUM(B7:AJ7))</f>
+        <v/>
+      </c>
       <c r="AL7">
-        <f>IF(COUNT(B7:AK7)=0,"",SUM(B7:AK7))</f>
+        <f>COUNT(B7:AJ7)</f>
         <v/>
       </c>
       <c r="AM7">
-        <f>COUNT(B7:AK7)</f>
-        <v/>
-      </c>
-      <c r="AN7">
-        <f>IF(OR(AL7="",COUNT($AL$5:$AL$39)&lt;3),"",IF(RANK(AL7,$AL$5:$AL$39,0)&lt;=ROUND(COUNT($AL$5:$AL$39)/3,0),"top",IF(RANK(AL7,$AL$5:$AL$39,1)&lt;=ROUND(COUNT($AL$5:$AL$39)/3,0),"bottom","middle")))</f>
+        <f>IF(OR(AK7="",COUNT($AK$5:$AK$39)&lt;3),"",IF(RANK(AK7,$AK$5:$AK$39,0)&lt;=ROUND(COUNT($AK$5:$AK$39)/3,0),"top",IF(RANK(AK7,$AK$5:$AK$39,1)&lt;=ROUND(COUNT($AK$5:$AK$39)/3,0),"bottom","middle")))</f>
         <v/>
       </c>
     </row>
@@ -1221,17 +1205,16 @@
       <c r="AH8" s="5" t="n"/>
       <c r="AI8" s="5" t="n"/>
       <c r="AJ8" s="5" t="n"/>
-      <c r="AK8" s="5" t="n"/>
+      <c r="AK8">
+        <f>IF(COUNT(B8:AJ8)=0,"",SUM(B8:AJ8))</f>
+        <v/>
+      </c>
       <c r="AL8">
-        <f>IF(COUNT(B8:AK8)=0,"",SUM(B8:AK8))</f>
+        <f>COUNT(B8:AJ8)</f>
         <v/>
       </c>
       <c r="AM8">
-        <f>COUNT(B8:AK8)</f>
-        <v/>
-      </c>
-      <c r="AN8">
-        <f>IF(OR(AL8="",COUNT($AL$5:$AL$39)&lt;3),"",IF(RANK(AL8,$AL$5:$AL$39,0)&lt;=ROUND(COUNT($AL$5:$AL$39)/3,0),"top",IF(RANK(AL8,$AL$5:$AL$39,1)&lt;=ROUND(COUNT($AL$5:$AL$39)/3,0),"bottom","middle")))</f>
+        <f>IF(OR(AK8="",COUNT($AK$5:$AK$39)&lt;3),"",IF(RANK(AK8,$AK$5:$AK$39,0)&lt;=ROUND(COUNT($AK$5:$AK$39)/3,0),"top",IF(RANK(AK8,$AK$5:$AK$39,1)&lt;=ROUND(COUNT($AK$5:$AK$39)/3,0),"bottom","middle")))</f>
         <v/>
       </c>
     </row>
@@ -1274,17 +1257,16 @@
       <c r="AH9" s="5" t="n"/>
       <c r="AI9" s="5" t="n"/>
       <c r="AJ9" s="5" t="n"/>
-      <c r="AK9" s="5" t="n"/>
+      <c r="AK9">
+        <f>IF(COUNT(B9:AJ9)=0,"",SUM(B9:AJ9))</f>
+        <v/>
+      </c>
       <c r="AL9">
-        <f>IF(COUNT(B9:AK9)=0,"",SUM(B9:AK9))</f>
+        <f>COUNT(B9:AJ9)</f>
         <v/>
       </c>
       <c r="AM9">
-        <f>COUNT(B9:AK9)</f>
-        <v/>
-      </c>
-      <c r="AN9">
-        <f>IF(OR(AL9="",COUNT($AL$5:$AL$39)&lt;3),"",IF(RANK(AL9,$AL$5:$AL$39,0)&lt;=ROUND(COUNT($AL$5:$AL$39)/3,0),"top",IF(RANK(AL9,$AL$5:$AL$39,1)&lt;=ROUND(COUNT($AL$5:$AL$39)/3,0),"bottom","middle")))</f>
+        <f>IF(OR(AK9="",COUNT($AK$5:$AK$39)&lt;3),"",IF(RANK(AK9,$AK$5:$AK$39,0)&lt;=ROUND(COUNT($AK$5:$AK$39)/3,0),"top",IF(RANK(AK9,$AK$5:$AK$39,1)&lt;=ROUND(COUNT($AK$5:$AK$39)/3,0),"bottom","middle")))</f>
         <v/>
       </c>
     </row>
@@ -1327,17 +1309,16 @@
       <c r="AH10" s="5" t="n"/>
       <c r="AI10" s="5" t="n"/>
       <c r="AJ10" s="5" t="n"/>
-      <c r="AK10" s="5" t="n"/>
+      <c r="AK10">
+        <f>IF(COUNT(B10:AJ10)=0,"",SUM(B10:AJ10))</f>
+        <v/>
+      </c>
       <c r="AL10">
-        <f>IF(COUNT(B10:AK10)=0,"",SUM(B10:AK10))</f>
+        <f>COUNT(B10:AJ10)</f>
         <v/>
       </c>
       <c r="AM10">
-        <f>COUNT(B10:AK10)</f>
-        <v/>
-      </c>
-      <c r="AN10">
-        <f>IF(OR(AL10="",COUNT($AL$5:$AL$39)&lt;3),"",IF(RANK(AL10,$AL$5:$AL$39,0)&lt;=ROUND(COUNT($AL$5:$AL$39)/3,0),"top",IF(RANK(AL10,$AL$5:$AL$39,1)&lt;=ROUND(COUNT($AL$5:$AL$39)/3,0),"bottom","middle")))</f>
+        <f>IF(OR(AK10="",COUNT($AK$5:$AK$39)&lt;3),"",IF(RANK(AK10,$AK$5:$AK$39,0)&lt;=ROUND(COUNT($AK$5:$AK$39)/3,0),"top",IF(RANK(AK10,$AK$5:$AK$39,1)&lt;=ROUND(COUNT($AK$5:$AK$39)/3,0),"bottom","middle")))</f>
         <v/>
       </c>
     </row>
@@ -1380,17 +1361,16 @@
       <c r="AH11" s="5" t="n"/>
       <c r="AI11" s="5" t="n"/>
       <c r="AJ11" s="5" t="n"/>
-      <c r="AK11" s="5" t="n"/>
+      <c r="AK11">
+        <f>IF(COUNT(B11:AJ11)=0,"",SUM(B11:AJ11))</f>
+        <v/>
+      </c>
       <c r="AL11">
-        <f>IF(COUNT(B11:AK11)=0,"",SUM(B11:AK11))</f>
+        <f>COUNT(B11:AJ11)</f>
         <v/>
       </c>
       <c r="AM11">
-        <f>COUNT(B11:AK11)</f>
-        <v/>
-      </c>
-      <c r="AN11">
-        <f>IF(OR(AL11="",COUNT($AL$5:$AL$39)&lt;3),"",IF(RANK(AL11,$AL$5:$AL$39,0)&lt;=ROUND(COUNT($AL$5:$AL$39)/3,0),"top",IF(RANK(AL11,$AL$5:$AL$39,1)&lt;=ROUND(COUNT($AL$5:$AL$39)/3,0),"bottom","middle")))</f>
+        <f>IF(OR(AK11="",COUNT($AK$5:$AK$39)&lt;3),"",IF(RANK(AK11,$AK$5:$AK$39,0)&lt;=ROUND(COUNT($AK$5:$AK$39)/3,0),"top",IF(RANK(AK11,$AK$5:$AK$39,1)&lt;=ROUND(COUNT($AK$5:$AK$39)/3,0),"bottom","middle")))</f>
         <v/>
       </c>
     </row>
@@ -1433,17 +1413,16 @@
       <c r="AH12" s="5" t="n"/>
       <c r="AI12" s="5" t="n"/>
       <c r="AJ12" s="5" t="n"/>
-      <c r="AK12" s="5" t="n"/>
+      <c r="AK12">
+        <f>IF(COUNT(B12:AJ12)=0,"",SUM(B12:AJ12))</f>
+        <v/>
+      </c>
       <c r="AL12">
-        <f>IF(COUNT(B12:AK12)=0,"",SUM(B12:AK12))</f>
+        <f>COUNT(B12:AJ12)</f>
         <v/>
       </c>
       <c r="AM12">
-        <f>COUNT(B12:AK12)</f>
-        <v/>
-      </c>
-      <c r="AN12">
-        <f>IF(OR(AL12="",COUNT($AL$5:$AL$39)&lt;3),"",IF(RANK(AL12,$AL$5:$AL$39,0)&lt;=ROUND(COUNT($AL$5:$AL$39)/3,0),"top",IF(RANK(AL12,$AL$5:$AL$39,1)&lt;=ROUND(COUNT($AL$5:$AL$39)/3,0),"bottom","middle")))</f>
+        <f>IF(OR(AK12="",COUNT($AK$5:$AK$39)&lt;3),"",IF(RANK(AK12,$AK$5:$AK$39,0)&lt;=ROUND(COUNT($AK$5:$AK$39)/3,0),"top",IF(RANK(AK12,$AK$5:$AK$39,1)&lt;=ROUND(COUNT($AK$5:$AK$39)/3,0),"bottom","middle")))</f>
         <v/>
       </c>
     </row>
@@ -1486,17 +1465,16 @@
       <c r="AH13" s="5" t="n"/>
       <c r="AI13" s="5" t="n"/>
       <c r="AJ13" s="5" t="n"/>
-      <c r="AK13" s="5" t="n"/>
+      <c r="AK13">
+        <f>IF(COUNT(B13:AJ13)=0,"",SUM(B13:AJ13))</f>
+        <v/>
+      </c>
       <c r="AL13">
-        <f>IF(COUNT(B13:AK13)=0,"",SUM(B13:AK13))</f>
+        <f>COUNT(B13:AJ13)</f>
         <v/>
       </c>
       <c r="AM13">
-        <f>COUNT(B13:AK13)</f>
-        <v/>
-      </c>
-      <c r="AN13">
-        <f>IF(OR(AL13="",COUNT($AL$5:$AL$39)&lt;3),"",IF(RANK(AL13,$AL$5:$AL$39,0)&lt;=ROUND(COUNT($AL$5:$AL$39)/3,0),"top",IF(RANK(AL13,$AL$5:$AL$39,1)&lt;=ROUND(COUNT($AL$5:$AL$39)/3,0),"bottom","middle")))</f>
+        <f>IF(OR(AK13="",COUNT($AK$5:$AK$39)&lt;3),"",IF(RANK(AK13,$AK$5:$AK$39,0)&lt;=ROUND(COUNT($AK$5:$AK$39)/3,0),"top",IF(RANK(AK13,$AK$5:$AK$39,1)&lt;=ROUND(COUNT($AK$5:$AK$39)/3,0),"bottom","middle")))</f>
         <v/>
       </c>
     </row>
@@ -1539,17 +1517,16 @@
       <c r="AH14" s="5" t="n"/>
       <c r="AI14" s="5" t="n"/>
       <c r="AJ14" s="5" t="n"/>
-      <c r="AK14" s="5" t="n"/>
+      <c r="AK14">
+        <f>IF(COUNT(B14:AJ14)=0,"",SUM(B14:AJ14))</f>
+        <v/>
+      </c>
       <c r="AL14">
-        <f>IF(COUNT(B14:AK14)=0,"",SUM(B14:AK14))</f>
+        <f>COUNT(B14:AJ14)</f>
         <v/>
       </c>
       <c r="AM14">
-        <f>COUNT(B14:AK14)</f>
-        <v/>
-      </c>
-      <c r="AN14">
-        <f>IF(OR(AL14="",COUNT($AL$5:$AL$39)&lt;3),"",IF(RANK(AL14,$AL$5:$AL$39,0)&lt;=ROUND(COUNT($AL$5:$AL$39)/3,0),"top",IF(RANK(AL14,$AL$5:$AL$39,1)&lt;=ROUND(COUNT($AL$5:$AL$39)/3,0),"bottom","middle")))</f>
+        <f>IF(OR(AK14="",COUNT($AK$5:$AK$39)&lt;3),"",IF(RANK(AK14,$AK$5:$AK$39,0)&lt;=ROUND(COUNT($AK$5:$AK$39)/3,0),"top",IF(RANK(AK14,$AK$5:$AK$39,1)&lt;=ROUND(COUNT($AK$5:$AK$39)/3,0),"bottom","middle")))</f>
         <v/>
       </c>
     </row>
@@ -1592,17 +1569,16 @@
       <c r="AH15" s="5" t="n"/>
       <c r="AI15" s="5" t="n"/>
       <c r="AJ15" s="5" t="n"/>
-      <c r="AK15" s="5" t="n"/>
+      <c r="AK15">
+        <f>IF(COUNT(B15:AJ15)=0,"",SUM(B15:AJ15))</f>
+        <v/>
+      </c>
       <c r="AL15">
-        <f>IF(COUNT(B15:AK15)=0,"",SUM(B15:AK15))</f>
+        <f>COUNT(B15:AJ15)</f>
         <v/>
       </c>
       <c r="AM15">
-        <f>COUNT(B15:AK15)</f>
-        <v/>
-      </c>
-      <c r="AN15">
-        <f>IF(OR(AL15="",COUNT($AL$5:$AL$39)&lt;3),"",IF(RANK(AL15,$AL$5:$AL$39,0)&lt;=ROUND(COUNT($AL$5:$AL$39)/3,0),"top",IF(RANK(AL15,$AL$5:$AL$39,1)&lt;=ROUND(COUNT($AL$5:$AL$39)/3,0),"bottom","middle")))</f>
+        <f>IF(OR(AK15="",COUNT($AK$5:$AK$39)&lt;3),"",IF(RANK(AK15,$AK$5:$AK$39,0)&lt;=ROUND(COUNT($AK$5:$AK$39)/3,0),"top",IF(RANK(AK15,$AK$5:$AK$39,1)&lt;=ROUND(COUNT($AK$5:$AK$39)/3,0),"bottom","middle")))</f>
         <v/>
       </c>
     </row>
@@ -1645,17 +1621,16 @@
       <c r="AH16" s="5" t="n"/>
       <c r="AI16" s="5" t="n"/>
       <c r="AJ16" s="5" t="n"/>
-      <c r="AK16" s="5" t="n"/>
+      <c r="AK16">
+        <f>IF(COUNT(B16:AJ16)=0,"",SUM(B16:AJ16))</f>
+        <v/>
+      </c>
       <c r="AL16">
-        <f>IF(COUNT(B16:AK16)=0,"",SUM(B16:AK16))</f>
+        <f>COUNT(B16:AJ16)</f>
         <v/>
       </c>
       <c r="AM16">
-        <f>COUNT(B16:AK16)</f>
-        <v/>
-      </c>
-      <c r="AN16">
-        <f>IF(OR(AL16="",COUNT($AL$5:$AL$39)&lt;3),"",IF(RANK(AL16,$AL$5:$AL$39,0)&lt;=ROUND(COUNT($AL$5:$AL$39)/3,0),"top",IF(RANK(AL16,$AL$5:$AL$39,1)&lt;=ROUND(COUNT($AL$5:$AL$39)/3,0),"bottom","middle")))</f>
+        <f>IF(OR(AK16="",COUNT($AK$5:$AK$39)&lt;3),"",IF(RANK(AK16,$AK$5:$AK$39,0)&lt;=ROUND(COUNT($AK$5:$AK$39)/3,0),"top",IF(RANK(AK16,$AK$5:$AK$39,1)&lt;=ROUND(COUNT($AK$5:$AK$39)/3,0),"bottom","middle")))</f>
         <v/>
       </c>
     </row>
@@ -1698,17 +1673,16 @@
       <c r="AH17" s="5" t="n"/>
       <c r="AI17" s="5" t="n"/>
       <c r="AJ17" s="5" t="n"/>
-      <c r="AK17" s="5" t="n"/>
+      <c r="AK17">
+        <f>IF(COUNT(B17:AJ17)=0,"",SUM(B17:AJ17))</f>
+        <v/>
+      </c>
       <c r="AL17">
-        <f>IF(COUNT(B17:AK17)=0,"",SUM(B17:AK17))</f>
+        <f>COUNT(B17:AJ17)</f>
         <v/>
       </c>
       <c r="AM17">
-        <f>COUNT(B17:AK17)</f>
-        <v/>
-      </c>
-      <c r="AN17">
-        <f>IF(OR(AL17="",COUNT($AL$5:$AL$39)&lt;3),"",IF(RANK(AL17,$AL$5:$AL$39,0)&lt;=ROUND(COUNT($AL$5:$AL$39)/3,0),"top",IF(RANK(AL17,$AL$5:$AL$39,1)&lt;=ROUND(COUNT($AL$5:$AL$39)/3,0),"bottom","middle")))</f>
+        <f>IF(OR(AK17="",COUNT($AK$5:$AK$39)&lt;3),"",IF(RANK(AK17,$AK$5:$AK$39,0)&lt;=ROUND(COUNT($AK$5:$AK$39)/3,0),"top",IF(RANK(AK17,$AK$5:$AK$39,1)&lt;=ROUND(COUNT($AK$5:$AK$39)/3,0),"bottom","middle")))</f>
         <v/>
       </c>
     </row>
@@ -1751,17 +1725,16 @@
       <c r="AH18" s="5" t="n"/>
       <c r="AI18" s="5" t="n"/>
       <c r="AJ18" s="5" t="n"/>
-      <c r="AK18" s="5" t="n"/>
+      <c r="AK18">
+        <f>IF(COUNT(B18:AJ18)=0,"",SUM(B18:AJ18))</f>
+        <v/>
+      </c>
       <c r="AL18">
-        <f>IF(COUNT(B18:AK18)=0,"",SUM(B18:AK18))</f>
+        <f>COUNT(B18:AJ18)</f>
         <v/>
       </c>
       <c r="AM18">
-        <f>COUNT(B18:AK18)</f>
-        <v/>
-      </c>
-      <c r="AN18">
-        <f>IF(OR(AL18="",COUNT($AL$5:$AL$39)&lt;3),"",IF(RANK(AL18,$AL$5:$AL$39,0)&lt;=ROUND(COUNT($AL$5:$AL$39)/3,0),"top",IF(RANK(AL18,$AL$5:$AL$39,1)&lt;=ROUND(COUNT($AL$5:$AL$39)/3,0),"bottom","middle")))</f>
+        <f>IF(OR(AK18="",COUNT($AK$5:$AK$39)&lt;3),"",IF(RANK(AK18,$AK$5:$AK$39,0)&lt;=ROUND(COUNT($AK$5:$AK$39)/3,0),"top",IF(RANK(AK18,$AK$5:$AK$39,1)&lt;=ROUND(COUNT($AK$5:$AK$39)/3,0),"bottom","middle")))</f>
         <v/>
       </c>
     </row>
@@ -1804,17 +1777,16 @@
       <c r="AH19" s="5" t="n"/>
       <c r="AI19" s="5" t="n"/>
       <c r="AJ19" s="5" t="n"/>
-      <c r="AK19" s="5" t="n"/>
+      <c r="AK19">
+        <f>IF(COUNT(B19:AJ19)=0,"",SUM(B19:AJ19))</f>
+        <v/>
+      </c>
       <c r="AL19">
-        <f>IF(COUNT(B19:AK19)=0,"",SUM(B19:AK19))</f>
+        <f>COUNT(B19:AJ19)</f>
         <v/>
       </c>
       <c r="AM19">
-        <f>COUNT(B19:AK19)</f>
-        <v/>
-      </c>
-      <c r="AN19">
-        <f>IF(OR(AL19="",COUNT($AL$5:$AL$39)&lt;3),"",IF(RANK(AL19,$AL$5:$AL$39,0)&lt;=ROUND(COUNT($AL$5:$AL$39)/3,0),"top",IF(RANK(AL19,$AL$5:$AL$39,1)&lt;=ROUND(COUNT($AL$5:$AL$39)/3,0),"bottom","middle")))</f>
+        <f>IF(OR(AK19="",COUNT($AK$5:$AK$39)&lt;3),"",IF(RANK(AK19,$AK$5:$AK$39,0)&lt;=ROUND(COUNT($AK$5:$AK$39)/3,0),"top",IF(RANK(AK19,$AK$5:$AK$39,1)&lt;=ROUND(COUNT($AK$5:$AK$39)/3,0),"bottom","middle")))</f>
         <v/>
       </c>
     </row>
@@ -1857,17 +1829,16 @@
       <c r="AH20" s="5" t="n"/>
       <c r="AI20" s="5" t="n"/>
       <c r="AJ20" s="5" t="n"/>
-      <c r="AK20" s="5" t="n"/>
+      <c r="AK20">
+        <f>IF(COUNT(B20:AJ20)=0,"",SUM(B20:AJ20))</f>
+        <v/>
+      </c>
       <c r="AL20">
-        <f>IF(COUNT(B20:AK20)=0,"",SUM(B20:AK20))</f>
+        <f>COUNT(B20:AJ20)</f>
         <v/>
       </c>
       <c r="AM20">
-        <f>COUNT(B20:AK20)</f>
-        <v/>
-      </c>
-      <c r="AN20">
-        <f>IF(OR(AL20="",COUNT($AL$5:$AL$39)&lt;3),"",IF(RANK(AL20,$AL$5:$AL$39,0)&lt;=ROUND(COUNT($AL$5:$AL$39)/3,0),"top",IF(RANK(AL20,$AL$5:$AL$39,1)&lt;=ROUND(COUNT($AL$5:$AL$39)/3,0),"bottom","middle")))</f>
+        <f>IF(OR(AK20="",COUNT($AK$5:$AK$39)&lt;3),"",IF(RANK(AK20,$AK$5:$AK$39,0)&lt;=ROUND(COUNT($AK$5:$AK$39)/3,0),"top",IF(RANK(AK20,$AK$5:$AK$39,1)&lt;=ROUND(COUNT($AK$5:$AK$39)/3,0),"bottom","middle")))</f>
         <v/>
       </c>
     </row>
@@ -1910,17 +1881,16 @@
       <c r="AH21" s="5" t="n"/>
       <c r="AI21" s="5" t="n"/>
       <c r="AJ21" s="5" t="n"/>
-      <c r="AK21" s="5" t="n"/>
+      <c r="AK21">
+        <f>IF(COUNT(B21:AJ21)=0,"",SUM(B21:AJ21))</f>
+        <v/>
+      </c>
       <c r="AL21">
-        <f>IF(COUNT(B21:AK21)=0,"",SUM(B21:AK21))</f>
+        <f>COUNT(B21:AJ21)</f>
         <v/>
       </c>
       <c r="AM21">
-        <f>COUNT(B21:AK21)</f>
-        <v/>
-      </c>
-      <c r="AN21">
-        <f>IF(OR(AL21="",COUNT($AL$5:$AL$39)&lt;3),"",IF(RANK(AL21,$AL$5:$AL$39,0)&lt;=ROUND(COUNT($AL$5:$AL$39)/3,0),"top",IF(RANK(AL21,$AL$5:$AL$39,1)&lt;=ROUND(COUNT($AL$5:$AL$39)/3,0),"bottom","middle")))</f>
+        <f>IF(OR(AK21="",COUNT($AK$5:$AK$39)&lt;3),"",IF(RANK(AK21,$AK$5:$AK$39,0)&lt;=ROUND(COUNT($AK$5:$AK$39)/3,0),"top",IF(RANK(AK21,$AK$5:$AK$39,1)&lt;=ROUND(COUNT($AK$5:$AK$39)/3,0),"bottom","middle")))</f>
         <v/>
       </c>
     </row>
@@ -1963,17 +1933,16 @@
       <c r="AH22" s="5" t="n"/>
       <c r="AI22" s="5" t="n"/>
       <c r="AJ22" s="5" t="n"/>
-      <c r="AK22" s="5" t="n"/>
+      <c r="AK22">
+        <f>IF(COUNT(B22:AJ22)=0,"",SUM(B22:AJ22))</f>
+        <v/>
+      </c>
       <c r="AL22">
-        <f>IF(COUNT(B22:AK22)=0,"",SUM(B22:AK22))</f>
+        <f>COUNT(B22:AJ22)</f>
         <v/>
       </c>
       <c r="AM22">
-        <f>COUNT(B22:AK22)</f>
-        <v/>
-      </c>
-      <c r="AN22">
-        <f>IF(OR(AL22="",COUNT($AL$5:$AL$39)&lt;3),"",IF(RANK(AL22,$AL$5:$AL$39,0)&lt;=ROUND(COUNT($AL$5:$AL$39)/3,0),"top",IF(RANK(AL22,$AL$5:$AL$39,1)&lt;=ROUND(COUNT($AL$5:$AL$39)/3,0),"bottom","middle")))</f>
+        <f>IF(OR(AK22="",COUNT($AK$5:$AK$39)&lt;3),"",IF(RANK(AK22,$AK$5:$AK$39,0)&lt;=ROUND(COUNT($AK$5:$AK$39)/3,0),"top",IF(RANK(AK22,$AK$5:$AK$39,1)&lt;=ROUND(COUNT($AK$5:$AK$39)/3,0),"bottom","middle")))</f>
         <v/>
       </c>
     </row>
@@ -2016,17 +1985,16 @@
       <c r="AH23" s="5" t="n"/>
       <c r="AI23" s="5" t="n"/>
       <c r="AJ23" s="5" t="n"/>
-      <c r="AK23" s="5" t="n"/>
+      <c r="AK23">
+        <f>IF(COUNT(B23:AJ23)=0,"",SUM(B23:AJ23))</f>
+        <v/>
+      </c>
       <c r="AL23">
-        <f>IF(COUNT(B23:AK23)=0,"",SUM(B23:AK23))</f>
+        <f>COUNT(B23:AJ23)</f>
         <v/>
       </c>
       <c r="AM23">
-        <f>COUNT(B23:AK23)</f>
-        <v/>
-      </c>
-      <c r="AN23">
-        <f>IF(OR(AL23="",COUNT($AL$5:$AL$39)&lt;3),"",IF(RANK(AL23,$AL$5:$AL$39,0)&lt;=ROUND(COUNT($AL$5:$AL$39)/3,0),"top",IF(RANK(AL23,$AL$5:$AL$39,1)&lt;=ROUND(COUNT($AL$5:$AL$39)/3,0),"bottom","middle")))</f>
+        <f>IF(OR(AK23="",COUNT($AK$5:$AK$39)&lt;3),"",IF(RANK(AK23,$AK$5:$AK$39,0)&lt;=ROUND(COUNT($AK$5:$AK$39)/3,0),"top",IF(RANK(AK23,$AK$5:$AK$39,1)&lt;=ROUND(COUNT($AK$5:$AK$39)/3,0),"bottom","middle")))</f>
         <v/>
       </c>
     </row>
@@ -2069,17 +2037,16 @@
       <c r="AH24" s="5" t="n"/>
       <c r="AI24" s="5" t="n"/>
       <c r="AJ24" s="5" t="n"/>
-      <c r="AK24" s="5" t="n"/>
+      <c r="AK24">
+        <f>IF(COUNT(B24:AJ24)=0,"",SUM(B24:AJ24))</f>
+        <v/>
+      </c>
       <c r="AL24">
-        <f>IF(COUNT(B24:AK24)=0,"",SUM(B24:AK24))</f>
+        <f>COUNT(B24:AJ24)</f>
         <v/>
       </c>
       <c r="AM24">
-        <f>COUNT(B24:AK24)</f>
-        <v/>
-      </c>
-      <c r="AN24">
-        <f>IF(OR(AL24="",COUNT($AL$5:$AL$39)&lt;3),"",IF(RANK(AL24,$AL$5:$AL$39,0)&lt;=ROUND(COUNT($AL$5:$AL$39)/3,0),"top",IF(RANK(AL24,$AL$5:$AL$39,1)&lt;=ROUND(COUNT($AL$5:$AL$39)/3,0),"bottom","middle")))</f>
+        <f>IF(OR(AK24="",COUNT($AK$5:$AK$39)&lt;3),"",IF(RANK(AK24,$AK$5:$AK$39,0)&lt;=ROUND(COUNT($AK$5:$AK$39)/3,0),"top",IF(RANK(AK24,$AK$5:$AK$39,1)&lt;=ROUND(COUNT($AK$5:$AK$39)/3,0),"bottom","middle")))</f>
         <v/>
       </c>
     </row>
@@ -2122,17 +2089,16 @@
       <c r="AH25" s="5" t="n"/>
       <c r="AI25" s="5" t="n"/>
       <c r="AJ25" s="5" t="n"/>
-      <c r="AK25" s="5" t="n"/>
+      <c r="AK25">
+        <f>IF(COUNT(B25:AJ25)=0,"",SUM(B25:AJ25))</f>
+        <v/>
+      </c>
       <c r="AL25">
-        <f>IF(COUNT(B25:AK25)=0,"",SUM(B25:AK25))</f>
+        <f>COUNT(B25:AJ25)</f>
         <v/>
       </c>
       <c r="AM25">
-        <f>COUNT(B25:AK25)</f>
-        <v/>
-      </c>
-      <c r="AN25">
-        <f>IF(OR(AL25="",COUNT($AL$5:$AL$39)&lt;3),"",IF(RANK(AL25,$AL$5:$AL$39,0)&lt;=ROUND(COUNT($AL$5:$AL$39)/3,0),"top",IF(RANK(AL25,$AL$5:$AL$39,1)&lt;=ROUND(COUNT($AL$5:$AL$39)/3,0),"bottom","middle")))</f>
+        <f>IF(OR(AK25="",COUNT($AK$5:$AK$39)&lt;3),"",IF(RANK(AK25,$AK$5:$AK$39,0)&lt;=ROUND(COUNT($AK$5:$AK$39)/3,0),"top",IF(RANK(AK25,$AK$5:$AK$39,1)&lt;=ROUND(COUNT($AK$5:$AK$39)/3,0),"bottom","middle")))</f>
         <v/>
       </c>
     </row>
@@ -2175,17 +2141,16 @@
       <c r="AH26" s="5" t="n"/>
       <c r="AI26" s="5" t="n"/>
       <c r="AJ26" s="5" t="n"/>
-      <c r="AK26" s="5" t="n"/>
+      <c r="AK26">
+        <f>IF(COUNT(B26:AJ26)=0,"",SUM(B26:AJ26))</f>
+        <v/>
+      </c>
       <c r="AL26">
-        <f>IF(COUNT(B26:AK26)=0,"",SUM(B26:AK26))</f>
+        <f>COUNT(B26:AJ26)</f>
         <v/>
       </c>
       <c r="AM26">
-        <f>COUNT(B26:AK26)</f>
-        <v/>
-      </c>
-      <c r="AN26">
-        <f>IF(OR(AL26="",COUNT($AL$5:$AL$39)&lt;3),"",IF(RANK(AL26,$AL$5:$AL$39,0)&lt;=ROUND(COUNT($AL$5:$AL$39)/3,0),"top",IF(RANK(AL26,$AL$5:$AL$39,1)&lt;=ROUND(COUNT($AL$5:$AL$39)/3,0),"bottom","middle")))</f>
+        <f>IF(OR(AK26="",COUNT($AK$5:$AK$39)&lt;3),"",IF(RANK(AK26,$AK$5:$AK$39,0)&lt;=ROUND(COUNT($AK$5:$AK$39)/3,0),"top",IF(RANK(AK26,$AK$5:$AK$39,1)&lt;=ROUND(COUNT($AK$5:$AK$39)/3,0),"bottom","middle")))</f>
         <v/>
       </c>
     </row>
@@ -2228,17 +2193,16 @@
       <c r="AH27" s="5" t="n"/>
       <c r="AI27" s="5" t="n"/>
       <c r="AJ27" s="5" t="n"/>
-      <c r="AK27" s="5" t="n"/>
+      <c r="AK27">
+        <f>IF(COUNT(B27:AJ27)=0,"",SUM(B27:AJ27))</f>
+        <v/>
+      </c>
       <c r="AL27">
-        <f>IF(COUNT(B27:AK27)=0,"",SUM(B27:AK27))</f>
+        <f>COUNT(B27:AJ27)</f>
         <v/>
       </c>
       <c r="AM27">
-        <f>COUNT(B27:AK27)</f>
-        <v/>
-      </c>
-      <c r="AN27">
-        <f>IF(OR(AL27="",COUNT($AL$5:$AL$39)&lt;3),"",IF(RANK(AL27,$AL$5:$AL$39,0)&lt;=ROUND(COUNT($AL$5:$AL$39)/3,0),"top",IF(RANK(AL27,$AL$5:$AL$39,1)&lt;=ROUND(COUNT($AL$5:$AL$39)/3,0),"bottom","middle")))</f>
+        <f>IF(OR(AK27="",COUNT($AK$5:$AK$39)&lt;3),"",IF(RANK(AK27,$AK$5:$AK$39,0)&lt;=ROUND(COUNT($AK$5:$AK$39)/3,0),"top",IF(RANK(AK27,$AK$5:$AK$39,1)&lt;=ROUND(COUNT($AK$5:$AK$39)/3,0),"bottom","middle")))</f>
         <v/>
       </c>
     </row>
@@ -2281,17 +2245,16 @@
       <c r="AH28" s="5" t="n"/>
       <c r="AI28" s="5" t="n"/>
       <c r="AJ28" s="5" t="n"/>
-      <c r="AK28" s="5" t="n"/>
+      <c r="AK28">
+        <f>IF(COUNT(B28:AJ28)=0,"",SUM(B28:AJ28))</f>
+        <v/>
+      </c>
       <c r="AL28">
-        <f>IF(COUNT(B28:AK28)=0,"",SUM(B28:AK28))</f>
+        <f>COUNT(B28:AJ28)</f>
         <v/>
       </c>
       <c r="AM28">
-        <f>COUNT(B28:AK28)</f>
-        <v/>
-      </c>
-      <c r="AN28">
-        <f>IF(OR(AL28="",COUNT($AL$5:$AL$39)&lt;3),"",IF(RANK(AL28,$AL$5:$AL$39,0)&lt;=ROUND(COUNT($AL$5:$AL$39)/3,0),"top",IF(RANK(AL28,$AL$5:$AL$39,1)&lt;=ROUND(COUNT($AL$5:$AL$39)/3,0),"bottom","middle")))</f>
+        <f>IF(OR(AK28="",COUNT($AK$5:$AK$39)&lt;3),"",IF(RANK(AK28,$AK$5:$AK$39,0)&lt;=ROUND(COUNT($AK$5:$AK$39)/3,0),"top",IF(RANK(AK28,$AK$5:$AK$39,1)&lt;=ROUND(COUNT($AK$5:$AK$39)/3,0),"bottom","middle")))</f>
         <v/>
       </c>
     </row>
@@ -2334,17 +2297,16 @@
       <c r="AH29" s="5" t="n"/>
       <c r="AI29" s="5" t="n"/>
       <c r="AJ29" s="5" t="n"/>
-      <c r="AK29" s="5" t="n"/>
+      <c r="AK29">
+        <f>IF(COUNT(B29:AJ29)=0,"",SUM(B29:AJ29))</f>
+        <v/>
+      </c>
       <c r="AL29">
-        <f>IF(COUNT(B29:AK29)=0,"",SUM(B29:AK29))</f>
+        <f>COUNT(B29:AJ29)</f>
         <v/>
       </c>
       <c r="AM29">
-        <f>COUNT(B29:AK29)</f>
-        <v/>
-      </c>
-      <c r="AN29">
-        <f>IF(OR(AL29="",COUNT($AL$5:$AL$39)&lt;3),"",IF(RANK(AL29,$AL$5:$AL$39,0)&lt;=ROUND(COUNT($AL$5:$AL$39)/3,0),"top",IF(RANK(AL29,$AL$5:$AL$39,1)&lt;=ROUND(COUNT($AL$5:$AL$39)/3,0),"bottom","middle")))</f>
+        <f>IF(OR(AK29="",COUNT($AK$5:$AK$39)&lt;3),"",IF(RANK(AK29,$AK$5:$AK$39,0)&lt;=ROUND(COUNT($AK$5:$AK$39)/3,0),"top",IF(RANK(AK29,$AK$5:$AK$39,1)&lt;=ROUND(COUNT($AK$5:$AK$39)/3,0),"bottom","middle")))</f>
         <v/>
       </c>
     </row>
@@ -2387,17 +2349,16 @@
       <c r="AH30" s="5" t="n"/>
       <c r="AI30" s="5" t="n"/>
       <c r="AJ30" s="5" t="n"/>
-      <c r="AK30" s="5" t="n"/>
+      <c r="AK30">
+        <f>IF(COUNT(B30:AJ30)=0,"",SUM(B30:AJ30))</f>
+        <v/>
+      </c>
       <c r="AL30">
-        <f>IF(COUNT(B30:AK30)=0,"",SUM(B30:AK30))</f>
+        <f>COUNT(B30:AJ30)</f>
         <v/>
       </c>
       <c r="AM30">
-        <f>COUNT(B30:AK30)</f>
-        <v/>
-      </c>
-      <c r="AN30">
-        <f>IF(OR(AL30="",COUNT($AL$5:$AL$39)&lt;3),"",IF(RANK(AL30,$AL$5:$AL$39,0)&lt;=ROUND(COUNT($AL$5:$AL$39)/3,0),"top",IF(RANK(AL30,$AL$5:$AL$39,1)&lt;=ROUND(COUNT($AL$5:$AL$39)/3,0),"bottom","middle")))</f>
+        <f>IF(OR(AK30="",COUNT($AK$5:$AK$39)&lt;3),"",IF(RANK(AK30,$AK$5:$AK$39,0)&lt;=ROUND(COUNT($AK$5:$AK$39)/3,0),"top",IF(RANK(AK30,$AK$5:$AK$39,1)&lt;=ROUND(COUNT($AK$5:$AK$39)/3,0),"bottom","middle")))</f>
         <v/>
       </c>
     </row>
@@ -2440,17 +2401,16 @@
       <c r="AH31" s="5" t="n"/>
       <c r="AI31" s="5" t="n"/>
       <c r="AJ31" s="5" t="n"/>
-      <c r="AK31" s="5" t="n"/>
+      <c r="AK31">
+        <f>IF(COUNT(B31:AJ31)=0,"",SUM(B31:AJ31))</f>
+        <v/>
+      </c>
       <c r="AL31">
-        <f>IF(COUNT(B31:AK31)=0,"",SUM(B31:AK31))</f>
+        <f>COUNT(B31:AJ31)</f>
         <v/>
       </c>
       <c r="AM31">
-        <f>COUNT(B31:AK31)</f>
-        <v/>
-      </c>
-      <c r="AN31">
-        <f>IF(OR(AL31="",COUNT($AL$5:$AL$39)&lt;3),"",IF(RANK(AL31,$AL$5:$AL$39,0)&lt;=ROUND(COUNT($AL$5:$AL$39)/3,0),"top",IF(RANK(AL31,$AL$5:$AL$39,1)&lt;=ROUND(COUNT($AL$5:$AL$39)/3,0),"bottom","middle")))</f>
+        <f>IF(OR(AK31="",COUNT($AK$5:$AK$39)&lt;3),"",IF(RANK(AK31,$AK$5:$AK$39,0)&lt;=ROUND(COUNT($AK$5:$AK$39)/3,0),"top",IF(RANK(AK31,$AK$5:$AK$39,1)&lt;=ROUND(COUNT($AK$5:$AK$39)/3,0),"bottom","middle")))</f>
         <v/>
       </c>
     </row>
@@ -2493,17 +2453,16 @@
       <c r="AH32" s="5" t="n"/>
       <c r="AI32" s="5" t="n"/>
       <c r="AJ32" s="5" t="n"/>
-      <c r="AK32" s="5" t="n"/>
+      <c r="AK32">
+        <f>IF(COUNT(B32:AJ32)=0,"",SUM(B32:AJ32))</f>
+        <v/>
+      </c>
       <c r="AL32">
-        <f>IF(COUNT(B32:AK32)=0,"",SUM(B32:AK32))</f>
+        <f>COUNT(B32:AJ32)</f>
         <v/>
       </c>
       <c r="AM32">
-        <f>COUNT(B32:AK32)</f>
-        <v/>
-      </c>
-      <c r="AN32">
-        <f>IF(OR(AL32="",COUNT($AL$5:$AL$39)&lt;3),"",IF(RANK(AL32,$AL$5:$AL$39,0)&lt;=ROUND(COUNT($AL$5:$AL$39)/3,0),"top",IF(RANK(AL32,$AL$5:$AL$39,1)&lt;=ROUND(COUNT($AL$5:$AL$39)/3,0),"bottom","middle")))</f>
+        <f>IF(OR(AK32="",COUNT($AK$5:$AK$39)&lt;3),"",IF(RANK(AK32,$AK$5:$AK$39,0)&lt;=ROUND(COUNT($AK$5:$AK$39)/3,0),"top",IF(RANK(AK32,$AK$5:$AK$39,1)&lt;=ROUND(COUNT($AK$5:$AK$39)/3,0),"bottom","middle")))</f>
         <v/>
       </c>
     </row>
@@ -2546,17 +2505,16 @@
       <c r="AH33" s="5" t="n"/>
       <c r="AI33" s="5" t="n"/>
       <c r="AJ33" s="5" t="n"/>
-      <c r="AK33" s="5" t="n"/>
+      <c r="AK33">
+        <f>IF(COUNT(B33:AJ33)=0,"",SUM(B33:AJ33))</f>
+        <v/>
+      </c>
       <c r="AL33">
-        <f>IF(COUNT(B33:AK33)=0,"",SUM(B33:AK33))</f>
+        <f>COUNT(B33:AJ33)</f>
         <v/>
       </c>
       <c r="AM33">
-        <f>COUNT(B33:AK33)</f>
-        <v/>
-      </c>
-      <c r="AN33">
-        <f>IF(OR(AL33="",COUNT($AL$5:$AL$39)&lt;3),"",IF(RANK(AL33,$AL$5:$AL$39,0)&lt;=ROUND(COUNT($AL$5:$AL$39)/3,0),"top",IF(RANK(AL33,$AL$5:$AL$39,1)&lt;=ROUND(COUNT($AL$5:$AL$39)/3,0),"bottom","middle")))</f>
+        <f>IF(OR(AK33="",COUNT($AK$5:$AK$39)&lt;3),"",IF(RANK(AK33,$AK$5:$AK$39,0)&lt;=ROUND(COUNT($AK$5:$AK$39)/3,0),"top",IF(RANK(AK33,$AK$5:$AK$39,1)&lt;=ROUND(COUNT($AK$5:$AK$39)/3,0),"bottom","middle")))</f>
         <v/>
       </c>
     </row>
@@ -2599,17 +2557,16 @@
       <c r="AH34" s="5" t="n"/>
       <c r="AI34" s="5" t="n"/>
       <c r="AJ34" s="5" t="n"/>
-      <c r="AK34" s="5" t="n"/>
+      <c r="AK34">
+        <f>IF(COUNT(B34:AJ34)=0,"",SUM(B34:AJ34))</f>
+        <v/>
+      </c>
       <c r="AL34">
-        <f>IF(COUNT(B34:AK34)=0,"",SUM(B34:AK34))</f>
+        <f>COUNT(B34:AJ34)</f>
         <v/>
       </c>
       <c r="AM34">
-        <f>COUNT(B34:AK34)</f>
-        <v/>
-      </c>
-      <c r="AN34">
-        <f>IF(OR(AL34="",COUNT($AL$5:$AL$39)&lt;3),"",IF(RANK(AL34,$AL$5:$AL$39,0)&lt;=ROUND(COUNT($AL$5:$AL$39)/3,0),"top",IF(RANK(AL34,$AL$5:$AL$39,1)&lt;=ROUND(COUNT($AL$5:$AL$39)/3,0),"bottom","middle")))</f>
+        <f>IF(OR(AK34="",COUNT($AK$5:$AK$39)&lt;3),"",IF(RANK(AK34,$AK$5:$AK$39,0)&lt;=ROUND(COUNT($AK$5:$AK$39)/3,0),"top",IF(RANK(AK34,$AK$5:$AK$39,1)&lt;=ROUND(COUNT($AK$5:$AK$39)/3,0),"bottom","middle")))</f>
         <v/>
       </c>
     </row>
@@ -2652,17 +2609,16 @@
       <c r="AH35" s="5" t="n"/>
       <c r="AI35" s="5" t="n"/>
       <c r="AJ35" s="5" t="n"/>
-      <c r="AK35" s="5" t="n"/>
+      <c r="AK35">
+        <f>IF(COUNT(B35:AJ35)=0,"",SUM(B35:AJ35))</f>
+        <v/>
+      </c>
       <c r="AL35">
-        <f>IF(COUNT(B35:AK35)=0,"",SUM(B35:AK35))</f>
+        <f>COUNT(B35:AJ35)</f>
         <v/>
       </c>
       <c r="AM35">
-        <f>COUNT(B35:AK35)</f>
-        <v/>
-      </c>
-      <c r="AN35">
-        <f>IF(OR(AL35="",COUNT($AL$5:$AL$39)&lt;3),"",IF(RANK(AL35,$AL$5:$AL$39,0)&lt;=ROUND(COUNT($AL$5:$AL$39)/3,0),"top",IF(RANK(AL35,$AL$5:$AL$39,1)&lt;=ROUND(COUNT($AL$5:$AL$39)/3,0),"bottom","middle")))</f>
+        <f>IF(OR(AK35="",COUNT($AK$5:$AK$39)&lt;3),"",IF(RANK(AK35,$AK$5:$AK$39,0)&lt;=ROUND(COUNT($AK$5:$AK$39)/3,0),"top",IF(RANK(AK35,$AK$5:$AK$39,1)&lt;=ROUND(COUNT($AK$5:$AK$39)/3,0),"bottom","middle")))</f>
         <v/>
       </c>
     </row>
@@ -2705,17 +2661,16 @@
       <c r="AH36" s="5" t="n"/>
       <c r="AI36" s="5" t="n"/>
       <c r="AJ36" s="5" t="n"/>
-      <c r="AK36" s="5" t="n"/>
+      <c r="AK36">
+        <f>IF(COUNT(B36:AJ36)=0,"",SUM(B36:AJ36))</f>
+        <v/>
+      </c>
       <c r="AL36">
-        <f>IF(COUNT(B36:AK36)=0,"",SUM(B36:AK36))</f>
+        <f>COUNT(B36:AJ36)</f>
         <v/>
       </c>
       <c r="AM36">
-        <f>COUNT(B36:AK36)</f>
-        <v/>
-      </c>
-      <c r="AN36">
-        <f>IF(OR(AL36="",COUNT($AL$5:$AL$39)&lt;3),"",IF(RANK(AL36,$AL$5:$AL$39,0)&lt;=ROUND(COUNT($AL$5:$AL$39)/3,0),"top",IF(RANK(AL36,$AL$5:$AL$39,1)&lt;=ROUND(COUNT($AL$5:$AL$39)/3,0),"bottom","middle")))</f>
+        <f>IF(OR(AK36="",COUNT($AK$5:$AK$39)&lt;3),"",IF(RANK(AK36,$AK$5:$AK$39,0)&lt;=ROUND(COUNT($AK$5:$AK$39)/3,0),"top",IF(RANK(AK36,$AK$5:$AK$39,1)&lt;=ROUND(COUNT($AK$5:$AK$39)/3,0),"bottom","middle")))</f>
         <v/>
       </c>
     </row>
@@ -2758,17 +2713,16 @@
       <c r="AH37" s="5" t="n"/>
       <c r="AI37" s="5" t="n"/>
       <c r="AJ37" s="5" t="n"/>
-      <c r="AK37" s="5" t="n"/>
+      <c r="AK37">
+        <f>IF(COUNT(B37:AJ37)=0,"",SUM(B37:AJ37))</f>
+        <v/>
+      </c>
       <c r="AL37">
-        <f>IF(COUNT(B37:AK37)=0,"",SUM(B37:AK37))</f>
+        <f>COUNT(B37:AJ37)</f>
         <v/>
       </c>
       <c r="AM37">
-        <f>COUNT(B37:AK37)</f>
-        <v/>
-      </c>
-      <c r="AN37">
-        <f>IF(OR(AL37="",COUNT($AL$5:$AL$39)&lt;3),"",IF(RANK(AL37,$AL$5:$AL$39,0)&lt;=ROUND(COUNT($AL$5:$AL$39)/3,0),"top",IF(RANK(AL37,$AL$5:$AL$39,1)&lt;=ROUND(COUNT($AL$5:$AL$39)/3,0),"bottom","middle")))</f>
+        <f>IF(OR(AK37="",COUNT($AK$5:$AK$39)&lt;3),"",IF(RANK(AK37,$AK$5:$AK$39,0)&lt;=ROUND(COUNT($AK$5:$AK$39)/3,0),"top",IF(RANK(AK37,$AK$5:$AK$39,1)&lt;=ROUND(COUNT($AK$5:$AK$39)/3,0),"bottom","middle")))</f>
         <v/>
       </c>
     </row>
@@ -2811,17 +2765,16 @@
       <c r="AH38" s="5" t="n"/>
       <c r="AI38" s="5" t="n"/>
       <c r="AJ38" s="5" t="n"/>
-      <c r="AK38" s="5" t="n"/>
+      <c r="AK38">
+        <f>IF(COUNT(B38:AJ38)=0,"",SUM(B38:AJ38))</f>
+        <v/>
+      </c>
       <c r="AL38">
-        <f>IF(COUNT(B38:AK38)=0,"",SUM(B38:AK38))</f>
+        <f>COUNT(B38:AJ38)</f>
         <v/>
       </c>
       <c r="AM38">
-        <f>COUNT(B38:AK38)</f>
-        <v/>
-      </c>
-      <c r="AN38">
-        <f>IF(OR(AL38="",COUNT($AL$5:$AL$39)&lt;3),"",IF(RANK(AL38,$AL$5:$AL$39,0)&lt;=ROUND(COUNT($AL$5:$AL$39)/3,0),"top",IF(RANK(AL38,$AL$5:$AL$39,1)&lt;=ROUND(COUNT($AL$5:$AL$39)/3,0),"bottom","middle")))</f>
+        <f>IF(OR(AK38="",COUNT($AK$5:$AK$39)&lt;3),"",IF(RANK(AK38,$AK$5:$AK$39,0)&lt;=ROUND(COUNT($AK$5:$AK$39)/3,0),"top",IF(RANK(AK38,$AK$5:$AK$39,1)&lt;=ROUND(COUNT($AK$5:$AK$39)/3,0),"bottom","middle")))</f>
         <v/>
       </c>
     </row>
@@ -2864,17 +2817,16 @@
       <c r="AH39" s="5" t="n"/>
       <c r="AI39" s="5" t="n"/>
       <c r="AJ39" s="5" t="n"/>
-      <c r="AK39" s="5" t="n"/>
+      <c r="AK39">
+        <f>IF(COUNT(B39:AJ39)=0,"",SUM(B39:AJ39))</f>
+        <v/>
+      </c>
       <c r="AL39">
-        <f>IF(COUNT(B39:AK39)=0,"",SUM(B39:AK39))</f>
+        <f>COUNT(B39:AJ39)</f>
         <v/>
       </c>
       <c r="AM39">
-        <f>COUNT(B39:AK39)</f>
-        <v/>
-      </c>
-      <c r="AN39">
-        <f>IF(OR(AL39="",COUNT($AL$5:$AL$39)&lt;3),"",IF(RANK(AL39,$AL$5:$AL$39,0)&lt;=ROUND(COUNT($AL$5:$AL$39)/3,0),"top",IF(RANK(AL39,$AL$5:$AL$39,1)&lt;=ROUND(COUNT($AL$5:$AL$39)/3,0),"bottom","middle")))</f>
+        <f>IF(OR(AK39="",COUNT($AK$5:$AK$39)&lt;3),"",IF(RANK(AK39,$AK$5:$AK$39,0)&lt;=ROUND(COUNT($AK$5:$AK$39)/3,0),"top",IF(RANK(AK39,$AK$5:$AK$39,1)&lt;=ROUND(COUNT($AK$5:$AK$39)/3,0),"bottom","middle")))</f>
         <v/>
       </c>
     </row>
@@ -2889,7 +2841,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N40"/>
+  <dimension ref="A1:N39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="13" max="13"/>
@@ -3014,11 +2966,11 @@
         <v/>
       </c>
       <c r="J5" s="6">
-        <f>IF(SUMPRODUCT((Marks!$AN$5:$AN$39="top")*ISNUMBER(Marks!B$5:B$39))=0,"",SUMPRODUCT((Marks!$AN$5:$AN$39="top")*(Marks!B$5:B$39=1))/SUMPRODUCT((Marks!$AN$5:$AN$39="top")*ISNUMBER(Marks!B$5:B$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AM$5:$AM$39="top")*ISNUMBER(Marks!B$5:B$39))=0,"",SUMPRODUCT((Marks!$AM$5:$AM$39="top")*(Marks!B$5:B$39=1))/SUMPRODUCT((Marks!$AM$5:$AM$39="top")*ISNUMBER(Marks!B$5:B$39)))</f>
         <v/>
       </c>
       <c r="K5" s="6">
-        <f>IF(SUMPRODUCT((Marks!$AN$5:$AN$39="bottom")*ISNUMBER(Marks!B$5:B$39))=0,"",SUMPRODUCT((Marks!$AN$5:$AN$39="bottom")*(Marks!B$5:B$39=1))/SUMPRODUCT((Marks!$AN$5:$AN$39="bottom")*ISNUMBER(Marks!B$5:B$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*ISNUMBER(Marks!B$5:B$39))=0,"",SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*(Marks!B$5:B$39=1))/SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*ISNUMBER(Marks!B$5:B$39)))</f>
         <v/>
       </c>
       <c r="L5" s="6">
@@ -3058,7 +3010,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>c</t>
+          <t>b</t>
         </is>
       </c>
       <c r="G6">
@@ -3074,11 +3026,11 @@
         <v/>
       </c>
       <c r="J6" s="6">
-        <f>IF(SUMPRODUCT((Marks!$AN$5:$AN$39="top")*ISNUMBER(Marks!C$5:C$39))=0,"",SUMPRODUCT((Marks!$AN$5:$AN$39="top")*(Marks!C$5:C$39=1))/SUMPRODUCT((Marks!$AN$5:$AN$39="top")*ISNUMBER(Marks!C$5:C$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AM$5:$AM$39="top")*ISNUMBER(Marks!C$5:C$39))=0,"",SUMPRODUCT((Marks!$AM$5:$AM$39="top")*(Marks!C$5:C$39=1))/SUMPRODUCT((Marks!$AM$5:$AM$39="top")*ISNUMBER(Marks!C$5:C$39)))</f>
         <v/>
       </c>
       <c r="K6" s="6">
-        <f>IF(SUMPRODUCT((Marks!$AN$5:$AN$39="bottom")*ISNUMBER(Marks!C$5:C$39))=0,"",SUMPRODUCT((Marks!$AN$5:$AN$39="bottom")*(Marks!C$5:C$39=1))/SUMPRODUCT((Marks!$AN$5:$AN$39="bottom")*ISNUMBER(Marks!C$5:C$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*ISNUMBER(Marks!C$5:C$39))=0,"",SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*(Marks!C$5:C$39=1))/SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*ISNUMBER(Marks!C$5:C$39)))</f>
         <v/>
       </c>
       <c r="L6" s="6">
@@ -3103,7 +3055,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>One correct option</t>
+          <t>Applied maths</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -3118,7 +3070,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>Rs 2,060.</t>
         </is>
       </c>
       <c r="G7">
@@ -3134,11 +3086,11 @@
         <v/>
       </c>
       <c r="J7" s="6">
-        <f>IF(SUMPRODUCT((Marks!$AN$5:$AN$39="top")*ISNUMBER(Marks!D$5:D$39))=0,"",SUMPRODUCT((Marks!$AN$5:$AN$39="top")*(Marks!D$5:D$39=1))/SUMPRODUCT((Marks!$AN$5:$AN$39="top")*ISNUMBER(Marks!D$5:D$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AM$5:$AM$39="top")*ISNUMBER(Marks!D$5:D$39))=0,"",SUMPRODUCT((Marks!$AM$5:$AM$39="top")*(Marks!D$5:D$39=1))/SUMPRODUCT((Marks!$AM$5:$AM$39="top")*ISNUMBER(Marks!D$5:D$39)))</f>
         <v/>
       </c>
       <c r="K7" s="6">
-        <f>IF(SUMPRODUCT((Marks!$AN$5:$AN$39="bottom")*ISNUMBER(Marks!D$5:D$39))=0,"",SUMPRODUCT((Marks!$AN$5:$AN$39="bottom")*(Marks!D$5:D$39=1))/SUMPRODUCT((Marks!$AN$5:$AN$39="bottom")*ISNUMBER(Marks!D$5:D$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*ISNUMBER(Marks!D$5:D$39))=0,"",SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*(Marks!D$5:D$39=1))/SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*ISNUMBER(Marks!D$5:D$39)))</f>
         <v/>
       </c>
       <c r="L7" s="6">
@@ -3163,7 +3115,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Applied maths</t>
+          <t>One correct option</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -3173,12 +3125,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>[F]</t>
+          <t>[S]</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Revenue falls by 6.5 percent (1.10 x 0.85 = 0.935).</t>
+          <t>d</t>
         </is>
       </c>
       <c r="G8">
@@ -3194,11 +3146,11 @@
         <v/>
       </c>
       <c r="J8" s="6">
-        <f>IF(SUMPRODUCT((Marks!$AN$5:$AN$39="top")*ISNUMBER(Marks!E$5:E$39))=0,"",SUMPRODUCT((Marks!$AN$5:$AN$39="top")*(Marks!E$5:E$39=1))/SUMPRODUCT((Marks!$AN$5:$AN$39="top")*ISNUMBER(Marks!E$5:E$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AM$5:$AM$39="top")*ISNUMBER(Marks!E$5:E$39))=0,"",SUMPRODUCT((Marks!$AM$5:$AM$39="top")*(Marks!E$5:E$39=1))/SUMPRODUCT((Marks!$AM$5:$AM$39="top")*ISNUMBER(Marks!E$5:E$39)))</f>
         <v/>
       </c>
       <c r="K8" s="6">
-        <f>IF(SUMPRODUCT((Marks!$AN$5:$AN$39="bottom")*ISNUMBER(Marks!E$5:E$39))=0,"",SUMPRODUCT((Marks!$AN$5:$AN$39="bottom")*(Marks!E$5:E$39=1))/SUMPRODUCT((Marks!$AN$5:$AN$39="bottom")*ISNUMBER(Marks!E$5:E$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*ISNUMBER(Marks!E$5:E$39))=0,"",SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*(Marks!E$5:E$39=1))/SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*ISNUMBER(Marks!E$5:E$39)))</f>
         <v/>
       </c>
       <c r="L8" s="6">
@@ -3228,7 +3180,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Hard</t>
+          <t>Easy</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3238,7 +3190,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>d</t>
+          <t>a</t>
         </is>
       </c>
       <c r="G9">
@@ -3254,11 +3206,11 @@
         <v/>
       </c>
       <c r="J9" s="6">
-        <f>IF(SUMPRODUCT((Marks!$AN$5:$AN$39="top")*ISNUMBER(Marks!F$5:F$39))=0,"",SUMPRODUCT((Marks!$AN$5:$AN$39="top")*(Marks!F$5:F$39=1))/SUMPRODUCT((Marks!$AN$5:$AN$39="top")*ISNUMBER(Marks!F$5:F$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AM$5:$AM$39="top")*ISNUMBER(Marks!F$5:F$39))=0,"",SUMPRODUCT((Marks!$AM$5:$AM$39="top")*(Marks!F$5:F$39=1))/SUMPRODUCT((Marks!$AM$5:$AM$39="top")*ISNUMBER(Marks!F$5:F$39)))</f>
         <v/>
       </c>
       <c r="K9" s="6">
-        <f>IF(SUMPRODUCT((Marks!$AN$5:$AN$39="bottom")*ISNUMBER(Marks!F$5:F$39))=0,"",SUMPRODUCT((Marks!$AN$5:$AN$39="bottom")*(Marks!F$5:F$39=1))/SUMPRODUCT((Marks!$AN$5:$AN$39="bottom")*ISNUMBER(Marks!F$5:F$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*ISNUMBER(Marks!F$5:F$39))=0,"",SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*(Marks!F$5:F$39=1))/SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*ISNUMBER(Marks!F$5:F$39)))</f>
         <v/>
       </c>
       <c r="L9" s="6">
@@ -3288,17 +3240,17 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>Hard</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>[S]</t>
+          <t>[D]</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>a</t>
+          <t>c</t>
         </is>
       </c>
       <c r="G10">
@@ -3314,11 +3266,11 @@
         <v/>
       </c>
       <c r="J10" s="6">
-        <f>IF(SUMPRODUCT((Marks!$AN$5:$AN$39="top")*ISNUMBER(Marks!G$5:G$39))=0,"",SUMPRODUCT((Marks!$AN$5:$AN$39="top")*(Marks!G$5:G$39=1))/SUMPRODUCT((Marks!$AN$5:$AN$39="top")*ISNUMBER(Marks!G$5:G$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AM$5:$AM$39="top")*ISNUMBER(Marks!G$5:G$39))=0,"",SUMPRODUCT((Marks!$AM$5:$AM$39="top")*(Marks!G$5:G$39=1))/SUMPRODUCT((Marks!$AM$5:$AM$39="top")*ISNUMBER(Marks!G$5:G$39)))</f>
         <v/>
       </c>
       <c r="K10" s="6">
-        <f>IF(SUMPRODUCT((Marks!$AN$5:$AN$39="bottom")*ISNUMBER(Marks!G$5:G$39))=0,"",SUMPRODUCT((Marks!$AN$5:$AN$39="bottom")*(Marks!G$5:G$39=1))/SUMPRODUCT((Marks!$AN$5:$AN$39="bottom")*ISNUMBER(Marks!G$5:G$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*ISNUMBER(Marks!G$5:G$39))=0,"",SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*(Marks!G$5:G$39=1))/SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*ISNUMBER(Marks!G$5:G$39)))</f>
         <v/>
       </c>
       <c r="L10" s="6">
@@ -3343,22 +3295,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>One correct option</t>
+          <t>Order the steps</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Hard</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>[D]</t>
+          <t>[S]</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>d</t>
+          <t>b, d, e, a, c</t>
         </is>
       </c>
       <c r="G11">
@@ -3374,11 +3326,11 @@
         <v/>
       </c>
       <c r="J11" s="6">
-        <f>IF(SUMPRODUCT((Marks!$AN$5:$AN$39="top")*ISNUMBER(Marks!H$5:H$39))=0,"",SUMPRODUCT((Marks!$AN$5:$AN$39="top")*(Marks!H$5:H$39=1))/SUMPRODUCT((Marks!$AN$5:$AN$39="top")*ISNUMBER(Marks!H$5:H$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AM$5:$AM$39="top")*ISNUMBER(Marks!H$5:H$39))=0,"",SUMPRODUCT((Marks!$AM$5:$AM$39="top")*(Marks!H$5:H$39=1))/SUMPRODUCT((Marks!$AM$5:$AM$39="top")*ISNUMBER(Marks!H$5:H$39)))</f>
         <v/>
       </c>
       <c r="K11" s="6">
-        <f>IF(SUMPRODUCT((Marks!$AN$5:$AN$39="bottom")*ISNUMBER(Marks!H$5:H$39))=0,"",SUMPRODUCT((Marks!$AN$5:$AN$39="bottom")*(Marks!H$5:H$39=1))/SUMPRODUCT((Marks!$AN$5:$AN$39="bottom")*ISNUMBER(Marks!H$5:H$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*ISNUMBER(Marks!H$5:H$39))=0,"",SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*(Marks!H$5:H$39=1))/SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*ISNUMBER(Marks!H$5:H$39)))</f>
         <v/>
       </c>
       <c r="L11" s="6">
@@ -3399,26 +3351,26 @@
         <v>8</v>
       </c>
       <c r="B12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Order the steps</t>
+          <t>One correct option</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Hard</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>[S]</t>
+          <t>[F]</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>b, d, e, a, c</t>
+          <t>c</t>
         </is>
       </c>
       <c r="G12">
@@ -3434,11 +3386,11 @@
         <v/>
       </c>
       <c r="J12" s="6">
-        <f>IF(SUMPRODUCT((Marks!$AN$5:$AN$39="top")*ISNUMBER(Marks!I$5:I$39))=0,"",SUMPRODUCT((Marks!$AN$5:$AN$39="top")*(Marks!I$5:I$39=1))/SUMPRODUCT((Marks!$AN$5:$AN$39="top")*ISNUMBER(Marks!I$5:I$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AM$5:$AM$39="top")*ISNUMBER(Marks!I$5:I$39))=0,"",SUMPRODUCT((Marks!$AM$5:$AM$39="top")*(Marks!I$5:I$39=1))/SUMPRODUCT((Marks!$AM$5:$AM$39="top")*ISNUMBER(Marks!I$5:I$39)))</f>
         <v/>
       </c>
       <c r="K12" s="6">
-        <f>IF(SUMPRODUCT((Marks!$AN$5:$AN$39="bottom")*ISNUMBER(Marks!I$5:I$39))=0,"",SUMPRODUCT((Marks!$AN$5:$AN$39="bottom")*(Marks!I$5:I$39=1))/SUMPRODUCT((Marks!$AN$5:$AN$39="bottom")*ISNUMBER(Marks!I$5:I$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*ISNUMBER(Marks!I$5:I$39))=0,"",SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*(Marks!I$5:I$39=1))/SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*ISNUMBER(Marks!I$5:I$39)))</f>
         <v/>
       </c>
       <c r="L12" s="6">
@@ -3463,22 +3415,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>One correct option</t>
+          <t>True or false</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Hard</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>[F]</t>
+          <t>[SV]</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>d</t>
         </is>
       </c>
       <c r="G13">
@@ -3494,11 +3446,11 @@
         <v/>
       </c>
       <c r="J13" s="6">
-        <f>IF(SUMPRODUCT((Marks!$AN$5:$AN$39="top")*ISNUMBER(Marks!J$5:J$39))=0,"",SUMPRODUCT((Marks!$AN$5:$AN$39="top")*(Marks!J$5:J$39=1))/SUMPRODUCT((Marks!$AN$5:$AN$39="top")*ISNUMBER(Marks!J$5:J$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AM$5:$AM$39="top")*ISNUMBER(Marks!J$5:J$39))=0,"",SUMPRODUCT((Marks!$AM$5:$AM$39="top")*(Marks!J$5:J$39=1))/SUMPRODUCT((Marks!$AM$5:$AM$39="top")*ISNUMBER(Marks!J$5:J$39)))</f>
         <v/>
       </c>
       <c r="K13" s="6">
-        <f>IF(SUMPRODUCT((Marks!$AN$5:$AN$39="bottom")*ISNUMBER(Marks!J$5:J$39))=0,"",SUMPRODUCT((Marks!$AN$5:$AN$39="bottom")*(Marks!J$5:J$39=1))/SUMPRODUCT((Marks!$AN$5:$AN$39="bottom")*ISNUMBER(Marks!J$5:J$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*ISNUMBER(Marks!J$5:J$39))=0,"",SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*(Marks!J$5:J$39=1))/SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*ISNUMBER(Marks!J$5:J$39)))</f>
         <v/>
       </c>
       <c r="L13" s="6">
@@ -3528,17 +3480,17 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Hard</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>[SV]</t>
+          <t>[D]</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>c</t>
         </is>
       </c>
       <c r="G14">
@@ -3554,11 +3506,11 @@
         <v/>
       </c>
       <c r="J14" s="6">
-        <f>IF(SUMPRODUCT((Marks!$AN$5:$AN$39="top")*ISNUMBER(Marks!K$5:K$39))=0,"",SUMPRODUCT((Marks!$AN$5:$AN$39="top")*(Marks!K$5:K$39=1))/SUMPRODUCT((Marks!$AN$5:$AN$39="top")*ISNUMBER(Marks!K$5:K$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AM$5:$AM$39="top")*ISNUMBER(Marks!K$5:K$39))=0,"",SUMPRODUCT((Marks!$AM$5:$AM$39="top")*(Marks!K$5:K$39=1))/SUMPRODUCT((Marks!$AM$5:$AM$39="top")*ISNUMBER(Marks!K$5:K$39)))</f>
         <v/>
       </c>
       <c r="K14" s="6">
-        <f>IF(SUMPRODUCT((Marks!$AN$5:$AN$39="bottom")*ISNUMBER(Marks!K$5:K$39))=0,"",SUMPRODUCT((Marks!$AN$5:$AN$39="bottom")*(Marks!K$5:K$39=1))/SUMPRODUCT((Marks!$AN$5:$AN$39="bottom")*ISNUMBER(Marks!K$5:K$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*ISNUMBER(Marks!K$5:K$39))=0,"",SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*(Marks!K$5:K$39=1))/SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*ISNUMBER(Marks!K$5:K$39)))</f>
         <v/>
       </c>
       <c r="L14" s="6">
@@ -3583,7 +3535,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>True or false</t>
+          <t>More than one correct</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3593,12 +3545,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>[D]</t>
+          <t>[F]</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>c</t>
+          <t>b, d</t>
         </is>
       </c>
       <c r="G15">
@@ -3614,11 +3566,11 @@
         <v/>
       </c>
       <c r="J15" s="6">
-        <f>IF(SUMPRODUCT((Marks!$AN$5:$AN$39="top")*ISNUMBER(Marks!L$5:L$39))=0,"",SUMPRODUCT((Marks!$AN$5:$AN$39="top")*(Marks!L$5:L$39=1))/SUMPRODUCT((Marks!$AN$5:$AN$39="top")*ISNUMBER(Marks!L$5:L$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AM$5:$AM$39="top")*ISNUMBER(Marks!L$5:L$39))=0,"",SUMPRODUCT((Marks!$AM$5:$AM$39="top")*(Marks!L$5:L$39=1))/SUMPRODUCT((Marks!$AM$5:$AM$39="top")*ISNUMBER(Marks!L$5:L$39)))</f>
         <v/>
       </c>
       <c r="K15" s="6">
-        <f>IF(SUMPRODUCT((Marks!$AN$5:$AN$39="bottom")*ISNUMBER(Marks!L$5:L$39))=0,"",SUMPRODUCT((Marks!$AN$5:$AN$39="bottom")*(Marks!L$5:L$39=1))/SUMPRODUCT((Marks!$AN$5:$AN$39="bottom")*ISNUMBER(Marks!L$5:L$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*ISNUMBER(Marks!L$5:L$39))=0,"",SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*(Marks!L$5:L$39=1))/SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*ISNUMBER(Marks!L$5:L$39)))</f>
         <v/>
       </c>
       <c r="L15" s="6">
@@ -3643,7 +3595,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>More than one correct</t>
+          <t>Applied maths</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3658,7 +3610,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>b, d</t>
+          <t>Rs 10,930.</t>
         </is>
       </c>
       <c r="G16">
@@ -3674,11 +3626,11 @@
         <v/>
       </c>
       <c r="J16" s="6">
-        <f>IF(SUMPRODUCT((Marks!$AN$5:$AN$39="top")*ISNUMBER(Marks!M$5:M$39))=0,"",SUMPRODUCT((Marks!$AN$5:$AN$39="top")*(Marks!M$5:M$39=1))/SUMPRODUCT((Marks!$AN$5:$AN$39="top")*ISNUMBER(Marks!M$5:M$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AM$5:$AM$39="top")*ISNUMBER(Marks!M$5:M$39))=0,"",SUMPRODUCT((Marks!$AM$5:$AM$39="top")*(Marks!M$5:M$39=1))/SUMPRODUCT((Marks!$AM$5:$AM$39="top")*ISNUMBER(Marks!M$5:M$39)))</f>
         <v/>
       </c>
       <c r="K16" s="6">
-        <f>IF(SUMPRODUCT((Marks!$AN$5:$AN$39="bottom")*ISNUMBER(Marks!M$5:M$39))=0,"",SUMPRODUCT((Marks!$AN$5:$AN$39="bottom")*(Marks!M$5:M$39=1))/SUMPRODUCT((Marks!$AN$5:$AN$39="bottom")*ISNUMBER(Marks!M$5:M$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*ISNUMBER(Marks!M$5:M$39))=0,"",SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*(Marks!M$5:M$39=1))/SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*ISNUMBER(Marks!M$5:M$39)))</f>
         <v/>
       </c>
       <c r="L16" s="6">
@@ -3703,12 +3655,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>One correct option</t>
+          <t>Scenario set</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Hard</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -3718,7 +3670,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>A fall of 1.6 percent.</t>
         </is>
       </c>
       <c r="G17">
@@ -3734,11 +3686,11 @@
         <v/>
       </c>
       <c r="J17" s="6">
-        <f>IF(SUMPRODUCT((Marks!$AN$5:$AN$39="top")*ISNUMBER(Marks!N$5:N$39))=0,"",SUMPRODUCT((Marks!$AN$5:$AN$39="top")*(Marks!N$5:N$39=1))/SUMPRODUCT((Marks!$AN$5:$AN$39="top")*ISNUMBER(Marks!N$5:N$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AM$5:$AM$39="top")*ISNUMBER(Marks!N$5:N$39))=0,"",SUMPRODUCT((Marks!$AM$5:$AM$39="top")*(Marks!N$5:N$39=1))/SUMPRODUCT((Marks!$AM$5:$AM$39="top")*ISNUMBER(Marks!N$5:N$39)))</f>
         <v/>
       </c>
       <c r="K17" s="6">
-        <f>IF(SUMPRODUCT((Marks!$AN$5:$AN$39="bottom")*ISNUMBER(Marks!N$5:N$39))=0,"",SUMPRODUCT((Marks!$AN$5:$AN$39="bottom")*(Marks!N$5:N$39=1))/SUMPRODUCT((Marks!$AN$5:$AN$39="bottom")*ISNUMBER(Marks!N$5:N$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*ISNUMBER(Marks!N$5:N$39))=0,"",SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*(Marks!N$5:N$39=1))/SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*ISNUMBER(Marks!N$5:N$39)))</f>
         <v/>
       </c>
       <c r="L17" s="6">
@@ -3773,12 +3725,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>[F]</t>
+          <t>[S]</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>d</t>
+          <t>A fall of 35.0 percent.</t>
         </is>
       </c>
       <c r="G18">
@@ -3794,11 +3746,11 @@
         <v/>
       </c>
       <c r="J18" s="6">
-        <f>IF(SUMPRODUCT((Marks!$AN$5:$AN$39="top")*ISNUMBER(Marks!O$5:O$39))=0,"",SUMPRODUCT((Marks!$AN$5:$AN$39="top")*(Marks!O$5:O$39=1))/SUMPRODUCT((Marks!$AN$5:$AN$39="top")*ISNUMBER(Marks!O$5:O$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AM$5:$AM$39="top")*ISNUMBER(Marks!O$5:O$39))=0,"",SUMPRODUCT((Marks!$AM$5:$AM$39="top")*(Marks!O$5:O$39=1))/SUMPRODUCT((Marks!$AM$5:$AM$39="top")*ISNUMBER(Marks!O$5:O$39)))</f>
         <v/>
       </c>
       <c r="K18" s="6">
-        <f>IF(SUMPRODUCT((Marks!$AN$5:$AN$39="bottom")*ISNUMBER(Marks!O$5:O$39))=0,"",SUMPRODUCT((Marks!$AN$5:$AN$39="bottom")*(Marks!O$5:O$39=1))/SUMPRODUCT((Marks!$AN$5:$AN$39="bottom")*ISNUMBER(Marks!O$5:O$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*ISNUMBER(Marks!O$5:O$39))=0,"",SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*(Marks!O$5:O$39=1))/SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*ISNUMBER(Marks!O$5:O$39)))</f>
         <v/>
       </c>
       <c r="L18" s="6">
@@ -3823,22 +3775,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Scenario set</t>
+          <t>Order the steps</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Hard</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>[S]</t>
+          <t>[F]</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>A fall of 35.0 percent.</t>
+          <t>b, d, a, c</t>
         </is>
       </c>
       <c r="G19">
@@ -3854,11 +3806,11 @@
         <v/>
       </c>
       <c r="J19" s="6">
-        <f>IF(SUMPRODUCT((Marks!$AN$5:$AN$39="top")*ISNUMBER(Marks!P$5:P$39))=0,"",SUMPRODUCT((Marks!$AN$5:$AN$39="top")*(Marks!P$5:P$39=1))/SUMPRODUCT((Marks!$AN$5:$AN$39="top")*ISNUMBER(Marks!P$5:P$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AM$5:$AM$39="top")*ISNUMBER(Marks!P$5:P$39))=0,"",SUMPRODUCT((Marks!$AM$5:$AM$39="top")*(Marks!P$5:P$39=1))/SUMPRODUCT((Marks!$AM$5:$AM$39="top")*ISNUMBER(Marks!P$5:P$39)))</f>
         <v/>
       </c>
       <c r="K19" s="6">
-        <f>IF(SUMPRODUCT((Marks!$AN$5:$AN$39="bottom")*ISNUMBER(Marks!P$5:P$39))=0,"",SUMPRODUCT((Marks!$AN$5:$AN$39="bottom")*(Marks!P$5:P$39=1))/SUMPRODUCT((Marks!$AN$5:$AN$39="bottom")*ISNUMBER(Marks!P$5:P$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*ISNUMBER(Marks!P$5:P$39))=0,"",SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*(Marks!P$5:P$39=1))/SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*ISNUMBER(Marks!P$5:P$39)))</f>
         <v/>
       </c>
       <c r="L19" s="6">
@@ -3879,26 +3831,26 @@
         <v>16</v>
       </c>
       <c r="B20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Order the steps</t>
+          <t>One correct option</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Hard</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>[F]</t>
+          <t>[S]</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>b, d, a, c</t>
+          <t>a</t>
         </is>
       </c>
       <c r="G20">
@@ -3914,11 +3866,11 @@
         <v/>
       </c>
       <c r="J20" s="6">
-        <f>IF(SUMPRODUCT((Marks!$AN$5:$AN$39="top")*ISNUMBER(Marks!Q$5:Q$39))=0,"",SUMPRODUCT((Marks!$AN$5:$AN$39="top")*(Marks!Q$5:Q$39=1))/SUMPRODUCT((Marks!$AN$5:$AN$39="top")*ISNUMBER(Marks!Q$5:Q$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AM$5:$AM$39="top")*ISNUMBER(Marks!Q$5:Q$39))=0,"",SUMPRODUCT((Marks!$AM$5:$AM$39="top")*(Marks!Q$5:Q$39=1))/SUMPRODUCT((Marks!$AM$5:$AM$39="top")*ISNUMBER(Marks!Q$5:Q$39)))</f>
         <v/>
       </c>
       <c r="K20" s="6">
-        <f>IF(SUMPRODUCT((Marks!$AN$5:$AN$39="bottom")*ISNUMBER(Marks!Q$5:Q$39))=0,"",SUMPRODUCT((Marks!$AN$5:$AN$39="bottom")*(Marks!Q$5:Q$39=1))/SUMPRODUCT((Marks!$AN$5:$AN$39="bottom")*ISNUMBER(Marks!Q$5:Q$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*ISNUMBER(Marks!Q$5:Q$39))=0,"",SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*(Marks!Q$5:Q$39=1))/SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*ISNUMBER(Marks!Q$5:Q$39)))</f>
         <v/>
       </c>
       <c r="L20" s="6">
@@ -3948,7 +3900,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Hard</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -3974,11 +3926,11 @@
         <v/>
       </c>
       <c r="J21" s="6">
-        <f>IF(SUMPRODUCT((Marks!$AN$5:$AN$39="top")*ISNUMBER(Marks!R$5:R$39))=0,"",SUMPRODUCT((Marks!$AN$5:$AN$39="top")*(Marks!R$5:R$39=1))/SUMPRODUCT((Marks!$AN$5:$AN$39="top")*ISNUMBER(Marks!R$5:R$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AM$5:$AM$39="top")*ISNUMBER(Marks!R$5:R$39))=0,"",SUMPRODUCT((Marks!$AM$5:$AM$39="top")*(Marks!R$5:R$39=1))/SUMPRODUCT((Marks!$AM$5:$AM$39="top")*ISNUMBER(Marks!R$5:R$39)))</f>
         <v/>
       </c>
       <c r="K21" s="6">
-        <f>IF(SUMPRODUCT((Marks!$AN$5:$AN$39="bottom")*ISNUMBER(Marks!R$5:R$39))=0,"",SUMPRODUCT((Marks!$AN$5:$AN$39="bottom")*(Marks!R$5:R$39=1))/SUMPRODUCT((Marks!$AN$5:$AN$39="bottom")*ISNUMBER(Marks!R$5:R$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*ISNUMBER(Marks!R$5:R$39))=0,"",SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*(Marks!R$5:R$39=1))/SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*ISNUMBER(Marks!R$5:R$39)))</f>
         <v/>
       </c>
       <c r="L21" s="6">
@@ -4034,11 +3986,11 @@
         <v/>
       </c>
       <c r="J22" s="6">
-        <f>IF(SUMPRODUCT((Marks!$AN$5:$AN$39="top")*ISNUMBER(Marks!S$5:S$39))=0,"",SUMPRODUCT((Marks!$AN$5:$AN$39="top")*(Marks!S$5:S$39=1))/SUMPRODUCT((Marks!$AN$5:$AN$39="top")*ISNUMBER(Marks!S$5:S$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AM$5:$AM$39="top")*ISNUMBER(Marks!S$5:S$39))=0,"",SUMPRODUCT((Marks!$AM$5:$AM$39="top")*(Marks!S$5:S$39=1))/SUMPRODUCT((Marks!$AM$5:$AM$39="top")*ISNUMBER(Marks!S$5:S$39)))</f>
         <v/>
       </c>
       <c r="K22" s="6">
-        <f>IF(SUMPRODUCT((Marks!$AN$5:$AN$39="bottom")*ISNUMBER(Marks!S$5:S$39))=0,"",SUMPRODUCT((Marks!$AN$5:$AN$39="bottom")*(Marks!S$5:S$39=1))/SUMPRODUCT((Marks!$AN$5:$AN$39="bottom")*ISNUMBER(Marks!S$5:S$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*ISNUMBER(Marks!S$5:S$39))=0,"",SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*(Marks!S$5:S$39=1))/SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*ISNUMBER(Marks!S$5:S$39)))</f>
         <v/>
       </c>
       <c r="L22" s="6">
@@ -4094,11 +4046,11 @@
         <v/>
       </c>
       <c r="J23" s="6">
-        <f>IF(SUMPRODUCT((Marks!$AN$5:$AN$39="top")*ISNUMBER(Marks!T$5:T$39))=0,"",SUMPRODUCT((Marks!$AN$5:$AN$39="top")*(Marks!T$5:T$39=1))/SUMPRODUCT((Marks!$AN$5:$AN$39="top")*ISNUMBER(Marks!T$5:T$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AM$5:$AM$39="top")*ISNUMBER(Marks!T$5:T$39))=0,"",SUMPRODUCT((Marks!$AM$5:$AM$39="top")*(Marks!T$5:T$39=1))/SUMPRODUCT((Marks!$AM$5:$AM$39="top")*ISNUMBER(Marks!T$5:T$39)))</f>
         <v/>
       </c>
       <c r="K23" s="6">
-        <f>IF(SUMPRODUCT((Marks!$AN$5:$AN$39="bottom")*ISNUMBER(Marks!T$5:T$39))=0,"",SUMPRODUCT((Marks!$AN$5:$AN$39="bottom")*(Marks!T$5:T$39=1))/SUMPRODUCT((Marks!$AN$5:$AN$39="bottom")*ISNUMBER(Marks!T$5:T$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*ISNUMBER(Marks!T$5:T$39))=0,"",SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*(Marks!T$5:T$39=1))/SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*ISNUMBER(Marks!T$5:T$39)))</f>
         <v/>
       </c>
       <c r="L23" s="6">
@@ -4123,17 +4075,17 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Scenario set</t>
+          <t>One correct option</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Hard</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>[D]</t>
+          <t>[F]</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -4154,11 +4106,11 @@
         <v/>
       </c>
       <c r="J24" s="6">
-        <f>IF(SUMPRODUCT((Marks!$AN$5:$AN$39="top")*ISNUMBER(Marks!U$5:U$39))=0,"",SUMPRODUCT((Marks!$AN$5:$AN$39="top")*(Marks!U$5:U$39=1))/SUMPRODUCT((Marks!$AN$5:$AN$39="top")*ISNUMBER(Marks!U$5:U$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AM$5:$AM$39="top")*ISNUMBER(Marks!U$5:U$39))=0,"",SUMPRODUCT((Marks!$AM$5:$AM$39="top")*(Marks!U$5:U$39=1))/SUMPRODUCT((Marks!$AM$5:$AM$39="top")*ISNUMBER(Marks!U$5:U$39)))</f>
         <v/>
       </c>
       <c r="K24" s="6">
-        <f>IF(SUMPRODUCT((Marks!$AN$5:$AN$39="bottom")*ISNUMBER(Marks!U$5:U$39))=0,"",SUMPRODUCT((Marks!$AN$5:$AN$39="bottom")*(Marks!U$5:U$39=1))/SUMPRODUCT((Marks!$AN$5:$AN$39="bottom")*ISNUMBER(Marks!U$5:U$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*ISNUMBER(Marks!U$5:U$39))=0,"",SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*(Marks!U$5:U$39=1))/SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*ISNUMBER(Marks!U$5:U$39)))</f>
         <v/>
       </c>
       <c r="L24" s="6">
@@ -4179,7 +4131,7 @@
         <v>21</v>
       </c>
       <c r="B25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -4193,12 +4145,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>[D]</t>
+          <t>[S]</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>d</t>
+          <t>a</t>
         </is>
       </c>
       <c r="G25">
@@ -4214,11 +4166,11 @@
         <v/>
       </c>
       <c r="J25" s="6">
-        <f>IF(SUMPRODUCT((Marks!$AN$5:$AN$39="top")*ISNUMBER(Marks!V$5:V$39))=0,"",SUMPRODUCT((Marks!$AN$5:$AN$39="top")*(Marks!V$5:V$39=1))/SUMPRODUCT((Marks!$AN$5:$AN$39="top")*ISNUMBER(Marks!V$5:V$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AM$5:$AM$39="top")*ISNUMBER(Marks!V$5:V$39))=0,"",SUMPRODUCT((Marks!$AM$5:$AM$39="top")*(Marks!V$5:V$39=1))/SUMPRODUCT((Marks!$AM$5:$AM$39="top")*ISNUMBER(Marks!V$5:V$39)))</f>
         <v/>
       </c>
       <c r="K25" s="6">
-        <f>IF(SUMPRODUCT((Marks!$AN$5:$AN$39="bottom")*ISNUMBER(Marks!V$5:V$39))=0,"",SUMPRODUCT((Marks!$AN$5:$AN$39="bottom")*(Marks!V$5:V$39=1))/SUMPRODUCT((Marks!$AN$5:$AN$39="bottom")*ISNUMBER(Marks!V$5:V$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*ISNUMBER(Marks!V$5:V$39))=0,"",SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*(Marks!V$5:V$39=1))/SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*ISNUMBER(Marks!V$5:V$39)))</f>
         <v/>
       </c>
       <c r="L25" s="6">
@@ -4239,7 +4191,7 @@
         <v>22</v>
       </c>
       <c r="B26" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -4258,7 +4210,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>c</t>
+          <t>d</t>
         </is>
       </c>
       <c r="G26">
@@ -4274,11 +4226,11 @@
         <v/>
       </c>
       <c r="J26" s="6">
-        <f>IF(SUMPRODUCT((Marks!$AN$5:$AN$39="top")*ISNUMBER(Marks!W$5:W$39))=0,"",SUMPRODUCT((Marks!$AN$5:$AN$39="top")*(Marks!W$5:W$39=1))/SUMPRODUCT((Marks!$AN$5:$AN$39="top")*ISNUMBER(Marks!W$5:W$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AM$5:$AM$39="top")*ISNUMBER(Marks!W$5:W$39))=0,"",SUMPRODUCT((Marks!$AM$5:$AM$39="top")*(Marks!W$5:W$39=1))/SUMPRODUCT((Marks!$AM$5:$AM$39="top")*ISNUMBER(Marks!W$5:W$39)))</f>
         <v/>
       </c>
       <c r="K26" s="6">
-        <f>IF(SUMPRODUCT((Marks!$AN$5:$AN$39="bottom")*ISNUMBER(Marks!W$5:W$39))=0,"",SUMPRODUCT((Marks!$AN$5:$AN$39="bottom")*(Marks!W$5:W$39=1))/SUMPRODUCT((Marks!$AN$5:$AN$39="bottom")*ISNUMBER(Marks!W$5:W$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*ISNUMBER(Marks!W$5:W$39))=0,"",SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*(Marks!W$5:W$39=1))/SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*ISNUMBER(Marks!W$5:W$39)))</f>
         <v/>
       </c>
       <c r="L26" s="6">
@@ -4303,7 +4255,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Scenario set</t>
+          <t>True or false</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4318,7 +4270,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>a</t>
+          <t>d</t>
         </is>
       </c>
       <c r="G27">
@@ -4334,11 +4286,11 @@
         <v/>
       </c>
       <c r="J27" s="6">
-        <f>IF(SUMPRODUCT((Marks!$AN$5:$AN$39="top")*ISNUMBER(Marks!X$5:X$39))=0,"",SUMPRODUCT((Marks!$AN$5:$AN$39="top")*(Marks!X$5:X$39=1))/SUMPRODUCT((Marks!$AN$5:$AN$39="top")*ISNUMBER(Marks!X$5:X$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AM$5:$AM$39="top")*ISNUMBER(Marks!X$5:X$39))=0,"",SUMPRODUCT((Marks!$AM$5:$AM$39="top")*(Marks!X$5:X$39=1))/SUMPRODUCT((Marks!$AM$5:$AM$39="top")*ISNUMBER(Marks!X$5:X$39)))</f>
         <v/>
       </c>
       <c r="K27" s="6">
-        <f>IF(SUMPRODUCT((Marks!$AN$5:$AN$39="bottom")*ISNUMBER(Marks!X$5:X$39))=0,"",SUMPRODUCT((Marks!$AN$5:$AN$39="bottom")*(Marks!X$5:X$39=1))/SUMPRODUCT((Marks!$AN$5:$AN$39="bottom")*ISNUMBER(Marks!X$5:X$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*ISNUMBER(Marks!X$5:X$39))=0,"",SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*(Marks!X$5:X$39=1))/SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*ISNUMBER(Marks!X$5:X$39)))</f>
         <v/>
       </c>
       <c r="L27" s="6">
@@ -4363,7 +4315,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Scenario set</t>
+          <t>One correct option</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4373,12 +4325,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>[F]</t>
+          <t>[S]</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>a</t>
+          <t>b</t>
         </is>
       </c>
       <c r="G28">
@@ -4394,11 +4346,11 @@
         <v/>
       </c>
       <c r="J28" s="6">
-        <f>IF(SUMPRODUCT((Marks!$AN$5:$AN$39="top")*ISNUMBER(Marks!Y$5:Y$39))=0,"",SUMPRODUCT((Marks!$AN$5:$AN$39="top")*(Marks!Y$5:Y$39=1))/SUMPRODUCT((Marks!$AN$5:$AN$39="top")*ISNUMBER(Marks!Y$5:Y$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AM$5:$AM$39="top")*ISNUMBER(Marks!Y$5:Y$39))=0,"",SUMPRODUCT((Marks!$AM$5:$AM$39="top")*(Marks!Y$5:Y$39=1))/SUMPRODUCT((Marks!$AM$5:$AM$39="top")*ISNUMBER(Marks!Y$5:Y$39)))</f>
         <v/>
       </c>
       <c r="K28" s="6">
-        <f>IF(SUMPRODUCT((Marks!$AN$5:$AN$39="bottom")*ISNUMBER(Marks!Y$5:Y$39))=0,"",SUMPRODUCT((Marks!$AN$5:$AN$39="bottom")*(Marks!Y$5:Y$39=1))/SUMPRODUCT((Marks!$AN$5:$AN$39="bottom")*ISNUMBER(Marks!Y$5:Y$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*ISNUMBER(Marks!Y$5:Y$39))=0,"",SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*(Marks!Y$5:Y$39=1))/SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*ISNUMBER(Marks!Y$5:Y$39)))</f>
         <v/>
       </c>
       <c r="L28" s="6">
@@ -4423,7 +4375,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>One correct option</t>
+          <t>More than one correct</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4433,12 +4385,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>[S]</t>
+          <t>[F]</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>c</t>
+          <t>b, e</t>
         </is>
       </c>
       <c r="G29">
@@ -4454,11 +4406,11 @@
         <v/>
       </c>
       <c r="J29" s="6">
-        <f>IF(SUMPRODUCT((Marks!$AN$5:$AN$39="top")*ISNUMBER(Marks!Z$5:Z$39))=0,"",SUMPRODUCT((Marks!$AN$5:$AN$39="top")*(Marks!Z$5:Z$39=1))/SUMPRODUCT((Marks!$AN$5:$AN$39="top")*ISNUMBER(Marks!Z$5:Z$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AM$5:$AM$39="top")*ISNUMBER(Marks!Z$5:Z$39))=0,"",SUMPRODUCT((Marks!$AM$5:$AM$39="top")*(Marks!Z$5:Z$39=1))/SUMPRODUCT((Marks!$AM$5:$AM$39="top")*ISNUMBER(Marks!Z$5:Z$39)))</f>
         <v/>
       </c>
       <c r="K29" s="6">
-        <f>IF(SUMPRODUCT((Marks!$AN$5:$AN$39="bottom")*ISNUMBER(Marks!Z$5:Z$39))=0,"",SUMPRODUCT((Marks!$AN$5:$AN$39="bottom")*(Marks!Z$5:Z$39=1))/SUMPRODUCT((Marks!$AN$5:$AN$39="bottom")*ISNUMBER(Marks!Z$5:Z$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*ISNUMBER(Marks!Z$5:Z$39))=0,"",SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*(Marks!Z$5:Z$39=1))/SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*ISNUMBER(Marks!Z$5:Z$39)))</f>
         <v/>
       </c>
       <c r="L29" s="6">
@@ -4483,22 +4435,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>More than one correct</t>
+          <t>One correct option</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Hard</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>[F]</t>
+          <t>[S]</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>b, e</t>
+          <t>b</t>
         </is>
       </c>
       <c r="G30">
@@ -4514,11 +4466,11 @@
         <v/>
       </c>
       <c r="J30" s="6">
-        <f>IF(SUMPRODUCT((Marks!$AN$5:$AN$39="top")*ISNUMBER(Marks!AA$5:AA$39))=0,"",SUMPRODUCT((Marks!$AN$5:$AN$39="top")*(Marks!AA$5:AA$39=1))/SUMPRODUCT((Marks!$AN$5:$AN$39="top")*ISNUMBER(Marks!AA$5:AA$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AM$5:$AM$39="top")*ISNUMBER(Marks!AA$5:AA$39))=0,"",SUMPRODUCT((Marks!$AM$5:$AM$39="top")*(Marks!AA$5:AA$39=1))/SUMPRODUCT((Marks!$AM$5:$AM$39="top")*ISNUMBER(Marks!AA$5:AA$39)))</f>
         <v/>
       </c>
       <c r="K30" s="6">
-        <f>IF(SUMPRODUCT((Marks!$AN$5:$AN$39="bottom")*ISNUMBER(Marks!AA$5:AA$39))=0,"",SUMPRODUCT((Marks!$AN$5:$AN$39="bottom")*(Marks!AA$5:AA$39=1))/SUMPRODUCT((Marks!$AN$5:$AN$39="bottom")*ISNUMBER(Marks!AA$5:AA$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*ISNUMBER(Marks!AA$5:AA$39))=0,"",SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*(Marks!AA$5:AA$39=1))/SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*ISNUMBER(Marks!AA$5:AA$39)))</f>
         <v/>
       </c>
       <c r="L30" s="6">
@@ -4539,11 +4491,11 @@
         <v>27</v>
       </c>
       <c r="B31" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>One correct option</t>
+          <t>Scenario set</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4553,12 +4505,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>[S]</t>
+          <t>[D]</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>A fall of 2.5 percent.</t>
         </is>
       </c>
       <c r="G31">
@@ -4574,11 +4526,11 @@
         <v/>
       </c>
       <c r="J31" s="6">
-        <f>IF(SUMPRODUCT((Marks!$AN$5:$AN$39="top")*ISNUMBER(Marks!AB$5:AB$39))=0,"",SUMPRODUCT((Marks!$AN$5:$AN$39="top")*(Marks!AB$5:AB$39=1))/SUMPRODUCT((Marks!$AN$5:$AN$39="top")*ISNUMBER(Marks!AB$5:AB$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AM$5:$AM$39="top")*ISNUMBER(Marks!AB$5:AB$39))=0,"",SUMPRODUCT((Marks!$AM$5:$AM$39="top")*(Marks!AB$5:AB$39=1))/SUMPRODUCT((Marks!$AM$5:$AM$39="top")*ISNUMBER(Marks!AB$5:AB$39)))</f>
         <v/>
       </c>
       <c r="K31" s="6">
-        <f>IF(SUMPRODUCT((Marks!$AN$5:$AN$39="bottom")*ISNUMBER(Marks!AB$5:AB$39))=0,"",SUMPRODUCT((Marks!$AN$5:$AN$39="bottom")*(Marks!AB$5:AB$39=1))/SUMPRODUCT((Marks!$AN$5:$AN$39="bottom")*ISNUMBER(Marks!AB$5:AB$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*ISNUMBER(Marks!AB$5:AB$39))=0,"",SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*(Marks!AB$5:AB$39=1))/SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*ISNUMBER(Marks!AB$5:AB$39)))</f>
         <v/>
       </c>
       <c r="L31" s="6">
@@ -4599,11 +4551,11 @@
         <v>28</v>
       </c>
       <c r="B32" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>True or false</t>
+          <t>Scenario set</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4613,7 +4565,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>[S]</t>
+          <t>[D]</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -4634,11 +4586,11 @@
         <v/>
       </c>
       <c r="J32" s="6">
-        <f>IF(SUMPRODUCT((Marks!$AN$5:$AN$39="top")*ISNUMBER(Marks!AC$5:AC$39))=0,"",SUMPRODUCT((Marks!$AN$5:$AN$39="top")*(Marks!AC$5:AC$39=1))/SUMPRODUCT((Marks!$AN$5:$AN$39="top")*ISNUMBER(Marks!AC$5:AC$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AM$5:$AM$39="top")*ISNUMBER(Marks!AC$5:AC$39))=0,"",SUMPRODUCT((Marks!$AM$5:$AM$39="top")*(Marks!AC$5:AC$39=1))/SUMPRODUCT((Marks!$AM$5:$AM$39="top")*ISNUMBER(Marks!AC$5:AC$39)))</f>
         <v/>
       </c>
       <c r="K32" s="6">
-        <f>IF(SUMPRODUCT((Marks!$AN$5:$AN$39="bottom")*ISNUMBER(Marks!AC$5:AC$39))=0,"",SUMPRODUCT((Marks!$AN$5:$AN$39="bottom")*(Marks!AC$5:AC$39=1))/SUMPRODUCT((Marks!$AN$5:$AN$39="bottom")*ISNUMBER(Marks!AC$5:AC$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*ISNUMBER(Marks!AC$5:AC$39))=0,"",SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*(Marks!AC$5:AC$39=1))/SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*ISNUMBER(Marks!AC$5:AC$39)))</f>
         <v/>
       </c>
       <c r="L32" s="6">
@@ -4694,11 +4646,11 @@
         <v/>
       </c>
       <c r="J33" s="6">
-        <f>IF(SUMPRODUCT((Marks!$AN$5:$AN$39="top")*ISNUMBER(Marks!AD$5:AD$39))=0,"",SUMPRODUCT((Marks!$AN$5:$AN$39="top")*(Marks!AD$5:AD$39=1))/SUMPRODUCT((Marks!$AN$5:$AN$39="top")*ISNUMBER(Marks!AD$5:AD$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AM$5:$AM$39="top")*ISNUMBER(Marks!AD$5:AD$39))=0,"",SUMPRODUCT((Marks!$AM$5:$AM$39="top")*(Marks!AD$5:AD$39=1))/SUMPRODUCT((Marks!$AM$5:$AM$39="top")*ISNUMBER(Marks!AD$5:AD$39)))</f>
         <v/>
       </c>
       <c r="K33" s="6">
-        <f>IF(SUMPRODUCT((Marks!$AN$5:$AN$39="bottom")*ISNUMBER(Marks!AD$5:AD$39))=0,"",SUMPRODUCT((Marks!$AN$5:$AN$39="bottom")*(Marks!AD$5:AD$39=1))/SUMPRODUCT((Marks!$AN$5:$AN$39="bottom")*ISNUMBER(Marks!AD$5:AD$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*ISNUMBER(Marks!AD$5:AD$39))=0,"",SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*(Marks!AD$5:AD$39=1))/SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*ISNUMBER(Marks!AD$5:AD$39)))</f>
         <v/>
       </c>
       <c r="L33" s="6">
@@ -4728,7 +4680,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Hard</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -4754,11 +4706,11 @@
         <v/>
       </c>
       <c r="J34" s="6">
-        <f>IF(SUMPRODUCT((Marks!$AN$5:$AN$39="top")*ISNUMBER(Marks!AE$5:AE$39))=0,"",SUMPRODUCT((Marks!$AN$5:$AN$39="top")*(Marks!AE$5:AE$39=1))/SUMPRODUCT((Marks!$AN$5:$AN$39="top")*ISNUMBER(Marks!AE$5:AE$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AM$5:$AM$39="top")*ISNUMBER(Marks!AE$5:AE$39))=0,"",SUMPRODUCT((Marks!$AM$5:$AM$39="top")*(Marks!AE$5:AE$39=1))/SUMPRODUCT((Marks!$AM$5:$AM$39="top")*ISNUMBER(Marks!AE$5:AE$39)))</f>
         <v/>
       </c>
       <c r="K34" s="6">
-        <f>IF(SUMPRODUCT((Marks!$AN$5:$AN$39="bottom")*ISNUMBER(Marks!AE$5:AE$39))=0,"",SUMPRODUCT((Marks!$AN$5:$AN$39="bottom")*(Marks!AE$5:AE$39=1))/SUMPRODUCT((Marks!$AN$5:$AN$39="bottom")*ISNUMBER(Marks!AE$5:AE$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*ISNUMBER(Marks!AE$5:AE$39))=0,"",SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*(Marks!AE$5:AE$39=1))/SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*ISNUMBER(Marks!AE$5:AE$39)))</f>
         <v/>
       </c>
       <c r="L34" s="6">
@@ -4814,11 +4766,11 @@
         <v/>
       </c>
       <c r="J35" s="6">
-        <f>IF(SUMPRODUCT((Marks!$AN$5:$AN$39="top")*ISNUMBER(Marks!AF$5:AF$39))=0,"",SUMPRODUCT((Marks!$AN$5:$AN$39="top")*(Marks!AF$5:AF$39=1))/SUMPRODUCT((Marks!$AN$5:$AN$39="top")*ISNUMBER(Marks!AF$5:AF$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AM$5:$AM$39="top")*ISNUMBER(Marks!AF$5:AF$39))=0,"",SUMPRODUCT((Marks!$AM$5:$AM$39="top")*(Marks!AF$5:AF$39=1))/SUMPRODUCT((Marks!$AM$5:$AM$39="top")*ISNUMBER(Marks!AF$5:AF$39)))</f>
         <v/>
       </c>
       <c r="K35" s="6">
-        <f>IF(SUMPRODUCT((Marks!$AN$5:$AN$39="bottom")*ISNUMBER(Marks!AF$5:AF$39))=0,"",SUMPRODUCT((Marks!$AN$5:$AN$39="bottom")*(Marks!AF$5:AF$39=1))/SUMPRODUCT((Marks!$AN$5:$AN$39="bottom")*ISNUMBER(Marks!AF$5:AF$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*ISNUMBER(Marks!AF$5:AF$39))=0,"",SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*(Marks!AF$5:AF$39=1))/SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*ISNUMBER(Marks!AF$5:AF$39)))</f>
         <v/>
       </c>
       <c r="L35" s="6">
@@ -4843,12 +4795,12 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Fill in the blank</t>
+          <t>One correct option</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Hard</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -4858,7 +4810,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>d</t>
+          <t>a</t>
         </is>
       </c>
       <c r="G36">
@@ -4874,11 +4826,11 @@
         <v/>
       </c>
       <c r="J36" s="6">
-        <f>IF(SUMPRODUCT((Marks!$AN$5:$AN$39="top")*ISNUMBER(Marks!AG$5:AG$39))=0,"",SUMPRODUCT((Marks!$AN$5:$AN$39="top")*(Marks!AG$5:AG$39=1))/SUMPRODUCT((Marks!$AN$5:$AN$39="top")*ISNUMBER(Marks!AG$5:AG$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AM$5:$AM$39="top")*ISNUMBER(Marks!AG$5:AG$39))=0,"",SUMPRODUCT((Marks!$AM$5:$AM$39="top")*(Marks!AG$5:AG$39=1))/SUMPRODUCT((Marks!$AM$5:$AM$39="top")*ISNUMBER(Marks!AG$5:AG$39)))</f>
         <v/>
       </c>
       <c r="K36" s="6">
-        <f>IF(SUMPRODUCT((Marks!$AN$5:$AN$39="bottom")*ISNUMBER(Marks!AG$5:AG$39))=0,"",SUMPRODUCT((Marks!$AN$5:$AN$39="bottom")*(Marks!AG$5:AG$39=1))/SUMPRODUCT((Marks!$AN$5:$AN$39="bottom")*ISNUMBER(Marks!AG$5:AG$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*ISNUMBER(Marks!AG$5:AG$39))=0,"",SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*(Marks!AG$5:AG$39=1))/SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*ISNUMBER(Marks!AG$5:AG$39)))</f>
         <v/>
       </c>
       <c r="L36" s="6">
@@ -4903,7 +4855,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Fill in the blank</t>
+          <t>Match the following</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4913,12 +4865,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>[F]</t>
+          <t>[S]</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>c</t>
         </is>
       </c>
       <c r="G37">
@@ -4934,11 +4886,11 @@
         <v/>
       </c>
       <c r="J37" s="6">
-        <f>IF(SUMPRODUCT((Marks!$AN$5:$AN$39="top")*ISNUMBER(Marks!AH$5:AH$39))=0,"",SUMPRODUCT((Marks!$AN$5:$AN$39="top")*(Marks!AH$5:AH$39=1))/SUMPRODUCT((Marks!$AN$5:$AN$39="top")*ISNUMBER(Marks!AH$5:AH$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AM$5:$AM$39="top")*ISNUMBER(Marks!AH$5:AH$39))=0,"",SUMPRODUCT((Marks!$AM$5:$AM$39="top")*(Marks!AH$5:AH$39=1))/SUMPRODUCT((Marks!$AM$5:$AM$39="top")*ISNUMBER(Marks!AH$5:AH$39)))</f>
         <v/>
       </c>
       <c r="K37" s="6">
-        <f>IF(SUMPRODUCT((Marks!$AN$5:$AN$39="bottom")*ISNUMBER(Marks!AH$5:AH$39))=0,"",SUMPRODUCT((Marks!$AN$5:$AN$39="bottom")*(Marks!AH$5:AH$39=1))/SUMPRODUCT((Marks!$AN$5:$AN$39="bottom")*ISNUMBER(Marks!AH$5:AH$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*ISNUMBER(Marks!AH$5:AH$39))=0,"",SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*(Marks!AH$5:AH$39=1))/SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*ISNUMBER(Marks!AH$5:AH$39)))</f>
         <v/>
       </c>
       <c r="L37" s="6">
@@ -4978,7 +4930,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>c</t>
+          <t>f</t>
         </is>
       </c>
       <c r="G38">
@@ -4994,11 +4946,11 @@
         <v/>
       </c>
       <c r="J38" s="6">
-        <f>IF(SUMPRODUCT((Marks!$AN$5:$AN$39="top")*ISNUMBER(Marks!AI$5:AI$39))=0,"",SUMPRODUCT((Marks!$AN$5:$AN$39="top")*(Marks!AI$5:AI$39=1))/SUMPRODUCT((Marks!$AN$5:$AN$39="top")*ISNUMBER(Marks!AI$5:AI$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AM$5:$AM$39="top")*ISNUMBER(Marks!AI$5:AI$39))=0,"",SUMPRODUCT((Marks!$AM$5:$AM$39="top")*(Marks!AI$5:AI$39=1))/SUMPRODUCT((Marks!$AM$5:$AM$39="top")*ISNUMBER(Marks!AI$5:AI$39)))</f>
         <v/>
       </c>
       <c r="K38" s="6">
-        <f>IF(SUMPRODUCT((Marks!$AN$5:$AN$39="bottom")*ISNUMBER(Marks!AI$5:AI$39))=0,"",SUMPRODUCT((Marks!$AN$5:$AN$39="bottom")*(Marks!AI$5:AI$39=1))/SUMPRODUCT((Marks!$AN$5:$AN$39="bottom")*ISNUMBER(Marks!AI$5:AI$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*ISNUMBER(Marks!AI$5:AI$39))=0,"",SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*(Marks!AI$5:AI$39=1))/SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*ISNUMBER(Marks!AI$5:AI$39)))</f>
         <v/>
       </c>
       <c r="L38" s="6">
@@ -5038,7 +4990,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>f</t>
+          <t>a</t>
         </is>
       </c>
       <c r="G39">
@@ -5054,11 +5006,11 @@
         <v/>
       </c>
       <c r="J39" s="6">
-        <f>IF(SUMPRODUCT((Marks!$AN$5:$AN$39="top")*ISNUMBER(Marks!AJ$5:AJ$39))=0,"",SUMPRODUCT((Marks!$AN$5:$AN$39="top")*(Marks!AJ$5:AJ$39=1))/SUMPRODUCT((Marks!$AN$5:$AN$39="top")*ISNUMBER(Marks!AJ$5:AJ$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AM$5:$AM$39="top")*ISNUMBER(Marks!AJ$5:AJ$39))=0,"",SUMPRODUCT((Marks!$AM$5:$AM$39="top")*(Marks!AJ$5:AJ$39=1))/SUMPRODUCT((Marks!$AM$5:$AM$39="top")*ISNUMBER(Marks!AJ$5:AJ$39)))</f>
         <v/>
       </c>
       <c r="K39" s="6">
-        <f>IF(SUMPRODUCT((Marks!$AN$5:$AN$39="bottom")*ISNUMBER(Marks!AJ$5:AJ$39))=0,"",SUMPRODUCT((Marks!$AN$5:$AN$39="bottom")*(Marks!AJ$5:AJ$39=1))/SUMPRODUCT((Marks!$AN$5:$AN$39="bottom")*ISNUMBER(Marks!AJ$5:AJ$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*ISNUMBER(Marks!AJ$5:AJ$39))=0,"",SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*(Marks!AJ$5:AJ$39=1))/SUMPRODUCT((Marks!$AM$5:$AM$39="bottom")*ISNUMBER(Marks!AJ$5:AJ$39)))</f>
         <v/>
       </c>
       <c r="L39" s="6">
@@ -5071,66 +5023,6 @@
       </c>
       <c r="N39">
         <f>IF(H39=0,"",I39+ROW()/1000000)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="n">
-        <v>36</v>
-      </c>
-      <c r="B40" t="n">
-        <v>5</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Match the following</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>[S]</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
-      <c r="G40">
-        <f>COUNTIF(Marks!AK$5:AK$39,1)</f>
-        <v/>
-      </c>
-      <c r="H40">
-        <f>COUNT(Marks!AK$5:AK$39)</f>
-        <v/>
-      </c>
-      <c r="I40" s="6">
-        <f>IF(H40=0,"",G40/H40)</f>
-        <v/>
-      </c>
-      <c r="J40" s="6">
-        <f>IF(SUMPRODUCT((Marks!$AN$5:$AN$39="top")*ISNUMBER(Marks!AK$5:AK$39))=0,"",SUMPRODUCT((Marks!$AN$5:$AN$39="top")*(Marks!AK$5:AK$39=1))/SUMPRODUCT((Marks!$AN$5:$AN$39="top")*ISNUMBER(Marks!AK$5:AK$39)))</f>
-        <v/>
-      </c>
-      <c r="K40" s="6">
-        <f>IF(SUMPRODUCT((Marks!$AN$5:$AN$39="bottom")*ISNUMBER(Marks!AK$5:AK$39))=0,"",SUMPRODUCT((Marks!$AN$5:$AN$39="bottom")*(Marks!AK$5:AK$39=1))/SUMPRODUCT((Marks!$AN$5:$AN$39="bottom")*ISNUMBER(Marks!AK$5:AK$39)))</f>
-        <v/>
-      </c>
-      <c r="L40" s="6">
-        <f>IF(OR(J40="",K40=""),"",J40-K40)</f>
-        <v/>
-      </c>
-      <c r="M40">
-        <f>IF(H40=0,"",IF(I40&lt;0.2,"Check the item: fewer than one in five got it right",IF(AND(L40&lt;&gt;"",N(L40)&lt;0),"Check the item: the bottom third beat the top third","")))</f>
-        <v/>
-      </c>
-      <c r="N40">
-        <f>IF(H40=0,"",I40+ROW()/1000000)</f>
         <v/>
       </c>
     </row>
@@ -5145,7 +5037,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F40"/>
+  <dimension ref="A1:F39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="6" max="6"/>
@@ -5160,7 +5052,7 @@
     </row>
     <row r="2">
       <c r="B2">
-        <f>IF(SUM(Items!H5:H40)=0,"No marks entered yet.","Most-missed first: take the items from the top.")</f>
+        <f>IF(SUM(Items!H5:H39)=0,"No marks entered yet.","Most-missed first: take the items from the top.")</f>
         <v/>
       </c>
     </row>
@@ -5201,23 +5093,23 @@
         <v>1</v>
       </c>
       <c r="B5">
-        <f>IF(COUNT(Items!$N$5:$N$40)&lt;A5,"",INDEX(Items!$A$5:$A$40,MATCH(SMALL(Items!$N$5:$N$40,A5),Items!$N$5:$N$40,0)))</f>
+        <f>IF(COUNT(Items!$N$5:$N$39)&lt;A5,"",INDEX(Items!$A$5:$A$39,MATCH(SMALL(Items!$N$5:$N$39,A5),Items!$N$5:$N$39,0)))</f>
         <v/>
       </c>
       <c r="C5" s="6">
-        <f>IF(B5="","",INDEX(Items!$I$5:$I$40,MATCH(B5,Items!$A$5:$A$40,0)))</f>
+        <f>IF(B5="","",INDEX(Items!$I$5:$I$39,MATCH(B5,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
       <c r="D5">
-        <f>IF(B5="","",INDEX(Items!$B$5:$B$40,MATCH(B5,Items!$A$5:$A$40,0)))</f>
+        <f>IF(B5="","",INDEX(Items!$B$5:$B$39,MATCH(B5,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
       <c r="E5">
-        <f>IF(B5="","",INDEX(Items!$E$5:$E$40,MATCH(B5,Items!$A$5:$A$40,0)))</f>
+        <f>IF(B5="","",INDEX(Items!$E$5:$E$39,MATCH(B5,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
       <c r="F5">
-        <f>IF(B5="","",INDEX(Items!$M$5:$M$40,MATCH(B5,Items!$A$5:$A$40,0)))</f>
+        <f>IF(B5="","",INDEX(Items!$M$5:$M$39,MATCH(B5,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
     </row>
@@ -5226,23 +5118,23 @@
         <v>2</v>
       </c>
       <c r="B6">
-        <f>IF(COUNT(Items!$N$5:$N$40)&lt;A6,"",INDEX(Items!$A$5:$A$40,MATCH(SMALL(Items!$N$5:$N$40,A6),Items!$N$5:$N$40,0)))</f>
+        <f>IF(COUNT(Items!$N$5:$N$39)&lt;A6,"",INDEX(Items!$A$5:$A$39,MATCH(SMALL(Items!$N$5:$N$39,A6),Items!$N$5:$N$39,0)))</f>
         <v/>
       </c>
       <c r="C6" s="6">
-        <f>IF(B6="","",INDEX(Items!$I$5:$I$40,MATCH(B6,Items!$A$5:$A$40,0)))</f>
+        <f>IF(B6="","",INDEX(Items!$I$5:$I$39,MATCH(B6,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
       <c r="D6">
-        <f>IF(B6="","",INDEX(Items!$B$5:$B$40,MATCH(B6,Items!$A$5:$A$40,0)))</f>
+        <f>IF(B6="","",INDEX(Items!$B$5:$B$39,MATCH(B6,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
       <c r="E6">
-        <f>IF(B6="","",INDEX(Items!$E$5:$E$40,MATCH(B6,Items!$A$5:$A$40,0)))</f>
+        <f>IF(B6="","",INDEX(Items!$E$5:$E$39,MATCH(B6,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
       <c r="F6">
-        <f>IF(B6="","",INDEX(Items!$M$5:$M$40,MATCH(B6,Items!$A$5:$A$40,0)))</f>
+        <f>IF(B6="","",INDEX(Items!$M$5:$M$39,MATCH(B6,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
     </row>
@@ -5251,23 +5143,23 @@
         <v>3</v>
       </c>
       <c r="B7">
-        <f>IF(COUNT(Items!$N$5:$N$40)&lt;A7,"",INDEX(Items!$A$5:$A$40,MATCH(SMALL(Items!$N$5:$N$40,A7),Items!$N$5:$N$40,0)))</f>
+        <f>IF(COUNT(Items!$N$5:$N$39)&lt;A7,"",INDEX(Items!$A$5:$A$39,MATCH(SMALL(Items!$N$5:$N$39,A7),Items!$N$5:$N$39,0)))</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>IF(B7="","",INDEX(Items!$I$5:$I$40,MATCH(B7,Items!$A$5:$A$40,0)))</f>
+        <f>IF(B7="","",INDEX(Items!$I$5:$I$39,MATCH(B7,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
       <c r="D7">
-        <f>IF(B7="","",INDEX(Items!$B$5:$B$40,MATCH(B7,Items!$A$5:$A$40,0)))</f>
+        <f>IF(B7="","",INDEX(Items!$B$5:$B$39,MATCH(B7,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
       <c r="E7">
-        <f>IF(B7="","",INDEX(Items!$E$5:$E$40,MATCH(B7,Items!$A$5:$A$40,0)))</f>
+        <f>IF(B7="","",INDEX(Items!$E$5:$E$39,MATCH(B7,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
       <c r="F7">
-        <f>IF(B7="","",INDEX(Items!$M$5:$M$40,MATCH(B7,Items!$A$5:$A$40,0)))</f>
+        <f>IF(B7="","",INDEX(Items!$M$5:$M$39,MATCH(B7,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
     </row>
@@ -5276,23 +5168,23 @@
         <v>4</v>
       </c>
       <c r="B8">
-        <f>IF(COUNT(Items!$N$5:$N$40)&lt;A8,"",INDEX(Items!$A$5:$A$40,MATCH(SMALL(Items!$N$5:$N$40,A8),Items!$N$5:$N$40,0)))</f>
+        <f>IF(COUNT(Items!$N$5:$N$39)&lt;A8,"",INDEX(Items!$A$5:$A$39,MATCH(SMALL(Items!$N$5:$N$39,A8),Items!$N$5:$N$39,0)))</f>
         <v/>
       </c>
       <c r="C8" s="6">
-        <f>IF(B8="","",INDEX(Items!$I$5:$I$40,MATCH(B8,Items!$A$5:$A$40,0)))</f>
+        <f>IF(B8="","",INDEX(Items!$I$5:$I$39,MATCH(B8,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
       <c r="D8">
-        <f>IF(B8="","",INDEX(Items!$B$5:$B$40,MATCH(B8,Items!$A$5:$A$40,0)))</f>
+        <f>IF(B8="","",INDEX(Items!$B$5:$B$39,MATCH(B8,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
       <c r="E8">
-        <f>IF(B8="","",INDEX(Items!$E$5:$E$40,MATCH(B8,Items!$A$5:$A$40,0)))</f>
+        <f>IF(B8="","",INDEX(Items!$E$5:$E$39,MATCH(B8,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
       <c r="F8">
-        <f>IF(B8="","",INDEX(Items!$M$5:$M$40,MATCH(B8,Items!$A$5:$A$40,0)))</f>
+        <f>IF(B8="","",INDEX(Items!$M$5:$M$39,MATCH(B8,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
     </row>
@@ -5301,23 +5193,23 @@
         <v>5</v>
       </c>
       <c r="B9">
-        <f>IF(COUNT(Items!$N$5:$N$40)&lt;A9,"",INDEX(Items!$A$5:$A$40,MATCH(SMALL(Items!$N$5:$N$40,A9),Items!$N$5:$N$40,0)))</f>
+        <f>IF(COUNT(Items!$N$5:$N$39)&lt;A9,"",INDEX(Items!$A$5:$A$39,MATCH(SMALL(Items!$N$5:$N$39,A9),Items!$N$5:$N$39,0)))</f>
         <v/>
       </c>
       <c r="C9" s="6">
-        <f>IF(B9="","",INDEX(Items!$I$5:$I$40,MATCH(B9,Items!$A$5:$A$40,0)))</f>
+        <f>IF(B9="","",INDEX(Items!$I$5:$I$39,MATCH(B9,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
       <c r="D9">
-        <f>IF(B9="","",INDEX(Items!$B$5:$B$40,MATCH(B9,Items!$A$5:$A$40,0)))</f>
+        <f>IF(B9="","",INDEX(Items!$B$5:$B$39,MATCH(B9,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
       <c r="E9">
-        <f>IF(B9="","",INDEX(Items!$E$5:$E$40,MATCH(B9,Items!$A$5:$A$40,0)))</f>
+        <f>IF(B9="","",INDEX(Items!$E$5:$E$39,MATCH(B9,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
       <c r="F9">
-        <f>IF(B9="","",INDEX(Items!$M$5:$M$40,MATCH(B9,Items!$A$5:$A$40,0)))</f>
+        <f>IF(B9="","",INDEX(Items!$M$5:$M$39,MATCH(B9,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
     </row>
@@ -5326,23 +5218,23 @@
         <v>6</v>
       </c>
       <c r="B10">
-        <f>IF(COUNT(Items!$N$5:$N$40)&lt;A10,"",INDEX(Items!$A$5:$A$40,MATCH(SMALL(Items!$N$5:$N$40,A10),Items!$N$5:$N$40,0)))</f>
+        <f>IF(COUNT(Items!$N$5:$N$39)&lt;A10,"",INDEX(Items!$A$5:$A$39,MATCH(SMALL(Items!$N$5:$N$39,A10),Items!$N$5:$N$39,0)))</f>
         <v/>
       </c>
       <c r="C10" s="6">
-        <f>IF(B10="","",INDEX(Items!$I$5:$I$40,MATCH(B10,Items!$A$5:$A$40,0)))</f>
+        <f>IF(B10="","",INDEX(Items!$I$5:$I$39,MATCH(B10,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
       <c r="D10">
-        <f>IF(B10="","",INDEX(Items!$B$5:$B$40,MATCH(B10,Items!$A$5:$A$40,0)))</f>
+        <f>IF(B10="","",INDEX(Items!$B$5:$B$39,MATCH(B10,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
       <c r="E10">
-        <f>IF(B10="","",INDEX(Items!$E$5:$E$40,MATCH(B10,Items!$A$5:$A$40,0)))</f>
+        <f>IF(B10="","",INDEX(Items!$E$5:$E$39,MATCH(B10,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
       <c r="F10">
-        <f>IF(B10="","",INDEX(Items!$M$5:$M$40,MATCH(B10,Items!$A$5:$A$40,0)))</f>
+        <f>IF(B10="","",INDEX(Items!$M$5:$M$39,MATCH(B10,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
     </row>
@@ -5351,23 +5243,23 @@
         <v>7</v>
       </c>
       <c r="B11">
-        <f>IF(COUNT(Items!$N$5:$N$40)&lt;A11,"",INDEX(Items!$A$5:$A$40,MATCH(SMALL(Items!$N$5:$N$40,A11),Items!$N$5:$N$40,0)))</f>
+        <f>IF(COUNT(Items!$N$5:$N$39)&lt;A11,"",INDEX(Items!$A$5:$A$39,MATCH(SMALL(Items!$N$5:$N$39,A11),Items!$N$5:$N$39,0)))</f>
         <v/>
       </c>
       <c r="C11" s="6">
-        <f>IF(B11="","",INDEX(Items!$I$5:$I$40,MATCH(B11,Items!$A$5:$A$40,0)))</f>
+        <f>IF(B11="","",INDEX(Items!$I$5:$I$39,MATCH(B11,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
       <c r="D11">
-        <f>IF(B11="","",INDEX(Items!$B$5:$B$40,MATCH(B11,Items!$A$5:$A$40,0)))</f>
+        <f>IF(B11="","",INDEX(Items!$B$5:$B$39,MATCH(B11,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
       <c r="E11">
-        <f>IF(B11="","",INDEX(Items!$E$5:$E$40,MATCH(B11,Items!$A$5:$A$40,0)))</f>
+        <f>IF(B11="","",INDEX(Items!$E$5:$E$39,MATCH(B11,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
       <c r="F11">
-        <f>IF(B11="","",INDEX(Items!$M$5:$M$40,MATCH(B11,Items!$A$5:$A$40,0)))</f>
+        <f>IF(B11="","",INDEX(Items!$M$5:$M$39,MATCH(B11,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
     </row>
@@ -5376,23 +5268,23 @@
         <v>8</v>
       </c>
       <c r="B12">
-        <f>IF(COUNT(Items!$N$5:$N$40)&lt;A12,"",INDEX(Items!$A$5:$A$40,MATCH(SMALL(Items!$N$5:$N$40,A12),Items!$N$5:$N$40,0)))</f>
+        <f>IF(COUNT(Items!$N$5:$N$39)&lt;A12,"",INDEX(Items!$A$5:$A$39,MATCH(SMALL(Items!$N$5:$N$39,A12),Items!$N$5:$N$39,0)))</f>
         <v/>
       </c>
       <c r="C12" s="6">
-        <f>IF(B12="","",INDEX(Items!$I$5:$I$40,MATCH(B12,Items!$A$5:$A$40,0)))</f>
+        <f>IF(B12="","",INDEX(Items!$I$5:$I$39,MATCH(B12,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
       <c r="D12">
-        <f>IF(B12="","",INDEX(Items!$B$5:$B$40,MATCH(B12,Items!$A$5:$A$40,0)))</f>
+        <f>IF(B12="","",INDEX(Items!$B$5:$B$39,MATCH(B12,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
       <c r="E12">
-        <f>IF(B12="","",INDEX(Items!$E$5:$E$40,MATCH(B12,Items!$A$5:$A$40,0)))</f>
+        <f>IF(B12="","",INDEX(Items!$E$5:$E$39,MATCH(B12,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
       <c r="F12">
-        <f>IF(B12="","",INDEX(Items!$M$5:$M$40,MATCH(B12,Items!$A$5:$A$40,0)))</f>
+        <f>IF(B12="","",INDEX(Items!$M$5:$M$39,MATCH(B12,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
     </row>
@@ -5401,23 +5293,23 @@
         <v>9</v>
       </c>
       <c r="B13">
-        <f>IF(COUNT(Items!$N$5:$N$40)&lt;A13,"",INDEX(Items!$A$5:$A$40,MATCH(SMALL(Items!$N$5:$N$40,A13),Items!$N$5:$N$40,0)))</f>
+        <f>IF(COUNT(Items!$N$5:$N$39)&lt;A13,"",INDEX(Items!$A$5:$A$39,MATCH(SMALL(Items!$N$5:$N$39,A13),Items!$N$5:$N$39,0)))</f>
         <v/>
       </c>
       <c r="C13" s="6">
-        <f>IF(B13="","",INDEX(Items!$I$5:$I$40,MATCH(B13,Items!$A$5:$A$40,0)))</f>
+        <f>IF(B13="","",INDEX(Items!$I$5:$I$39,MATCH(B13,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
       <c r="D13">
-        <f>IF(B13="","",INDEX(Items!$B$5:$B$40,MATCH(B13,Items!$A$5:$A$40,0)))</f>
+        <f>IF(B13="","",INDEX(Items!$B$5:$B$39,MATCH(B13,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
       <c r="E13">
-        <f>IF(B13="","",INDEX(Items!$E$5:$E$40,MATCH(B13,Items!$A$5:$A$40,0)))</f>
+        <f>IF(B13="","",INDEX(Items!$E$5:$E$39,MATCH(B13,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
       <c r="F13">
-        <f>IF(B13="","",INDEX(Items!$M$5:$M$40,MATCH(B13,Items!$A$5:$A$40,0)))</f>
+        <f>IF(B13="","",INDEX(Items!$M$5:$M$39,MATCH(B13,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
     </row>
@@ -5426,23 +5318,23 @@
         <v>10</v>
       </c>
       <c r="B14">
-        <f>IF(COUNT(Items!$N$5:$N$40)&lt;A14,"",INDEX(Items!$A$5:$A$40,MATCH(SMALL(Items!$N$5:$N$40,A14),Items!$N$5:$N$40,0)))</f>
+        <f>IF(COUNT(Items!$N$5:$N$39)&lt;A14,"",INDEX(Items!$A$5:$A$39,MATCH(SMALL(Items!$N$5:$N$39,A14),Items!$N$5:$N$39,0)))</f>
         <v/>
       </c>
       <c r="C14" s="6">
-        <f>IF(B14="","",INDEX(Items!$I$5:$I$40,MATCH(B14,Items!$A$5:$A$40,0)))</f>
+        <f>IF(B14="","",INDEX(Items!$I$5:$I$39,MATCH(B14,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
       <c r="D14">
-        <f>IF(B14="","",INDEX(Items!$B$5:$B$40,MATCH(B14,Items!$A$5:$A$40,0)))</f>
+        <f>IF(B14="","",INDEX(Items!$B$5:$B$39,MATCH(B14,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
       <c r="E14">
-        <f>IF(B14="","",INDEX(Items!$E$5:$E$40,MATCH(B14,Items!$A$5:$A$40,0)))</f>
+        <f>IF(B14="","",INDEX(Items!$E$5:$E$39,MATCH(B14,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
       <c r="F14">
-        <f>IF(B14="","",INDEX(Items!$M$5:$M$40,MATCH(B14,Items!$A$5:$A$40,0)))</f>
+        <f>IF(B14="","",INDEX(Items!$M$5:$M$39,MATCH(B14,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
     </row>
@@ -5451,23 +5343,23 @@
         <v>11</v>
       </c>
       <c r="B15">
-        <f>IF(COUNT(Items!$N$5:$N$40)&lt;A15,"",INDEX(Items!$A$5:$A$40,MATCH(SMALL(Items!$N$5:$N$40,A15),Items!$N$5:$N$40,0)))</f>
+        <f>IF(COUNT(Items!$N$5:$N$39)&lt;A15,"",INDEX(Items!$A$5:$A$39,MATCH(SMALL(Items!$N$5:$N$39,A15),Items!$N$5:$N$39,0)))</f>
         <v/>
       </c>
       <c r="C15" s="6">
-        <f>IF(B15="","",INDEX(Items!$I$5:$I$40,MATCH(B15,Items!$A$5:$A$40,0)))</f>
+        <f>IF(B15="","",INDEX(Items!$I$5:$I$39,MATCH(B15,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
       <c r="D15">
-        <f>IF(B15="","",INDEX(Items!$B$5:$B$40,MATCH(B15,Items!$A$5:$A$40,0)))</f>
+        <f>IF(B15="","",INDEX(Items!$B$5:$B$39,MATCH(B15,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
       <c r="E15">
-        <f>IF(B15="","",INDEX(Items!$E$5:$E$40,MATCH(B15,Items!$A$5:$A$40,0)))</f>
+        <f>IF(B15="","",INDEX(Items!$E$5:$E$39,MATCH(B15,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
       <c r="F15">
-        <f>IF(B15="","",INDEX(Items!$M$5:$M$40,MATCH(B15,Items!$A$5:$A$40,0)))</f>
+        <f>IF(B15="","",INDEX(Items!$M$5:$M$39,MATCH(B15,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
     </row>
@@ -5476,23 +5368,23 @@
         <v>12</v>
       </c>
       <c r="B16">
-        <f>IF(COUNT(Items!$N$5:$N$40)&lt;A16,"",INDEX(Items!$A$5:$A$40,MATCH(SMALL(Items!$N$5:$N$40,A16),Items!$N$5:$N$40,0)))</f>
+        <f>IF(COUNT(Items!$N$5:$N$39)&lt;A16,"",INDEX(Items!$A$5:$A$39,MATCH(SMALL(Items!$N$5:$N$39,A16),Items!$N$5:$N$39,0)))</f>
         <v/>
       </c>
       <c r="C16" s="6">
-        <f>IF(B16="","",INDEX(Items!$I$5:$I$40,MATCH(B16,Items!$A$5:$A$40,0)))</f>
+        <f>IF(B16="","",INDEX(Items!$I$5:$I$39,MATCH(B16,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
       <c r="D16">
-        <f>IF(B16="","",INDEX(Items!$B$5:$B$40,MATCH(B16,Items!$A$5:$A$40,0)))</f>
+        <f>IF(B16="","",INDEX(Items!$B$5:$B$39,MATCH(B16,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
       <c r="E16">
-        <f>IF(B16="","",INDEX(Items!$E$5:$E$40,MATCH(B16,Items!$A$5:$A$40,0)))</f>
+        <f>IF(B16="","",INDEX(Items!$E$5:$E$39,MATCH(B16,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
       <c r="F16">
-        <f>IF(B16="","",INDEX(Items!$M$5:$M$40,MATCH(B16,Items!$A$5:$A$40,0)))</f>
+        <f>IF(B16="","",INDEX(Items!$M$5:$M$39,MATCH(B16,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
     </row>
@@ -5501,23 +5393,23 @@
         <v>13</v>
       </c>
       <c r="B17">
-        <f>IF(COUNT(Items!$N$5:$N$40)&lt;A17,"",INDEX(Items!$A$5:$A$40,MATCH(SMALL(Items!$N$5:$N$40,A17),Items!$N$5:$N$40,0)))</f>
+        <f>IF(COUNT(Items!$N$5:$N$39)&lt;A17,"",INDEX(Items!$A$5:$A$39,MATCH(SMALL(Items!$N$5:$N$39,A17),Items!$N$5:$N$39,0)))</f>
         <v/>
       </c>
       <c r="C17" s="6">
-        <f>IF(B17="","",INDEX(Items!$I$5:$I$40,MATCH(B17,Items!$A$5:$A$40,0)))</f>
+        <f>IF(B17="","",INDEX(Items!$I$5:$I$39,MATCH(B17,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
       <c r="D17">
-        <f>IF(B17="","",INDEX(Items!$B$5:$B$40,MATCH(B17,Items!$A$5:$A$40,0)))</f>
+        <f>IF(B17="","",INDEX(Items!$B$5:$B$39,MATCH(B17,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
       <c r="E17">
-        <f>IF(B17="","",INDEX(Items!$E$5:$E$40,MATCH(B17,Items!$A$5:$A$40,0)))</f>
+        <f>IF(B17="","",INDEX(Items!$E$5:$E$39,MATCH(B17,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
       <c r="F17">
-        <f>IF(B17="","",INDEX(Items!$M$5:$M$40,MATCH(B17,Items!$A$5:$A$40,0)))</f>
+        <f>IF(B17="","",INDEX(Items!$M$5:$M$39,MATCH(B17,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
     </row>
@@ -5526,23 +5418,23 @@
         <v>14</v>
       </c>
       <c r="B18">
-        <f>IF(COUNT(Items!$N$5:$N$40)&lt;A18,"",INDEX(Items!$A$5:$A$40,MATCH(SMALL(Items!$N$5:$N$40,A18),Items!$N$5:$N$40,0)))</f>
+        <f>IF(COUNT(Items!$N$5:$N$39)&lt;A18,"",INDEX(Items!$A$5:$A$39,MATCH(SMALL(Items!$N$5:$N$39,A18),Items!$N$5:$N$39,0)))</f>
         <v/>
       </c>
       <c r="C18" s="6">
-        <f>IF(B18="","",INDEX(Items!$I$5:$I$40,MATCH(B18,Items!$A$5:$A$40,0)))</f>
+        <f>IF(B18="","",INDEX(Items!$I$5:$I$39,MATCH(B18,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
       <c r="D18">
-        <f>IF(B18="","",INDEX(Items!$B$5:$B$40,MATCH(B18,Items!$A$5:$A$40,0)))</f>
+        <f>IF(B18="","",INDEX(Items!$B$5:$B$39,MATCH(B18,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
       <c r="E18">
-        <f>IF(B18="","",INDEX(Items!$E$5:$E$40,MATCH(B18,Items!$A$5:$A$40,0)))</f>
+        <f>IF(B18="","",INDEX(Items!$E$5:$E$39,MATCH(B18,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
       <c r="F18">
-        <f>IF(B18="","",INDEX(Items!$M$5:$M$40,MATCH(B18,Items!$A$5:$A$40,0)))</f>
+        <f>IF(B18="","",INDEX(Items!$M$5:$M$39,MATCH(B18,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
     </row>
@@ -5551,23 +5443,23 @@
         <v>15</v>
       </c>
       <c r="B19">
-        <f>IF(COUNT(Items!$N$5:$N$40)&lt;A19,"",INDEX(Items!$A$5:$A$40,MATCH(SMALL(Items!$N$5:$N$40,A19),Items!$N$5:$N$40,0)))</f>
+        <f>IF(COUNT(Items!$N$5:$N$39)&lt;A19,"",INDEX(Items!$A$5:$A$39,MATCH(SMALL(Items!$N$5:$N$39,A19),Items!$N$5:$N$39,0)))</f>
         <v/>
       </c>
       <c r="C19" s="6">
-        <f>IF(B19="","",INDEX(Items!$I$5:$I$40,MATCH(B19,Items!$A$5:$A$40,0)))</f>
+        <f>IF(B19="","",INDEX(Items!$I$5:$I$39,MATCH(B19,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
       <c r="D19">
-        <f>IF(B19="","",INDEX(Items!$B$5:$B$40,MATCH(B19,Items!$A$5:$A$40,0)))</f>
+        <f>IF(B19="","",INDEX(Items!$B$5:$B$39,MATCH(B19,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
       <c r="E19">
-        <f>IF(B19="","",INDEX(Items!$E$5:$E$40,MATCH(B19,Items!$A$5:$A$40,0)))</f>
+        <f>IF(B19="","",INDEX(Items!$E$5:$E$39,MATCH(B19,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
       <c r="F19">
-        <f>IF(B19="","",INDEX(Items!$M$5:$M$40,MATCH(B19,Items!$A$5:$A$40,0)))</f>
+        <f>IF(B19="","",INDEX(Items!$M$5:$M$39,MATCH(B19,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
     </row>
@@ -5576,23 +5468,23 @@
         <v>16</v>
       </c>
       <c r="B20">
-        <f>IF(COUNT(Items!$N$5:$N$40)&lt;A20,"",INDEX(Items!$A$5:$A$40,MATCH(SMALL(Items!$N$5:$N$40,A20),Items!$N$5:$N$40,0)))</f>
+        <f>IF(COUNT(Items!$N$5:$N$39)&lt;A20,"",INDEX(Items!$A$5:$A$39,MATCH(SMALL(Items!$N$5:$N$39,A20),Items!$N$5:$N$39,0)))</f>
         <v/>
       </c>
       <c r="C20" s="6">
-        <f>IF(B20="","",INDEX(Items!$I$5:$I$40,MATCH(B20,Items!$A$5:$A$40,0)))</f>
+        <f>IF(B20="","",INDEX(Items!$I$5:$I$39,MATCH(B20,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
       <c r="D20">
-        <f>IF(B20="","",INDEX(Items!$B$5:$B$40,MATCH(B20,Items!$A$5:$A$40,0)))</f>
+        <f>IF(B20="","",INDEX(Items!$B$5:$B$39,MATCH(B20,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
       <c r="E20">
-        <f>IF(B20="","",INDEX(Items!$E$5:$E$40,MATCH(B20,Items!$A$5:$A$40,0)))</f>
+        <f>IF(B20="","",INDEX(Items!$E$5:$E$39,MATCH(B20,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
       <c r="F20">
-        <f>IF(B20="","",INDEX(Items!$M$5:$M$40,MATCH(B20,Items!$A$5:$A$40,0)))</f>
+        <f>IF(B20="","",INDEX(Items!$M$5:$M$39,MATCH(B20,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
     </row>
@@ -5601,23 +5493,23 @@
         <v>17</v>
       </c>
       <c r="B21">
-        <f>IF(COUNT(Items!$N$5:$N$40)&lt;A21,"",INDEX(Items!$A$5:$A$40,MATCH(SMALL(Items!$N$5:$N$40,A21),Items!$N$5:$N$40,0)))</f>
+        <f>IF(COUNT(Items!$N$5:$N$39)&lt;A21,"",INDEX(Items!$A$5:$A$39,MATCH(SMALL(Items!$N$5:$N$39,A21),Items!$N$5:$N$39,0)))</f>
         <v/>
       </c>
       <c r="C21" s="6">
-        <f>IF(B21="","",INDEX(Items!$I$5:$I$40,MATCH(B21,Items!$A$5:$A$40,0)))</f>
+        <f>IF(B21="","",INDEX(Items!$I$5:$I$39,MATCH(B21,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
       <c r="D21">
-        <f>IF(B21="","",INDEX(Items!$B$5:$B$40,MATCH(B21,Items!$A$5:$A$40,0)))</f>
+        <f>IF(B21="","",INDEX(Items!$B$5:$B$39,MATCH(B21,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
       <c r="E21">
-        <f>IF(B21="","",INDEX(Items!$E$5:$E$40,MATCH(B21,Items!$A$5:$A$40,0)))</f>
+        <f>IF(B21="","",INDEX(Items!$E$5:$E$39,MATCH(B21,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
       <c r="F21">
-        <f>IF(B21="","",INDEX(Items!$M$5:$M$40,MATCH(B21,Items!$A$5:$A$40,0)))</f>
+        <f>IF(B21="","",INDEX(Items!$M$5:$M$39,MATCH(B21,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
     </row>
@@ -5626,23 +5518,23 @@
         <v>18</v>
       </c>
       <c r="B22">
-        <f>IF(COUNT(Items!$N$5:$N$40)&lt;A22,"",INDEX(Items!$A$5:$A$40,MATCH(SMALL(Items!$N$5:$N$40,A22),Items!$N$5:$N$40,0)))</f>
+        <f>IF(COUNT(Items!$N$5:$N$39)&lt;A22,"",INDEX(Items!$A$5:$A$39,MATCH(SMALL(Items!$N$5:$N$39,A22),Items!$N$5:$N$39,0)))</f>
         <v/>
       </c>
       <c r="C22" s="6">
-        <f>IF(B22="","",INDEX(Items!$I$5:$I$40,MATCH(B22,Items!$A$5:$A$40,0)))</f>
+        <f>IF(B22="","",INDEX(Items!$I$5:$I$39,MATCH(B22,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
       <c r="D22">
-        <f>IF(B22="","",INDEX(Items!$B$5:$B$40,MATCH(B22,Items!$A$5:$A$40,0)))</f>
+        <f>IF(B22="","",INDEX(Items!$B$5:$B$39,MATCH(B22,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
       <c r="E22">
-        <f>IF(B22="","",INDEX(Items!$E$5:$E$40,MATCH(B22,Items!$A$5:$A$40,0)))</f>
+        <f>IF(B22="","",INDEX(Items!$E$5:$E$39,MATCH(B22,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
       <c r="F22">
-        <f>IF(B22="","",INDEX(Items!$M$5:$M$40,MATCH(B22,Items!$A$5:$A$40,0)))</f>
+        <f>IF(B22="","",INDEX(Items!$M$5:$M$39,MATCH(B22,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
     </row>
@@ -5651,23 +5543,23 @@
         <v>19</v>
       </c>
       <c r="B23">
-        <f>IF(COUNT(Items!$N$5:$N$40)&lt;A23,"",INDEX(Items!$A$5:$A$40,MATCH(SMALL(Items!$N$5:$N$40,A23),Items!$N$5:$N$40,0)))</f>
+        <f>IF(COUNT(Items!$N$5:$N$39)&lt;A23,"",INDEX(Items!$A$5:$A$39,MATCH(SMALL(Items!$N$5:$N$39,A23),Items!$N$5:$N$39,0)))</f>
         <v/>
       </c>
       <c r="C23" s="6">
-        <f>IF(B23="","",INDEX(Items!$I$5:$I$40,MATCH(B23,Items!$A$5:$A$40,0)))</f>
+        <f>IF(B23="","",INDEX(Items!$I$5:$I$39,MATCH(B23,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
       <c r="D23">
-        <f>IF(B23="","",INDEX(Items!$B$5:$B$40,MATCH(B23,Items!$A$5:$A$40,0)))</f>
+        <f>IF(B23="","",INDEX(Items!$B$5:$B$39,MATCH(B23,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
       <c r="E23">
-        <f>IF(B23="","",INDEX(Items!$E$5:$E$40,MATCH(B23,Items!$A$5:$A$40,0)))</f>
+        <f>IF(B23="","",INDEX(Items!$E$5:$E$39,MATCH(B23,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
       <c r="F23">
-        <f>IF(B23="","",INDEX(Items!$M$5:$M$40,MATCH(B23,Items!$A$5:$A$40,0)))</f>
+        <f>IF(B23="","",INDEX(Items!$M$5:$M$39,MATCH(B23,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
     </row>
@@ -5676,23 +5568,23 @@
         <v>20</v>
       </c>
       <c r="B24">
-        <f>IF(COUNT(Items!$N$5:$N$40)&lt;A24,"",INDEX(Items!$A$5:$A$40,MATCH(SMALL(Items!$N$5:$N$40,A24),Items!$N$5:$N$40,0)))</f>
+        <f>IF(COUNT(Items!$N$5:$N$39)&lt;A24,"",INDEX(Items!$A$5:$A$39,MATCH(SMALL(Items!$N$5:$N$39,A24),Items!$N$5:$N$39,0)))</f>
         <v/>
       </c>
       <c r="C24" s="6">
-        <f>IF(B24="","",INDEX(Items!$I$5:$I$40,MATCH(B24,Items!$A$5:$A$40,0)))</f>
+        <f>IF(B24="","",INDEX(Items!$I$5:$I$39,MATCH(B24,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
       <c r="D24">
-        <f>IF(B24="","",INDEX(Items!$B$5:$B$40,MATCH(B24,Items!$A$5:$A$40,0)))</f>
+        <f>IF(B24="","",INDEX(Items!$B$5:$B$39,MATCH(B24,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
       <c r="E24">
-        <f>IF(B24="","",INDEX(Items!$E$5:$E$40,MATCH(B24,Items!$A$5:$A$40,0)))</f>
+        <f>IF(B24="","",INDEX(Items!$E$5:$E$39,MATCH(B24,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
       <c r="F24">
-        <f>IF(B24="","",INDEX(Items!$M$5:$M$40,MATCH(B24,Items!$A$5:$A$40,0)))</f>
+        <f>IF(B24="","",INDEX(Items!$M$5:$M$39,MATCH(B24,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
     </row>
@@ -5701,23 +5593,23 @@
         <v>21</v>
       </c>
       <c r="B25">
-        <f>IF(COUNT(Items!$N$5:$N$40)&lt;A25,"",INDEX(Items!$A$5:$A$40,MATCH(SMALL(Items!$N$5:$N$40,A25),Items!$N$5:$N$40,0)))</f>
+        <f>IF(COUNT(Items!$N$5:$N$39)&lt;A25,"",INDEX(Items!$A$5:$A$39,MATCH(SMALL(Items!$N$5:$N$39,A25),Items!$N$5:$N$39,0)))</f>
         <v/>
       </c>
       <c r="C25" s="6">
-        <f>IF(B25="","",INDEX(Items!$I$5:$I$40,MATCH(B25,Items!$A$5:$A$40,0)))</f>
+        <f>IF(B25="","",INDEX(Items!$I$5:$I$39,MATCH(B25,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
       <c r="D25">
-        <f>IF(B25="","",INDEX(Items!$B$5:$B$40,MATCH(B25,Items!$A$5:$A$40,0)))</f>
+        <f>IF(B25="","",INDEX(Items!$B$5:$B$39,MATCH(B25,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
       <c r="E25">
-        <f>IF(B25="","",INDEX(Items!$E$5:$E$40,MATCH(B25,Items!$A$5:$A$40,0)))</f>
+        <f>IF(B25="","",INDEX(Items!$E$5:$E$39,MATCH(B25,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
       <c r="F25">
-        <f>IF(B25="","",INDEX(Items!$M$5:$M$40,MATCH(B25,Items!$A$5:$A$40,0)))</f>
+        <f>IF(B25="","",INDEX(Items!$M$5:$M$39,MATCH(B25,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
     </row>
@@ -5726,23 +5618,23 @@
         <v>22</v>
       </c>
       <c r="B26">
-        <f>IF(COUNT(Items!$N$5:$N$40)&lt;A26,"",INDEX(Items!$A$5:$A$40,MATCH(SMALL(Items!$N$5:$N$40,A26),Items!$N$5:$N$40,0)))</f>
+        <f>IF(COUNT(Items!$N$5:$N$39)&lt;A26,"",INDEX(Items!$A$5:$A$39,MATCH(SMALL(Items!$N$5:$N$39,A26),Items!$N$5:$N$39,0)))</f>
         <v/>
       </c>
       <c r="C26" s="6">
-        <f>IF(B26="","",INDEX(Items!$I$5:$I$40,MATCH(B26,Items!$A$5:$A$40,0)))</f>
+        <f>IF(B26="","",INDEX(Items!$I$5:$I$39,MATCH(B26,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
       <c r="D26">
-        <f>IF(B26="","",INDEX(Items!$B$5:$B$40,MATCH(B26,Items!$A$5:$A$40,0)))</f>
+        <f>IF(B26="","",INDEX(Items!$B$5:$B$39,MATCH(B26,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
       <c r="E26">
-        <f>IF(B26="","",INDEX(Items!$E$5:$E$40,MATCH(B26,Items!$A$5:$A$40,0)))</f>
+        <f>IF(B26="","",INDEX(Items!$E$5:$E$39,MATCH(B26,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
       <c r="F26">
-        <f>IF(B26="","",INDEX(Items!$M$5:$M$40,MATCH(B26,Items!$A$5:$A$40,0)))</f>
+        <f>IF(B26="","",INDEX(Items!$M$5:$M$39,MATCH(B26,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
     </row>
@@ -5751,23 +5643,23 @@
         <v>23</v>
       </c>
       <c r="B27">
-        <f>IF(COUNT(Items!$N$5:$N$40)&lt;A27,"",INDEX(Items!$A$5:$A$40,MATCH(SMALL(Items!$N$5:$N$40,A27),Items!$N$5:$N$40,0)))</f>
+        <f>IF(COUNT(Items!$N$5:$N$39)&lt;A27,"",INDEX(Items!$A$5:$A$39,MATCH(SMALL(Items!$N$5:$N$39,A27),Items!$N$5:$N$39,0)))</f>
         <v/>
       </c>
       <c r="C27" s="6">
-        <f>IF(B27="","",INDEX(Items!$I$5:$I$40,MATCH(B27,Items!$A$5:$A$40,0)))</f>
+        <f>IF(B27="","",INDEX(Items!$I$5:$I$39,MATCH(B27,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
       <c r="D27">
-        <f>IF(B27="","",INDEX(Items!$B$5:$B$40,MATCH(B27,Items!$A$5:$A$40,0)))</f>
+        <f>IF(B27="","",INDEX(Items!$B$5:$B$39,MATCH(B27,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
       <c r="E27">
-        <f>IF(B27="","",INDEX(Items!$E$5:$E$40,MATCH(B27,Items!$A$5:$A$40,0)))</f>
+        <f>IF(B27="","",INDEX(Items!$E$5:$E$39,MATCH(B27,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
       <c r="F27">
-        <f>IF(B27="","",INDEX(Items!$M$5:$M$40,MATCH(B27,Items!$A$5:$A$40,0)))</f>
+        <f>IF(B27="","",INDEX(Items!$M$5:$M$39,MATCH(B27,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
     </row>
@@ -5776,23 +5668,23 @@
         <v>24</v>
       </c>
       <c r="B28">
-        <f>IF(COUNT(Items!$N$5:$N$40)&lt;A28,"",INDEX(Items!$A$5:$A$40,MATCH(SMALL(Items!$N$5:$N$40,A28),Items!$N$5:$N$40,0)))</f>
+        <f>IF(COUNT(Items!$N$5:$N$39)&lt;A28,"",INDEX(Items!$A$5:$A$39,MATCH(SMALL(Items!$N$5:$N$39,A28),Items!$N$5:$N$39,0)))</f>
         <v/>
       </c>
       <c r="C28" s="6">
-        <f>IF(B28="","",INDEX(Items!$I$5:$I$40,MATCH(B28,Items!$A$5:$A$40,0)))</f>
+        <f>IF(B28="","",INDEX(Items!$I$5:$I$39,MATCH(B28,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
       <c r="D28">
-        <f>IF(B28="","",INDEX(Items!$B$5:$B$40,MATCH(B28,Items!$A$5:$A$40,0)))</f>
+        <f>IF(B28="","",INDEX(Items!$B$5:$B$39,MATCH(B28,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
       <c r="E28">
-        <f>IF(B28="","",INDEX(Items!$E$5:$E$40,MATCH(B28,Items!$A$5:$A$40,0)))</f>
+        <f>IF(B28="","",INDEX(Items!$E$5:$E$39,MATCH(B28,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
       <c r="F28">
-        <f>IF(B28="","",INDEX(Items!$M$5:$M$40,MATCH(B28,Items!$A$5:$A$40,0)))</f>
+        <f>IF(B28="","",INDEX(Items!$M$5:$M$39,MATCH(B28,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
     </row>
@@ -5801,23 +5693,23 @@
         <v>25</v>
       </c>
       <c r="B29">
-        <f>IF(COUNT(Items!$N$5:$N$40)&lt;A29,"",INDEX(Items!$A$5:$A$40,MATCH(SMALL(Items!$N$5:$N$40,A29),Items!$N$5:$N$40,0)))</f>
+        <f>IF(COUNT(Items!$N$5:$N$39)&lt;A29,"",INDEX(Items!$A$5:$A$39,MATCH(SMALL(Items!$N$5:$N$39,A29),Items!$N$5:$N$39,0)))</f>
         <v/>
       </c>
       <c r="C29" s="6">
-        <f>IF(B29="","",INDEX(Items!$I$5:$I$40,MATCH(B29,Items!$A$5:$A$40,0)))</f>
+        <f>IF(B29="","",INDEX(Items!$I$5:$I$39,MATCH(B29,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
       <c r="D29">
-        <f>IF(B29="","",INDEX(Items!$B$5:$B$40,MATCH(B29,Items!$A$5:$A$40,0)))</f>
+        <f>IF(B29="","",INDEX(Items!$B$5:$B$39,MATCH(B29,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
       <c r="E29">
-        <f>IF(B29="","",INDEX(Items!$E$5:$E$40,MATCH(B29,Items!$A$5:$A$40,0)))</f>
+        <f>IF(B29="","",INDEX(Items!$E$5:$E$39,MATCH(B29,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
       <c r="F29">
-        <f>IF(B29="","",INDEX(Items!$M$5:$M$40,MATCH(B29,Items!$A$5:$A$40,0)))</f>
+        <f>IF(B29="","",INDEX(Items!$M$5:$M$39,MATCH(B29,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
     </row>
@@ -5826,23 +5718,23 @@
         <v>26</v>
       </c>
       <c r="B30">
-        <f>IF(COUNT(Items!$N$5:$N$40)&lt;A30,"",INDEX(Items!$A$5:$A$40,MATCH(SMALL(Items!$N$5:$N$40,A30),Items!$N$5:$N$40,0)))</f>
+        <f>IF(COUNT(Items!$N$5:$N$39)&lt;A30,"",INDEX(Items!$A$5:$A$39,MATCH(SMALL(Items!$N$5:$N$39,A30),Items!$N$5:$N$39,0)))</f>
         <v/>
       </c>
       <c r="C30" s="6">
-        <f>IF(B30="","",INDEX(Items!$I$5:$I$40,MATCH(B30,Items!$A$5:$A$40,0)))</f>
+        <f>IF(B30="","",INDEX(Items!$I$5:$I$39,MATCH(B30,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
       <c r="D30">
-        <f>IF(B30="","",INDEX(Items!$B$5:$B$40,MATCH(B30,Items!$A$5:$A$40,0)))</f>
+        <f>IF(B30="","",INDEX(Items!$B$5:$B$39,MATCH(B30,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
       <c r="E30">
-        <f>IF(B30="","",INDEX(Items!$E$5:$E$40,MATCH(B30,Items!$A$5:$A$40,0)))</f>
+        <f>IF(B30="","",INDEX(Items!$E$5:$E$39,MATCH(B30,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
       <c r="F30">
-        <f>IF(B30="","",INDEX(Items!$M$5:$M$40,MATCH(B30,Items!$A$5:$A$40,0)))</f>
+        <f>IF(B30="","",INDEX(Items!$M$5:$M$39,MATCH(B30,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
     </row>
@@ -5851,23 +5743,23 @@
         <v>27</v>
       </c>
       <c r="B31">
-        <f>IF(COUNT(Items!$N$5:$N$40)&lt;A31,"",INDEX(Items!$A$5:$A$40,MATCH(SMALL(Items!$N$5:$N$40,A31),Items!$N$5:$N$40,0)))</f>
+        <f>IF(COUNT(Items!$N$5:$N$39)&lt;A31,"",INDEX(Items!$A$5:$A$39,MATCH(SMALL(Items!$N$5:$N$39,A31),Items!$N$5:$N$39,0)))</f>
         <v/>
       </c>
       <c r="C31" s="6">
-        <f>IF(B31="","",INDEX(Items!$I$5:$I$40,MATCH(B31,Items!$A$5:$A$40,0)))</f>
+        <f>IF(B31="","",INDEX(Items!$I$5:$I$39,MATCH(B31,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
       <c r="D31">
-        <f>IF(B31="","",INDEX(Items!$B$5:$B$40,MATCH(B31,Items!$A$5:$A$40,0)))</f>
+        <f>IF(B31="","",INDEX(Items!$B$5:$B$39,MATCH(B31,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
       <c r="E31">
-        <f>IF(B31="","",INDEX(Items!$E$5:$E$40,MATCH(B31,Items!$A$5:$A$40,0)))</f>
+        <f>IF(B31="","",INDEX(Items!$E$5:$E$39,MATCH(B31,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
       <c r="F31">
-        <f>IF(B31="","",INDEX(Items!$M$5:$M$40,MATCH(B31,Items!$A$5:$A$40,0)))</f>
+        <f>IF(B31="","",INDEX(Items!$M$5:$M$39,MATCH(B31,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
     </row>
@@ -5876,23 +5768,23 @@
         <v>28</v>
       </c>
       <c r="B32">
-        <f>IF(COUNT(Items!$N$5:$N$40)&lt;A32,"",INDEX(Items!$A$5:$A$40,MATCH(SMALL(Items!$N$5:$N$40,A32),Items!$N$5:$N$40,0)))</f>
+        <f>IF(COUNT(Items!$N$5:$N$39)&lt;A32,"",INDEX(Items!$A$5:$A$39,MATCH(SMALL(Items!$N$5:$N$39,A32),Items!$N$5:$N$39,0)))</f>
         <v/>
       </c>
       <c r="C32" s="6">
-        <f>IF(B32="","",INDEX(Items!$I$5:$I$40,MATCH(B32,Items!$A$5:$A$40,0)))</f>
+        <f>IF(B32="","",INDEX(Items!$I$5:$I$39,MATCH(B32,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
       <c r="D32">
-        <f>IF(B32="","",INDEX(Items!$B$5:$B$40,MATCH(B32,Items!$A$5:$A$40,0)))</f>
+        <f>IF(B32="","",INDEX(Items!$B$5:$B$39,MATCH(B32,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
       <c r="E32">
-        <f>IF(B32="","",INDEX(Items!$E$5:$E$40,MATCH(B32,Items!$A$5:$A$40,0)))</f>
+        <f>IF(B32="","",INDEX(Items!$E$5:$E$39,MATCH(B32,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
       <c r="F32">
-        <f>IF(B32="","",INDEX(Items!$M$5:$M$40,MATCH(B32,Items!$A$5:$A$40,0)))</f>
+        <f>IF(B32="","",INDEX(Items!$M$5:$M$39,MATCH(B32,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
     </row>
@@ -5901,23 +5793,23 @@
         <v>29</v>
       </c>
       <c r="B33">
-        <f>IF(COUNT(Items!$N$5:$N$40)&lt;A33,"",INDEX(Items!$A$5:$A$40,MATCH(SMALL(Items!$N$5:$N$40,A33),Items!$N$5:$N$40,0)))</f>
+        <f>IF(COUNT(Items!$N$5:$N$39)&lt;A33,"",INDEX(Items!$A$5:$A$39,MATCH(SMALL(Items!$N$5:$N$39,A33),Items!$N$5:$N$39,0)))</f>
         <v/>
       </c>
       <c r="C33" s="6">
-        <f>IF(B33="","",INDEX(Items!$I$5:$I$40,MATCH(B33,Items!$A$5:$A$40,0)))</f>
+        <f>IF(B33="","",INDEX(Items!$I$5:$I$39,MATCH(B33,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
       <c r="D33">
-        <f>IF(B33="","",INDEX(Items!$B$5:$B$40,MATCH(B33,Items!$A$5:$A$40,0)))</f>
+        <f>IF(B33="","",INDEX(Items!$B$5:$B$39,MATCH(B33,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
       <c r="E33">
-        <f>IF(B33="","",INDEX(Items!$E$5:$E$40,MATCH(B33,Items!$A$5:$A$40,0)))</f>
+        <f>IF(B33="","",INDEX(Items!$E$5:$E$39,MATCH(B33,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
       <c r="F33">
-        <f>IF(B33="","",INDEX(Items!$M$5:$M$40,MATCH(B33,Items!$A$5:$A$40,0)))</f>
+        <f>IF(B33="","",INDEX(Items!$M$5:$M$39,MATCH(B33,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
     </row>
@@ -5926,23 +5818,23 @@
         <v>30</v>
       </c>
       <c r="B34">
-        <f>IF(COUNT(Items!$N$5:$N$40)&lt;A34,"",INDEX(Items!$A$5:$A$40,MATCH(SMALL(Items!$N$5:$N$40,A34),Items!$N$5:$N$40,0)))</f>
+        <f>IF(COUNT(Items!$N$5:$N$39)&lt;A34,"",INDEX(Items!$A$5:$A$39,MATCH(SMALL(Items!$N$5:$N$39,A34),Items!$N$5:$N$39,0)))</f>
         <v/>
       </c>
       <c r="C34" s="6">
-        <f>IF(B34="","",INDEX(Items!$I$5:$I$40,MATCH(B34,Items!$A$5:$A$40,0)))</f>
+        <f>IF(B34="","",INDEX(Items!$I$5:$I$39,MATCH(B34,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
       <c r="D34">
-        <f>IF(B34="","",INDEX(Items!$B$5:$B$40,MATCH(B34,Items!$A$5:$A$40,0)))</f>
+        <f>IF(B34="","",INDEX(Items!$B$5:$B$39,MATCH(B34,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
       <c r="E34">
-        <f>IF(B34="","",INDEX(Items!$E$5:$E$40,MATCH(B34,Items!$A$5:$A$40,0)))</f>
+        <f>IF(B34="","",INDEX(Items!$E$5:$E$39,MATCH(B34,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
       <c r="F34">
-        <f>IF(B34="","",INDEX(Items!$M$5:$M$40,MATCH(B34,Items!$A$5:$A$40,0)))</f>
+        <f>IF(B34="","",INDEX(Items!$M$5:$M$39,MATCH(B34,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
     </row>
@@ -5951,23 +5843,23 @@
         <v>31</v>
       </c>
       <c r="B35">
-        <f>IF(COUNT(Items!$N$5:$N$40)&lt;A35,"",INDEX(Items!$A$5:$A$40,MATCH(SMALL(Items!$N$5:$N$40,A35),Items!$N$5:$N$40,0)))</f>
+        <f>IF(COUNT(Items!$N$5:$N$39)&lt;A35,"",INDEX(Items!$A$5:$A$39,MATCH(SMALL(Items!$N$5:$N$39,A35),Items!$N$5:$N$39,0)))</f>
         <v/>
       </c>
       <c r="C35" s="6">
-        <f>IF(B35="","",INDEX(Items!$I$5:$I$40,MATCH(B35,Items!$A$5:$A$40,0)))</f>
+        <f>IF(B35="","",INDEX(Items!$I$5:$I$39,MATCH(B35,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
       <c r="D35">
-        <f>IF(B35="","",INDEX(Items!$B$5:$B$40,MATCH(B35,Items!$A$5:$A$40,0)))</f>
+        <f>IF(B35="","",INDEX(Items!$B$5:$B$39,MATCH(B35,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
       <c r="E35">
-        <f>IF(B35="","",INDEX(Items!$E$5:$E$40,MATCH(B35,Items!$A$5:$A$40,0)))</f>
+        <f>IF(B35="","",INDEX(Items!$E$5:$E$39,MATCH(B35,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
       <c r="F35">
-        <f>IF(B35="","",INDEX(Items!$M$5:$M$40,MATCH(B35,Items!$A$5:$A$40,0)))</f>
+        <f>IF(B35="","",INDEX(Items!$M$5:$M$39,MATCH(B35,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
     </row>
@@ -5976,23 +5868,23 @@
         <v>32</v>
       </c>
       <c r="B36">
-        <f>IF(COUNT(Items!$N$5:$N$40)&lt;A36,"",INDEX(Items!$A$5:$A$40,MATCH(SMALL(Items!$N$5:$N$40,A36),Items!$N$5:$N$40,0)))</f>
+        <f>IF(COUNT(Items!$N$5:$N$39)&lt;A36,"",INDEX(Items!$A$5:$A$39,MATCH(SMALL(Items!$N$5:$N$39,A36),Items!$N$5:$N$39,0)))</f>
         <v/>
       </c>
       <c r="C36" s="6">
-        <f>IF(B36="","",INDEX(Items!$I$5:$I$40,MATCH(B36,Items!$A$5:$A$40,0)))</f>
+        <f>IF(B36="","",INDEX(Items!$I$5:$I$39,MATCH(B36,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
       <c r="D36">
-        <f>IF(B36="","",INDEX(Items!$B$5:$B$40,MATCH(B36,Items!$A$5:$A$40,0)))</f>
+        <f>IF(B36="","",INDEX(Items!$B$5:$B$39,MATCH(B36,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
       <c r="E36">
-        <f>IF(B36="","",INDEX(Items!$E$5:$E$40,MATCH(B36,Items!$A$5:$A$40,0)))</f>
+        <f>IF(B36="","",INDEX(Items!$E$5:$E$39,MATCH(B36,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
       <c r="F36">
-        <f>IF(B36="","",INDEX(Items!$M$5:$M$40,MATCH(B36,Items!$A$5:$A$40,0)))</f>
+        <f>IF(B36="","",INDEX(Items!$M$5:$M$39,MATCH(B36,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
     </row>
@@ -6001,23 +5893,23 @@
         <v>33</v>
       </c>
       <c r="B37">
-        <f>IF(COUNT(Items!$N$5:$N$40)&lt;A37,"",INDEX(Items!$A$5:$A$40,MATCH(SMALL(Items!$N$5:$N$40,A37),Items!$N$5:$N$40,0)))</f>
+        <f>IF(COUNT(Items!$N$5:$N$39)&lt;A37,"",INDEX(Items!$A$5:$A$39,MATCH(SMALL(Items!$N$5:$N$39,A37),Items!$N$5:$N$39,0)))</f>
         <v/>
       </c>
       <c r="C37" s="6">
-        <f>IF(B37="","",INDEX(Items!$I$5:$I$40,MATCH(B37,Items!$A$5:$A$40,0)))</f>
+        <f>IF(B37="","",INDEX(Items!$I$5:$I$39,MATCH(B37,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
       <c r="D37">
-        <f>IF(B37="","",INDEX(Items!$B$5:$B$40,MATCH(B37,Items!$A$5:$A$40,0)))</f>
+        <f>IF(B37="","",INDEX(Items!$B$5:$B$39,MATCH(B37,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
       <c r="E37">
-        <f>IF(B37="","",INDEX(Items!$E$5:$E$40,MATCH(B37,Items!$A$5:$A$40,0)))</f>
+        <f>IF(B37="","",INDEX(Items!$E$5:$E$39,MATCH(B37,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
       <c r="F37">
-        <f>IF(B37="","",INDEX(Items!$M$5:$M$40,MATCH(B37,Items!$A$5:$A$40,0)))</f>
+        <f>IF(B37="","",INDEX(Items!$M$5:$M$39,MATCH(B37,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
     </row>
@@ -6026,23 +5918,23 @@
         <v>34</v>
       </c>
       <c r="B38">
-        <f>IF(COUNT(Items!$N$5:$N$40)&lt;A38,"",INDEX(Items!$A$5:$A$40,MATCH(SMALL(Items!$N$5:$N$40,A38),Items!$N$5:$N$40,0)))</f>
+        <f>IF(COUNT(Items!$N$5:$N$39)&lt;A38,"",INDEX(Items!$A$5:$A$39,MATCH(SMALL(Items!$N$5:$N$39,A38),Items!$N$5:$N$39,0)))</f>
         <v/>
       </c>
       <c r="C38" s="6">
-        <f>IF(B38="","",INDEX(Items!$I$5:$I$40,MATCH(B38,Items!$A$5:$A$40,0)))</f>
+        <f>IF(B38="","",INDEX(Items!$I$5:$I$39,MATCH(B38,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
       <c r="D38">
-        <f>IF(B38="","",INDEX(Items!$B$5:$B$40,MATCH(B38,Items!$A$5:$A$40,0)))</f>
+        <f>IF(B38="","",INDEX(Items!$B$5:$B$39,MATCH(B38,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
       <c r="E38">
-        <f>IF(B38="","",INDEX(Items!$E$5:$E$40,MATCH(B38,Items!$A$5:$A$40,0)))</f>
+        <f>IF(B38="","",INDEX(Items!$E$5:$E$39,MATCH(B38,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
       <c r="F38">
-        <f>IF(B38="","",INDEX(Items!$M$5:$M$40,MATCH(B38,Items!$A$5:$A$40,0)))</f>
+        <f>IF(B38="","",INDEX(Items!$M$5:$M$39,MATCH(B38,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
     </row>
@@ -6051,48 +5943,23 @@
         <v>35</v>
       </c>
       <c r="B39">
-        <f>IF(COUNT(Items!$N$5:$N$40)&lt;A39,"",INDEX(Items!$A$5:$A$40,MATCH(SMALL(Items!$N$5:$N$40,A39),Items!$N$5:$N$40,0)))</f>
+        <f>IF(COUNT(Items!$N$5:$N$39)&lt;A39,"",INDEX(Items!$A$5:$A$39,MATCH(SMALL(Items!$N$5:$N$39,A39),Items!$N$5:$N$39,0)))</f>
         <v/>
       </c>
       <c r="C39" s="6">
-        <f>IF(B39="","",INDEX(Items!$I$5:$I$40,MATCH(B39,Items!$A$5:$A$40,0)))</f>
+        <f>IF(B39="","",INDEX(Items!$I$5:$I$39,MATCH(B39,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
       <c r="D39">
-        <f>IF(B39="","",INDEX(Items!$B$5:$B$40,MATCH(B39,Items!$A$5:$A$40,0)))</f>
+        <f>IF(B39="","",INDEX(Items!$B$5:$B$39,MATCH(B39,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
       <c r="E39">
-        <f>IF(B39="","",INDEX(Items!$E$5:$E$40,MATCH(B39,Items!$A$5:$A$40,0)))</f>
+        <f>IF(B39="","",INDEX(Items!$E$5:$E$39,MATCH(B39,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
       <c r="F39">
-        <f>IF(B39="","",INDEX(Items!$M$5:$M$40,MATCH(B39,Items!$A$5:$A$40,0)))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="n">
-        <v>36</v>
-      </c>
-      <c r="B40">
-        <f>IF(COUNT(Items!$N$5:$N$40)&lt;A40,"",INDEX(Items!$A$5:$A$40,MATCH(SMALL(Items!$N$5:$N$40,A40),Items!$N$5:$N$40,0)))</f>
-        <v/>
-      </c>
-      <c r="C40" s="6">
-        <f>IF(B40="","",INDEX(Items!$I$5:$I$40,MATCH(B40,Items!$A$5:$A$40,0)))</f>
-        <v/>
-      </c>
-      <c r="D40">
-        <f>IF(B40="","",INDEX(Items!$B$5:$B$40,MATCH(B40,Items!$A$5:$A$40,0)))</f>
-        <v/>
-      </c>
-      <c r="E40">
-        <f>IF(B40="","",INDEX(Items!$E$5:$E$40,MATCH(B40,Items!$A$5:$A$40,0)))</f>
-        <v/>
-      </c>
-      <c r="F40">
-        <f>IF(B40="","",INDEX(Items!$M$5:$M$40,MATCH(B40,Items!$A$5:$A$40,0)))</f>
+        <f>IF(B39="","",INDEX(Items!$M$5:$M$39,MATCH(B39,Items!$A$5:$A$39,0)))</f>
         <v/>
       </c>
     </row>
@@ -6154,11 +6021,11 @@
         </is>
       </c>
       <c r="C5">
-        <f>COUNTIF(Items!$E$5:$E$40,A5)</f>
+        <f>COUNTIF(Items!$E$5:$E$39,A5)</f>
         <v/>
       </c>
       <c r="D5" s="6">
-        <f>IF(SUMPRODUCT((Items!$E$5:$E$40=A5)*Items!$H$5:$H$40)=0,"",SUMPRODUCT((Items!$E$5:$E$40=A5)*Items!$G$5:$G$40)/SUMPRODUCT((Items!$E$5:$E$40=A5)*Items!$H$5:$H$40))</f>
+        <f>IF(SUMPRODUCT((Items!$E$5:$E$39=A5)*Items!$H$5:$H$39)=0,"",SUMPRODUCT((Items!$E$5:$E$39=A5)*Items!$G$5:$G$39)/SUMPRODUCT((Items!$E$5:$E$39=A5)*Items!$H$5:$H$39))</f>
         <v/>
       </c>
     </row>
@@ -6174,11 +6041,11 @@
         </is>
       </c>
       <c r="C6">
-        <f>COUNTIF(Items!$E$5:$E$40,A6)</f>
+        <f>COUNTIF(Items!$E$5:$E$39,A6)</f>
         <v/>
       </c>
       <c r="D6" s="6">
-        <f>IF(SUMPRODUCT((Items!$E$5:$E$40=A6)*Items!$H$5:$H$40)=0,"",SUMPRODUCT((Items!$E$5:$E$40=A6)*Items!$G$5:$G$40)/SUMPRODUCT((Items!$E$5:$E$40=A6)*Items!$H$5:$H$40))</f>
+        <f>IF(SUMPRODUCT((Items!$E$5:$E$39=A6)*Items!$H$5:$H$39)=0,"",SUMPRODUCT((Items!$E$5:$E$39=A6)*Items!$G$5:$G$39)/SUMPRODUCT((Items!$E$5:$E$39=A6)*Items!$H$5:$H$39))</f>
         <v/>
       </c>
     </row>
@@ -6194,11 +6061,11 @@
         </is>
       </c>
       <c r="C7">
-        <f>COUNTIF(Items!$E$5:$E$40,A7)</f>
+        <f>COUNTIF(Items!$E$5:$E$39,A7)</f>
         <v/>
       </c>
       <c r="D7" s="6">
-        <f>IF(SUMPRODUCT((Items!$E$5:$E$40=A7)*Items!$H$5:$H$40)=0,"",SUMPRODUCT((Items!$E$5:$E$40=A7)*Items!$G$5:$G$40)/SUMPRODUCT((Items!$E$5:$E$40=A7)*Items!$H$5:$H$40))</f>
+        <f>IF(SUMPRODUCT((Items!$E$5:$E$39=A7)*Items!$H$5:$H$39)=0,"",SUMPRODUCT((Items!$E$5:$E$39=A7)*Items!$G$5:$G$39)/SUMPRODUCT((Items!$E$5:$E$39=A7)*Items!$H$5:$H$39))</f>
         <v/>
       </c>
     </row>
@@ -6214,11 +6081,11 @@
         </is>
       </c>
       <c r="C8">
-        <f>COUNTIF(Items!$E$5:$E$40,A8)</f>
+        <f>COUNTIF(Items!$E$5:$E$39,A8)</f>
         <v/>
       </c>
       <c r="D8" s="6">
-        <f>IF(SUMPRODUCT((Items!$E$5:$E$40=A8)*Items!$H$5:$H$40)=0,"",SUMPRODUCT((Items!$E$5:$E$40=A8)*Items!$G$5:$G$40)/SUMPRODUCT((Items!$E$5:$E$40=A8)*Items!$H$5:$H$40))</f>
+        <f>IF(SUMPRODUCT((Items!$E$5:$E$39=A8)*Items!$H$5:$H$39)=0,"",SUMPRODUCT((Items!$E$5:$E$39=A8)*Items!$G$5:$G$39)/SUMPRODUCT((Items!$E$5:$E$39=A8)*Items!$H$5:$H$39))</f>
         <v/>
       </c>
     </row>
@@ -6232,11 +6099,11 @@
         </is>
       </c>
       <c r="C9">
-        <f>COUNTIF(Items!$B$5:$B$40,A9)</f>
+        <f>COUNTIF(Items!$B$5:$B$39,A9)</f>
         <v/>
       </c>
       <c r="D9" s="6">
-        <f>IF(SUMPRODUCT((Items!$B$5:$B$40=A9)*Items!$H$5:$H$40)=0,"",SUMPRODUCT((Items!$B$5:$B$40=A9)*Items!$G$5:$G$40)/SUMPRODUCT((Items!$B$5:$B$40=A9)*Items!$H$5:$H$40))</f>
+        <f>IF(SUMPRODUCT((Items!$B$5:$B$39=A9)*Items!$H$5:$H$39)=0,"",SUMPRODUCT((Items!$B$5:$B$39=A9)*Items!$G$5:$G$39)/SUMPRODUCT((Items!$B$5:$B$39=A9)*Items!$H$5:$H$39))</f>
         <v/>
       </c>
     </row>
@@ -6250,11 +6117,11 @@
         </is>
       </c>
       <c r="C10">
-        <f>COUNTIF(Items!$B$5:$B$40,A10)</f>
+        <f>COUNTIF(Items!$B$5:$B$39,A10)</f>
         <v/>
       </c>
       <c r="D10" s="6">
-        <f>IF(SUMPRODUCT((Items!$B$5:$B$40=A10)*Items!$H$5:$H$40)=0,"",SUMPRODUCT((Items!$B$5:$B$40=A10)*Items!$G$5:$G$40)/SUMPRODUCT((Items!$B$5:$B$40=A10)*Items!$H$5:$H$40))</f>
+        <f>IF(SUMPRODUCT((Items!$B$5:$B$39=A10)*Items!$H$5:$H$39)=0,"",SUMPRODUCT((Items!$B$5:$B$39=A10)*Items!$G$5:$G$39)/SUMPRODUCT((Items!$B$5:$B$39=A10)*Items!$H$5:$H$39))</f>
         <v/>
       </c>
     </row>
@@ -6264,15 +6131,15 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Part 3. Real, worth it, and caused</t>
+          <t>Part 3. Real, or the wobble</t>
         </is>
       </c>
       <c r="C11">
-        <f>COUNTIF(Items!$B$5:$B$40,A11)</f>
+        <f>COUNTIF(Items!$B$5:$B$39,A11)</f>
         <v/>
       </c>
       <c r="D11" s="6">
-        <f>IF(SUMPRODUCT((Items!$B$5:$B$40=A11)*Items!$H$5:$H$40)=0,"",SUMPRODUCT((Items!$B$5:$B$40=A11)*Items!$G$5:$G$40)/SUMPRODUCT((Items!$B$5:$B$40=A11)*Items!$H$5:$H$40))</f>
+        <f>IF(SUMPRODUCT((Items!$B$5:$B$39=A11)*Items!$H$5:$H$39)=0,"",SUMPRODUCT((Items!$B$5:$B$39=A11)*Items!$G$5:$G$39)/SUMPRODUCT((Items!$B$5:$B$39=A11)*Items!$H$5:$H$39))</f>
         <v/>
       </c>
     </row>
@@ -6286,11 +6153,11 @@
         </is>
       </c>
       <c r="C12">
-        <f>COUNTIF(Items!$B$5:$B$40,A12)</f>
+        <f>COUNTIF(Items!$B$5:$B$39,A12)</f>
         <v/>
       </c>
       <c r="D12" s="6">
-        <f>IF(SUMPRODUCT((Items!$B$5:$B$40=A12)*Items!$H$5:$H$40)=0,"",SUMPRODUCT((Items!$B$5:$B$40=A12)*Items!$G$5:$G$40)/SUMPRODUCT((Items!$B$5:$B$40=A12)*Items!$H$5:$H$40))</f>
+        <f>IF(SUMPRODUCT((Items!$B$5:$B$39=A12)*Items!$H$5:$H$39)=0,"",SUMPRODUCT((Items!$B$5:$B$39=A12)*Items!$G$5:$G$39)/SUMPRODUCT((Items!$B$5:$B$39=A12)*Items!$H$5:$H$39))</f>
         <v/>
       </c>
     </row>
@@ -6300,15 +6167,15 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Part 5. The agent's bill and its logs</t>
+          <t>Part 5. An offer, an agent and its logs</t>
         </is>
       </c>
       <c r="C13">
-        <f>COUNTIF(Items!$B$5:$B$40,A13)</f>
+        <f>COUNTIF(Items!$B$5:$B$39,A13)</f>
         <v/>
       </c>
       <c r="D13" s="6">
-        <f>IF(SUMPRODUCT((Items!$B$5:$B$40=A13)*Items!$H$5:$H$40)=0,"",SUMPRODUCT((Items!$B$5:$B$40=A13)*Items!$G$5:$G$40)/SUMPRODUCT((Items!$B$5:$B$40=A13)*Items!$H$5:$H$40))</f>
+        <f>IF(SUMPRODUCT((Items!$B$5:$B$39=A13)*Items!$H$5:$H$39)=0,"",SUMPRODUCT((Items!$B$5:$B$39=A13)*Items!$G$5:$G$39)/SUMPRODUCT((Items!$B$5:$B$39=A13)*Items!$H$5:$H$39))</f>
         <v/>
       </c>
     </row>
@@ -6365,19 +6232,19 @@
         <v>1</v>
       </c>
       <c r="B5" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=B$4)*ISNUMBER(Marks!$B$5:$AK$5))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=B$4)*(Marks!$B$5:$AK$5=1))/SUMPRODUCT((Marks!$B$3:$AK$3=B$4)*ISNUMBER(Marks!$B$5:$AK$5)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*ISNUMBER(Marks!$B$5:$AJ$5))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*(Marks!$B$5:$AJ$5=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*ISNUMBER(Marks!$B$5:$AJ$5)))</f>
         <v/>
       </c>
       <c r="C5" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=C$4)*ISNUMBER(Marks!$B$5:$AK$5))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=C$4)*(Marks!$B$5:$AK$5=1))/SUMPRODUCT((Marks!$B$3:$AK$3=C$4)*ISNUMBER(Marks!$B$5:$AK$5)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*ISNUMBER(Marks!$B$5:$AJ$5))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*(Marks!$B$5:$AJ$5=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*ISNUMBER(Marks!$B$5:$AJ$5)))</f>
         <v/>
       </c>
       <c r="D5" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=D$4)*ISNUMBER(Marks!$B$5:$AK$5))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=D$4)*(Marks!$B$5:$AK$5=1))/SUMPRODUCT((Marks!$B$3:$AK$3=D$4)*ISNUMBER(Marks!$B$5:$AK$5)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*ISNUMBER(Marks!$B$5:$AJ$5))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*(Marks!$B$5:$AJ$5=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*ISNUMBER(Marks!$B$5:$AJ$5)))</f>
         <v/>
       </c>
       <c r="E5" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=E$4)*ISNUMBER(Marks!$B$5:$AK$5))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=E$4)*(Marks!$B$5:$AK$5=1))/SUMPRODUCT((Marks!$B$3:$AK$3=E$4)*ISNUMBER(Marks!$B$5:$AK$5)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=E$4)*ISNUMBER(Marks!$B$5:$AJ$5))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=E$4)*(Marks!$B$5:$AJ$5=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=E$4)*ISNUMBER(Marks!$B$5:$AJ$5)))</f>
         <v/>
       </c>
     </row>
@@ -6386,19 +6253,19 @@
         <v>2</v>
       </c>
       <c r="B6" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=B$4)*ISNUMBER(Marks!$B$6:$AK$6))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=B$4)*(Marks!$B$6:$AK$6=1))/SUMPRODUCT((Marks!$B$3:$AK$3=B$4)*ISNUMBER(Marks!$B$6:$AK$6)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*ISNUMBER(Marks!$B$6:$AJ$6))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*(Marks!$B$6:$AJ$6=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*ISNUMBER(Marks!$B$6:$AJ$6)))</f>
         <v/>
       </c>
       <c r="C6" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=C$4)*ISNUMBER(Marks!$B$6:$AK$6))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=C$4)*(Marks!$B$6:$AK$6=1))/SUMPRODUCT((Marks!$B$3:$AK$3=C$4)*ISNUMBER(Marks!$B$6:$AK$6)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*ISNUMBER(Marks!$B$6:$AJ$6))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*(Marks!$B$6:$AJ$6=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*ISNUMBER(Marks!$B$6:$AJ$6)))</f>
         <v/>
       </c>
       <c r="D6" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=D$4)*ISNUMBER(Marks!$B$6:$AK$6))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=D$4)*(Marks!$B$6:$AK$6=1))/SUMPRODUCT((Marks!$B$3:$AK$3=D$4)*ISNUMBER(Marks!$B$6:$AK$6)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*ISNUMBER(Marks!$B$6:$AJ$6))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*(Marks!$B$6:$AJ$6=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*ISNUMBER(Marks!$B$6:$AJ$6)))</f>
         <v/>
       </c>
       <c r="E6" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=E$4)*ISNUMBER(Marks!$B$6:$AK$6))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=E$4)*(Marks!$B$6:$AK$6=1))/SUMPRODUCT((Marks!$B$3:$AK$3=E$4)*ISNUMBER(Marks!$B$6:$AK$6)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=E$4)*ISNUMBER(Marks!$B$6:$AJ$6))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=E$4)*(Marks!$B$6:$AJ$6=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=E$4)*ISNUMBER(Marks!$B$6:$AJ$6)))</f>
         <v/>
       </c>
     </row>
@@ -6407,19 +6274,19 @@
         <v>3</v>
       </c>
       <c r="B7" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=B$4)*ISNUMBER(Marks!$B$7:$AK$7))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=B$4)*(Marks!$B$7:$AK$7=1))/SUMPRODUCT((Marks!$B$3:$AK$3=B$4)*ISNUMBER(Marks!$B$7:$AK$7)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*ISNUMBER(Marks!$B$7:$AJ$7))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*(Marks!$B$7:$AJ$7=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*ISNUMBER(Marks!$B$7:$AJ$7)))</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=C$4)*ISNUMBER(Marks!$B$7:$AK$7))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=C$4)*(Marks!$B$7:$AK$7=1))/SUMPRODUCT((Marks!$B$3:$AK$3=C$4)*ISNUMBER(Marks!$B$7:$AK$7)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*ISNUMBER(Marks!$B$7:$AJ$7))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*(Marks!$B$7:$AJ$7=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*ISNUMBER(Marks!$B$7:$AJ$7)))</f>
         <v/>
       </c>
       <c r="D7" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=D$4)*ISNUMBER(Marks!$B$7:$AK$7))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=D$4)*(Marks!$B$7:$AK$7=1))/SUMPRODUCT((Marks!$B$3:$AK$3=D$4)*ISNUMBER(Marks!$B$7:$AK$7)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*ISNUMBER(Marks!$B$7:$AJ$7))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*(Marks!$B$7:$AJ$7=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*ISNUMBER(Marks!$B$7:$AJ$7)))</f>
         <v/>
       </c>
       <c r="E7" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=E$4)*ISNUMBER(Marks!$B$7:$AK$7))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=E$4)*(Marks!$B$7:$AK$7=1))/SUMPRODUCT((Marks!$B$3:$AK$3=E$4)*ISNUMBER(Marks!$B$7:$AK$7)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=E$4)*ISNUMBER(Marks!$B$7:$AJ$7))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=E$4)*(Marks!$B$7:$AJ$7=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=E$4)*ISNUMBER(Marks!$B$7:$AJ$7)))</f>
         <v/>
       </c>
     </row>
@@ -6428,19 +6295,19 @@
         <v>4</v>
       </c>
       <c r="B8" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=B$4)*ISNUMBER(Marks!$B$8:$AK$8))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=B$4)*(Marks!$B$8:$AK$8=1))/SUMPRODUCT((Marks!$B$3:$AK$3=B$4)*ISNUMBER(Marks!$B$8:$AK$8)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*ISNUMBER(Marks!$B$8:$AJ$8))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*(Marks!$B$8:$AJ$8=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*ISNUMBER(Marks!$B$8:$AJ$8)))</f>
         <v/>
       </c>
       <c r="C8" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=C$4)*ISNUMBER(Marks!$B$8:$AK$8))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=C$4)*(Marks!$B$8:$AK$8=1))/SUMPRODUCT((Marks!$B$3:$AK$3=C$4)*ISNUMBER(Marks!$B$8:$AK$8)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*ISNUMBER(Marks!$B$8:$AJ$8))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*(Marks!$B$8:$AJ$8=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*ISNUMBER(Marks!$B$8:$AJ$8)))</f>
         <v/>
       </c>
       <c r="D8" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=D$4)*ISNUMBER(Marks!$B$8:$AK$8))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=D$4)*(Marks!$B$8:$AK$8=1))/SUMPRODUCT((Marks!$B$3:$AK$3=D$4)*ISNUMBER(Marks!$B$8:$AK$8)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*ISNUMBER(Marks!$B$8:$AJ$8))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*(Marks!$B$8:$AJ$8=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*ISNUMBER(Marks!$B$8:$AJ$8)))</f>
         <v/>
       </c>
       <c r="E8" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=E$4)*ISNUMBER(Marks!$B$8:$AK$8))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=E$4)*(Marks!$B$8:$AK$8=1))/SUMPRODUCT((Marks!$B$3:$AK$3=E$4)*ISNUMBER(Marks!$B$8:$AK$8)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=E$4)*ISNUMBER(Marks!$B$8:$AJ$8))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=E$4)*(Marks!$B$8:$AJ$8=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=E$4)*ISNUMBER(Marks!$B$8:$AJ$8)))</f>
         <v/>
       </c>
     </row>
@@ -6449,19 +6316,19 @@
         <v>5</v>
       </c>
       <c r="B9" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=B$4)*ISNUMBER(Marks!$B$9:$AK$9))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=B$4)*(Marks!$B$9:$AK$9=1))/SUMPRODUCT((Marks!$B$3:$AK$3=B$4)*ISNUMBER(Marks!$B$9:$AK$9)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*ISNUMBER(Marks!$B$9:$AJ$9))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*(Marks!$B$9:$AJ$9=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*ISNUMBER(Marks!$B$9:$AJ$9)))</f>
         <v/>
       </c>
       <c r="C9" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=C$4)*ISNUMBER(Marks!$B$9:$AK$9))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=C$4)*(Marks!$B$9:$AK$9=1))/SUMPRODUCT((Marks!$B$3:$AK$3=C$4)*ISNUMBER(Marks!$B$9:$AK$9)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*ISNUMBER(Marks!$B$9:$AJ$9))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*(Marks!$B$9:$AJ$9=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*ISNUMBER(Marks!$B$9:$AJ$9)))</f>
         <v/>
       </c>
       <c r="D9" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=D$4)*ISNUMBER(Marks!$B$9:$AK$9))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=D$4)*(Marks!$B$9:$AK$9=1))/SUMPRODUCT((Marks!$B$3:$AK$3=D$4)*ISNUMBER(Marks!$B$9:$AK$9)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*ISNUMBER(Marks!$B$9:$AJ$9))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*(Marks!$B$9:$AJ$9=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*ISNUMBER(Marks!$B$9:$AJ$9)))</f>
         <v/>
       </c>
       <c r="E9" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=E$4)*ISNUMBER(Marks!$B$9:$AK$9))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=E$4)*(Marks!$B$9:$AK$9=1))/SUMPRODUCT((Marks!$B$3:$AK$3=E$4)*ISNUMBER(Marks!$B$9:$AK$9)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=E$4)*ISNUMBER(Marks!$B$9:$AJ$9))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=E$4)*(Marks!$B$9:$AJ$9=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=E$4)*ISNUMBER(Marks!$B$9:$AJ$9)))</f>
         <v/>
       </c>
     </row>
@@ -6470,19 +6337,19 @@
         <v>6</v>
       </c>
       <c r="B10" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=B$4)*ISNUMBER(Marks!$B$10:$AK$10))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=B$4)*(Marks!$B$10:$AK$10=1))/SUMPRODUCT((Marks!$B$3:$AK$3=B$4)*ISNUMBER(Marks!$B$10:$AK$10)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*ISNUMBER(Marks!$B$10:$AJ$10))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*(Marks!$B$10:$AJ$10=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*ISNUMBER(Marks!$B$10:$AJ$10)))</f>
         <v/>
       </c>
       <c r="C10" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=C$4)*ISNUMBER(Marks!$B$10:$AK$10))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=C$4)*(Marks!$B$10:$AK$10=1))/SUMPRODUCT((Marks!$B$3:$AK$3=C$4)*ISNUMBER(Marks!$B$10:$AK$10)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*ISNUMBER(Marks!$B$10:$AJ$10))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*(Marks!$B$10:$AJ$10=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*ISNUMBER(Marks!$B$10:$AJ$10)))</f>
         <v/>
       </c>
       <c r="D10" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=D$4)*ISNUMBER(Marks!$B$10:$AK$10))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=D$4)*(Marks!$B$10:$AK$10=1))/SUMPRODUCT((Marks!$B$3:$AK$3=D$4)*ISNUMBER(Marks!$B$10:$AK$10)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*ISNUMBER(Marks!$B$10:$AJ$10))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*(Marks!$B$10:$AJ$10=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*ISNUMBER(Marks!$B$10:$AJ$10)))</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=E$4)*ISNUMBER(Marks!$B$10:$AK$10))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=E$4)*(Marks!$B$10:$AK$10=1))/SUMPRODUCT((Marks!$B$3:$AK$3=E$4)*ISNUMBER(Marks!$B$10:$AK$10)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=E$4)*ISNUMBER(Marks!$B$10:$AJ$10))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=E$4)*(Marks!$B$10:$AJ$10=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=E$4)*ISNUMBER(Marks!$B$10:$AJ$10)))</f>
         <v/>
       </c>
     </row>
@@ -6491,19 +6358,19 @@
         <v>7</v>
       </c>
       <c r="B11" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=B$4)*ISNUMBER(Marks!$B$11:$AK$11))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=B$4)*(Marks!$B$11:$AK$11=1))/SUMPRODUCT((Marks!$B$3:$AK$3=B$4)*ISNUMBER(Marks!$B$11:$AK$11)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*ISNUMBER(Marks!$B$11:$AJ$11))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*(Marks!$B$11:$AJ$11=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*ISNUMBER(Marks!$B$11:$AJ$11)))</f>
         <v/>
       </c>
       <c r="C11" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=C$4)*ISNUMBER(Marks!$B$11:$AK$11))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=C$4)*(Marks!$B$11:$AK$11=1))/SUMPRODUCT((Marks!$B$3:$AK$3=C$4)*ISNUMBER(Marks!$B$11:$AK$11)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*ISNUMBER(Marks!$B$11:$AJ$11))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*(Marks!$B$11:$AJ$11=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*ISNUMBER(Marks!$B$11:$AJ$11)))</f>
         <v/>
       </c>
       <c r="D11" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=D$4)*ISNUMBER(Marks!$B$11:$AK$11))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=D$4)*(Marks!$B$11:$AK$11=1))/SUMPRODUCT((Marks!$B$3:$AK$3=D$4)*ISNUMBER(Marks!$B$11:$AK$11)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*ISNUMBER(Marks!$B$11:$AJ$11))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*(Marks!$B$11:$AJ$11=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*ISNUMBER(Marks!$B$11:$AJ$11)))</f>
         <v/>
       </c>
       <c r="E11" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=E$4)*ISNUMBER(Marks!$B$11:$AK$11))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=E$4)*(Marks!$B$11:$AK$11=1))/SUMPRODUCT((Marks!$B$3:$AK$3=E$4)*ISNUMBER(Marks!$B$11:$AK$11)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=E$4)*ISNUMBER(Marks!$B$11:$AJ$11))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=E$4)*(Marks!$B$11:$AJ$11=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=E$4)*ISNUMBER(Marks!$B$11:$AJ$11)))</f>
         <v/>
       </c>
     </row>
@@ -6512,19 +6379,19 @@
         <v>8</v>
       </c>
       <c r="B12" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=B$4)*ISNUMBER(Marks!$B$12:$AK$12))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=B$4)*(Marks!$B$12:$AK$12=1))/SUMPRODUCT((Marks!$B$3:$AK$3=B$4)*ISNUMBER(Marks!$B$12:$AK$12)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*ISNUMBER(Marks!$B$12:$AJ$12))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*(Marks!$B$12:$AJ$12=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*ISNUMBER(Marks!$B$12:$AJ$12)))</f>
         <v/>
       </c>
       <c r="C12" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=C$4)*ISNUMBER(Marks!$B$12:$AK$12))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=C$4)*(Marks!$B$12:$AK$12=1))/SUMPRODUCT((Marks!$B$3:$AK$3=C$4)*ISNUMBER(Marks!$B$12:$AK$12)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*ISNUMBER(Marks!$B$12:$AJ$12))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*(Marks!$B$12:$AJ$12=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*ISNUMBER(Marks!$B$12:$AJ$12)))</f>
         <v/>
       </c>
       <c r="D12" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=D$4)*ISNUMBER(Marks!$B$12:$AK$12))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=D$4)*(Marks!$B$12:$AK$12=1))/SUMPRODUCT((Marks!$B$3:$AK$3=D$4)*ISNUMBER(Marks!$B$12:$AK$12)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*ISNUMBER(Marks!$B$12:$AJ$12))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*(Marks!$B$12:$AJ$12=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*ISNUMBER(Marks!$B$12:$AJ$12)))</f>
         <v/>
       </c>
       <c r="E12" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=E$4)*ISNUMBER(Marks!$B$12:$AK$12))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=E$4)*(Marks!$B$12:$AK$12=1))/SUMPRODUCT((Marks!$B$3:$AK$3=E$4)*ISNUMBER(Marks!$B$12:$AK$12)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=E$4)*ISNUMBER(Marks!$B$12:$AJ$12))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=E$4)*(Marks!$B$12:$AJ$12=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=E$4)*ISNUMBER(Marks!$B$12:$AJ$12)))</f>
         <v/>
       </c>
     </row>
@@ -6533,19 +6400,19 @@
         <v>9</v>
       </c>
       <c r="B13" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=B$4)*ISNUMBER(Marks!$B$13:$AK$13))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=B$4)*(Marks!$B$13:$AK$13=1))/SUMPRODUCT((Marks!$B$3:$AK$3=B$4)*ISNUMBER(Marks!$B$13:$AK$13)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*ISNUMBER(Marks!$B$13:$AJ$13))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*(Marks!$B$13:$AJ$13=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*ISNUMBER(Marks!$B$13:$AJ$13)))</f>
         <v/>
       </c>
       <c r="C13" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=C$4)*ISNUMBER(Marks!$B$13:$AK$13))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=C$4)*(Marks!$B$13:$AK$13=1))/SUMPRODUCT((Marks!$B$3:$AK$3=C$4)*ISNUMBER(Marks!$B$13:$AK$13)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*ISNUMBER(Marks!$B$13:$AJ$13))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*(Marks!$B$13:$AJ$13=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*ISNUMBER(Marks!$B$13:$AJ$13)))</f>
         <v/>
       </c>
       <c r="D13" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=D$4)*ISNUMBER(Marks!$B$13:$AK$13))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=D$4)*(Marks!$B$13:$AK$13=1))/SUMPRODUCT((Marks!$B$3:$AK$3=D$4)*ISNUMBER(Marks!$B$13:$AK$13)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*ISNUMBER(Marks!$B$13:$AJ$13))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*(Marks!$B$13:$AJ$13=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*ISNUMBER(Marks!$B$13:$AJ$13)))</f>
         <v/>
       </c>
       <c r="E13" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=E$4)*ISNUMBER(Marks!$B$13:$AK$13))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=E$4)*(Marks!$B$13:$AK$13=1))/SUMPRODUCT((Marks!$B$3:$AK$3=E$4)*ISNUMBER(Marks!$B$13:$AK$13)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=E$4)*ISNUMBER(Marks!$B$13:$AJ$13))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=E$4)*(Marks!$B$13:$AJ$13=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=E$4)*ISNUMBER(Marks!$B$13:$AJ$13)))</f>
         <v/>
       </c>
     </row>
@@ -6554,19 +6421,19 @@
         <v>10</v>
       </c>
       <c r="B14" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=B$4)*ISNUMBER(Marks!$B$14:$AK$14))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=B$4)*(Marks!$B$14:$AK$14=1))/SUMPRODUCT((Marks!$B$3:$AK$3=B$4)*ISNUMBER(Marks!$B$14:$AK$14)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*ISNUMBER(Marks!$B$14:$AJ$14))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*(Marks!$B$14:$AJ$14=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*ISNUMBER(Marks!$B$14:$AJ$14)))</f>
         <v/>
       </c>
       <c r="C14" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=C$4)*ISNUMBER(Marks!$B$14:$AK$14))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=C$4)*(Marks!$B$14:$AK$14=1))/SUMPRODUCT((Marks!$B$3:$AK$3=C$4)*ISNUMBER(Marks!$B$14:$AK$14)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*ISNUMBER(Marks!$B$14:$AJ$14))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*(Marks!$B$14:$AJ$14=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*ISNUMBER(Marks!$B$14:$AJ$14)))</f>
         <v/>
       </c>
       <c r="D14" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=D$4)*ISNUMBER(Marks!$B$14:$AK$14))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=D$4)*(Marks!$B$14:$AK$14=1))/SUMPRODUCT((Marks!$B$3:$AK$3=D$4)*ISNUMBER(Marks!$B$14:$AK$14)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*ISNUMBER(Marks!$B$14:$AJ$14))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*(Marks!$B$14:$AJ$14=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*ISNUMBER(Marks!$B$14:$AJ$14)))</f>
         <v/>
       </c>
       <c r="E14" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=E$4)*ISNUMBER(Marks!$B$14:$AK$14))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=E$4)*(Marks!$B$14:$AK$14=1))/SUMPRODUCT((Marks!$B$3:$AK$3=E$4)*ISNUMBER(Marks!$B$14:$AK$14)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=E$4)*ISNUMBER(Marks!$B$14:$AJ$14))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=E$4)*(Marks!$B$14:$AJ$14=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=E$4)*ISNUMBER(Marks!$B$14:$AJ$14)))</f>
         <v/>
       </c>
     </row>
@@ -6575,19 +6442,19 @@
         <v>11</v>
       </c>
       <c r="B15" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=B$4)*ISNUMBER(Marks!$B$15:$AK$15))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=B$4)*(Marks!$B$15:$AK$15=1))/SUMPRODUCT((Marks!$B$3:$AK$3=B$4)*ISNUMBER(Marks!$B$15:$AK$15)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*ISNUMBER(Marks!$B$15:$AJ$15))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*(Marks!$B$15:$AJ$15=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*ISNUMBER(Marks!$B$15:$AJ$15)))</f>
         <v/>
       </c>
       <c r="C15" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=C$4)*ISNUMBER(Marks!$B$15:$AK$15))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=C$4)*(Marks!$B$15:$AK$15=1))/SUMPRODUCT((Marks!$B$3:$AK$3=C$4)*ISNUMBER(Marks!$B$15:$AK$15)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*ISNUMBER(Marks!$B$15:$AJ$15))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*(Marks!$B$15:$AJ$15=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*ISNUMBER(Marks!$B$15:$AJ$15)))</f>
         <v/>
       </c>
       <c r="D15" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=D$4)*ISNUMBER(Marks!$B$15:$AK$15))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=D$4)*(Marks!$B$15:$AK$15=1))/SUMPRODUCT((Marks!$B$3:$AK$3=D$4)*ISNUMBER(Marks!$B$15:$AK$15)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*ISNUMBER(Marks!$B$15:$AJ$15))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*(Marks!$B$15:$AJ$15=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*ISNUMBER(Marks!$B$15:$AJ$15)))</f>
         <v/>
       </c>
       <c r="E15" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=E$4)*ISNUMBER(Marks!$B$15:$AK$15))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=E$4)*(Marks!$B$15:$AK$15=1))/SUMPRODUCT((Marks!$B$3:$AK$3=E$4)*ISNUMBER(Marks!$B$15:$AK$15)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=E$4)*ISNUMBER(Marks!$B$15:$AJ$15))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=E$4)*(Marks!$B$15:$AJ$15=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=E$4)*ISNUMBER(Marks!$B$15:$AJ$15)))</f>
         <v/>
       </c>
     </row>
@@ -6596,19 +6463,19 @@
         <v>12</v>
       </c>
       <c r="B16" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=B$4)*ISNUMBER(Marks!$B$16:$AK$16))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=B$4)*(Marks!$B$16:$AK$16=1))/SUMPRODUCT((Marks!$B$3:$AK$3=B$4)*ISNUMBER(Marks!$B$16:$AK$16)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*ISNUMBER(Marks!$B$16:$AJ$16))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*(Marks!$B$16:$AJ$16=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*ISNUMBER(Marks!$B$16:$AJ$16)))</f>
         <v/>
       </c>
       <c r="C16" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=C$4)*ISNUMBER(Marks!$B$16:$AK$16))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=C$4)*(Marks!$B$16:$AK$16=1))/SUMPRODUCT((Marks!$B$3:$AK$3=C$4)*ISNUMBER(Marks!$B$16:$AK$16)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*ISNUMBER(Marks!$B$16:$AJ$16))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*(Marks!$B$16:$AJ$16=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*ISNUMBER(Marks!$B$16:$AJ$16)))</f>
         <v/>
       </c>
       <c r="D16" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=D$4)*ISNUMBER(Marks!$B$16:$AK$16))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=D$4)*(Marks!$B$16:$AK$16=1))/SUMPRODUCT((Marks!$B$3:$AK$3=D$4)*ISNUMBER(Marks!$B$16:$AK$16)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*ISNUMBER(Marks!$B$16:$AJ$16))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*(Marks!$B$16:$AJ$16=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*ISNUMBER(Marks!$B$16:$AJ$16)))</f>
         <v/>
       </c>
       <c r="E16" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=E$4)*ISNUMBER(Marks!$B$16:$AK$16))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=E$4)*(Marks!$B$16:$AK$16=1))/SUMPRODUCT((Marks!$B$3:$AK$3=E$4)*ISNUMBER(Marks!$B$16:$AK$16)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=E$4)*ISNUMBER(Marks!$B$16:$AJ$16))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=E$4)*(Marks!$B$16:$AJ$16=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=E$4)*ISNUMBER(Marks!$B$16:$AJ$16)))</f>
         <v/>
       </c>
     </row>
@@ -6617,19 +6484,19 @@
         <v>13</v>
       </c>
       <c r="B17" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=B$4)*ISNUMBER(Marks!$B$17:$AK$17))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=B$4)*(Marks!$B$17:$AK$17=1))/SUMPRODUCT((Marks!$B$3:$AK$3=B$4)*ISNUMBER(Marks!$B$17:$AK$17)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*ISNUMBER(Marks!$B$17:$AJ$17))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*(Marks!$B$17:$AJ$17=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*ISNUMBER(Marks!$B$17:$AJ$17)))</f>
         <v/>
       </c>
       <c r="C17" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=C$4)*ISNUMBER(Marks!$B$17:$AK$17))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=C$4)*(Marks!$B$17:$AK$17=1))/SUMPRODUCT((Marks!$B$3:$AK$3=C$4)*ISNUMBER(Marks!$B$17:$AK$17)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*ISNUMBER(Marks!$B$17:$AJ$17))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*(Marks!$B$17:$AJ$17=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*ISNUMBER(Marks!$B$17:$AJ$17)))</f>
         <v/>
       </c>
       <c r="D17" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=D$4)*ISNUMBER(Marks!$B$17:$AK$17))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=D$4)*(Marks!$B$17:$AK$17=1))/SUMPRODUCT((Marks!$B$3:$AK$3=D$4)*ISNUMBER(Marks!$B$17:$AK$17)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*ISNUMBER(Marks!$B$17:$AJ$17))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*(Marks!$B$17:$AJ$17=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*ISNUMBER(Marks!$B$17:$AJ$17)))</f>
         <v/>
       </c>
       <c r="E17" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=E$4)*ISNUMBER(Marks!$B$17:$AK$17))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=E$4)*(Marks!$B$17:$AK$17=1))/SUMPRODUCT((Marks!$B$3:$AK$3=E$4)*ISNUMBER(Marks!$B$17:$AK$17)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=E$4)*ISNUMBER(Marks!$B$17:$AJ$17))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=E$4)*(Marks!$B$17:$AJ$17=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=E$4)*ISNUMBER(Marks!$B$17:$AJ$17)))</f>
         <v/>
       </c>
     </row>
@@ -6638,19 +6505,19 @@
         <v>14</v>
       </c>
       <c r="B18" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=B$4)*ISNUMBER(Marks!$B$18:$AK$18))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=B$4)*(Marks!$B$18:$AK$18=1))/SUMPRODUCT((Marks!$B$3:$AK$3=B$4)*ISNUMBER(Marks!$B$18:$AK$18)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*ISNUMBER(Marks!$B$18:$AJ$18))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*(Marks!$B$18:$AJ$18=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*ISNUMBER(Marks!$B$18:$AJ$18)))</f>
         <v/>
       </c>
       <c r="C18" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=C$4)*ISNUMBER(Marks!$B$18:$AK$18))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=C$4)*(Marks!$B$18:$AK$18=1))/SUMPRODUCT((Marks!$B$3:$AK$3=C$4)*ISNUMBER(Marks!$B$18:$AK$18)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*ISNUMBER(Marks!$B$18:$AJ$18))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*(Marks!$B$18:$AJ$18=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*ISNUMBER(Marks!$B$18:$AJ$18)))</f>
         <v/>
       </c>
       <c r="D18" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=D$4)*ISNUMBER(Marks!$B$18:$AK$18))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=D$4)*(Marks!$B$18:$AK$18=1))/SUMPRODUCT((Marks!$B$3:$AK$3=D$4)*ISNUMBER(Marks!$B$18:$AK$18)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*ISNUMBER(Marks!$B$18:$AJ$18))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*(Marks!$B$18:$AJ$18=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*ISNUMBER(Marks!$B$18:$AJ$18)))</f>
         <v/>
       </c>
       <c r="E18" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=E$4)*ISNUMBER(Marks!$B$18:$AK$18))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=E$4)*(Marks!$B$18:$AK$18=1))/SUMPRODUCT((Marks!$B$3:$AK$3=E$4)*ISNUMBER(Marks!$B$18:$AK$18)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=E$4)*ISNUMBER(Marks!$B$18:$AJ$18))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=E$4)*(Marks!$B$18:$AJ$18=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=E$4)*ISNUMBER(Marks!$B$18:$AJ$18)))</f>
         <v/>
       </c>
     </row>
@@ -6659,19 +6526,19 @@
         <v>15</v>
       </c>
       <c r="B19" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=B$4)*ISNUMBER(Marks!$B$19:$AK$19))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=B$4)*(Marks!$B$19:$AK$19=1))/SUMPRODUCT((Marks!$B$3:$AK$3=B$4)*ISNUMBER(Marks!$B$19:$AK$19)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*ISNUMBER(Marks!$B$19:$AJ$19))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*(Marks!$B$19:$AJ$19=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*ISNUMBER(Marks!$B$19:$AJ$19)))</f>
         <v/>
       </c>
       <c r="C19" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=C$4)*ISNUMBER(Marks!$B$19:$AK$19))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=C$4)*(Marks!$B$19:$AK$19=1))/SUMPRODUCT((Marks!$B$3:$AK$3=C$4)*ISNUMBER(Marks!$B$19:$AK$19)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*ISNUMBER(Marks!$B$19:$AJ$19))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*(Marks!$B$19:$AJ$19=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*ISNUMBER(Marks!$B$19:$AJ$19)))</f>
         <v/>
       </c>
       <c r="D19" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=D$4)*ISNUMBER(Marks!$B$19:$AK$19))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=D$4)*(Marks!$B$19:$AK$19=1))/SUMPRODUCT((Marks!$B$3:$AK$3=D$4)*ISNUMBER(Marks!$B$19:$AK$19)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*ISNUMBER(Marks!$B$19:$AJ$19))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*(Marks!$B$19:$AJ$19=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*ISNUMBER(Marks!$B$19:$AJ$19)))</f>
         <v/>
       </c>
       <c r="E19" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=E$4)*ISNUMBER(Marks!$B$19:$AK$19))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=E$4)*(Marks!$B$19:$AK$19=1))/SUMPRODUCT((Marks!$B$3:$AK$3=E$4)*ISNUMBER(Marks!$B$19:$AK$19)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=E$4)*ISNUMBER(Marks!$B$19:$AJ$19))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=E$4)*(Marks!$B$19:$AJ$19=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=E$4)*ISNUMBER(Marks!$B$19:$AJ$19)))</f>
         <v/>
       </c>
     </row>
@@ -6680,19 +6547,19 @@
         <v>16</v>
       </c>
       <c r="B20" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=B$4)*ISNUMBER(Marks!$B$20:$AK$20))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=B$4)*(Marks!$B$20:$AK$20=1))/SUMPRODUCT((Marks!$B$3:$AK$3=B$4)*ISNUMBER(Marks!$B$20:$AK$20)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*ISNUMBER(Marks!$B$20:$AJ$20))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*(Marks!$B$20:$AJ$20=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*ISNUMBER(Marks!$B$20:$AJ$20)))</f>
         <v/>
       </c>
       <c r="C20" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=C$4)*ISNUMBER(Marks!$B$20:$AK$20))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=C$4)*(Marks!$B$20:$AK$20=1))/SUMPRODUCT((Marks!$B$3:$AK$3=C$4)*ISNUMBER(Marks!$B$20:$AK$20)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*ISNUMBER(Marks!$B$20:$AJ$20))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*(Marks!$B$20:$AJ$20=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*ISNUMBER(Marks!$B$20:$AJ$20)))</f>
         <v/>
       </c>
       <c r="D20" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=D$4)*ISNUMBER(Marks!$B$20:$AK$20))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=D$4)*(Marks!$B$20:$AK$20=1))/SUMPRODUCT((Marks!$B$3:$AK$3=D$4)*ISNUMBER(Marks!$B$20:$AK$20)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*ISNUMBER(Marks!$B$20:$AJ$20))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*(Marks!$B$20:$AJ$20=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*ISNUMBER(Marks!$B$20:$AJ$20)))</f>
         <v/>
       </c>
       <c r="E20" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=E$4)*ISNUMBER(Marks!$B$20:$AK$20))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=E$4)*(Marks!$B$20:$AK$20=1))/SUMPRODUCT((Marks!$B$3:$AK$3=E$4)*ISNUMBER(Marks!$B$20:$AK$20)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=E$4)*ISNUMBER(Marks!$B$20:$AJ$20))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=E$4)*(Marks!$B$20:$AJ$20=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=E$4)*ISNUMBER(Marks!$B$20:$AJ$20)))</f>
         <v/>
       </c>
     </row>
@@ -6701,19 +6568,19 @@
         <v>17</v>
       </c>
       <c r="B21" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=B$4)*ISNUMBER(Marks!$B$21:$AK$21))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=B$4)*(Marks!$B$21:$AK$21=1))/SUMPRODUCT((Marks!$B$3:$AK$3=B$4)*ISNUMBER(Marks!$B$21:$AK$21)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*ISNUMBER(Marks!$B$21:$AJ$21))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*(Marks!$B$21:$AJ$21=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*ISNUMBER(Marks!$B$21:$AJ$21)))</f>
         <v/>
       </c>
       <c r="C21" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=C$4)*ISNUMBER(Marks!$B$21:$AK$21))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=C$4)*(Marks!$B$21:$AK$21=1))/SUMPRODUCT((Marks!$B$3:$AK$3=C$4)*ISNUMBER(Marks!$B$21:$AK$21)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*ISNUMBER(Marks!$B$21:$AJ$21))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*(Marks!$B$21:$AJ$21=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*ISNUMBER(Marks!$B$21:$AJ$21)))</f>
         <v/>
       </c>
       <c r="D21" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=D$4)*ISNUMBER(Marks!$B$21:$AK$21))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=D$4)*(Marks!$B$21:$AK$21=1))/SUMPRODUCT((Marks!$B$3:$AK$3=D$4)*ISNUMBER(Marks!$B$21:$AK$21)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*ISNUMBER(Marks!$B$21:$AJ$21))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*(Marks!$B$21:$AJ$21=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*ISNUMBER(Marks!$B$21:$AJ$21)))</f>
         <v/>
       </c>
       <c r="E21" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=E$4)*ISNUMBER(Marks!$B$21:$AK$21))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=E$4)*(Marks!$B$21:$AK$21=1))/SUMPRODUCT((Marks!$B$3:$AK$3=E$4)*ISNUMBER(Marks!$B$21:$AK$21)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=E$4)*ISNUMBER(Marks!$B$21:$AJ$21))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=E$4)*(Marks!$B$21:$AJ$21=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=E$4)*ISNUMBER(Marks!$B$21:$AJ$21)))</f>
         <v/>
       </c>
     </row>
@@ -6722,19 +6589,19 @@
         <v>18</v>
       </c>
       <c r="B22" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=B$4)*ISNUMBER(Marks!$B$22:$AK$22))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=B$4)*(Marks!$B$22:$AK$22=1))/SUMPRODUCT((Marks!$B$3:$AK$3=B$4)*ISNUMBER(Marks!$B$22:$AK$22)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*ISNUMBER(Marks!$B$22:$AJ$22))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*(Marks!$B$22:$AJ$22=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*ISNUMBER(Marks!$B$22:$AJ$22)))</f>
         <v/>
       </c>
       <c r="C22" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=C$4)*ISNUMBER(Marks!$B$22:$AK$22))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=C$4)*(Marks!$B$22:$AK$22=1))/SUMPRODUCT((Marks!$B$3:$AK$3=C$4)*ISNUMBER(Marks!$B$22:$AK$22)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*ISNUMBER(Marks!$B$22:$AJ$22))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*(Marks!$B$22:$AJ$22=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*ISNUMBER(Marks!$B$22:$AJ$22)))</f>
         <v/>
       </c>
       <c r="D22" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=D$4)*ISNUMBER(Marks!$B$22:$AK$22))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=D$4)*(Marks!$B$22:$AK$22=1))/SUMPRODUCT((Marks!$B$3:$AK$3=D$4)*ISNUMBER(Marks!$B$22:$AK$22)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*ISNUMBER(Marks!$B$22:$AJ$22))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*(Marks!$B$22:$AJ$22=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*ISNUMBER(Marks!$B$22:$AJ$22)))</f>
         <v/>
       </c>
       <c r="E22" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=E$4)*ISNUMBER(Marks!$B$22:$AK$22))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=E$4)*(Marks!$B$22:$AK$22=1))/SUMPRODUCT((Marks!$B$3:$AK$3=E$4)*ISNUMBER(Marks!$B$22:$AK$22)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=E$4)*ISNUMBER(Marks!$B$22:$AJ$22))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=E$4)*(Marks!$B$22:$AJ$22=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=E$4)*ISNUMBER(Marks!$B$22:$AJ$22)))</f>
         <v/>
       </c>
     </row>
@@ -6743,19 +6610,19 @@
         <v>19</v>
       </c>
       <c r="B23" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=B$4)*ISNUMBER(Marks!$B$23:$AK$23))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=B$4)*(Marks!$B$23:$AK$23=1))/SUMPRODUCT((Marks!$B$3:$AK$3=B$4)*ISNUMBER(Marks!$B$23:$AK$23)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*ISNUMBER(Marks!$B$23:$AJ$23))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*(Marks!$B$23:$AJ$23=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*ISNUMBER(Marks!$B$23:$AJ$23)))</f>
         <v/>
       </c>
       <c r="C23" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=C$4)*ISNUMBER(Marks!$B$23:$AK$23))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=C$4)*(Marks!$B$23:$AK$23=1))/SUMPRODUCT((Marks!$B$3:$AK$3=C$4)*ISNUMBER(Marks!$B$23:$AK$23)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*ISNUMBER(Marks!$B$23:$AJ$23))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*(Marks!$B$23:$AJ$23=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*ISNUMBER(Marks!$B$23:$AJ$23)))</f>
         <v/>
       </c>
       <c r="D23" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=D$4)*ISNUMBER(Marks!$B$23:$AK$23))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=D$4)*(Marks!$B$23:$AK$23=1))/SUMPRODUCT((Marks!$B$3:$AK$3=D$4)*ISNUMBER(Marks!$B$23:$AK$23)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*ISNUMBER(Marks!$B$23:$AJ$23))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*(Marks!$B$23:$AJ$23=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*ISNUMBER(Marks!$B$23:$AJ$23)))</f>
         <v/>
       </c>
       <c r="E23" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=E$4)*ISNUMBER(Marks!$B$23:$AK$23))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=E$4)*(Marks!$B$23:$AK$23=1))/SUMPRODUCT((Marks!$B$3:$AK$3=E$4)*ISNUMBER(Marks!$B$23:$AK$23)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=E$4)*ISNUMBER(Marks!$B$23:$AJ$23))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=E$4)*(Marks!$B$23:$AJ$23=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=E$4)*ISNUMBER(Marks!$B$23:$AJ$23)))</f>
         <v/>
       </c>
     </row>
@@ -6764,19 +6631,19 @@
         <v>20</v>
       </c>
       <c r="B24" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=B$4)*ISNUMBER(Marks!$B$24:$AK$24))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=B$4)*(Marks!$B$24:$AK$24=1))/SUMPRODUCT((Marks!$B$3:$AK$3=B$4)*ISNUMBER(Marks!$B$24:$AK$24)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*ISNUMBER(Marks!$B$24:$AJ$24))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*(Marks!$B$24:$AJ$24=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*ISNUMBER(Marks!$B$24:$AJ$24)))</f>
         <v/>
       </c>
       <c r="C24" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=C$4)*ISNUMBER(Marks!$B$24:$AK$24))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=C$4)*(Marks!$B$24:$AK$24=1))/SUMPRODUCT((Marks!$B$3:$AK$3=C$4)*ISNUMBER(Marks!$B$24:$AK$24)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*ISNUMBER(Marks!$B$24:$AJ$24))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*(Marks!$B$24:$AJ$24=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*ISNUMBER(Marks!$B$24:$AJ$24)))</f>
         <v/>
       </c>
       <c r="D24" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=D$4)*ISNUMBER(Marks!$B$24:$AK$24))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=D$4)*(Marks!$B$24:$AK$24=1))/SUMPRODUCT((Marks!$B$3:$AK$3=D$4)*ISNUMBER(Marks!$B$24:$AK$24)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*ISNUMBER(Marks!$B$24:$AJ$24))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*(Marks!$B$24:$AJ$24=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*ISNUMBER(Marks!$B$24:$AJ$24)))</f>
         <v/>
       </c>
       <c r="E24" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=E$4)*ISNUMBER(Marks!$B$24:$AK$24))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=E$4)*(Marks!$B$24:$AK$24=1))/SUMPRODUCT((Marks!$B$3:$AK$3=E$4)*ISNUMBER(Marks!$B$24:$AK$24)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=E$4)*ISNUMBER(Marks!$B$24:$AJ$24))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=E$4)*(Marks!$B$24:$AJ$24=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=E$4)*ISNUMBER(Marks!$B$24:$AJ$24)))</f>
         <v/>
       </c>
     </row>
@@ -6785,19 +6652,19 @@
         <v>21</v>
       </c>
       <c r="B25" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=B$4)*ISNUMBER(Marks!$B$25:$AK$25))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=B$4)*(Marks!$B$25:$AK$25=1))/SUMPRODUCT((Marks!$B$3:$AK$3=B$4)*ISNUMBER(Marks!$B$25:$AK$25)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*ISNUMBER(Marks!$B$25:$AJ$25))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*(Marks!$B$25:$AJ$25=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*ISNUMBER(Marks!$B$25:$AJ$25)))</f>
         <v/>
       </c>
       <c r="C25" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=C$4)*ISNUMBER(Marks!$B$25:$AK$25))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=C$4)*(Marks!$B$25:$AK$25=1))/SUMPRODUCT((Marks!$B$3:$AK$3=C$4)*ISNUMBER(Marks!$B$25:$AK$25)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*ISNUMBER(Marks!$B$25:$AJ$25))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*(Marks!$B$25:$AJ$25=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*ISNUMBER(Marks!$B$25:$AJ$25)))</f>
         <v/>
       </c>
       <c r="D25" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=D$4)*ISNUMBER(Marks!$B$25:$AK$25))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=D$4)*(Marks!$B$25:$AK$25=1))/SUMPRODUCT((Marks!$B$3:$AK$3=D$4)*ISNUMBER(Marks!$B$25:$AK$25)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*ISNUMBER(Marks!$B$25:$AJ$25))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*(Marks!$B$25:$AJ$25=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*ISNUMBER(Marks!$B$25:$AJ$25)))</f>
         <v/>
       </c>
       <c r="E25" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=E$4)*ISNUMBER(Marks!$B$25:$AK$25))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=E$4)*(Marks!$B$25:$AK$25=1))/SUMPRODUCT((Marks!$B$3:$AK$3=E$4)*ISNUMBER(Marks!$B$25:$AK$25)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=E$4)*ISNUMBER(Marks!$B$25:$AJ$25))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=E$4)*(Marks!$B$25:$AJ$25=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=E$4)*ISNUMBER(Marks!$B$25:$AJ$25)))</f>
         <v/>
       </c>
     </row>
@@ -6806,19 +6673,19 @@
         <v>22</v>
       </c>
       <c r="B26" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=B$4)*ISNUMBER(Marks!$B$26:$AK$26))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=B$4)*(Marks!$B$26:$AK$26=1))/SUMPRODUCT((Marks!$B$3:$AK$3=B$4)*ISNUMBER(Marks!$B$26:$AK$26)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*ISNUMBER(Marks!$B$26:$AJ$26))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*(Marks!$B$26:$AJ$26=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*ISNUMBER(Marks!$B$26:$AJ$26)))</f>
         <v/>
       </c>
       <c r="C26" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=C$4)*ISNUMBER(Marks!$B$26:$AK$26))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=C$4)*(Marks!$B$26:$AK$26=1))/SUMPRODUCT((Marks!$B$3:$AK$3=C$4)*ISNUMBER(Marks!$B$26:$AK$26)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*ISNUMBER(Marks!$B$26:$AJ$26))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*(Marks!$B$26:$AJ$26=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*ISNUMBER(Marks!$B$26:$AJ$26)))</f>
         <v/>
       </c>
       <c r="D26" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=D$4)*ISNUMBER(Marks!$B$26:$AK$26))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=D$4)*(Marks!$B$26:$AK$26=1))/SUMPRODUCT((Marks!$B$3:$AK$3=D$4)*ISNUMBER(Marks!$B$26:$AK$26)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*ISNUMBER(Marks!$B$26:$AJ$26))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*(Marks!$B$26:$AJ$26=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*ISNUMBER(Marks!$B$26:$AJ$26)))</f>
         <v/>
       </c>
       <c r="E26" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=E$4)*ISNUMBER(Marks!$B$26:$AK$26))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=E$4)*(Marks!$B$26:$AK$26=1))/SUMPRODUCT((Marks!$B$3:$AK$3=E$4)*ISNUMBER(Marks!$B$26:$AK$26)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=E$4)*ISNUMBER(Marks!$B$26:$AJ$26))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=E$4)*(Marks!$B$26:$AJ$26=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=E$4)*ISNUMBER(Marks!$B$26:$AJ$26)))</f>
         <v/>
       </c>
     </row>
@@ -6827,19 +6694,19 @@
         <v>23</v>
       </c>
       <c r="B27" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=B$4)*ISNUMBER(Marks!$B$27:$AK$27))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=B$4)*(Marks!$B$27:$AK$27=1))/SUMPRODUCT((Marks!$B$3:$AK$3=B$4)*ISNUMBER(Marks!$B$27:$AK$27)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*ISNUMBER(Marks!$B$27:$AJ$27))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*(Marks!$B$27:$AJ$27=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*ISNUMBER(Marks!$B$27:$AJ$27)))</f>
         <v/>
       </c>
       <c r="C27" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=C$4)*ISNUMBER(Marks!$B$27:$AK$27))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=C$4)*(Marks!$B$27:$AK$27=1))/SUMPRODUCT((Marks!$B$3:$AK$3=C$4)*ISNUMBER(Marks!$B$27:$AK$27)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*ISNUMBER(Marks!$B$27:$AJ$27))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*(Marks!$B$27:$AJ$27=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*ISNUMBER(Marks!$B$27:$AJ$27)))</f>
         <v/>
       </c>
       <c r="D27" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=D$4)*ISNUMBER(Marks!$B$27:$AK$27))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=D$4)*(Marks!$B$27:$AK$27=1))/SUMPRODUCT((Marks!$B$3:$AK$3=D$4)*ISNUMBER(Marks!$B$27:$AK$27)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*ISNUMBER(Marks!$B$27:$AJ$27))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*(Marks!$B$27:$AJ$27=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*ISNUMBER(Marks!$B$27:$AJ$27)))</f>
         <v/>
       </c>
       <c r="E27" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=E$4)*ISNUMBER(Marks!$B$27:$AK$27))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=E$4)*(Marks!$B$27:$AK$27=1))/SUMPRODUCT((Marks!$B$3:$AK$3=E$4)*ISNUMBER(Marks!$B$27:$AK$27)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=E$4)*ISNUMBER(Marks!$B$27:$AJ$27))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=E$4)*(Marks!$B$27:$AJ$27=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=E$4)*ISNUMBER(Marks!$B$27:$AJ$27)))</f>
         <v/>
       </c>
     </row>
@@ -6848,19 +6715,19 @@
         <v>24</v>
       </c>
       <c r="B28" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=B$4)*ISNUMBER(Marks!$B$28:$AK$28))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=B$4)*(Marks!$B$28:$AK$28=1))/SUMPRODUCT((Marks!$B$3:$AK$3=B$4)*ISNUMBER(Marks!$B$28:$AK$28)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*ISNUMBER(Marks!$B$28:$AJ$28))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*(Marks!$B$28:$AJ$28=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*ISNUMBER(Marks!$B$28:$AJ$28)))</f>
         <v/>
       </c>
       <c r="C28" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=C$4)*ISNUMBER(Marks!$B$28:$AK$28))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=C$4)*(Marks!$B$28:$AK$28=1))/SUMPRODUCT((Marks!$B$3:$AK$3=C$4)*ISNUMBER(Marks!$B$28:$AK$28)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*ISNUMBER(Marks!$B$28:$AJ$28))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*(Marks!$B$28:$AJ$28=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*ISNUMBER(Marks!$B$28:$AJ$28)))</f>
         <v/>
       </c>
       <c r="D28" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=D$4)*ISNUMBER(Marks!$B$28:$AK$28))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=D$4)*(Marks!$B$28:$AK$28=1))/SUMPRODUCT((Marks!$B$3:$AK$3=D$4)*ISNUMBER(Marks!$B$28:$AK$28)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*ISNUMBER(Marks!$B$28:$AJ$28))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*(Marks!$B$28:$AJ$28=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*ISNUMBER(Marks!$B$28:$AJ$28)))</f>
         <v/>
       </c>
       <c r="E28" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=E$4)*ISNUMBER(Marks!$B$28:$AK$28))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=E$4)*(Marks!$B$28:$AK$28=1))/SUMPRODUCT((Marks!$B$3:$AK$3=E$4)*ISNUMBER(Marks!$B$28:$AK$28)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=E$4)*ISNUMBER(Marks!$B$28:$AJ$28))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=E$4)*(Marks!$B$28:$AJ$28=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=E$4)*ISNUMBER(Marks!$B$28:$AJ$28)))</f>
         <v/>
       </c>
     </row>
@@ -6869,19 +6736,19 @@
         <v>25</v>
       </c>
       <c r="B29" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=B$4)*ISNUMBER(Marks!$B$29:$AK$29))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=B$4)*(Marks!$B$29:$AK$29=1))/SUMPRODUCT((Marks!$B$3:$AK$3=B$4)*ISNUMBER(Marks!$B$29:$AK$29)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*ISNUMBER(Marks!$B$29:$AJ$29))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*(Marks!$B$29:$AJ$29=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*ISNUMBER(Marks!$B$29:$AJ$29)))</f>
         <v/>
       </c>
       <c r="C29" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=C$4)*ISNUMBER(Marks!$B$29:$AK$29))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=C$4)*(Marks!$B$29:$AK$29=1))/SUMPRODUCT((Marks!$B$3:$AK$3=C$4)*ISNUMBER(Marks!$B$29:$AK$29)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*ISNUMBER(Marks!$B$29:$AJ$29))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*(Marks!$B$29:$AJ$29=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*ISNUMBER(Marks!$B$29:$AJ$29)))</f>
         <v/>
       </c>
       <c r="D29" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=D$4)*ISNUMBER(Marks!$B$29:$AK$29))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=D$4)*(Marks!$B$29:$AK$29=1))/SUMPRODUCT((Marks!$B$3:$AK$3=D$4)*ISNUMBER(Marks!$B$29:$AK$29)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*ISNUMBER(Marks!$B$29:$AJ$29))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*(Marks!$B$29:$AJ$29=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*ISNUMBER(Marks!$B$29:$AJ$29)))</f>
         <v/>
       </c>
       <c r="E29" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=E$4)*ISNUMBER(Marks!$B$29:$AK$29))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=E$4)*(Marks!$B$29:$AK$29=1))/SUMPRODUCT((Marks!$B$3:$AK$3=E$4)*ISNUMBER(Marks!$B$29:$AK$29)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=E$4)*ISNUMBER(Marks!$B$29:$AJ$29))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=E$4)*(Marks!$B$29:$AJ$29=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=E$4)*ISNUMBER(Marks!$B$29:$AJ$29)))</f>
         <v/>
       </c>
     </row>
@@ -6890,19 +6757,19 @@
         <v>26</v>
       </c>
       <c r="B30" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=B$4)*ISNUMBER(Marks!$B$30:$AK$30))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=B$4)*(Marks!$B$30:$AK$30=1))/SUMPRODUCT((Marks!$B$3:$AK$3=B$4)*ISNUMBER(Marks!$B$30:$AK$30)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*ISNUMBER(Marks!$B$30:$AJ$30))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*(Marks!$B$30:$AJ$30=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*ISNUMBER(Marks!$B$30:$AJ$30)))</f>
         <v/>
       </c>
       <c r="C30" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=C$4)*ISNUMBER(Marks!$B$30:$AK$30))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=C$4)*(Marks!$B$30:$AK$30=1))/SUMPRODUCT((Marks!$B$3:$AK$3=C$4)*ISNUMBER(Marks!$B$30:$AK$30)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*ISNUMBER(Marks!$B$30:$AJ$30))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*(Marks!$B$30:$AJ$30=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*ISNUMBER(Marks!$B$30:$AJ$30)))</f>
         <v/>
       </c>
       <c r="D30" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=D$4)*ISNUMBER(Marks!$B$30:$AK$30))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=D$4)*(Marks!$B$30:$AK$30=1))/SUMPRODUCT((Marks!$B$3:$AK$3=D$4)*ISNUMBER(Marks!$B$30:$AK$30)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*ISNUMBER(Marks!$B$30:$AJ$30))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*(Marks!$B$30:$AJ$30=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*ISNUMBER(Marks!$B$30:$AJ$30)))</f>
         <v/>
       </c>
       <c r="E30" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=E$4)*ISNUMBER(Marks!$B$30:$AK$30))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=E$4)*(Marks!$B$30:$AK$30=1))/SUMPRODUCT((Marks!$B$3:$AK$3=E$4)*ISNUMBER(Marks!$B$30:$AK$30)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=E$4)*ISNUMBER(Marks!$B$30:$AJ$30))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=E$4)*(Marks!$B$30:$AJ$30=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=E$4)*ISNUMBER(Marks!$B$30:$AJ$30)))</f>
         <v/>
       </c>
     </row>
@@ -6911,19 +6778,19 @@
         <v>27</v>
       </c>
       <c r="B31" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=B$4)*ISNUMBER(Marks!$B$31:$AK$31))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=B$4)*(Marks!$B$31:$AK$31=1))/SUMPRODUCT((Marks!$B$3:$AK$3=B$4)*ISNUMBER(Marks!$B$31:$AK$31)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*ISNUMBER(Marks!$B$31:$AJ$31))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*(Marks!$B$31:$AJ$31=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*ISNUMBER(Marks!$B$31:$AJ$31)))</f>
         <v/>
       </c>
       <c r="C31" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=C$4)*ISNUMBER(Marks!$B$31:$AK$31))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=C$4)*(Marks!$B$31:$AK$31=1))/SUMPRODUCT((Marks!$B$3:$AK$3=C$4)*ISNUMBER(Marks!$B$31:$AK$31)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*ISNUMBER(Marks!$B$31:$AJ$31))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*(Marks!$B$31:$AJ$31=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*ISNUMBER(Marks!$B$31:$AJ$31)))</f>
         <v/>
       </c>
       <c r="D31" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=D$4)*ISNUMBER(Marks!$B$31:$AK$31))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=D$4)*(Marks!$B$31:$AK$31=1))/SUMPRODUCT((Marks!$B$3:$AK$3=D$4)*ISNUMBER(Marks!$B$31:$AK$31)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*ISNUMBER(Marks!$B$31:$AJ$31))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*(Marks!$B$31:$AJ$31=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*ISNUMBER(Marks!$B$31:$AJ$31)))</f>
         <v/>
       </c>
       <c r="E31" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=E$4)*ISNUMBER(Marks!$B$31:$AK$31))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=E$4)*(Marks!$B$31:$AK$31=1))/SUMPRODUCT((Marks!$B$3:$AK$3=E$4)*ISNUMBER(Marks!$B$31:$AK$31)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=E$4)*ISNUMBER(Marks!$B$31:$AJ$31))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=E$4)*(Marks!$B$31:$AJ$31=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=E$4)*ISNUMBER(Marks!$B$31:$AJ$31)))</f>
         <v/>
       </c>
     </row>
@@ -6932,19 +6799,19 @@
         <v>28</v>
       </c>
       <c r="B32" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=B$4)*ISNUMBER(Marks!$B$32:$AK$32))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=B$4)*(Marks!$B$32:$AK$32=1))/SUMPRODUCT((Marks!$B$3:$AK$3=B$4)*ISNUMBER(Marks!$B$32:$AK$32)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*ISNUMBER(Marks!$B$32:$AJ$32))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*(Marks!$B$32:$AJ$32=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*ISNUMBER(Marks!$B$32:$AJ$32)))</f>
         <v/>
       </c>
       <c r="C32" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=C$4)*ISNUMBER(Marks!$B$32:$AK$32))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=C$4)*(Marks!$B$32:$AK$32=1))/SUMPRODUCT((Marks!$B$3:$AK$3=C$4)*ISNUMBER(Marks!$B$32:$AK$32)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*ISNUMBER(Marks!$B$32:$AJ$32))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*(Marks!$B$32:$AJ$32=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*ISNUMBER(Marks!$B$32:$AJ$32)))</f>
         <v/>
       </c>
       <c r="D32" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=D$4)*ISNUMBER(Marks!$B$32:$AK$32))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=D$4)*(Marks!$B$32:$AK$32=1))/SUMPRODUCT((Marks!$B$3:$AK$3=D$4)*ISNUMBER(Marks!$B$32:$AK$32)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*ISNUMBER(Marks!$B$32:$AJ$32))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*(Marks!$B$32:$AJ$32=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*ISNUMBER(Marks!$B$32:$AJ$32)))</f>
         <v/>
       </c>
       <c r="E32" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=E$4)*ISNUMBER(Marks!$B$32:$AK$32))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=E$4)*(Marks!$B$32:$AK$32=1))/SUMPRODUCT((Marks!$B$3:$AK$3=E$4)*ISNUMBER(Marks!$B$32:$AK$32)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=E$4)*ISNUMBER(Marks!$B$32:$AJ$32))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=E$4)*(Marks!$B$32:$AJ$32=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=E$4)*ISNUMBER(Marks!$B$32:$AJ$32)))</f>
         <v/>
       </c>
     </row>
@@ -6953,19 +6820,19 @@
         <v>29</v>
       </c>
       <c r="B33" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=B$4)*ISNUMBER(Marks!$B$33:$AK$33))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=B$4)*(Marks!$B$33:$AK$33=1))/SUMPRODUCT((Marks!$B$3:$AK$3=B$4)*ISNUMBER(Marks!$B$33:$AK$33)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*ISNUMBER(Marks!$B$33:$AJ$33))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*(Marks!$B$33:$AJ$33=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*ISNUMBER(Marks!$B$33:$AJ$33)))</f>
         <v/>
       </c>
       <c r="C33" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=C$4)*ISNUMBER(Marks!$B$33:$AK$33))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=C$4)*(Marks!$B$33:$AK$33=1))/SUMPRODUCT((Marks!$B$3:$AK$3=C$4)*ISNUMBER(Marks!$B$33:$AK$33)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*ISNUMBER(Marks!$B$33:$AJ$33))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*(Marks!$B$33:$AJ$33=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*ISNUMBER(Marks!$B$33:$AJ$33)))</f>
         <v/>
       </c>
       <c r="D33" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=D$4)*ISNUMBER(Marks!$B$33:$AK$33))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=D$4)*(Marks!$B$33:$AK$33=1))/SUMPRODUCT((Marks!$B$3:$AK$3=D$4)*ISNUMBER(Marks!$B$33:$AK$33)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*ISNUMBER(Marks!$B$33:$AJ$33))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*(Marks!$B$33:$AJ$33=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*ISNUMBER(Marks!$B$33:$AJ$33)))</f>
         <v/>
       </c>
       <c r="E33" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=E$4)*ISNUMBER(Marks!$B$33:$AK$33))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=E$4)*(Marks!$B$33:$AK$33=1))/SUMPRODUCT((Marks!$B$3:$AK$3=E$4)*ISNUMBER(Marks!$B$33:$AK$33)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=E$4)*ISNUMBER(Marks!$B$33:$AJ$33))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=E$4)*(Marks!$B$33:$AJ$33=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=E$4)*ISNUMBER(Marks!$B$33:$AJ$33)))</f>
         <v/>
       </c>
     </row>
@@ -6974,19 +6841,19 @@
         <v>30</v>
       </c>
       <c r="B34" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=B$4)*ISNUMBER(Marks!$B$34:$AK$34))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=B$4)*(Marks!$B$34:$AK$34=1))/SUMPRODUCT((Marks!$B$3:$AK$3=B$4)*ISNUMBER(Marks!$B$34:$AK$34)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*ISNUMBER(Marks!$B$34:$AJ$34))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*(Marks!$B$34:$AJ$34=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*ISNUMBER(Marks!$B$34:$AJ$34)))</f>
         <v/>
       </c>
       <c r="C34" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=C$4)*ISNUMBER(Marks!$B$34:$AK$34))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=C$4)*(Marks!$B$34:$AK$34=1))/SUMPRODUCT((Marks!$B$3:$AK$3=C$4)*ISNUMBER(Marks!$B$34:$AK$34)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*ISNUMBER(Marks!$B$34:$AJ$34))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*(Marks!$B$34:$AJ$34=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*ISNUMBER(Marks!$B$34:$AJ$34)))</f>
         <v/>
       </c>
       <c r="D34" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=D$4)*ISNUMBER(Marks!$B$34:$AK$34))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=D$4)*(Marks!$B$34:$AK$34=1))/SUMPRODUCT((Marks!$B$3:$AK$3=D$4)*ISNUMBER(Marks!$B$34:$AK$34)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*ISNUMBER(Marks!$B$34:$AJ$34))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*(Marks!$B$34:$AJ$34=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*ISNUMBER(Marks!$B$34:$AJ$34)))</f>
         <v/>
       </c>
       <c r="E34" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=E$4)*ISNUMBER(Marks!$B$34:$AK$34))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=E$4)*(Marks!$B$34:$AK$34=1))/SUMPRODUCT((Marks!$B$3:$AK$3=E$4)*ISNUMBER(Marks!$B$34:$AK$34)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=E$4)*ISNUMBER(Marks!$B$34:$AJ$34))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=E$4)*(Marks!$B$34:$AJ$34=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=E$4)*ISNUMBER(Marks!$B$34:$AJ$34)))</f>
         <v/>
       </c>
     </row>
@@ -6995,19 +6862,19 @@
         <v>31</v>
       </c>
       <c r="B35" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=B$4)*ISNUMBER(Marks!$B$35:$AK$35))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=B$4)*(Marks!$B$35:$AK$35=1))/SUMPRODUCT((Marks!$B$3:$AK$3=B$4)*ISNUMBER(Marks!$B$35:$AK$35)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*ISNUMBER(Marks!$B$35:$AJ$35))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*(Marks!$B$35:$AJ$35=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*ISNUMBER(Marks!$B$35:$AJ$35)))</f>
         <v/>
       </c>
       <c r="C35" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=C$4)*ISNUMBER(Marks!$B$35:$AK$35))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=C$4)*(Marks!$B$35:$AK$35=1))/SUMPRODUCT((Marks!$B$3:$AK$3=C$4)*ISNUMBER(Marks!$B$35:$AK$35)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*ISNUMBER(Marks!$B$35:$AJ$35))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*(Marks!$B$35:$AJ$35=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*ISNUMBER(Marks!$B$35:$AJ$35)))</f>
         <v/>
       </c>
       <c r="D35" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=D$4)*ISNUMBER(Marks!$B$35:$AK$35))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=D$4)*(Marks!$B$35:$AK$35=1))/SUMPRODUCT((Marks!$B$3:$AK$3=D$4)*ISNUMBER(Marks!$B$35:$AK$35)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*ISNUMBER(Marks!$B$35:$AJ$35))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*(Marks!$B$35:$AJ$35=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*ISNUMBER(Marks!$B$35:$AJ$35)))</f>
         <v/>
       </c>
       <c r="E35" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=E$4)*ISNUMBER(Marks!$B$35:$AK$35))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=E$4)*(Marks!$B$35:$AK$35=1))/SUMPRODUCT((Marks!$B$3:$AK$3=E$4)*ISNUMBER(Marks!$B$35:$AK$35)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=E$4)*ISNUMBER(Marks!$B$35:$AJ$35))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=E$4)*(Marks!$B$35:$AJ$35=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=E$4)*ISNUMBER(Marks!$B$35:$AJ$35)))</f>
         <v/>
       </c>
     </row>
@@ -7016,19 +6883,19 @@
         <v>32</v>
       </c>
       <c r="B36" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=B$4)*ISNUMBER(Marks!$B$36:$AK$36))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=B$4)*(Marks!$B$36:$AK$36=1))/SUMPRODUCT((Marks!$B$3:$AK$3=B$4)*ISNUMBER(Marks!$B$36:$AK$36)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*ISNUMBER(Marks!$B$36:$AJ$36))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*(Marks!$B$36:$AJ$36=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*ISNUMBER(Marks!$B$36:$AJ$36)))</f>
         <v/>
       </c>
       <c r="C36" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=C$4)*ISNUMBER(Marks!$B$36:$AK$36))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=C$4)*(Marks!$B$36:$AK$36=1))/SUMPRODUCT((Marks!$B$3:$AK$3=C$4)*ISNUMBER(Marks!$B$36:$AK$36)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*ISNUMBER(Marks!$B$36:$AJ$36))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*(Marks!$B$36:$AJ$36=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*ISNUMBER(Marks!$B$36:$AJ$36)))</f>
         <v/>
       </c>
       <c r="D36" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=D$4)*ISNUMBER(Marks!$B$36:$AK$36))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=D$4)*(Marks!$B$36:$AK$36=1))/SUMPRODUCT((Marks!$B$3:$AK$3=D$4)*ISNUMBER(Marks!$B$36:$AK$36)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*ISNUMBER(Marks!$B$36:$AJ$36))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*(Marks!$B$36:$AJ$36=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*ISNUMBER(Marks!$B$36:$AJ$36)))</f>
         <v/>
       </c>
       <c r="E36" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=E$4)*ISNUMBER(Marks!$B$36:$AK$36))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=E$4)*(Marks!$B$36:$AK$36=1))/SUMPRODUCT((Marks!$B$3:$AK$3=E$4)*ISNUMBER(Marks!$B$36:$AK$36)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=E$4)*ISNUMBER(Marks!$B$36:$AJ$36))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=E$4)*(Marks!$B$36:$AJ$36=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=E$4)*ISNUMBER(Marks!$B$36:$AJ$36)))</f>
         <v/>
       </c>
     </row>
@@ -7037,19 +6904,19 @@
         <v>33</v>
       </c>
       <c r="B37" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=B$4)*ISNUMBER(Marks!$B$37:$AK$37))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=B$4)*(Marks!$B$37:$AK$37=1))/SUMPRODUCT((Marks!$B$3:$AK$3=B$4)*ISNUMBER(Marks!$B$37:$AK$37)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*ISNUMBER(Marks!$B$37:$AJ$37))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*(Marks!$B$37:$AJ$37=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*ISNUMBER(Marks!$B$37:$AJ$37)))</f>
         <v/>
       </c>
       <c r="C37" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=C$4)*ISNUMBER(Marks!$B$37:$AK$37))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=C$4)*(Marks!$B$37:$AK$37=1))/SUMPRODUCT((Marks!$B$3:$AK$3=C$4)*ISNUMBER(Marks!$B$37:$AK$37)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*ISNUMBER(Marks!$B$37:$AJ$37))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*(Marks!$B$37:$AJ$37=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*ISNUMBER(Marks!$B$37:$AJ$37)))</f>
         <v/>
       </c>
       <c r="D37" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=D$4)*ISNUMBER(Marks!$B$37:$AK$37))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=D$4)*(Marks!$B$37:$AK$37=1))/SUMPRODUCT((Marks!$B$3:$AK$3=D$4)*ISNUMBER(Marks!$B$37:$AK$37)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*ISNUMBER(Marks!$B$37:$AJ$37))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*(Marks!$B$37:$AJ$37=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*ISNUMBER(Marks!$B$37:$AJ$37)))</f>
         <v/>
       </c>
       <c r="E37" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=E$4)*ISNUMBER(Marks!$B$37:$AK$37))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=E$4)*(Marks!$B$37:$AK$37=1))/SUMPRODUCT((Marks!$B$3:$AK$3=E$4)*ISNUMBER(Marks!$B$37:$AK$37)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=E$4)*ISNUMBER(Marks!$B$37:$AJ$37))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=E$4)*(Marks!$B$37:$AJ$37=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=E$4)*ISNUMBER(Marks!$B$37:$AJ$37)))</f>
         <v/>
       </c>
     </row>
@@ -7058,19 +6925,19 @@
         <v>34</v>
       </c>
       <c r="B38" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=B$4)*ISNUMBER(Marks!$B$38:$AK$38))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=B$4)*(Marks!$B$38:$AK$38=1))/SUMPRODUCT((Marks!$B$3:$AK$3=B$4)*ISNUMBER(Marks!$B$38:$AK$38)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*ISNUMBER(Marks!$B$38:$AJ$38))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*(Marks!$B$38:$AJ$38=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*ISNUMBER(Marks!$B$38:$AJ$38)))</f>
         <v/>
       </c>
       <c r="C38" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=C$4)*ISNUMBER(Marks!$B$38:$AK$38))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=C$4)*(Marks!$B$38:$AK$38=1))/SUMPRODUCT((Marks!$B$3:$AK$3=C$4)*ISNUMBER(Marks!$B$38:$AK$38)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*ISNUMBER(Marks!$B$38:$AJ$38))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*(Marks!$B$38:$AJ$38=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*ISNUMBER(Marks!$B$38:$AJ$38)))</f>
         <v/>
       </c>
       <c r="D38" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=D$4)*ISNUMBER(Marks!$B$38:$AK$38))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=D$4)*(Marks!$B$38:$AK$38=1))/SUMPRODUCT((Marks!$B$3:$AK$3=D$4)*ISNUMBER(Marks!$B$38:$AK$38)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*ISNUMBER(Marks!$B$38:$AJ$38))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*(Marks!$B$38:$AJ$38=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*ISNUMBER(Marks!$B$38:$AJ$38)))</f>
         <v/>
       </c>
       <c r="E38" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=E$4)*ISNUMBER(Marks!$B$38:$AK$38))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=E$4)*(Marks!$B$38:$AK$38=1))/SUMPRODUCT((Marks!$B$3:$AK$3=E$4)*ISNUMBER(Marks!$B$38:$AK$38)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=E$4)*ISNUMBER(Marks!$B$38:$AJ$38))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=E$4)*(Marks!$B$38:$AJ$38=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=E$4)*ISNUMBER(Marks!$B$38:$AJ$38)))</f>
         <v/>
       </c>
     </row>
@@ -7079,19 +6946,19 @@
         <v>35</v>
       </c>
       <c r="B39" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=B$4)*ISNUMBER(Marks!$B$39:$AK$39))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=B$4)*(Marks!$B$39:$AK$39=1))/SUMPRODUCT((Marks!$B$3:$AK$3=B$4)*ISNUMBER(Marks!$B$39:$AK$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*ISNUMBER(Marks!$B$39:$AJ$39))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*(Marks!$B$39:$AJ$39=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=B$4)*ISNUMBER(Marks!$B$39:$AJ$39)))</f>
         <v/>
       </c>
       <c r="C39" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=C$4)*ISNUMBER(Marks!$B$39:$AK$39))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=C$4)*(Marks!$B$39:$AK$39=1))/SUMPRODUCT((Marks!$B$3:$AK$3=C$4)*ISNUMBER(Marks!$B$39:$AK$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*ISNUMBER(Marks!$B$39:$AJ$39))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*(Marks!$B$39:$AJ$39=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=C$4)*ISNUMBER(Marks!$B$39:$AJ$39)))</f>
         <v/>
       </c>
       <c r="D39" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=D$4)*ISNUMBER(Marks!$B$39:$AK$39))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=D$4)*(Marks!$B$39:$AK$39=1))/SUMPRODUCT((Marks!$B$3:$AK$3=D$4)*ISNUMBER(Marks!$B$39:$AK$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*ISNUMBER(Marks!$B$39:$AJ$39))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*(Marks!$B$39:$AJ$39=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=D$4)*ISNUMBER(Marks!$B$39:$AJ$39)))</f>
         <v/>
       </c>
       <c r="E39" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$3:$AK$3=E$4)*ISNUMBER(Marks!$B$39:$AK$39))=0,"",SUMPRODUCT((Marks!$B$3:$AK$3=E$4)*(Marks!$B$39:$AK$39=1))/SUMPRODUCT((Marks!$B$3:$AK$3=E$4)*ISNUMBER(Marks!$B$39:$AK$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$3:$AJ$3=E$4)*ISNUMBER(Marks!$B$39:$AJ$39))=0,"",SUMPRODUCT((Marks!$B$3:$AJ$3=E$4)*(Marks!$B$39:$AJ$39=1))/SUMPRODUCT((Marks!$B$3:$AJ$3=E$4)*ISNUMBER(Marks!$B$39:$AJ$39)))</f>
         <v/>
       </c>
     </row>
@@ -7225,23 +7092,23 @@
       <c r="E5" s="5" t="n"/>
       <c r="F5" s="5" t="n"/>
       <c r="H5" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=H$3)*ISNUMBER(Marks!$B$5:$AK$5))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=H$3)*(Marks!$B$5:$AK$5=1))/SUMPRODUCT((Marks!$B$2:$AK$2=H$3)*ISNUMBER(Marks!$B$5:$AK$5)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=H$3)*ISNUMBER(Marks!$B$5:$AJ$5))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=H$3)*(Marks!$B$5:$AJ$5=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=H$3)*ISNUMBER(Marks!$B$5:$AJ$5)))</f>
         <v/>
       </c>
       <c r="I5" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=I$3)*ISNUMBER(Marks!$B$5:$AK$5))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=I$3)*(Marks!$B$5:$AK$5=1))/SUMPRODUCT((Marks!$B$2:$AK$2=I$3)*ISNUMBER(Marks!$B$5:$AK$5)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*ISNUMBER(Marks!$B$5:$AJ$5))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*(Marks!$B$5:$AJ$5=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*ISNUMBER(Marks!$B$5:$AJ$5)))</f>
         <v/>
       </c>
       <c r="J5" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=J$3)*ISNUMBER(Marks!$B$5:$AK$5))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=J$3)*(Marks!$B$5:$AK$5=1))/SUMPRODUCT((Marks!$B$2:$AK$2=J$3)*ISNUMBER(Marks!$B$5:$AK$5)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*ISNUMBER(Marks!$B$5:$AJ$5))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*(Marks!$B$5:$AJ$5=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*ISNUMBER(Marks!$B$5:$AJ$5)))</f>
         <v/>
       </c>
       <c r="K5" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=K$3)*ISNUMBER(Marks!$B$5:$AK$5))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=K$3)*(Marks!$B$5:$AK$5=1))/SUMPRODUCT((Marks!$B$2:$AK$2=K$3)*ISNUMBER(Marks!$B$5:$AK$5)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*ISNUMBER(Marks!$B$5:$AJ$5))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*(Marks!$B$5:$AJ$5=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*ISNUMBER(Marks!$B$5:$AJ$5)))</f>
         <v/>
       </c>
       <c r="L5" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=L$3)*ISNUMBER(Marks!$B$5:$AK$5))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=L$3)*(Marks!$B$5:$AK$5=1))/SUMPRODUCT((Marks!$B$2:$AK$2=L$3)*ISNUMBER(Marks!$B$5:$AK$5)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*ISNUMBER(Marks!$B$5:$AJ$5))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*(Marks!$B$5:$AJ$5=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*ISNUMBER(Marks!$B$5:$AJ$5)))</f>
         <v/>
       </c>
     </row>
@@ -7255,23 +7122,23 @@
       <c r="E6" s="5" t="n"/>
       <c r="F6" s="5" t="n"/>
       <c r="H6" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=H$3)*ISNUMBER(Marks!$B$6:$AK$6))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=H$3)*(Marks!$B$6:$AK$6=1))/SUMPRODUCT((Marks!$B$2:$AK$2=H$3)*ISNUMBER(Marks!$B$6:$AK$6)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=H$3)*ISNUMBER(Marks!$B$6:$AJ$6))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=H$3)*(Marks!$B$6:$AJ$6=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=H$3)*ISNUMBER(Marks!$B$6:$AJ$6)))</f>
         <v/>
       </c>
       <c r="I6" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=I$3)*ISNUMBER(Marks!$B$6:$AK$6))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=I$3)*(Marks!$B$6:$AK$6=1))/SUMPRODUCT((Marks!$B$2:$AK$2=I$3)*ISNUMBER(Marks!$B$6:$AK$6)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*ISNUMBER(Marks!$B$6:$AJ$6))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*(Marks!$B$6:$AJ$6=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*ISNUMBER(Marks!$B$6:$AJ$6)))</f>
         <v/>
       </c>
       <c r="J6" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=J$3)*ISNUMBER(Marks!$B$6:$AK$6))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=J$3)*(Marks!$B$6:$AK$6=1))/SUMPRODUCT((Marks!$B$2:$AK$2=J$3)*ISNUMBER(Marks!$B$6:$AK$6)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*ISNUMBER(Marks!$B$6:$AJ$6))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*(Marks!$B$6:$AJ$6=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*ISNUMBER(Marks!$B$6:$AJ$6)))</f>
         <v/>
       </c>
       <c r="K6" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=K$3)*ISNUMBER(Marks!$B$6:$AK$6))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=K$3)*(Marks!$B$6:$AK$6=1))/SUMPRODUCT((Marks!$B$2:$AK$2=K$3)*ISNUMBER(Marks!$B$6:$AK$6)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*ISNUMBER(Marks!$B$6:$AJ$6))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*(Marks!$B$6:$AJ$6=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*ISNUMBER(Marks!$B$6:$AJ$6)))</f>
         <v/>
       </c>
       <c r="L6" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=L$3)*ISNUMBER(Marks!$B$6:$AK$6))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=L$3)*(Marks!$B$6:$AK$6=1))/SUMPRODUCT((Marks!$B$2:$AK$2=L$3)*ISNUMBER(Marks!$B$6:$AK$6)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*ISNUMBER(Marks!$B$6:$AJ$6))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*(Marks!$B$6:$AJ$6=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*ISNUMBER(Marks!$B$6:$AJ$6)))</f>
         <v/>
       </c>
     </row>
@@ -7285,23 +7152,23 @@
       <c r="E7" s="5" t="n"/>
       <c r="F7" s="5" t="n"/>
       <c r="H7" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=H$3)*ISNUMBER(Marks!$B$7:$AK$7))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=H$3)*(Marks!$B$7:$AK$7=1))/SUMPRODUCT((Marks!$B$2:$AK$2=H$3)*ISNUMBER(Marks!$B$7:$AK$7)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=H$3)*ISNUMBER(Marks!$B$7:$AJ$7))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=H$3)*(Marks!$B$7:$AJ$7=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=H$3)*ISNUMBER(Marks!$B$7:$AJ$7)))</f>
         <v/>
       </c>
       <c r="I7" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=I$3)*ISNUMBER(Marks!$B$7:$AK$7))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=I$3)*(Marks!$B$7:$AK$7=1))/SUMPRODUCT((Marks!$B$2:$AK$2=I$3)*ISNUMBER(Marks!$B$7:$AK$7)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*ISNUMBER(Marks!$B$7:$AJ$7))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*(Marks!$B$7:$AJ$7=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*ISNUMBER(Marks!$B$7:$AJ$7)))</f>
         <v/>
       </c>
       <c r="J7" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=J$3)*ISNUMBER(Marks!$B$7:$AK$7))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=J$3)*(Marks!$B$7:$AK$7=1))/SUMPRODUCT((Marks!$B$2:$AK$2=J$3)*ISNUMBER(Marks!$B$7:$AK$7)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*ISNUMBER(Marks!$B$7:$AJ$7))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*(Marks!$B$7:$AJ$7=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*ISNUMBER(Marks!$B$7:$AJ$7)))</f>
         <v/>
       </c>
       <c r="K7" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=K$3)*ISNUMBER(Marks!$B$7:$AK$7))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=K$3)*(Marks!$B$7:$AK$7=1))/SUMPRODUCT((Marks!$B$2:$AK$2=K$3)*ISNUMBER(Marks!$B$7:$AK$7)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*ISNUMBER(Marks!$B$7:$AJ$7))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*(Marks!$B$7:$AJ$7=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*ISNUMBER(Marks!$B$7:$AJ$7)))</f>
         <v/>
       </c>
       <c r="L7" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=L$3)*ISNUMBER(Marks!$B$7:$AK$7))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=L$3)*(Marks!$B$7:$AK$7=1))/SUMPRODUCT((Marks!$B$2:$AK$2=L$3)*ISNUMBER(Marks!$B$7:$AK$7)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*ISNUMBER(Marks!$B$7:$AJ$7))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*(Marks!$B$7:$AJ$7=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*ISNUMBER(Marks!$B$7:$AJ$7)))</f>
         <v/>
       </c>
     </row>
@@ -7315,23 +7182,23 @@
       <c r="E8" s="5" t="n"/>
       <c r="F8" s="5" t="n"/>
       <c r="H8" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=H$3)*ISNUMBER(Marks!$B$8:$AK$8))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=H$3)*(Marks!$B$8:$AK$8=1))/SUMPRODUCT((Marks!$B$2:$AK$2=H$3)*ISNUMBER(Marks!$B$8:$AK$8)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=H$3)*ISNUMBER(Marks!$B$8:$AJ$8))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=H$3)*(Marks!$B$8:$AJ$8=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=H$3)*ISNUMBER(Marks!$B$8:$AJ$8)))</f>
         <v/>
       </c>
       <c r="I8" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=I$3)*ISNUMBER(Marks!$B$8:$AK$8))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=I$3)*(Marks!$B$8:$AK$8=1))/SUMPRODUCT((Marks!$B$2:$AK$2=I$3)*ISNUMBER(Marks!$B$8:$AK$8)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*ISNUMBER(Marks!$B$8:$AJ$8))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*(Marks!$B$8:$AJ$8=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*ISNUMBER(Marks!$B$8:$AJ$8)))</f>
         <v/>
       </c>
       <c r="J8" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=J$3)*ISNUMBER(Marks!$B$8:$AK$8))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=J$3)*(Marks!$B$8:$AK$8=1))/SUMPRODUCT((Marks!$B$2:$AK$2=J$3)*ISNUMBER(Marks!$B$8:$AK$8)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*ISNUMBER(Marks!$B$8:$AJ$8))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*(Marks!$B$8:$AJ$8=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*ISNUMBER(Marks!$B$8:$AJ$8)))</f>
         <v/>
       </c>
       <c r="K8" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=K$3)*ISNUMBER(Marks!$B$8:$AK$8))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=K$3)*(Marks!$B$8:$AK$8=1))/SUMPRODUCT((Marks!$B$2:$AK$2=K$3)*ISNUMBER(Marks!$B$8:$AK$8)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*ISNUMBER(Marks!$B$8:$AJ$8))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*(Marks!$B$8:$AJ$8=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*ISNUMBER(Marks!$B$8:$AJ$8)))</f>
         <v/>
       </c>
       <c r="L8" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=L$3)*ISNUMBER(Marks!$B$8:$AK$8))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=L$3)*(Marks!$B$8:$AK$8=1))/SUMPRODUCT((Marks!$B$2:$AK$2=L$3)*ISNUMBER(Marks!$B$8:$AK$8)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*ISNUMBER(Marks!$B$8:$AJ$8))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*(Marks!$B$8:$AJ$8=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*ISNUMBER(Marks!$B$8:$AJ$8)))</f>
         <v/>
       </c>
     </row>
@@ -7345,23 +7212,23 @@
       <c r="E9" s="5" t="n"/>
       <c r="F9" s="5" t="n"/>
       <c r="H9" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=H$3)*ISNUMBER(Marks!$B$9:$AK$9))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=H$3)*(Marks!$B$9:$AK$9=1))/SUMPRODUCT((Marks!$B$2:$AK$2=H$3)*ISNUMBER(Marks!$B$9:$AK$9)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=H$3)*ISNUMBER(Marks!$B$9:$AJ$9))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=H$3)*(Marks!$B$9:$AJ$9=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=H$3)*ISNUMBER(Marks!$B$9:$AJ$9)))</f>
         <v/>
       </c>
       <c r="I9" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=I$3)*ISNUMBER(Marks!$B$9:$AK$9))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=I$3)*(Marks!$B$9:$AK$9=1))/SUMPRODUCT((Marks!$B$2:$AK$2=I$3)*ISNUMBER(Marks!$B$9:$AK$9)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*ISNUMBER(Marks!$B$9:$AJ$9))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*(Marks!$B$9:$AJ$9=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*ISNUMBER(Marks!$B$9:$AJ$9)))</f>
         <v/>
       </c>
       <c r="J9" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=J$3)*ISNUMBER(Marks!$B$9:$AK$9))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=J$3)*(Marks!$B$9:$AK$9=1))/SUMPRODUCT((Marks!$B$2:$AK$2=J$3)*ISNUMBER(Marks!$B$9:$AK$9)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*ISNUMBER(Marks!$B$9:$AJ$9))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*(Marks!$B$9:$AJ$9=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*ISNUMBER(Marks!$B$9:$AJ$9)))</f>
         <v/>
       </c>
       <c r="K9" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=K$3)*ISNUMBER(Marks!$B$9:$AK$9))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=K$3)*(Marks!$B$9:$AK$9=1))/SUMPRODUCT((Marks!$B$2:$AK$2=K$3)*ISNUMBER(Marks!$B$9:$AK$9)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*ISNUMBER(Marks!$B$9:$AJ$9))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*(Marks!$B$9:$AJ$9=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*ISNUMBER(Marks!$B$9:$AJ$9)))</f>
         <v/>
       </c>
       <c r="L9" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=L$3)*ISNUMBER(Marks!$B$9:$AK$9))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=L$3)*(Marks!$B$9:$AK$9=1))/SUMPRODUCT((Marks!$B$2:$AK$2=L$3)*ISNUMBER(Marks!$B$9:$AK$9)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*ISNUMBER(Marks!$B$9:$AJ$9))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*(Marks!$B$9:$AJ$9=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*ISNUMBER(Marks!$B$9:$AJ$9)))</f>
         <v/>
       </c>
     </row>
@@ -7375,23 +7242,23 @@
       <c r="E10" s="5" t="n"/>
       <c r="F10" s="5" t="n"/>
       <c r="H10" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=H$3)*ISNUMBER(Marks!$B$10:$AK$10))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=H$3)*(Marks!$B$10:$AK$10=1))/SUMPRODUCT((Marks!$B$2:$AK$2=H$3)*ISNUMBER(Marks!$B$10:$AK$10)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=H$3)*ISNUMBER(Marks!$B$10:$AJ$10))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=H$3)*(Marks!$B$10:$AJ$10=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=H$3)*ISNUMBER(Marks!$B$10:$AJ$10)))</f>
         <v/>
       </c>
       <c r="I10" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=I$3)*ISNUMBER(Marks!$B$10:$AK$10))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=I$3)*(Marks!$B$10:$AK$10=1))/SUMPRODUCT((Marks!$B$2:$AK$2=I$3)*ISNUMBER(Marks!$B$10:$AK$10)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*ISNUMBER(Marks!$B$10:$AJ$10))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*(Marks!$B$10:$AJ$10=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*ISNUMBER(Marks!$B$10:$AJ$10)))</f>
         <v/>
       </c>
       <c r="J10" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=J$3)*ISNUMBER(Marks!$B$10:$AK$10))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=J$3)*(Marks!$B$10:$AK$10=1))/SUMPRODUCT((Marks!$B$2:$AK$2=J$3)*ISNUMBER(Marks!$B$10:$AK$10)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*ISNUMBER(Marks!$B$10:$AJ$10))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*(Marks!$B$10:$AJ$10=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*ISNUMBER(Marks!$B$10:$AJ$10)))</f>
         <v/>
       </c>
       <c r="K10" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=K$3)*ISNUMBER(Marks!$B$10:$AK$10))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=K$3)*(Marks!$B$10:$AK$10=1))/SUMPRODUCT((Marks!$B$2:$AK$2=K$3)*ISNUMBER(Marks!$B$10:$AK$10)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*ISNUMBER(Marks!$B$10:$AJ$10))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*(Marks!$B$10:$AJ$10=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*ISNUMBER(Marks!$B$10:$AJ$10)))</f>
         <v/>
       </c>
       <c r="L10" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=L$3)*ISNUMBER(Marks!$B$10:$AK$10))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=L$3)*(Marks!$B$10:$AK$10=1))/SUMPRODUCT((Marks!$B$2:$AK$2=L$3)*ISNUMBER(Marks!$B$10:$AK$10)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*ISNUMBER(Marks!$B$10:$AJ$10))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*(Marks!$B$10:$AJ$10=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*ISNUMBER(Marks!$B$10:$AJ$10)))</f>
         <v/>
       </c>
     </row>
@@ -7405,23 +7272,23 @@
       <c r="E11" s="5" t="n"/>
       <c r="F11" s="5" t="n"/>
       <c r="H11" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=H$3)*ISNUMBER(Marks!$B$11:$AK$11))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=H$3)*(Marks!$B$11:$AK$11=1))/SUMPRODUCT((Marks!$B$2:$AK$2=H$3)*ISNUMBER(Marks!$B$11:$AK$11)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=H$3)*ISNUMBER(Marks!$B$11:$AJ$11))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=H$3)*(Marks!$B$11:$AJ$11=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=H$3)*ISNUMBER(Marks!$B$11:$AJ$11)))</f>
         <v/>
       </c>
       <c r="I11" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=I$3)*ISNUMBER(Marks!$B$11:$AK$11))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=I$3)*(Marks!$B$11:$AK$11=1))/SUMPRODUCT((Marks!$B$2:$AK$2=I$3)*ISNUMBER(Marks!$B$11:$AK$11)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*ISNUMBER(Marks!$B$11:$AJ$11))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*(Marks!$B$11:$AJ$11=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*ISNUMBER(Marks!$B$11:$AJ$11)))</f>
         <v/>
       </c>
       <c r="J11" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=J$3)*ISNUMBER(Marks!$B$11:$AK$11))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=J$3)*(Marks!$B$11:$AK$11=1))/SUMPRODUCT((Marks!$B$2:$AK$2=J$3)*ISNUMBER(Marks!$B$11:$AK$11)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*ISNUMBER(Marks!$B$11:$AJ$11))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*(Marks!$B$11:$AJ$11=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*ISNUMBER(Marks!$B$11:$AJ$11)))</f>
         <v/>
       </c>
       <c r="K11" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=K$3)*ISNUMBER(Marks!$B$11:$AK$11))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=K$3)*(Marks!$B$11:$AK$11=1))/SUMPRODUCT((Marks!$B$2:$AK$2=K$3)*ISNUMBER(Marks!$B$11:$AK$11)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*ISNUMBER(Marks!$B$11:$AJ$11))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*(Marks!$B$11:$AJ$11=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*ISNUMBER(Marks!$B$11:$AJ$11)))</f>
         <v/>
       </c>
       <c r="L11" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=L$3)*ISNUMBER(Marks!$B$11:$AK$11))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=L$3)*(Marks!$B$11:$AK$11=1))/SUMPRODUCT((Marks!$B$2:$AK$2=L$3)*ISNUMBER(Marks!$B$11:$AK$11)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*ISNUMBER(Marks!$B$11:$AJ$11))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*(Marks!$B$11:$AJ$11=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*ISNUMBER(Marks!$B$11:$AJ$11)))</f>
         <v/>
       </c>
     </row>
@@ -7435,23 +7302,23 @@
       <c r="E12" s="5" t="n"/>
       <c r="F12" s="5" t="n"/>
       <c r="H12" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=H$3)*ISNUMBER(Marks!$B$12:$AK$12))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=H$3)*(Marks!$B$12:$AK$12=1))/SUMPRODUCT((Marks!$B$2:$AK$2=H$3)*ISNUMBER(Marks!$B$12:$AK$12)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=H$3)*ISNUMBER(Marks!$B$12:$AJ$12))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=H$3)*(Marks!$B$12:$AJ$12=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=H$3)*ISNUMBER(Marks!$B$12:$AJ$12)))</f>
         <v/>
       </c>
       <c r="I12" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=I$3)*ISNUMBER(Marks!$B$12:$AK$12))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=I$3)*(Marks!$B$12:$AK$12=1))/SUMPRODUCT((Marks!$B$2:$AK$2=I$3)*ISNUMBER(Marks!$B$12:$AK$12)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*ISNUMBER(Marks!$B$12:$AJ$12))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*(Marks!$B$12:$AJ$12=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*ISNUMBER(Marks!$B$12:$AJ$12)))</f>
         <v/>
       </c>
       <c r="J12" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=J$3)*ISNUMBER(Marks!$B$12:$AK$12))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=J$3)*(Marks!$B$12:$AK$12=1))/SUMPRODUCT((Marks!$B$2:$AK$2=J$3)*ISNUMBER(Marks!$B$12:$AK$12)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*ISNUMBER(Marks!$B$12:$AJ$12))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*(Marks!$B$12:$AJ$12=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*ISNUMBER(Marks!$B$12:$AJ$12)))</f>
         <v/>
       </c>
       <c r="K12" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=K$3)*ISNUMBER(Marks!$B$12:$AK$12))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=K$3)*(Marks!$B$12:$AK$12=1))/SUMPRODUCT((Marks!$B$2:$AK$2=K$3)*ISNUMBER(Marks!$B$12:$AK$12)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*ISNUMBER(Marks!$B$12:$AJ$12))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*(Marks!$B$12:$AJ$12=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*ISNUMBER(Marks!$B$12:$AJ$12)))</f>
         <v/>
       </c>
       <c r="L12" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=L$3)*ISNUMBER(Marks!$B$12:$AK$12))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=L$3)*(Marks!$B$12:$AK$12=1))/SUMPRODUCT((Marks!$B$2:$AK$2=L$3)*ISNUMBER(Marks!$B$12:$AK$12)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*ISNUMBER(Marks!$B$12:$AJ$12))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*(Marks!$B$12:$AJ$12=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*ISNUMBER(Marks!$B$12:$AJ$12)))</f>
         <v/>
       </c>
     </row>
@@ -7465,23 +7332,23 @@
       <c r="E13" s="5" t="n"/>
       <c r="F13" s="5" t="n"/>
       <c r="H13" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=H$3)*ISNUMBER(Marks!$B$13:$AK$13))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=H$3)*(Marks!$B$13:$AK$13=1))/SUMPRODUCT((Marks!$B$2:$AK$2=H$3)*ISNUMBER(Marks!$B$13:$AK$13)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=H$3)*ISNUMBER(Marks!$B$13:$AJ$13))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=H$3)*(Marks!$B$13:$AJ$13=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=H$3)*ISNUMBER(Marks!$B$13:$AJ$13)))</f>
         <v/>
       </c>
       <c r="I13" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=I$3)*ISNUMBER(Marks!$B$13:$AK$13))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=I$3)*(Marks!$B$13:$AK$13=1))/SUMPRODUCT((Marks!$B$2:$AK$2=I$3)*ISNUMBER(Marks!$B$13:$AK$13)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*ISNUMBER(Marks!$B$13:$AJ$13))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*(Marks!$B$13:$AJ$13=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*ISNUMBER(Marks!$B$13:$AJ$13)))</f>
         <v/>
       </c>
       <c r="J13" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=J$3)*ISNUMBER(Marks!$B$13:$AK$13))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=J$3)*(Marks!$B$13:$AK$13=1))/SUMPRODUCT((Marks!$B$2:$AK$2=J$3)*ISNUMBER(Marks!$B$13:$AK$13)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*ISNUMBER(Marks!$B$13:$AJ$13))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*(Marks!$B$13:$AJ$13=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*ISNUMBER(Marks!$B$13:$AJ$13)))</f>
         <v/>
       </c>
       <c r="K13" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=K$3)*ISNUMBER(Marks!$B$13:$AK$13))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=K$3)*(Marks!$B$13:$AK$13=1))/SUMPRODUCT((Marks!$B$2:$AK$2=K$3)*ISNUMBER(Marks!$B$13:$AK$13)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*ISNUMBER(Marks!$B$13:$AJ$13))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*(Marks!$B$13:$AJ$13=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*ISNUMBER(Marks!$B$13:$AJ$13)))</f>
         <v/>
       </c>
       <c r="L13" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=L$3)*ISNUMBER(Marks!$B$13:$AK$13))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=L$3)*(Marks!$B$13:$AK$13=1))/SUMPRODUCT((Marks!$B$2:$AK$2=L$3)*ISNUMBER(Marks!$B$13:$AK$13)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*ISNUMBER(Marks!$B$13:$AJ$13))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*(Marks!$B$13:$AJ$13=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*ISNUMBER(Marks!$B$13:$AJ$13)))</f>
         <v/>
       </c>
     </row>
@@ -7495,23 +7362,23 @@
       <c r="E14" s="5" t="n"/>
       <c r="F14" s="5" t="n"/>
       <c r="H14" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=H$3)*ISNUMBER(Marks!$B$14:$AK$14))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=H$3)*(Marks!$B$14:$AK$14=1))/SUMPRODUCT((Marks!$B$2:$AK$2=H$3)*ISNUMBER(Marks!$B$14:$AK$14)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=H$3)*ISNUMBER(Marks!$B$14:$AJ$14))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=H$3)*(Marks!$B$14:$AJ$14=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=H$3)*ISNUMBER(Marks!$B$14:$AJ$14)))</f>
         <v/>
       </c>
       <c r="I14" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=I$3)*ISNUMBER(Marks!$B$14:$AK$14))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=I$3)*(Marks!$B$14:$AK$14=1))/SUMPRODUCT((Marks!$B$2:$AK$2=I$3)*ISNUMBER(Marks!$B$14:$AK$14)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*ISNUMBER(Marks!$B$14:$AJ$14))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*(Marks!$B$14:$AJ$14=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*ISNUMBER(Marks!$B$14:$AJ$14)))</f>
         <v/>
       </c>
       <c r="J14" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=J$3)*ISNUMBER(Marks!$B$14:$AK$14))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=J$3)*(Marks!$B$14:$AK$14=1))/SUMPRODUCT((Marks!$B$2:$AK$2=J$3)*ISNUMBER(Marks!$B$14:$AK$14)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*ISNUMBER(Marks!$B$14:$AJ$14))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*(Marks!$B$14:$AJ$14=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*ISNUMBER(Marks!$B$14:$AJ$14)))</f>
         <v/>
       </c>
       <c r="K14" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=K$3)*ISNUMBER(Marks!$B$14:$AK$14))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=K$3)*(Marks!$B$14:$AK$14=1))/SUMPRODUCT((Marks!$B$2:$AK$2=K$3)*ISNUMBER(Marks!$B$14:$AK$14)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*ISNUMBER(Marks!$B$14:$AJ$14))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*(Marks!$B$14:$AJ$14=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*ISNUMBER(Marks!$B$14:$AJ$14)))</f>
         <v/>
       </c>
       <c r="L14" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=L$3)*ISNUMBER(Marks!$B$14:$AK$14))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=L$3)*(Marks!$B$14:$AK$14=1))/SUMPRODUCT((Marks!$B$2:$AK$2=L$3)*ISNUMBER(Marks!$B$14:$AK$14)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*ISNUMBER(Marks!$B$14:$AJ$14))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*(Marks!$B$14:$AJ$14=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*ISNUMBER(Marks!$B$14:$AJ$14)))</f>
         <v/>
       </c>
     </row>
@@ -7525,23 +7392,23 @@
       <c r="E15" s="5" t="n"/>
       <c r="F15" s="5" t="n"/>
       <c r="H15" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=H$3)*ISNUMBER(Marks!$B$15:$AK$15))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=H$3)*(Marks!$B$15:$AK$15=1))/SUMPRODUCT((Marks!$B$2:$AK$2=H$3)*ISNUMBER(Marks!$B$15:$AK$15)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=H$3)*ISNUMBER(Marks!$B$15:$AJ$15))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=H$3)*(Marks!$B$15:$AJ$15=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=H$3)*ISNUMBER(Marks!$B$15:$AJ$15)))</f>
         <v/>
       </c>
       <c r="I15" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=I$3)*ISNUMBER(Marks!$B$15:$AK$15))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=I$3)*(Marks!$B$15:$AK$15=1))/SUMPRODUCT((Marks!$B$2:$AK$2=I$3)*ISNUMBER(Marks!$B$15:$AK$15)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*ISNUMBER(Marks!$B$15:$AJ$15))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*(Marks!$B$15:$AJ$15=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*ISNUMBER(Marks!$B$15:$AJ$15)))</f>
         <v/>
       </c>
       <c r="J15" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=J$3)*ISNUMBER(Marks!$B$15:$AK$15))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=J$3)*(Marks!$B$15:$AK$15=1))/SUMPRODUCT((Marks!$B$2:$AK$2=J$3)*ISNUMBER(Marks!$B$15:$AK$15)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*ISNUMBER(Marks!$B$15:$AJ$15))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*(Marks!$B$15:$AJ$15=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*ISNUMBER(Marks!$B$15:$AJ$15)))</f>
         <v/>
       </c>
       <c r="K15" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=K$3)*ISNUMBER(Marks!$B$15:$AK$15))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=K$3)*(Marks!$B$15:$AK$15=1))/SUMPRODUCT((Marks!$B$2:$AK$2=K$3)*ISNUMBER(Marks!$B$15:$AK$15)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*ISNUMBER(Marks!$B$15:$AJ$15))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*(Marks!$B$15:$AJ$15=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*ISNUMBER(Marks!$B$15:$AJ$15)))</f>
         <v/>
       </c>
       <c r="L15" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=L$3)*ISNUMBER(Marks!$B$15:$AK$15))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=L$3)*(Marks!$B$15:$AK$15=1))/SUMPRODUCT((Marks!$B$2:$AK$2=L$3)*ISNUMBER(Marks!$B$15:$AK$15)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*ISNUMBER(Marks!$B$15:$AJ$15))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*(Marks!$B$15:$AJ$15=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*ISNUMBER(Marks!$B$15:$AJ$15)))</f>
         <v/>
       </c>
     </row>
@@ -7555,23 +7422,23 @@
       <c r="E16" s="5" t="n"/>
       <c r="F16" s="5" t="n"/>
       <c r="H16" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=H$3)*ISNUMBER(Marks!$B$16:$AK$16))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=H$3)*(Marks!$B$16:$AK$16=1))/SUMPRODUCT((Marks!$B$2:$AK$2=H$3)*ISNUMBER(Marks!$B$16:$AK$16)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=H$3)*ISNUMBER(Marks!$B$16:$AJ$16))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=H$3)*(Marks!$B$16:$AJ$16=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=H$3)*ISNUMBER(Marks!$B$16:$AJ$16)))</f>
         <v/>
       </c>
       <c r="I16" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=I$3)*ISNUMBER(Marks!$B$16:$AK$16))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=I$3)*(Marks!$B$16:$AK$16=1))/SUMPRODUCT((Marks!$B$2:$AK$2=I$3)*ISNUMBER(Marks!$B$16:$AK$16)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*ISNUMBER(Marks!$B$16:$AJ$16))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*(Marks!$B$16:$AJ$16=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*ISNUMBER(Marks!$B$16:$AJ$16)))</f>
         <v/>
       </c>
       <c r="J16" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=J$3)*ISNUMBER(Marks!$B$16:$AK$16))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=J$3)*(Marks!$B$16:$AK$16=1))/SUMPRODUCT((Marks!$B$2:$AK$2=J$3)*ISNUMBER(Marks!$B$16:$AK$16)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*ISNUMBER(Marks!$B$16:$AJ$16))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*(Marks!$B$16:$AJ$16=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*ISNUMBER(Marks!$B$16:$AJ$16)))</f>
         <v/>
       </c>
       <c r="K16" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=K$3)*ISNUMBER(Marks!$B$16:$AK$16))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=K$3)*(Marks!$B$16:$AK$16=1))/SUMPRODUCT((Marks!$B$2:$AK$2=K$3)*ISNUMBER(Marks!$B$16:$AK$16)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*ISNUMBER(Marks!$B$16:$AJ$16))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*(Marks!$B$16:$AJ$16=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*ISNUMBER(Marks!$B$16:$AJ$16)))</f>
         <v/>
       </c>
       <c r="L16" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=L$3)*ISNUMBER(Marks!$B$16:$AK$16))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=L$3)*(Marks!$B$16:$AK$16=1))/SUMPRODUCT((Marks!$B$2:$AK$2=L$3)*ISNUMBER(Marks!$B$16:$AK$16)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*ISNUMBER(Marks!$B$16:$AJ$16))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*(Marks!$B$16:$AJ$16=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*ISNUMBER(Marks!$B$16:$AJ$16)))</f>
         <v/>
       </c>
     </row>
@@ -7585,23 +7452,23 @@
       <c r="E17" s="5" t="n"/>
       <c r="F17" s="5" t="n"/>
       <c r="H17" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=H$3)*ISNUMBER(Marks!$B$17:$AK$17))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=H$3)*(Marks!$B$17:$AK$17=1))/SUMPRODUCT((Marks!$B$2:$AK$2=H$3)*ISNUMBER(Marks!$B$17:$AK$17)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=H$3)*ISNUMBER(Marks!$B$17:$AJ$17))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=H$3)*(Marks!$B$17:$AJ$17=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=H$3)*ISNUMBER(Marks!$B$17:$AJ$17)))</f>
         <v/>
       </c>
       <c r="I17" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=I$3)*ISNUMBER(Marks!$B$17:$AK$17))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=I$3)*(Marks!$B$17:$AK$17=1))/SUMPRODUCT((Marks!$B$2:$AK$2=I$3)*ISNUMBER(Marks!$B$17:$AK$17)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*ISNUMBER(Marks!$B$17:$AJ$17))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*(Marks!$B$17:$AJ$17=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*ISNUMBER(Marks!$B$17:$AJ$17)))</f>
         <v/>
       </c>
       <c r="J17" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=J$3)*ISNUMBER(Marks!$B$17:$AK$17))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=J$3)*(Marks!$B$17:$AK$17=1))/SUMPRODUCT((Marks!$B$2:$AK$2=J$3)*ISNUMBER(Marks!$B$17:$AK$17)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*ISNUMBER(Marks!$B$17:$AJ$17))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*(Marks!$B$17:$AJ$17=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*ISNUMBER(Marks!$B$17:$AJ$17)))</f>
         <v/>
       </c>
       <c r="K17" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=K$3)*ISNUMBER(Marks!$B$17:$AK$17))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=K$3)*(Marks!$B$17:$AK$17=1))/SUMPRODUCT((Marks!$B$2:$AK$2=K$3)*ISNUMBER(Marks!$B$17:$AK$17)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*ISNUMBER(Marks!$B$17:$AJ$17))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*(Marks!$B$17:$AJ$17=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*ISNUMBER(Marks!$B$17:$AJ$17)))</f>
         <v/>
       </c>
       <c r="L17" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=L$3)*ISNUMBER(Marks!$B$17:$AK$17))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=L$3)*(Marks!$B$17:$AK$17=1))/SUMPRODUCT((Marks!$B$2:$AK$2=L$3)*ISNUMBER(Marks!$B$17:$AK$17)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*ISNUMBER(Marks!$B$17:$AJ$17))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*(Marks!$B$17:$AJ$17=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*ISNUMBER(Marks!$B$17:$AJ$17)))</f>
         <v/>
       </c>
     </row>
@@ -7615,23 +7482,23 @@
       <c r="E18" s="5" t="n"/>
       <c r="F18" s="5" t="n"/>
       <c r="H18" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=H$3)*ISNUMBER(Marks!$B$18:$AK$18))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=H$3)*(Marks!$B$18:$AK$18=1))/SUMPRODUCT((Marks!$B$2:$AK$2=H$3)*ISNUMBER(Marks!$B$18:$AK$18)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=H$3)*ISNUMBER(Marks!$B$18:$AJ$18))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=H$3)*(Marks!$B$18:$AJ$18=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=H$3)*ISNUMBER(Marks!$B$18:$AJ$18)))</f>
         <v/>
       </c>
       <c r="I18" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=I$3)*ISNUMBER(Marks!$B$18:$AK$18))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=I$3)*(Marks!$B$18:$AK$18=1))/SUMPRODUCT((Marks!$B$2:$AK$2=I$3)*ISNUMBER(Marks!$B$18:$AK$18)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*ISNUMBER(Marks!$B$18:$AJ$18))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*(Marks!$B$18:$AJ$18=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*ISNUMBER(Marks!$B$18:$AJ$18)))</f>
         <v/>
       </c>
       <c r="J18" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=J$3)*ISNUMBER(Marks!$B$18:$AK$18))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=J$3)*(Marks!$B$18:$AK$18=1))/SUMPRODUCT((Marks!$B$2:$AK$2=J$3)*ISNUMBER(Marks!$B$18:$AK$18)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*ISNUMBER(Marks!$B$18:$AJ$18))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*(Marks!$B$18:$AJ$18=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*ISNUMBER(Marks!$B$18:$AJ$18)))</f>
         <v/>
       </c>
       <c r="K18" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=K$3)*ISNUMBER(Marks!$B$18:$AK$18))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=K$3)*(Marks!$B$18:$AK$18=1))/SUMPRODUCT((Marks!$B$2:$AK$2=K$3)*ISNUMBER(Marks!$B$18:$AK$18)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*ISNUMBER(Marks!$B$18:$AJ$18))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*(Marks!$B$18:$AJ$18=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*ISNUMBER(Marks!$B$18:$AJ$18)))</f>
         <v/>
       </c>
       <c r="L18" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=L$3)*ISNUMBER(Marks!$B$18:$AK$18))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=L$3)*(Marks!$B$18:$AK$18=1))/SUMPRODUCT((Marks!$B$2:$AK$2=L$3)*ISNUMBER(Marks!$B$18:$AK$18)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*ISNUMBER(Marks!$B$18:$AJ$18))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*(Marks!$B$18:$AJ$18=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*ISNUMBER(Marks!$B$18:$AJ$18)))</f>
         <v/>
       </c>
     </row>
@@ -7645,23 +7512,23 @@
       <c r="E19" s="5" t="n"/>
       <c r="F19" s="5" t="n"/>
       <c r="H19" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=H$3)*ISNUMBER(Marks!$B$19:$AK$19))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=H$3)*(Marks!$B$19:$AK$19=1))/SUMPRODUCT((Marks!$B$2:$AK$2=H$3)*ISNUMBER(Marks!$B$19:$AK$19)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=H$3)*ISNUMBER(Marks!$B$19:$AJ$19))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=H$3)*(Marks!$B$19:$AJ$19=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=H$3)*ISNUMBER(Marks!$B$19:$AJ$19)))</f>
         <v/>
       </c>
       <c r="I19" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=I$3)*ISNUMBER(Marks!$B$19:$AK$19))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=I$3)*(Marks!$B$19:$AK$19=1))/SUMPRODUCT((Marks!$B$2:$AK$2=I$3)*ISNUMBER(Marks!$B$19:$AK$19)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*ISNUMBER(Marks!$B$19:$AJ$19))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*(Marks!$B$19:$AJ$19=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*ISNUMBER(Marks!$B$19:$AJ$19)))</f>
         <v/>
       </c>
       <c r="J19" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=J$3)*ISNUMBER(Marks!$B$19:$AK$19))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=J$3)*(Marks!$B$19:$AK$19=1))/SUMPRODUCT((Marks!$B$2:$AK$2=J$3)*ISNUMBER(Marks!$B$19:$AK$19)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*ISNUMBER(Marks!$B$19:$AJ$19))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*(Marks!$B$19:$AJ$19=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*ISNUMBER(Marks!$B$19:$AJ$19)))</f>
         <v/>
       </c>
       <c r="K19" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=K$3)*ISNUMBER(Marks!$B$19:$AK$19))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=K$3)*(Marks!$B$19:$AK$19=1))/SUMPRODUCT((Marks!$B$2:$AK$2=K$3)*ISNUMBER(Marks!$B$19:$AK$19)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*ISNUMBER(Marks!$B$19:$AJ$19))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*(Marks!$B$19:$AJ$19=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*ISNUMBER(Marks!$B$19:$AJ$19)))</f>
         <v/>
       </c>
       <c r="L19" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=L$3)*ISNUMBER(Marks!$B$19:$AK$19))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=L$3)*(Marks!$B$19:$AK$19=1))/SUMPRODUCT((Marks!$B$2:$AK$2=L$3)*ISNUMBER(Marks!$B$19:$AK$19)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*ISNUMBER(Marks!$B$19:$AJ$19))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*(Marks!$B$19:$AJ$19=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*ISNUMBER(Marks!$B$19:$AJ$19)))</f>
         <v/>
       </c>
     </row>
@@ -7675,23 +7542,23 @@
       <c r="E20" s="5" t="n"/>
       <c r="F20" s="5" t="n"/>
       <c r="H20" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=H$3)*ISNUMBER(Marks!$B$20:$AK$20))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=H$3)*(Marks!$B$20:$AK$20=1))/SUMPRODUCT((Marks!$B$2:$AK$2=H$3)*ISNUMBER(Marks!$B$20:$AK$20)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=H$3)*ISNUMBER(Marks!$B$20:$AJ$20))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=H$3)*(Marks!$B$20:$AJ$20=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=H$3)*ISNUMBER(Marks!$B$20:$AJ$20)))</f>
         <v/>
       </c>
       <c r="I20" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=I$3)*ISNUMBER(Marks!$B$20:$AK$20))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=I$3)*(Marks!$B$20:$AK$20=1))/SUMPRODUCT((Marks!$B$2:$AK$2=I$3)*ISNUMBER(Marks!$B$20:$AK$20)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*ISNUMBER(Marks!$B$20:$AJ$20))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*(Marks!$B$20:$AJ$20=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*ISNUMBER(Marks!$B$20:$AJ$20)))</f>
         <v/>
       </c>
       <c r="J20" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=J$3)*ISNUMBER(Marks!$B$20:$AK$20))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=J$3)*(Marks!$B$20:$AK$20=1))/SUMPRODUCT((Marks!$B$2:$AK$2=J$3)*ISNUMBER(Marks!$B$20:$AK$20)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*ISNUMBER(Marks!$B$20:$AJ$20))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*(Marks!$B$20:$AJ$20=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*ISNUMBER(Marks!$B$20:$AJ$20)))</f>
         <v/>
       </c>
       <c r="K20" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=K$3)*ISNUMBER(Marks!$B$20:$AK$20))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=K$3)*(Marks!$B$20:$AK$20=1))/SUMPRODUCT((Marks!$B$2:$AK$2=K$3)*ISNUMBER(Marks!$B$20:$AK$20)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*ISNUMBER(Marks!$B$20:$AJ$20))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*(Marks!$B$20:$AJ$20=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*ISNUMBER(Marks!$B$20:$AJ$20)))</f>
         <v/>
       </c>
       <c r="L20" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=L$3)*ISNUMBER(Marks!$B$20:$AK$20))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=L$3)*(Marks!$B$20:$AK$20=1))/SUMPRODUCT((Marks!$B$2:$AK$2=L$3)*ISNUMBER(Marks!$B$20:$AK$20)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*ISNUMBER(Marks!$B$20:$AJ$20))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*(Marks!$B$20:$AJ$20=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*ISNUMBER(Marks!$B$20:$AJ$20)))</f>
         <v/>
       </c>
     </row>
@@ -7705,23 +7572,23 @@
       <c r="E21" s="5" t="n"/>
       <c r="F21" s="5" t="n"/>
       <c r="H21" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=H$3)*ISNUMBER(Marks!$B$21:$AK$21))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=H$3)*(Marks!$B$21:$AK$21=1))/SUMPRODUCT((Marks!$B$2:$AK$2=H$3)*ISNUMBER(Marks!$B$21:$AK$21)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=H$3)*ISNUMBER(Marks!$B$21:$AJ$21))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=H$3)*(Marks!$B$21:$AJ$21=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=H$3)*ISNUMBER(Marks!$B$21:$AJ$21)))</f>
         <v/>
       </c>
       <c r="I21" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=I$3)*ISNUMBER(Marks!$B$21:$AK$21))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=I$3)*(Marks!$B$21:$AK$21=1))/SUMPRODUCT((Marks!$B$2:$AK$2=I$3)*ISNUMBER(Marks!$B$21:$AK$21)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*ISNUMBER(Marks!$B$21:$AJ$21))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*(Marks!$B$21:$AJ$21=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*ISNUMBER(Marks!$B$21:$AJ$21)))</f>
         <v/>
       </c>
       <c r="J21" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=J$3)*ISNUMBER(Marks!$B$21:$AK$21))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=J$3)*(Marks!$B$21:$AK$21=1))/SUMPRODUCT((Marks!$B$2:$AK$2=J$3)*ISNUMBER(Marks!$B$21:$AK$21)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*ISNUMBER(Marks!$B$21:$AJ$21))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*(Marks!$B$21:$AJ$21=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*ISNUMBER(Marks!$B$21:$AJ$21)))</f>
         <v/>
       </c>
       <c r="K21" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=K$3)*ISNUMBER(Marks!$B$21:$AK$21))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=K$3)*(Marks!$B$21:$AK$21=1))/SUMPRODUCT((Marks!$B$2:$AK$2=K$3)*ISNUMBER(Marks!$B$21:$AK$21)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*ISNUMBER(Marks!$B$21:$AJ$21))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*(Marks!$B$21:$AJ$21=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*ISNUMBER(Marks!$B$21:$AJ$21)))</f>
         <v/>
       </c>
       <c r="L21" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=L$3)*ISNUMBER(Marks!$B$21:$AK$21))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=L$3)*(Marks!$B$21:$AK$21=1))/SUMPRODUCT((Marks!$B$2:$AK$2=L$3)*ISNUMBER(Marks!$B$21:$AK$21)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*ISNUMBER(Marks!$B$21:$AJ$21))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*(Marks!$B$21:$AJ$21=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*ISNUMBER(Marks!$B$21:$AJ$21)))</f>
         <v/>
       </c>
     </row>
@@ -7735,23 +7602,23 @@
       <c r="E22" s="5" t="n"/>
       <c r="F22" s="5" t="n"/>
       <c r="H22" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=H$3)*ISNUMBER(Marks!$B$22:$AK$22))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=H$3)*(Marks!$B$22:$AK$22=1))/SUMPRODUCT((Marks!$B$2:$AK$2=H$3)*ISNUMBER(Marks!$B$22:$AK$22)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=H$3)*ISNUMBER(Marks!$B$22:$AJ$22))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=H$3)*(Marks!$B$22:$AJ$22=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=H$3)*ISNUMBER(Marks!$B$22:$AJ$22)))</f>
         <v/>
       </c>
       <c r="I22" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=I$3)*ISNUMBER(Marks!$B$22:$AK$22))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=I$3)*(Marks!$B$22:$AK$22=1))/SUMPRODUCT((Marks!$B$2:$AK$2=I$3)*ISNUMBER(Marks!$B$22:$AK$22)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*ISNUMBER(Marks!$B$22:$AJ$22))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*(Marks!$B$22:$AJ$22=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*ISNUMBER(Marks!$B$22:$AJ$22)))</f>
         <v/>
       </c>
       <c r="J22" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=J$3)*ISNUMBER(Marks!$B$22:$AK$22))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=J$3)*(Marks!$B$22:$AK$22=1))/SUMPRODUCT((Marks!$B$2:$AK$2=J$3)*ISNUMBER(Marks!$B$22:$AK$22)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*ISNUMBER(Marks!$B$22:$AJ$22))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*(Marks!$B$22:$AJ$22=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*ISNUMBER(Marks!$B$22:$AJ$22)))</f>
         <v/>
       </c>
       <c r="K22" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=K$3)*ISNUMBER(Marks!$B$22:$AK$22))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=K$3)*(Marks!$B$22:$AK$22=1))/SUMPRODUCT((Marks!$B$2:$AK$2=K$3)*ISNUMBER(Marks!$B$22:$AK$22)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*ISNUMBER(Marks!$B$22:$AJ$22))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*(Marks!$B$22:$AJ$22=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*ISNUMBER(Marks!$B$22:$AJ$22)))</f>
         <v/>
       </c>
       <c r="L22" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=L$3)*ISNUMBER(Marks!$B$22:$AK$22))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=L$3)*(Marks!$B$22:$AK$22=1))/SUMPRODUCT((Marks!$B$2:$AK$2=L$3)*ISNUMBER(Marks!$B$22:$AK$22)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*ISNUMBER(Marks!$B$22:$AJ$22))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*(Marks!$B$22:$AJ$22=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*ISNUMBER(Marks!$B$22:$AJ$22)))</f>
         <v/>
       </c>
     </row>
@@ -7765,23 +7632,23 @@
       <c r="E23" s="5" t="n"/>
       <c r="F23" s="5" t="n"/>
       <c r="H23" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=H$3)*ISNUMBER(Marks!$B$23:$AK$23))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=H$3)*(Marks!$B$23:$AK$23=1))/SUMPRODUCT((Marks!$B$2:$AK$2=H$3)*ISNUMBER(Marks!$B$23:$AK$23)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=H$3)*ISNUMBER(Marks!$B$23:$AJ$23))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=H$3)*(Marks!$B$23:$AJ$23=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=H$3)*ISNUMBER(Marks!$B$23:$AJ$23)))</f>
         <v/>
       </c>
       <c r="I23" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=I$3)*ISNUMBER(Marks!$B$23:$AK$23))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=I$3)*(Marks!$B$23:$AK$23=1))/SUMPRODUCT((Marks!$B$2:$AK$2=I$3)*ISNUMBER(Marks!$B$23:$AK$23)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*ISNUMBER(Marks!$B$23:$AJ$23))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*(Marks!$B$23:$AJ$23=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*ISNUMBER(Marks!$B$23:$AJ$23)))</f>
         <v/>
       </c>
       <c r="J23" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=J$3)*ISNUMBER(Marks!$B$23:$AK$23))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=J$3)*(Marks!$B$23:$AK$23=1))/SUMPRODUCT((Marks!$B$2:$AK$2=J$3)*ISNUMBER(Marks!$B$23:$AK$23)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*ISNUMBER(Marks!$B$23:$AJ$23))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*(Marks!$B$23:$AJ$23=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*ISNUMBER(Marks!$B$23:$AJ$23)))</f>
         <v/>
       </c>
       <c r="K23" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=K$3)*ISNUMBER(Marks!$B$23:$AK$23))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=K$3)*(Marks!$B$23:$AK$23=1))/SUMPRODUCT((Marks!$B$2:$AK$2=K$3)*ISNUMBER(Marks!$B$23:$AK$23)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*ISNUMBER(Marks!$B$23:$AJ$23))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*(Marks!$B$23:$AJ$23=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*ISNUMBER(Marks!$B$23:$AJ$23)))</f>
         <v/>
       </c>
       <c r="L23" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=L$3)*ISNUMBER(Marks!$B$23:$AK$23))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=L$3)*(Marks!$B$23:$AK$23=1))/SUMPRODUCT((Marks!$B$2:$AK$2=L$3)*ISNUMBER(Marks!$B$23:$AK$23)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*ISNUMBER(Marks!$B$23:$AJ$23))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*(Marks!$B$23:$AJ$23=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*ISNUMBER(Marks!$B$23:$AJ$23)))</f>
         <v/>
       </c>
     </row>
@@ -7795,23 +7662,23 @@
       <c r="E24" s="5" t="n"/>
       <c r="F24" s="5" t="n"/>
       <c r="H24" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=H$3)*ISNUMBER(Marks!$B$24:$AK$24))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=H$3)*(Marks!$B$24:$AK$24=1))/SUMPRODUCT((Marks!$B$2:$AK$2=H$3)*ISNUMBER(Marks!$B$24:$AK$24)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=H$3)*ISNUMBER(Marks!$B$24:$AJ$24))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=H$3)*(Marks!$B$24:$AJ$24=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=H$3)*ISNUMBER(Marks!$B$24:$AJ$24)))</f>
         <v/>
       </c>
       <c r="I24" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=I$3)*ISNUMBER(Marks!$B$24:$AK$24))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=I$3)*(Marks!$B$24:$AK$24=1))/SUMPRODUCT((Marks!$B$2:$AK$2=I$3)*ISNUMBER(Marks!$B$24:$AK$24)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*ISNUMBER(Marks!$B$24:$AJ$24))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*(Marks!$B$24:$AJ$24=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*ISNUMBER(Marks!$B$24:$AJ$24)))</f>
         <v/>
       </c>
       <c r="J24" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=J$3)*ISNUMBER(Marks!$B$24:$AK$24))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=J$3)*(Marks!$B$24:$AK$24=1))/SUMPRODUCT((Marks!$B$2:$AK$2=J$3)*ISNUMBER(Marks!$B$24:$AK$24)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*ISNUMBER(Marks!$B$24:$AJ$24))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*(Marks!$B$24:$AJ$24=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*ISNUMBER(Marks!$B$24:$AJ$24)))</f>
         <v/>
       </c>
       <c r="K24" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=K$3)*ISNUMBER(Marks!$B$24:$AK$24))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=K$3)*(Marks!$B$24:$AK$24=1))/SUMPRODUCT((Marks!$B$2:$AK$2=K$3)*ISNUMBER(Marks!$B$24:$AK$24)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*ISNUMBER(Marks!$B$24:$AJ$24))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*(Marks!$B$24:$AJ$24=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*ISNUMBER(Marks!$B$24:$AJ$24)))</f>
         <v/>
       </c>
       <c r="L24" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=L$3)*ISNUMBER(Marks!$B$24:$AK$24))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=L$3)*(Marks!$B$24:$AK$24=1))/SUMPRODUCT((Marks!$B$2:$AK$2=L$3)*ISNUMBER(Marks!$B$24:$AK$24)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*ISNUMBER(Marks!$B$24:$AJ$24))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*(Marks!$B$24:$AJ$24=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*ISNUMBER(Marks!$B$24:$AJ$24)))</f>
         <v/>
       </c>
     </row>
@@ -7825,23 +7692,23 @@
       <c r="E25" s="5" t="n"/>
       <c r="F25" s="5" t="n"/>
       <c r="H25" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=H$3)*ISNUMBER(Marks!$B$25:$AK$25))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=H$3)*(Marks!$B$25:$AK$25=1))/SUMPRODUCT((Marks!$B$2:$AK$2=H$3)*ISNUMBER(Marks!$B$25:$AK$25)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=H$3)*ISNUMBER(Marks!$B$25:$AJ$25))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=H$3)*(Marks!$B$25:$AJ$25=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=H$3)*ISNUMBER(Marks!$B$25:$AJ$25)))</f>
         <v/>
       </c>
       <c r="I25" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=I$3)*ISNUMBER(Marks!$B$25:$AK$25))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=I$3)*(Marks!$B$25:$AK$25=1))/SUMPRODUCT((Marks!$B$2:$AK$2=I$3)*ISNUMBER(Marks!$B$25:$AK$25)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*ISNUMBER(Marks!$B$25:$AJ$25))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*(Marks!$B$25:$AJ$25=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*ISNUMBER(Marks!$B$25:$AJ$25)))</f>
         <v/>
       </c>
       <c r="J25" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=J$3)*ISNUMBER(Marks!$B$25:$AK$25))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=J$3)*(Marks!$B$25:$AK$25=1))/SUMPRODUCT((Marks!$B$2:$AK$2=J$3)*ISNUMBER(Marks!$B$25:$AK$25)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*ISNUMBER(Marks!$B$25:$AJ$25))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*(Marks!$B$25:$AJ$25=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*ISNUMBER(Marks!$B$25:$AJ$25)))</f>
         <v/>
       </c>
       <c r="K25" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=K$3)*ISNUMBER(Marks!$B$25:$AK$25))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=K$3)*(Marks!$B$25:$AK$25=1))/SUMPRODUCT((Marks!$B$2:$AK$2=K$3)*ISNUMBER(Marks!$B$25:$AK$25)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*ISNUMBER(Marks!$B$25:$AJ$25))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*(Marks!$B$25:$AJ$25=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*ISNUMBER(Marks!$B$25:$AJ$25)))</f>
         <v/>
       </c>
       <c r="L25" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=L$3)*ISNUMBER(Marks!$B$25:$AK$25))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=L$3)*(Marks!$B$25:$AK$25=1))/SUMPRODUCT((Marks!$B$2:$AK$2=L$3)*ISNUMBER(Marks!$B$25:$AK$25)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*ISNUMBER(Marks!$B$25:$AJ$25))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*(Marks!$B$25:$AJ$25=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*ISNUMBER(Marks!$B$25:$AJ$25)))</f>
         <v/>
       </c>
     </row>
@@ -7855,23 +7722,23 @@
       <c r="E26" s="5" t="n"/>
       <c r="F26" s="5" t="n"/>
       <c r="H26" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=H$3)*ISNUMBER(Marks!$B$26:$AK$26))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=H$3)*(Marks!$B$26:$AK$26=1))/SUMPRODUCT((Marks!$B$2:$AK$2=H$3)*ISNUMBER(Marks!$B$26:$AK$26)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=H$3)*ISNUMBER(Marks!$B$26:$AJ$26))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=H$3)*(Marks!$B$26:$AJ$26=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=H$3)*ISNUMBER(Marks!$B$26:$AJ$26)))</f>
         <v/>
       </c>
       <c r="I26" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=I$3)*ISNUMBER(Marks!$B$26:$AK$26))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=I$3)*(Marks!$B$26:$AK$26=1))/SUMPRODUCT((Marks!$B$2:$AK$2=I$3)*ISNUMBER(Marks!$B$26:$AK$26)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*ISNUMBER(Marks!$B$26:$AJ$26))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*(Marks!$B$26:$AJ$26=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*ISNUMBER(Marks!$B$26:$AJ$26)))</f>
         <v/>
       </c>
       <c r="J26" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=J$3)*ISNUMBER(Marks!$B$26:$AK$26))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=J$3)*(Marks!$B$26:$AK$26=1))/SUMPRODUCT((Marks!$B$2:$AK$2=J$3)*ISNUMBER(Marks!$B$26:$AK$26)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*ISNUMBER(Marks!$B$26:$AJ$26))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*(Marks!$B$26:$AJ$26=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*ISNUMBER(Marks!$B$26:$AJ$26)))</f>
         <v/>
       </c>
       <c r="K26" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=K$3)*ISNUMBER(Marks!$B$26:$AK$26))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=K$3)*(Marks!$B$26:$AK$26=1))/SUMPRODUCT((Marks!$B$2:$AK$2=K$3)*ISNUMBER(Marks!$B$26:$AK$26)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*ISNUMBER(Marks!$B$26:$AJ$26))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*(Marks!$B$26:$AJ$26=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*ISNUMBER(Marks!$B$26:$AJ$26)))</f>
         <v/>
       </c>
       <c r="L26" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=L$3)*ISNUMBER(Marks!$B$26:$AK$26))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=L$3)*(Marks!$B$26:$AK$26=1))/SUMPRODUCT((Marks!$B$2:$AK$2=L$3)*ISNUMBER(Marks!$B$26:$AK$26)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*ISNUMBER(Marks!$B$26:$AJ$26))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*(Marks!$B$26:$AJ$26=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*ISNUMBER(Marks!$B$26:$AJ$26)))</f>
         <v/>
       </c>
     </row>
@@ -7885,23 +7752,23 @@
       <c r="E27" s="5" t="n"/>
       <c r="F27" s="5" t="n"/>
       <c r="H27" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=H$3)*ISNUMBER(Marks!$B$27:$AK$27))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=H$3)*(Marks!$B$27:$AK$27=1))/SUMPRODUCT((Marks!$B$2:$AK$2=H$3)*ISNUMBER(Marks!$B$27:$AK$27)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=H$3)*ISNUMBER(Marks!$B$27:$AJ$27))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=H$3)*(Marks!$B$27:$AJ$27=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=H$3)*ISNUMBER(Marks!$B$27:$AJ$27)))</f>
         <v/>
       </c>
       <c r="I27" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=I$3)*ISNUMBER(Marks!$B$27:$AK$27))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=I$3)*(Marks!$B$27:$AK$27=1))/SUMPRODUCT((Marks!$B$2:$AK$2=I$3)*ISNUMBER(Marks!$B$27:$AK$27)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*ISNUMBER(Marks!$B$27:$AJ$27))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*(Marks!$B$27:$AJ$27=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*ISNUMBER(Marks!$B$27:$AJ$27)))</f>
         <v/>
       </c>
       <c r="J27" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=J$3)*ISNUMBER(Marks!$B$27:$AK$27))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=J$3)*(Marks!$B$27:$AK$27=1))/SUMPRODUCT((Marks!$B$2:$AK$2=J$3)*ISNUMBER(Marks!$B$27:$AK$27)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*ISNUMBER(Marks!$B$27:$AJ$27))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*(Marks!$B$27:$AJ$27=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*ISNUMBER(Marks!$B$27:$AJ$27)))</f>
         <v/>
       </c>
       <c r="K27" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=K$3)*ISNUMBER(Marks!$B$27:$AK$27))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=K$3)*(Marks!$B$27:$AK$27=1))/SUMPRODUCT((Marks!$B$2:$AK$2=K$3)*ISNUMBER(Marks!$B$27:$AK$27)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*ISNUMBER(Marks!$B$27:$AJ$27))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*(Marks!$B$27:$AJ$27=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*ISNUMBER(Marks!$B$27:$AJ$27)))</f>
         <v/>
       </c>
       <c r="L27" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=L$3)*ISNUMBER(Marks!$B$27:$AK$27))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=L$3)*(Marks!$B$27:$AK$27=1))/SUMPRODUCT((Marks!$B$2:$AK$2=L$3)*ISNUMBER(Marks!$B$27:$AK$27)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*ISNUMBER(Marks!$B$27:$AJ$27))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*(Marks!$B$27:$AJ$27=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*ISNUMBER(Marks!$B$27:$AJ$27)))</f>
         <v/>
       </c>
     </row>
@@ -7915,23 +7782,23 @@
       <c r="E28" s="5" t="n"/>
       <c r="F28" s="5" t="n"/>
       <c r="H28" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=H$3)*ISNUMBER(Marks!$B$28:$AK$28))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=H$3)*(Marks!$B$28:$AK$28=1))/SUMPRODUCT((Marks!$B$2:$AK$2=H$3)*ISNUMBER(Marks!$B$28:$AK$28)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=H$3)*ISNUMBER(Marks!$B$28:$AJ$28))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=H$3)*(Marks!$B$28:$AJ$28=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=H$3)*ISNUMBER(Marks!$B$28:$AJ$28)))</f>
         <v/>
       </c>
       <c r="I28" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=I$3)*ISNUMBER(Marks!$B$28:$AK$28))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=I$3)*(Marks!$B$28:$AK$28=1))/SUMPRODUCT((Marks!$B$2:$AK$2=I$3)*ISNUMBER(Marks!$B$28:$AK$28)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*ISNUMBER(Marks!$B$28:$AJ$28))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*(Marks!$B$28:$AJ$28=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*ISNUMBER(Marks!$B$28:$AJ$28)))</f>
         <v/>
       </c>
       <c r="J28" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=J$3)*ISNUMBER(Marks!$B$28:$AK$28))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=J$3)*(Marks!$B$28:$AK$28=1))/SUMPRODUCT((Marks!$B$2:$AK$2=J$3)*ISNUMBER(Marks!$B$28:$AK$28)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*ISNUMBER(Marks!$B$28:$AJ$28))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*(Marks!$B$28:$AJ$28=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*ISNUMBER(Marks!$B$28:$AJ$28)))</f>
         <v/>
       </c>
       <c r="K28" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=K$3)*ISNUMBER(Marks!$B$28:$AK$28))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=K$3)*(Marks!$B$28:$AK$28=1))/SUMPRODUCT((Marks!$B$2:$AK$2=K$3)*ISNUMBER(Marks!$B$28:$AK$28)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*ISNUMBER(Marks!$B$28:$AJ$28))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*(Marks!$B$28:$AJ$28=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*ISNUMBER(Marks!$B$28:$AJ$28)))</f>
         <v/>
       </c>
       <c r="L28" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=L$3)*ISNUMBER(Marks!$B$28:$AK$28))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=L$3)*(Marks!$B$28:$AK$28=1))/SUMPRODUCT((Marks!$B$2:$AK$2=L$3)*ISNUMBER(Marks!$B$28:$AK$28)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*ISNUMBER(Marks!$B$28:$AJ$28))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*(Marks!$B$28:$AJ$28=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*ISNUMBER(Marks!$B$28:$AJ$28)))</f>
         <v/>
       </c>
     </row>
@@ -7945,23 +7812,23 @@
       <c r="E29" s="5" t="n"/>
       <c r="F29" s="5" t="n"/>
       <c r="H29" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=H$3)*ISNUMBER(Marks!$B$29:$AK$29))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=H$3)*(Marks!$B$29:$AK$29=1))/SUMPRODUCT((Marks!$B$2:$AK$2=H$3)*ISNUMBER(Marks!$B$29:$AK$29)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=H$3)*ISNUMBER(Marks!$B$29:$AJ$29))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=H$3)*(Marks!$B$29:$AJ$29=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=H$3)*ISNUMBER(Marks!$B$29:$AJ$29)))</f>
         <v/>
       </c>
       <c r="I29" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=I$3)*ISNUMBER(Marks!$B$29:$AK$29))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=I$3)*(Marks!$B$29:$AK$29=1))/SUMPRODUCT((Marks!$B$2:$AK$2=I$3)*ISNUMBER(Marks!$B$29:$AK$29)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*ISNUMBER(Marks!$B$29:$AJ$29))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*(Marks!$B$29:$AJ$29=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*ISNUMBER(Marks!$B$29:$AJ$29)))</f>
         <v/>
       </c>
       <c r="J29" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=J$3)*ISNUMBER(Marks!$B$29:$AK$29))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=J$3)*(Marks!$B$29:$AK$29=1))/SUMPRODUCT((Marks!$B$2:$AK$2=J$3)*ISNUMBER(Marks!$B$29:$AK$29)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*ISNUMBER(Marks!$B$29:$AJ$29))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*(Marks!$B$29:$AJ$29=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*ISNUMBER(Marks!$B$29:$AJ$29)))</f>
         <v/>
       </c>
       <c r="K29" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=K$3)*ISNUMBER(Marks!$B$29:$AK$29))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=K$3)*(Marks!$B$29:$AK$29=1))/SUMPRODUCT((Marks!$B$2:$AK$2=K$3)*ISNUMBER(Marks!$B$29:$AK$29)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*ISNUMBER(Marks!$B$29:$AJ$29))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*(Marks!$B$29:$AJ$29=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*ISNUMBER(Marks!$B$29:$AJ$29)))</f>
         <v/>
       </c>
       <c r="L29" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=L$3)*ISNUMBER(Marks!$B$29:$AK$29))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=L$3)*(Marks!$B$29:$AK$29=1))/SUMPRODUCT((Marks!$B$2:$AK$2=L$3)*ISNUMBER(Marks!$B$29:$AK$29)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*ISNUMBER(Marks!$B$29:$AJ$29))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*(Marks!$B$29:$AJ$29=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*ISNUMBER(Marks!$B$29:$AJ$29)))</f>
         <v/>
       </c>
     </row>
@@ -7975,23 +7842,23 @@
       <c r="E30" s="5" t="n"/>
       <c r="F30" s="5" t="n"/>
       <c r="H30" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=H$3)*ISNUMBER(Marks!$B$30:$AK$30))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=H$3)*(Marks!$B$30:$AK$30=1))/SUMPRODUCT((Marks!$B$2:$AK$2=H$3)*ISNUMBER(Marks!$B$30:$AK$30)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=H$3)*ISNUMBER(Marks!$B$30:$AJ$30))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=H$3)*(Marks!$B$30:$AJ$30=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=H$3)*ISNUMBER(Marks!$B$30:$AJ$30)))</f>
         <v/>
       </c>
       <c r="I30" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=I$3)*ISNUMBER(Marks!$B$30:$AK$30))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=I$3)*(Marks!$B$30:$AK$30=1))/SUMPRODUCT((Marks!$B$2:$AK$2=I$3)*ISNUMBER(Marks!$B$30:$AK$30)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*ISNUMBER(Marks!$B$30:$AJ$30))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*(Marks!$B$30:$AJ$30=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*ISNUMBER(Marks!$B$30:$AJ$30)))</f>
         <v/>
       </c>
       <c r="J30" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=J$3)*ISNUMBER(Marks!$B$30:$AK$30))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=J$3)*(Marks!$B$30:$AK$30=1))/SUMPRODUCT((Marks!$B$2:$AK$2=J$3)*ISNUMBER(Marks!$B$30:$AK$30)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*ISNUMBER(Marks!$B$30:$AJ$30))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*(Marks!$B$30:$AJ$30=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*ISNUMBER(Marks!$B$30:$AJ$30)))</f>
         <v/>
       </c>
       <c r="K30" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=K$3)*ISNUMBER(Marks!$B$30:$AK$30))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=K$3)*(Marks!$B$30:$AK$30=1))/SUMPRODUCT((Marks!$B$2:$AK$2=K$3)*ISNUMBER(Marks!$B$30:$AK$30)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*ISNUMBER(Marks!$B$30:$AJ$30))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*(Marks!$B$30:$AJ$30=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*ISNUMBER(Marks!$B$30:$AJ$30)))</f>
         <v/>
       </c>
       <c r="L30" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=L$3)*ISNUMBER(Marks!$B$30:$AK$30))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=L$3)*(Marks!$B$30:$AK$30=1))/SUMPRODUCT((Marks!$B$2:$AK$2=L$3)*ISNUMBER(Marks!$B$30:$AK$30)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*ISNUMBER(Marks!$B$30:$AJ$30))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*(Marks!$B$30:$AJ$30=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*ISNUMBER(Marks!$B$30:$AJ$30)))</f>
         <v/>
       </c>
     </row>
@@ -8005,23 +7872,23 @@
       <c r="E31" s="5" t="n"/>
       <c r="F31" s="5" t="n"/>
       <c r="H31" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=H$3)*ISNUMBER(Marks!$B$31:$AK$31))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=H$3)*(Marks!$B$31:$AK$31=1))/SUMPRODUCT((Marks!$B$2:$AK$2=H$3)*ISNUMBER(Marks!$B$31:$AK$31)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=H$3)*ISNUMBER(Marks!$B$31:$AJ$31))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=H$3)*(Marks!$B$31:$AJ$31=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=H$3)*ISNUMBER(Marks!$B$31:$AJ$31)))</f>
         <v/>
       </c>
       <c r="I31" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=I$3)*ISNUMBER(Marks!$B$31:$AK$31))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=I$3)*(Marks!$B$31:$AK$31=1))/SUMPRODUCT((Marks!$B$2:$AK$2=I$3)*ISNUMBER(Marks!$B$31:$AK$31)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*ISNUMBER(Marks!$B$31:$AJ$31))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*(Marks!$B$31:$AJ$31=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*ISNUMBER(Marks!$B$31:$AJ$31)))</f>
         <v/>
       </c>
       <c r="J31" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=J$3)*ISNUMBER(Marks!$B$31:$AK$31))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=J$3)*(Marks!$B$31:$AK$31=1))/SUMPRODUCT((Marks!$B$2:$AK$2=J$3)*ISNUMBER(Marks!$B$31:$AK$31)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*ISNUMBER(Marks!$B$31:$AJ$31))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*(Marks!$B$31:$AJ$31=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*ISNUMBER(Marks!$B$31:$AJ$31)))</f>
         <v/>
       </c>
       <c r="K31" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=K$3)*ISNUMBER(Marks!$B$31:$AK$31))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=K$3)*(Marks!$B$31:$AK$31=1))/SUMPRODUCT((Marks!$B$2:$AK$2=K$3)*ISNUMBER(Marks!$B$31:$AK$31)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*ISNUMBER(Marks!$B$31:$AJ$31))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*(Marks!$B$31:$AJ$31=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*ISNUMBER(Marks!$B$31:$AJ$31)))</f>
         <v/>
       </c>
       <c r="L31" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=L$3)*ISNUMBER(Marks!$B$31:$AK$31))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=L$3)*(Marks!$B$31:$AK$31=1))/SUMPRODUCT((Marks!$B$2:$AK$2=L$3)*ISNUMBER(Marks!$B$31:$AK$31)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*ISNUMBER(Marks!$B$31:$AJ$31))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*(Marks!$B$31:$AJ$31=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*ISNUMBER(Marks!$B$31:$AJ$31)))</f>
         <v/>
       </c>
     </row>
@@ -8035,23 +7902,23 @@
       <c r="E32" s="5" t="n"/>
       <c r="F32" s="5" t="n"/>
       <c r="H32" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=H$3)*ISNUMBER(Marks!$B$32:$AK$32))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=H$3)*(Marks!$B$32:$AK$32=1))/SUMPRODUCT((Marks!$B$2:$AK$2=H$3)*ISNUMBER(Marks!$B$32:$AK$32)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=H$3)*ISNUMBER(Marks!$B$32:$AJ$32))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=H$3)*(Marks!$B$32:$AJ$32=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=H$3)*ISNUMBER(Marks!$B$32:$AJ$32)))</f>
         <v/>
       </c>
       <c r="I32" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=I$3)*ISNUMBER(Marks!$B$32:$AK$32))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=I$3)*(Marks!$B$32:$AK$32=1))/SUMPRODUCT((Marks!$B$2:$AK$2=I$3)*ISNUMBER(Marks!$B$32:$AK$32)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*ISNUMBER(Marks!$B$32:$AJ$32))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*(Marks!$B$32:$AJ$32=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*ISNUMBER(Marks!$B$32:$AJ$32)))</f>
         <v/>
       </c>
       <c r="J32" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=J$3)*ISNUMBER(Marks!$B$32:$AK$32))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=J$3)*(Marks!$B$32:$AK$32=1))/SUMPRODUCT((Marks!$B$2:$AK$2=J$3)*ISNUMBER(Marks!$B$32:$AK$32)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*ISNUMBER(Marks!$B$32:$AJ$32))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*(Marks!$B$32:$AJ$32=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*ISNUMBER(Marks!$B$32:$AJ$32)))</f>
         <v/>
       </c>
       <c r="K32" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=K$3)*ISNUMBER(Marks!$B$32:$AK$32))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=K$3)*(Marks!$B$32:$AK$32=1))/SUMPRODUCT((Marks!$B$2:$AK$2=K$3)*ISNUMBER(Marks!$B$32:$AK$32)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*ISNUMBER(Marks!$B$32:$AJ$32))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*(Marks!$B$32:$AJ$32=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*ISNUMBER(Marks!$B$32:$AJ$32)))</f>
         <v/>
       </c>
       <c r="L32" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=L$3)*ISNUMBER(Marks!$B$32:$AK$32))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=L$3)*(Marks!$B$32:$AK$32=1))/SUMPRODUCT((Marks!$B$2:$AK$2=L$3)*ISNUMBER(Marks!$B$32:$AK$32)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*ISNUMBER(Marks!$B$32:$AJ$32))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*(Marks!$B$32:$AJ$32=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*ISNUMBER(Marks!$B$32:$AJ$32)))</f>
         <v/>
       </c>
     </row>
@@ -8065,23 +7932,23 @@
       <c r="E33" s="5" t="n"/>
       <c r="F33" s="5" t="n"/>
       <c r="H33" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=H$3)*ISNUMBER(Marks!$B$33:$AK$33))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=H$3)*(Marks!$B$33:$AK$33=1))/SUMPRODUCT((Marks!$B$2:$AK$2=H$3)*ISNUMBER(Marks!$B$33:$AK$33)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=H$3)*ISNUMBER(Marks!$B$33:$AJ$33))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=H$3)*(Marks!$B$33:$AJ$33=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=H$3)*ISNUMBER(Marks!$B$33:$AJ$33)))</f>
         <v/>
       </c>
       <c r="I33" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=I$3)*ISNUMBER(Marks!$B$33:$AK$33))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=I$3)*(Marks!$B$33:$AK$33=1))/SUMPRODUCT((Marks!$B$2:$AK$2=I$3)*ISNUMBER(Marks!$B$33:$AK$33)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*ISNUMBER(Marks!$B$33:$AJ$33))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*(Marks!$B$33:$AJ$33=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*ISNUMBER(Marks!$B$33:$AJ$33)))</f>
         <v/>
       </c>
       <c r="J33" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=J$3)*ISNUMBER(Marks!$B$33:$AK$33))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=J$3)*(Marks!$B$33:$AK$33=1))/SUMPRODUCT((Marks!$B$2:$AK$2=J$3)*ISNUMBER(Marks!$B$33:$AK$33)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*ISNUMBER(Marks!$B$33:$AJ$33))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*(Marks!$B$33:$AJ$33=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*ISNUMBER(Marks!$B$33:$AJ$33)))</f>
         <v/>
       </c>
       <c r="K33" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=K$3)*ISNUMBER(Marks!$B$33:$AK$33))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=K$3)*(Marks!$B$33:$AK$33=1))/SUMPRODUCT((Marks!$B$2:$AK$2=K$3)*ISNUMBER(Marks!$B$33:$AK$33)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*ISNUMBER(Marks!$B$33:$AJ$33))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*(Marks!$B$33:$AJ$33=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*ISNUMBER(Marks!$B$33:$AJ$33)))</f>
         <v/>
       </c>
       <c r="L33" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=L$3)*ISNUMBER(Marks!$B$33:$AK$33))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=L$3)*(Marks!$B$33:$AK$33=1))/SUMPRODUCT((Marks!$B$2:$AK$2=L$3)*ISNUMBER(Marks!$B$33:$AK$33)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*ISNUMBER(Marks!$B$33:$AJ$33))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*(Marks!$B$33:$AJ$33=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*ISNUMBER(Marks!$B$33:$AJ$33)))</f>
         <v/>
       </c>
     </row>
@@ -8095,23 +7962,23 @@
       <c r="E34" s="5" t="n"/>
       <c r="F34" s="5" t="n"/>
       <c r="H34" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=H$3)*ISNUMBER(Marks!$B$34:$AK$34))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=H$3)*(Marks!$B$34:$AK$34=1))/SUMPRODUCT((Marks!$B$2:$AK$2=H$3)*ISNUMBER(Marks!$B$34:$AK$34)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=H$3)*ISNUMBER(Marks!$B$34:$AJ$34))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=H$3)*(Marks!$B$34:$AJ$34=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=H$3)*ISNUMBER(Marks!$B$34:$AJ$34)))</f>
         <v/>
       </c>
       <c r="I34" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=I$3)*ISNUMBER(Marks!$B$34:$AK$34))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=I$3)*(Marks!$B$34:$AK$34=1))/SUMPRODUCT((Marks!$B$2:$AK$2=I$3)*ISNUMBER(Marks!$B$34:$AK$34)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*ISNUMBER(Marks!$B$34:$AJ$34))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*(Marks!$B$34:$AJ$34=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*ISNUMBER(Marks!$B$34:$AJ$34)))</f>
         <v/>
       </c>
       <c r="J34" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=J$3)*ISNUMBER(Marks!$B$34:$AK$34))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=J$3)*(Marks!$B$34:$AK$34=1))/SUMPRODUCT((Marks!$B$2:$AK$2=J$3)*ISNUMBER(Marks!$B$34:$AK$34)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*ISNUMBER(Marks!$B$34:$AJ$34))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*(Marks!$B$34:$AJ$34=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*ISNUMBER(Marks!$B$34:$AJ$34)))</f>
         <v/>
       </c>
       <c r="K34" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=K$3)*ISNUMBER(Marks!$B$34:$AK$34))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=K$3)*(Marks!$B$34:$AK$34=1))/SUMPRODUCT((Marks!$B$2:$AK$2=K$3)*ISNUMBER(Marks!$B$34:$AK$34)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*ISNUMBER(Marks!$B$34:$AJ$34))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*(Marks!$B$34:$AJ$34=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*ISNUMBER(Marks!$B$34:$AJ$34)))</f>
         <v/>
       </c>
       <c r="L34" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=L$3)*ISNUMBER(Marks!$B$34:$AK$34))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=L$3)*(Marks!$B$34:$AK$34=1))/SUMPRODUCT((Marks!$B$2:$AK$2=L$3)*ISNUMBER(Marks!$B$34:$AK$34)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*ISNUMBER(Marks!$B$34:$AJ$34))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*(Marks!$B$34:$AJ$34=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*ISNUMBER(Marks!$B$34:$AJ$34)))</f>
         <v/>
       </c>
     </row>
@@ -8125,23 +7992,23 @@
       <c r="E35" s="5" t="n"/>
       <c r="F35" s="5" t="n"/>
       <c r="H35" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=H$3)*ISNUMBER(Marks!$B$35:$AK$35))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=H$3)*(Marks!$B$35:$AK$35=1))/SUMPRODUCT((Marks!$B$2:$AK$2=H$3)*ISNUMBER(Marks!$B$35:$AK$35)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=H$3)*ISNUMBER(Marks!$B$35:$AJ$35))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=H$3)*(Marks!$B$35:$AJ$35=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=H$3)*ISNUMBER(Marks!$B$35:$AJ$35)))</f>
         <v/>
       </c>
       <c r="I35" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=I$3)*ISNUMBER(Marks!$B$35:$AK$35))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=I$3)*(Marks!$B$35:$AK$35=1))/SUMPRODUCT((Marks!$B$2:$AK$2=I$3)*ISNUMBER(Marks!$B$35:$AK$35)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*ISNUMBER(Marks!$B$35:$AJ$35))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*(Marks!$B$35:$AJ$35=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*ISNUMBER(Marks!$B$35:$AJ$35)))</f>
         <v/>
       </c>
       <c r="J35" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=J$3)*ISNUMBER(Marks!$B$35:$AK$35))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=J$3)*(Marks!$B$35:$AK$35=1))/SUMPRODUCT((Marks!$B$2:$AK$2=J$3)*ISNUMBER(Marks!$B$35:$AK$35)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*ISNUMBER(Marks!$B$35:$AJ$35))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*(Marks!$B$35:$AJ$35=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*ISNUMBER(Marks!$B$35:$AJ$35)))</f>
         <v/>
       </c>
       <c r="K35" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=K$3)*ISNUMBER(Marks!$B$35:$AK$35))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=K$3)*(Marks!$B$35:$AK$35=1))/SUMPRODUCT((Marks!$B$2:$AK$2=K$3)*ISNUMBER(Marks!$B$35:$AK$35)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*ISNUMBER(Marks!$B$35:$AJ$35))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*(Marks!$B$35:$AJ$35=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*ISNUMBER(Marks!$B$35:$AJ$35)))</f>
         <v/>
       </c>
       <c r="L35" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=L$3)*ISNUMBER(Marks!$B$35:$AK$35))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=L$3)*(Marks!$B$35:$AK$35=1))/SUMPRODUCT((Marks!$B$2:$AK$2=L$3)*ISNUMBER(Marks!$B$35:$AK$35)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*ISNUMBER(Marks!$B$35:$AJ$35))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*(Marks!$B$35:$AJ$35=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*ISNUMBER(Marks!$B$35:$AJ$35)))</f>
         <v/>
       </c>
     </row>
@@ -8155,23 +8022,23 @@
       <c r="E36" s="5" t="n"/>
       <c r="F36" s="5" t="n"/>
       <c r="H36" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=H$3)*ISNUMBER(Marks!$B$36:$AK$36))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=H$3)*(Marks!$B$36:$AK$36=1))/SUMPRODUCT((Marks!$B$2:$AK$2=H$3)*ISNUMBER(Marks!$B$36:$AK$36)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=H$3)*ISNUMBER(Marks!$B$36:$AJ$36))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=H$3)*(Marks!$B$36:$AJ$36=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=H$3)*ISNUMBER(Marks!$B$36:$AJ$36)))</f>
         <v/>
       </c>
       <c r="I36" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=I$3)*ISNUMBER(Marks!$B$36:$AK$36))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=I$3)*(Marks!$B$36:$AK$36=1))/SUMPRODUCT((Marks!$B$2:$AK$2=I$3)*ISNUMBER(Marks!$B$36:$AK$36)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*ISNUMBER(Marks!$B$36:$AJ$36))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*(Marks!$B$36:$AJ$36=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*ISNUMBER(Marks!$B$36:$AJ$36)))</f>
         <v/>
       </c>
       <c r="J36" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=J$3)*ISNUMBER(Marks!$B$36:$AK$36))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=J$3)*(Marks!$B$36:$AK$36=1))/SUMPRODUCT((Marks!$B$2:$AK$2=J$3)*ISNUMBER(Marks!$B$36:$AK$36)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*ISNUMBER(Marks!$B$36:$AJ$36))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*(Marks!$B$36:$AJ$36=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*ISNUMBER(Marks!$B$36:$AJ$36)))</f>
         <v/>
       </c>
       <c r="K36" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=K$3)*ISNUMBER(Marks!$B$36:$AK$36))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=K$3)*(Marks!$B$36:$AK$36=1))/SUMPRODUCT((Marks!$B$2:$AK$2=K$3)*ISNUMBER(Marks!$B$36:$AK$36)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*ISNUMBER(Marks!$B$36:$AJ$36))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*(Marks!$B$36:$AJ$36=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*ISNUMBER(Marks!$B$36:$AJ$36)))</f>
         <v/>
       </c>
       <c r="L36" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=L$3)*ISNUMBER(Marks!$B$36:$AK$36))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=L$3)*(Marks!$B$36:$AK$36=1))/SUMPRODUCT((Marks!$B$2:$AK$2=L$3)*ISNUMBER(Marks!$B$36:$AK$36)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*ISNUMBER(Marks!$B$36:$AJ$36))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*(Marks!$B$36:$AJ$36=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*ISNUMBER(Marks!$B$36:$AJ$36)))</f>
         <v/>
       </c>
     </row>
@@ -8185,23 +8052,23 @@
       <c r="E37" s="5" t="n"/>
       <c r="F37" s="5" t="n"/>
       <c r="H37" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=H$3)*ISNUMBER(Marks!$B$37:$AK$37))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=H$3)*(Marks!$B$37:$AK$37=1))/SUMPRODUCT((Marks!$B$2:$AK$2=H$3)*ISNUMBER(Marks!$B$37:$AK$37)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=H$3)*ISNUMBER(Marks!$B$37:$AJ$37))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=H$3)*(Marks!$B$37:$AJ$37=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=H$3)*ISNUMBER(Marks!$B$37:$AJ$37)))</f>
         <v/>
       </c>
       <c r="I37" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=I$3)*ISNUMBER(Marks!$B$37:$AK$37))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=I$3)*(Marks!$B$37:$AK$37=1))/SUMPRODUCT((Marks!$B$2:$AK$2=I$3)*ISNUMBER(Marks!$B$37:$AK$37)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*ISNUMBER(Marks!$B$37:$AJ$37))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*(Marks!$B$37:$AJ$37=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*ISNUMBER(Marks!$B$37:$AJ$37)))</f>
         <v/>
       </c>
       <c r="J37" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=J$3)*ISNUMBER(Marks!$B$37:$AK$37))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=J$3)*(Marks!$B$37:$AK$37=1))/SUMPRODUCT((Marks!$B$2:$AK$2=J$3)*ISNUMBER(Marks!$B$37:$AK$37)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*ISNUMBER(Marks!$B$37:$AJ$37))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*(Marks!$B$37:$AJ$37=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*ISNUMBER(Marks!$B$37:$AJ$37)))</f>
         <v/>
       </c>
       <c r="K37" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=K$3)*ISNUMBER(Marks!$B$37:$AK$37))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=K$3)*(Marks!$B$37:$AK$37=1))/SUMPRODUCT((Marks!$B$2:$AK$2=K$3)*ISNUMBER(Marks!$B$37:$AK$37)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*ISNUMBER(Marks!$B$37:$AJ$37))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*(Marks!$B$37:$AJ$37=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*ISNUMBER(Marks!$B$37:$AJ$37)))</f>
         <v/>
       </c>
       <c r="L37" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=L$3)*ISNUMBER(Marks!$B$37:$AK$37))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=L$3)*(Marks!$B$37:$AK$37=1))/SUMPRODUCT((Marks!$B$2:$AK$2=L$3)*ISNUMBER(Marks!$B$37:$AK$37)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*ISNUMBER(Marks!$B$37:$AJ$37))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*(Marks!$B$37:$AJ$37=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*ISNUMBER(Marks!$B$37:$AJ$37)))</f>
         <v/>
       </c>
     </row>
@@ -8215,23 +8082,23 @@
       <c r="E38" s="5" t="n"/>
       <c r="F38" s="5" t="n"/>
       <c r="H38" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=H$3)*ISNUMBER(Marks!$B$38:$AK$38))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=H$3)*(Marks!$B$38:$AK$38=1))/SUMPRODUCT((Marks!$B$2:$AK$2=H$3)*ISNUMBER(Marks!$B$38:$AK$38)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=H$3)*ISNUMBER(Marks!$B$38:$AJ$38))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=H$3)*(Marks!$B$38:$AJ$38=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=H$3)*ISNUMBER(Marks!$B$38:$AJ$38)))</f>
         <v/>
       </c>
       <c r="I38" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=I$3)*ISNUMBER(Marks!$B$38:$AK$38))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=I$3)*(Marks!$B$38:$AK$38=1))/SUMPRODUCT((Marks!$B$2:$AK$2=I$3)*ISNUMBER(Marks!$B$38:$AK$38)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*ISNUMBER(Marks!$B$38:$AJ$38))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*(Marks!$B$38:$AJ$38=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*ISNUMBER(Marks!$B$38:$AJ$38)))</f>
         <v/>
       </c>
       <c r="J38" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=J$3)*ISNUMBER(Marks!$B$38:$AK$38))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=J$3)*(Marks!$B$38:$AK$38=1))/SUMPRODUCT((Marks!$B$2:$AK$2=J$3)*ISNUMBER(Marks!$B$38:$AK$38)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*ISNUMBER(Marks!$B$38:$AJ$38))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*(Marks!$B$38:$AJ$38=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*ISNUMBER(Marks!$B$38:$AJ$38)))</f>
         <v/>
       </c>
       <c r="K38" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=K$3)*ISNUMBER(Marks!$B$38:$AK$38))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=K$3)*(Marks!$B$38:$AK$38=1))/SUMPRODUCT((Marks!$B$2:$AK$2=K$3)*ISNUMBER(Marks!$B$38:$AK$38)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*ISNUMBER(Marks!$B$38:$AJ$38))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*(Marks!$B$38:$AJ$38=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*ISNUMBER(Marks!$B$38:$AJ$38)))</f>
         <v/>
       </c>
       <c r="L38" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=L$3)*ISNUMBER(Marks!$B$38:$AK$38))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=L$3)*(Marks!$B$38:$AK$38=1))/SUMPRODUCT((Marks!$B$2:$AK$2=L$3)*ISNUMBER(Marks!$B$38:$AK$38)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*ISNUMBER(Marks!$B$38:$AJ$38))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*(Marks!$B$38:$AJ$38=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*ISNUMBER(Marks!$B$38:$AJ$38)))</f>
         <v/>
       </c>
     </row>
@@ -8245,23 +8112,23 @@
       <c r="E39" s="5" t="n"/>
       <c r="F39" s="5" t="n"/>
       <c r="H39" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=H$3)*ISNUMBER(Marks!$B$39:$AK$39))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=H$3)*(Marks!$B$39:$AK$39=1))/SUMPRODUCT((Marks!$B$2:$AK$2=H$3)*ISNUMBER(Marks!$B$39:$AK$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=H$3)*ISNUMBER(Marks!$B$39:$AJ$39))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=H$3)*(Marks!$B$39:$AJ$39=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=H$3)*ISNUMBER(Marks!$B$39:$AJ$39)))</f>
         <v/>
       </c>
       <c r="I39" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=I$3)*ISNUMBER(Marks!$B$39:$AK$39))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=I$3)*(Marks!$B$39:$AK$39=1))/SUMPRODUCT((Marks!$B$2:$AK$2=I$3)*ISNUMBER(Marks!$B$39:$AK$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*ISNUMBER(Marks!$B$39:$AJ$39))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*(Marks!$B$39:$AJ$39=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=I$3)*ISNUMBER(Marks!$B$39:$AJ$39)))</f>
         <v/>
       </c>
       <c r="J39" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=J$3)*ISNUMBER(Marks!$B$39:$AK$39))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=J$3)*(Marks!$B$39:$AK$39=1))/SUMPRODUCT((Marks!$B$2:$AK$2=J$3)*ISNUMBER(Marks!$B$39:$AK$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*ISNUMBER(Marks!$B$39:$AJ$39))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*(Marks!$B$39:$AJ$39=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=J$3)*ISNUMBER(Marks!$B$39:$AJ$39)))</f>
         <v/>
       </c>
       <c r="K39" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=K$3)*ISNUMBER(Marks!$B$39:$AK$39))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=K$3)*(Marks!$B$39:$AK$39=1))/SUMPRODUCT((Marks!$B$2:$AK$2=K$3)*ISNUMBER(Marks!$B$39:$AK$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*ISNUMBER(Marks!$B$39:$AJ$39))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*(Marks!$B$39:$AJ$39=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=K$3)*ISNUMBER(Marks!$B$39:$AJ$39)))</f>
         <v/>
       </c>
       <c r="L39" s="6">
-        <f>IF(SUMPRODUCT((Marks!$B$2:$AK$2=L$3)*ISNUMBER(Marks!$B$39:$AK$39))=0,"",SUMPRODUCT((Marks!$B$2:$AK$2=L$3)*(Marks!$B$39:$AK$39=1))/SUMPRODUCT((Marks!$B$2:$AK$2=L$3)*ISNUMBER(Marks!$B$39:$AK$39)))</f>
+        <f>IF(SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*ISNUMBER(Marks!$B$39:$AJ$39))=0,"",SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*(Marks!$B$39:$AJ$39=1))/SUMPRODUCT((Marks!$B$2:$AJ$2=L$3)*ISNUMBER(Marks!$B$39:$AJ$39)))</f>
         <v/>
       </c>
     </row>
@@ -8335,7 +8202,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Part 3. Real, worth it, and caused</t>
+          <t>Part 3. Real, or the wobble</t>
         </is>
       </c>
       <c r="B45" s="7">
@@ -8373,7 +8240,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Part 5. The agent's bill and its logs</t>
+          <t>Part 5. An offer, an agent and its logs</t>
         </is>
       </c>
       <c r="B47" s="7">

--- a/content/W01/SAT/answer-key/C2_W01_SAT_item_analysis_TRAINER.xlsx
+++ b/content/W01/SAT/answer-key/C2_W01_SAT_item_analysis_TRAINER.xlsx
@@ -586,7 +586,7 @@
         <v>3</v>
       </c>
       <c r="V2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="W2" t="n">
         <v>4</v>
@@ -704,52 +704,52 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
+          <t>[F]</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
           <t>[S]</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>[S]</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>[S]</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>[S]</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>[S]</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
         <is>
           <t>[F]</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>[F]</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
         <is>
           <t>[S]</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>[S]</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>[S]</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
+      <c r="X3" t="inlineStr">
         <is>
           <t>[F]</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>[F]</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>[S]</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>[F]</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>[S]</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -2940,7 +2940,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2950,7 +2950,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Median Rs 1,400; mean Rs 97,080.</t>
+          <t>Rs 11 crore (Rs 12 crore before discounts).</t>
         </is>
       </c>
       <c r="G5">
@@ -3010,7 +3010,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>c</t>
         </is>
       </c>
       <c r="G6">
@@ -3120,7 +3120,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Hard</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3475,7 +3475,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>True or false</t>
+          <t>One correct option</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3490,7 +3490,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>c</t>
+          <t>a</t>
         </is>
       </c>
       <c r="G14">
@@ -3610,7 +3610,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rs 10,930.</t>
+          <t>Q1 Rs 4,680 and Q2 Rs 7,410.</t>
         </is>
       </c>
       <c r="G16">
@@ -3655,12 +3655,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Scenario set</t>
+          <t>Order the steps</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Hard</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>A fall of 1.6 percent.</t>
+          <t>b, d, a, c</t>
         </is>
       </c>
       <c r="G17">
@@ -3725,12 +3725,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>[S]</t>
+          <t>[F]</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>A fall of 35.0 percent.</t>
+          <t>A fall of 1.6 percent (down 1.6, or -1.6).</t>
         </is>
       </c>
       <c r="G18">
@@ -3775,22 +3775,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Order the steps</t>
+          <t>Scenario set</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Hard</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>[F]</t>
+          <t>[S]</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>b, d, a, c</t>
+          <t>a</t>
         </is>
       </c>
       <c r="G19">
@@ -3850,7 +3850,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>a</t>
+          <t>c</t>
         </is>
       </c>
       <c r="G20">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>More than one correct</t>
+          <t>True or false</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Hard</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -3910,7 +3910,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>a, c, d</t>
+          <t>a</t>
         </is>
       </c>
       <c r="G21">
@@ -3955,12 +3955,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>One correct option</t>
+          <t>More than one correct</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Hard</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -3970,7 +3970,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>c</t>
+          <t>a, c, d</t>
         </is>
       </c>
       <c r="G22">
@@ -4025,12 +4025,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>[F]</t>
+          <t>[S]</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>d</t>
         </is>
       </c>
       <c r="G23">
@@ -4080,7 +4080,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Hard</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -4090,7 +4090,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>a</t>
+          <t>b</t>
         </is>
       </c>
       <c r="G24">
@@ -4131,11 +4131,11 @@
         <v>21</v>
       </c>
       <c r="B25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Scenario set</t>
+          <t>One correct option</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4145,12 +4145,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>[S]</t>
+          <t>[F]</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>a</t>
+          <t>c</t>
         </is>
       </c>
       <c r="G25">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Hard</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>[F]</t>
+          <t>[S]</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -4255,17 +4255,17 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>True or false</t>
+          <t>Scenario set</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Hard</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>[S]</t>
+          <t>[F]</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -4510,7 +4510,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>A fall of 2.5 percent.</t>
+          <t>A fall of Rs 12,500.</t>
         </is>
       </c>
       <c r="G31">
@@ -4570,7 +4570,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>c</t>
+          <t>b</t>
         </is>
       </c>
       <c r="G32">
@@ -4630,7 +4630,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>c</t>
         </is>
       </c>
       <c r="G33">
@@ -4750,7 +4750,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>d</t>
+          <t>b</t>
         </is>
       </c>
       <c r="G35">

--- a/content/W01/SAT/answer-key/C2_W01_SAT_item_analysis_TRAINER.xlsx
+++ b/content/W01/SAT/answer-key/C2_W01_SAT_item_analysis_TRAINER.xlsx
@@ -6095,7 +6095,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Part 1. Where the revenue went</t>
+          <t>Part 1. Where did Kalpa's revenue go between the first quarter and the second?</t>
         </is>
       </c>
       <c r="C9">
@@ -6113,7 +6113,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Part 2. Which Q1 figure is right</t>
+          <t>Part 2. Did Kalpa book Rs 2.1 crore in the first quarter, or Rs 1.9 crore?</t>
         </is>
       </c>
       <c r="C10">
@@ -6131,7 +6131,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Part 3. Real, or the wobble</t>
+          <t>Part 3. Is the Retail-Plus fall more than chance, and what should Meera's note say?</t>
         </is>
       </c>
       <c r="C11">
@@ -6149,7 +6149,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Part 4. The same traps, in public</t>
+          <t>Part 4. Which check would have caught the misleading number in five public cases?</t>
         </is>
       </c>
       <c r="C12">
@@ -6167,7 +6167,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Part 5. An offer, an agent and its logs</t>
+          <t>Part 5. Did a delivery company's offer raise spending, and are its AI agent's numbers right?</t>
         </is>
       </c>
       <c r="C13">
@@ -8164,7 +8164,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Part 1. Where the revenue went</t>
+          <t>Part 1. Where did Kalpa's revenue go between the first quarter and the second?</t>
         </is>
       </c>
       <c r="B43" s="7">
@@ -8183,7 +8183,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Part 2. Which Q1 figure is right</t>
+          <t>Part 2. Did Kalpa book Rs 2.1 crore in the first quarter, or Rs 1.9 crore?</t>
         </is>
       </c>
       <c r="B44" s="7">
@@ -8202,7 +8202,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Part 3. Real, or the wobble</t>
+          <t>Part 3. Is the Retail-Plus fall more than chance, and what should Meera's note say?</t>
         </is>
       </c>
       <c r="B45" s="7">
@@ -8221,7 +8221,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Part 4. The same traps, in public</t>
+          <t>Part 4. Which check would have caught the misleading number in five public cases?</t>
         </is>
       </c>
       <c r="B46" s="7">
@@ -8240,7 +8240,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Part 5. An offer, an agent and its logs</t>
+          <t>Part 5. Did a delivery company's offer raise spending, and are its AI agent's numbers right?</t>
         </is>
       </c>
       <c r="B47" s="7">

--- a/content/W01/SAT/answer-key/C2_W01_SAT_item_analysis_TRAINER.xlsx
+++ b/content/W01/SAT/answer-key/C2_W01_SAT_item_analysis_TRAINER.xlsx
@@ -3070,7 +3070,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rs 2,060.</t>
+          <t>Rs 2,205.</t>
         </is>
       </c>
       <c r="G7">
@@ -6149,7 +6149,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Part 4. Which check would have caught the misleading number in five public cases?</t>
+          <t>Part 4. What should a team check before it acts on a surprising number, in four public cases?</t>
         </is>
       </c>
       <c r="C12">
@@ -8221,7 +8221,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Part 4. Which check would have caught the misleading number in five public cases?</t>
+          <t>Part 4. What should a team check before it acts on a surprising number, in four public cases?</t>
         </is>
       </c>
       <c r="B46" s="7">
